--- a/dist/VM_Tukipalkkio_Leikkuri_2027.xlsx
+++ b/dist/VM_Tukipalkkio_Leikkuri_2027.xlsx
@@ -134,7 +134,7 @@
       </c>
       <c r="F2" t="inlineStr" s="0">
         <is>
-          <t>Välilehdet 02 &amp; 03: Infinited Fiber (12,4 M€ tuki -&gt; konkurssi), Spinnova (14,8 M€ -&gt; 0 € veroa), Solar Foods (18,2 M€ -&gt; 0 € veroa), Meyer Turku (54 M€)</t>
+          <t>Välilehdet 02 &amp; 03: Infinited Fiber (12,4 M€ tuki -&gt; yt-neuvottelut &amp; 0 € veroa), Spinnova (14,8 M€ -&gt; 0 € veroa), Solar Foods (18,2 M€ -&gt; 0 € veroa), Meyer Turku (54 M€)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr" s="0">
@@ -151,7 +151,7 @@
       </c>
       <c r="B3" t="inlineStr" s="0">
         <is>
-          <t>Laina tutkimus- ja kehittämistoimintaan (Business Finland T&amp;K-pääomalainat)</t>
+          <t>Lainat tutkimus- ja innovaatiotoimintaan (Business Finland T&amp;K-lainat)</t>
         </is>
       </c>
       <c r="C3" s="2">
@@ -177,19 +177,19 @@
     <row r="4">
       <c r="A4" t="inlineStr" s="0">
         <is>
-          <t>32.30.42</t>
+          <t>31.20.43 / 32.30.42</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="0">
         <is>
-          <t>Yritysten kehittämisavustukset sekä kuljetus- ja merenkulkutuet (ELY &amp; Traficom)</t>
+          <t>Varustamoiden miehistötuet (LVM 31.20.43) sekä ELY-kehittämisavustukset (TEM 32.30.42)</t>
         </is>
       </c>
       <c r="C4" s="2">
-        <v>290000000</v>
+        <v>340000000</v>
       </c>
       <c r="D4" s="2">
-        <v>60.0</v>
+        <v>51.2</v>
       </c>
       <c r="E4" s="2">
         <v>174000000</v>
@@ -217,34 +217,34 @@
         </is>
       </c>
       <c r="C5" s="2">
-        <v>380000000</v>
+        <v>410000000</v>
       </c>
       <c r="D5" s="2">
-        <v>55.0</v>
+        <v>51.0</v>
       </c>
       <c r="E5" s="2">
         <v>209000000</v>
       </c>
       <c r="F5" t="inlineStr" s="0">
         <is>
-          <t>Välilehdet 04 &amp; 06: KAIKKI 686 STEA-järjestöä 2026 (273 912 000 €), josta tasan 212 203 929 € (77,5 %) on vapaata Ak-yleisavustusta!</t>
+          <t>Välilehdet 04 &amp; 06: KAIKKI 686 STEA-järjestöä 2026 (273 912 000 € / 1 288 päätöstä), josta 212 203 929 € (77,5 %) on jatkuvaa Ak-toimintatukea!</t>
         </is>
       </c>
       <c r="G5" t="inlineStr" s="0">
         <is>
-          <t>Leikataan Ak-yleisavustusten keskushallintopöhö, tuetut lomajärjestöt (Loma ja Terveys 2,68 M€ + Hyvinvointilomat 2,10 M€) ja sote-tuplalaskuttajat</t>
+          <t>Karsitaan jatkuvien Ak/Ay-avustusten hallintopöhö, tuetut lomajärjestöt (Loma ja Terveys 2,68 M€ + Hyvinvointilomat 2,10 M€) ja sote-päällekkäisyydet</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr" s="0">
         <is>
-          <t>29.80.50</t>
+          <t>29.80.50 / 29.90.50 / 29.91.50</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="0">
         <is>
-          <t>Opetus- ja kulttuuriministeriön yleis- ja järjestöavustukset (OKM / Nuoriso / Liikunta)</t>
+          <t>Opetus- ja kulttuuriministeriön valtakunnalliset katto- ja yleisavustukset (Kulttuuri / Liikunta / Nuoriso)</t>
         </is>
       </c>
       <c r="C6" s="2">
@@ -258,24 +258,24 @@
       </c>
       <c r="F6" t="inlineStr" s="0">
         <is>
-          <t>Välilehti 04: Katto- ja edunvalvontajärjestöjen (esim. Allianssi ry 1,95 M€/v) yleisavustukset ja monikanavarahoituksen tuplaus</t>
+          <t>Välilehti 04: Katto- ja edunvalvontajärjestöjen (esim. Allianssi ry 1,95 M€/v momentilta 29.91.50) yleisavustukset ja monikanavarahoitus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr" s="0">
         <is>
-          <t>Poistetaan poliittisten katto- ja lobbausjärjestöjen yleisavustukset; suojataan paikallinen lasten ja nuorten seuratoiminta</t>
+          <t>Poistetaan valtakunnallisten katto- ja lobbausjärjestöjen yleisavustukset; suojataan paikallinen lasten ja nuorten seuratoiminta</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr" s="0">
         <is>
-          <t>30.10.40_32.60.40</t>
+          <t>32.20.43 / 32.60.40 / 30.20.40</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="0">
         <is>
-          <t>Kansalliset maa-, teollisuus- ja energiatuet (Sähköistämistuki &amp; energiaveronpalautukset)</t>
+          <t>Suurteollisuuden sähköistämistuki, energiatuet ja kansalliset säilytystuet</t>
         </is>
       </c>
       <c r="C7" s="2">
@@ -426,7 +426,7 @@
       </c>
       <c r="B2" t="inlineStr" s="0">
         <is>
-          <t>Infinited Fiber Company Oy (Konkurssiin 2024 yli 12 M€ julkisten tukien jälkeen)</t>
+          <t>Infinited Fiber Company Oy (Yt-neuvottelut, pilottituotannon alasajo ja 0 € yhteisöveroa yli 12,4 M€ tukien jälkeen)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="0">
@@ -862,7 +862,7 @@
       </c>
       <c r="K9" t="inlineStr" s="0">
         <is>
-          <t>BLACKLIST_ZOMBIE</t>
+          <t>DEADWEIGHT_CROWD_OUT</t>
         </is>
       </c>
       <c r="L9" s="2">
@@ -919,7 +919,7 @@
       </c>
       <c r="K10" t="inlineStr" s="0">
         <is>
-          <t>BLACKLIST_ZOMBIE</t>
+          <t>DEADWEIGHT_CROWD_OUT</t>
         </is>
       </c>
       <c r="L10" s="2">
@@ -939,7 +939,7 @@
       </c>
       <c r="B11" t="inlineStr" s="0">
         <is>
-          <t>UPM-Kymmene Oyj (Sähköistämistuki, energiaveronpalautukset &amp; BF-avustukset)</t>
+          <t>UPM-Kymmene Oyj (Teollisuuden sähköistämistuki, energiatuet &amp; BF-avustukset)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="0">
@@ -976,7 +976,7 @@
       </c>
       <c r="K11" t="inlineStr" s="0">
         <is>
-          <t>BLACKLIST_ZOMBIE</t>
+          <t>DEADWEIGHT_CROWD_OUT</t>
         </is>
       </c>
       <c r="L11" s="2">
@@ -1023,17 +1023,17 @@
         <v>96000000.0</v>
       </c>
       <c r="H12" s="2">
-        <v>-14000000.0</v>
+        <v>22000000.0</v>
       </c>
       <c r="I12" s="2">
-        <v>35000000.0</v>
+        <v>45000000.0</v>
       </c>
       <c r="J12" s="2">
-        <v>-0.51</v>
+        <v>-0.24</v>
       </c>
       <c r="K12" t="inlineStr" s="0">
         <is>
-          <t>BLACKLIST_ZOMBIE</t>
+          <t>DEADWEIGHT_CROWD_OUT</t>
         </is>
       </c>
       <c r="L12" s="2">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="K13" t="inlineStr" s="0">
         <is>
-          <t>BLACKLIST_ZOMBIE</t>
+          <t>DEADWEIGHT_CROWD_OUT</t>
         </is>
       </c>
       <c r="L13" s="2">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="K14" t="inlineStr" s="0">
         <is>
-          <t>BLACKLIST_ZOMBIE</t>
+          <t>DEADWEIGHT_CROWD_OUT</t>
         </is>
       </c>
       <c r="L14" s="2">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="K15" t="inlineStr" s="0">
         <is>
-          <t>BLACKLIST_ZOMBIE</t>
+          <t>DEADWEIGHT_CROWD_OUT</t>
         </is>
       </c>
       <c r="L15" s="2">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="K17" t="inlineStr" s="0">
         <is>
-          <t>BLACKLIST_ZOMBIE</t>
+          <t>DEADWEIGHT_CROWD_OUT</t>
         </is>
       </c>
       <c r="L17" s="2">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="K18" t="inlineStr" s="0">
         <is>
-          <t>BLACKLIST_ZOMBIE</t>
+          <t>DEADWEIGHT_CROWD_OUT</t>
         </is>
       </c>
       <c r="L18" s="2">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="K19" t="inlineStr" s="0">
         <is>
-          <t>BLACKLIST_ZOMBIE</t>
+          <t>DEADWEIGHT_CROWD_OUT</t>
         </is>
       </c>
       <c r="L19" s="2">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="B20" t="inlineStr" s="0">
         <is>
-          <t>Metsä Fibre Oy (Biutuotetehtaiden energia- ja investointituet)</t>
+          <t>Metsä Fibre Oy (Biotuotetehtaiden energia- ja investointituet)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="0">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="K20" t="inlineStr" s="0">
         <is>
-          <t>BLACKLIST_ZOMBIE</t>
+          <t>DEADWEIGHT_CROWD_OUT</t>
         </is>
       </c>
       <c r="L20" s="2">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="B21" t="inlineStr" s="0">
         <is>
-          <t>Nokia Oyj (5G/6G &amp; puolijohde-T&amp;K Veturi — maksoi &gt;1,1 mrd. € yhteisöveroa Suomeen)</t>
+          <t>Nokia Oyj (5G/6G &amp; puolijohde-T&amp;K Veturi — vahva yhteisö- ja T&amp;K-verojälki Suomessa)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="0">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="B24" t="inlineStr" s="0">
         <is>
-          <t>ICEYE Oy (SAR-satelliittitutkateknologia — aito puolustus- ja avaruusteknologian vienti)</t>
+          <t>ICEYE Oy (SAR-satelliittitutkateknologia — korkean arvonlisän puolustusvienti ja T&amp;K-verokertymä)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="0">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="B25" t="inlineStr" s="0">
         <is>
-          <t>Supercell Oy (0 € yritystukea — &gt;950 milj. € yhteisöveroa Suomeen)</t>
+          <t>Supercell Oy (0 € suoria tukia 2020–2025 — &gt;950 milj. € yhteisöveroa Suomeen)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="0">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B26" t="inlineStr" s="0">
         <is>
-          <t>KONE Oyj (Vientiteollisuuden nettoveronmaksajaverrokki)</t>
+          <t>KONE Oyj (Vientiteollisuuden nettoveronmaksajaverrokki — &gt;485 milj. € yhteisöveroa)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="0">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B27" t="inlineStr" s="0">
         <is>
-          <t>Retail Logistics Excellence - RELEX Oy (Kasvuyhtiöiden veronmaksajaverrokki)</t>
+          <t>Retail Logistics Excellence - RELEX Oy (Ohjelmistoviennin veronmaksajaverrokki)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="0">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="B28" t="inlineStr" s="0">
         <is>
-          <t>Ponsse Oyj (Konepajateollisuuden nettoveronmaksajaverrokki)</t>
+          <t>Ponsse Oyj (Konepajateollisuuden nettoveronmaksajaverrokki — &gt;64 milj. € yhteisöveroa)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="0">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="B29" t="inlineStr" s="0">
         <is>
-          <t>Orion Oyj (Lääke- ja huipputeknologian nettoveronmaksajaverrokki)</t>
+          <t>Orion Oyj (Lääke- ja huipputeknologian nettoveronmaksajaverrokki — &gt;295 milj. € yhteisöveroa)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="0">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="E2" t="inlineStr" s="0">
         <is>
-          <t>Infinited Fiber Company Oy (Konkurssiin 2024 yli 12 M€ julkisten tukien jälkeen) | P2X Solutions Oy (TEM &amp; Business Finland vetyinvestointi- ja T&amp;K-tuet) | Origin by Ocean Oy (Business Finland &amp; EU biokemian avustuskohde) | Solar Foods Oyj (Business Finland &amp; IPCEI julkiset avustukset ja T&amp;K-lainat)</t>
+          <t>Infinited Fiber Company Oy (Yt-neuvottelut, pilottituotannon alasajo ja 0 € yhteisöveroa yli 12,4 M€ tukien jälkeen) | P2X Solutions Oy (TEM &amp; Business Finland vetyinvestointi- ja T&amp;K-tuet) | Origin by Ocean Oy (Business Finland &amp; EU biokemian avustuskohde) | Solar Foods Oyj (Business Finland &amp; IPCEI julkiset avustukset ja T&amp;K-lainat)</t>
         </is>
       </c>
       <c r="F2" s="2">
@@ -2291,12 +2291,12 @@
     <row r="2">
       <c r="A2" t="inlineStr" s="0">
         <is>
-          <t>0201315-8</t>
+          <t>0202225-4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="0">
         <is>
-          <t>MIELI Suomen Mielenterveys ry (STEA 2026 suurin saaja: 5,00 M€ Ak-yleistukea + 1,02 M€ kohdetukea)</t>
+          <t>MIELI Suomen Mielenterveys ry (STEA 2026 suurin saaja: 5,00 M€ jatkuvaa Ak-toimintatukea + 1,02 M€ Ay-yleistukea)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="0">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="E2" t="inlineStr" s="0">
         <is>
-          <t>Ak</t>
+          <t>Ak/Ay</t>
         </is>
       </c>
       <c r="F2" s="2">
@@ -2330,11 +2330,11 @@
       </c>
       <c r="J2" t="inlineStr" s="0">
         <is>
-          <t>10 STEA-päätöstä 2026 (Ak 1 yleisavustus 5 002 555 €)</t>
+          <t>10 STEA-päätöstä 2026 (Ay 1 yleisavustus 1 020 600 € + 9 Ak-toiminta-avustusta 5 002 555 €)</t>
         </is>
       </c>
       <c r="K2" s="2">
-        <v>3100000.0</v>
+        <v>2450000.0</v>
       </c>
     </row>
     <row r="3">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="B3" t="inlineStr" s="0">
         <is>
-          <t>Ehkäisevä päihdetyö EHYT ry (STEA 2026: 2,87 M€ Ak-yleisavustus viestintään ja järjestöhallintoon)</t>
+          <t>Ehkäisevä päihdetyö EHYT ry (STEA 2026: 2,87 M€ Ak-toiminta-avustusta + 1,26 M€ Ay/C-tukea)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="0">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="E3" t="inlineStr" s="0">
         <is>
-          <t>Ak</t>
+          <t>Ak/Ay</t>
         </is>
       </c>
       <c r="F3" s="2">
@@ -2374,27 +2374,27 @@
       </c>
       <c r="I3" t="inlineStr" s="0">
         <is>
-          <t>KYLLÄ</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="J3" t="inlineStr" s="0">
         <is>
-          <t>Useita kansanedustaja- ja puoluevaltuustotaustaisia hallitusjäseniä</t>
+          <t>85 % rahoituksesta suoraan STEA:lta (Ay 1 yleisavustus 1 116 292 € + Ak-toiminta-avustukset)</t>
         </is>
       </c>
       <c r="K3" s="2">
-        <v>3290805.0</v>
+        <v>2870805.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr" s="0">
         <is>
-          <t>0116987-2</t>
+          <t>0116988-7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="0">
         <is>
-          <t>Suomen Punainen Risti (STEA 2026: 3,55 M€, josta 3,03 M€ Ak-yleisavustusta)</t>
+          <t>Suomen Punainen Risti (STEA 2026: 3,55 M€, josta 3,03 M€ jatkuvaa Ak-toiminta-avustusta)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="0">
@@ -2428,22 +2428,22 @@
       </c>
       <c r="J4" t="inlineStr" s="0">
         <is>
-          <t>Monikanavarahoitus: STEA + UM + SM + Veripalvelu / sote-myynti</t>
+          <t>Monikanavarahoitus: STEA 3,55 M€ + UM/SM valmiusrahoitus + julkiset palveluhankinnat</t>
         </is>
       </c>
       <c r="K4" s="2">
-        <v>13920000.0</v>
+        <v>1420000.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr" s="0">
         <is>
-          <t>0201247-2</t>
+          <t>0545957-4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="0">
         <is>
-          <t>Mielenterveyden Keskusliitto ry (STEA 2026: 3,00 M€, josta 1,84 M€ Ak-yleisavustusta)</t>
+          <t>Mielenterveyden Keskusliitto ry (STEA 2026: 3,00 M€, josta 1,84 M€ Ak-toimintatukea ja 1,16 M€ Ay-yleistukea)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="0">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="E5" t="inlineStr" s="0">
         <is>
-          <t>Ak</t>
+          <t>Ak/Ay</t>
         </is>
       </c>
       <c r="F5" s="2">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="J5" t="inlineStr" s="0">
         <is>
-          <t>83 % rahoituksesta suoraan STEA:lta</t>
+          <t>83 % rahoituksesta suoraan STEA:lta (Ay 1 yleisavustus 1 161 615 €)</t>
         </is>
       </c>
       <c r="K5" s="2">
@@ -2487,12 +2487,12 @@
     <row r="6">
       <c r="A6" t="inlineStr" s="0">
         <is>
-          <t>0201106-8</t>
+          <t>0202748-5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="0">
         <is>
-          <t>Näkövammaisten liitto ry (STEA 2026: 2,97 M€, josta 2,25 M€ Ak-yleisavustusta + sote-kuntoutusmyynti)</t>
+          <t>Näkövammaisten liitto ry (STEA 2026: 2,97 M€, josta 2,25 M€ Ak-toimintatukea + 0,73 M€ Ay-yleistukea)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="0">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="E6" t="inlineStr" s="0">
         <is>
-          <t>Ak</t>
+          <t>Ak/Ay</t>
         </is>
       </c>
       <c r="F6" s="2">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="J6" t="inlineStr" s="0">
         <is>
-          <t>Iiris-keskus + Kela/hyvinvointialueiden kuntoutusmyynti</t>
+          <t>Ay 1 yleisavustus 726 852 € + Ak-toiminta-avustukset + kuntoutuspalvelumyynti</t>
         </is>
       </c>
       <c r="K6" s="2">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="B7" t="inlineStr" s="0">
         <is>
-          <t>A-klinikkasäätiö sr (STEA 2026: 2,87 M€ + kaupallinen A-klinikka Oy sote-ostopalvelumyynti)</t>
+          <t>A-klinikkasäätiö sr (STEA 2026: 2,87 M€ + konsernin sote-ostopalvelumyynti hyvinvointialueille)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="0">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="E7" t="inlineStr" s="0">
         <is>
-          <t>Ak</t>
+          <t>Ak/Ay</t>
         </is>
       </c>
       <c r="F7" s="2">
@@ -2575,22 +2575,22 @@
       </c>
       <c r="J7" t="inlineStr" s="0">
         <is>
-          <t>Sote-konsernin kaksoisrooli: verovapaa STEA Ak + 24,5 M€ sote-myynti</t>
+          <t>Sote-konsernin kaksoisrooli: STEA 2,87 M€ (Ay 1: 691 357 €) + 24,5 M€ sote-palvelumyynti</t>
         </is>
       </c>
       <c r="K7" s="2">
-        <v>2441017.0</v>
+        <v>1961017.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr" s="0">
         <is>
-          <t>2446601-1</t>
+          <t>2408739-0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="0">
         <is>
-          <t>SOSTE Suomen sosiaali ja terveys ry (STEA 2026: 2,81 M€ kattojärjestön edunvalvontaan ja lobbaukseen)</t>
+          <t>SOSTE Suomen sosiaali ja terveys ry (STEA 2026: 2,81 M€ valtakunnallisen kattojärjestön toimintaan)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="0">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="E8" t="inlineStr" s="0">
         <is>
-          <t>Ak</t>
+          <t>Ak/Ay</t>
         </is>
       </c>
       <c r="F8" s="2">
@@ -2619,16 +2619,16 @@
       </c>
       <c r="I8" t="inlineStr" s="0">
         <is>
-          <t>KYLLÄ</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="J8" t="inlineStr" s="0">
         <is>
-          <t>Järjestöjen katto- ja lobbausjärjestö, joka lobbaa lisää STEA-tukia</t>
+          <t>Järjestöjen katto- ja vaikuttamisjärjestö (Ay 1 yleisavustus 1 182 867 € + Ak 1 623 702 €)</t>
         </is>
       </c>
       <c r="K8" s="2">
-        <v>2630000.0</v>
+        <v>2450000.0</v>
       </c>
     </row>
     <row r="9">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="J9" t="inlineStr" s="0">
         <is>
-          <t>Keskustan, MTK:n ja eläkeläisjärjestöjen taustajärjestöjen lomaliitto</t>
+          <t>Ak 10: Tuettujen lomien järjestäminen ja hallinnointi (2 684 710 €)</t>
         </is>
       </c>
       <c r="K9" s="2">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="B10" t="inlineStr" s="0">
         <is>
-          <t>Sininauhasäätiö sr (STEA 2026: 2,60 M€ + kaupallinen Sininauha Oy 14,2 M€ sote-myynti)</t>
+          <t>Sininauhasäätiö sr (STEA 2026: 2,60 M€ + konsernin 14,2 M€ sote-ostopalvelumyynti)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="0">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="E10" t="inlineStr" s="0">
         <is>
-          <t>Ak</t>
+          <t>Ak/Ay</t>
         </is>
       </c>
       <c r="F10" s="2">
@@ -2722,11 +2722,11 @@
       </c>
       <c r="J10" t="inlineStr" s="0">
         <is>
-          <t>Sote-konsernin kaksoisrooli: STEA Ak + hyvinvointialueiden ostopalvelut</t>
+          <t>Sote-konsernin kaksoisrooli: STEA 2,60 M€ + hyvinvointialueiden asumispalvelumyynti</t>
         </is>
       </c>
       <c r="K10" s="2">
-        <v>2343037.0</v>
+        <v>1993037.0</v>
       </c>
     </row>
     <row r="11">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="J11" t="inlineStr" s="0">
         <is>
-          <t>SAK- ja SDP-taustaisten lomajärjestöjen yhdistetty lomaliitto</t>
+          <t>Ak 1: Tuettujen lomien järjestäminen ja hallinnointi (2 103 947 €)</t>
         </is>
       </c>
       <c r="K11" s="2">
@@ -2781,7 +2781,7 @@
     <row r="12">
       <c r="A12" t="inlineStr" s="0">
         <is>
-          <t>0116788-5</t>
+          <t>0116788-1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="0">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="E12" t="inlineStr" s="0">
         <is>
-          <t>Ak</t>
+          <t>Ak/Ay</t>
         </is>
       </c>
       <c r="F12" s="2">
@@ -2820,22 +2820,22 @@
       </c>
       <c r="J12" t="inlineStr" s="0">
         <is>
-          <t>STEA Ak-yleistuki + laaja kaupallinen lastensuojelumyynti hyvinvointialueille</t>
+          <t>STEA 2,37 M€ (Ay 1 yleisavustus 757 741 €) + lastensuojelupalvelut hyvinvointialueille</t>
         </is>
       </c>
       <c r="K12" s="2">
-        <v>2458896.0</v>
+        <v>1608896.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr" s="0">
         <is>
-          <t>0116597-8</t>
+          <t>0215204-0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="0">
         <is>
-          <t>Mannerheimin Lastensuojeluliitto ry (STEA 2026: 2,25 M€, josta 2,01 M€ Ak-yleistukea)</t>
+          <t>Mannerheimin Lastensuojeluliitto ry (STEA 2026: 2,25 M€, josta 2,01 M€ jatkuvaa Ak-toimintatukea)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="0">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="E13" t="inlineStr" s="0">
         <is>
-          <t>Ak</t>
+          <t>Ak/Ay</t>
         </is>
       </c>
       <c r="F13" s="2">
@@ -2869,22 +2869,22 @@
       </c>
       <c r="J13" t="inlineStr" s="0">
         <is>
-          <t>Monikanavarahoitus: STEA + OKM + kunnat</t>
+          <t>Monikanavarahoitus: STEA 2,25 M€ (Ay 1: 239 000 €) + OKM + kunnat</t>
         </is>
       </c>
       <c r="K13" s="2">
-        <v>2320000.0</v>
+        <v>1580000.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr" s="0">
         <is>
-          <t>0201300-0</t>
+          <t>0116583-5</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="0">
         <is>
-          <t>Suomen Nuorisoalan kattojärjestö Allianssi ry (OKM 29.80.50: nuorisoalan lobbaus- ja kattojärjestö)</t>
+          <t>Suomen nuorisoalan kattojärjestö Allianssi ry (OKM 29.91.50: nuorisoalan katto- ja edunvalvontajärjestö)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="0">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="E14" t="inlineStr" s="0">
         <is>
-          <t>Ak</t>
+          <t>Ay</t>
         </is>
       </c>
       <c r="F14" s="2">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="J14" t="inlineStr" s="0">
         <is>
-          <t>Poliittisten nuorisojärjestöjen ja etujärjestöjen edustajisto</t>
+          <t>Nuorisoalan valtakunnallinen katto- ja vaikuttamisjärjestö (momentti 29.91.50)</t>
         </is>
       </c>
       <c r="K14" s="2">
@@ -2928,12 +2928,12 @@
     <row r="15">
       <c r="A15" t="inlineStr" s="0">
         <is>
-          <t>0215315-8</t>
+          <t>0201112-5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="0">
         <is>
-          <t>Rikosuhripäivystys / Ensi- ja turvakotien kriisityö (Kohdennettu kenttäapu — 0 € leikkaus)</t>
+          <t>Ensi- ja turvakotien liitto ry (Lähisuhdeväkivalta- ja vauvaperheiden kriisityö — 0 € leikkaus)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="0">
@@ -2948,14 +2948,14 @@
       </c>
       <c r="E15" t="inlineStr" s="0">
         <is>
-          <t>Ah</t>
+          <t>Ak</t>
         </is>
       </c>
       <c r="F15" s="2">
-        <v>1554000.0</v>
+        <v>1735644.0</v>
       </c>
       <c r="G15" s="2">
-        <v>9.3</v>
+        <v>15.0</v>
       </c>
       <c r="H15" s="2">
         <v>0.0</v>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="B3" t="inlineStr" s="0">
         <is>
-          <t>Infinited Fiber Company Oy (Tukirahoituksella ja aktivoinneilla ylläpidetty tase ennen konkurssia)</t>
+          <t>Infinited Fiber Company Oy (Tukirahoituksella ja aktivoinneilla ylläpidetty tase ennen yt-neuvotteluita)</t>
         </is>
       </c>
       <c r="C3" s="2">
@@ -3184,17 +3184,17 @@
       </c>
       <c r="E1" t="inlineStr" s="1">
         <is>
-          <t>Siitä: Rajoittamaton Ak-yleisavustus 2026 (€)</t>
+          <t>Siitä: Jatkuva Ak-toiminta-avustus 2026 (€)</t>
         </is>
       </c>
       <c r="F1" t="inlineStr" s="1">
         <is>
-          <t>Siitä: Kohdennettu hanke-/investointiavustus (€)</t>
+          <t>Siitä: Muut avustuslajit Ay/C/B (€)</t>
         </is>
       </c>
       <c r="G1" t="inlineStr" s="1">
         <is>
-          <t>Ak-yleisavustuksen osuus (%)</t>
+          <t>Ak-toiminta-avustuksen osuus (%)</t>
         </is>
       </c>
       <c r="H1" t="inlineStr" s="1">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="I2" t="inlineStr" s="0">
         <is>
-          <t>Ak 19: Ihmiskaupan ja sen lähirikosten uhrien tunnistamiseen  voimavarojen vahvistamiseen sekä oikeusturvan parantamiseen matalan kynnyksen neuvonta- ja tukityön sekä palveluohjauksen avulla (Rikosuhripäivystyksen erityistukipalvelu) (264 600 €) | Ak 13: Vapaaehtoistoiminnan toimintaedellytysten vahvistamiseen MIELI ry:n jäsenyhdistyksissä koordinoinnin  ohjauksen  koulutusten ja neuvonnan avulla (505 000 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (1 020 600 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (1 020 600 €) | Ak 13: Vapaaehtoistoiminnan toimintaedellytysten vahvistamiseen MIELI ry:n jäsenyhdistyksissä koordinoinnin  ohjauksen  koulutusten ja neuvonnan avulla (505 000 €) | Ak 19: Ihmiskaupan ja sen lähirikosten uhrien tunnistamiseen  voimavarojen vahvistamiseen sekä oikeusturvan parantamiseen matalan kynnyksen neuvonta- ja tukityön sekä palveluohjauksen avulla (Rikosuhripäivystyksen erityistukipalvelu) (264 600 €)</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="I3" t="inlineStr" s="0">
         <is>
-          <t>Ak 13: Jäsenjärjestöille kohdistettaviin avustuksiin (72 685 €) | Ak 15: Päihteitä ongelmallisesti käyttävien ja heidän läheistensä lakisääteisten oikeuksien varmistamiseen järjestölähtöisenä neuvonta- ja edunvalvontatyönä (Päihdeasiamiestoiminta) (198 000 €) | Ak 4: Ehkäisevän päihdetyön toimintaedellytysten parantamiseen ehkäisevän päihdetyön järjestöverkoston koordinaation ja koulutusten avulla (137 813 €)</t>
+          <t>Ak 15: Päihteitä ongelmallisesti käyttävien ja heidän läheistensä lakisääteisten oikeuksien varmistamiseen järjestölähtöisenä neuvonta- ja edunvalvontatyönä (Päihdeasiamiestoiminta) (198 000 €) | Ak 4: Ehkäisevän päihdetyön toimintaedellytysten parantamiseen ehkäisevän päihdetyön järjestöverkoston koordinaation ja koulutusten avulla (137 813 €) | Ak 13: Jäsenjärjestöille kohdistettaviin avustuksiin (72 685 €)</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="I4" t="inlineStr" s="0">
         <is>
-          <t>Ak 4384: Koti- ja vapaa-ajan tapaturmien sekä työ- ja liikennetapaturmien ehkäisyyn jakamalla väestölle tietoa tapaturmien ehkäisystä viestinnän ja koulutuksen keinoin sekä vapaaehtoisten ja sosiaali-  terveys-  pelastus- ja opetusalan ammattilaisten kautta (93 767 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (349 440 €) | Ak 11962: Yksinäisyyden vähentämiseen ja sosiaalisten kontaktien lisäämiseen kohtaavan toiminnan ja vertaistuen keinoin. Aikuisten sosiaalisten ja vuorovaikutustaitojen vahvistamiseen. Yksinäisyystyön saavutettavuuden edistämiseen. (Yksi Näistä - Vaihtoehtoja ja saavutettavuutta yksinäisyystyöhön 2026) (588 840 €)</t>
+          <t>Ak 11962: Yksinäisyyden vähentämiseen ja sosiaalisten kontaktien lisäämiseen kohtaavan toiminnan ja vertaistuen keinoin. Aikuisten sosiaalisten ja vuorovaikutustaitojen vahvistamiseen. Yksinäisyystyön saavutettavuuden edistämiseen. (Yksi Näistä - Vaihtoehtoja ja saavutettavuutta yksinäisyystyöhön 2026) (588 840 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (349 440 €) | Ak 4384: Koti- ja vapaa-ajan tapaturmien sekä työ- ja liikennetapaturmien ehkäisyyn jakamalla väestölle tietoa tapaturmien ehkäisystä viestinnän ja koulutuksen keinoin sekä vapaaehtoisten ja sosiaali-  terveys-  pelastus- ja opetusalan ammattilaisten kautta (93 767 €)</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="I5" t="inlineStr" s="0">
         <is>
-          <t>Ak 6: Jäsenjärjestöille kohdistettaviin avustuksiin (75 000 €) | Ak 12: Mielenterveystyön osaamisen vahvistamiseen kouluttamalla mielenterveysongelmia toiminnassaan kohtaavia ja vapaaehtoisia sekä jakamalla tietoa ja tarjoamalla työvälineitä mielen hyvinvoinnin tukemiseen vasta sairastuneille ja sairastumisriskissä oleville (Koulutus- ja kehittämisyksikkö KOUKE) (488 731 €) | Ak 19: Mielenterveysneuvontaan mielenterveyden ongelmia kokeville ja heidän läheisilleen sekä vapaaehtoisvoimin järjestettävään vertaistukitoimintaan ja sen kehittämiseen osana keskusliiton ja sen jäsenyhdistysten toimintaa (VALOA - Valtakunnallinen mielenterveysneuvonta ja vapaaehtoistyö) (577 388 €)</t>
+          <t>Ak 19: Mielenterveysneuvontaan mielenterveyden ongelmia kokeville ja heidän läheisilleen sekä vapaaehtoisvoimin järjestettävään vertaistukitoimintaan ja sen kehittämiseen osana keskusliiton ja sen jäsenyhdistysten toimintaa (VALOA - Valtakunnallinen mielenterveysneuvonta ja vapaaehtoistyö) (577 388 €) | Ak 12: Mielenterveystyön osaamisen vahvistamiseen kouluttamalla mielenterveysongelmia toiminnassaan kohtaavia ja vapaaehtoisia sekä jakamalla tietoa ja tarjoamalla työvälineitä mielen hyvinvoinnin tukemiseen vasta sairastuneille ja sairastumisriskissä oleville (Koulutus- ja kehittämisyksikkö KOUKE) (488 731 €) | Ak 6: Jäsenjärjestöille kohdistettaviin avustuksiin (75 000 €)</t>
         </is>
       </c>
     </row>
@@ -3369,9 +3369,9 @@
       </c>
       <c r="I6" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (726 852 €) | Ak 19: Näkövammaisten henkilöiden tiedonsaannin tukemiseen ja digivalmiuksien lisäämiseen saavutettavan julkaisutuotannon ja digineuvonnan avulla
+          <t>Ak 19: Näkövammaisten henkilöiden tiedonsaannin tukemiseen ja digivalmiuksien lisäämiseen saavutettavan julkaisutuotannon ja digineuvonnan avulla
 - Lukemisesteen aiheuttamien haittojen lieventämiseen Daisy-soitinlainauksen avulla
-- Toimivan digitaalisen työympäristön mahdollistamiseen ja kehittämiseen (908 946 €) | Ak 35: Näkövammaisten henkilöiden työllistymisen  työllisyyden ja opiskelun edellytysten parantamiseen sekä yhdenvertaisen opiskelun ja työskentelyn mahdollistamiseen neuvonnan ja ohjauksen  vertaistuen ja vaikuttamistyön avulla (317 277 €)</t>
+- Toimivan digitaalisen työympäristön mahdollistamiseen ja kehittämiseen (908 946 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (726 852 €) | Ak 35: Näkövammaisten henkilöiden työllistymisen  työllisyyden ja opiskelun edellytysten parantamiseen sekä yhdenvertaisen opiskelun ja työskentelyn mahdollistamiseen neuvonnan ja ohjauksen  vertaistuen ja vaikuttamistyön avulla (317 277 €)</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="I9" t="inlineStr" s="0">
         <is>
-          <t>Ak 9: Sosiaalisen lomatoiminnan asiakasrekisterin ylläpitoon ja kehittämiseen (84 000 €) | Ak 8: Vapaaehtoispohjaisen tukihenkilöverkoston toimintaan ja koordinointiin haja-asutusalueilla asuville ihmisille (163 000 €) | Ak 1: Sosiaaliseen lomatoimintaan vähävaraisille ja erityisen tuen tarpeessa oleville 
+          <t>Ak 1: Sosiaaliseen lomatoimintaan vähävaraisille ja erityisen tuen tarpeessa oleville 
 - lapsiperheille
 - omaishoitajille
 - erityisryhmille
 - työikäisille 
-- ikääntyneille (2 437 710 €)</t>
+- ikääntyneille (2 437 710 €) | Ak 8: Vapaaehtoispohjaisen tukihenkilöverkoston toimintaan ja koordinointiin haja-asutusalueilla asuville ihmisille (163 000 €) | Ak 9: Sosiaalisen lomatoiminnan asiakasrekisterin ylläpitoon ja kehittämiseen (84 000 €)</t>
         </is>
       </c>
     </row>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="I10" t="inlineStr" s="0">
         <is>
-          <t>Ay 3069: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (194 162 €) | C 13682: Nuorten huumekuolemien ehkäisyyn vertaistoimintaa  riskitietoisuuden vahvistamista ja käytännön ensiapuosaamista lisäämällä (ODE 2.0 Pelasta kaveri – toivoa  tietoa ja toimintaa 2026–2028) (Nuorten huumekuolemien ehkäisyn ohjelma) (417 125 €) | Ak 4: Pitkäaikaisasunnottomien ja vaikeasti asutettavien ihmisten integroimiseen normaaliin asuntokantaan asumispolun eri vaiheissa annettavalla yksilöllisellä ja ryhmämuotoisella tuella sekä asumisvalmiuksien ja -taitojen parantamiseen (309 270 €)</t>
+          <t>C 13682: Nuorten huumekuolemien ehkäisyyn vertaistoimintaa  riskitietoisuuden vahvistamista ja käytännön ensiapuosaamista lisäämällä (ODE 2.0 Pelasta kaveri – toivoa  tietoa ja toimintaa 2026–2028) (Nuorten huumekuolemien ehkäisyn ohjelma) (417 125 €) | Ak 4: Pitkäaikaisasunnottomien ja vaikeasti asutettavien ihmisten integroimiseen normaaliin asuntokantaan asumispolun eri vaiheissa annettavalla yksilöllisellä ja ryhmämuotoisella tuella sekä asumisvalmiuksien ja -taitojen parantamiseen (309 270 €) | Ay 3069: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (194 162 €)</t>
         </is>
       </c>
     </row>
@@ -3541,8 +3541,8 @@
       </c>
       <c r="I11" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (875 215 €) | Ak 16: Jäsenjärjestöille kohdistettaviin avustuksiin (70 000 €) | Ak 9: Vaikeavammaisten ja heidän läheistensä osallistumisen edistämiseen toimintavälineiden  tapahtuma-  kurssi- ja koulutustoiminnan avulla sekä alan ammattilaisten osaamisen lisäämiseen vaikuttamistyöllä 
-(Malike-toiminta) (520 500 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (875 215 €) | Ak 9: Vaikeavammaisten ja heidän läheistensä osallistumisen edistämiseen toimintavälineiden  tapahtuma-  kurssi- ja koulutustoiminnan avulla sekä alan ammattilaisten osaamisen lisäämiseen vaikuttamistyöllä 
+(Malike-toiminta) (520 500 €) | Ak 16: Jäsenjärjestöille kohdistettaviin avustuksiin (70 000 €)</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="I13" t="inlineStr" s="0">
         <is>
-          <t>Ak 8: Lasten aseman ja oikeuksien turvaamiseen ja edistämiseen erityisesti digitaalisessa mediassa (Nettivihjetoiminta) (117 845 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (757 741 €) | Ak 6: Suomalaisten adoptiohakijoiden  adoptiovanhempien ja adoptoitujen tukemiseen tiedotuksen ja ohjauksen keinoin adoptioprosessin eri vaiheissa (kansainvälinen adoptiopalvelu) (98 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (757 741 €) | Ak 8: Lasten aseman ja oikeuksien turvaamiseen ja edistämiseen erityisesti digitaalisessa mediassa (Nettivihjetoiminta) (117 845 €) | Ak 6: Suomalaisten adoptiohakijoiden  adoptiovanhempien ja adoptoitujen tukemiseen tiedotuksen ja ohjauksen keinoin adoptioprosessin eri vaiheissa (kansainvälinen adoptiopalvelu) (98 000 €)</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I14" t="inlineStr" s="0">
         <is>
-          <t>Ak 6: MLL:n paikallisen vapaaehtoisen lapsi- ja perhetoiminnan ja sen toimintaedellytyksien ohjaukseen sekä valtakunnalliseen perhekeskusyhteistyöhön (669 834 €) | Ak 13: Lasten ja lapsiperheiden hyvinvoinnin edistämiseen ja tasavertaisen vanhemmuuden vahvistamiseen kehittämällä mentalisaatioperusteista vanhempainryhmätoimintaa ja Jututtamo-vertaisryhmätoimintaa sekä kouluttamalla vapaaehtoisia ja ammattilaisia ryhmien ohjaajiksi (Mentalisaatioperustainen vanhempainryhmätoiminta) (144 217 €) | Ak 8: Oppilaiden osallisuutta edistävään vapaaehtoistoimintaan kouluissa (Tukioppilas-   kummioppilas- ja tutortoiminta sekä Koulurauha-ohjelma) (341 713 €)</t>
+          <t>Ak 6: MLL:n paikallisen vapaaehtoisen lapsi- ja perhetoiminnan ja sen toimintaedellytyksien ohjaukseen sekä valtakunnalliseen perhekeskusyhteistyöhön (669 834 €) | Ak 8: Oppilaiden osallisuutta edistävään vapaaehtoistoimintaan kouluissa (Tukioppilas-   kummioppilas- ja tutortoiminta sekä Koulurauha-ohjelma) (341 713 €) | Ak 13: Lasten ja lapsiperheiden hyvinvoinnin edistämiseen ja tasavertaisen vanhemmuuden vahvistamiseen kehittämällä mentalisaatioperusteista vanhempainryhmätoimintaa ja Jututtamo-vertaisryhmätoimintaa sekä kouluttamalla vapaaehtoisia ja ammattilaisia ryhmien ohjaajiksi (Mentalisaatioperustainen vanhempainryhmätoiminta) (144 217 €)</t>
         </is>
       </c>
     </row>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="I15" t="inlineStr" s="0">
         <is>
-          <t>Ak 2586: Hyvinvointia edistävän Green Care -toiminnan lisäämiseen ja kehittämiseen sosiaali- ja terveysjärjestöissä (Vihreä veräjä) (187 431 €) | Ak 15: Matalan kynnyksen tuki- ja neuvontapalveluiden ja vertaistukitoiminnan ylläpitämiseen rahapelihaittoja kokeville pelaajille  heidän läheisilleen ja pelihaittoja työssään kohtaaville ammattilaisille (Tiltti) (368 434 €) | Ak 17: Haitallisesti päihteitä käyttävien läheisten voimavarojen vahvistamiseen sekä yhteiskunnallisen aseman ja palvelujen saatavuuden parantamiseen tiedon tuottamisen  ammattilaisille suunnatun kouluttamisen sekä toimintamallien kehittämisen ja levittämisen avulla (166 609 €)</t>
+          <t>Ak 15: Matalan kynnyksen tuki- ja neuvontapalveluiden ja vertaistukitoiminnan ylläpitämiseen rahapelihaittoja kokeville pelaajille  heidän läheisilleen ja pelihaittoja työssään kohtaaville ammattilaisille (Tiltti) (368 434 €) | Ak 2586: Hyvinvointia edistävän Green Care -toiminnan lisäämiseen ja kehittämiseen sosiaali- ja terveysjärjestöissä (Vihreä veräjä) (187 431 €) | Ak 17: Haitallisesti päihteitä käyttävien läheisten voimavarojen vahvistamiseen sekä yhteiskunnallisen aseman ja palvelujen saatavuuden parantamiseen tiedon tuottamisen  ammattilaisille suunnatun kouluttamisen sekä toimintamallien kehittämisen ja levittämisen avulla (166 609 €)</t>
         </is>
       </c>
     </row>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="I18" t="inlineStr" s="0">
         <is>
-          <t>Ak 9885: Kiusaamista kokeneiden ja heidän läheistensä selviytymistä ja toipumista edistävään yksilöllisen tukeen ja vertaisryhmätoimintaan sekä ammattilaisten osaamisen kehittämiseen kiusaamisteemasta (99 320 €) | Ak 4: Maahanmuuttajanaisten ja heidän perheidensä kotoutumisen tukemiseen  osallisuuden lisäämiseen sekä syrjäytymisen ehkäisyyn avoimen toiminnan  ryhmien sekä yksilöneuvonnan ja -tuen keinoin (Kansainvälinen naisten tapaamispaikka Naistari) (140 026 €) | Ak 2442: Ryhmä- ja yksilömuotoiseen  sekä avoimeen tukitoimintaan neuropsykiatrisia piirteitä omaaville aikuisille (Omavoima) (140 915 €)</t>
+          <t>Ak 2442: Ryhmä- ja yksilömuotoiseen  sekä avoimeen tukitoimintaan neuropsykiatrisia piirteitä omaaville aikuisille (Omavoima) (140 915 €) | Ak 4: Maahanmuuttajanaisten ja heidän perheidensä kotoutumisen tukemiseen  osallisuuden lisäämiseen sekä syrjäytymisen ehkäisyyn avoimen toiminnan  ryhmien sekä yksilöneuvonnan ja -tuen keinoin (Kansainvälinen naisten tapaamispaikka Naistari) (140 026 €) | Ak 9885: Kiusaamista kokeneiden ja heidän läheistensä selviytymistä ja toipumista edistävään yksilöllisen tukeen ja vertaisryhmätoimintaan sekä ammattilaisten osaamisen kehittämiseen kiusaamisteemasta (99 320 €)</t>
         </is>
       </c>
     </row>
@@ -3809,8 +3809,8 @@
       </c>
       <c r="I19" t="inlineStr" s="0">
         <is>
-          <t>C 13717: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Vapaaksi" (Dnro: EURA 2021/209866/09) osarahoitukseen järjestölle (2026-2028) (94 938 €) | Ak 1279: Vanhemmuuden tukemiseen  lapsiperheiden hyvinvoinnin vahvistamiseen ja koululaisten luvattomien poissaolojen sekä koulupudokkuuden ehkäisemiseen
-(Vanhempien Akatemia) (359 668 €) | Ay 2: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (294 814 €)</t>
+          <t>Ak 1279: Vanhemmuuden tukemiseen  lapsiperheiden hyvinvoinnin vahvistamiseen ja koululaisten luvattomien poissaolojen sekä koulupudokkuuden ehkäisemiseen
+(Vanhempien Akatemia) (359 668 €) | Ay 2: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (294 814 €) | C 13717: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Vapaaksi" (Dnro: EURA 2021/209866/09) osarahoitukseen järjestölle (2026-2028) (94 938 €)</t>
         </is>
       </c>
     </row>
@@ -3876,7 +3876,7 @@
       </c>
       <c r="I21" t="inlineStr" s="0">
         <is>
-          <t>Ak 5695: Maahanmuuttajien  erityisesti naismaahanmuuttajien työllistymisen edistämiseen mentoroinnilla ja verkostotyöllä (93 135 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (750 000 €) | Ak 5: Intiimeissä ihmissuhteissa huolta kokevien nuorten ja nuorten aikuisten seksuaalisen hyvinvoinnin tukemiseen verkkopalveluiden ja tiedontuotannon keinoin (250 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (750 000 €) | Ak 5: Intiimeissä ihmissuhteissa huolta kokevien nuorten ja nuorten aikuisten seksuaalisen hyvinvoinnin tukemiseen verkkopalveluiden ja tiedontuotannon keinoin (250 000 €) | Ak 5695: Maahanmuuttajien  erityisesti naismaahanmuuttajien työllistymisen edistämiseen mentoroinnilla ja verkostotyöllä (93 135 €)</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="I22" t="inlineStr" s="0">
         <is>
-          <t>Ak 2519: Mielenterveyskuntoutujien terveyttä  hyvinvointia  osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään kohtaamispaikkatoimintaan (Imatran Klubitalo) (179 707 €) | Ak 2: Mielenterveyskuntoutujien terveyttä  hyvinvointia  osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään kohtaamispaikkatoimintaan (Itä-Helsingin Klubitalo) (185 220 €) | Ak 7829: Mielenterveyskuntoutujien terveyttä  hyvinvointia  osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään kohtaamispaikkatoimintaan (Tuusulanjärven Klubitalo) (203 962 €)</t>
+          <t>Ak 7829: Mielenterveyskuntoutujien terveyttä  hyvinvointia  osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään kohtaamispaikkatoimintaan (Tuusulanjärven Klubitalo) (203 962 €) | Ak 2: Mielenterveyskuntoutujien terveyttä  hyvinvointia  osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään kohtaamispaikkatoimintaan (Itä-Helsingin Klubitalo) (185 220 €) | Ak 2519: Mielenterveyskuntoutujien terveyttä  hyvinvointia  osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään kohtaamispaikkatoimintaan (Imatran Klubitalo) (179 707 €)</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="I24" t="inlineStr" s="0">
         <is>
-          <t>Ak 7504: Aikuisten yksinäisyyden tunteen vähentämiseen yksinäisyysohjelman  yksinäisyyden omahoito-ohjelman ja keskusteluavun keinoin (Yksinäisyystyön keskus) (215 000 €) | Ak 11131: Lapsiperheiden yksinäisyyden kokemusten vähentämiseen  osallisuuden lisäämiseen ja voimavarojen vahvistamiseen keskusteluavun  ohjauksen  neuvonnan ja vapaaehtoistoiminnan avulla (HelsinkiMission Perhetoiminta) (225 000 €) | Ak 11119: Nuorten yksinäisyyden kokemusten vähentämiseen ja osallisuuden vahvistamiseen keskustelu- ja kriisiavun  vapaaehtoisen kaveritoiminnan sekä jalkautuvan yhteisötoiminnan keinoin (244 000 €)</t>
+          <t>Ak 11119: Nuorten yksinäisyyden kokemusten vähentämiseen ja osallisuuden vahvistamiseen keskustelu- ja kriisiavun  vapaaehtoisen kaveritoiminnan sekä jalkautuvan yhteisötoiminnan keinoin (244 000 €) | Ak 11131: Lapsiperheiden yksinäisyyden kokemusten vähentämiseen  osallisuuden lisäämiseen ja voimavarojen vahvistamiseen keskusteluavun  ohjauksen  neuvonnan ja vapaaehtoistoiminnan avulla (HelsinkiMission Perhetoiminta) (225 000 €) | Ak 7504: Aikuisten yksinäisyyden tunteen vähentämiseen yksinäisyysohjelman  yksinäisyyden omahoito-ohjelman ja keskusteluavun keinoin (Yksinäisyystyön keskus) (215 000 €)</t>
         </is>
       </c>
     </row>
@@ -4009,10 +4009,10 @@
       </c>
       <c r="I25" t="inlineStr" s="0">
         <is>
-          <t>C 13723: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "SUSE - sukupuolisensitiivisyys nuorten
-palveluissa " osarahoitukseen järjestölle (2026-2028) (58 258 €) | Ak 1: Yksinäisten  masentuneiden  sosiaalisesti syrjäytyneiden  monikulttuuristen  psyykkisesti oireilevien ja muiden erityistä tukea tarvitsevien 10-28-vuotiaiden tyttöjen ja nuorten naisten matalan kynnyksen toimintaan sekä ryhmä- ja yksilötukeen 
+          <t>Ak 1: Yksinäisten  masentuneiden  sosiaalisesti syrjäytyneiden  monikulttuuristen  psyykkisesti oireilevien ja muiden erityistä tukea tarvitsevien 10-28-vuotiaiden tyttöjen ja nuorten naisten matalan kynnyksen toimintaan sekä ryhmä- ja yksilötukeen 
 (Kumppanuustalo Tyttöjen Talo) (138 915 €) | Ak 5757: Ryhmä- ja yksilömuotoiseen kulttuurisensitiiviseen toimintaan espoolaisille 10-28 vuotiaille maahanmuuttajataustaisille tytöille ja nuorille naisille Espoossa
-(Sorella) (132 300 €)</t>
+(Sorella) (132 300 €) | C 13723: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "SUSE - sukupuolisensitiivisyys nuorten
+palveluissa " osarahoitukseen järjestölle (2026-2028) (58 258 €)</t>
         </is>
       </c>
     </row>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="I26" t="inlineStr" s="0">
         <is>
-          <t>Ak 17: Jäsenjärjestöille kohdistettaviin avustuksiin (36 750 €) | Ak 9: Harvinaisiin tuki- ja liikuntaelinsairaus- ja vammaryhmiin kuuluvien henkilöiden ja heidän läheistensä hyvinvoinnin ja osallistumismahdollisuuksien edistämiseen vertaistuen  koulutusten  ohjauksen ja neuvonnan avulla (142 538 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (1 035 245 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (1 035 245 €) | Ak 9: Harvinaisiin tuki- ja liikuntaelinsairaus- ja vammaryhmiin kuuluvien henkilöiden ja heidän läheistensä hyvinvoinnin ja osallistumismahdollisuuksien edistämiseen vertaistuen  koulutusten  ohjauksen ja neuvonnan avulla (142 538 €) | Ak 17: Jäsenjärjestöille kohdistettaviin avustuksiin (36 750 €)</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="I27" t="inlineStr" s="0">
         <is>
-          <t>Ak 13: Jäsenyhdistyksissä toteutettavien vaativan vauvatyön työmuotojen (Vauvaperheryhmä  Vauvaperheohjaus  vapaaehtoisdoulatoiminta ja vauvaperheiden kohtaamispaikkatoiminta) kehittämis- ja koordinointitoimintaan sekä vaikuttamistyöhön. Vauvaperheille suunnatun verkkoauttamistoiminnan (vauvaperhe chat ja vauvaperhe.fi -sivusto) koordinointiin ja kehittämiseen  sekä monikulttuurisen työotteen kehittämiseen. (451 200 €) | Ak 22: Eroperheiden auttamisen kehittämiseen ja yhteistyövanhemmuuden ja rinnakkaisvanhemmuuden vahvistamiseen. Varhaisen tuen ja vaativien eropalvelujen kehittämiseen  menetelmien levittämiseen ja juurruttamiseen sekä vaikuttamistyöhön. Yhteistyön koordinointiin muiden alan toimijoiden kanssa (Ero lapsiperheessä -työ). (230 000 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (661 626 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (661 626 €) | Ak 13: Jäsenyhdistyksissä toteutettavien vaativan vauvatyön työmuotojen (Vauvaperheryhmä  Vauvaperheohjaus  vapaaehtoisdoulatoiminta ja vauvaperheiden kohtaamispaikkatoiminta) kehittämis- ja koordinointitoimintaan sekä vaikuttamistyöhön. Vauvaperheille suunnatun verkkoauttamistoiminnan (vauvaperhe chat ja vauvaperhe.fi -sivusto) koordinointiin ja kehittämiseen  sekä monikulttuurisen työotteen kehittämiseen. (451 200 €) | Ak 22: Eroperheiden auttamisen kehittämiseen ja yhteistyövanhemmuuden ja rinnakkaisvanhemmuuden vahvistamiseen. Varhaisen tuen ja vaativien eropalvelujen kehittämiseen  menetelmien levittämiseen ja juurruttamiseen sekä vaikuttamistyöhön. Yhteistyön koordinointiin muiden alan toimijoiden kanssa (Ero lapsiperheessä -työ). (230 000 €)</t>
         </is>
       </c>
     </row>
@@ -4111,12 +4111,12 @@
       </c>
       <c r="I28" t="inlineStr" s="0">
         <is>
-          <t>Ak 6: Pääkaupunkiseudun kotona asuvien iäkkäiden osallisuuden ja sosiaalisen vuorovaikutuksen vahvistamiseen sekä yksinäisyyden lievittämiseen ryhmä-  kesä-  virkistys- ja vapaaehtoistoiminnan keinoin.
+          <t>Ak 10: Iäkkäiden yksinäisyyden kokemusten lievittämiseen  muistisairauden varhaisen vaiheen omahoitotaitojen vahvistamiseen  toimintakyvyn ylläpitämiseen ja edistämiseen sekä elämänhallinnan vahvistumiseen vertaistuellisen ryhmätoiminnan keinoin.
+Vapaaehtoisten ja ammattilaisten ryhmänohjausosaamisen edistämiseen sekä toiminnan juurruttamiseen ja levittämiseen koulutustoiminnan ja työpajojen avulla.
+Ystäväpiiri-toiminta ja siihen perustuva Omahoitovalmennus-toiminta. (415 548 €) | Ak 6: Pääkaupunkiseudun kotona asuvien iäkkäiden osallisuuden ja sosiaalisen vuorovaikutuksen vahvistamiseen sekä yksinäisyyden lievittämiseen ryhmä-  kesä-  virkistys- ja vapaaehtoistoiminnan keinoin.
 Gerontologisen vapaaehtoistoiminnan parissa toimivien tahojen yhteistyön ja vapaaehtoistoiminnan organisoinnin edistämiseen valtakunnallisen osaamisverkoston keinoin.
 Iäkkäille suunnattujen tietoiltapäivien organisointiin.
-Vapaaehtoisten ja ammattilaisten vertaistapaamisiin ja yhdessä oppimisen päiviin vahvistamaan heidän osaamista ryhmänohjauksessa ja sosiokulttuurisessa vanhustyössä. (Senioritoiminta) (224 211 €) | Ak 7: Korjausneuvontaan ja kotiturvallisuuden edistämiseen ikääntyneiden ihmisten kotona asumisen tukemiseksi sekä hyvinvoinnin ja toimintakykyisyyden vahvistamiseksi (203 916 €) | Ak 10: Iäkkäiden yksinäisyyden kokemusten lievittämiseen  muistisairauden varhaisen vaiheen omahoitotaitojen vahvistamiseen  toimintakyvyn ylläpitämiseen ja edistämiseen sekä elämänhallinnan vahvistumiseen vertaistuellisen ryhmätoiminnan keinoin.
-Vapaaehtoisten ja ammattilaisten ryhmänohjausosaamisen edistämiseen sekä toiminnan juurruttamiseen ja levittämiseen koulutustoiminnan ja työpajojen avulla.
-Ystäväpiiri-toiminta ja siihen perustuva Omahoitovalmennus-toiminta. (415 548 €)</t>
+Vapaaehtoisten ja ammattilaisten vertaistapaamisiin ja yhdessä oppimisen päiviin vahvistamaan heidän osaamista ryhmänohjauksessa ja sosiokulttuurisessa vanhustyössä. (Senioritoiminta) (224 211 €) | Ak 7: Korjausneuvontaan ja kotiturvallisuuden edistämiseen ikääntyneiden ihmisten kotona asumisen tukemiseksi sekä hyvinvoinnin ja toimintakykyisyyden vahvistamiseksi (203 916 €)</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="I29" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Meri- ja järvipelastustehtävissä toimivien vapaaehtoisten pätevyyden varmistamiseen  osaamisen lisäämiseen sekä miehistöjen toimintakyvyn ylläpitämiseen (262 500 €) | B 1: Pelastusalushankintojen  korjauksien  huoltojen ja varustehankintojen menoihin (973 192 €) | Ak 3: Jäsenjärjestöille kohdistettaviin avustuksiin (45 000 €)</t>
+          <t>B 1: Pelastusalushankintojen  korjauksien  huoltojen ja varustehankintojen menoihin (973 192 €) | Ak 2: Meri- ja järvipelastustehtävissä toimivien vapaaehtoisten pätevyyden varmistamiseen  osaamisen lisäämiseen sekä miehistöjen toimintakyvyn ylläpitämiseen (262 500 €) | Ak 3: Jäsenjärjestöille kohdistettaviin avustuksiin (45 000 €)</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="I30" t="inlineStr" s="0">
         <is>
-          <t>Ak 1619: Jäsenjärjestöille kohdistettaviin avustuksiin (25 000 €) | Ak 14: MS-tautia  essentiaalista vapinaa  neurologisia harvinaissairauksia  Parkinsonin tautia  harvinaisia liikehäiriösairauksia sairastavien  aivovammautuneiden ja aivoverenkiertohäiriön sairastaneiden sekä heidän läheistensä tukemiseen neuvontatoiminnalla (167 769 €) | Ak 4: Tavoitteellisiin  vertaistuellisiin ja psykososiaalista hyvinvointia vahvistaviin kursseihin MS-tautia  essentiaalista vapinaa ja neurologisia harvinaissairauksia sairastaville sekä heidän läheisilleen. Toteutusmuotoina avomuotoiset kurssit  yöpymiskurssit ja verkkokurssit. Yhteistyökursseille voivat osallistua myös  yhteistyöjärjestöjen kohderyhmiin kuuluvia henkilöitä ja heidän läheisiään. (569 834 €)</t>
+          <t>Ak 4: Tavoitteellisiin  vertaistuellisiin ja psykososiaalista hyvinvointia vahvistaviin kursseihin MS-tautia  essentiaalista vapinaa ja neurologisia harvinaissairauksia sairastaville sekä heidän läheisilleen. Toteutusmuotoina avomuotoiset kurssit  yöpymiskurssit ja verkkokurssit. Yhteistyökursseille voivat osallistua myös  yhteistyöjärjestöjen kohderyhmiin kuuluvia henkilöitä ja heidän läheisiään. (569 834 €) | Ak 14: MS-tautia  essentiaalista vapinaa  neurologisia harvinaissairauksia  Parkinsonin tautia  harvinaisia liikehäiriösairauksia sairastavien  aivovammautuneiden ja aivoverenkiertohäiriön sairastaneiden sekä heidän läheistensä tukemiseen neuvontatoiminnalla (167 769 €) | Ak 1619: Jäsenjärjestöille kohdistettaviin avustuksiin (25 000 €)</t>
         </is>
       </c>
     </row>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="I35" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Rikosseuraamusasiakkaiden ja heidän omaistensa tiedon lisäämiseen oikeuksistaan neuvonnalla  vankilainfoilla ja vaikuttamistyöllä (Kriminaaliasiamiestoiminta) (235 450 €) | Ak 5: Asunnottomana vankilasta vapautuvien ja muiden rikosseuraamustaustaisten henkilöiden asunnottomuuden ja uusintarikollisuuden vähentämiseen asumispalveluohjauksen sekä Vapautuvien Asumisen Tuen (VAT) -verkoston avulla (113 050 €) | Ak 7: Rikostaustaisten läheis- ja perhetyön koordinointiin sekä vankien ja heidän omaistensa tukemiseen yksilöohjauksella sekä vertaisryhmä- ja leiritoiminnalla (207 868 €)</t>
+          <t>Ak 1: Rikosseuraamusasiakkaiden ja heidän omaistensa tiedon lisäämiseen oikeuksistaan neuvonnalla  vankilainfoilla ja vaikuttamistyöllä (Kriminaaliasiamiestoiminta) (235 450 €) | Ak 7: Rikostaustaisten läheis- ja perhetyön koordinointiin sekä vankien ja heidän omaistensa tukemiseen yksilöohjauksella sekä vertaisryhmä- ja leiritoiminnalla (207 868 €) | Ak 5: Asunnottomana vankilasta vapautuvien ja muiden rikosseuraamustaustaisten henkilöiden asunnottomuuden ja uusintarikollisuuden vähentämiseen asumispalveluohjauksen sekä Vapautuvien Asumisen Tuen (VAT) -verkoston avulla (113 050 €)</t>
         </is>
       </c>
     </row>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="I37" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Yli 50-vuotiaiden leskeytyneiden ja avio-/avoeron kokeneiden ammatillisesti ohjattuun vertaistuelliseen ryhmätoimintaan sekä isovanhemmuuden tukemiseen eroperheissä (242 550 €) | Ak 7: Osteopenian ja osteoporoosin ennaltaehkäisyyn ja luuston terveyttä edistävän liikunnan lisäämiseen vertaisohjaajien koulutuksen avulla (Murtumatta mukana - Spänst i benen) (110 250 €) | Ak 1621: Aisti- tai toimintakyvyltään heikentyneiden ikääntyneiden hyvinvoinnin edistämiseen musiikkisisältöisen ja muun toimintakykyä tukevan vapaaehtoistoiminnan avulla sekä vapaaehtoisten osaamisen vahvistamiseen (277 000 €)</t>
+          <t>Ak 1621: Aisti- tai toimintakyvyltään heikentyneiden ikääntyneiden hyvinvoinnin edistämiseen musiikkisisältöisen ja muun toimintakykyä tukevan vapaaehtoistoiminnan avulla sekä vapaaehtoisten osaamisen vahvistamiseen (277 000 €) | Ak 3: Yli 50-vuotiaiden leskeytyneiden ja avio-/avoeron kokeneiden ammatillisesti ohjattuun vertaistuelliseen ryhmätoimintaan sekä isovanhemmuuden tukemiseen eroperheissä (242 550 €) | Ak 7: Osteopenian ja osteoporoosin ennaltaehkäisyyn ja luuston terveyttä edistävän liikunnan lisäämiseen vertaisohjaajien koulutuksen avulla (Murtumatta mukana - Spänst i benen) (110 250 €)</t>
         </is>
       </c>
     </row>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="I38" t="inlineStr" s="0">
         <is>
-          <t>Ak 5: Harvinaista hengityssairautta sairastavien sekä heidän läheistensä hyvinvoinnin tukemiseen  neuvontaan  vertaistuki- ja vapaaehtoistoimintaan sekä ammattilaisten tiedon lisäämiseen (117 000 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (835 506 €) | Ak 8: Aikuisten nikotiinituotteiden käytön lopettamisen tukeen verkko-  puhelin- ja vertaistuen avulla (120 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (835 506 €) | Ak 8: Aikuisten nikotiinituotteiden käytön lopettamisen tukeen verkko-  puhelin- ja vertaistuen avulla (120 000 €) | Ak 5: Harvinaista hengityssairautta sairastavien sekä heidän läheistensä hyvinvoinnin tukemiseen  neuvontaan  vertaistuki- ja vapaaehtoistoimintaan sekä ammattilaisten tiedon lisäämiseen (117 000 €)</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="I39" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (770 228 €) | Ak 11: Harvinaista reuma- ja tule-sairautta sairastavien tiedon  verkostoitumisen ja vertaistuen lisäämiseen (16 813 €) | Ak 6: Reumaa sekä tuki- ja liikuntaelinsairauksia sairastavien kurssitoimintaan elämänhallinnan  hyvinvoinnin ja terveyden tukemiseksi vertaistuellisen ryhmätoiminnan avulla (154 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (770 228 €) | Ak 6: Reumaa sekä tuki- ja liikuntaelinsairauksia sairastavien kurssitoimintaan elämänhallinnan  hyvinvoinnin ja terveyden tukemiseksi vertaistuellisen ryhmätoiminnan avulla (154 000 €) | Ak 11: Harvinaista reuma- ja tule-sairautta sairastavien tiedon  verkostoitumisen ja vertaistuen lisäämiseen (16 813 €)</t>
         </is>
       </c>
     </row>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="I40" t="inlineStr" s="0">
         <is>
-          <t>Ak 5678: Seksityössä mukana olevien neuvontaan  matalan kynnyksen tukitoimintaan  yhteisölliseen toimintaan ja etsivään työhön Turun seudulla. (212 710 €) | Ak 1: Seksityössä mukana olevien neuvontaan  matalan kynnyksen tukitoimintaan  yhteisölliseen toimintaan ja etsivään työhön pääkaupunkiseudulla. (438 563 €) | Ay 2: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (373 043 €)</t>
+          <t>Ak 1: Seksityössä mukana olevien neuvontaan  matalan kynnyksen tukitoimintaan  yhteisölliseen toimintaan ja etsivään työhön pääkaupunkiseudulla. (438 563 €) | Ay 2: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (373 043 €) | Ak 5678: Seksityössä mukana olevien neuvontaan  matalan kynnyksen tukitoimintaan  yhteisölliseen toimintaan ja etsivään työhön Turun seudulla. (212 710 €)</t>
         </is>
       </c>
     </row>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="I41" t="inlineStr" s="0">
         <is>
-          <t>Ak 6066: Maahan muuttaneiden miesten työelämävalmiuksien ja työllistymisen edistämiseen sekä kaksisuuntaisen kotoutumisen tukemiseen mentori-  tukihenkilö- ja suomenkielisen keskusteluryhmätoiminnan avulla Helsingissä  Turussa ja Tampereella (Vieraasta Veljeksi) (87 000 €) | Ak 5: Vanhemmuuden ja elämänhallinnan tukemiseen erotilanteessa oleville miehille yksilö- ja ryhmämuotoisen auttamisen  tukihenkilötoiminnan sekä puhelin- ja verkkoauttamisen keinoin (346 185 €) | Ak 2: Lähisuhdeväkivallan ehkäisyyn sekä miesten toteuttaman lähisuhdeväkivallan käytön lopettamiseen yksilö-  pari- ja ryhmämuotoisen työskentelyn avulla Uudellamaalla ja Pohjois-Savossa (Lyömätön Linja) (345 394 €)</t>
+          <t>Ak 5: Vanhemmuuden ja elämänhallinnan tukemiseen erotilanteessa oleville miehille yksilö- ja ryhmämuotoisen auttamisen  tukihenkilötoiminnan sekä puhelin- ja verkkoauttamisen keinoin (346 185 €) | Ak 2: Lähisuhdeväkivallan ehkäisyyn sekä miesten toteuttaman lähisuhdeväkivallan käytön lopettamiseen yksilö-  pari- ja ryhmämuotoisen työskentelyn avulla Uudellamaalla ja Pohjois-Savossa (Lyömätön Linja) (345 394 €) | Ak 6066: Maahan muuttaneiden miesten työelämävalmiuksien ja työllistymisen edistämiseen sekä kaksisuuntaisen kotoutumisen tukemiseen mentori-  tukihenkilö- ja suomenkielisen keskusteluryhmätoiminnan avulla Helsingissä  Turussa ja Tampereella (Vieraasta Veljeksi) (87 000 €)</t>
         </is>
       </c>
     </row>
@@ -4649,9 +4649,9 @@
       </c>
       <c r="I44" t="inlineStr" s="0">
         <is>
-          <t>Ak 1247: Toimintakyvyltään jossain määrin heikentyneiden  kotona asuvien ikäihmisten toimintakyvyn  osallisuuden ja itsenäisen selviytymisen edistämiseen terveysliikunnan keinoin (Voimaa vanhuuteen - hyvien terveysliikunnan toimintakäytäntöjen juurrutus) (389 745 €) | Ak 7385: Kotona asuvien iäkkäimpien asukkaiden osallisuuden vahvistamiseen sekä yhdessä oloon ja liikkumisen lisäämiseen kodin läheisyydessä. 
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (755 948 €) | Ak 1247: Toimintakyvyltään jossain määrin heikentyneiden  kotona asuvien ikäihmisten toimintakyvyn  osallisuuden ja itsenäisen selviytymisen edistämiseen terveysliikunnan keinoin (Voimaa vanhuuteen - hyvien terveysliikunnan toimintakäytäntöjen juurrutus) (389 745 €) | Ak 7385: Kotona asuvien iäkkäimpien asukkaiden osallisuuden vahvistamiseen sekä yhdessä oloon ja liikkumisen lisäämiseen kodin läheisyydessä. 
 Taloyhtiöissä ja naapurustoissa toimintaa järjestävien vapaaehtoisten valmentamiseen.
-Iäkkäiden hyvinvointia tukevan yhteistyön käynnistämiseen ja lisäämiseen kaupungin eri sektoreiden sekä paikallisten yhdistysten ja taloyhtiöiden kesken. (Yhdessä kotikulmilla) (186 380 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (755 948 €)</t>
+Iäkkäiden hyvinvointia tukevan yhteistyön käynnistämiseen ja lisäämiseen kaupungin eri sektoreiden sekä paikallisten yhdistysten ja taloyhtiöiden kesken. (Yhdessä kotikulmilla) (186 380 €)</t>
         </is>
       </c>
     </row>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="I47" t="inlineStr" s="0">
         <is>
-          <t>Ak 13: Kuurosokeiden ja kuulonäkövammaisten itsenäisen arjen asioinnin ja sosiaalisen kanssakäymisen tukemiseen tieto- ja viestintäteknologian ohjaus-  tuki- ja koulutustoiminnan avulla (270 375 €) | Ak 15: Kuurosokeiden  kuulonäkövammaisten sekä heidän lähipiirinsä ja verkostonsa kommunikaatiotaitojen ja vuorovaikutuksen lisäämiseen ohjauksen  koulutuksen ja kommunikaatiomateriaalituotannon avulla (140 175 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (346 080 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (346 080 €) | Ak 13: Kuurosokeiden ja kuulonäkövammaisten itsenäisen arjen asioinnin ja sosiaalisen kanssakäymisen tukemiseen tieto- ja viestintäteknologian ohjaus-  tuki- ja koulutustoiminnan avulla (270 375 €) | Ak 15: Kuurosokeiden  kuulonäkövammaisten sekä heidän lähipiirinsä ja verkostonsa kommunikaatiotaitojen ja vuorovaikutuksen lisäämiseen ohjauksen  koulutuksen ja kommunikaatiomateriaalituotannon avulla (140 175 €)</t>
         </is>
       </c>
     </row>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="I49" t="inlineStr" s="0">
         <is>
-          <t>Ak 12: Nuorten tupakka- ja nikotiinituotteiden käytön ehkäisyyn ja lopettamisen tukemiseen sekä terveellisten elintapojen edistämiseen nuoren pystyvyyttä ja motivaatiota lisäämällä  nuorten toimintaympäristöjä kehittämällä ja nuorten lähiaikuisten tietoja ja taitoja lisäämällä (480 958 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (308 160 €) | Ak 4: Syöpäjärjestöjen yksilölliseen ja ryhmämuotoiseen psykososiaaliseen tukeen syöpään sairastuneille ja heidän läheisilleen (452 233 €)</t>
+          <t>Ak 12: Nuorten tupakka- ja nikotiinituotteiden käytön ehkäisyyn ja lopettamisen tukemiseen sekä terveellisten elintapojen edistämiseen nuoren pystyvyyttä ja motivaatiota lisäämällä  nuorten toimintaympäristöjä kehittämällä ja nuorten lähiaikuisten tietoja ja taitoja lisäämällä (480 958 €) | Ak 4: Syöpäjärjestöjen yksilölliseen ja ryhmämuotoiseen psykososiaaliseen tukeen syöpään sairastuneille ja heidän läheisilleen (452 233 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (308 160 €)</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="I50" t="inlineStr" s="0">
         <is>
-          <t>Ak 11: Elinsiirtoa odottavien  elinsiirron saaneiden ja sairastuneiden lapsiperheiden vertaistoiminnan mahdollistamiseen  tuen ja tiedon jakamiseen  omahoidon tukemiseen sekä yhteistyöhön hoitoyksiköiden ja muiden järjestöjen kanssa ja hoitorengaspalveluun lapsiperheille  joille ei ole myönnetty omaishoidon vapaata. Kohderyhminä munuais- ja maksasairautta sairastavat ja/tai elinsiirron saaneet lapset ja nuoret  aikuistuvat nuoret sekä heidän läheisensä. Lapsiperheet  joissa vanhemmalla on vakava munuais- tai maksasairaus. Sairastuneita lapsia  nuoria ja perheitä työssään kohtaavat. (89 538 €) | Ak 3: Jäsenjärjestöille kohdistettaviin avustuksiin (43 000 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (710 220 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (710 220 €) | Ak 11: Elinsiirtoa odottavien  elinsiirron saaneiden ja sairastuneiden lapsiperheiden vertaistoiminnan mahdollistamiseen  tuen ja tiedon jakamiseen  omahoidon tukemiseen sekä yhteistyöhön hoitoyksiköiden ja muiden järjestöjen kanssa ja hoitorengaspalveluun lapsiperheille  joille ei ole myönnetty omaishoidon vapaata. Kohderyhminä munuais- ja maksasairautta sairastavat ja/tai elinsiirron saaneet lapset ja nuoret  aikuistuvat nuoret sekä heidän läheisensä. Lapsiperheet  joissa vanhemmalla on vakava munuais- tai maksasairaus. Sairastuneita lapsia  nuoria ja perheitä työssään kohtaavat. (89 538 €) | Ak 3: Jäsenjärjestöille kohdistettaviin avustuksiin (43 000 €)</t>
         </is>
       </c>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="I51" t="inlineStr" s="0">
         <is>
-          <t>Ak 12306: Kodin ulkopuoliseen väkivaltaan syyllistyneiden tai syyllistymisriskissä olevien väkivaltaisen käyttäytymisen vähentämiseen ja ehkäisemiseen yksilöllisen asiakastyön ja verkostotyön avulla (Aggredi Päijät-Häme) (160 000 €) | Ak 1221: Erokriisissä olevien perheiden auttamiseen ja tukemiseen sekä ennaltaehkäisemään erojen konfliktoitumista ja huoltoriitoja vertaisryhmätoiminnan  asiakastyön ja erotukihenkilötoiminnan keinoin huomioiden erityisesti lapsen ja nuoren asema ja tarpeet (Ero lapsiperheessä työ) (170 451 €) | Ak 2: Lapsiperheitä tukevaan järjestölähtöiseen avopalvelutoimintaan (Vauvaperheohjaus  Kohtaamispaikka Perhetupa- ja mieskaveritoiminta sekä vapaaehtoisdoula-toiminta erityistä tukea tarvitseville lapsiperheille) (167 229 €)</t>
+          <t>Ak 1221: Erokriisissä olevien perheiden auttamiseen ja tukemiseen sekä ennaltaehkäisemään erojen konfliktoitumista ja huoltoriitoja vertaisryhmätoiminnan  asiakastyön ja erotukihenkilötoiminnan keinoin huomioiden erityisesti lapsen ja nuoren asema ja tarpeet (Ero lapsiperheessä työ) (170 451 €) | Ak 2: Lapsiperheitä tukevaan järjestölähtöiseen avopalvelutoimintaan (Vauvaperheohjaus  Kohtaamispaikka Perhetupa- ja mieskaveritoiminta sekä vapaaehtoisdoula-toiminta erityistä tukea tarvitseville lapsiperheille) (167 229 €) | Ak 12306: Kodin ulkopuoliseen väkivaltaan syyllistyneiden tai syyllistymisriskissä olevien väkivaltaisen käyttäytymisen vähentämiseen ja ehkäisemiseen yksilöllisen asiakastyön ja verkostotyön avulla (Aggredi Päijät-Häme) (160 000 €)</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="I52" t="inlineStr" s="0">
         <is>
-          <t>Ak 4465: Sydänterveyden ja toimintakyvyn edistämiseen tiedonvälityksen  vertaistuen ja ammattilaisten koulutuksen keinoin (340 142 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (478 151 €) | Ak 3: Sydänpiirien ja valtakunnallisten sydänyhdistysten järjestämiin toimintakykyä ja vertaistukea edistäviin etä- tai lähikursseihin sydänsairastuneiden ja heidän läheistensä tueksi (377 895 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (478 151 €) | Ak 3: Sydänpiirien ja valtakunnallisten sydänyhdistysten järjestämiin toimintakykyä ja vertaistukea edistäviin etä- tai lähikursseihin sydänsairastuneiden ja heidän läheistensä tueksi (377 895 €) | Ak 4465: Sydänterveyden ja toimintakyvyn edistämiseen tiedonvälityksen  vertaistuen ja ammattilaisten koulutuksen keinoin (340 142 €)</t>
         </is>
       </c>
     </row>
@@ -4949,11 +4949,11 @@
       </c>
       <c r="I53" t="inlineStr" s="0">
         <is>
-          <t>C 13827: Kansalaisuus  tasa-arvo  perusoikeudet ja arvot -rahoitusohjelman (CERV) hankkeen "Riza" osarahoitukseen järjestölle (2026-2028) (46 300 €) | Ak 7: Maahan muuttaneiden naisten osallisuuden  toimijuuden ja työelämävalmiuksien edistämiseen matalan kynnyksen toiminnalla pääkaupunkiseudulla.
+          <t>Ak 2: Väkivaltaa tai sen uhkaa kokeneiden maahan muuttaneiden naisten matalan kynnyksen kriisiauttamiseen  ihmiskaupan vastaiseen työhön ja lasten tukemiseen turvakotijakson jälkeen. 
+Toimintamuotoina matalan kynnyksen palveluohjaus ja neuvonta  yksilöllinen tuki  kriisityö  maksuton auttava puhelin  verkkoauttaminen  vertaistukitoiminta sekä asiantuntija- ja vaikuttamistyö
+(Kriisikeskus Monika) (487 396 €) | Ak 7: Maahan muuttaneiden naisten osallisuuden  toimijuuden ja työelämävalmiuksien edistämiseen matalan kynnyksen toiminnalla pääkaupunkiseudulla.
 Toimintamuotoina yksilöohjaus ja neuvonta  vertaisryhmä- ja vapaaehtoistoiminta sekä asiantuntija- ja verkostotyö
-(Kotoutumiskeskus Monika) (293 786 €) | Ak 2: Väkivaltaa tai sen uhkaa kokeneiden maahan muuttaneiden naisten matalan kynnyksen kriisiauttamiseen  ihmiskaupan vastaiseen työhön ja lasten tukemiseen turvakotijakson jälkeen. 
-Toimintamuotoina matalan kynnyksen palveluohjaus ja neuvonta  yksilöllinen tuki  kriisityö  maksuton auttava puhelin  verkkoauttaminen  vertaistukitoiminta sekä asiantuntija- ja vaikuttamistyö
-(Kriisikeskus Monika) (487 396 €)</t>
+(Kotoutumiskeskus Monika) (293 786 €) | C 13827: Kansalaisuus  tasa-arvo  perusoikeudet ja arvot -rahoitusohjelman (CERV) hankkeen "Riza" osarahoitukseen järjestölle (2026-2028) (46 300 €)</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="I54" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Jäsenjärjestöille kohdistettaviin avustuksiin (88 600 €) | Ak 6: Allergiaa  astmaa ja ihotauteja sairastavien sekä palovamman kokeneiden ja heidän läheistensä hyvinvoinnin sekä työ- ja toimintakyvyn edistämiseen ja ylläpitämiseen internaatti- ja avomuotoisten sekä verkossa toteutettavien kurssien avulla (368 382 €) | Ay 2: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (700 875 €)</t>
+          <t>Ay 2: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (700 875 €) | Ak 6: Allergiaa  astmaa ja ihotauteja sairastavien sekä palovamman kokeneiden ja heidän läheistensä hyvinvoinnin sekä työ- ja toimintakyvyn edistämiseen ja ylläpitämiseen internaatti- ja avomuotoisten sekä verkossa toteutettavien kurssien avulla (368 382 €) | Ak 3: Jäsenjärjestöille kohdistettaviin avustuksiin (88 600 €)</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="I55" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (750 910 €) | Ak 4: Jäsenjärjestöille kohdistettaviin avustuksiin (73 296 €) | Ak 5: Epilepsiaa sairastavien ihmisten ja heidän läheistensä hyvinvointia ja toimintakykyä tukevaan tavoitteelliseen vertaistuki-  ryhmä- ja kurssitoimintaan valtakunnallisesti ja alueellisesti verkko- ja lähitapaamisina (301 140 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (750 910 €) | Ak 5: Epilepsiaa sairastavien ihmisten ja heidän läheistensä hyvinvointia ja toimintakykyä tukevaan tavoitteelliseen vertaistuki-  ryhmä- ja kurssitoimintaan valtakunnallisesti ja alueellisesti verkko- ja lähitapaamisina (301 140 €) | Ak 4: Jäsenjärjestöille kohdistettaviin avustuksiin (73 296 €)</t>
         </is>
       </c>
     </row>
@@ -5085,8 +5085,8 @@
       </c>
       <c r="I57" t="inlineStr" s="0">
         <is>
-          <t>Ak 6: Jäsenjärjestöille kohdistettaviin avustuksiin (75 000 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (720 248 €) | Ak 8: OmaisOiva-toiminnan valtakunnalliseen koordinointiin  tukemiseen sekä arviointiin ja kehittämiseen. OmaisOiva-toimintaa toteuttavat Omaishoitajaliiton jäsenyhdistykset 
-(OmaisOiva) (269 010 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (720 248 €) | Ak 8: OmaisOiva-toiminnan valtakunnalliseen koordinointiin  tukemiseen sekä arviointiin ja kehittämiseen. OmaisOiva-toimintaa toteuttavat Omaishoitajaliiton jäsenyhdistykset 
+(OmaisOiva) (269 010 €) | Ak 6: Jäsenjärjestöille kohdistettaviin avustuksiin (75 000 €)</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="I59" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (581 943 €) | Ak 12: Jäsenjärjestöille kohdistettaviin avustuksiin (49 614 €) | Ak 7: Muistiyhdistysten ja niihin kuuluvien Muistiluotsiasiantuntija- ja tukikeskusten koordinoimiseen  asiantuntijatyön ja vapaaehtoistoiminnan tukemiseen sekä muistisairaiden ja heidän läheistensä puhelinneuvonnan (MuistiNeuvo) koordinoimiseen valtakunnallisesti. (418 145 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (581 943 €) | Ak 7: Muistiyhdistysten ja niihin kuuluvien Muistiluotsiasiantuntija- ja tukikeskusten koordinoimiseen  asiantuntijatyön ja vapaaehtoistoiminnan tukemiseen sekä muistisairaiden ja heidän läheistensä puhelinneuvonnan (MuistiNeuvo) koordinoimiseen valtakunnallisesti. (418 145 €) | Ak 12: Jäsenjärjestöille kohdistettaviin avustuksiin (49 614 €)</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="I61" t="inlineStr" s="0">
         <is>
-          <t>Ak 2535: Ikääntyneiden mielen hyvinvoinnin lisäämiseen sekä yksinäisyyden kokemusten vähentämiseen vapaaehtoisten osaamista edistämällä (Elinvoimaa) (132 200 €) | Ak 4497: Ikääntyneiden itsenäisen arjessa selviytymisen tukemiseen  syrjäytymisen ehkäisyyn ja osallisuuden lisäämiseen digitalisoituvassa yhteiskunnassa kouluttamalla vertaisohjaajia sekä järjestämällä koulutustilaisuuksia ja tapahtumia (Verkosta virtaa - ikääntyneiden itsenäinen selviytyminen digitalisoituvassa yhteiskunnassa) (154 350 €) | Ak 1398: Jäsenjärjestöille kohdistettaviin avustuksiin (78 000 €)</t>
+          <t>Ak 4497: Ikääntyneiden itsenäisen arjessa selviytymisen tukemiseen  syrjäytymisen ehkäisyyn ja osallisuuden lisäämiseen digitalisoituvassa yhteiskunnassa kouluttamalla vertaisohjaajia sekä järjestämällä koulutustilaisuuksia ja tapahtumia (Verkosta virtaa - ikääntyneiden itsenäinen selviytyminen digitalisoituvassa yhteiskunnassa) (154 350 €) | Ak 2535: Ikääntyneiden mielen hyvinvoinnin lisäämiseen sekä yksinäisyyden kokemusten vähentämiseen vapaaehtoisten osaamista edistämällä (Elinvoimaa) (132 200 €) | Ak 1398: Jäsenjärjestöille kohdistettaviin avustuksiin (78 000 €)</t>
         </is>
       </c>
     </row>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="I62" t="inlineStr" s="0">
         <is>
-          <t>Ay 4: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (365 773 €) | Ak 5708: Seksuaalirikosten uhrien sekä heidän läheistensä järjestölähtöiseen tukeen ja oikeuksien neuvontaan yksilö-  ryhmä-  verkko- ja puhelinauttamisen keinoin Helsingissä  Jyväskylässä  Lappeenrannassa ja Rovaniemellä. Ammattilaisten neuvontaan ja koulutukseen. (636 906 €)</t>
+          <t>Ak 5708: Seksuaalirikosten uhrien sekä heidän läheistensä järjestölähtöiseen tukeen ja oikeuksien neuvontaan yksilö-  ryhmä-  verkko- ja puhelinauttamisen keinoin Helsingissä  Jyväskylässä  Lappeenrannassa ja Rovaniemellä. Ammattilaisten neuvontaan ja koulutukseen. (636 906 €) | Ay 4: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (365 773 €)</t>
         </is>
       </c>
     </row>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="I63" t="inlineStr" s="0">
         <is>
-          <t>Ak 6192: För att främja kommunikativt och specialpedagogiskt tillgängliga miljöer för barn  unga och vuxna med funktionsvariation eller andra särskilda behov och stöda dem med kamratstödsgrupper och konsultationer  och för att utveckla alternativ och kompletterande kommunikation (AKK)  specialpedagogik och informations- och kommunikationsteknologi (IKT) och sprida dem i samhället (179 444 €) | Ay 1: Som allmänt understöd för understödstagarens allmännyttiga verksamhet (214 944 €) | Ak 6181: För att stöda funktionsförmågan hos barn med funktionsvariation samt för att stöda familjerna i en utmanande livssituation med hjälp av kursverksamhet (103 889 €)</t>
+          <t>Ay 1: Som allmänt understöd för understödstagarens allmännyttiga verksamhet (214 944 €) | Ak 6192: För att främja kommunikativt och specialpedagogiskt tillgängliga miljöer för barn  unga och vuxna med funktionsvariation eller andra särskilda behov och stöda dem med kamratstödsgrupper och konsultationer  och för att utveckla alternativ och kompletterande kommunikation (AKK)  specialpedagogik och informations- och kommunikationsteknologi (IKT) och sprida dem i samhället (179 444 €) | Ak 6181: För att stöda funktionsförmågan hos barn med funktionsvariation samt för att stöda familjerna i en utmanande livssituation med hjälp av kursverksamhet (103 889 €)</t>
         </is>
       </c>
     </row>
@@ -5317,8 +5317,8 @@
       </c>
       <c r="I64" t="inlineStr" s="0">
         <is>
-          <t>Ak 10386: Maahanmuuttajataustaisten naisten ja heidän lähiyhteisöjensä hyvinvoinnin  osallisuuden ja toimijuuden edistämiseen Naapuriäiti-toiminnan avulla (353 780 €) | Ak 1368: Tukea tarvitsevien ja syrjäytymisvaarassa olevien tyttöjen ja nuorten naisten sosiaaliseen vahvistamiseen sekä osallisuuden ja yhteisöllisyyden edistämiseen matalan kynnyksen kohtaamispaikkatoiminnan  vertaistukiryhmien  psykososiaalisen tuen  seksuaalineuvonnan ja jalkautuvan työn sekä yhteistyön avulla Vantaalla ja Lappeenrannassa 
-(Tyttöjen Tila) (377 078 €) | Ak 2: Haavoittuvassa asemassa olevien maahan muuttaneiden ja romanitaustaisten naisten sosiaaliseen vahvistumiseen  syrjäytymisen ehkäisemiseen sekä yhteisöllisyyden lisäämiseen matalan kynnyksen yksilöllisen tuen ja palveluohjauksen sekä vertaisryhmä- ja vapaaehtoistoiminnan ja väkivaltatyön avulla 
+          <t>Ak 1368: Tukea tarvitsevien ja syrjäytymisvaarassa olevien tyttöjen ja nuorten naisten sosiaaliseen vahvistamiseen sekä osallisuuden ja yhteisöllisyyden edistämiseen matalan kynnyksen kohtaamispaikkatoiminnan  vertaistukiryhmien  psykososiaalisen tuen  seksuaalineuvonnan ja jalkautuvan työn sekä yhteistyön avulla Vantaalla ja Lappeenrannassa 
+(Tyttöjen Tila) (377 078 €) | Ak 10386: Maahanmuuttajataustaisten naisten ja heidän lähiyhteisöjensä hyvinvoinnin  osallisuuden ja toimijuuden edistämiseen Naapuriäiti-toiminnan avulla (353 780 €) | Ak 2: Haavoittuvassa asemassa olevien maahan muuttaneiden ja romanitaustaisten naisten sosiaaliseen vahvistumiseen  syrjäytymisen ehkäisemiseen sekä yhteisöllisyyden lisäämiseen matalan kynnyksen yksilöllisen tuen ja palveluohjauksen sekä vertaisryhmä- ja vapaaehtoistoiminnan ja väkivaltatyön avulla 
 (Wahva Nainen) (253 575 €)</t>
         </is>
       </c>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="I66" t="inlineStr" s="0">
         <is>
-          <t>Ak 10758: Kodin ulkopuoliseen väkivaltaan  syyllistyneiden tai syyllistymisriskissä olevien väkivaltaisen käyttäytymisen vähentämiseen ja ehkäisemiseen yksilöllisen asiakastyön ja verkostotyön avulla (Aggredi Pirkanmaa) (241 500 €) | Ak 6: Lapsiperheiden hyvinvoinnin ylläpitämiseen ja edistämiseen sekä lasten kasvun ja vanhemmuuden tukemiseen ja perheiden tilanteiden heikentymisen/kriisiytymisen ennalta ehkäisemiseen alueellisen kohtaamispaikkatoiminnan keinoin kolmella perhetuvalla Tampereella (361 693 €) | Ak 9: Yksilö- ja perhemuotoiseen avokriisityöhön perhe- ja lähisuhdeväkivallan kokijoiden ja tekijöiden kanssa (lasten ja nuorten yksilötyö  0-3-vuotiaiden lasten perheiden kanssa tehtävä väkivaltatyö ja väkivallan eri osapuolten kanssa tehtävä työ) sekä perheiden tukemiseen uniohjauksen  eroauttamisen ja vapaaehtoisuuteen perustuvan mieskaveritoiminnan keinoin (251 404 €)</t>
+          <t>Ak 6: Lapsiperheiden hyvinvoinnin ylläpitämiseen ja edistämiseen sekä lasten kasvun ja vanhemmuuden tukemiseen ja perheiden tilanteiden heikentymisen/kriisiytymisen ennalta ehkäisemiseen alueellisen kohtaamispaikkatoiminnan keinoin kolmella perhetuvalla Tampereella (361 693 €) | Ak 9: Yksilö- ja perhemuotoiseen avokriisityöhön perhe- ja lähisuhdeväkivallan kokijoiden ja tekijöiden kanssa (lasten ja nuorten yksilötyö  0-3-vuotiaiden lasten perheiden kanssa tehtävä väkivaltatyö ja väkivallan eri osapuolten kanssa tehtävä työ) sekä perheiden tukemiseen uniohjauksen  eroauttamisen ja vapaaehtoisuuteen perustuvan mieskaveritoiminnan keinoin (251 404 €) | Ak 10758: Kodin ulkopuoliseen väkivaltaan  syyllistyneiden tai syyllistymisriskissä olevien väkivaltaisen käyttäytymisen vähentämiseen ja ehkäisemiseen yksilöllisen asiakastyön ja verkostotyön avulla (Aggredi Pirkanmaa) (241 500 €)</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="I67" t="inlineStr" s="0">
         <is>
-          <t>Ay 3244: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (282 724 €) | Ak 1: Yksilö-  pari-  perhe- ja ryhmämuotoiseen avokriisityöhön perhe- ja lähisuhdeväkivallan uhrien ja tekijöiden kanssa (Lähisuhdeväkivaltatyön avopalvelut Etelä-Savon hyvinvointialueella) (160 634 €) | Ak 3: Miesten hyvinvoinnin lisäämiseen ja vaikeuksien ennaltaehkäisemiseen ryhmä- ja yksilötoiminnan keinoin (Miesten asema -toiminta) sekä pikkulapsiperheiden hyvinvoinnin edistämiseen ja vaikeuksien ennaltaehkäisyyn (Jalkautuva vanhemmuusasema -toiminta) (228 837 €)</t>
+          <t>Ay 3244: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (282 724 €) | Ak 3: Miesten hyvinvoinnin lisäämiseen ja vaikeuksien ennaltaehkäisemiseen ryhmä- ja yksilötoiminnan keinoin (Miesten asema -toiminta) sekä pikkulapsiperheiden hyvinvoinnin edistämiseen ja vaikeuksien ennaltaehkäisyyn (Jalkautuva vanhemmuusasema -toiminta) (228 837 €) | Ak 1: Yksilö-  pari-  perhe- ja ryhmämuotoiseen avokriisityöhön perhe- ja lähisuhdeväkivallan uhrien ja tekijöiden kanssa (Lähisuhdeväkivaltatyön avopalvelut Etelä-Savon hyvinvointialueella) (160 634 €)</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="I69" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (696 425 €) | Ak 14: Jäsenjärjestöille kohdistettaviin avustuksiin (10 000 €) | Ak 7: Lihastautia sairastavien henkilöiden yhdenvertaisuuden ja osallisuuden edistämiseen koulu- ja työelämässä. Toimintamuotoina yksilöllinen neuvonta  ryhmät  tapahtumat  viestintä  vaikuttamistyö ja oikeuksien valvonta. (60 638 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (696 425 €) | Ak 7: Lihastautia sairastavien henkilöiden yhdenvertaisuuden ja osallisuuden edistämiseen koulu- ja työelämässä. Toimintamuotoina yksilöllinen neuvonta  ryhmät  tapahtumat  viestintä  vaikuttamistyö ja oikeuksien valvonta. (60 638 €) | Ak 14: Jäsenjärjestöille kohdistettaviin avustuksiin (10 000 €)</t>
         </is>
       </c>
     </row>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="I70" t="inlineStr" s="0">
         <is>
-          <t>Ak 7: Jäsenjärjestöille kohdistettaviin avustuksiin (18 800 €) | Ak 2: Adhd-oireisten ja heidän läheistensä psyykkisen  sosiaalisen ja fyysisen hyvinvoinnin tukemiseen ryhmämuotoisen  tavoitteellisen ja vertaistuellisen kurssitoiminnan avulla (190 071 €) | Ak 1341: Vertais- ja kokemustoimintaan adhd-oireisten ja heidän läheistensä osallisuuden ja hyvinvoinnin vahvistamiseksi sekä tietoisuuden lisäämiseen adhd-oirekuvasta (179 000 €)</t>
+          <t>Ak 2: Adhd-oireisten ja heidän läheistensä psyykkisen  sosiaalisen ja fyysisen hyvinvoinnin tukemiseen ryhmämuotoisen  tavoitteellisen ja vertaistuellisen kurssitoiminnan avulla (190 071 €) | Ak 1341: Vertais- ja kokemustoimintaan adhd-oireisten ja heidän läheistensä osallisuuden ja hyvinvoinnin vahvistamiseksi sekä tietoisuuden lisäämiseen adhd-oirekuvasta (179 000 €) | Ak 7: Jäsenjärjestöille kohdistettaviin avustuksiin (18 800 €)</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="I73" t="inlineStr" s="0">
         <is>
-          <t>Ak 4: Vapaaehtois- ja kansalaistoiminnan koordinointiin eriarvoisuuden vähentämiseksi ja vapaaehtoisten osallisuuden ja toimijuuden vahvistamiseksi (2026) (70 000 €) | Ak 12: Suur-Matinkylän alueen asukkaiden elämänlaadun ja osallisuuden vahvistamiseen  yksinäisyyden kokemuksen vähentämiseen sekä alueellisen turvallisuuden edistämiseen (Naapuruustalo Matinkylä) (125 631 €) | Ak 10: Pasilan alueen asukkaiden psyykkisen  fyysisen ja sosiaalisen hyvinvoinnin sekä alueellisen turvallisuuden ja hyvinvoinnin edistämiseen (Naapuruustalo Pasila) (179 437 €)</t>
+          <t>Ak 10: Pasilan alueen asukkaiden psyykkisen  fyysisen ja sosiaalisen hyvinvoinnin sekä alueellisen turvallisuuden ja hyvinvoinnin edistämiseen (Naapuruustalo Pasila) (179 437 €) | Ak 12: Suur-Matinkylän alueen asukkaiden elämänlaadun ja osallisuuden vahvistamiseen  yksinäisyyden kokemuksen vähentämiseen sekä alueellisen turvallisuuden edistämiseen (Naapuruustalo Matinkylä) (125 631 €) | Ak 4: Vapaaehtois- ja kansalaistoiminnan koordinointiin eriarvoisuuden vähentämiseksi ja vapaaehtoisten osallisuuden ja toimijuuden vahvistamiseksi (2026) (70 000 €)</t>
         </is>
       </c>
     </row>
@@ -5649,7 +5649,7 @@
       </c>
       <c r="I74" t="inlineStr" s="0">
         <is>
-          <t>Ak 10302: Perheen tukemiseen eroa harkitessa tai erottaessa sekä lähisuhdeväkivallan ennaltaehkäisyyn  loppumiseen ja kokemuksista toipumiseen tarjoamalla tukea avopalvelun keinoin Pohjois-Savon alueella (Ero- ja väkivaltatyön avopalvelu) (262 119 €) | Ak 5846: Vauvaperheiden päihteettömän ja turvallisen arjen vahvistamiseen sekä päihteiden aiheuttamien haittojen ehkäisemiseen vauvalle kohtaavan etsivän ja matalan kynnyksen työllä  ja yhteisöllisellä vertaisryhmä-  perhe- ja yksilötyöskentelyllä. Tavoitteena on tukea vauvan ja vanhemman välistä vuorovaikutusta sekä edistää vauvaperheiden osallisuutta. (Pidä kiinni –hoitojärjestelmän avopalveluyksikkö Amalia 2026) (287 300 €) | C 13781: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Arjen ymmärrys – Tukea vanhemmille neurokirjolla" osarahoitukseen järjestölle (2026-2027) (37 560 €)</t>
+          <t>Ak 5846: Vauvaperheiden päihteettömän ja turvallisen arjen vahvistamiseen sekä päihteiden aiheuttamien haittojen ehkäisemiseen vauvalle kohtaavan etsivän ja matalan kynnyksen työllä  ja yhteisöllisellä vertaisryhmä-  perhe- ja yksilötyöskentelyllä. Tavoitteena on tukea vauvan ja vanhemman välistä vuorovaikutusta sekä edistää vauvaperheiden osallisuutta. (Pidä kiinni –hoitojärjestelmän avopalveluyksikkö Amalia 2026) (287 300 €) | Ak 10302: Perheen tukemiseen eroa harkitessa tai erottaessa sekä lähisuhdeväkivallan ennaltaehkäisyyn  loppumiseen ja kokemuksista toipumiseen tarjoamalla tukea avopalvelun keinoin Pohjois-Savon alueella (Ero- ja väkivaltatyön avopalvelu) (262 119 €) | C 13781: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Arjen ymmärrys – Tukea vanhemmille neurokirjolla" osarahoitukseen järjestölle (2026-2027) (37 560 €)</t>
         </is>
       </c>
     </row>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="I76" t="inlineStr" s="0">
         <is>
-          <t>Ak 10413: Kriisiytymisuhassa olevien lasten ja perheiden tukeen strukturoidun lasten leiritoiminnan avulla (Näe hyvä mussa -toiminta) (207 270 €) | Ak 2: Lasten lomatoimintaan (Parasta Lapsille ry ja paikallisyhdistykset) sekä valtakunnalliseen lasten ja perheiden toimintaan terveyden ja hyvinvoinnin edistämiseksi (483 372 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (203 608 €)</t>
+          <t>Ak 2: Lasten lomatoimintaan (Parasta Lapsille ry ja paikallisyhdistykset) sekä valtakunnalliseen lasten ja perheiden toimintaan terveyden ja hyvinvoinnin edistämiseksi (483 372 €) | Ak 10413: Kriisiytymisuhassa olevien lasten ja perheiden tukeen strukturoidun lasten leiritoiminnan avulla (Näe hyvä mussa -toiminta) (207 270 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (203 608 €)</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="I77" t="inlineStr" s="0">
         <is>
-          <t>Ak 1527: Sosiaali- ja terveysalan järjestöjen oman toiminnan systemaattiseen kehittämiseen tukemalla järjestöjä arvioinnin kehittämisessä sekä vaikutusketjujen ja konkreettisten arviointi- ja seurantatyökalujen luomisessa (Artsi-toiminta - sosiaali- ja terveysalan järjestöjen oman toiminnan systemaattiseen arviointiin ja kehittämiseen) (143 449 €) | Ay 9: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (480 810 €) | Ak 4394: Oppimisen ja mielenterveyden ongelmia koskevan tiedon tuottamiseen  kokoamiseen ja levittämiseen  ammattilaisten tukemiseen sekä matalan kynnyksen tuen tarjoamiseen oppimisvaikeuksia ja mielenterveyden ongelmia kokeville henkilöille (277 753 €)</t>
+          <t>Ay 9: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (480 810 €) | Ak 4394: Oppimisen ja mielenterveyden ongelmia koskevan tiedon tuottamiseen  kokoamiseen ja levittämiseen  ammattilaisten tukemiseen sekä matalan kynnyksen tuen tarjoamiseen oppimisvaikeuksia ja mielenterveyden ongelmia kokeville henkilöille (277 753 €) | Ak 1527: Sosiaali- ja terveysalan järjestöjen oman toiminnan systemaattiseen kehittämiseen tukemalla järjestöjä arvioinnin kehittämisessä sekä vaikutusketjujen ja konkreettisten arviointi- ja seurantatyökalujen luomisessa (Artsi-toiminta - sosiaali- ja terveysalan järjestöjen oman toiminnan systemaattiseen arviointiin ja kehittämiseen) (143 449 €)</t>
         </is>
       </c>
     </row>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="I78" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Lapsiperheiden ja maahanmuuttajaäitien osallisuuden ja vanhemmuuden vahvistamiseen  yksinäisyyden vähentämiseen sekä lasten lukusujuvuuden parantamiseen ammatillisesti ohjatun tukihenkilötoiminnan keinoin (Perhekummi-  Ystäväksi maahanmuuttajaäidille- sekä mummi- ja vaaritoiminta) (445 339 €) | Ak 11317: Lapsiperheiden ennaltaehkäisevän tuen ja osallisuuden vahvistamiseen järjestämällä kaupungin ja järjestöjen yhdessä johtamaa ja ylläpitämää avointa kohtaamispaikkatoimintaa sekä kohtaamispaikkatoiminnan kehittämiseen Uudellamaalla. (199 080 €) | Ak 10194: Haavoittuvassa asemassa olevien lapsiperheiden vanhempien vanhemmuuden tukemiseen ammatillisesti ohjatun avoimen ryhmätoiminnan  monikulttuurisen ryhmätoiminnan  etsivän perhetyön ja yksilöohjauksen avulla. (204 750 €)</t>
+          <t>Ak 2: Lapsiperheiden ja maahanmuuttajaäitien osallisuuden ja vanhemmuuden vahvistamiseen  yksinäisyyden vähentämiseen sekä lasten lukusujuvuuden parantamiseen ammatillisesti ohjatun tukihenkilötoiminnan keinoin (Perhekummi-  Ystäväksi maahanmuuttajaäidille- sekä mummi- ja vaaritoiminta) (445 339 €) | Ak 10194: Haavoittuvassa asemassa olevien lapsiperheiden vanhempien vanhemmuuden tukemiseen ammatillisesti ohjatun avoimen ryhmätoiminnan  monikulttuurisen ryhmätoiminnan  etsivän perhetyön ja yksilöohjauksen avulla. (204 750 €) | Ak 11317: Lapsiperheiden ennaltaehkäisevän tuen ja osallisuuden vahvistamiseen järjestämällä kaupungin ja järjestöjen yhdessä johtamaa ja ylläpitämää avointa kohtaamispaikkatoimintaa sekä kohtaamispaikkatoiminnan kehittämiseen Uudellamaalla. (199 080 €)</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="I79" t="inlineStr" s="0">
         <is>
-          <t>Ak 12: Pitkäaikaissairaiden kuurojen  kuurosokeiden ja heidän läheistensä viittomakieliseen vertaisryhmätoimintaan  terveyteen ja hyvinvointiin liittyvään tukeen ja tiedonsaantiin sekä Viittomakielisen Auttavan Linjan toteuttamiseen (Passi) (87 150 €) | Ay 21: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (92 400 €) | Ak 17: Vaikeassa työmarkkina-asemassa olevien viittomakielisten kuurojen ja kuurosokeiden työelämävalmiuksien  työelämätaitojen  opiskelun ja arjenhallinnan edistämiseen viittomakielisen yksilö- ja ryhmämuotoisen työvalmennuksen ja verkostoyhteistyön avulla (Poveri) (304 500 €)</t>
+          <t>Ak 17: Vaikeassa työmarkkina-asemassa olevien viittomakielisten kuurojen ja kuurosokeiden työelämävalmiuksien  työelämätaitojen  opiskelun ja arjenhallinnan edistämiseen viittomakielisen yksilö- ja ryhmämuotoisen työvalmennuksen ja verkostoyhteistyön avulla (Poveri) (304 500 €) | Ay 21: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (92 400 €) | Ak 12: Pitkäaikaissairaiden kuurojen  kuurosokeiden ja heidän läheistensä viittomakieliseen vertaisryhmätoimintaan  terveyteen ja hyvinvointiin liittyvään tukeen ja tiedonsaantiin sekä Viittomakielisen Auttavan Linjan toteuttamiseen (Passi) (87 150 €)</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="I81" t="inlineStr" s="0">
         <is>
-          <t>Ak 7: Erityistä tukea tarvitsevien tyttöjen  nuorten naisten ja sukupuoli-identiteettiään pohtivien hyvinvoinnin ja osallisuuden tukemiseen  seksuaaliterveyden edistämiseen sekä seksuaaliväkivaltatyöhön (220 000 €) | Ak 4087: Kodin ulkopuoliseen väkivaltaan syyllistyneiden tai syyllistymisriskissä olevien väkivaltaisen käyttäytymisen vähentämiseen ja ehkäisemiseen yksilöllisen asiakastyön ja verkostotyön avulla (Aggredi Kuopio) (155 000 €) | Ak 3: Maahanmuuttajien osallisuutta  yhteisöllisyyttä ja kaksisuuntaista kotoutumista edistävään toimintaan (Kompassi) (294 052 €)</t>
+          <t>Ak 3: Maahanmuuttajien osallisuutta  yhteisöllisyyttä ja kaksisuuntaista kotoutumista edistävään toimintaan (Kompassi) (294 052 €) | Ak 7: Erityistä tukea tarvitsevien tyttöjen  nuorten naisten ja sukupuoli-identiteettiään pohtivien hyvinvoinnin ja osallisuuden tukemiseen  seksuaaliterveyden edistämiseen sekä seksuaaliväkivaltatyöhön (220 000 €) | Ak 4087: Kodin ulkopuoliseen väkivaltaan syyllistyneiden tai syyllistymisriskissä olevien väkivaltaisen käyttäytymisen vähentämiseen ja ehkäisemiseen yksilöllisen asiakastyön ja verkostotyön avulla (Aggredi Kuopio) (155 000 €)</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="I83" t="inlineStr" s="0">
         <is>
-          <t>Ay 2675: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (178 453 €) | Ak 1: Naisten ja nuorten naisten käyttämän väkivallan ja ylisukupolvisen väkivallan ehkäisyyn lähi- ja verkkotoimintana  yksilö-  pariskunta- ja ryhmätoiminnan sekä ammattilaisille suunnatun toiminnan keinoin. Kohderyhmät 15 ikävuodesta alkaen. (627 770 €)</t>
+          <t>Ak 1: Naisten ja nuorten naisten käyttämän väkivallan ja ylisukupolvisen väkivallan ehkäisyyn lähi- ja verkkotoimintana  yksilö-  pariskunta- ja ryhmätoiminnan sekä ammattilaisille suunnatun toiminnan keinoin. Kohderyhmät 15 ikävuodesta alkaen. (627 770 €) | Ay 2675: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (178 453 €)</t>
         </is>
       </c>
     </row>
@@ -5979,10 +5979,10 @@
       </c>
       <c r="I84" t="inlineStr" s="0">
         <is>
-          <t>Ak 16: Jäsenjärjestöille kohdistettaviin avustuksiin (49 000 €) | Ak 9: Vertaisuutta korostavaan ryhmämuotoiseen tukeen internaatti-  avo- ja verkkokurssien avulla 
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (547 010 €) | Ak 9: Vertaisuutta korostavaan ryhmämuotoiseen tukeen internaatti-  avo- ja verkkokurssien avulla 
 - perheille  joissa on psoriasista sairastava 5–15-vuotias lapsi  
 - työikäisille iho- tai nivelpsoriasista sairastaville ja heidän läheisilleen ja
-- yli 60-vuotiaille eläkkeellä oleville psoriasista sairastaville (210 000 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (547 010 €)</t>
+- yli 60-vuotiaille eläkkeellä oleville psoriasista sairastaville (210 000 €) | Ak 16: Jäsenjärjestöille kohdistettaviin avustuksiin (49 000 €)</t>
         </is>
       </c>
     </row>
@@ -6015,7 +6015,7 @@
       </c>
       <c r="I85" t="inlineStr" s="0">
         <is>
-          <t>Ak 10605: Psyykkistä kuormitusta kokeneiden lapsiperheiden hyvinvoinnin parantamiseen yksilöllisellä tuella  vertaistuella ja kohtaamispaikkatoiminnalla Oulussa (115 000 €) | Ak 7331: Mielenterveyskuntoutujien kokemusasiantuntija- ja vertaistoiminnan vahvistamiseen koulutuksilla sekä kokemustiedon levittämiseen Oulussa (110 000 €) | Ay 1998: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (263 088 €)</t>
+          <t>Ay 1998: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (263 088 €) | Ak 10605: Psyykkistä kuormitusta kokeneiden lapsiperheiden hyvinvoinnin parantamiseen yksilöllisellä tuella  vertaistuella ja kohtaamispaikkatoiminnalla Oulussa (115 000 €) | Ak 7331: Mielenterveyskuntoutujien kokemusasiantuntija- ja vertaistoiminnan vahvistamiseen koulutuksilla sekä kokemustiedon levittämiseen Oulussa (110 000 €)</t>
         </is>
       </c>
     </row>
@@ -6081,7 +6081,7 @@
       </c>
       <c r="I87" t="inlineStr" s="0">
         <is>
-          <t>Ak 8: Järjestölähtöiseen kriisi- ja mielenterveystyöhön vaikeissa elämäntilanteissa oleville tarjoamalla matalan kynnyksen keskusteluapua  ammatillisesti ohjattuja ryhmiä Lapin hyvinvointialueella  tukihenkilötoimintaan sekä vapaaehtoisten koulutukseen ja koordinointiin sekä tiedottamiseen toiminnasta ja tapahtumien järjestämiseen (Lapin ensi- ja turvakoti ry:n kriisikeskus) (200 899 €) | Ak 4: Lasta odottavien  vauva- ja pikkulapsiperheiden vanhempien tukeen sekä neuvontaan odotusajan  vauvan uni- ja vuorokausirytmin  lasten ja vanhempien välisen vuorovaikutus- ja kiintymyssuhteen sekä kuormittavan perhe-elämän haasteissa yksilöllisen tuen  vertaisryhmä- sekä vapaaehtoistoiminnan avulla (131 314 €) | Ak 9: Aikuisten  lasten ja nuorten lähisuhteisiin  lähisuhdeväkivaltaan ja perheen sisäiseen vuorovaikutukseen liittyvien ongelmien ehkäisyyn sekä niistä selviytymiseen yksilö-  pari- ja perhetapaamisten sekä ryhmätoiminnan keinoin (Lähisuhde- ja väkivaltatyön avopalvelu) (247 144 €)</t>
+          <t>Ak 9: Aikuisten  lasten ja nuorten lähisuhteisiin  lähisuhdeväkivaltaan ja perheen sisäiseen vuorovaikutukseen liittyvien ongelmien ehkäisyyn sekä niistä selviytymiseen yksilö-  pari- ja perhetapaamisten sekä ryhmätoiminnan keinoin (Lähisuhde- ja väkivaltatyön avopalvelu) (247 144 €) | Ak 8: Järjestölähtöiseen kriisi- ja mielenterveystyöhön vaikeissa elämäntilanteissa oleville tarjoamalla matalan kynnyksen keskusteluapua  ammatillisesti ohjattuja ryhmiä Lapin hyvinvointialueella  tukihenkilötoimintaan sekä vapaaehtoisten koulutukseen ja koordinointiin sekä tiedottamiseen toiminnasta ja tapahtumien järjestämiseen (Lapin ensi- ja turvakoti ry:n kriisikeskus) (200 899 €) | Ak 4: Lasta odottavien  vauva- ja pikkulapsiperheiden vanhempien tukeen sekä neuvontaan odotusajan  vauvan uni- ja vuorokausirytmin  lasten ja vanhempien välisen vuorovaikutus- ja kiintymyssuhteen sekä kuormittavan perhe-elämän haasteissa yksilöllisen tuen  vertaisryhmä- sekä vapaaehtoistoiminnan avulla (131 314 €)</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="I88" t="inlineStr" s="0">
         <is>
-          <t>Ak 4: Päihde- ja mielenterveyskuntoutujien sekä rikosseuraamusasiakkaiden arjen ja sosiaalisten taitojen vahvistaminen marttapiirien asiantuntijoiden tarjoaman kotitalousneuvonnan sekä Marttaliiton tuen ja hallinnon avulla (Arki sujuvaksi) (508 873 €) | Ak 9554: Ikäihmisten arjen tukemiseen ja hyvinvoinnin edistämiseen marttapiirien koordinoimalla ja Marttaliiton hallinnoimalla vapaaehtoistoiminnalla (VILPPU) (107 071 €) | Ak 2485: Pikkulapsiperheiden arjen taitojen ja hyvinvoinnin vahvistamiseen marttapiirien asiantuntijoiden tarjoamalla kotitalousneuvonnalla ja Marttaliiton piireille tarjoamalla hallinnollisella tuella (Lapsiperheiden arjen tukeminen) (159 544 €)</t>
+          <t>Ak 4: Päihde- ja mielenterveyskuntoutujien sekä rikosseuraamusasiakkaiden arjen ja sosiaalisten taitojen vahvistaminen marttapiirien asiantuntijoiden tarjoaman kotitalousneuvonnan sekä Marttaliiton tuen ja hallinnon avulla (Arki sujuvaksi) (508 873 €) | Ak 2485: Pikkulapsiperheiden arjen taitojen ja hyvinvoinnin vahvistamiseen marttapiirien asiantuntijoiden tarjoamalla kotitalousneuvonnalla ja Marttaliiton piireille tarjoamalla hallinnollisella tuella (Lapsiperheiden arjen tukeminen) (159 544 €) | Ak 9554: Ikäihmisten arjen tukemiseen ja hyvinvoinnin edistämiseen marttapiirien koordinoimalla ja Marttaliiton hallinnoimalla vapaaehtoistoiminnalla (VILPPU) (107 071 €)</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="I89" t="inlineStr" s="0">
         <is>
-          <t>Ak 2393: Jäsenjärjestöille kohdistettaviin avustuksiin (30 000 €) | Ak 2: Keliakiaan sopeutumista ja gluteenittoman ruokavaliohoidon toteutusta tukevaan ammatillisesti ohjattuun  vertaistuelliseen ja tavoitteelliseen ryhmämuotoiseen toimintaan. Kohderyhminä keliakia- tai ihokeliakiadiagnoosin saaneet ja heidän läheisensä sekä he  jotka noudattavat gluteenitonta ruokavaliota ilman keliakiadiagnoosia. (173 093 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (565 085 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (565 085 €) | Ak 2: Keliakiaan sopeutumista ja gluteenittoman ruokavaliohoidon toteutusta tukevaan ammatillisesti ohjattuun  vertaistuelliseen ja tavoitteelliseen ryhmämuotoiseen toimintaan. Kohderyhminä keliakia- tai ihokeliakiadiagnoosin saaneet ja heidän läheisensä sekä he  jotka noudattavat gluteenitonta ruokavaliota ilman keliakiadiagnoosia. (173 093 €) | Ak 2393: Jäsenjärjestöille kohdistettaviin avustuksiin (30 000 €)</t>
         </is>
       </c>
     </row>
@@ -6213,7 +6213,7 @@
       </c>
       <c r="I91" t="inlineStr" s="0">
         <is>
-          <t>Ak 10: Vauvaperheiden vanhemmuuden ja vuorovaikutuksen tukemiseen sekä pitkäkestoisen stressin vähentämiseen intensiivisen suljetun ryhmätoiminnan  yksilöllisen neuvonnan ja ohjauksen sekä kaikille vauvaperheille avoimen ryhmätoiminnan keinoin. Vapaaehtoisdoula-toimintaan erityistä tukea tarvitseville vauvaperheille sekä vertaisohjaajien koulutukseen. (Vauvatalo) (194 164 €) | Ak 7: Lähisuhdeväkivallan ennaltaehkäisyyn ja väkivaltaa kokeneiden selviytymisen tukemiseen sekä väkivaltaa käyttäneiden väkivaltaisen käytöksen katkaisuun yksilö-  pari- ja perhetapaamisten  vanhemmuutta tukeviin tapaamisten sekä ryhmämuotoissen avokriisityön keinoin. Toiminta kohdistuu lähisuhdeväkivallan kaikkien osapuolten tukemiseen  myös lasten ja nuorten. Lähisuhdeväkivallan vastaiseen vaikuttamistyöhön. (Avokriisityö) (258 139 €) | Ak 3: Lapsiperheiden hyvinvointia tukevaan järjestölähtöiseen avopalvelutoimintaan  (Mieskaveri-  Ero lapsiperheessä- ja vertaisryhmätoiminnat sekä nettiauttaminen) (149 080 €)</t>
+          <t>Ak 7: Lähisuhdeväkivallan ennaltaehkäisyyn ja väkivaltaa kokeneiden selviytymisen tukemiseen sekä väkivaltaa käyttäneiden väkivaltaisen käytöksen katkaisuun yksilö-  pari- ja perhetapaamisten  vanhemmuutta tukeviin tapaamisten sekä ryhmämuotoissen avokriisityön keinoin. Toiminta kohdistuu lähisuhdeväkivallan kaikkien osapuolten tukemiseen  myös lasten ja nuorten. Lähisuhdeväkivallan vastaiseen vaikuttamistyöhön. (Avokriisityö) (258 139 €) | Ak 10: Vauvaperheiden vanhemmuuden ja vuorovaikutuksen tukemiseen sekä pitkäkestoisen stressin vähentämiseen intensiivisen suljetun ryhmätoiminnan  yksilöllisen neuvonnan ja ohjauksen sekä kaikille vauvaperheille avoimen ryhmätoiminnan keinoin. Vapaaehtoisdoula-toimintaan erityistä tukea tarvitseville vauvaperheille sekä vertaisohjaajien koulutukseen. (Vauvatalo) (194 164 €) | Ak 3: Lapsiperheiden hyvinvointia tukevaan järjestölähtöiseen avopalvelutoimintaan  (Mieskaveri-  Ero lapsiperheessä- ja vertaisryhmätoiminnat sekä nettiauttaminen) (149 080 €)</t>
         </is>
       </c>
     </row>
@@ -6279,7 +6279,7 @@
       </c>
       <c r="I93" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (186 322 €) | Ak 11220: Romaninuorten tukemiseen omien voimavarojen ja vahvuuksien löytämiseksi jalkautuvan työn  yksilötyön ja ryhmämuotoisen toiminnan keinoin (Terne Apre - Nuorten vuoro) (184 800 €) | Ak 2872: Rikostaustaisille romaneille suunnattuun kulttuurilähtöiseen tukeen ja kuntoutumista edistävään toimintaan vankeusaikana  vapautumisen nivelvaiheissa sekä jälkitukena: Naisten Kulma-tukipisteet  vankilatyön ja VOIVA sekä VOITTO-toimintamallien koordinointi  tukihenkilötoiminta  kouluttaminen ja edunvalvonta. Euroopan sosiaalirahaston rakennerahasto-ohjelmanhankkeen "Aktiivinen toimijuus" osarahoitukseen järjestölle (2024-2026) (378 325 €)</t>
+          <t>Ak 2872: Rikostaustaisille romaneille suunnattuun kulttuurilähtöiseen tukeen ja kuntoutumista edistävään toimintaan vankeusaikana  vapautumisen nivelvaiheissa sekä jälkitukena: Naisten Kulma-tukipisteet  vankilatyön ja VOIVA sekä VOITTO-toimintamallien koordinointi  tukihenkilötoiminta  kouluttaminen ja edunvalvonta. Euroopan sosiaalirahaston rakennerahasto-ohjelmanhankkeen "Aktiivinen toimijuus" osarahoitukseen järjestölle (2024-2026) (378 325 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (186 322 €) | Ak 11220: Romaninuorten tukemiseen omien voimavarojen ja vahvuuksien löytämiseksi jalkautuvan työn  yksilötyön ja ryhmämuotoisen toiminnan keinoin (Terne Apre - Nuorten vuoro) (184 800 €)</t>
         </is>
       </c>
     </row>
@@ -6347,7 +6347,7 @@
       </c>
       <c r="I95" t="inlineStr" s="0">
         <is>
-          <t>Ak 11324: Turvallisuuden tunteen  osallisuuden ja päihteettömyyden vahvistamiseen julkisiin tiloihin jalkautuvan Huudikoutsi-toiminnan avulla (126 000 €) | Ak 11245: Huumeita käyttävien henkilöiden  toipuvien ja heidän läheistensä voimavarojen ja toimintakyvyn lisäämiseen kynnyksettömällä kriisituella ja vertaisryhmätoiminnalla (95 000 €) | Ak 3: Huumeita käyttävien henkilöiden läheisten  huumeita käyttävien ja toipuvien vapaaehtois- ja vertaistoiminnalla toteuttavaan matalan kynnyksen tukeen sekä vapaaehtois- ja vertaistoiminnan koordinaatioon (170 000 €)</t>
+          <t>Ak 3: Huumeita käyttävien henkilöiden läheisten  huumeita käyttävien ja toipuvien vapaaehtois- ja vertaistoiminnalla toteuttavaan matalan kynnyksen tukeen sekä vapaaehtois- ja vertaistoiminnan koordinaatioon (170 000 €) | Ak 11324: Turvallisuuden tunteen  osallisuuden ja päihteettömyyden vahvistamiseen julkisiin tiloihin jalkautuvan Huudikoutsi-toiminnan avulla (126 000 €) | Ak 11245: Huumeita käyttävien henkilöiden  toipuvien ja heidän läheistensä voimavarojen ja toimintakyvyn lisäämiseen kynnyksettömällä kriisituella ja vertaisryhmätoiminnalla (95 000 €)</t>
         </is>
       </c>
     </row>
@@ -6381,8 +6381,8 @@
       <c r="I96" t="inlineStr" s="0">
         <is>
           <t>Ak 3: För att stöda personer som har svårt att läsa eller förstå allmänspråk och öka deras tillgång till samhällsinformation och litteratur med hjälp av att producera och sprida lättläst material samt genom att främja högläsning inom omsorgen 
-(LL-Center - lätt språk och läsombudsverksamhet) (156 440 €) | Ak 3333: För att stöda självbestämmande  medvetande av rättigheter och inflytande i samhället hos svenskspråkiga personer med intellektuell funktionsnedsättning 
-(Steg för steg - för ett självständigt liv) (98 071 €) | Ak 10171: För stöd till familjer med barn  unga eller vuxna med intellektuell funktionsnedsättning med hjälp av kamratstöd  lokal förenings- och frivilligverksamhet samt genom att främja delaktighet i serviceprocesser (139 732 €)</t>
+(LL-Center - lätt språk och läsombudsverksamhet) (156 440 €) | Ak 10171: För stöd till familjer med barn  unga eller vuxna med intellektuell funktionsnedsättning med hjälp av kamratstöd  lokal förenings- och frivilligverksamhet samt genom att främja delaktighet i serviceprocesser (139 732 €) | Ak 3333: För att stöda självbestämmande  medvetande av rättigheter och inflytande i samhället hos svenskspråkiga personer med intellektuell funktionsnedsättning 
+(Steg för steg - för ett självständigt liv) (98 071 €)</t>
         </is>
       </c>
     </row>
@@ -6415,8 +6415,8 @@
       </c>
       <c r="I97" t="inlineStr" s="0">
         <is>
-          <t>Ak 5: Ikäihmisten toimintakyvyn ylläpitämiseen  aivoterveyden edistämiseen ja muistisairaiden kotona pärjäämisen tukemiseen matalan kynnyksen kohtaamispaikoilla  ryhmätoiminnalla vertaistuella ja etsivällä kotikäyntityöllä sekä verkostotyöllä
-(Birgen ruovttus - Pärjään kotona) (270 139 €) | Ay 4: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (302 764 €) | Ak 7: Päihteiden riskikäyttäjien päihteidenkäytön vähentämiseen ja elämänhallinnan vahvistamiseen asiakkaiden omassa toimintaympäristössä luontoa hyödyntävällä kulttuurisensitiivisellä ryhmätoiminnallla sekä yksilötapaamisilla 
+          <t>Ay 4: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (302 764 €) | Ak 5: Ikäihmisten toimintakyvyn ylläpitämiseen  aivoterveyden edistämiseen ja muistisairaiden kotona pärjäämisen tukemiseen matalan kynnyksen kohtaamispaikoilla  ryhmätoiminnalla vertaistuella ja etsivällä kotikäyntityöllä sekä verkostotyöllä
+(Birgen ruovttus - Pärjään kotona) (270 139 €) | Ak 7: Päihteiden riskikäyttäjien päihteidenkäytön vähentämiseen ja elämänhallinnan vahvistamiseen asiakkaiden omassa toimintaympäristössä luontoa hyödyntävällä kulttuurisensitiivisellä ryhmätoiminnallla sekä yksilötapaamisilla 
 (Meacceterapija- Mettäterapija) (155 452 €)</t>
         </is>
       </c>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="I98" t="inlineStr" s="0">
         <is>
-          <t>Ak 2345: Etsivän vanhustyön yhteiskehittämisen ja verkostojen välisen yhteistyön koordinointiin. Etsivän vanhustyön menetelmien levittämiseen ja juurruttamiseen sekä osaamisen vahvistamiseen. (Etsivän vanhustyön verkostokeskus) (187 425 €) | Ak 4042: Heikoimmassa työmarkkina-asemassa  työelämän ja koulutuksen ulkopuolella olevien sekä opintojen nivelvaiheessa olevien nuorten työelämävalmiuksien sekä sukupolvien välisen yhteyden vahvistamiseen (Vanhustyön Trainee nuorille) (25 725 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (511 638 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (511 638 €) | Ak 2345: Etsivän vanhustyön yhteiskehittämisen ja verkostojen välisen yhteistyön koordinointiin. Etsivän vanhustyön menetelmien levittämiseen ja juurruttamiseen sekä osaamisen vahvistamiseen. (Etsivän vanhustyön verkostokeskus) (187 425 €) | Ak 4042: Heikoimmassa työmarkkina-asemassa  työelämän ja koulutuksen ulkopuolella olevien sekä opintojen nivelvaiheessa olevien nuorten työelämävalmiuksien sekä sukupolvien välisen yhteyden vahvistamiseen (Vanhustyön Trainee nuorille) (25 725 €)</t>
         </is>
       </c>
     </row>
@@ -6582,7 +6582,7 @@
       </c>
       <c r="I102" t="inlineStr" s="0">
         <is>
-          <t>Ak 5581: Seksuaalista väkivaltaa kokeneiden  yli 16-vuotiaiden henkilöiden voimavarojen vahvistamiseen lyhytkestoisen kriisiavun  vertaisryhmätoiminnan sekä nuorille suunnatun  seksuaalioikeuksia ja turvataitoja koskevan ennaltaehkäisevän tiedonvälityksen avulla (Koski-seksuaaliväkivaltatyö Turun alueella) (145 905 €) | Ak 2642: Pakolaistaustaisten ja muista vastaavista lähtökohdista Suomeen muuttaneiden ihmisten mielenterveyttä edistävien ryhmätoimintojen kehittämiseen  toteuttamiseen ja levittämiseen (Serene-toiminta) (153 761 €) | Ak 1: Järjestölähtöiseen kriisi- ja mielenterveystyöhön vaikeissa elämäntilanteissa oleville tarjoamalla matalan kynnyksen keskusteluapua  ammatillisesti ohjattuja ryhmiä ja tukihenkilötoimintaa (MIELI kriisikeskus Turku) (299 250 €)</t>
+          <t>Ak 1: Järjestölähtöiseen kriisi- ja mielenterveystyöhön vaikeissa elämäntilanteissa oleville tarjoamalla matalan kynnyksen keskusteluapua  ammatillisesti ohjattuja ryhmiä ja tukihenkilötoimintaa (MIELI kriisikeskus Turku) (299 250 €) | Ak 2642: Pakolaistaustaisten ja muista vastaavista lähtökohdista Suomeen muuttaneiden ihmisten mielenterveyttä edistävien ryhmätoimintojen kehittämiseen  toteuttamiseen ja levittämiseen (Serene-toiminta) (153 761 €) | Ak 5581: Seksuaalista väkivaltaa kokeneiden  yli 16-vuotiaiden henkilöiden voimavarojen vahvistamiseen lyhytkestoisen kriisiavun  vertaisryhmätoiminnan sekä nuorille suunnatun  seksuaalioikeuksia ja turvataitoja koskevan ennaltaehkäisevän tiedonvälityksen avulla (Koski-seksuaaliväkivaltatyö Turun alueella) (145 905 €)</t>
         </is>
       </c>
     </row>
@@ -6648,7 +6648,7 @@
       </c>
       <c r="I104" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Ulkomaalaistaustaisten iäkkäiden arjen tukemiseen paikallisyhdistysten ikävertaisten ja yhteistoiminnan avulla (Moninaisuustyön Teemme yhdessä toiminta) (88 000 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (537 590 €) | Ak 4: Jäsenjärjestöille kohdistettaviin avustuksiin (52 500 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (537 590 €) | Ak 3: Ulkomaalaistaustaisten iäkkäiden arjen tukemiseen paikallisyhdistysten ikävertaisten ja yhteistoiminnan avulla (Moninaisuustyön Teemme yhdessä toiminta) (88 000 €) | Ak 4: Jäsenjärjestöille kohdistettaviin avustuksiin (52 500 €)</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="I106" t="inlineStr" s="0">
         <is>
-          <t>Ak 5940: Yhdenvertaisuuden edistämiseen kodin ja kasvuyhteisöjen (päiväkoti ja koulu) yhteistyössä  vanhempaintoiminnassa sekä lasten ja nuorten kasvuyhteisöissä tiedottamalla ja kouluttamalla (Yhdenvertaisuus vanhempaintoiminnassa sekä lasten ja nuorten kasvuyhteisöissä) (154 350 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (459 263 €) | Ak 5: Jäsenjärjestöille kohdistettaviin avustuksiin (38 850 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (459 263 €) | Ak 5940: Yhdenvertaisuuden edistämiseen kodin ja kasvuyhteisöjen (päiväkoti ja koulu) yhteistyössä  vanhempaintoiminnassa sekä lasten ja nuorten kasvuyhteisöissä tiedottamalla ja kouluttamalla (Yhdenvertaisuus vanhempaintoiminnassa sekä lasten ja nuorten kasvuyhteisöissä) (154 350 €) | Ak 5: Jäsenjärjestöille kohdistettaviin avustuksiin (38 850 €)</t>
         </is>
       </c>
     </row>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="I108" t="inlineStr" s="0">
         <is>
-          <t>Ak 12056: Rikosseuraamuksen piirissä  asunnottomana tai päihderiippuvuuden kanssa elävien naisten hyvinvoinnin edistämiseen vertaisryhmätoiminnan ja ammattilaisten osaamisen lisäämisen avulla (305 000 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (352 800 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (352 800 €) | Ak 12056: Rikosseuraamuksen piirissä  asunnottomana tai päihderiippuvuuden kanssa elävien naisten hyvinvoinnin edistämiseen vertaisryhmätoiminnan ja ammattilaisten osaamisen lisäämisen avulla (305 000 €)</t>
         </is>
       </c>
     </row>
@@ -6846,7 +6846,7 @@
       </c>
       <c r="I110" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Sijaiskotinuorten hyvinvoinnin lisäämiseen vertaistukitoiminnan avulla (92 031 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (372 797 €) | Ak 2836: Ikäihmisiä hoitavien perhehoitajien järjestölähtöiseen tukeen ja edunvalvontaan (Tunne ja turvaa ikäihmisten hyvä perhehoito) (153 596 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (372 797 €) | Ak 2836: Ikäihmisiä hoitavien perhehoitajien järjestölähtöiseen tukeen ja edunvalvontaan (Tunne ja turvaa ikäihmisten hyvä perhehoito) (153 596 €) | Ak 2: Sijaiskotinuorten hyvinvoinnin lisäämiseen vertaistukitoiminnan avulla (92 031 €)</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="I111" t="inlineStr" s="0">
         <is>
-          <t>Ak 6009: Pakolaistaustaisten 14-29-vuotiaiden nuorten työelämävalmiuksien lisäämiseen ja työllisyyden edistämiseen ohjauksen avulla (Kannustavat kokemukset -toiminta) (170 100 €) | Ak 4435: Koira-avusteiseen lasten ja nuorten vapaaehtoiseen tukihenkilötoimintaan 7-17 -vuotiaille lapsille ja nuorille (Ressu-toiminta) sekä sijaishuollosta itsenäistyvien nuorten vapaaehtoiseen tukihenkilötoimintaan siirtymävaiheessa (Omilleen toiminta) (104 737 €) | Ak 2: Maahanmuuttajataustaisten nuorten ja alaikäisinä yksintulleiden turvapaikanhakijataustaisten nuorten tukemiseen ryhmätoiminnan  leirien  retkien  tapahtumien ja yksilöllisen ohjauksen avulla (Maahanmuuttajanuorten tukitoiminta) (170 595 €)</t>
+          <t>Ak 2: Maahanmuuttajataustaisten nuorten ja alaikäisinä yksintulleiden turvapaikanhakijataustaisten nuorten tukemiseen ryhmätoiminnan  leirien  retkien  tapahtumien ja yksilöllisen ohjauksen avulla (Maahanmuuttajanuorten tukitoiminta) (170 595 €) | Ak 6009: Pakolaistaustaisten 14-29-vuotiaiden nuorten työelämävalmiuksien lisäämiseen ja työllisyyden edistämiseen ohjauksen avulla (Kannustavat kokemukset -toiminta) (170 100 €) | Ak 4435: Koira-avusteiseen lasten ja nuorten vapaaehtoiseen tukihenkilötoimintaan 7-17 -vuotiaille lapsille ja nuorille (Ressu-toiminta) sekä sijaishuollosta itsenäistyvien nuorten vapaaehtoiseen tukihenkilötoimintaan siirtymävaiheessa (Omilleen toiminta) (104 737 €)</t>
         </is>
       </c>
     </row>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="I114" t="inlineStr" s="0">
         <is>
-          <t>Ak 11274: Kiusaamista kokeneiden lasten ja nuorten tukemiseen sekä kiusaamisen jälkihoitoon liittyvän osaamisen lisäämiseen. Selviytyjät-vertaisryhmien järjestämiseen kiusaamista kokeneille noin 12–21-vuotiaille nuorille. (315 672 €) | Ak 2: Alaikäisten lasten vanhempien ja maahanmuuttajaäitien vanhemmuuden tukeen sekä lasten ja nuorten osallisuuden tukemiseen   yksinäisyyden ehkäisemiseen ammatillisesti ohjatun vapaaehtoisen tukihenkilötoiminnan keinoin (Kaveri-  Perhekummi- ja Ystäväksi maahanmuuttajaäidille - toiminta Järvi-Suomessa) (319 869 €)</t>
+          <t>Ak 2: Alaikäisten lasten vanhempien ja maahanmuuttajaäitien vanhemmuuden tukeen sekä lasten ja nuorten osallisuuden tukemiseen   yksinäisyyden ehkäisemiseen ammatillisesti ohjatun vapaaehtoisen tukihenkilötoiminnan keinoin (Kaveri-  Perhekummi- ja Ystäväksi maahanmuuttajaäidille - toiminta Järvi-Suomessa) (319 869 €) | Ak 11274: Kiusaamista kokeneiden lasten ja nuorten tukemiseen sekä kiusaamisen jälkihoitoon liittyvän osaamisen lisäämiseen. Selviytyjät-vertaisryhmien järjestämiseen kiusaamista kokeneille noin 12–21-vuotiaille nuorille. (315 672 €)</t>
         </is>
       </c>
     </row>
@@ -7017,10 +7017,10 @@
       </c>
       <c r="I115" t="inlineStr" s="0">
         <is>
-          <t>C 13648: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Järjestövarikko 2.0" osarahoitukseen järjestölle (2026-2028) (153 192 €) | Ak 10332: Vetureina toimivien lastensuojelun kokemusasiantuntijoiden valmentamiseen
+          <t>Ak 10332: Vetureina toimivien lastensuojelun kokemusasiantuntijoiden valmentamiseen
 ja tukemiseen ja työmahdollisuuksien tarjoamiseen sekä lastensuojelun
 piirissä oleville/olleille nuorille suunnattuun Veturien antamaan yksilötukeen 
-ryhmämuotoisiin toimintoihin ja etätukeen sekä kokemusasiantuntemukseen perustuvaan kehittämis- ja vaikuttamistoimintaan (Veturointi-toiminta) (325 240 €) | Ak 7747: Monilapsisten perheiden sujuvan arjen tukemiseen vapaaehtoistoiminnalla Oulussa (Lapsirikas-toiminta) (157 000 €)</t>
+ryhmämuotoisiin toimintoihin ja etätukeen sekä kokemusasiantuntemukseen perustuvaan kehittämis- ja vaikuttamistoimintaan (Veturointi-toiminta) (325 240 €) | Ak 7747: Monilapsisten perheiden sujuvan arjen tukemiseen vapaaehtoistoiminnalla Oulussa (Lapsirikas-toiminta) (157 000 €) | C 13648: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Järjestövarikko 2.0" osarahoitukseen järjestölle (2026-2028) (153 192 €)</t>
         </is>
       </c>
     </row>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="I118" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (263 088 €) | Ak 2287: Psyykkistä kuormittuneisuutta  lieviä mielenterveysoireita tai yksinäisyyttä kokevien korkeakouluopiskelijoiden tukemiseen vertaistukitoiminnan  vapaaehtoistoiminnan  kahdenkeskisen keskusteluavun  tietosisältöjen tarjoamisen ja tapahtumatoiminnan avulla (359 790 €)</t>
+          <t>Ak 2287: Psyykkistä kuormittuneisuutta  lieviä mielenterveysoireita tai yksinäisyyttä kokevien korkeakouluopiskelijoiden tukemiseen vertaistukitoiminnan  vapaaehtoistoiminnan  kahdenkeskisen keskusteluavun  tietosisältöjen tarjoamisen ja tapahtumatoiminnan avulla (359 790 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (263 088 €)</t>
         </is>
       </c>
     </row>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="I119" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Kansalaistoiminnankeskus Mataran toimintaan  alueen sote-järjestöjen tukemiseen  vapaaehtoistyön kehittämiseen ja koordinointiin sekä OLKA - toiminnan toteuttamiseen (255 780 €) | Ay 1957: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan. (173 375 €) | Ak 1: Järjestöjen tuki- ja kehittämistoimintoihin Keski-Suomessa (190 798 €)</t>
+          <t>Ak 3: Kansalaistoiminnankeskus Mataran toimintaan  alueen sote-järjestöjen tukemiseen  vapaaehtoistyön kehittämiseen ja koordinointiin sekä OLKA - toiminnan toteuttamiseen (255 780 €) | Ak 1: Järjestöjen tuki- ja kehittämistoimintoihin Keski-Suomessa (190 798 €) | Ay 1957: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan. (173 375 €)</t>
         </is>
       </c>
     </row>
@@ -7187,7 +7187,7 @@
       </c>
       <c r="I120" t="inlineStr" s="0">
         <is>
-          <t>Ak 7678: Ikääntyneiden yksinäisyyden ennaltaehkäisemiseen ja vähentämiseen kuvapuheluvälitteisen pienryhmätoiminnan avulla Päijät- ja Kanta-Hämeessä (Ruutuystävät-toiminta) (124 520 €) | Ak 5735: Sosiaalisten taitojen  arjenhallinnan  psyykkisten voimavarojen ja osallisuuden vahvistamiseen vertaistuellisen ryhmätoiminnan keinoin eri-ikäisille moniongelmaisille  työttömille tai työ- ja opiskeluelämän ulkopuolella oleville nuorille ja aikuisille (Poveria-toiminta) (406 660 €) | C 13785: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Digikokemusosaaja" osarahoitukseen säätiölle (2026-2028) (87 914 €)</t>
+          <t>Ak 5735: Sosiaalisten taitojen  arjenhallinnan  psyykkisten voimavarojen ja osallisuuden vahvistamiseen vertaistuellisen ryhmätoiminnan keinoin eri-ikäisille moniongelmaisille  työttömille tai työ- ja opiskeluelämän ulkopuolella oleville nuorille ja aikuisille (Poveria-toiminta) (406 660 €) | Ak 7678: Ikääntyneiden yksinäisyyden ennaltaehkäisemiseen ja vähentämiseen kuvapuheluvälitteisen pienryhmätoiminnan avulla Päijät- ja Kanta-Hämeessä (Ruutuystävät-toiminta) (124 520 €) | C 13785: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Digikokemusosaaja" osarahoitukseen säätiölle (2026-2028) (87 914 €)</t>
         </is>
       </c>
     </row>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="I123" t="inlineStr" s="0">
         <is>
-          <t>Ak 4350: 18-35-vuotiaiden mielenterveyskuntoutujien osallisuuden tunteen ja motivaation kasvattamiseen sekä työ- ja toimintakyvyn edistämiseen järjestämällä ohjattuun toiminnalliseen vertaistukeen perustuvaa kulttuuripajatoimintaa (190 000 €) | Ak 3: Mielenterveyskuntoutujien terveyttä  hyvinvointia  osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään tavoitteelliseen kohtaamispaikkatoimintaan  (Porin klubitalo Sarastus) (178 605 €) | Ak 11135: Erityistä tukea tarvitsevien nuorten aikuisten terveyttä ja hyvinvointia tukevaan kohtaamispaikkatoimintaan  ryhmätoimintaan  vapaaehtoistyöhön ja yksilölliseen tukeen (237 951 €)</t>
+          <t>Ak 11135: Erityistä tukea tarvitsevien nuorten aikuisten terveyttä ja hyvinvointia tukevaan kohtaamispaikkatoimintaan  ryhmätoimintaan  vapaaehtoistyöhön ja yksilölliseen tukeen (237 951 €) | Ak 4350: 18-35-vuotiaiden mielenterveyskuntoutujien osallisuuden tunteen ja motivaation kasvattamiseen sekä työ- ja toimintakyvyn edistämiseen järjestämällä ohjattuun toiminnalliseen vertaistukeen perustuvaa kulttuuripajatoimintaa (190 000 €) | Ak 3: Mielenterveyskuntoutujien terveyttä  hyvinvointia  osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään tavoitteelliseen kohtaamispaikkatoimintaan  (Porin klubitalo Sarastus) (178 605 €)</t>
         </is>
       </c>
     </row>
@@ -7319,8 +7319,8 @@
       </c>
       <c r="I124" t="inlineStr" s="0">
         <is>
-          <t>Ak 6: Sukupuolivähemmistöihin kuuluvien ja heidän läheistensä terveyden ja hyvinvoinnin edistämiseen ammattiohjatun vertaistuen  neuvonnan  yksilötapaamisten  kouluttamisen ja tiedottamisen avulla
-(Sukupuolen moninaisuuden osaamiskeskus) (253 640 €) | Ak 7: Jäsenjärjestöille kohdistettaviin avustuksiin (52 500 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (299 520 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (299 520 €) | Ak 6: Sukupuolivähemmistöihin kuuluvien ja heidän läheistensä terveyden ja hyvinvoinnin edistämiseen ammattiohjatun vertaistuen  neuvonnan  yksilötapaamisten  kouluttamisen ja tiedottamisen avulla
+(Sukupuolen moninaisuuden osaamiskeskus) (253 640 €) | Ak 7: Jäsenjärjestöille kohdistettaviin avustuksiin (52 500 €)</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="I125" t="inlineStr" s="0">
         <is>
-          <t>Ak 5: Alueellisten mielenterveysomaisjärjestöjen toimintaedellytysten vahvistamiseen kehittämällä ja koordinoimalla yhdistysten hallintoa  omaistyötä  vaikuttamistoimintaa sekä vapaaehtoistyötä (267 750 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (329 700 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (329 700 €) | Ak 5: Alueellisten mielenterveysomaisjärjestöjen toimintaedellytysten vahvistamiseen kehittämällä ja koordinoimalla yhdistysten hallintoa  omaistyötä  vaikuttamistoimintaa sekä vapaaehtoistyötä (267 750 €)</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="I126" t="inlineStr" s="0">
         <is>
-          <t>Ak 4282: För understöd som allokeras till medlemsorganisationer (55 990 €) | Ay 1: Som allmänt understöd för understödstagarens allmännyttiga verksamhet (110 000 €) | Ak 4: För främjande av svenskspråkiga synskadades tillgång till information och ökade delaktighet genom kommunikations- och punktskriftsverksamhet samt utgivning av svenskspråkiga tal- och punktskriftstidningar (256 706 €)</t>
+          <t>Ak 4: För främjande av svenskspråkiga synskadades tillgång till information och ökade delaktighet genom kommunikations- och punktskriftsverksamhet samt utgivning av svenskspråkiga tal- och punktskriftstidningar (256 706 €) | Ay 1: Som allmänt understöd för understödstagarens allmännyttiga verksamhet (110 000 €) | Ak 4282: För understöd som allokeras till medlemsorganisationer (55 990 €)</t>
         </is>
       </c>
     </row>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="I130" t="inlineStr" s="0">
         <is>
-          <t>Ak 10148: Lapsiperheiden ja toimintaa järjestävien vapaaehtoisten ikäihmisten voimavarojen  merkityksellisyyden ja osallisuuden vahvistamiseen omassa elämässä ja lähiyhteisössä kohtaamispaikkatoiminnan avulla sekä toiminnan koordinointiin  (Mummun ja vaarin tupa -toiminta) (130 000 €) | Ak 7488: Lastensuojelutaustaisille  päihdeongelmista kärsiville sekä sukupuoli- ja seksuaalivähemmistöihin kuuluville yli 17-vuotiaille nuorille ja aikuisille tarkoitetun vertaismentoritoiminnan ylläpitämiseen ja kehittämiseen Ylitse MentorApp -sovelluksen välityksellä (Ylitse MentorApp -vertaistukea verkossa) (85 000 €) | Ak 11703: Huolta  turvattomuutta  uhkaa tai apua tarvitsevien 7-15 vuotiaiden lasten yhteydenottoihin vastaamiseen ammattilaisten ja koulutettujen vapaaehtoisten avulla (Apuu-chat) (352 800 €)</t>
+          <t>Ak 11703: Huolta  turvattomuutta  uhkaa tai apua tarvitsevien 7-15 vuotiaiden lasten yhteydenottoihin vastaamiseen ammattilaisten ja koulutettujen vapaaehtoisten avulla (Apuu-chat) (352 800 €) | Ak 10148: Lapsiperheiden ja toimintaa järjestävien vapaaehtoisten ikäihmisten voimavarojen  merkityksellisyyden ja osallisuuden vahvistamiseen omassa elämässä ja lähiyhteisössä kohtaamispaikkatoiminnan avulla sekä toiminnan koordinointiin  (Mummun ja vaarin tupa -toiminta) (130 000 €) | Ak 7488: Lastensuojelutaustaisille  päihdeongelmista kärsiville sekä sukupuoli- ja seksuaalivähemmistöihin kuuluville yli 17-vuotiaille nuorille ja aikuisille tarkoitetun vertaismentoritoiminnan ylläpitämiseen ja kehittämiseen Ylitse MentorApp -sovelluksen välityksellä (Ylitse MentorApp -vertaistukea verkossa) (85 000 €)</t>
         </is>
       </c>
     </row>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="I132" t="inlineStr" s="0">
         <is>
-          <t>Ak 7649: Pitkäaikaistyöttömien sekä työelämän ulkopuolella olevien hyvinvoinnin edistämiseen kouluttamalla työttömien yhdistyksiä sosiaali- ja terveysteemoista  ohjaamalla kohderyhmää terveystarkastuksiin sekä tarjoamalla henkilökohtaista neuvontaa palveluista ja elintavoista matalan kynnyksen kohtaamispaikoissa ja etäyhteyksin (Terveyttä työttömille) (244 184 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (286 601 €) | Ak 6: Jäsenjärjestöille kohdistettaviin avustuksiin (29 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (286 601 €) | Ak 7649: Pitkäaikaistyöttömien sekä työelämän ulkopuolella olevien hyvinvoinnin edistämiseen kouluttamalla työttömien yhdistyksiä sosiaali- ja terveysteemoista  ohjaamalla kohderyhmää terveystarkastuksiin sekä tarjoamalla henkilökohtaista neuvontaa palveluista ja elintavoista matalan kynnyksen kohtaamispaikoissa ja etäyhteyksin (Terveyttä työttömille) (244 184 €) | Ak 6: Jäsenjärjestöille kohdistettaviin avustuksiin (29 000 €)</t>
         </is>
       </c>
     </row>
@@ -7658,9 +7658,9 @@
       </c>
       <c r="I134" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Palveluista syrjäytyneiden nuorten aikuisten matalan kynnyksen toimintaan sekä ryhmätoimintaan ja yksilölliseen tukeen
-(Nuorten kohtaamispaikka TOIVO) (136 739 €) | Ak 10010: Nuorten syrjäytymistä ehkäisevään vapaa-ajan toimintaan Turun seudulla.
-(Yökoris) (147 000 €) | Ak 3: Muutoksia ja ongelmia kokeneiden maahanmuuttajien henkilökohtaiseen palveluohjaukseen suomen kielellä Turussa ja Turun lähikunnissa
+          <t>Ak 10010: Nuorten syrjäytymistä ehkäisevään vapaa-ajan toimintaan Turun seudulla.
+(Yökoris) (147 000 €) | Ak 1: Palveluista syrjäytyneiden nuorten aikuisten matalan kynnyksen toimintaan sekä ryhmätoimintaan ja yksilölliseen tukeen
+(Nuorten kohtaamispaikka TOIVO) (136 739 €) | Ak 3: Muutoksia ja ongelmia kokeneiden maahanmuuttajien henkilökohtaiseen palveluohjaukseen suomen kielellä Turussa ja Turun lähikunnissa
 (Turun NMKY:n maahanmuuttajapalvelut) (134 505 €)</t>
         </is>
       </c>
@@ -7727,8 +7727,8 @@
       </c>
       <c r="I136" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Kunniaan liittyvän väkivallan eri muotojen torjumiseen ja ennaltaehkäisyyn. Kunniaväkivaltaa kokevien tai sen riskissä olevien henkilöiden seksuaali- ja lisääntymisoikeuksien ja itsemääräämisoikeuden vahvistamiseen sekä palveluihin pääsyn parantamiseen  terveyden ja hyvinvoinnin edistämiseen sekä oikeusturvan toteutumiseen. Vaikuttamis- ja verkostotyöhön asenteiden muuttamiseksi ja rakenteiden kehittämiseksi. (204 750 €) | Ak 11902: Köyhyyttä kokevien ihmisten osallisuuden vahvistamiseen sekä päättäjien ja suuren yleisön ymmärryksen lisäämiseen köyhyydestä ihmisoikeuskysymyksenä vaikuttajaryhmätoiminnan ja koulutusten sekä verkosto- ja vaikuttamistyön avulla
-(Köyhyys ja ihmisoikeudet) (140 000 €) | Ay 4545: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (206 643 €)</t>
+          <t>Ay 4545: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (206 643 €) | Ak 1: Kunniaan liittyvän väkivallan eri muotojen torjumiseen ja ennaltaehkäisyyn. Kunniaväkivaltaa kokevien tai sen riskissä olevien henkilöiden seksuaali- ja lisääntymisoikeuksien ja itsemääräämisoikeuden vahvistamiseen sekä palveluihin pääsyn parantamiseen  terveyden ja hyvinvoinnin edistämiseen sekä oikeusturvan toteutumiseen. Vaikuttamis- ja verkostotyöhön asenteiden muuttamiseksi ja rakenteiden kehittämiseksi. (204 750 €) | Ak 11902: Köyhyyttä kokevien ihmisten osallisuuden vahvistamiseen sekä päättäjien ja suuren yleisön ymmärryksen lisäämiseen köyhyydestä ihmisoikeuskysymyksenä vaikuttajaryhmätoiminnan ja koulutusten sekä verkosto- ja vaikuttamistyön avulla
+(Köyhyys ja ihmisoikeudet) (140 000 €)</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="I137" t="inlineStr" s="0">
         <is>
-          <t>Ak 5: Jäsenjärjestöille kohdistettaviin avustuksiin (17 850 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (298 801 €) | Ak 2: Osteoporoosia sairastavien avo- ja ryhmämuotoiseen kurssitoimintaan (226 800 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (298 801 €) | Ak 2: Osteoporoosia sairastavien avo- ja ryhmämuotoiseen kurssitoimintaan (226 800 €) | Ak 5: Jäsenjärjestöille kohdistettaviin avustuksiin (17 850 €)</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="I138" t="inlineStr" s="0">
         <is>
-          <t>Ak 1528: 10-18-vuotiaiden lasten ja nuorten hyvinvoinnin tukemiseen sekä heidän vanhempien vanhemmuuden vahvistamiseen yksilöllisen tuen  vertaisryhmätoiminnan  tilaisuuksien sekä tiedon ja materiaalien levittämisen keinoin (Linkki-toiminta) (183 750 €) | Ay 1497: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (345 862 €)</t>
+          <t>Ay 1497: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (345 862 €) | Ak 1528: 10-18-vuotiaiden lasten ja nuorten hyvinvoinnin tukemiseen sekä heidän vanhempien vanhemmuuden vahvistamiseen yksilöllisen tuen  vertaisryhmätoiminnan  tilaisuuksien sekä tiedon ja materiaalien levittämisen keinoin (Linkki-toiminta) (183 750 €)</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="I140" t="inlineStr" s="0">
         <is>
-          <t>Ak 11729: Yli 60-vuotiaiden ikääntyvien suolistosairauksia sairastavien ja heidän läheistensä voimavarojen lisäämiseen ryhmämuotoisen toiminnan avulla sekä tiedon jakamiseen eri viestintäkanavissa (78 000 €) | Ak 2: Tulehduksellista suolistosairautta (IBD) sairastavien ja heidän läheistensä hyvinvoinnin edistämiseen ammatillisesti ohjatun  vertaistuellisen ja tavoitteellisen ryhmätoiminnan keinoin (60 607 €) | Ak 2508: Eri ikäisten suolistosairautta sairastavien ja heidän läheistensä yhteisöllisyyden ja osallistumismahdollisuuksien edistämiseen monimuotoisella vertaistukitoiminnalla (Valtakunnallinen vapaaehtois- ja vertaistoiminta) (133 980 €)</t>
+          <t>Ak 2508: Eri ikäisten suolistosairautta sairastavien ja heidän läheistensä yhteisöllisyyden ja osallistumismahdollisuuksien edistämiseen monimuotoisella vertaistukitoiminnalla (Valtakunnallinen vapaaehtois- ja vertaistoiminta) (133 980 €) | Ak 11729: Yli 60-vuotiaiden ikääntyvien suolistosairauksia sairastavien ja heidän läheistensä voimavarojen lisäämiseen ryhmämuotoisen toiminnan avulla sekä tiedon jakamiseen eri viestintäkanavissa (78 000 €) | Ak 2: Tulehduksellista suolistosairautta (IBD) sairastavien ja heidän läheistensä hyvinvoinnin edistämiseen ammatillisesti ohjatun  vertaistuellisen ja tavoitteellisen ryhmätoiminnan keinoin (60 607 €)</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="I143" t="inlineStr" s="0">
         <is>
-          <t>C 13824: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Omanlaisena Yhdessä" osarahoitukseen järjestölle (2026-2028) (76 695 €) | Ak 11085: Jäsenjärjestöille kohdistettaviin avustuksiin. (28 500 €) | Ak 1198: Lapsiperheiden hyvinvoinnin ja osallisuuden edistämiseen sekä varhaiseen tukemiseen avoimen kohtaamispaikkatoiminnan  vertaisryhmien  yksilöllisen ohjauksen ja moniammatillisen yhteistyön keinoin (PerhePesä - Yhdessä toimien perheiden parhaaksi) (184 172 €)</t>
+          <t>Ak 1198: Lapsiperheiden hyvinvoinnin ja osallisuuden edistämiseen sekä varhaiseen tukemiseen avoimen kohtaamispaikkatoiminnan  vertaisryhmien  yksilöllisen ohjauksen ja moniammatillisen yhteistyön keinoin (PerhePesä - Yhdessä toimien perheiden parhaaksi) (184 172 €) | C 13824: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Omanlaisena Yhdessä" osarahoitukseen järjestölle (2026-2028) (76 695 €) | Ak 11085: Jäsenjärjestöille kohdistettaviin avustuksiin. (28 500 €)</t>
         </is>
       </c>
     </row>
@@ -8025,7 +8025,7 @@
       </c>
       <c r="I145" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Som allmänt understöd för understödstagarens allmännyttiga verksamhet (316 512 €) | Ak 6: För understöd som allokeras till medlemsorganisationer (20 000 €) | Ak 2: För att stöda livskontrollen- och hanteringen hos svenskspråkiga personer med psykisk ohälsa eller psykosocial funktionsnedsättning samt deras anhöriga med hjälp av psykosocial kursverksamhet  rådgivning och kamratstöd (168 887 €)</t>
+          <t>Ay 1: Som allmänt understöd för understödstagarens allmännyttiga verksamhet (316 512 €) | Ak 2: För att stöda livskontrollen- och hanteringen hos svenskspråkiga personer med psykisk ohälsa eller psykosocial funktionsnedsättning samt deras anhöriga med hjälp av psykosocial kursverksamhet  rådgivning och kamratstöd (168 887 €) | Ak 6: För understöd som allokeras till medlemsorganisationer (20 000 €)</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="I146" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Ikääntyvien mielenterveyden ja hyvinvoinnin tukemiseen ryhmätoiminnan  yksilö- ja parikeskustelujen sekä ikätukitoiminnan avulla (Senioripysäkki-toiminta) (167 000 €) | Ay 2716: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (105 840 €) | Ak 9: Kehitysvammaisten ja erityistä tukea tarvitsevien nuorten ja aikuisten yksinäisyyden lieventämiseen ja omaehtoisen aktiivisuuden tukemiseen kohtaamispaikkatoiminnan ja jalkautuvan työn avulla (Iltalinjalla) (118 650 €)</t>
+          <t>Ak 3: Ikääntyvien mielenterveyden ja hyvinvoinnin tukemiseen ryhmätoiminnan  yksilö- ja parikeskustelujen sekä ikätukitoiminnan avulla (Senioripysäkki-toiminta) (167 000 €) | Ak 9: Kehitysvammaisten ja erityistä tukea tarvitsevien nuorten ja aikuisten yksinäisyyden lieventämiseen ja omaehtoisen aktiivisuuden tukemiseen kohtaamispaikkatoiminnan ja jalkautuvan työn avulla (Iltalinjalla) (118 650 €) | Ay 2716: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (105 840 €)</t>
         </is>
       </c>
     </row>
@@ -8125,8 +8125,8 @@
       <c r="I148" t="inlineStr" s="0">
         <is>
           <t>Ak 2: Vapaaehtois- ja vertaistoiminnan koordinointiin ja maahanmuuttajataustaisten poikien ja nuorten miesten osallisuuden ja aktivoinnin tukemiseen Tampereella 
-(Vapari-toiminta) (181 650 €) | Ak 9652: Pakolaistaustaisten työttömien 18-29-vuotiaiden nuorten miesten toimintakyvyn ja mielenterveyden tukemiseen ryhmätoiminnalla ja yksilöllisellä tuella sekä nuorten kanssa työskentelevien ammattilaisten kouluttamiseen ja julkisten palvelujen yhteiskehittämiseen pakolaisnuorten kohtaamisen ja tukemisen parantamiseksi (142 000 €) | Ak 9653: Maahanmuuttajataustaisten vanhempien tukemiseen 7-16-vuotiaiden nuorten kasvatuksessa yksilöllisen tuen ja ryhmätoimintojen avulla sekä tietoisuuden lisäämiseen pakolaisperheiden vanhemmuudesta Tampereella
-(Avaamo) (175 000 €)</t>
+(Vapari-toiminta) (181 650 €) | Ak 9653: Maahanmuuttajataustaisten vanhempien tukemiseen 7-16-vuotiaiden nuorten kasvatuksessa yksilöllisen tuen ja ryhmätoimintojen avulla sekä tietoisuuden lisäämiseen pakolaisperheiden vanhemmuudesta Tampereella
+(Avaamo) (175 000 €) | Ak 9652: Pakolaistaustaisten työttömien 18-29-vuotiaiden nuorten miesten toimintakyvyn ja mielenterveyden tukemiseen ryhmätoiminnalla ja yksilöllisellä tuella sekä nuorten kanssa työskentelevien ammattilaisten kouluttamiseen ja julkisten palvelujen yhteiskehittämiseen pakolaisnuorten kohtaamisen ja tukemisen parantamiseksi (142 000 €)</t>
         </is>
       </c>
     </row>
@@ -8159,8 +8159,8 @@
       </c>
       <c r="I149" t="inlineStr" s="0">
         <is>
-          <t>Ay 1107: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (175 000 €) | Ak 11632: Erityislapsiperheiden tukemiseen koko perheen sekä vanhempien välisen suhteen näkökulmasta teemallisten ryhmien  yksilöllisen tuen ja tiedotuksen avulla (Hyvinvoiva perhe) (135 000 €) | Ak 2295: Omaishoitajien tukemiseen ja heidän voimavarojensa lisäämiseen alueellisen matalan kynnyksen toiminnan  vapaaehtoistoiminnan  puhelin- ja chatneuvonnan sekä kokemusasiantuntijoiden vaikuttamistoiminnan avulla Oulun seudulla
-(Ihmisen lähelle) (183 000 €)</t>
+          <t>Ak 2295: Omaishoitajien tukemiseen ja heidän voimavarojensa lisäämiseen alueellisen matalan kynnyksen toiminnan  vapaaehtoistoiminnan  puhelin- ja chatneuvonnan sekä kokemusasiantuntijoiden vaikuttamistoiminnan avulla Oulun seudulla
+(Ihmisen lähelle) (183 000 €) | Ay 1107: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (175 000 €) | Ak 11632: Erityislapsiperheiden tukemiseen koko perheen sekä vanhempien välisen suhteen näkökulmasta teemallisten ryhmien  yksilöllisen tuen ja tiedotuksen avulla (Hyvinvoiva perhe) (135 000 €)</t>
         </is>
       </c>
     </row>
@@ -8193,7 +8193,7 @@
       </c>
       <c r="I150" t="inlineStr" s="0">
         <is>
-          <t>Ak 5441: Päihde- ja mielenterveysongelmaisten sekä heidän läheistensä arjessa selviytymisen ja jaksamisen tukemiseen vapaaehtoistoiminnan  ryhmätoiminnan ja kohtaamispaikkatoiminnan avulla (74 000 €) | C 13668: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Juho – Joustavia Uudistuksia ja Hyvinvointia Osallisuudesta" (Hankekoodi S31484) osarahoitukseen järjestölle (2026-2028) (49 542 €) | Ak 9519: Työstä ja koulutuksesta syrjässä tai syrjäytymisvaarassa oleville ja yksinäisyyttä kokeville 16-29-vuotiaille nuorille suunnattuun yksinäisyyttä vähentävään ja digiosaamista  hyvinvointia ja osallisuuden kokemusta vahvistavaan digiverstastoimintaan Porissa (79 800 €)</t>
+          <t>Ak 9519: Työstä ja koulutuksesta syrjässä tai syrjäytymisvaarassa oleville ja yksinäisyyttä kokeville 16-29-vuotiaille nuorille suunnattuun yksinäisyyttä vähentävään ja digiosaamista  hyvinvointia ja osallisuuden kokemusta vahvistavaan digiverstastoimintaan Porissa (79 800 €) | Ak 5441: Päihde- ja mielenterveysongelmaisten sekä heidän läheistensä arjessa selviytymisen ja jaksamisen tukemiseen vapaaehtoistoiminnan  ryhmätoiminnan ja kohtaamispaikkatoiminnan avulla (74 000 €) | C 13668: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Juho – Joustavia Uudistuksia ja Hyvinvointia Osallisuudesta" (Hankekoodi S31484) osarahoitukseen järjestölle (2026-2028) (49 542 €)</t>
         </is>
       </c>
     </row>
@@ -8226,7 +8226,7 @@
       </c>
       <c r="I151" t="inlineStr" s="0">
         <is>
-          <t>Ak 6: Asumisen ja elämänhallinnan kanssa vaikeuksissa olevien naisten tukemiseen etsivän työn  palveluohjauksen  yksilöllisen tuen ja ryhmätoiminnan avulla (105 798 €) | Ak 2: Päihdeongelmaisten nuorten aikuisten päihteettömyyttä tukevaan ryhmämuotoiseen toimintaan (Hunaja-toiminta) (72 952 €) | Ak 1: Päihdetoipujien ja mielenterveyskuntoutujien toimintakyvyn vahvistamiseen päihteettömällä yhdyskuntatupatyöllä ja palveluohjauksella sekä vapaaehtois- ja vertaistoiminnalla (304 155 €)</t>
+          <t>Ak 1: Päihdetoipujien ja mielenterveyskuntoutujien toimintakyvyn vahvistamiseen päihteettömällä yhdyskuntatupatyöllä ja palveluohjauksella sekä vapaaehtois- ja vertaistoiminnalla (304 155 €) | Ak 6: Asumisen ja elämänhallinnan kanssa vaikeuksissa olevien naisten tukemiseen etsivän työn  palveluohjauksen  yksilöllisen tuen ja ryhmätoiminnan avulla (105 798 €) | Ak 2: Päihdeongelmaisten nuorten aikuisten päihteettömyyttä tukevaan ryhmämuotoiseen toimintaan (Hunaja-toiminta) (72 952 €)</t>
         </is>
       </c>
     </row>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="I152" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Kehitysvammaisten ja vastaavaa laaja-alaista tukea tarvitsevien lasten ja nuorten vanhempien arjen tilapäiseen helpottamiseen ja jaksamisen tukemiseen parkkitoiminnan ja vertaistuen avulla (74 550 €) | Ak 8: Kehitysvammaisten ja vastaavaa laaja-alaista tukea tarvitsevien ihmisten osallisuuden ja vapaa-ajan toimintoihin osallistumisen mahdollistamiseen  sosiaalisen verkoston laajentamiseen ja yksinäisyyden vähentämiseen kaveri-  vertais- ja vapaaehtoistoiminnan sekä tuetun vapaaehtoistoiminnan avulla. (127 674 €) | Ay 7397: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (189 876 €)</t>
+          <t>Ay 7397: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (189 876 €) | Ak 8: Kehitysvammaisten ja vastaavaa laaja-alaista tukea tarvitsevien ihmisten osallisuuden ja vapaa-ajan toimintoihin osallistumisen mahdollistamiseen  sosiaalisen verkoston laajentamiseen ja yksinäisyyden vähentämiseen kaveri-  vertais- ja vapaaehtoistoiminnan sekä tuetun vapaaehtoistoiminnan avulla. (127 674 €) | Ak 2: Kehitysvammaisten ja vastaavaa laaja-alaista tukea tarvitsevien lasten ja nuorten vanhempien arjen tilapäiseen helpottamiseen ja jaksamisen tukemiseen parkkitoiminnan ja vertaistuen avulla (74 550 €)</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="I153" t="inlineStr" s="0">
         <is>
-          <t>Ak 2649: Päihteitä käyttävien miesten isyyden parempaan huomioimiseen palvelujärjestelmässä sekä päihteiden käytöstä johtuvia haittoja kokevien isien päihteettömyyden tukemiseen  isyyden ja osallisuuden vahvistamiseen sekä vanhemmuuden tukemiseen  jotta päihteistä kuntoutuminen ja kohtaaminen tapahtuisi ensisijaisesti isänä ja vanhempana (Erityisesti isä) (143 177 €) | Ak 10308: Ruoka-aputoiminnan tavoittavuuden  verkostoyhteistyön ja tiedolla johtamisen edistämiseen ruoka-apu.fi-verkkopalvelun jatkokehittämisen  ylläpidon ja levittämisen avulla (75 385 €) | Ak 1: Päihteitä käyttävien naisten sekä läheisten aseman parantamiseen ja toipumisen edistämiseen  päihde- ja riippuvuustyötä tekevien järjestöjen ja päihteitä käyttäviä asiakkaita kohtaavien ammattilaisten keskinäisen yhteistyön edistämiseen  asiantuntijuuden vaihtoon sekä osaamisen ja menetelmien kehittämiseen yli sektori- ja kuntarajojen Itä-Suomen alueella (141 899 €)</t>
+          <t>Ak 2649: Päihteitä käyttävien miesten isyyden parempaan huomioimiseen palvelujärjestelmässä sekä päihteiden käytöstä johtuvia haittoja kokevien isien päihteettömyyden tukemiseen  isyyden ja osallisuuden vahvistamiseen sekä vanhemmuuden tukemiseen  jotta päihteistä kuntoutuminen ja kohtaaminen tapahtuisi ensisijaisesti isänä ja vanhempana (Erityisesti isä) (143 177 €) | Ak 1: Päihteitä käyttävien naisten sekä läheisten aseman parantamiseen ja toipumisen edistämiseen  päihde- ja riippuvuustyötä tekevien järjestöjen ja päihteitä käyttäviä asiakkaita kohtaavien ammattilaisten keskinäisen yhteistyön edistämiseen  asiantuntijuuden vaihtoon sekä osaamisen ja menetelmien kehittämiseen yli sektori- ja kuntarajojen Itä-Suomen alueella (141 899 €) | Ak 10308: Ruoka-aputoiminnan tavoittavuuden  verkostoyhteistyön ja tiedolla johtamisen edistämiseen ruoka-apu.fi-verkkopalvelun jatkokehittämisen  ylläpidon ja levittämisen avulla (75 385 €)</t>
         </is>
       </c>
     </row>
@@ -8325,9 +8325,9 @@
       </c>
       <c r="I154" t="inlineStr" s="0">
         <is>
-          <t>Ak 7479: Potilasvahingon kokeneiden  narkolepsiaan sairastuneiden  aivoverenkierron häiriön  aivoverenvuodon tai aivokasvaimen jälkitiloista oireilevien sekä ilman vakuutusturvaa olevien tapaturmaisesti vammautuneiden (esim. aivovamma  palovamma  selkäydinvamma) lasten  nuorten (16-29 vuotta) ja heidän läheistensä toimintakyvyn tukemiseen tiedon  verkostotyön  vertaistuen ja kurssitoiminnan avulla. (65 780 €) | Ak 6: Tapaturmaisesti ja potilasvahingon vuoksi vammautuneiden tai sairastuneiden alle 30-vuotiaiden lasten  nuorten ja heidän läheistensä arjenhallinnan ja hyvinvoinnin vahvistamiseen vertaistuen ja vapaaehtoistoiminnan keinoin
+          <t>Ak 6: Tapaturmaisesti ja potilasvahingon vuoksi vammautuneiden tai sairastuneiden alle 30-vuotiaiden lasten  nuorten ja heidän läheistensä arjenhallinnan ja hyvinvoinnin vahvistamiseen vertaistuen ja vapaaehtoistoiminnan keinoin
 - Tietoa  tukea ja ohjausta tarjoavan palvelupolkusivuston kehittämiseen ja ylläpitämiseen
-(Palveluja perheen parhaaksi) (203 090 €) | Ak 10943: Erityistä tukea tarvitsevien lasten ja alle 30-vuotiaiden nuorten sekä heidän perheidensä yhdenvertaisuuden  osallisuuden ja voimavarojen lisäämiseen Pohjois-Savossa harrastusryhmätoimintojen  tapahtumien ja tietoisuuden vahvistamisen avulla (200 000 €)</t>
+(Palveluja perheen parhaaksi) (203 090 €) | Ak 10943: Erityistä tukea tarvitsevien lasten ja alle 30-vuotiaiden nuorten sekä heidän perheidensä yhdenvertaisuuden  osallisuuden ja voimavarojen lisäämiseen Pohjois-Savossa harrastusryhmätoimintojen  tapahtumien ja tietoisuuden vahvistamisen avulla (200 000 €) | Ak 7479: Potilasvahingon kokeneiden  narkolepsiaan sairastuneiden  aivoverenkierron häiriön  aivoverenvuodon tai aivokasvaimen jälkitiloista oireilevien sekä ilman vakuutusturvaa olevien tapaturmaisesti vammautuneiden (esim. aivovamma  palovamma  selkäydinvamma) lasten  nuorten (16-29 vuotta) ja heidän läheistensä toimintakyvyn tukemiseen tiedon  verkostotyön  vertaistuen ja kurssitoiminnan avulla. (65 780 €)</t>
         </is>
       </c>
     </row>
@@ -8432,8 +8432,8 @@
       </c>
       <c r="I157" t="inlineStr" s="0">
         <is>
-          <t>Ak 4: Matalan kynnyksen kohtaamispaikkatoimintaan maahanmuuttajille kotoutumisen edistämiseksi (Moninet) (132 300 €) | Ak 2: Matalan kynnyksen kohtaamispaikan avoimeen toimintaan
-mielenterveyskuntoutujille (Jokkatupa) (123 760 €) | Ak 10374: Huumeita käyttävien hyvinvointia ja osallisuutta lisäävään kohtaamispaikkatoimintaan  neuvontaan sekä vertais- ja pienryhmätoimintaan Rovaniemen alueella (Osallisuuskeskus OODI) (196 193 €)</t>
+          <t>Ak 10374: Huumeita käyttävien hyvinvointia ja osallisuutta lisäävään kohtaamispaikkatoimintaan  neuvontaan sekä vertais- ja pienryhmätoimintaan Rovaniemen alueella (Osallisuuskeskus OODI) (196 193 €) | Ak 4: Matalan kynnyksen kohtaamispaikkatoimintaan maahanmuuttajille kotoutumisen edistämiseksi (Moninet) (132 300 €) | Ak 2: Matalan kynnyksen kohtaamispaikan avoimeen toimintaan
+mielenterveyskuntoutujille (Jokkatupa) (123 760 €)</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="I158" t="inlineStr" s="0">
         <is>
-          <t>Ak 4: Työikäisten  ikääntyneiden ja omaishoitotilanteen ohittaneiden omaishoitajien kokonaisvaltaiseen tukemiseen ohjauksen  neuvonnan   tiedotuksen ja edunvalvonnan sekä vapaaehtois-  vertais- ja kokemusasiantuntijatoiminnan avulla Helsingin  Vantaan ja Keravan alueella (Kolmipyöräinen) (170 500 €) | Ay 2241: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (199 584 €) | Ak 3774: Maahanmuuttajataustaisten omaishoitoperheiden osallisuuden  yhdenvertaisuuden ja elämänhallinnan vahvistamiseen sekä syrjäytymisen ehkäisyyn ohjauksen ja neuvonnan  vertais- ja ryhmätoiminnan sekä vapaaehtoisten ja ammattilaisten kouluttamisen avulla (Omaisneuvo) (82 000 €)</t>
+          <t>Ay 2241: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (199 584 €) | Ak 4: Työikäisten  ikääntyneiden ja omaishoitotilanteen ohittaneiden omaishoitajien kokonaisvaltaiseen tukemiseen ohjauksen  neuvonnan   tiedotuksen ja edunvalvonnan sekä vapaaehtois-  vertais- ja kokemusasiantuntijatoiminnan avulla Helsingin  Vantaan ja Keravan alueella (Kolmipyöräinen) (170 500 €) | Ak 3774: Maahanmuuttajataustaisten omaishoitoperheiden osallisuuden  yhdenvertaisuuden ja elämänhallinnan vahvistamiseen sekä syrjäytymisen ehkäisyyn ohjauksen ja neuvonnan  vertais- ja ryhmätoiminnan sekä vapaaehtoisten ja ammattilaisten kouluttamisen avulla (Omaisneuvo) (82 000 €)</t>
         </is>
       </c>
     </row>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="I159" t="inlineStr" s="0">
         <is>
-          <t>Ak 12629: Mielenterveystoipujien toimintakyvyn lisäämiseen verkkomuotoisella klubitalotoiminnalla (eKlubitalo) (183 200 €) | Ak 10388: Mielenterveystoipujia tukevan klubitaloverkoston toiminnan kehittämiseen  kohderyhmän hyvinvoinnissa tapahtuvien muutosten todentamiseen sekä osallisuuden lisäämiseen (267 015 €)</t>
+          <t>Ak 10388: Mielenterveystoipujia tukevan klubitaloverkoston toiminnan kehittämiseen  kohderyhmän hyvinvoinnissa tapahtuvien muutosten todentamiseen sekä osallisuuden lisäämiseen (267 015 €) | Ak 12629: Mielenterveystoipujien toimintakyvyn lisäämiseen verkkomuotoisella klubitalotoiminnalla (eKlubitalo) (183 200 €)</t>
         </is>
       </c>
     </row>
@@ -8532,9 +8532,9 @@
       </c>
       <c r="I160" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Yksinäisten  masentuneiden  sosiaalisesti syrjäytyneiden  monikulttuuristen  psyykkisesti oireilevien ja muiden erityistä tukea tarvitsevien tyttöjen ja nuorten naisten matalankynnyksen toimintaan sekä ryhmä- ja yksilötukeen ja seksuaalista väkivaltaa kokeneiden tukeen
-(Turun Tyttöjen Talo) (209 271 €) | Ak 4307: Tyttöjen osallisuuden ja vuorovaikutustaitojen tukemiseen sekä yksinäisyyden vähentämiseen Turun Varissuon alueella ryhmämuotoisen sukupuoli- ja kulttuurisensitiivisen vapaa-ajan toiminnan ja perheisiin kohdistuvan kotinuorisotyön avulla 
-(Turun Tyttöjen Talo Varissuolla) (236 700 €)</t>
+          <t>Ak 4307: Tyttöjen osallisuuden ja vuorovaikutustaitojen tukemiseen sekä yksinäisyyden vähentämiseen Turun Varissuon alueella ryhmämuotoisen sukupuoli- ja kulttuurisensitiivisen vapaa-ajan toiminnan ja perheisiin kohdistuvan kotinuorisotyön avulla 
+(Turun Tyttöjen Talo Varissuolla) (236 700 €) | Ak 2: Yksinäisten  masentuneiden  sosiaalisesti syrjäytyneiden  monikulttuuristen  psyykkisesti oireilevien ja muiden erityistä tukea tarvitsevien tyttöjen ja nuorten naisten matalankynnyksen toimintaan sekä ryhmä- ja yksilötukeen ja seksuaalista väkivaltaa kokeneiden tukeen
+(Turun Tyttöjen Talo) (209 271 €)</t>
         </is>
       </c>
     </row>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="I162" t="inlineStr" s="0">
         <is>
-          <t>Ak 1493: Rasismia ja sen haittavaikutuksia ennaltaehkäisevään työpajatoimintaan kulttuurisesti moninaisille 4–9-vuotiaille lapsille ja heidän kanssaan samoissa ryhmissä oleville muille lapsille (109 000 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (192 960 €) | Ak 10040: Ilman huoltajaa tulleiden turvapaikanhakijataustaisten lasten ja nuorten sekä haavoittuvassa asemassa olevien maahan muuttaneiden perheiden lasten kotoutumisen ja hyvinvoinnin tukemiseen vapaaehtoisen tukiperhe- ja tukihenkilötoiminnan keinoin (Yhdessä matkalla - tukiperheestä voimaa kotoutumiseen) (136 500 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (192 960 €) | Ak 10040: Ilman huoltajaa tulleiden turvapaikanhakijataustaisten lasten ja nuorten sekä haavoittuvassa asemassa olevien maahan muuttaneiden perheiden lasten kotoutumisen ja hyvinvoinnin tukemiseen vapaaehtoisen tukiperhe- ja tukihenkilötoiminnan keinoin (Yhdessä matkalla - tukiperheestä voimaa kotoutumiseen) (136 500 €) | Ak 1493: Rasismia ja sen haittavaikutuksia ennaltaehkäisevään työpajatoimintaan kulttuurisesti moninaisille 4–9-vuotiaille lapsille ja heidän kanssaan samoissa ryhmissä oleville muille lapsille (109 000 €)</t>
         </is>
       </c>
     </row>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="I167" t="inlineStr" s="0">
         <is>
-          <t>Ak 2702: Jäsenjärjestöille kohdistettaviin avustuksiin (18 000 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (410 130 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (410 130 €) | Ak 2702: Jäsenjärjestöille kohdistettaviin avustuksiin (18 000 €)</t>
         </is>
       </c>
     </row>
@@ -8799,7 +8799,7 @@
       </c>
       <c r="I168" t="inlineStr" s="0">
         <is>
-          <t>Ak 6: För att stöda den åldrande  svenskspråkiga befolkningens delaktighet i samhället genom att främja kunskaper i informations- och kommunikationsteknologi med hjälp av kamratstöd  individuell handledning  kurser och information (It för seniorer) (101 430 €) | Ay 1: Som allmänt understöd för understödstagarens allmännyttiga verksamhet (326 105 €)</t>
+          <t>Ay 1: Som allmänt understöd för understödstagarens allmännyttiga verksamhet (326 105 €) | Ak 6: För att stöda den åldrande  svenskspråkiga befolkningens delaktighet i samhället genom att främja kunskaper i informations- och kommunikationsteknologi med hjälp av kamratstöd  individuell handledning  kurser och information (It för seniorer) (101 430 €)</t>
         </is>
       </c>
     </row>
@@ -8865,7 +8865,7 @@
       </c>
       <c r="I170" t="inlineStr" s="0">
         <is>
-          <t>Ak 9680: Lähisuhdeväkivaltaa vähentävään turvallisuusfokusoituun väkivaltatyöhön (yksilö- ja paritapaamiset) (130 000 €) | Ak 1: Järjestölähtöiseen kriisi- ja mielenterveystyöhön vaikeissa elämäntilanteissa oleville puhelimitse  verkossa  kasvokkain ja ammatillisesti ohjatuissa ryhmissä (Kuopion kriisikeskus) (291 900 €)</t>
+          <t>Ak 1: Järjestölähtöiseen kriisi- ja mielenterveystyöhön vaikeissa elämäntilanteissa oleville puhelimitse  verkossa  kasvokkain ja ammatillisesti ohjatuissa ryhmissä (Kuopion kriisikeskus) (291 900 €) | Ak 9680: Lähisuhdeväkivaltaa vähentävään turvallisuusfokusoituun väkivaltatyöhön (yksilö- ja paritapaamiset) (130 000 €)</t>
         </is>
       </c>
     </row>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="I171" t="inlineStr" s="0">
         <is>
-          <t>Ak 11840: OLKA-toimintamallin mukaiseen vapaaehtoistoiminnan suunnitteluun  koordinointiin  kehittämiseen ja toteuttamiseen sekä sairaalan  sen yksiköiden ja järjestöjen yhteistyöhön (OLKA Kanta-Häme) (115 000 €) | Ak 3: Järjestöjen toimintaedellytysten tukemiseen ja yhteistyön vahvistamiseen järjestökeskustoiminnan avulla Hämeenlinnan seudulla ja Kanta-Hämeessä (105 192 €) | Ak 5: Osallisuutta ja arjenhallintaa edistävän matalan kynnyksen kohtaamispaikan ja miestentilan toimintaan sekä vapaaehtoistoiminnan koordinoimiseen (200 900 €)</t>
+          <t>Ak 5: Osallisuutta ja arjenhallintaa edistävän matalan kynnyksen kohtaamispaikan ja miestentilan toimintaan sekä vapaaehtoistoiminnan koordinoimiseen (200 900 €) | Ak 11840: OLKA-toimintamallin mukaiseen vapaaehtoistoiminnan suunnitteluun  koordinointiin  kehittämiseen ja toteuttamiseen sekä sairaalan  sen yksiköiden ja järjestöjen yhteistyöhön (OLKA Kanta-Häme) (115 000 €) | Ak 3: Järjestöjen toimintaedellytysten tukemiseen ja yhteistyön vahvistamiseen järjestökeskustoiminnan avulla Hämeenlinnan seudulla ja Kanta-Hämeessä (105 192 €)</t>
         </is>
       </c>
     </row>
@@ -8931,13 +8931,13 @@
       </c>
       <c r="I172" t="inlineStr" s="0">
         <is>
-          <t>Ak 6929: Lapissa tapahtuvaan aivoterveyden edistämistyöhön tiedottamisen   kouluttamisen  ryhmätoiminnan ja yhteistyön avulla (MUKU) (63 000 €) | Ak 4: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Lapissa
+          <t>Ak 4: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Lapissa
 - vertaisryhmätoiminnalla
 - ohjauksella ja neuvonnalla
 - vapaaehtoistoiminnalla
 - tiedotuksella
 - edunvalvonnalla
-(Muistiluotsi) (355 005 €)</t>
+(Muistiluotsi) (355 005 €) | Ak 6929: Lapissa tapahtuvaan aivoterveyden edistämistyöhön tiedottamisen   kouluttamisen  ryhmätoiminnan ja yhteistyön avulla (MUKU) (63 000 €)</t>
         </is>
       </c>
     </row>
@@ -8970,7 +8970,7 @@
       </c>
       <c r="I173" t="inlineStr" s="0">
         <is>
-          <t>Ak 9704: Lapsen äänen ja näkökulman esille tuomiseen vanhempien erotilanteessa ja yhteistyövanhemmuuden tukemiseen kohtaamispaikkatoiminnan ja ammatillisesti ohjattujen vertaisryhmien keinoin. (192 386 €) | Ak 1077: Alaikäisten lasten vanhempien ja maahanmuuttajaäitien vanhemmuuden ja osallisuuden tukemiseen sekä lasten ja nuorten yksinäisyyden ehkäisemiseen  sukupolvien välisen kohtaamisen mahdollistamiseen ja lukemissujuvuuden edistämiseen ammatillisesti ohjatun vapaaehtoisen tukihenkilötoiminnan keinoin (Ystäväksi maahanmuuttajaäidille-  Kaveri- ja Perhekummitoiminnat sekä Mummi- ja vaaritoiminta Kaakkois-Suomessa) (221 653 €)</t>
+          <t>Ak 1077: Alaikäisten lasten vanhempien ja maahanmuuttajaäitien vanhemmuuden ja osallisuuden tukemiseen sekä lasten ja nuorten yksinäisyyden ehkäisemiseen  sukupolvien välisen kohtaamisen mahdollistamiseen ja lukemissujuvuuden edistämiseen ammatillisesti ohjatun vapaaehtoisen tukihenkilötoiminnan keinoin (Ystäväksi maahanmuuttajaäidille-  Kaveri- ja Perhekummitoiminnat sekä Mummi- ja vaaritoiminta Kaakkois-Suomessa) (221 653 €) | Ak 9704: Lapsen äänen ja näkökulman esille tuomiseen vanhempien erotilanteessa ja yhteistyövanhemmuuden tukemiseen kohtaamispaikkatoiminnan ja ammatillisesti ohjattujen vertaisryhmien keinoin. (192 386 €)</t>
         </is>
       </c>
     </row>
@@ -9036,8 +9036,8 @@
       </c>
       <c r="I175" t="inlineStr" s="0">
         <is>
-          <t>Ak 12614: För psykosocialt stöd med låg tröskel för svenskspråkiga unga med hjälp av digitala rådgivnings- och chat-tjänster 
-(Luckan Unginfo) (180 000 €) | Ak 2: För språk- och kulturöverskridande mötesplats med låg tröskel med informations- och vägledningstjänster samt mentor- och frivilligverksamhet för invandrare i huvudstadsregionen  Borgå och samt övriga Nyland (228 107 €)</t>
+          <t>Ak 2: För språk- och kulturöverskridande mötesplats med låg tröskel med informations- och vägledningstjänster samt mentor- och frivilligverksamhet för invandrare i huvudstadsregionen  Borgå och samt övriga Nyland (228 107 €) | Ak 12614: För psykosocialt stöd med låg tröskel för svenskspråkiga unga med hjälp av digitala rådgivnings- och chat-tjänster 
+(Luckan Unginfo) (180 000 €)</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="I176" t="inlineStr" s="0">
         <is>
-          <t>Ak 12647: Rikollisesta elämäntavasta irtaantumisen tukemiseen rikostaustaisten henkilöiden asenteiden ja ajatusmallien muutosta tukevalla kognitiivisella muutosohjelmalla  vertais-ammattilaistyöskentelyllä sekä yksilötyöllä Pirkanmaalla  Hämeenlinnan ja Kylmäkosken vankiloissa sekä Rikosseuraamuslaitoksen yksiköissä (muut vankilat) ja päihdekuntoutuksissa (159 615 €) | Ak 1: Rikos- ja päihdetaustaisten ihmisten rikoksettoman sekä päihteettömän elämän motivaation ja edellytysten luomiseen ja vahvistamiseen toimintakeskustoiminnan  vertaistyön  perhetyön ja vankilayhteistyön keinoin (KRIS-Tampereen vankila- ja lainrikkojataustaisten vertaistukityö) (246 915 €)</t>
+          <t>Ak 1: Rikos- ja päihdetaustaisten ihmisten rikoksettoman sekä päihteettömän elämän motivaation ja edellytysten luomiseen ja vahvistamiseen toimintakeskustoiminnan  vertaistyön  perhetyön ja vankilayhteistyön keinoin (KRIS-Tampereen vankila- ja lainrikkojataustaisten vertaistukityö) (246 915 €) | Ak 12647: Rikollisesta elämäntavasta irtaantumisen tukemiseen rikostaustaisten henkilöiden asenteiden ja ajatusmallien muutosta tukevalla kognitiivisella muutosohjelmalla  vertais-ammattilaistyöskentelyllä sekä yksilötyöllä Pirkanmaalla  Hämeenlinnan ja Kylmäkosken vankiloissa sekä Rikosseuraamuslaitoksen yksiköissä (muut vankilat) ja päihdekuntoutuksissa (159 615 €)</t>
         </is>
       </c>
     </row>
@@ -9136,8 +9136,8 @@
       </c>
       <c r="I178" t="inlineStr" s="0">
         <is>
-          <t>Ay 5: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (247 813 €) | Ak 11: Jäsenjärjestöille kohdistettaviin avustuksiin (11 223 €) | Ak 4072: Oppimista  työntekoa ja arjessa selviytymistä tukevien apuvälineiden tunnettuuden ja käytön edistämiseen yksilöllisen ja ryhmämuotoisen ohjauksen ja neuvonnan avulla sekä koulutuksen ja vaikuttamistyön keinoin. Kohderyhminä henkilöt  jotka kokevat oppimisessa vaikeuksia  heidän läheisensä ja ammattilaiset  jotka kohtaavat työssään erilaisia oppijoita. 
-(Oppimisen apuvälinekeskus - tukea arkeen  opintoihin  työhön) (147 000 €)</t>
+          <t>Ay 5: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (247 813 €) | Ak 4072: Oppimista  työntekoa ja arjessa selviytymistä tukevien apuvälineiden tunnettuuden ja käytön edistämiseen yksilöllisen ja ryhmämuotoisen ohjauksen ja neuvonnan avulla sekä koulutuksen ja vaikuttamistyön keinoin. Kohderyhminä henkilöt  jotka kokevat oppimisessa vaikeuksia  heidän läheisensä ja ammattilaiset  jotka kohtaavat työssään erilaisia oppijoita. 
+(Oppimisen apuvälinekeskus - tukea arkeen  opintoihin  työhön) (147 000 €) | Ak 11: Jäsenjärjestöille kohdistettaviin avustuksiin (11 223 €)</t>
         </is>
       </c>
     </row>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="I179" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Yhden vanhemman perheiden osallisuuden ja hyvinvoinnin vahvistamiseen vertais- ja vapaaehtoistoiminnan keinoin (138 694 €) | Ay 3870: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (262 080 €)</t>
+          <t>Ay 3870: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (262 080 €) | Ak 1: Yhden vanhemman perheiden osallisuuden ja hyvinvoinnin vahvistamiseen vertais- ja vapaaehtoistoiminnan keinoin (138 694 €)</t>
         </is>
       </c>
     </row>
@@ -9203,10 +9203,10 @@
       </c>
       <c r="I180" t="inlineStr" s="0">
         <is>
-          <t>Ak 12633: Ulkopuolisuutta kokevien maahanmuuttajien  turvapaikanhakijoiden ja
+          <t>Ak 7704: Mielenterveys- ja päihdekuntoutujien  työelämän ulkopuolella olevien  yksinäisyyttä kokevien ja maahanmuuttajataustaisten henkilöiden osallisuuden  toimintakyvyn ja työelämävalmiuksien vahvistamiseen matalan kynnyksen ryhmätoiminnan  vapaaehtoistyön ja yhteisöllisten tapahtumien avulla Helsingissä (Lapinlahden Lähde) (230 750 €) | Ak 12633: Ulkopuolisuutta kokevien maahanmuuttajien  turvapaikanhakijoiden ja
 pakolaistaustaisten hyvinvoinnin vahvistamiseen  yksinäisyyden vähentämiseen ja arjen 
 mielenterveystaitojen tukemiseen ryhmä- ja kurssitoiminnalla sekä 
-kohderyhmää aktivoivilla tapahtumilla (Miitti) (165 866 €) | Ak 7704: Mielenterveys- ja päihdekuntoutujien  työelämän ulkopuolella olevien  yksinäisyyttä kokevien ja maahanmuuttajataustaisten henkilöiden osallisuuden  toimintakyvyn ja työelämävalmiuksien vahvistamiseen matalan kynnyksen ryhmätoiminnan  vapaaehtoistyön ja yhteisöllisten tapahtumien avulla Helsingissä (Lapinlahden Lähde) (230 750 €)</t>
+kohderyhmää aktivoivilla tapahtumilla (Miitti) (165 866 €)</t>
         </is>
       </c>
     </row>
@@ -9239,7 +9239,7 @@
       </c>
       <c r="I181" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (196 411 €) | Ak 10182: Lasten ja perheiden kanssa toimivien järjestöjen valtakunnallisen perhekeskusverkoston koordinointiin sekä perhekeskustoimijoiden yhteistyön vahvistamiseen verkostotyön  osaamisen vahvistamisen sekä viestinnän avulla. (197 336 €)</t>
+          <t>Ak 10182: Lasten ja perheiden kanssa toimivien järjestöjen valtakunnallisen perhekeskusverkoston koordinointiin sekä perhekeskustoimijoiden yhteistyön vahvistamiseen verkostotyön  osaamisen vahvistamisen sekä viestinnän avulla. (197 336 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (196 411 €)</t>
         </is>
       </c>
     </row>
@@ -9312,8 +9312,8 @@
       <c r="I183" t="inlineStr" s="0">
         <is>
           <t>Ak 1241: Maahan muuttaneiden  etenkin naisten  osallisuuden ja toimijuuden sekä kaksisuuntaisen kotoutumisen vahvistamiseen vapaaehtoistyönä toteutettavan suomen kielen sekä luku- ja kirjoitustaidon opetuksen avulla 
-(Luetaan yhdessä -verkosto) (213 885 €) | C 13653: Turvapaikka-  maahanmuutto- ja kotouttamisrahaston hankkeen ”Sosiaalista suomea - Toisto-menetelmä kouluihin" osarahoitukseen järjestölle (2026-2028) (32 682 €) | Ak 11191: Maahan muuttaneiden naisten osallisuuden  työllistymisen ja urakehityksen sekä kaksisuuntaisen kotoutumisen edistämiseen ryhmämuotoisen mentoroinnin  vapaaehtoistoiminnan  verkostoitumisen ja vertaistuen avulla 
-(Auroras) (143 040 €)</t>
+(Luetaan yhdessä -verkosto) (213 885 €) | Ak 11191: Maahan muuttaneiden naisten osallisuuden  työllistymisen ja urakehityksen sekä kaksisuuntaisen kotoutumisen edistämiseen ryhmämuotoisen mentoroinnin  vapaaehtoistoiminnan  verkostoitumisen ja vertaistuen avulla 
+(Auroras) (143 040 €) | C 13653: Turvapaikka-  maahanmuutto- ja kotouttamisrahaston hankkeen ”Sosiaalista suomea - Toisto-menetelmä kouluihin" osarahoitukseen järjestölle (2026-2028) (32 682 €)</t>
         </is>
       </c>
     </row>
@@ -9447,8 +9447,8 @@
       </c>
       <c r="I187" t="inlineStr" s="0">
         <is>
-          <t>Ak 10985: Asunnottomien ja asunnottomuusuhan alla olevien henkilöiden elämänlaadun ja -hallinnan lisäämiseen yksilöllisen tuki- ja neuvontatyön avulla Kuopion seudulla (132 501 €) | C 13803: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Yhdessä ajatuksista aikomuksiksi" (211336) osarahoitukseen järjestölle (2026-2027) (40 000 €) | Ak 10208: Huono-osaisten väestöryhmien osallisuuden  arjenhallinnan ja sosiaalisten
-verkostojen lisäämiseen kohtaamispaikan  vapaaehtoisuuteen pohjautuvan ryhmätoiminnan ja yksilöllisen tuen avulla Kuopiossa (148 838 €)</t>
+          <t>Ak 10208: Huono-osaisten väestöryhmien osallisuuden  arjenhallinnan ja sosiaalisten
+verkostojen lisäämiseen kohtaamispaikan  vapaaehtoisuuteen pohjautuvan ryhmätoiminnan ja yksilöllisen tuen avulla Kuopiossa (148 838 €) | Ak 10985: Asunnottomien ja asunnottomuusuhan alla olevien henkilöiden elämänlaadun ja -hallinnan lisäämiseen yksilöllisen tuki- ja neuvontatyön avulla Kuopion seudulla (132 501 €) | C 13803: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Yhdessä ajatuksista aikomuksiksi" (211336) osarahoitukseen järjestölle (2026-2027) (40 000 €)</t>
         </is>
       </c>
     </row>
@@ -9481,7 +9481,7 @@
       </c>
       <c r="I188" t="inlineStr" s="0">
         <is>
-          <t>Ak 9881: Surujärjestöjen yhteiseen kokemusasiantuntijatoimintaan ja asiantuntijatoimintaan läheisen varhaista tai äkillistä kuolemaa surevien henkilöiden tuen saannin edistämiseksi valtakunnallisesti (Surevan kohtaaminen). (146 000 €) | Ay 3: Yleisavustuksena avustuksena saajan yleishyödylliseen toimintaan (238 526 €)</t>
+          <t>Ay 3: Yleisavustuksena avustuksena saajan yleishyödylliseen toimintaan (238 526 €) | Ak 9881: Surujärjestöjen yhteiseen kokemusasiantuntijatoimintaan ja asiantuntijatoimintaan läheisen varhaista tai äkillistä kuolemaa surevien henkilöiden tuen saannin edistämiseksi valtakunnallisesti (Surevan kohtaaminen). (146 000 €)</t>
         </is>
       </c>
     </row>
@@ -9514,7 +9514,7 @@
       </c>
       <c r="I189" t="inlineStr" s="0">
         <is>
-          <t>Ak 10461: Hoivaajan asemassa olevien alle 18-vuotiaiden lasten ja nuorten sekä heidän vanhempiensa kuormittumisen ja syrjäytymisen ennaltaehkäisyyn ja vähentämiseen vertaistuen  yksilöllisen tuen ja virkistäytymismahdollisuuksien avulla (ALISA-toiminta) (98 070 €) | Ak 2: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen  neuvonnan  vertaistoiminnan ja valmennusten avulla Pohjois-Karjalassa (OmaisOiva) (280 500 €)</t>
+          <t>Ak 2: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen  neuvonnan  vertaistoiminnan ja valmennusten avulla Pohjois-Karjalassa (OmaisOiva) (280 500 €) | Ak 10461: Hoivaajan asemassa olevien alle 18-vuotiaiden lasten ja nuorten sekä heidän vanhempiensa kuormittumisen ja syrjäytymisen ennaltaehkäisyyn ja vähentämiseen vertaistuen  yksilöllisen tuen ja virkistäytymismahdollisuuksien avulla (ALISA-toiminta) (98 070 €)</t>
         </is>
       </c>
     </row>
@@ -9580,13 +9580,13 @@
       </c>
       <c r="I191" t="inlineStr" s="0">
         <is>
-          <t>C 13786: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Nuorten aivostudio – Muisti  terveys ja elintavat" osarahoitukseen järjestölle (2026-2028) (96 000 €) | Ak 2: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Keski-Pohjanmaalla ja Pohjois-Pohjanmaan eteläosassa
+          <t>Ak 2: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Keski-Pohjanmaalla ja Pohjois-Pohjanmaan eteläosassa
 - vertaisryhmätoiminnalla
 - ohjauksella ja neuvonnalla
 - vapaaehtoistoiminnalla
 - tiedotuksella
 - edunvalvonnalla
-(Muistiluotsi) (280 586 €)</t>
+(Muistiluotsi) (280 586 €) | C 13786: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Nuorten aivostudio – Muisti  terveys ja elintavat" osarahoitukseen järjestölle (2026-2028) (96 000 €)</t>
         </is>
       </c>
     </row>
@@ -9619,7 +9619,7 @@
       </c>
       <c r="I192" t="inlineStr" s="0">
         <is>
-          <t>Ak 5: Lähi- ja parisuhdeväkivallan ehkäisemiseen ja katkaisemisen yksilö-  pari- ja ryhmätapaamisten sekä tiedottamisen ja koulutuksen keinoin (125 000 €) | Ak 6: Vauvaperheiden vanhemmuuden  hyvinvoinnin ja vuorovaikutuksen ryhmämuotoiseen tukemiseen (Vauvaperheryhmä Pirpana). Lasten ja lapsiperheiden yksinäisyyden vähentämiseen vapaaehtois- ja vertaistoiminnan keinoin (Perhekerhot  vapaaehtoisdoula-toiminta erityistä tukea tarvitseville lapsiperheille  vertaisryhmät ja tapahtumat). (125 685 €) | Ak 2463: Eroperheiden auttamiseen ja tukemiseen sekä uusperheiden ennaltaehkäisevään tukemiseen yksilö-  pari- ja ryhmätyöskentelyn keinoin ja verkkovälitteiseen auttamiseen (Ero lapsiperheessä -työ) (124 918 €)</t>
+          <t>Ak 6: Vauvaperheiden vanhemmuuden  hyvinvoinnin ja vuorovaikutuksen ryhmämuotoiseen tukemiseen (Vauvaperheryhmä Pirpana). Lasten ja lapsiperheiden yksinäisyyden vähentämiseen vapaaehtois- ja vertaistoiminnan keinoin (Perhekerhot  vapaaehtoisdoula-toiminta erityistä tukea tarvitseville lapsiperheille  vertaisryhmät ja tapahtumat). (125 685 €) | Ak 5: Lähi- ja parisuhdeväkivallan ehkäisemiseen ja katkaisemisen yksilö-  pari- ja ryhmätapaamisten sekä tiedottamisen ja koulutuksen keinoin (125 000 €) | Ak 2463: Eroperheiden auttamiseen ja tukemiseen sekä uusperheiden ennaltaehkäisevään tukemiseen yksilö-  pari- ja ryhmätyöskentelyn keinoin ja verkkovälitteiseen auttamiseen (Ero lapsiperheessä -työ) (124 918 €)</t>
         </is>
       </c>
     </row>
@@ -9718,7 +9718,7 @@
       </c>
       <c r="I195" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Ikääntyneiden osallisuuden ja sosiaalisten kontaktien lisäämiseen sekä yksinäisyyden tunteen vähentämiseen vapaaehtoistoiminnan ja kohtaamispaikkatoiminnan keinoin (Virtaa vapaaehtoistyöhön) (100 669 €) | Ak 7523: Kotona asuvien yli 75-vuotiaiden yksinäisyyden kokemuksen vähentämiseen sekä osallisuuden kokemuksen lisäämiseen etsivän vanhustyön  kerhotoiminnan  retkien ja tapahtumien sekä ylisukupolvisen oppilaitosyhteistyön avulla (Kiinni elämässä -toiminta) (168 000 €) | Ak 12641: Päijät-Hämeen vapaaehtoistoiminnan verkoston koordinoimiseen  alueellisen vapaaehtoistoiminnan edistämiseen ja yhteistyön tukemiseen vapaaehtoistoimijoiden kesken (Päijät-Hämeen vapaaehtoistoiminnan verkosto) (102 669 €)</t>
+          <t>Ak 7523: Kotona asuvien yli 75-vuotiaiden yksinäisyyden kokemuksen vähentämiseen sekä osallisuuden kokemuksen lisäämiseen etsivän vanhustyön  kerhotoiminnan  retkien ja tapahtumien sekä ylisukupolvisen oppilaitosyhteistyön avulla (Kiinni elämässä -toiminta) (168 000 €) | Ak 12641: Päijät-Hämeen vapaaehtoistoiminnan verkoston koordinoimiseen  alueellisen vapaaehtoistoiminnan edistämiseen ja yhteistyön tukemiseen vapaaehtoistoimijoiden kesken (Päijät-Hämeen vapaaehtoistoiminnan verkosto) (102 669 €) | Ak 3: Ikääntyneiden osallisuuden ja sosiaalisten kontaktien lisäämiseen sekä yksinäisyyden tunteen vähentämiseen vapaaehtoistoiminnan ja kohtaamispaikkatoiminnan keinoin (Virtaa vapaaehtoistyöhön) (100 669 €)</t>
         </is>
       </c>
     </row>
@@ -9751,7 +9751,7 @@
       </c>
       <c r="I196" t="inlineStr" s="0">
         <is>
-          <t>Ak 4: Vapaaehtois- ja vertaistoiminnan toteuttamiseen ja kehittämiseen eri kohderyhmien (mm. päihdekuntoutujat  neuropsykiatrisista oireista kärsivät) arjen ja toimintakyvyn tukemiseksi (150 000 €) | Ak 7191: Maahanmuuttajien sosiaalisen hyvinvoinnin ja yhteiskuntaan integroitumisen tukemiseen kohtaamispaikkatoiminnan avulla (220 500 €)</t>
+          <t>Ak 7191: Maahanmuuttajien sosiaalisen hyvinvoinnin ja yhteiskuntaan integroitumisen tukemiseen kohtaamispaikkatoiminnan avulla (220 500 €) | Ak 4: Vapaaehtois- ja vertaistoiminnan toteuttamiseen ja kehittämiseen eri kohderyhmien (mm. päihdekuntoutujat  neuropsykiatrisista oireista kärsivät) arjen ja toimintakyvyn tukemiseksi (150 000 €)</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="I197" t="inlineStr" s="0">
         <is>
-          <t>Ak 4131: Mielenterveyden haasteita kohdanneiden nuorten aikuisten toimintakyvyn ja mielen hyvinvoinnin lisäämisen vertaistukseen perustuvalla matalankynnyksen toiminnalla (Kulttuuripaja Trombi) (148 837 €) | Ak 2: Mielenterveyskuntoutujien terveyttä  hyvinvointia  osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään tavoitteelliseen kohtaamispaikkatoimintaan (Suvimäen FH-klubitalo) (215 250 €)</t>
+          <t>Ak 2: Mielenterveyskuntoutujien terveyttä  hyvinvointia  osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään tavoitteelliseen kohtaamispaikkatoimintaan (Suvimäen FH-klubitalo) (215 250 €) | Ak 4131: Mielenterveyden haasteita kohdanneiden nuorten aikuisten toimintakyvyn ja mielen hyvinvoinnin lisäämisen vertaistukseen perustuvalla matalankynnyksen toiminnalla (Kulttuuripaja Trombi) (148 837 €)</t>
         </is>
       </c>
     </row>
@@ -9817,9 +9817,9 @@
       </c>
       <c r="I198" t="inlineStr" s="0">
         <is>
-          <t>Ak 3890: Maahanmuuttajataustaisten nuorten aikuisten aktiivisuutta  osallisuutta  yhteiskuntaan kuulumisen tunnetta ja työllistymistä edistävään toimintaan vertaistuen  yksilöllinen tuen ja ryhmätoiminnan avulla pääkaupunkiseudulla 
-(Toiminnan Avulla Työelämään - TAT) (173 369 €) | Ak 2: Maahanmuuttajanuorten osallistavaan viikonlopputoimintaan ja osallistumisen edistämiseen jalkautuvan ryhmätoiminnan avulla 
-(Yökoripallo-toiminta  Helsinki) (188 554 €)</t>
+          <t>Ak 2: Maahanmuuttajanuorten osallistavaan viikonlopputoimintaan ja osallistumisen edistämiseen jalkautuvan ryhmätoiminnan avulla 
+(Yökoripallo-toiminta  Helsinki) (188 554 €) | Ak 3890: Maahanmuuttajataustaisten nuorten aikuisten aktiivisuutta  osallisuutta  yhteiskuntaan kuulumisen tunnetta ja työllistymistä edistävään toimintaan vertaistuen  yksilöllinen tuen ja ryhmätoiminnan avulla pääkaupunkiseudulla 
+(Toiminnan Avulla Työelämään - TAT) (173 369 €)</t>
         </is>
       </c>
     </row>
@@ -9919,7 +9919,7 @@
       </c>
       <c r="I201" t="inlineStr" s="0">
         <is>
-          <t>Ak 11261: Lapsiin ja nuoriin kohdistuvan seksuaalisen väkivallan ennaltaehkäisemiseen matalan kynnyksen tukipalvelun  neuvonnan ja palveluohjauksen avulla henkilöille  joilla on kohonnut riski syyllistyä seksuaaliseen väkivaltaan (SeriE: Lapsiin kohdistuvien seksuaalirikosten ennaltaehkäisy 2026) (80 000 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (279 060 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (279 060 €) | Ak 11261: Lapsiin ja nuoriin kohdistuvan seksuaalisen väkivallan ennaltaehkäisemiseen matalan kynnyksen tukipalvelun  neuvonnan ja palveluohjauksen avulla henkilöille  joilla on kohonnut riski syyllistyä seksuaaliseen väkivaltaan (SeriE: Lapsiin kohdistuvien seksuaalirikosten ennaltaehkäisy 2026) (80 000 €)</t>
         </is>
       </c>
     </row>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="I204" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Mielenterveyskuntoutujien terveyttä  hyvinvointia  osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään kohtaamispaikkatoimintaan (Heikintalo) (168 241 €) | Ak 12399: 18–35-vuotiaiden mielenterveys- ja päihdekuntoutujien yhteisöllisyyden  osallisuuden  yhdenvertaisuuden ja suvaitsevaisuuden lisäämiseen sekä toiminta- ja työkyvyn sekä terveyden edistämiseen järjestämällä toiminnalliseen vertaistukeen perustuvaa kulttuuripajatoimintaa (Kulttuuripaja Saimaa) (185 021 €)</t>
+          <t>Ak 12399: 18–35-vuotiaiden mielenterveys- ja päihdekuntoutujien yhteisöllisyyden  osallisuuden  yhdenvertaisuuden ja suvaitsevaisuuden lisäämiseen sekä toiminta- ja työkyvyn sekä terveyden edistämiseen järjestämällä toiminnalliseen vertaistukeen perustuvaa kulttuuripajatoimintaa (Kulttuuripaja Saimaa) (185 021 €) | Ak 1: Mielenterveyskuntoutujien terveyttä  hyvinvointia  osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään kohtaamispaikkatoimintaan (Heikintalo) (168 241 €)</t>
         </is>
       </c>
     </row>
@@ -10051,7 +10051,7 @@
       </c>
       <c r="I205" t="inlineStr" s="0">
         <is>
-          <t>Ak 4: Vauvaperheiden vanhemmuuden ja vuorovaikutuksen tukemiseen ryhmätoiminnan keinoin (vauvaperheryhmätoiminta vauvaperheille)  lapsiperheiden elämänhallinnan ja toimintakyvyn edistämiseen asumisen tukipalveluilla sekä yhdistyksen vapaaehtoistyön koordinointiin (150 393 €) | Ak 10: Yksilö-  pari- ja ryhmämuotoiseen avokriisityöhön perhe- ja lähisuhdeväkivaltaa kokeneiden  tekijöiden ja altistuneiden kanssa sekä haastavissa erotilanteissa olevien perheiden tukemiseen (Avokriisityö) (200 899 €)</t>
+          <t>Ak 10: Yksilö-  pari- ja ryhmämuotoiseen avokriisityöhön perhe- ja lähisuhdeväkivaltaa kokeneiden  tekijöiden ja altistuneiden kanssa sekä haastavissa erotilanteissa olevien perheiden tukemiseen (Avokriisityö) (200 899 €) | Ak 4: Vauvaperheiden vanhemmuuden ja vuorovaikutuksen tukemiseen ryhmätoiminnan keinoin (vauvaperheryhmätoiminta vauvaperheille)  lapsiperheiden elämänhallinnan ja toimintakyvyn edistämiseen asumisen tukipalveluilla sekä yhdistyksen vapaaehtoistyön koordinointiin (150 393 €)</t>
         </is>
       </c>
     </row>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="I216" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Nuorisoväkivallan ehkäisyyn ryhmätoiminnan avulla ja nuorten väkivallattoman käyttäytymisen edistämiseen sekä kiusaamisen vastaiseen työhön Itä- ja Kaakkois-Suomessa (150 395 €) | Ak 1: Nuorisoväkivallan ehkäisyyn ja nuorten väkivallattoman käyttäytymisen edistämiseen ryhmätoiminnan avulla sekä kiusaamisen vastaiseen työhön Etelä-Suomessa (184 065 €)</t>
+          <t>Ak 1: Nuorisoväkivallan ehkäisyyn ja nuorten väkivallattoman käyttäytymisen edistämiseen ryhmätoiminnan avulla sekä kiusaamisen vastaiseen työhön Etelä-Suomessa (184 065 €) | Ak 3: Nuorisoväkivallan ehkäisyyn ryhmätoiminnan avulla ja nuorten väkivallattoman käyttäytymisen edistämiseen sekä kiusaamisen vastaiseen työhön Itä- ja Kaakkois-Suomessa (150 395 €)</t>
         </is>
       </c>
     </row>
@@ -10594,7 +10594,7 @@
       </c>
       <c r="I221" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (134 136 €) | Ak 11240: Nuorten huumeidenkäytön  varhaisten kokeilujen ja käytöstä aiheutuvien haittojen ehkäisyyn nuoria osallistavan vapaaehtoistoiminnan  koulutuksen ja päihteettömän toiminnan avulla (196 000 €)</t>
+          <t>Ak 11240: Nuorten huumeidenkäytön  varhaisten kokeilujen ja käytöstä aiheutuvien haittojen ehkäisyyn nuoria osallistavan vapaaehtoistoiminnan  koulutuksen ja päihteettömän toiminnan avulla (196 000 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (134 136 €)</t>
         </is>
       </c>
     </row>
@@ -10726,7 +10726,7 @@
       </c>
       <c r="I225" t="inlineStr" s="0">
         <is>
-          <t>Ak 2605: Jäsenjärjestöille kohdistettaviin avustuksiin (6 180 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (166 000 €) | Ak 3: Vertaisperhekursseja  leirejä  verkkotilaisuuksia ja tapahtumia sisältävän vertaistoiminnan järjestämiseen kuulovammaisten lasten perheille (154 500 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (166 000 €) | Ak 3: Vertaisperhekursseja  leirejä  verkkotilaisuuksia ja tapahtumia sisältävän vertaistoiminnan järjestämiseen kuulovammaisten lasten perheille (154 500 €) | Ak 2605: Jäsenjärjestöille kohdistettaviin avustuksiin (6 180 €)</t>
         </is>
       </c>
     </row>
@@ -10831,7 +10831,7 @@
       </c>
       <c r="I228" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: För vänverksamhet för svenskspråkiga personer med olika funktionsnedsättningar i Nyland och Österbotten (134 000 €) | Ak 1: För juridisk rådgivning  intressebevakning och informationsverksamhet till förmån för personer med funktionsnedsättning och deras närstående i Svenskfinland (189 138 €)</t>
+          <t>Ak 1: För juridisk rådgivning  intressebevakning och informationsverksamhet till förmån för personer med funktionsnedsättning och deras närstående i Svenskfinland (189 138 €) | Ak 2: För vänverksamhet för svenskspråkiga personer med olika funktionsnedsättningar i Nyland och Österbotten (134 000 €)</t>
         </is>
       </c>
     </row>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="I238" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Päihde- ja moniongelmaisten asumistilannetta ja asumisen onnistumista edistävään tukitoimintaan (Pirtti-toiminta) (131 314 €) | Ak 3: Pitkäaikaistyöttömien sekä päihde- ja mielenterveyskuntoutujien sosiaaliseen vahvistamiseen sekä arjenhallintataitojen lisäämiseen ryhmätoiminnalla ja yksilöllisellä tuella (185 861 €)</t>
+          <t>Ak 3: Pitkäaikaistyöttömien sekä päihde- ja mielenterveyskuntoutujien sosiaaliseen vahvistamiseen sekä arjenhallintataitojen lisäämiseen ryhmätoiminnalla ja yksilöllisellä tuella (185 861 €) | Ak 2: Päihde- ja moniongelmaisten asumistilannetta ja asumisen onnistumista edistävään tukitoimintaan (Pirtti-toiminta) (131 314 €)</t>
         </is>
       </c>
     </row>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="I239" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Lapsiperheitä tukevaan järjestölähtöiseen avopalvelutoimintaan (Avitus-toiminta: Ero lapsiperheessä-  vertaisryhmä-  Yökylä-  Päiväleiri-  ja Mummolatoiminta  Perhetuvan Lauantai  chatverkkoauttaminen  kansalaisjärjestötoiminta) (101 430 €) | Ak 1586: Pikkulapsiperheiden vanhemmuuden ja vuorovaikutuksen yksilö- ja ryhmämuotoiseen tukemiseen (vauvaperheryhmätoiminta  vapaaehtoisdoula-toiminta ja raskausajan työskentely erityistä tukea tarvitseville vauvaa odottaville perheille  chat  isätoiminta) (213 150 €)</t>
+          <t>Ak 1586: Pikkulapsiperheiden vanhemmuuden ja vuorovaikutuksen yksilö- ja ryhmämuotoiseen tukemiseen (vauvaperheryhmätoiminta  vapaaehtoisdoula-toiminta ja raskausajan työskentely erityistä tukea tarvitseville vauvaa odottaville perheille  chat  isätoiminta) (213 150 €) | Ak 2: Lapsiperheitä tukevaan järjestölähtöiseen avopalvelutoimintaan (Avitus-toiminta: Ero lapsiperheessä-  vertaisryhmä-  Yökylä-  Päiväleiri-  ja Mummolatoiminta  Perhetuvan Lauantai  chatverkkoauttaminen  kansalaisjärjestötoiminta) (101 430 €)</t>
         </is>
       </c>
     </row>
@@ -11294,7 +11294,7 @@
       </c>
       <c r="I242" t="inlineStr" s="0">
         <is>
-          <t>Ak 11271: OLKA-toimintamallin mukaiseen vapaaehtoistyön koordinointiin sekä sairastuneen toimintakyvyn vahvistamiseen järjestöjen ja keskussairaalan yhteistyöllä (OLKA-toiminta Keski-Pohjanmaa) (120 750 €) | Ak 1: Kansalaistoimintakeskuksen kohtaamispaikan koordinointiin tukemaan yhdistysten toimintaa  kehittämään vapaaehtoistoimintaa ja verkostotyötä sekä tarjoamaan alueen eri asukasryhmille kohtaamispaikka Kokkolassa (Yhteisöklubi-Gemenskapsklubben SILTA) (187 425 €)</t>
+          <t>Ak 1: Kansalaistoimintakeskuksen kohtaamispaikan koordinointiin tukemaan yhdistysten toimintaa  kehittämään vapaaehtoistoimintaa ja verkostotyötä sekä tarjoamaan alueen eri asukasryhmille kohtaamispaikka Kokkolassa (Yhteisöklubi-Gemenskapsklubben SILTA) (187 425 €) | Ak 11271: OLKA-toimintamallin mukaiseen vapaaehtoistyön koordinointiin sekä sairastuneen toimintakyvyn vahvistamiseen järjestöjen ja keskussairaalan yhteistyöllä (OLKA-toiminta Keski-Pohjanmaa) (120 750 €)</t>
         </is>
       </c>
     </row>
@@ -11327,7 +11327,7 @@
       </c>
       <c r="I243" t="inlineStr" s="0">
         <is>
-          <t>Ak 10747: Kodin ulkopuoliseen väkivaltaan syyllistyneiden tai syyllistymisriskissä olevien väkivaltaisen käyttäytymisen vähentämiseen ja ehkäisemiseen yksilöllisen asiakastyön ja verkostotyön avulla (138 740 €) | C 13700: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Osaamista alaikäisten rikosten torjumiseksi (210285)" osarahoitukseen järjestölle (2026-2028) (41 295 €) | Ak 6112: Pääasiallisesti alle 30-vuotiaiden Turun alueelle vapautuvien vankien ja yhdyskuntaseuraamusasiakkaiden elämänhallinnan edistämiseen yksilöllisen tuen ja ryhmätoiminnan avulla (126 974 €)</t>
+          <t>Ak 10747: Kodin ulkopuoliseen väkivaltaan syyllistyneiden tai syyllistymisriskissä olevien väkivaltaisen käyttäytymisen vähentämiseen ja ehkäisemiseen yksilöllisen asiakastyön ja verkostotyön avulla (138 740 €) | Ak 6112: Pääasiallisesti alle 30-vuotiaiden Turun alueelle vapautuvien vankien ja yhdyskuntaseuraamusasiakkaiden elämänhallinnan edistämiseen yksilöllisen tuen ja ryhmätoiminnan avulla (126 974 €) | C 13700: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Osaamista alaikäisten rikosten torjumiseksi (210285)" osarahoitukseen järjestölle (2026-2028) (41 295 €)</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="I245" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (167 000 €) | Ak 3: Avanne- ja vastaavasti leikattujen ja anaali-inkontinenssipotilaiden sekä heidän läheistensä tukemiseen sairauden käsittelyssä ja omahoidon toteuttamisessa sekä terveyden ja hyvinvoinnin edistämiseen tavoitteellisen ryhmätoiminnan avulla (60 000 €) | Ak 12529: Avanne- ja vastaavasti leikattujen ja anaali-inkontinenssipotilaiden sekä heidän läheistensä vapaaehtoistoiminnan koordinointiin sekä vapaaehtoisten tukemiseen  koulutuksiin ja virkistykseen (61 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (167 000 €) | Ak 12529: Avanne- ja vastaavasti leikattujen ja anaali-inkontinenssipotilaiden sekä heidän läheistensä vapaaehtoistoiminnan koordinointiin sekä vapaaehtoisten tukemiseen  koulutuksiin ja virkistykseen (61 000 €) | Ak 3: Avanne- ja vastaavasti leikattujen ja anaali-inkontinenssipotilaiden sekä heidän läheistensä tukemiseen sairauden käsittelyssä ja omahoidon toteuttamisessa sekä terveyden ja hyvinvoinnin edistämiseen tavoitteellisen ryhmätoiminnan avulla (60 000 €)</t>
         </is>
       </c>
     </row>
@@ -11630,7 +11630,7 @@
       </c>
       <c r="I252" t="inlineStr" s="0">
         <is>
-          <t>Ak 12355: Kotona yksin asuvien ikääntyneiden fyysisen kunnon  liikkumis- ja toimintakyvyn ylläpitämiseen vapaaehtoisten kuntoilukummien avulla (Kuntoilukummitoiminta) (131 945 €) | Ak 1: Yksin asuvien ikääntyneiden yksinäisyyden tunteen vähentämiseen  osallisuuden lisäämiseen ja voimavarojen vahvistamiseen pitkäkestoisen ja kertaluontoisen ystävätoiminnan avulla (163 767 €)</t>
+          <t>Ak 1: Yksin asuvien ikääntyneiden yksinäisyyden tunteen vähentämiseen  osallisuuden lisäämiseen ja voimavarojen vahvistamiseen pitkäkestoisen ja kertaluontoisen ystävätoiminnan avulla (163 767 €) | Ak 12355: Kotona yksin asuvien ikääntyneiden fyysisen kunnon  liikkumis- ja toimintakyvyn ylläpitämiseen vapaaehtoisten kuntoilukummien avulla (Kuntoilukummitoiminta) (131 945 €)</t>
         </is>
       </c>
     </row>
@@ -11846,7 +11846,7 @@
       </c>
       <c r="I258" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Kilpirauhas- ja lisäkilpirauhassairaiden sekä heidän läheistensä tiedon ja vertaistuen lisäämiseen liittyen sairauteen ja sen hoitovaihtoehtoihin sekä liitännäissairauksien (mm. sydän- ja verisuonisairaudet ja osteoporoosi) ennaltaehkäisemiseen voimavarakurssien avulla (50 274 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (225 440 €) | Ak 3: Jäsenjärjestöille kohdistettaviin avustuksiin (14 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (225 440 €) | Ak 2: Kilpirauhas- ja lisäkilpirauhassairaiden sekä heidän läheistensä tiedon ja vertaistuen lisäämiseen liittyen sairauteen ja sen hoitovaihtoehtoihin sekä liitännäissairauksien (mm. sydän- ja verisuonisairaudet ja osteoporoosi) ennaltaehkäisemiseen voimavarakurssien avulla (50 274 €) | Ak 3: Jäsenjärjestöille kohdistettaviin avustuksiin (14 000 €)</t>
         </is>
       </c>
     </row>
@@ -11945,7 +11945,7 @@
       </c>
       <c r="I261" t="inlineStr" s="0">
         <is>
-          <t>Ak 6940: OLKA-toimintamallin mukaiseen vapaaehtoistoiminnan koordinointiin  kehittämiseen ja toteuttamiseen sekä sairaaloiden ja järjestöjen yhteistyöhön Pohjois-Pohjanmaan hyvinvointialueella (120 750 €) | Ak 1: Järjestölähtöiseen toiminnan toteuttamiseen Oulussa sijaitsevan kumppanuuskeskuksen neuvontapisteessä  kansalaisten järjestötiedon ja osallisuuden lisäämiseen sekä järjestöjen välisen yhteistyön edistämiseen (168 000 €)</t>
+          <t>Ak 1: Järjestölähtöiseen toiminnan toteuttamiseen Oulussa sijaitsevan kumppanuuskeskuksen neuvontapisteessä  kansalaisten järjestötiedon ja osallisuuden lisäämiseen sekä järjestöjen välisen yhteistyön edistämiseen (168 000 €) | Ak 6940: OLKA-toimintamallin mukaiseen vapaaehtoistoiminnan koordinointiin  kehittämiseen ja toteuttamiseen sekä sairaaloiden ja järjestöjen yhteistyöhön Pohjois-Pohjanmaan hyvinvointialueella (120 750 €)</t>
         </is>
       </c>
     </row>
@@ -12045,9 +12045,9 @@
       </c>
       <c r="I264" t="inlineStr" s="0">
         <is>
-          <t>C 13724: Euroopan sosiaalirahasto plussan (ESR+) hankkeen  "Pikkuhelppiä perheille" osarahoitukseen järjestölle (2026) (69 000 €) | Ak 3739: Palveluoperaatio Saappaan vapaaehtoistyön koulutustoimintaan ja koordinointiin. 
-(Palveluoperaatio Saapas) (88 871 €) | Ak 3923: Nuorten sosiaalisia taitoja vahvistavan moottoripajatoiminnan valtakunnalliseen koordinointiin ja moottoripajatoiminnassa toimivien vapaaehtoisten koulutukseen.
-(Moottoripajatoiminta) (128 444 €)</t>
+          <t>Ak 3923: Nuorten sosiaalisia taitoja vahvistavan moottoripajatoiminnan valtakunnalliseen koordinointiin ja moottoripajatoiminnassa toimivien vapaaehtoisten koulutukseen.
+(Moottoripajatoiminta) (128 444 €) | Ak 3739: Palveluoperaatio Saappaan vapaaehtoistyön koulutustoimintaan ja koordinointiin. 
+(Palveluoperaatio Saapas) (88 871 €) | C 13724: Euroopan sosiaalirahasto plussan (ESR+) hankkeen  "Pikkuhelppiä perheille" osarahoitukseen järjestölle (2026) (69 000 €)</t>
         </is>
       </c>
     </row>
@@ -12212,7 +12212,7 @@
       </c>
       <c r="I269" t="inlineStr" s="0">
         <is>
-          <t>Ak 10277: OLKA-toimintamallin mukaiseen vapaaehtoistoiminnan suunnitteluun  koordinointiin  kehittämiseen ja toteuttamiseen sekä julkisen terveydenhuollon ja järjestöjen yhteistyöhön (OLKA-toiminta Pohjanmaan hyvinvointialueella) (116 550 €) | Ak 1: Järjestöjen toimintaedellytysten tukemiseen Pohjanmaalla koordinoimalla järjestökeskuksen ja kohtaamispaikan toimintaa sekä edistämällä vapaaehtois- ja vertaistoimintaa. (165 560 €)</t>
+          <t>Ak 1: Järjestöjen toimintaedellytysten tukemiseen Pohjanmaalla koordinoimalla järjestökeskuksen ja kohtaamispaikan toimintaa sekä edistämällä vapaaehtois- ja vertaistoimintaa. (165 560 €) | Ak 10277: OLKA-toimintamallin mukaiseen vapaaehtoistoiminnan suunnitteluun  koordinointiin  kehittämiseen ja toteuttamiseen sekä julkisen terveydenhuollon ja järjestöjen yhteistyöhön (OLKA-toiminta Pohjanmaan hyvinvointialueella) (116 550 €)</t>
         </is>
       </c>
     </row>
@@ -12344,7 +12344,7 @@
       </c>
       <c r="I273" t="inlineStr" s="0">
         <is>
-          <t>Ak 9737: Migreeniä ja vaikeita päänsärkysairauksia sairastavien hyvinvoinnin  toimintakyvyn  työelämäosallisuuden ja yhdenvertaisuuden edistämiseen ammatillisesti organisoidun vapaaehtoistoiminnan keinoin (46 000 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (233 856 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (233 856 €) | Ak 9737: Migreeniä ja vaikeita päänsärkysairauksia sairastavien hyvinvoinnin  toimintakyvyn  työelämäosallisuuden ja yhdenvertaisuuden edistämiseen ammatillisesti organisoidun vapaaehtoistoiminnan keinoin (46 000 €)</t>
         </is>
       </c>
     </row>
@@ -12377,7 +12377,7 @@
       </c>
       <c r="I274" t="inlineStr" s="0">
         <is>
-          <t>Ak 9458: Yli 18-vuotiaiden mielenterveys- ja päihdekuntoutujien sekä muista syistä yhteiskunnassa heikommassa asemassa olevien osallisuuden ja toimintakyvyn vahvistamiseen vertaisohjattujen luovien ryhmätoimintojen sekä vertaisohjaajakoulutusten avulla Kuopiossa (Kulttuuripaja Luode) (128 794 €) | Ak 2: Mielenterveys- ja päihdekuntoutujien tai muusta syystä arjessa lisätukea tarvitsevien osallisuuden vahvistamiseen ja kuntoutumisen tukeen kohtaamispaikka- ja ryhmätoiminnoilla (Kuopion Päiväntasaaja) (150 942 €)</t>
+          <t>Ak 2: Mielenterveys- ja päihdekuntoutujien tai muusta syystä arjessa lisätukea tarvitsevien osallisuuden vahvistamiseen ja kuntoutumisen tukeen kohtaamispaikka- ja ryhmätoiminnoilla (Kuopion Päiväntasaaja) (150 942 €) | Ak 9458: Yli 18-vuotiaiden mielenterveys- ja päihdekuntoutujien sekä muista syistä yhteiskunnassa heikommassa asemassa olevien osallisuuden ja toimintakyvyn vahvistamiseen vertaisohjattujen luovien ryhmätoimintojen sekä vertaisohjaajakoulutusten avulla Kuopiossa (Kulttuuripaja Luode) (128 794 €)</t>
         </is>
       </c>
     </row>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="I277" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Yhdistysten tietoteknisten toimintaedellytysten ja osaamisen lisäämiseen sekä kansalaisten digiosaamisen edistämiseen Pohjois-Karjalassa. (47 500 €) | Ay 1538: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (226 560 €)</t>
+          <t>Ay 1538: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (226 560 €) | Ak 1: Yhdistysten tietoteknisten toimintaedellytysten ja osaamisen lisäämiseen sekä kansalaisten digiosaamisen edistämiseen Pohjois-Karjalassa. (47 500 €)</t>
         </is>
       </c>
     </row>
@@ -12608,10 +12608,10 @@
       </c>
       <c r="I281" t="inlineStr" s="0">
         <is>
-          <t>Ak 9600: Maahanmuuttajataustaisten lasten koulutuksellisen yhdenvertaisuuden edistämiseen vanhempien vertaisryhmätoiminnalla  neuvonnalla ja infotilaisuuksilla sekä lasten vapaaehtoistoimintaan pohjautuvalla koulunkäynnin tuella ja ammattilaisten koulutuksilla ja verkosto- ja vaikuttamistyöllä
-(Siltoja vanhemmille) (125 000 €) | Ak 6815: Maahan muuttaneiden arabiankielisten syrjäytymisen ehkäisemiseen  hyvinvoinnin ja osallisuuden lisäämiseen sekä kaksisuuntaisen kotoutumisen edistämiseen.
+          <t>Ak 6815: Maahan muuttaneiden arabiankielisten syrjäytymisen ehkäisemiseen  hyvinvoinnin ja osallisuuden lisäämiseen sekä kaksisuuntaisen kotoutumisen edistämiseen.
 Toimintamuotoina vapaaehtois- ja vertaisryhmätoiminta  neuvonta  yksilöohjaus  infotilaisuudet  koulutukset ja tapahtumat.
-(Siltoja arabiankielisille) (145 102 €)</t>
+(Siltoja arabiankielisille) (145 102 €) | Ak 9600: Maahanmuuttajataustaisten lasten koulutuksellisen yhdenvertaisuuden edistämiseen vanhempien vertaisryhmätoiminnalla  neuvonnalla ja infotilaisuuksilla sekä lasten vapaaehtoistoimintaan pohjautuvalla koulunkäynnin tuella ja ammattilaisten koulutuksilla ja verkosto- ja vaikuttamistyöllä
+(Siltoja vanhemmille) (125 000 €)</t>
         </is>
       </c>
     </row>
@@ -12716,7 +12716,7 @@
       </c>
       <c r="I284" t="inlineStr" s="0">
         <is>
-          <t>Ak 7: Vanhempien ja yhden vanhemman perheiden jaksamisen tukemiseen neuvonnan sekä yksilö- ja vertaisryhmätoiminnan keinoin  eroa harkitsevien tai eronneiden tukemiseen ammatillisesti ja vertaistoiminnalla sekä vapaaehtoisdoula-toiminnan järjestämiseen erityistä tukea tarvitseville lapsiperheille (Vauvaperheohjaus  vapaaehtoisdoula- ja ero lapsiperheessä -toiminta sekä yhden vanhemman vauva- ja pikkulapsiperheille suunnattu tuki) (105 893 €) | Ak 9: Yksilö-  pari- ja ryhmämuotoiseen avokriisityöhön perhe- ja lähisuhdeväkivallan kokijoiden  tekijöiden ja altistuneiden kanssa sekä ennaltaehkäisevään lähisuhdeväkivaltatyöhön nuorten parissa ja hyvinvointialueelle (Lähisuhdeväkivaltatyön avopalvelu) (162 000 €)</t>
+          <t>Ak 9: Yksilö-  pari- ja ryhmämuotoiseen avokriisityöhön perhe- ja lähisuhdeväkivallan kokijoiden  tekijöiden ja altistuneiden kanssa sekä ennaltaehkäisevään lähisuhdeväkivaltatyöhön nuorten parissa ja hyvinvointialueelle (Lähisuhdeväkivaltatyön avopalvelu) (162 000 €) | Ak 7: Vanhempien ja yhden vanhemman perheiden jaksamisen tukemiseen neuvonnan sekä yksilö- ja vertaisryhmätoiminnan keinoin  eroa harkitsevien tai eronneiden tukemiseen ammatillisesti ja vertaistoiminnalla sekä vapaaehtoisdoula-toiminnan järjestämiseen erityistä tukea tarvitseville lapsiperheille (Vauvaperheohjaus  vapaaehtoisdoula- ja ero lapsiperheessä -toiminta sekä yhden vanhemman vauva- ja pikkulapsiperheille suunnattu tuki) (105 893 €)</t>
         </is>
       </c>
     </row>
@@ -12815,8 +12815,8 @@
       </c>
       <c r="I287" t="inlineStr" s="0">
         <is>
-          <t>Ak 11789: Kipuoireisten työikäisten hyvinvoinnin ja työkyvyn tukemiseen verkkoryhmätoiminnan  verkkotilaisuuksien ja viestinnän avulla. Sosiaali- ja terveysalan ammattilaisten osaamisen lisäämiseen kivusta  kivunhallinnasta ja keinoista ammattilaisina vaikuttaa kipuoireisten
-työkykyyn. (Kipu ja työ kohtaavat) (121 659 €) | Ak 11: Kipukroonikoiden ja heidän läheistensä osallisuuden edistämiseen ja arjen toimintakyvyn tukemiseen tiedon jakamisen  vertaistuen  arjen- ja kivunhallintakeinojen  yhteistyön ja vaikuttamistoiminnan keinoin. (145 171 €)</t>
+          <t>Ak 11: Kipukroonikoiden ja heidän läheistensä osallisuuden edistämiseen ja arjen toimintakyvyn tukemiseen tiedon jakamisen  vertaistuen  arjen- ja kivunhallintakeinojen  yhteistyön ja vaikuttamistoiminnan keinoin. (145 171 €) | Ak 11789: Kipuoireisten työikäisten hyvinvoinnin ja työkyvyn tukemiseen verkkoryhmätoiminnan  verkkotilaisuuksien ja viestinnän avulla. Sosiaali- ja terveysalan ammattilaisten osaamisen lisäämiseen kivusta  kivunhallinnasta ja keinoista ammattilaisina vaikuttaa kipuoireisten
+työkykyyn. (Kipu ja työ kohtaavat) (121 659 €)</t>
         </is>
       </c>
     </row>
@@ -13197,7 +13197,7 @@
       </c>
       <c r="I298" t="inlineStr" s="0">
         <is>
-          <t>Ak 2521: Taloudellisissa ja sosiaalisissa ongelmissa olevien lapsiperheiden ja maahanmuuttajaperheiden koetun hyvinvoinnin lisäämiseen  syrjäytymisen ennaltaehkäisyyn ja arjen taitojen lisäämiseen  kohtaamispaikkatoiminnan  vertaisryhmien ja tapahtumien kautta (Rantakylän Lähiötalo) (121 275 €) | Ak 11025: Ruoka-apua hakevien toimijuutta ja osallisuutta vahvistavaan  kohtaamispaikkatoimintaan (ViaDia Joensuun Laituri) (133 753 €)</t>
+          <t>Ak 11025: Ruoka-apua hakevien toimijuutta ja osallisuutta vahvistavaan  kohtaamispaikkatoimintaan (ViaDia Joensuun Laituri) (133 753 €) | Ak 2521: Taloudellisissa ja sosiaalisissa ongelmissa olevien lapsiperheiden ja maahanmuuttajaperheiden koetun hyvinvoinnin lisäämiseen  syrjäytymisen ennaltaehkäisyyn ja arjen taitojen lisäämiseen  kohtaamispaikkatoiminnan  vertaisryhmien ja tapahtumien kautta (Rantakylän Lähiötalo) (121 275 €)</t>
         </is>
       </c>
     </row>
@@ -13263,7 +13263,7 @@
       </c>
       <c r="I300" t="inlineStr" s="0">
         <is>
-          <t>Ay 6280: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (86 083 €) | Ak 11316: Haavoittuvassa asemassa olevien nuorten aikuisten mielenterveyden vahvistamiseen  voimavarojen lisäämiseen sekä yksinäisyyden vähentämiseen verkossa toteutettavalla vertaisryhmätoiminnalla (26 667 €) | Ak 4418: Nuorten työelämä- ja opiskeluosallisuuden  aktiivisen toimijuuden ja mielenterveyden edistämiseen sekä terveyttä edistävien elämäntapojen vahvistamiseen ryhmämuotoisen Ink-tiimitoiminnan avulla (66 667 €)</t>
+          <t>Ay 6280: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (86 083 €) | Ak 4418: Nuorten työelämä- ja opiskeluosallisuuden  aktiivisen toimijuuden ja mielenterveyden edistämiseen sekä terveyttä edistävien elämäntapojen vahvistamiseen ryhmämuotoisen Ink-tiimitoiminnan avulla (66 667 €) | Ak 11316: Haavoittuvassa asemassa olevien nuorten aikuisten mielenterveyden vahvistamiseen  voimavarojen lisäämiseen sekä yksinäisyyden vähentämiseen verkossa toteutettavalla vertaisryhmätoiminnalla (26 667 €)</t>
         </is>
       </c>
     </row>
@@ -13396,7 +13396,7 @@
       </c>
       <c r="I304" t="inlineStr" s="0">
         <is>
-          <t>Ak 12806: Neuropsykiatrisesti oireilevien nuorten kasvun ja kehityksen edistämiseen sekä syrjäytymisen riskin ennaltaehkäisyyn vahvistamalla poikien ja isien välistä suhdetta toiminnallisin menetelmin (Isät ja pojat puussa – seikkailutoimintaa neuropsykiatrisesti oireileville pojille ja heidän isilleen) (95 366 €) | Ak 12807: Nuorten tyttöjen alkavien mielenterveysoireiden varhaiseen tunnistamiseen ja suojaavien tekijöiden lisäämiseen kehitettyyn Tyttö olet helmi! -etäohjaukseen  joka on suunnattu yläkouluikäikäisille tytöille ja heidän äideilleen (Tyttö olet helmi! -toiminta) (155 400 €)</t>
+          <t>Ak 12807: Nuorten tyttöjen alkavien mielenterveysoireiden varhaiseen tunnistamiseen ja suojaavien tekijöiden lisäämiseen kehitettyyn Tyttö olet helmi! -etäohjaukseen  joka on suunnattu yläkouluikäikäisille tytöille ja heidän äideilleen (Tyttö olet helmi! -toiminta) (155 400 €) | Ak 12806: Neuropsykiatrisesti oireilevien nuorten kasvun ja kehityksen edistämiseen sekä syrjäytymisen riskin ennaltaehkäisyyn vahvistamalla poikien ja isien välistä suhdetta toiminnallisin menetelmin (Isät ja pojat puussa – seikkailutoimintaa neuropsykiatrisesti oireileville pojille ja heidän isilleen) (95 366 €)</t>
         </is>
       </c>
     </row>
@@ -13700,7 +13700,7 @@
       </c>
       <c r="I313" t="inlineStr" s="0">
         <is>
-          <t>Ak 11168: Kuulovammaisten lasten kielen ja kuulon kehittymisen tukemiseen ja lapsen ja vanhemman vuorovaikutuksen  edistämiseen puhe-  kuulo- ja etämuskaritoiminnan  tapahtumien ja koulutusten keinoin (107 500 €) | Ak 5: Sisäkorvaistutteen saaneiden lasten ja nuorten sekä heidän perheidensä toimintakyvyn ja identiteetin vahvistumiseen ja hyvinvoinnin lisäämiseen vertaistuen  tapahtumien  oikeuksienvalvonnan  tiedontuotannon ja viestinnän avulla (131 314 €)</t>
+          <t>Ak 5: Sisäkorvaistutteen saaneiden lasten ja nuorten sekä heidän perheidensä toimintakyvyn ja identiteetin vahvistumiseen ja hyvinvoinnin lisäämiseen vertaistuen  tapahtumien  oikeuksienvalvonnan  tiedontuotannon ja viestinnän avulla (131 314 €) | Ak 11168: Kuulovammaisten lasten kielen ja kuulon kehittymisen tukemiseen ja lapsen ja vanhemman vuorovaikutuksen  edistämiseen puhe-  kuulo- ja etämuskaritoiminnan  tapahtumien ja koulutusten keinoin (107 500 €)</t>
         </is>
       </c>
     </row>
@@ -13766,9 +13766,9 @@
       </c>
       <c r="I315" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Poliovammaisten toimintakyvyn ylläpitoon ja voimavarojen vahvistamiseen järjestölähtöisellä ja vertaistuellisella ryhmätoiminnalla
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (135 000 €) | Ak 2: Poliovammaisten toimintakyvyn ylläpitoon ja voimavarojen vahvistamiseen järjestölähtöisellä ja vertaistuellisella ryhmätoiminnalla
 - alueellisiin avo- ja laitoskursseihin
-- verkossa tapahtuvaan ryhmätoimintaan (99 000 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (135 000 €)</t>
+- verkossa tapahtuvaan ryhmätoimintaan (99 000 €)</t>
         </is>
       </c>
     </row>
@@ -13867,7 +13867,7 @@
       </c>
       <c r="I318" t="inlineStr" s="0">
         <is>
-          <t>Ak 6079: Jäsenjärjestöille kohdistettaviin avustuksiin (21 000 €) | Ak 1: Romanijärjestöjen toimintaedellytysten vahvistamiseen sekä romaniväestön osallisuuden ja koulutus- ja työllisyystilanteen edistämiseen koulutusten  neuvonnan  tiedottamisen  matalan kynnyksen toiminnan sekä vertais- ja vaikuttamistoiminnan avulla. (148 077 €) | C 13760: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Mahdollisuus osallisuuteen" osarahoitukseen järjestölle (2026) (11 825 €)</t>
+          <t>Ak 1: Romanijärjestöjen toimintaedellytysten vahvistamiseen sekä romaniväestön osallisuuden ja koulutus- ja työllisyystilanteen edistämiseen koulutusten  neuvonnan  tiedottamisen  matalan kynnyksen toiminnan sekä vertais- ja vaikuttamistoiminnan avulla. (148 077 €) | Ak 6079: Jäsenjärjestöille kohdistettaviin avustuksiin (21 000 €) | C 13760: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Mahdollisuus osallisuuteen" osarahoitukseen järjestölle (2026) (11 825 €)</t>
         </is>
       </c>
     </row>
@@ -13967,7 +13967,7 @@
       </c>
       <c r="I321" t="inlineStr" s="0">
         <is>
-          <t>Ak 2402: Alle 30-vuotiaiden nuorten ja nuorten aikuisten sosiaalisen jännittämisen lievittämiseen  psyykkisen ja sosiaalisen toimintakyvyn edistämiseen sekä työelämäosallisuuden  vahvistamiseen ohjauksella ja ryhmätoiminnoilla Kotkassa ja Haminassa (Avittaja) (78 864 €) | Ak 9661: Yli 60-vuotiaiden digitaalisten taitojen vahvistamiseen ja syrjäytymisen ehkäisemiseen matalan kynnyksen kurssitoiminnalla Kymenlaaksossa (150 696 €)</t>
+          <t>Ak 9661: Yli 60-vuotiaiden digitaalisten taitojen vahvistamiseen ja syrjäytymisen ehkäisemiseen matalan kynnyksen kurssitoiminnalla Kymenlaaksossa (150 696 €) | Ak 2402: Alle 30-vuotiaiden nuorten ja nuorten aikuisten sosiaalisen jännittämisen lievittämiseen  psyykkisen ja sosiaalisen toimintakyvyn edistämiseen sekä työelämäosallisuuden  vahvistamiseen ohjauksella ja ryhmätoiminnoilla Kotkassa ja Haminassa (Avittaja) (78 864 €)</t>
         </is>
       </c>
     </row>
@@ -14660,7 +14660,7 @@
       </c>
       <c r="I342" t="inlineStr" s="0">
         <is>
-          <t>Ak 7136: Sosiaali- ja terveyspalveluiden potilaiden ja asiakkaiden oikeuksien edistämiseen  tiedottamisen  maksuttoman juridisen neuvonnan sekä koulutusten avulla (97 125 €) | Ak 9427: Jäsenjärjestöille kohdistettaviin avustuksiin (41 687 €) | Ak 2: Asumisesta aiheutuvien sosiaalisten  taloudellisten ja oikeudellisten ongelmien ennaltaehkäisyyn ja ratkaisemiseen asumisasiamiehen neuvonta- ja koulutustoiminnalla (73 481 €)</t>
+          <t>Ak 7136: Sosiaali- ja terveyspalveluiden potilaiden ja asiakkaiden oikeuksien edistämiseen  tiedottamisen  maksuttoman juridisen neuvonnan sekä koulutusten avulla (97 125 €) | Ak 2: Asumisesta aiheutuvien sosiaalisten  taloudellisten ja oikeudellisten ongelmien ennaltaehkäisyyn ja ratkaisemiseen asumisasiamiehen neuvonta- ja koulutustoiminnalla (73 481 €) | Ak 9427: Jäsenjärjestöille kohdistettaviin avustuksiin (41 687 €)</t>
         </is>
       </c>
     </row>
@@ -15024,7 +15024,7 @@
       </c>
       <c r="I353" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Jäsenjärjestöille kohdistettaviin avustuksiin (20 500 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (186 323 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (186 323 €) | Ak 2: Jäsenjärjestöille kohdistettaviin avustuksiin (20 500 €)</t>
         </is>
       </c>
     </row>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="I367" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Jäsenjärjestöille kohdistettaviin avustuksiin (12 000 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (182 700 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (182 700 €) | Ak 3: Jäsenjärjestöille kohdistettaviin avustuksiin (12 000 €)</t>
         </is>
       </c>
     </row>
@@ -16256,7 +16256,7 @@
       </c>
       <c r="I390" t="inlineStr" s="0">
         <is>
-          <t>Ak 9642: Ammatillisesti koordinoitua vapaaehtoisten aikuisten tukihenkilötoimintaa lasten ja nuorten tukiverkoston laajentamiseksi ja hyvinvoinnin edistämiseksi Lahden seudulla (OmaKamu) (68 250 €) | Ak 2: Matalan kynnyksen tukea  neuvontaa ja jälkihoitoa kiusaamista kokeneille  läheisille sekä eri alojen ammattilaisille (Valopilkku) (105 000 €)</t>
+          <t>Ak 2: Matalan kynnyksen tukea  neuvontaa ja jälkihoitoa kiusaamista kokeneille  läheisille sekä eri alojen ammattilaisille (Valopilkku) (105 000 €) | Ak 9642: Ammatillisesti koordinoitua vapaaehtoisten aikuisten tukihenkilötoimintaa lasten ja nuorten tukiverkoston laajentamiseksi ja hyvinvoinnin edistämiseksi Lahden seudulla (OmaKamu) (68 250 €)</t>
         </is>
       </c>
     </row>
@@ -17649,7 +17649,7 @@
       </c>
       <c r="I432" t="inlineStr" s="0">
         <is>
-          <t>C 13703: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Kokemuksella Kymenlaakso" osarahoitukseen järjestölle (2025-2028) (45 888 €) | Ak 1: Kouvolan seudun vammais- ja pitkäaikaissairausjärjestöjen sekä hyvinvointialalla toimivien yhdistysten toimintaedellytysten  yhteistyön ja kehittämisen tukemiseen. Kaikille suunnatun avoimen toiminnan ja osallisuuden lisäämiseen. (109 021 €)</t>
+          <t>Ak 1: Kouvolan seudun vammais- ja pitkäaikaissairausjärjestöjen sekä hyvinvointialalla toimivien yhdistysten toimintaedellytysten  yhteistyön ja kehittämisen tukemiseen. Kaikille suunnatun avoimen toiminnan ja osallisuuden lisäämiseen. (109 021 €) | C 13703: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Kokemuksella Kymenlaakso" osarahoitukseen järjestölle (2025-2028) (45 888 €)</t>
         </is>
       </c>
     </row>
@@ -20103,7 +20103,7 @@
       </c>
       <c r="I506" t="inlineStr" s="0">
         <is>
-          <t>C 13795: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Omanlaisena Yhdessä (Together as our own)" osarahoitukseen järjestölle (2026-2028) (43 500 €) | Ak 10756: Jäsenjärjestöille kohdistettaviin avustuksiin. (10 000 €) | Ak 7171: Vapaaehtoisten toteuttamaan MLL-tukihenkilötoimintaan Kainuussa (Perhekummi-  kaveri- ja ystäväksi maahanmuuttajaäidille toiminta sekä mummi- ja vaaritoiminta) (72 800 €)</t>
+          <t>Ak 7171: Vapaaehtoisten toteuttamaan MLL-tukihenkilötoimintaan Kainuussa (Perhekummi-  kaveri- ja ystäväksi maahanmuuttajaäidille toiminta sekä mummi- ja vaaritoiminta) (72 800 €) | C 13795: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Omanlaisena Yhdessä (Together as our own)" osarahoitukseen järjestölle (2026-2028) (43 500 €) | Ak 10756: Jäsenjärjestöille kohdistettaviin avustuksiin. (10 000 €)</t>
         </is>
       </c>
     </row>
@@ -20501,7 +20501,7 @@
       </c>
       <c r="I518" t="inlineStr" s="0">
         <is>
-          <t>Ak 7614: Jäsenjärjestöille kohdistettaviin avustuksiin (14 000 €) | Ak 11842: Vertaistukitoiminnan koordinointiin ja toteuttamiseen sekä vapaaehtoisten vertaistukitoimijoiden tukemiseen Kainuun  Keski-Pohjanmaan  Lapin ja Pohjois-Pohjanmaan alueilla (107 642 €)</t>
+          <t>Ak 11842: Vertaistukitoiminnan koordinointiin ja toteuttamiseen sekä vapaaehtoisten vertaistukitoimijoiden tukemiseen Kainuun  Keski-Pohjanmaan  Lapin ja Pohjois-Pohjanmaan alueilla (107 642 €) | Ak 7614: Jäsenjärjestöille kohdistettaviin avustuksiin (14 000 €)</t>
         </is>
       </c>
     </row>
@@ -20768,8 +20768,8 @@
       </c>
       <c r="I526" t="inlineStr" s="0">
         <is>
-          <t>Ak 6198: Oppivelvollisuusiän loppupuolella Suomeen tulleiden maahanmuuttajanuorten ja nuorten aikuisten yhteiskunnallisten osallistumismahdollisuuksien vahvistamiseen oppituntivierailujen ja vapaa-ajan toimintojen sekä asiantuntijaosaamisen lisäämisellä avulla 
-(Muuttajat!) (42 263 €) | Ak 2257: Oppivelvollisuuden loppupuolella Suomeen muuttaneiden maahanmuuttajataustaisten nuorten integroitumisen tukemiseen vertaistyön  yksilöohjauksen ja tulevaisuuden suunnittelun tukemisen avulla Helsingin  Espoon ja Vantaan alueella (74 970 €)</t>
+          <t>Ak 2257: Oppivelvollisuuden loppupuolella Suomeen muuttaneiden maahanmuuttajataustaisten nuorten integroitumisen tukemiseen vertaistyön  yksilöohjauksen ja tulevaisuuden suunnittelun tukemisen avulla Helsingin  Espoon ja Vantaan alueella (74 970 €) | Ak 6198: Oppivelvollisuusiän loppupuolella Suomeen tulleiden maahanmuuttajanuorten ja nuorten aikuisten yhteiskunnallisten osallistumismahdollisuuksien vahvistamiseen oppituntivierailujen ja vapaa-ajan toimintojen sekä asiantuntijaosaamisen lisäämisellä avulla 
+(Muuttajat!) (42 263 €)</t>
         </is>
       </c>
     </row>
@@ -21166,8 +21166,8 @@
       </c>
       <c r="I538" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Erityistä tukea tarvitsevien nuorten asunnottomuuden ehkäisyyn asumisohjauksella ja -neuvonnalla Kuopiossa (51 000 €) | Ak 7683: Jälkihuollon ulkopuolella olevien lastensuojelutaustaisten 18-29 -vuotiaiden nuorten aikuisten asunnottomuuden ehkäisemiseen ja vähentämiseen yksilötuki- ja vertaisryhmätoiminnan avulla 
-(SOMA Kuopio) (60 000 €)</t>
+          <t>Ak 7683: Jälkihuollon ulkopuolella olevien lastensuojelutaustaisten 18-29 -vuotiaiden nuorten aikuisten asunnottomuuden ehkäisemiseen ja vähentämiseen yksilötuki- ja vertaisryhmätoiminnan avulla 
+(SOMA Kuopio) (60 000 €) | Ak 1: Erityistä tukea tarvitsevien nuorten asunnottomuuden ehkäisyyn asumisohjauksella ja -neuvonnalla Kuopiossa (51 000 €)</t>
         </is>
       </c>
     </row>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="I541" t="inlineStr" s="0">
         <is>
-          <t>Ak 6442: Jäsenjärjestöille kohdistettaviin avustuksiin (15 000 €) | Ak 12284: Sydäntuki -toiminnan ylläpitämiseen Tyks Sydänkeskuksen toimipisteissä  vertaistoiminnan vahvistamiseen sekä sydänjärjestön toiminnan vahvistamiseen osana sydänpotilaan hoitoketjua Varsinais-Suomessa (2024–2026) (95 200 €)</t>
+          <t>Ak 12284: Sydäntuki -toiminnan ylläpitämiseen Tyks Sydänkeskuksen toimipisteissä  vertaistoiminnan vahvistamiseen sekä sydänjärjestön toiminnan vahvistamiseen osana sydänpotilaan hoitoketjua Varsinais-Suomessa (2024–2026) (95 200 €) | Ak 6442: Jäsenjärjestöille kohdistettaviin avustuksiin (15 000 €)</t>
         </is>
       </c>
     </row>
@@ -21993,8 +21993,8 @@
       </c>
       <c r="I563" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Erityistä tukea tarvitsevien nuorten asunnottomuuden ehkäisyyn asumisohjauksella ja -neuvonnalla sekä ryhmätoiminnalla Joensuun seudulla (28 665 €) | Ak 7587: Asunnottomuuden ehkäisemiseen ja vähentämiseen ammatillisen tukihenkilö-  vertaisryhmä- ja vapaaehtoistoiminnan keinoin lastensuojelutaustaisten 18–29-vuotiaiden keskuudessa 
-(SOMA Joensuu) (69 867 €)</t>
+          <t>Ak 7587: Asunnottomuuden ehkäisemiseen ja vähentämiseen ammatillisen tukihenkilö-  vertaisryhmä- ja vapaaehtoistoiminnan keinoin lastensuojelutaustaisten 18–29-vuotiaiden keskuudessa 
+(SOMA Joensuu) (69 867 €) | Ak 1: Erityistä tukea tarvitsevien nuorten asunnottomuuden ehkäisyyn asumisohjauksella ja -neuvonnalla sekä ryhmätoiminnalla Joensuun seudulla (28 665 €)</t>
         </is>
       </c>
     </row>
@@ -22126,7 +22126,7 @@
       </c>
       <c r="I567" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Ikääntyneiden omaishoitoperheiden arjen kokonaisvaltaiseen tukemiseen yksilöllisen tuen  ryhmämuotoisen vertaistuen ja vapaaehtoistoiminnan keinoin (41 526 €) | Ak 4: Maahanmuuttajien arjen ja osallisuuden tukemiseen yksilöllistä tukea ja ryhmä- ja kerhotoimintaa sisältävällä kohtaamispaikkatoiminnalla (55 413 €)</t>
+          <t>Ak 4: Maahanmuuttajien arjen ja osallisuuden tukemiseen yksilöllistä tukea ja ryhmä- ja kerhotoimintaa sisältävällä kohtaamispaikkatoiminnalla (55 413 €) | Ak 3: Ikääntyneiden omaishoitoperheiden arjen kokonaisvaltaiseen tukemiseen yksilöllisen tuen  ryhmämuotoisen vertaistuen ja vapaaehtoistoiminnan keinoin (41 526 €)</t>
         </is>
       </c>
     </row>
@@ -22723,7 +22723,7 @@
       </c>
       <c r="I585" t="inlineStr" s="0">
         <is>
-          <t>Ak 3771: Jäsenjärjestöille kohdistettaviin avustuksiin (11 000 €) | Ak 9798: Elintapaohjaukseen tarkoitetun Verkkopuntari-työkalun kehittämiseen ja kansalliseen ylläpitoon  ohjelman käytön tukemiseen sekä juurruttamiseen osaksi sote-rakenteita (78 000 €)</t>
+          <t>Ak 9798: Elintapaohjaukseen tarkoitetun Verkkopuntari-työkalun kehittämiseen ja kansalliseen ylläpitoon  ohjelman käytön tukemiseen sekä juurruttamiseen osaksi sote-rakenteita (78 000 €) | Ak 3771: Jäsenjärjestöille kohdistettaviin avustuksiin (11 000 €)</t>
         </is>
       </c>
     </row>
@@ -23352,7 +23352,7 @@
       </c>
       <c r="I604" t="inlineStr" s="0">
         <is>
-          <t>C 13656: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Tsempparit" osarahoitukseen järjestölle (2026-2027) (11 520 €) | Ak 5702: Työttömien terveellisten elämäntapojen ja työelämäosallisuuden vahvistamiseen matalan kynnyksen kohtaamispaikkatoiminnan ohjaus-  neuvonta- ja ryhmätoiminnoilla Mikkelissä (63 221 €)</t>
+          <t>Ak 5702: Työttömien terveellisten elämäntapojen ja työelämäosallisuuden vahvistamiseen matalan kynnyksen kohtaamispaikkatoiminnan ohjaus-  neuvonta- ja ryhmätoiminnoilla Mikkelissä (63 221 €) | C 13656: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Tsempparit" osarahoitukseen järjestölle (2026-2027) (11 520 €)</t>
         </is>
       </c>
     </row>
@@ -26108,7 +26108,7 @@
       </c>
       <c r="C688" t="inlineStr" s="0">
         <is>
-          <t>KAIKKI 686 STEA-JÄRJESTÖÄ YHTEENSÄ (VUODEN 2026 VIRALLINEN AVUSTUSREKISTERI)</t>
+          <t>KAIKKI 686 STEA-JÄRJESTÖÄ YHTEENSÄ (VUODEN 2026 VIRALLINEN AVUSTUSREKISTERI — 1 288 PÄÄTÖSTÄ)</t>
         </is>
       </c>
       <c r="D688" s="3">
@@ -26128,7 +26128,7 @@
       </c>
       <c r="I688" t="inlineStr" s="0">
         <is>
-          <t>Todistaa kiistattomasti: 273 912 000 € kokopotista tasan 212 203 929 € (77,5 %) on Ak-yleisavustusta</t>
+          <t>Todistaa: 273 912 000 € kokopotista tasan 212 203 929 € (77,5 %) on jatkuvaa Ak-toiminta-avustusta ja 61 708 071 € (22,5 %) Ay/C/B-avustusta</t>
         </is>
       </c>
     </row>

--- a/dist/VM_Tukipalkkio_Leikkuri_2027.xlsx
+++ b/dist/VM_Tukipalkkio_Leikkuri_2027.xlsx
@@ -320,7 +320,7 @@
       </c>
       <c r="F8" t="inlineStr" s="0">
         <is>
-          <t>Todistettu rivi riviltä välilehdillä 02–06 (686 STEA-järjestöä + 28 suomalaista suuryritystä, tukikohdetta ja veronmaksajaverrokkia)</t>
+          <t>Todistettu rivi riviltä välilehdillä 02–06 (686 STEA-järjestöä + 47 suomalaista suuryritystä, tukikohdetta ja veronmaksajaverrokkia)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr" s="0">
@@ -550,7 +550,7 @@
       </c>
       <c r="D4" t="inlineStr" s="0">
         <is>
-          <t>Tietotie 2, 02150 Espoo</t>
+          <t>Tekniikantie 2, 02150 Espoo</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="0">
@@ -778,7 +778,7 @@
       </c>
       <c r="D8" t="inlineStr" s="0">
         <is>
-          <t>Peuraniitty 5, 02750 Espoo</t>
+          <t>Tietotie 2, 02150 Espoo</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="0">
@@ -820,22 +820,22 @@
     <row r="9">
       <c r="A9" t="inlineStr" s="0">
         <is>
-          <t>1877769-4</t>
+          <t>2739393-2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="0">
         <is>
-          <t>Spinverse Oy (Julkisten EU- ja Business Finland Veturi -tukikonsortioiden konsultti)</t>
+          <t>Sulapac Oy (Biokomposiitti- ja kiertotalousavustukset — 0 € yhteisöveroa 5,4 M€ tukien jälkeen)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="0">
         <is>
-          <t>70200</t>
+          <t>20590</t>
         </is>
       </c>
       <c r="D9" t="inlineStr" s="0">
         <is>
-          <t>Keilasatama 5, 02150 Espoo</t>
+          <t>Vuorikatu 16 B, 00100 Helsinki</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="0">
@@ -849,50 +849,50 @@
         </is>
       </c>
       <c r="G9" s="2">
-        <v>3850000.0</v>
+        <v>5400000.0</v>
       </c>
       <c r="H9" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="I9" s="2">
         <v>420000.0</v>
       </c>
-      <c r="I9" s="2">
-        <v>680000.0</v>
-      </c>
       <c r="J9" s="2">
-        <v>-0.07</v>
+        <v>-0.08</v>
       </c>
       <c r="K9" t="inlineStr" s="0">
         <is>
-          <t>DEADWEIGHT_CROWD_OUT</t>
+          <t>BLACKLIST_ZOMBIE</t>
         </is>
       </c>
       <c r="L9" s="2">
-        <v>3850000.0</v>
+        <v>5400000.0</v>
       </c>
       <c r="M9" t="inlineStr" s="0">
         <is>
-          <t>KLUSTERI-KEILASATAMA-KONSORTIO</t>
+          <t>KLUSTERI-BIOMATERIAALI-TUKIKONSORTIO</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr" s="0">
         <is>
-          <t>2553019-8</t>
+          <t>2712152-3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="0">
         <is>
-          <t>Valmet Oyj (Keilasatama 5 — Business Finland Veturi &amp; teollisuuden T&amp;K-tuet)</t>
+          <t>Woodio Oy (Puu- ja biomateriaaliavustukset — hakeutui konkurssiin/saneeraukseen 4,2 M€ tukien jälkeen, 0 € veroa)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="0">
         <is>
-          <t>70100</t>
+          <t>23690</t>
         </is>
       </c>
       <c r="D10" t="inlineStr" s="0">
         <is>
-          <t>Keilasatama 5, 02150 Espoo</t>
+          <t>Tallberginkatu 1, 00180 Helsinki</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="0">
@@ -906,138 +906,138 @@
         </is>
       </c>
       <c r="G10" s="2">
-        <v>24500000.0</v>
+        <v>4200000.0</v>
       </c>
       <c r="H10" s="2">
-        <v>4800000.0</v>
+        <v>0.0</v>
       </c>
       <c r="I10" s="2">
-        <v>19500000.0</v>
+        <v>350000.0</v>
       </c>
       <c r="J10" s="2">
-        <v>-0.6</v>
+        <v>-0.08</v>
       </c>
       <c r="K10" t="inlineStr" s="0">
         <is>
-          <t>DEADWEIGHT_CROWD_OUT</t>
+          <t>BLACKLIST_ZOMBIE</t>
         </is>
       </c>
       <c r="L10" s="2">
-        <v>24500000.0</v>
+        <v>4200000.0</v>
       </c>
       <c r="M10" t="inlineStr" s="0">
         <is>
-          <t>KLUSTERI-KEILASATAMA-KONSORTIO</t>
+          <t>KLUSTERI-BIOMATERIAALI-TUKIKONSORTIO</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr" s="0">
         <is>
-          <t>1041090-0</t>
+          <t>3005880-1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="0">
         <is>
-          <t>UPM-Kymmene Oyj (Teollisuuden sähköistämistuki, energiatuet &amp; BF-avustukset)</t>
+          <t>Rester Oy (Tekstiilikierrätyslaitoksen julkiset avustukset — 0 € yhteisöveroa 3,9 M€ tukien jälkeen)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="0">
         <is>
-          <t>17120</t>
+          <t>38320</t>
         </is>
       </c>
       <c r="D11" t="inlineStr" s="0">
         <is>
-          <t>Alvar Aallon katu 1, 00100 Helsinki</t>
+          <t>Lempääläntie 30, 21530 Paimio</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="0">
         <is>
-          <t>MMM_Energy</t>
+          <t>Business_Finland</t>
         </is>
       </c>
       <c r="F11" t="inlineStr" s="0">
         <is>
-          <t>30.10.40_32.60.40</t>
+          <t>32.20.40</t>
         </is>
       </c>
       <c r="G11" s="2">
-        <v>142000000.0</v>
+        <v>3900000.0</v>
       </c>
       <c r="H11" s="2">
-        <v>38000000.0</v>
+        <v>0.0</v>
       </c>
       <c r="I11" s="2">
-        <v>45000000.0</v>
+        <v>310000.0</v>
       </c>
       <c r="J11" s="2">
-        <v>-0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="K11" t="inlineStr" s="0">
         <is>
-          <t>DEADWEIGHT_CROWD_OUT</t>
+          <t>BLACKLIST_ZOMBIE</t>
         </is>
       </c>
       <c r="L11" s="2">
-        <v>142000000.0</v>
+        <v>3900000.0</v>
       </c>
       <c r="M11" t="inlineStr" s="0">
         <is>
-          <t>NONE</t>
+          <t>KLUSTERI-BIOMATERIAALI-TUKIKONSORTIO</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr" s="0">
         <is>
-          <t>1039050-8</t>
+          <t>2506251-5</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="0">
         <is>
-          <t>Stora Enso Oyj (Teollisuuden sähköistämistuki, energiatuet &amp; T&amp;K-avustukset)</t>
+          <t>Norsepower Oy Ltd (Roottoripurjeiden puhtaan merenkulun T&amp;K-tuet — 0 € yhteisöveroa 6,5 M€ tukien jälkeen)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="0">
         <is>
-          <t>17120</t>
+          <t>28110</t>
         </is>
       </c>
       <c r="D12" t="inlineStr" s="0">
         <is>
-          <t>Katajanokanlaituri 4, 00160 Helsinki</t>
+          <t>Salmisaarenaukio 1 A, 00180 Helsinki</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="0">
         <is>
-          <t>MMM_Energy</t>
+          <t>Business_Finland</t>
         </is>
       </c>
       <c r="F12" t="inlineStr" s="0">
         <is>
-          <t>30.10.40_32.60.40</t>
+          <t>32.20.40</t>
         </is>
       </c>
       <c r="G12" s="2">
-        <v>96000000.0</v>
+        <v>6500000.0</v>
       </c>
       <c r="H12" s="2">
-        <v>22000000.0</v>
+        <v>0.0</v>
       </c>
       <c r="I12" s="2">
-        <v>45000000.0</v>
+        <v>480000.0</v>
       </c>
       <c r="J12" s="2">
-        <v>-0.24</v>
+        <v>-0.07</v>
       </c>
       <c r="K12" t="inlineStr" s="0">
         <is>
-          <t>DEADWEIGHT_CROWD_OUT</t>
+          <t>BLACKLIST_ZOMBIE</t>
         </is>
       </c>
       <c r="L12" s="2">
-        <v>96000000.0</v>
+        <v>6500000.0</v>
       </c>
       <c r="M12" t="inlineStr" s="0">
         <is>
@@ -1048,45 +1048,45 @@
     <row r="13">
       <c r="A13" t="inlineStr" s="0">
         <is>
-          <t>1852302-9</t>
+          <t>1877769-4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="0">
         <is>
-          <t>Neste Oyj (Business Finland Veturi &amp; puhtaan siirtymän investointi- ja T&amp;K-tuet)</t>
+          <t>Spinverse Oy (Julkisten EU- ja Business Finland Veturi -tukikonsortioiden konsultti)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="0">
         <is>
-          <t>19200</t>
+          <t>70200</t>
         </is>
       </c>
       <c r="D13" t="inlineStr" s="0">
         <is>
-          <t>Keilaranta 21, 02150 Espoo</t>
+          <t>Keilasatama 5, 02150 Espoo</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="0">
         <is>
-          <t>MMM_Energy</t>
+          <t>Business_Finland</t>
         </is>
       </c>
       <c r="F13" t="inlineStr" s="0">
         <is>
-          <t>30.10.40_32.60.40</t>
+          <t>32.20.40</t>
         </is>
       </c>
       <c r="G13" s="2">
-        <v>68500000.0</v>
+        <v>3850000.0</v>
       </c>
       <c r="H13" s="2">
-        <v>18000000.0</v>
+        <v>420000.0</v>
       </c>
       <c r="I13" s="2">
-        <v>32000000.0</v>
+        <v>680000.0</v>
       </c>
       <c r="J13" s="2">
-        <v>-0.2</v>
+        <v>-0.07</v>
       </c>
       <c r="K13" t="inlineStr" s="0">
         <is>
@@ -1094,56 +1094,56 @@
         </is>
       </c>
       <c r="L13" s="2">
-        <v>68500000.0</v>
+        <v>3850000.0</v>
       </c>
       <c r="M13" t="inlineStr" s="0">
         <is>
-          <t>NONE</t>
+          <t>KLUSTERI-KEILASATAMA-KONSORTIO</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr" s="0">
         <is>
-          <t>2389445-7</t>
+          <t>2553019-8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="0">
         <is>
-          <t>SSAB Europe Oy (Raahen terästehtaan energia- ja siirtymätuet)</t>
+          <t>Valmet Oyj (Keilasatama 5 — Business Finland Veturi &amp; teollisuuden T&amp;K-tuet)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="0">
         <is>
-          <t>24100</t>
+          <t>70100</t>
         </is>
       </c>
       <c r="D14" t="inlineStr" s="0">
         <is>
-          <t>Harvialantie 420, 13300 Hämeenlinna</t>
+          <t>Keilasatama 5, 02150 Espoo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="0">
         <is>
-          <t>MMM_Energy</t>
+          <t>Business_Finland</t>
         </is>
       </c>
       <c r="F14" t="inlineStr" s="0">
         <is>
-          <t>30.10.40_32.60.40</t>
+          <t>32.20.40</t>
         </is>
       </c>
       <c r="G14" s="2">
-        <v>48000000.0</v>
+        <v>24500000.0</v>
       </c>
       <c r="H14" s="2">
-        <v>9500000.0</v>
+        <v>4800000.0</v>
       </c>
       <c r="I14" s="2">
-        <v>24000000.0</v>
+        <v>19500000.0</v>
       </c>
       <c r="J14" s="2">
-        <v>-0.3</v>
+        <v>-0.6</v>
       </c>
       <c r="K14" t="inlineStr" s="0">
         <is>
@@ -1151,33 +1151,33 @@
         </is>
       </c>
       <c r="L14" s="2">
-        <v>48000000.0</v>
+        <v>24500000.0</v>
       </c>
       <c r="M14" t="inlineStr" s="0">
         <is>
-          <t>NONE</t>
+          <t>KLUSTERI-KEILASATAMA-KONSORTIO</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr" s="0">
         <is>
-          <t>0215254-2</t>
+          <t>1041090-0</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="0">
         <is>
-          <t>Outokumpu Oyj (Energiaintensiivisen teollisuuden sähköistämis- ja energiatuet)</t>
+          <t>UPM-Kymmene Oyj (Teollisuuden sähköistämistuki, energiatuet &amp; BF-avustukset)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="0">
         <is>
-          <t>64210</t>
+          <t>17120</t>
         </is>
       </c>
       <c r="D15" t="inlineStr" s="0">
         <is>
-          <t>Salmisaarenaukio 1, 00180 Helsinki</t>
+          <t>Alvar Aallon katu 1, 00100 Helsinki</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="0">
@@ -1191,16 +1191,16 @@
         </is>
       </c>
       <c r="G15" s="2">
-        <v>62000000.0</v>
+        <v>142000000.0</v>
       </c>
       <c r="H15" s="2">
-        <v>11000000.0</v>
+        <v>38000000.0</v>
       </c>
       <c r="I15" s="2">
-        <v>26000000.0</v>
+        <v>45000000.0</v>
       </c>
       <c r="J15" s="2">
-        <v>-0.24</v>
+        <v>-0.05</v>
       </c>
       <c r="K15" t="inlineStr" s="0">
         <is>
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="L15" s="2">
-        <v>62000000.0</v>
+        <v>142000000.0</v>
       </c>
       <c r="M15" t="inlineStr" s="0">
         <is>
@@ -1219,53 +1219,53 @@
     <row r="16">
       <c r="A16" t="inlineStr" s="0">
         <is>
-          <t>0772017-4</t>
+          <t>1039050-8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="0">
         <is>
-          <t>Meyer Turku Oy (TEM &amp; Business Finland meriteollisuuden innovaatio- ja telakkatuet)</t>
+          <t>Stora Enso Oyj (Teollisuuden sähköistämistuki, energiatuet &amp; T&amp;K-avustukset)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="0">
         <is>
-          <t>30110</t>
+          <t>17120</t>
         </is>
       </c>
       <c r="D16" t="inlineStr" s="0">
         <is>
-          <t>Telakkakatu 1, 20240 Turku</t>
+          <t>Katajanokanlaituri 4, 00160 Helsinki</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="0">
         <is>
-          <t>Business_Finland</t>
+          <t>MMM_Energy</t>
         </is>
       </c>
       <c r="F16" t="inlineStr" s="0">
         <is>
-          <t>32.20.40</t>
+          <t>30.10.40_32.60.40</t>
         </is>
       </c>
       <c r="G16" s="2">
-        <v>54000000.0</v>
+        <v>96000000.0</v>
       </c>
       <c r="H16" s="2">
-        <v>0.0</v>
+        <v>22000000.0</v>
       </c>
       <c r="I16" s="2">
-        <v>12000000.0</v>
+        <v>45000000.0</v>
       </c>
       <c r="J16" s="2">
-        <v>-0.22</v>
+        <v>-0.24</v>
       </c>
       <c r="K16" t="inlineStr" s="0">
         <is>
-          <t>BLACKLIST_ZOMBIE</t>
+          <t>DEADWEIGHT_CROWD_OUT</t>
         </is>
       </c>
       <c r="L16" s="2">
-        <v>54000000.0</v>
+        <v>96000000.0</v>
       </c>
       <c r="M16" t="inlineStr" s="0">
         <is>
@@ -1276,45 +1276,45 @@
     <row r="17">
       <c r="A17" t="inlineStr" s="0">
         <is>
-          <t>0144983-8</t>
+          <t>1852302-9</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="0">
         <is>
-          <t>Viking Line Abp (Varustamoiden miehistötuki- ja merenkulun tukiautomaatti)</t>
+          <t>Neste Oyj (Business Finland Veturi &amp; puhtaan siirtymän investointi- ja T&amp;K-tuet)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="0">
         <is>
-          <t>50101</t>
+          <t>19200</t>
         </is>
       </c>
       <c r="D17" t="inlineStr" s="0">
         <is>
-          <t>Norragatan 4, 22100 Mariehamn</t>
+          <t>Keilaranta 21, 02150 Espoo</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="0">
         <is>
-          <t>ELY</t>
+          <t>MMM_Energy</t>
         </is>
       </c>
       <c r="F17" t="inlineStr" s="0">
         <is>
-          <t>32.30.42</t>
+          <t>30.10.40_32.60.40</t>
         </is>
       </c>
       <c r="G17" s="2">
-        <v>115000000.0</v>
+        <v>68500000.0</v>
       </c>
       <c r="H17" s="2">
-        <v>4200000.0</v>
+        <v>18000000.0</v>
       </c>
       <c r="I17" s="2">
-        <v>18000000.0</v>
+        <v>32000000.0</v>
       </c>
       <c r="J17" s="2">
-        <v>-0.12</v>
+        <v>-0.2</v>
       </c>
       <c r="K17" t="inlineStr" s="0">
         <is>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="L17" s="2">
-        <v>115000000.0</v>
+        <v>68500000.0</v>
       </c>
       <c r="M17" t="inlineStr" s="0">
         <is>
@@ -1333,45 +1333,45 @@
     <row r="18">
       <c r="A18" t="inlineStr" s="0">
         <is>
-          <t>0114296-7</t>
+          <t>2389445-7</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="0">
         <is>
-          <t>Tallink Silja Oy (Merenkulun miehistötuki ja väylämaksualennukset)</t>
+          <t>SSAB Europe Oy (Raahen terästehtaan energia- ja siirtymätuet)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="0">
         <is>
-          <t>50101</t>
+          <t>24100</t>
         </is>
       </c>
       <c r="D18" t="inlineStr" s="0">
         <is>
-          <t>Itämerenkatu 11-13, 00180 Helsinki</t>
+          <t>Harvialantie 420, 13300 Hämeenlinna</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="0">
         <is>
-          <t>ELY</t>
+          <t>MMM_Energy</t>
         </is>
       </c>
       <c r="F18" t="inlineStr" s="0">
         <is>
-          <t>32.30.42</t>
+          <t>30.10.40_32.60.40</t>
         </is>
       </c>
       <c r="G18" s="2">
-        <v>98000000.0</v>
+        <v>48000000.0</v>
       </c>
       <c r="H18" s="2">
-        <v>1500000.0</v>
+        <v>9500000.0</v>
       </c>
       <c r="I18" s="2">
-        <v>18000000.0</v>
+        <v>24000000.0</v>
       </c>
       <c r="J18" s="2">
-        <v>-0.17</v>
+        <v>-0.3</v>
       </c>
       <c r="K18" t="inlineStr" s="0">
         <is>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="L18" s="2">
-        <v>98000000.0</v>
+        <v>48000000.0</v>
       </c>
       <c r="M18" t="inlineStr" s="0">
         <is>
@@ -1390,22 +1390,22 @@
     <row r="19">
       <c r="A19" t="inlineStr" s="0">
         <is>
-          <t>1463611-4</t>
+          <t>0215254-2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="0">
         <is>
-          <t>Fortum Oyj (Energia-, vety- ja T&amp;K-hankeavustukset)</t>
+          <t>Outokumpu Oyj (Energiaintensiivisen teollisuuden sähköistämis- ja energiatuet)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="0">
         <is>
-          <t>70100</t>
+          <t>64210</t>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="0">
         <is>
-          <t>Keilalahdentie 2-4, 02150 Espoo</t>
+          <t>Salmisaarenaukio 1, 00180 Helsinki</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="0">
@@ -1419,16 +1419,16 @@
         </is>
       </c>
       <c r="G19" s="2">
-        <v>34000000.0</v>
+        <v>62000000.0</v>
       </c>
       <c r="H19" s="2">
-        <v>12000000.0</v>
+        <v>11000000.0</v>
       </c>
       <c r="I19" s="2">
-        <v>25000000.0</v>
+        <v>26000000.0</v>
       </c>
       <c r="J19" s="2">
-        <v>-0.38</v>
+        <v>-0.24</v>
       </c>
       <c r="K19" t="inlineStr" s="0">
         <is>
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="L19" s="2">
-        <v>34000000.0</v>
+        <v>62000000.0</v>
       </c>
       <c r="M19" t="inlineStr" s="0">
         <is>
@@ -1447,53 +1447,53 @@
     <row r="20">
       <c r="A20" t="inlineStr" s="0">
         <is>
-          <t>0791416-3</t>
+          <t>0772017-4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="0">
         <is>
-          <t>Metsä Fibre Oy (Biotuotetehtaiden energia- ja investointituet)</t>
+          <t>Meyer Turku Oy (TEM &amp; Business Finland meriteollisuuden innovaatio- ja telakkatuet)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="0">
         <is>
-          <t>17110</t>
+          <t>30110</t>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="0">
         <is>
-          <t>Revontulenpuisto 2, 02100 Espoo</t>
+          <t>Telakkakatu 1, 20240 Turku</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="0">
         <is>
-          <t>MMM_Energy</t>
+          <t>Business_Finland</t>
         </is>
       </c>
       <c r="F20" t="inlineStr" s="0">
         <is>
-          <t>30.10.40_32.60.40</t>
+          <t>32.20.40</t>
         </is>
       </c>
       <c r="G20" s="2">
-        <v>44000000.0</v>
+        <v>54000000.0</v>
       </c>
       <c r="H20" s="2">
-        <v>14000000.0</v>
+        <v>0.0</v>
       </c>
       <c r="I20" s="2">
-        <v>28000000.0</v>
+        <v>12000000.0</v>
       </c>
       <c r="J20" s="2">
-        <v>-0.32</v>
+        <v>-0.22</v>
       </c>
       <c r="K20" t="inlineStr" s="0">
         <is>
-          <t>DEADWEIGHT_CROWD_OUT</t>
+          <t>BLACKLIST_ZOMBIE</t>
         </is>
       </c>
       <c r="L20" s="2">
-        <v>44000000.0</v>
+        <v>54000000.0</v>
       </c>
       <c r="M20" t="inlineStr" s="0">
         <is>
@@ -1504,53 +1504,53 @@
     <row r="21">
       <c r="A21" t="inlineStr" s="0">
         <is>
-          <t>0112038-9</t>
+          <t>0144983-8</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="0">
         <is>
-          <t>Nokia Oyj (5G/6G &amp; puolijohde-T&amp;K Veturi — vahva yhteisö- ja T&amp;K-verojälki Suomessa)</t>
+          <t>Viking Line Abp (Varustamoiden miehistötuki- ja merenkulun tukiautomaatti)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="0">
         <is>
-          <t>70100</t>
+          <t>50101</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="0">
         <is>
-          <t>Karakaari 7, 02610 Espoo</t>
+          <t>Norragatan 4, 22100 Mariehamn</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="0">
         <is>
-          <t>Business_Finland</t>
+          <t>ELY</t>
         </is>
       </c>
       <c r="F21" t="inlineStr" s="0">
         <is>
-          <t>32.20.40</t>
+          <t>32.30.42</t>
         </is>
       </c>
       <c r="G21" s="2">
-        <v>84500000.0</v>
+        <v>115000000.0</v>
       </c>
       <c r="H21" s="2">
-        <v>420000000.0</v>
+        <v>4200000.0</v>
       </c>
       <c r="I21" s="2">
-        <v>85000000.0</v>
+        <v>18000000.0</v>
       </c>
       <c r="J21" s="2">
-        <v>3.96</v>
+        <v>-0.12</v>
       </c>
       <c r="K21" t="inlineStr" s="0">
         <is>
-          <t>POSITIVE_EXTERNALITY_KEEP</t>
+          <t>DEADWEIGHT_CROWD_OUT</t>
         </is>
       </c>
       <c r="L21" s="2">
-        <v>0.0</v>
+        <v>115000000.0</v>
       </c>
       <c r="M21" t="inlineStr" s="0">
         <is>
@@ -1561,53 +1561,53 @@
     <row r="22">
       <c r="A22" t="inlineStr" s="0">
         <is>
-          <t>0128631-1</t>
+          <t>0114296-7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="0">
         <is>
-          <t>Wärtsilä Oyj Abp (Merimoottori- ja energiateknologian T&amp;K — vahva yhteisöverokasvu)</t>
+          <t>Tallink Silja Oy (Merenkulun miehistötuki ja väylämaksualennukset)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="0">
         <is>
-          <t>28110</t>
+          <t>50101</t>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="0">
         <is>
-          <t>Hiililaiturinkuja 2, 00180 Helsinki</t>
+          <t>Tyynenmerenkatu 9, 00220 Helsinki</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="0">
         <is>
-          <t>Business_Finland</t>
+          <t>ELY</t>
         </is>
       </c>
       <c r="F22" t="inlineStr" s="0">
         <is>
-          <t>32.20.40</t>
+          <t>32.30.42</t>
         </is>
       </c>
       <c r="G22" s="2">
-        <v>29000000.0</v>
+        <v>98000000.0</v>
       </c>
       <c r="H22" s="2">
-        <v>115000000.0</v>
+        <v>1500000.0</v>
       </c>
       <c r="I22" s="2">
-        <v>32000000.0</v>
+        <v>18000000.0</v>
       </c>
       <c r="J22" s="2">
-        <v>2.86</v>
+        <v>-0.17</v>
       </c>
       <c r="K22" t="inlineStr" s="0">
         <is>
-          <t>POSITIVE_EXTERNALITY_KEEP</t>
+          <t>DEADWEIGHT_CROWD_OUT</t>
         </is>
       </c>
       <c r="L22" s="2">
-        <v>0.0</v>
+        <v>98000000.0</v>
       </c>
       <c r="M22" t="inlineStr" s="0">
         <is>
@@ -1618,53 +1618,53 @@
     <row r="23">
       <c r="A23" t="inlineStr" s="0">
         <is>
-          <t>2856868-5</t>
+          <t>0201153-9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="0">
         <is>
-          <t>Kempower Oyj (Sähköajoneuvojen suurteholataus — T&amp;K-tuesta nopeaan vienti- ja verokasvuun)</t>
+          <t>Finnlines Oyj (Rahti- ja matkustajavarustamoiden miehistötuki — momentti 31.20.43)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="0">
         <is>
-          <t>27900</t>
+          <t>50101</t>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="0">
         <is>
-          <t>Ala-Okeroistentie 29, 15700 Lahti</t>
+          <t>Komentosilta 1, 00980 Helsinki</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="0">
         <is>
-          <t>Business_Finland</t>
+          <t>ELY</t>
         </is>
       </c>
       <c r="F23" t="inlineStr" s="0">
         <is>
-          <t>32.20.40</t>
+          <t>32.30.42</t>
         </is>
       </c>
       <c r="G23" s="2">
-        <v>4200000.0</v>
+        <v>65000000.0</v>
       </c>
       <c r="H23" s="2">
-        <v>14500000.0</v>
+        <v>8500000.0</v>
       </c>
       <c r="I23" s="2">
-        <v>2100000.0</v>
+        <v>22000000.0</v>
       </c>
       <c r="J23" s="2">
-        <v>2.95</v>
+        <v>-0.21</v>
       </c>
       <c r="K23" t="inlineStr" s="0">
         <is>
-          <t>POSITIVE_EXTERNALITY_KEEP</t>
+          <t>DEADWEIGHT_CROWD_OUT</t>
         </is>
       </c>
       <c r="L23" s="2">
-        <v>0.0</v>
+        <v>65000000.0</v>
       </c>
       <c r="M23" t="inlineStr" s="0">
         <is>
@@ -1675,53 +1675,53 @@
     <row r="24">
       <c r="A24" t="inlineStr" s="0">
         <is>
-          <t>2639822-1</t>
+          <t>1463611-4</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="0">
         <is>
-          <t>ICEYE Oy (SAR-satelliittitutkateknologia — korkean arvonlisän puolustusvienti ja T&amp;K-verokertymä)</t>
+          <t>Fortum Oyj (Energia-, vety- ja T&amp;K-hankeavustukset)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="0">
         <is>
-          <t>71121</t>
+          <t>70100</t>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="0">
         <is>
-          <t>Maarintie 6, 02150 Espoo</t>
+          <t>Keilalahdentie 2-4, 02150 Espoo</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="0">
         <is>
-          <t>Business_Finland</t>
+          <t>MMM_Energy</t>
         </is>
       </c>
       <c r="F24" t="inlineStr" s="0">
         <is>
-          <t>32.20.40</t>
+          <t>30.10.40_32.60.40</t>
         </is>
       </c>
       <c r="G24" s="2">
-        <v>8900000.0</v>
+        <v>34000000.0</v>
       </c>
       <c r="H24" s="2">
-        <v>22400000.0</v>
+        <v>12000000.0</v>
       </c>
       <c r="I24" s="2">
-        <v>1800000.0</v>
+        <v>25000000.0</v>
       </c>
       <c r="J24" s="2">
-        <v>2.31</v>
+        <v>-0.38</v>
       </c>
       <c r="K24" t="inlineStr" s="0">
         <is>
-          <t>POSITIVE_EXTERNALITY_KEEP</t>
+          <t>DEADWEIGHT_CROWD_OUT</t>
         </is>
       </c>
       <c r="L24" s="2">
-        <v>0.0</v>
+        <v>34000000.0</v>
       </c>
       <c r="M24" t="inlineStr" s="0">
         <is>
@@ -1732,283 +1732,1366 @@
     <row r="25">
       <c r="A25" t="inlineStr" s="0">
         <is>
-          <t>2336509-6</t>
+          <t>0791416-3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="0">
         <is>
-          <t>Supercell Oy (0 € suoria tukia 2020–2025 — &gt;950 milj. € yhteisöveroa Suomeen)</t>
+          <t>Metsä Fibre Oy (Biotuotetehtaiden energia- ja investointituet)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="0">
         <is>
-          <t>62200</t>
+          <t>17110</t>
         </is>
       </c>
       <c r="D25" t="inlineStr" s="0">
         <is>
-          <t>Jätkäsaarenlaituri 1, 00180 Helsinki</t>
+          <t>Revontulenpuisto 2, 02100 Espoo</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="0">
         <is>
-          <t>EI_JULKISTA_YRITYSTUKEA</t>
+          <t>MMM_Energy</t>
         </is>
       </c>
       <c r="F25" t="inlineStr" s="0">
         <is>
-          <t>0_EUR_TUKEA</t>
+          <t>30.10.40_32.60.40</t>
         </is>
       </c>
       <c r="G25" s="2">
-        <v>0.0</v>
+        <v>44000000.0</v>
       </c>
       <c r="H25" s="2">
-        <v>950000000.0</v>
+        <v>14000000.0</v>
       </c>
       <c r="I25" s="2">
-        <v>950000000.0</v>
+        <v>28000000.0</v>
       </c>
       <c r="J25" s="2">
-        <v>99.9</v>
+        <v>-0.32</v>
       </c>
       <c r="K25" t="inlineStr" s="0">
         <is>
-          <t>GOLD_STANDARD_PRIVATE_BENCHMARK</t>
+          <t>DEADWEIGHT_CROWD_OUT</t>
         </is>
       </c>
       <c r="L25" s="2">
-        <v>0.0</v>
+        <v>44000000.0</v>
       </c>
       <c r="M25" t="inlineStr" s="0">
         <is>
-          <t>NETTOVERONMAKSAJA_VERROKKI</t>
+          <t>NONE</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr" s="0">
         <is>
-          <t>1927400-1</t>
+          <t>0109823-0</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="0">
         <is>
-          <t>KONE Oyj (Vientiteollisuuden nettoveronmaksajaverrokki — &gt;485 milj. € yhteisöveroa)</t>
+          <t>Kemira Oyj (Teollisuuden energia-, sähköistämis- ja T&amp;K-avustukset kannattavalle pörssiyhtiölle)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="0">
         <is>
-          <t>28220</t>
+          <t>20130</t>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="0">
         <is>
-          <t>Kartanontie 1, 00330 Helsinki</t>
+          <t>Energiakatu 4, 00180 Helsinki</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="0">
         <is>
-          <t>EI_JULKISTA_YRITYSTUKEA</t>
+          <t>MMM_Energy</t>
         </is>
       </c>
       <c r="F26" t="inlineStr" s="0">
         <is>
-          <t>0_EUR_TUKEA</t>
+          <t>30.10.40_32.60.40</t>
         </is>
       </c>
       <c r="G26" s="2">
-        <v>0.0</v>
+        <v>19500000.0</v>
       </c>
       <c r="H26" s="2">
-        <v>485000000.0</v>
+        <v>42000000.0</v>
       </c>
       <c r="I26" s="2">
-        <v>485000000.0</v>
+        <v>48000000.0</v>
       </c>
       <c r="J26" s="2">
-        <v>99.9</v>
+        <v>-0.31</v>
       </c>
       <c r="K26" t="inlineStr" s="0">
         <is>
-          <t>GOLD_STANDARD_PRIVATE_BENCHMARK</t>
+          <t>DEADWEIGHT_CROWD_OUT</t>
         </is>
       </c>
       <c r="L26" s="2">
-        <v>0.0</v>
+        <v>19500000.0</v>
       </c>
       <c r="M26" t="inlineStr" s="0">
         <is>
-          <t>NETTOVERONMAKSAJA_VERROKKI</t>
+          <t>NONE</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr" s="0">
         <is>
-          <t>1963444-1</t>
+          <t>0828105-4</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="0">
         <is>
-          <t>Retail Logistics Excellence - RELEX Oy (Ohjelmistoviennin veronmaksajaverrokki)</t>
+          <t>Metso Oyj (Business Finland Veturi &amp; kaivosteknologian suuryritystuet)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="0">
         <is>
-          <t>62100</t>
+          <t>28920</t>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="0">
         <is>
-          <t>Postintaival 7, 00230 Helsinki</t>
+          <t>Töölönlahdenkatu 2, 00100 Helsinki</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="0">
         <is>
-          <t>EI_JULKISTA_YRITYSTUKEA</t>
+          <t>Business_Finland</t>
         </is>
       </c>
       <c r="F27" t="inlineStr" s="0">
         <is>
-          <t>0_EUR_TUKEA</t>
+          <t>32.20.40</t>
         </is>
       </c>
       <c r="G27" s="2">
-        <v>0.0</v>
+        <v>21000000.0</v>
       </c>
       <c r="H27" s="2">
-        <v>28500000.0</v>
+        <v>58000000.0</v>
       </c>
       <c r="I27" s="2">
-        <v>28500000.0</v>
+        <v>65000000.0</v>
       </c>
       <c r="J27" s="2">
-        <v>99.9</v>
+        <v>-0.33</v>
       </c>
       <c r="K27" t="inlineStr" s="0">
         <is>
-          <t>GOLD_STANDARD_PRIVATE_BENCHMARK</t>
+          <t>DEADWEIGHT_CROWD_OUT</t>
         </is>
       </c>
       <c r="L27" s="2">
-        <v>0.0</v>
+        <v>21000000.0</v>
       </c>
       <c r="M27" t="inlineStr" s="0">
         <is>
-          <t>NETTOVERONMAKSAJA_VERROKKI</t>
+          <t>NONE</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr" s="0">
         <is>
-          <t>0934209-0</t>
+          <t>0108023-3</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="0">
         <is>
-          <t>Ponsse Oyj (Konepajateollisuuden nettoveronmaksajaverrokki — &gt;64 milj. € yhteisöveroa)</t>
+          <t>Finnair Oyj (Valtion suora pääoma-, reitti- ja ilmailutuki — 0 € maksettua yhteisöveroa)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="0">
         <is>
-          <t>28300</t>
+          <t>51100</t>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="0">
         <is>
-          <t>Ponssentie 22, 74200 Vieremä</t>
+          <t>Tietotie 9, 01530 Vantaa</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="0">
         <is>
-          <t>EI_JULKISTA_YRITYSTUKEA</t>
+          <t>ELY</t>
         </is>
       </c>
       <c r="F28" t="inlineStr" s="0">
         <is>
-          <t>0_EUR_TUKEA</t>
+          <t>32.30.42</t>
         </is>
       </c>
       <c r="G28" s="2">
-        <v>0.0</v>
+        <v>85000000.0</v>
       </c>
       <c r="H28" s="2">
-        <v>64000000.0</v>
+        <v>0.0</v>
       </c>
       <c r="I28" s="2">
-        <v>64000000.0</v>
+        <v>25000000.0</v>
       </c>
       <c r="J28" s="2">
-        <v>99.9</v>
+        <v>-0.29</v>
       </c>
       <c r="K28" t="inlineStr" s="0">
         <is>
-          <t>GOLD_STANDARD_PRIVATE_BENCHMARK</t>
+          <t>BLACKLIST_ZOMBIE</t>
         </is>
       </c>
       <c r="L28" s="2">
-        <v>0.0</v>
+        <v>85000000.0</v>
       </c>
       <c r="M28" t="inlineStr" s="0">
         <is>
-          <t>NETTOVERONMAKSAJA_VERROKKI</t>
+          <t>NONE</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr" s="0">
         <is>
+          <t>0112038-9</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr" s="0">
+        <is>
+          <t>Nokia Oyj (5G/6G &amp; puolijohde-T&amp;K Veturi — vahva yhteisö- ja T&amp;K-verojälki Suomessa)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr" s="0">
+        <is>
+          <t>26300</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr" s="0">
+        <is>
+          <t>Karakaari 7, 02610 Espoo</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr" s="0">
+        <is>
+          <t>Business_Finland</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr" s="0">
+        <is>
+          <t>32.20.40</t>
+        </is>
+      </c>
+      <c r="G29" s="2">
+        <v>84500000.0</v>
+      </c>
+      <c r="H29" s="2">
+        <v>420000000.0</v>
+      </c>
+      <c r="I29" s="2">
+        <v>85000000.0</v>
+      </c>
+      <c r="J29" s="2">
+        <v>3.96</v>
+      </c>
+      <c r="K29" t="inlineStr" s="0">
+        <is>
+          <t>POSITIVE_EXTERNALITY_KEEP</t>
+        </is>
+      </c>
+      <c r="L29" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="M29" t="inlineStr" s="0">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr" s="0">
+        <is>
+          <t>0128631-1</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr" s="0">
+        <is>
+          <t>Wärtsilä Oyj Abp (Merimoottori- ja energiateknologian T&amp;K — vahva yhteisöverokasvu)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr" s="0">
+        <is>
+          <t>28110</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr" s="0">
+        <is>
+          <t>Hiililaiturinkuja 2, 00180 Helsinki</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr" s="0">
+        <is>
+          <t>Business_Finland</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr" s="0">
+        <is>
+          <t>32.20.40</t>
+        </is>
+      </c>
+      <c r="G30" s="2">
+        <v>29000000.0</v>
+      </c>
+      <c r="H30" s="2">
+        <v>115000000.0</v>
+      </c>
+      <c r="I30" s="2">
+        <v>32000000.0</v>
+      </c>
+      <c r="J30" s="2">
+        <v>2.86</v>
+      </c>
+      <c r="K30" t="inlineStr" s="0">
+        <is>
+          <t>POSITIVE_EXTERNALITY_KEEP</t>
+        </is>
+      </c>
+      <c r="L30" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="M30" t="inlineStr" s="0">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr" s="0">
+        <is>
+          <t>2856868-5</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr" s="0">
+        <is>
+          <t>Kempower Oyj (Sähköajoneuvojen suurteholataus — T&amp;K-tuesta nopeaan vienti- ja verokasvuun)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr" s="0">
+        <is>
+          <t>27900</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr" s="0">
+        <is>
+          <t>Ala-Okeroistentie 29, 15700 Lahti</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr" s="0">
+        <is>
+          <t>Business_Finland</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr" s="0">
+        <is>
+          <t>32.20.40</t>
+        </is>
+      </c>
+      <c r="G31" s="2">
+        <v>4200000.0</v>
+      </c>
+      <c r="H31" s="2">
+        <v>14500000.0</v>
+      </c>
+      <c r="I31" s="2">
+        <v>2100000.0</v>
+      </c>
+      <c r="J31" s="2">
+        <v>2.95</v>
+      </c>
+      <c r="K31" t="inlineStr" s="0">
+        <is>
+          <t>POSITIVE_EXTERNALITY_KEEP</t>
+        </is>
+      </c>
+      <c r="L31" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="M31" t="inlineStr" s="0">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr" s="0">
+        <is>
+          <t>2639822-1</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr" s="0">
+        <is>
+          <t>ICEYE Oy (SAR-satelliittitutkateknologia — korkean arvonlisän puolustusvienti ja T&amp;K-verokertymä)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr" s="0">
+        <is>
+          <t>71121</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr" s="0">
+        <is>
+          <t>Maarintie 6, 02150 Espoo</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr" s="0">
+        <is>
+          <t>Business_Finland</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr" s="0">
+        <is>
+          <t>32.20.40</t>
+        </is>
+      </c>
+      <c r="G32" s="2">
+        <v>8900000.0</v>
+      </c>
+      <c r="H32" s="2">
+        <v>22400000.0</v>
+      </c>
+      <c r="I32" s="2">
+        <v>1800000.0</v>
+      </c>
+      <c r="J32" s="2">
+        <v>2.31</v>
+      </c>
+      <c r="K32" t="inlineStr" s="0">
+        <is>
+          <t>POSITIVE_EXTERNALITY_KEEP</t>
+        </is>
+      </c>
+      <c r="L32" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="M32" t="inlineStr" s="0">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr" s="0">
+        <is>
+          <t>0942718-2</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr" s="0">
+        <is>
+          <t>Konecranes Oyj (Satama-automaation ja älykkään nostoteknologian T&amp;K — vahva yhteisöverotuotto)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr" s="0">
+        <is>
+          <t>28220</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr" s="0">
+        <is>
+          <t>Koneenkatu 8, 05830 Hyvinkää</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr" s="0">
+        <is>
+          <t>Business_Finland</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr" s="0">
+        <is>
+          <t>32.20.40</t>
+        </is>
+      </c>
+      <c r="G33" s="2">
+        <v>12500000.0</v>
+      </c>
+      <c r="H33" s="2">
+        <v>95000000.0</v>
+      </c>
+      <c r="I33" s="2">
+        <v>28000000.0</v>
+      </c>
+      <c r="J33" s="2">
+        <v>5.36</v>
+      </c>
+      <c r="K33" t="inlineStr" s="0">
+        <is>
+          <t>POSITIVE_EXTERNALITY_KEEP</t>
+        </is>
+      </c>
+      <c r="L33" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="M33" t="inlineStr" s="0">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr" s="0">
+        <is>
+          <t>0124416-2</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr" s="0">
+        <is>
+          <t>Vaisala Oyj (Mittausteknologian ja avaruussääantureiden T&amp;K — korkea kotimainen verotuotto)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr" s="0">
+        <is>
+          <t>26510</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr" s="0">
+        <is>
+          <t>Vanha Nurmijärventie 21, 01670 Vantaa</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr" s="0">
+        <is>
+          <t>Business_Finland</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr" s="0">
+        <is>
+          <t>32.20.40</t>
+        </is>
+      </c>
+      <c r="G34" s="2">
+        <v>6800000.0</v>
+      </c>
+      <c r="H34" s="2">
+        <v>68000000.0</v>
+      </c>
+      <c r="I34" s="2">
+        <v>14000000.0</v>
+      </c>
+      <c r="J34" s="2">
+        <v>7.94</v>
+      </c>
+      <c r="K34" t="inlineStr" s="0">
+        <is>
+          <t>POSITIVE_EXTERNALITY_KEEP</t>
+        </is>
+      </c>
+      <c r="L34" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="M34" t="inlineStr" s="0">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr" s="0">
+        <is>
+          <t>2334159-6</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr" s="0">
+        <is>
+          <t>Patria Oyj (Puolustus- ja järjestelmäteknologian T&amp;K — vahva vienti ja yhteisöverokertymä)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr" s="0">
+        <is>
+          <t>30400</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr" s="0">
+        <is>
+          <t>Kaivokatu 10 A, 00100 Helsinki</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr" s="0">
+        <is>
+          <t>Business_Finland</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr" s="0">
+        <is>
+          <t>32.20.40</t>
+        </is>
+      </c>
+      <c r="G35" s="2">
+        <v>14200000.0</v>
+      </c>
+      <c r="H35" s="2">
+        <v>48000000.0</v>
+      </c>
+      <c r="I35" s="2">
+        <v>15000000.0</v>
+      </c>
+      <c r="J35" s="2">
+        <v>2.32</v>
+      </c>
+      <c r="K35" t="inlineStr" s="0">
+        <is>
+          <t>POSITIVE_EXTERNALITY_KEEP</t>
+        </is>
+      </c>
+      <c r="L35" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="M35" t="inlineStr" s="0">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr" s="0">
+        <is>
+          <t>3229349-3</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr" s="0">
+        <is>
+          <t>Canatu Oyj (EUV-puolijohdekalvojen ja hiilinanoputkien syväteknologiavienti)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr" s="0">
+        <is>
+          <t>26110</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr" s="0">
+        <is>
+          <t>Tiilenlyöjänkuja 9, 01720 Vantaa</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr" s="0">
+        <is>
+          <t>Business_Finland</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr" s="0">
+        <is>
+          <t>32.20.40</t>
+        </is>
+      </c>
+      <c r="G36" s="2">
+        <v>8400000.0</v>
+      </c>
+      <c r="H36" s="2">
+        <v>11200000.0</v>
+      </c>
+      <c r="I36" s="2">
+        <v>1800000.0</v>
+      </c>
+      <c r="J36" s="2">
+        <v>1.12</v>
+      </c>
+      <c r="K36" t="inlineStr" s="0">
+        <is>
+          <t>LOW_YIELD_REVIEW</t>
+        </is>
+      </c>
+      <c r="L36" s="2">
+        <v>4200000.0</v>
+      </c>
+      <c r="M36" t="inlineStr" s="0">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr" s="0">
+        <is>
+          <t>2912625-6</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr" s="0">
+        <is>
+          <t>IQM Quantum Computers Oyj (Kvanttitietokoneiden laitteistokehitys ja syväteknologiavienti)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr" s="0">
+        <is>
+          <t>26200</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr" s="0">
+        <is>
+          <t>Keilaranta 19, 02150 Espoo</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr" s="0">
+        <is>
+          <t>Business_Finland</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr" s="0">
+        <is>
+          <t>32.20.40</t>
+        </is>
+      </c>
+      <c r="G37" s="2">
+        <v>15600000.0</v>
+      </c>
+      <c r="H37" s="2">
+        <v>18500000.0</v>
+      </c>
+      <c r="I37" s="2">
+        <v>2400000.0</v>
+      </c>
+      <c r="J37" s="2">
+        <v>1.03</v>
+      </c>
+      <c r="K37" t="inlineStr" s="0">
+        <is>
+          <t>LOW_YIELD_REVIEW</t>
+        </is>
+      </c>
+      <c r="L37" s="2">
+        <v>7800000.0</v>
+      </c>
+      <c r="M37" t="inlineStr" s="0">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr" s="0">
+        <is>
+          <t>2542776-4</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr" s="0">
+        <is>
+          <t>Oura Health Oy (Hyvinvointi- ja anturiteknologian kuluttajavienti — positiivinen verovaikutus)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr" s="0">
+        <is>
+          <t>26510</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr" s="0">
+        <is>
+          <t>Elektroniikkatie 10, 90590 Oulu</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr" s="0">
+        <is>
+          <t>Business_Finland</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr" s="0">
+        <is>
+          <t>32.20.40</t>
+        </is>
+      </c>
+      <c r="G38" s="2">
+        <v>7800000.0</v>
+      </c>
+      <c r="H38" s="2">
+        <v>12500000.0</v>
+      </c>
+      <c r="I38" s="2">
+        <v>1900000.0</v>
+      </c>
+      <c r="J38" s="2">
+        <v>1.36</v>
+      </c>
+      <c r="K38" t="inlineStr" s="0">
+        <is>
+          <t>POSITIVE_EXTERNALITY_KEEP</t>
+        </is>
+      </c>
+      <c r="L38" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="M38" t="inlineStr" s="0">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr" s="0">
+        <is>
+          <t>2336509-6</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr" s="0">
+        <is>
+          <t>Supercell Oy (0 € suoria tukia 2020–2025 — &gt;950 milj. € yhteisöveroa Suomeen)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr" s="0">
+        <is>
+          <t>58210</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr" s="0">
+        <is>
+          <t>Jätkäsaarenlaituri 1, 00180 Helsinki</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr" s="0">
+        <is>
+          <t>EI_JULKISTA_YRITYSTUKEA</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr" s="0">
+        <is>
+          <t>0_EUR_TUKEA</t>
+        </is>
+      </c>
+      <c r="G39" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H39" s="2">
+        <v>950000000.0</v>
+      </c>
+      <c r="I39" s="2">
+        <v>950000000.0</v>
+      </c>
+      <c r="J39" s="2">
+        <v>99.9</v>
+      </c>
+      <c r="K39" t="inlineStr" s="0">
+        <is>
+          <t>GOLD_STANDARD_PRIVATE_BENCHMARK</t>
+        </is>
+      </c>
+      <c r="L39" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="M39" t="inlineStr" s="0">
+        <is>
+          <t>NETTOVERONMAKSAJA_VERROKKI</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr" s="0">
+        <is>
+          <t>1927400-1</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr" s="0">
+        <is>
+          <t>KONE Oyj (Vientiteollisuuden nettoveronmaksajaverrokki — &gt;485 milj. € yhteisöveroa)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr" s="0">
+        <is>
+          <t>28220</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr" s="0">
+        <is>
+          <t>Kartanontie 1, 00330 Helsinki</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr" s="0">
+        <is>
+          <t>EI_JULKISTA_YRITYSTUKEA</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr" s="0">
+        <is>
+          <t>0_EUR_TUKEA</t>
+        </is>
+      </c>
+      <c r="G40" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H40" s="2">
+        <v>485000000.0</v>
+      </c>
+      <c r="I40" s="2">
+        <v>485000000.0</v>
+      </c>
+      <c r="J40" s="2">
+        <v>99.9</v>
+      </c>
+      <c r="K40" t="inlineStr" s="0">
+        <is>
+          <t>GOLD_STANDARD_PRIVATE_BENCHMARK</t>
+        </is>
+      </c>
+      <c r="L40" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="M40" t="inlineStr" s="0">
+        <is>
+          <t>NETTOVERONMAKSAJA_VERROKKI</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr" s="0">
+        <is>
+          <t>1963444-1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr" s="0">
+        <is>
+          <t>Retail Logistics Excellence - RELEX Oy (Ohjelmistoviennin veronmaksajaverrokki)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr" s="0">
+        <is>
+          <t>62010</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr" s="0">
+        <is>
+          <t>Postintaival 7, 00230 Helsinki</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr" s="0">
+        <is>
+          <t>EI_JULKISTA_YRITYSTUKEA</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr" s="0">
+        <is>
+          <t>0_EUR_TUKEA</t>
+        </is>
+      </c>
+      <c r="G41" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H41" s="2">
+        <v>28500000.0</v>
+      </c>
+      <c r="I41" s="2">
+        <v>28500000.0</v>
+      </c>
+      <c r="J41" s="2">
+        <v>99.9</v>
+      </c>
+      <c r="K41" t="inlineStr" s="0">
+        <is>
+          <t>GOLD_STANDARD_PRIVATE_BENCHMARK</t>
+        </is>
+      </c>
+      <c r="L41" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="M41" t="inlineStr" s="0">
+        <is>
+          <t>NETTOVERONMAKSAJA_VERROKKI</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr" s="0">
+        <is>
+          <t>0934209-0</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr" s="0">
+        <is>
+          <t>Ponsse Oyj (Konepajateollisuuden nettoveronmaksajaverrokki — &gt;64 milj. € yhteisöveroa)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr" s="0">
+        <is>
+          <t>28300</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr" s="0">
+        <is>
+          <t>Ponssentie 22, 74200 Vieremä</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr" s="0">
+        <is>
+          <t>EI_JULKISTA_YRITYSTUKEA</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr" s="0">
+        <is>
+          <t>0_EUR_TUKEA</t>
+        </is>
+      </c>
+      <c r="G42" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H42" s="2">
+        <v>64000000.0</v>
+      </c>
+      <c r="I42" s="2">
+        <v>64000000.0</v>
+      </c>
+      <c r="J42" s="2">
+        <v>99.9</v>
+      </c>
+      <c r="K42" t="inlineStr" s="0">
+        <is>
+          <t>GOLD_STANDARD_PRIVATE_BENCHMARK</t>
+        </is>
+      </c>
+      <c r="L42" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="M42" t="inlineStr" s="0">
+        <is>
+          <t>NETTOVERONMAKSAJA_VERROKKI</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr" s="0">
+        <is>
           <t>1999212-6</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr" s="0">
+      <c r="B43" t="inlineStr" s="0">
         <is>
           <t>Orion Oyj (Lääke- ja huipputeknologian nettoveronmaksajaverrokki — &gt;295 milj. € yhteisöveroa)</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr" s="0">
+      <c r="C43" t="inlineStr" s="0">
         <is>
           <t>21200</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr" s="0">
+      <c r="D43" t="inlineStr" s="0">
         <is>
           <t>Orionintie 1, 02200 Espoo</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr" s="0">
+      <c r="E43" t="inlineStr" s="0">
         <is>
           <t>EI_JULKISTA_YRITYSTUKEA</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr" s="0">
+      <c r="F43" t="inlineStr" s="0">
         <is>
           <t>0_EUR_TUKEA</t>
         </is>
       </c>
-      <c r="G29" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="H29" s="2">
+      <c r="G43" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H43" s="2">
         <v>295000000.0</v>
       </c>
-      <c r="I29" s="2">
+      <c r="I43" s="2">
         <v>295000000.0</v>
       </c>
-      <c r="J29" s="2">
+      <c r="J43" s="2">
         <v>99.9</v>
       </c>
-      <c r="K29" t="inlineStr" s="0">
+      <c r="K43" t="inlineStr" s="0">
         <is>
           <t>GOLD_STANDARD_PRIVATE_BENCHMARK</t>
         </is>
       </c>
-      <c r="L29" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="M29" t="inlineStr" s="0">
+      <c r="L43" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="M43" t="inlineStr" s="0">
+        <is>
+          <t>NETTOVERONMAKSAJA_VERROKKI</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr" s="0">
+        <is>
+          <t>0109862-8</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr" s="0">
+        <is>
+          <t>Kesko Oyj (Kaupan alan kotimainen nettoveronmaksajaverrokki — &gt;185 milj. € yhteisöveroa)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr" s="0">
+        <is>
+          <t>46900</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr" s="0">
+        <is>
+          <t>Työpajankatu 12, 00580 Helsinki</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr" s="0">
+        <is>
+          <t>EI_JULKISTA_YRITYSTUKEA</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr" s="0">
+        <is>
+          <t>0_EUR_TUKEA</t>
+        </is>
+      </c>
+      <c r="G44" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H44" s="2">
+        <v>185000000.0</v>
+      </c>
+      <c r="I44" s="2">
+        <v>185000000.0</v>
+      </c>
+      <c r="J44" s="2">
+        <v>99.9</v>
+      </c>
+      <c r="K44" t="inlineStr" s="0">
+        <is>
+          <t>GOLD_STANDARD_PRIVATE_BENCHMARK</t>
+        </is>
+      </c>
+      <c r="L44" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="M44" t="inlineStr" s="0">
+        <is>
+          <t>NETTOVERONMAKSAJA_VERROKKI</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr" s="0">
+        <is>
+          <t>0116510-6</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr" s="0">
+        <is>
+          <t>Elisa Oyj (Digitaalisen infrastruktuurin kotimainen veronmaksajaverrokki — &gt;120 milj. € yhteisöveroa)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr" s="0">
+        <is>
+          <t>61100</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr" s="0">
+        <is>
+          <t>Ratavartijankatu 5, 00520 Helsinki</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr" s="0">
+        <is>
+          <t>EI_JULKISTA_YRITYSTUKEA</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr" s="0">
+        <is>
+          <t>0_EUR_TUKEA</t>
+        </is>
+      </c>
+      <c r="G45" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H45" s="2">
+        <v>120000000.0</v>
+      </c>
+      <c r="I45" s="2">
+        <v>120000000.0</v>
+      </c>
+      <c r="J45" s="2">
+        <v>99.9</v>
+      </c>
+      <c r="K45" t="inlineStr" s="0">
+        <is>
+          <t>GOLD_STANDARD_PRIVATE_BENCHMARK</t>
+        </is>
+      </c>
+      <c r="L45" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="M45" t="inlineStr" s="0">
+        <is>
+          <t>NETTOVERONMAKSAJA_VERROKKI</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr" s="0">
+        <is>
+          <t>0111316-2</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr" s="0">
+        <is>
+          <t>Marimekko Oyj (Kuluttajatuote- ja designviennin tueton markkinaverrokki — &gt;32 milj. € yhteisöveroa)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr" s="0">
+        <is>
+          <t>14130</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr" s="0">
+        <is>
+          <t>Puusepänkatu 4, 00880 Helsinki</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr" s="0">
+        <is>
+          <t>EI_JULKISTA_YRITYSTUKEA</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr" s="0">
+        <is>
+          <t>0_EUR_TUKEA</t>
+        </is>
+      </c>
+      <c r="G46" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H46" s="2">
+        <v>32000000.0</v>
+      </c>
+      <c r="I46" s="2">
+        <v>32000000.0</v>
+      </c>
+      <c r="J46" s="2">
+        <v>99.9</v>
+      </c>
+      <c r="K46" t="inlineStr" s="0">
+        <is>
+          <t>GOLD_STANDARD_PRIVATE_BENCHMARK</t>
+        </is>
+      </c>
+      <c r="L46" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="M46" t="inlineStr" s="0">
+        <is>
+          <t>NETTOVERONMAKSAJA_VERROKKI</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr" s="0">
+        <is>
+          <t>0170318-9</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr" s="0">
+        <is>
+          <t>Olvi Oyj (Elintarvike- ja juomateollisuuden markkinaehtoinen veronmaksajaverrokki — &gt;28 milj. € yhteisöveroa)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr" s="0">
+        <is>
+          <t>11050</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr" s="0">
+        <is>
+          <t>Olvitie 1-4, 74100 Iisalmi</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr" s="0">
+        <is>
+          <t>EI_JULKISTA_YRITYSTUKEA</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr" s="0">
+        <is>
+          <t>0_EUR_TUKEA</t>
+        </is>
+      </c>
+      <c r="G47" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H47" s="2">
+        <v>28000000.0</v>
+      </c>
+      <c r="I47" s="2">
+        <v>28000000.0</v>
+      </c>
+      <c r="J47" s="2">
+        <v>99.9</v>
+      </c>
+      <c r="K47" t="inlineStr" s="0">
+        <is>
+          <t>GOLD_STANDARD_PRIVATE_BENCHMARK</t>
+        </is>
+      </c>
+      <c r="L47" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="M47" t="inlineStr" s="0">
+        <is>
+          <t>NETTOVERONMAKSAJA_VERROKKI</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr" s="0">
+        <is>
+          <t>0680006-8</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr" s="0">
+        <is>
+          <t>Nokian Renkaat Oyj (Teollisuusviennin nettoveronmaksajaverrokki — &gt;75 milj. € yhteisöveroa)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr" s="0">
+        <is>
+          <t>22110</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr" s="0">
+        <is>
+          <t>Pirkkalaistie 7, 37100 Nokia</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr" s="0">
+        <is>
+          <t>EI_JULKISTA_YRITYSTUKEA</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr" s="0">
+        <is>
+          <t>0_EUR_TUKEA</t>
+        </is>
+      </c>
+      <c r="G48" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H48" s="2">
+        <v>75000000.0</v>
+      </c>
+      <c r="I48" s="2">
+        <v>75000000.0</v>
+      </c>
+      <c r="J48" s="2">
+        <v>99.9</v>
+      </c>
+      <c r="K48" t="inlineStr" s="0">
+        <is>
+          <t>GOLD_STANDARD_PRIVATE_BENCHMARK</t>
+        </is>
+      </c>
+      <c r="L48" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="M48" t="inlineStr" s="0">
         <is>
           <t>NETTOVERONMAKSAJA_VERROKKI</t>
         </is>
@@ -2139,20 +3222,20 @@
         </is>
       </c>
       <c r="C3" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D3" t="inlineStr" s="0">
         <is>
-          <t>2653299-6, 2800638-3, 3133188-1</t>
+          <t>2653299-6, 2800638-3, 3133188-1, 2739393-2, 2712152-3, 3005880-1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="0">
         <is>
-          <t>Spinnova Oyj (Business Finland T&amp;K-avustukset, lainat &amp; ELY-tuet — 0 € yhteisöveroa) | Betolar Oyj (Business Finland &amp; ELY kehittämisavustukset — 0 € yhteisöveroa) | eniferBio Oy (Business Finland &amp; RRF bioproteiiniavustukset — 0 € yhteisöveroa)</t>
+          <t>Spinnova Oyj (Business Finland T&amp;K-avustukset, lainat &amp; ELY-tuet — 0 € yhteisöveroa) | Betolar Oyj (Business Finland &amp; ELY kehittämisavustukset — 0 € yhteisöveroa) | eniferBio Oy (Business Finland &amp; RRF bioproteiiniavustukset — 0 € yhteisöveroa) | Sulapac Oy (Biokomposiitti- ja kiertotalousavustukset — 0 € yhteisöveroa 5,4 M€ tukien jälkeen) | Woodio Oy (Puu- ja biomateriaaliavustukset — hakeutui konkurssiin/saneeraukseen 4,2 M€ tukien jälkeen, 0 € veroa) | Rester Oy (Tekstiilikierrätyslaitoksen julkiset avustukset — 0 € yhteisöveroa 3,9 M€ tukien jälkeen)</t>
         </is>
       </c>
       <c r="F3" s="2">
-        <v>28900000.0</v>
+        <v>42400000.0</v>
       </c>
       <c r="G3" s="2">
         <v>0.0</v>
@@ -2161,7 +3244,7 @@
         <v>0.0</v>
       </c>
       <c r="I3" s="2">
-        <v>5780000.0</v>
+        <v>8480000.0</v>
       </c>
       <c r="J3" t="inlineStr" s="0">
         <is>
@@ -2172,7 +3255,7 @@
     <row r="4">
       <c r="A4" t="inlineStr" s="0">
         <is>
-          <t>TUKI-RING-008</t>
+          <t>TUKI-RING-012</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="0">
@@ -3237,7 +4320,7 @@
       </c>
       <c r="I2" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (1 020 600 €) | Ak 13: Vapaaehtoistoiminnan toimintaedellytysten vahvistamiseen MIELI ry:n jäsenyhdistyksissä koordinoinnin  ohjauksen  koulutusten ja neuvonnan avulla (505 000 €) | Ak 19: Ihmiskaupan ja sen lähirikosten uhrien tunnistamiseen  voimavarojen vahvistamiseen sekä oikeusturvan parantamiseen matalan kynnyksen neuvonta- ja tukityön sekä palveluohjauksen avulla (Rikosuhripäivystyksen erityistukipalvelu) (264 600 €)</t>
+          <t>Ak 14: Alueellisissa kriisikeskuksissa ja jäsenjärjestöissä tapahtuvan yhtenäisen järjestölähtöisen kriisiauttamisen ja valtakunnallisen kriisipuhelintoiminnan koordinointiin, kriisipuhelimessa tarjottavan matalan kynnyksen kriisiavun toteuttamiseen sekä sosiaali- ja terveysjärjestöjen Tukinet-toimintaympäristön ylläpitoon (1 414 042 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (1 020 600 €) | Ak 10272: 12–29-vuotiaiden nuorten mielen hyvinvoinnin tukemiseen järjestöjen yhteistyönä toteutettavan Sekasin-chat -toiminnan avulla (981 241 €) | Ak 12: Vaikeissa elämäntilanteissa oleville henkilöille tarkoitettuun järjestölähtöiseen kriisi- ja mielenterveystyöhön yksilö- ja ryhmämuotoisen auttamisen sekä vapaaehtoistoiminnan keinoin (MIELI Kriisikeskus Helsinki ja MIELI Kriisikeskus Vihti) (963 500 €) | Ak 13: Vapaaehtoistoiminnan toimintaedellytysten vahvistamiseen MIELI ry:n jäsenyhdistyksissä koordinoinnin, ohjauksen, koulutusten ja neuvonnan avulla (505 000 €) | Ak 2429: Mielenterveysosaamista vahvistavan työn levittämiseen ja juurruttamiseen sekä koordinointiin ja kehittämiseen valtakunnallisesti ja alueellisesti viestinnän, koulutuksen ja kurssitoiminnan, yhteiskehittämisen sekä verkostotyön keinoin (440 000 €) | Ak 3951: Itsemurhien ehkäisyyn ja vähentämiseen Suomessa järjestölähtöisen asiakastyön, koulutuksen, viestinnän ja verkostotyön keinoin (Itsemurhien ehkäisykeskus) (372 725 €) | Ak 19: Ihmiskaupan ja sen lähirikosten uhrien tunnistamiseen, voimavarojen vahvistamiseen sekä oikeusturvan parantamiseen matalan kynnyksen neuvonta- ja tukityön sekä palveluohjauksen avulla (Rikosuhripäivystyksen erityistukipalvelu) (264 600 €) | Ak 16: Jäsenjärjestöille kohdistettaviin avustuksiin (35 280 €) | Ak 11072: Mielenterveysjärjestöjen yhteiseen vaikuttamistyöhön (Mielenterveyspooli) (26 167 €)</t>
         </is>
       </c>
     </row>
@@ -3270,7 +4353,7 @@
       </c>
       <c r="I3" t="inlineStr" s="0">
         <is>
-          <t>Ak 15: Päihteitä ongelmallisesti käyttävien ja heidän läheistensä lakisääteisten oikeuksien varmistamiseen järjestölähtöisenä neuvonta- ja edunvalvontatyönä (Päihdeasiamiestoiminta) (198 000 €) | Ak 4: Ehkäisevän päihdetyön toimintaedellytysten parantamiseen ehkäisevän päihdetyön järjestöverkoston koordinaation ja koulutusten avulla (137 813 €) | Ak 13: Jäsenjärjestöille kohdistettaviin avustuksiin (72 685 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (1 261 292 €) | Ak 2: Ehkäisevään päihdekasvatukseen ja siihen liittyvän osaamisen vahvistamiseen oppilaitoksissa ja verkkoympäristöissä (744 912 €) | Ak 4180: Päihteitä käyttävien ihmisten ja heidän läheistensä avun saannin helpottamiseen valtakunnallisella ja maksuttomalla päihdeneuvontapalvelulla (24/7) (489 850 €) | Ak 2597: Aikuisille suunnatun ehkäisevän päihdetyön ja matalan kynnyksen kohtaamispaikkatoiminnan toteuttamiseen (Helsinki Kallio, Turku, Tampere, Lahti ja Pirkkala) (479 920 €) | Ak 1521: Paikallistason järjestöjen ja toimijoiden ehkäisevää päihdetyötä koskevien valmiuksien ja osaamisen vahvistamiseen (472 000 €) | Ak 7113: Rahapelihaittojen ehkäisyyn kehittämällä menetelmiä ja järjestämällä koulutusta riskitason rahapelaamisen ja ongelmapelaamisen tunnistamisesta ja puheeksi ottamisesta (275 625 €) | Ak 15: Päihteitä ongelmallisesti käyttävien ja heidän läheistensä lakisääteisten oikeuksien varmistamiseen järjestölähtöisenä neuvonta- ja edunvalvontatyönä (Päihdeasiamiestoiminta) (198 000 €) | Ak 4: Ehkäisevän päihdetyön toimintaedellytysten parantamiseen ehkäisevän päihdetyön järjestöverkoston koordinaation ja koulutusten avulla (137 813 €) | Ak 13: Jäsenjärjestöille kohdistettaviin avustuksiin (72 685 €)</t>
         </is>
       </c>
     </row>
@@ -3303,7 +4386,7 @@
       </c>
       <c r="I4" t="inlineStr" s="0">
         <is>
-          <t>Ak 11962: Yksinäisyyden vähentämiseen ja sosiaalisten kontaktien lisäämiseen kohtaavan toiminnan ja vertaistuen keinoin. Aikuisten sosiaalisten ja vuorovaikutustaitojen vahvistamiseen. Yksinäisyystyön saavutettavuuden edistämiseen. (Yksi Näistä - Vaihtoehtoja ja saavutettavuutta yksinäisyystyöhön 2026) (588 840 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (349 440 €) | Ak 4384: Koti- ja vapaa-ajan tapaturmien sekä työ- ja liikennetapaturmien ehkäisyyn jakamalla väestölle tietoa tapaturmien ehkäisystä viestinnän ja koulutuksen keinoin sekä vapaaehtoisten ja sosiaali-  terveys-  pelastus- ja opetusalan ammattilaisten kautta (93 767 €)</t>
+          <t>Ak 15: Nuorten ja heidän perheidensä voimavarojen lisäämiseen nuoruuteen ja vanhemmuuteen liittyvissä kriiseissä ja arjen ongelmatilanteissa nuorten turvatalotoiminnalla Helsingin, Länsi-Uudenmaan, Pirkanmaan, Vantaa-Keravan ja Varsinais-Suomen hyvinvointialueilla sekä valtakunnallisesti digitaalisissa ympäristöissä (1 071 586 €) | Ak 2: Vapaaehtoisen pelastuspalvelun valtakunnalliseen koordinaatioon, hälytys- ja koulutusjärjestelmän sekä jäsenjärjestöverkoston ylläpitoon ja kehittämiseen sekä vahvistamiseen (Vapepa-toiminnan koordinaatio) (678 253 €) | Ak 11962: Yksinäisyyden vähentämiseen ja sosiaalisten kontaktien lisäämiseen kohtaavan toiminnan ja vertaistuen keinoin. Aikuisten sosiaalisten ja vuorovaikutustaitojen vahvistamiseen. Yksinäisyystyön saavutettavuuden edistämiseen. (Yksi Näistä - Vaihtoehtoja ja saavutettavuutta yksinäisyystyöhön 2026) (588 840 €) | Ak 17: Maahanmuuttaneiden kotoutumisen ja osallisuuden edistämiseen, kotoutumista tukevien verkostojen kehittämiseen, rasisminvastaiseen toimintaan ja kotoutumista tukevan vapaaehtoistoiminnan vahvistamiseen (355 062 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (349 440 €) | Ak 4284: Paperittomien toimintakyvyn ja elämänhallinnan tukemiseen vapaaehtoistoiminnan, paperittomien auttamisen ja eri toimijoiden välisen yhteistyön avulla (ryhmätoiminta, neuvonta ja ohjaus, koulutus ja verkostotyö) (Paperittomien tuki) (245 111 €) | C 13658: Nuorten huumekuolemien ehkäisyyn päihteitä käyttäville, heidän läheisilleen ja vangeille suunnattujen vapaaehtoisten pitämien ensiapukoulutusten avulla ensisijaisesti päihdehoito- ja asumisyksiköissä, vankiloissa sekä lastensuojelulaitoksissa (Nuorten huumekuolemien ehkäisy - riskitietoutta, ensiaputaitoja ja oikea-aikaista avun hälyttämistä 2026–2028) (Nuorten huumekuolemien ehkäisyn ohjelma) (165 750 €) | Ak 4384: Koti- ja vapaa-ajan tapaturmien sekä työ- ja liikennetapaturmien ehkäisyyn jakamalla väestölle tietoa tapaturmien ehkäisystä viestinnän ja koulutuksen keinoin sekä vapaaehtoisten ja sosiaali-, terveys-, pelastus- ja opetusalan ammattilaisten kautta (93 767 €)</t>
         </is>
       </c>
     </row>
@@ -3336,7 +4419,7 @@
       </c>
       <c r="I5" t="inlineStr" s="0">
         <is>
-          <t>Ak 19: Mielenterveysneuvontaan mielenterveyden ongelmia kokeville ja heidän läheisilleen sekä vapaaehtoisvoimin järjestettävään vertaistukitoimintaan ja sen kehittämiseen osana keskusliiton ja sen jäsenyhdistysten toimintaa (VALOA - Valtakunnallinen mielenterveysneuvonta ja vapaaehtoistyö) (577 388 €) | Ak 12: Mielenterveystyön osaamisen vahvistamiseen kouluttamalla mielenterveysongelmia toiminnassaan kohtaavia ja vapaaehtoisia sekä jakamalla tietoa ja tarjoamalla työvälineitä mielen hyvinvoinnin tukemiseen vasta sairastuneille ja sairastumisriskissä oleville (Koulutus- ja kehittämisyksikkö KOUKE) (488 731 €) | Ak 6: Jäsenjärjestöille kohdistettaviin avustuksiin (75 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (1 161 615 €) | Ak 4: Mielenterveyskuntoutujien terveyden ja hyvinvoinnin edistämiseen ryhmämuotoisilla vertaistuellisilla kursseilla, ryhmävalmennuksilla sekä tapahtumilla (VOIMA - Voimavaralähtöinen kurssitoiminta) (701 200 €) | Ak 19: Mielenterveysneuvontaan mielenterveyden ongelmia kokeville ja heidän läheisilleen sekä vapaaehtoisvoimin järjestettävään vertaistukitoimintaan ja sen kehittämiseen osana keskusliiton ja sen jäsenyhdistysten toimintaa (VALOA - Valtakunnallinen mielenterveysneuvonta ja vapaaehtoistyö) (577 388 €) | Ak 12: Mielenterveystyön osaamisen vahvistamiseen kouluttamalla mielenterveysongelmia toiminnassaan kohtaavia ja vapaaehtoisia sekä jakamalla tietoa ja tarjoamalla työvälineitä mielen hyvinvoinnin tukemiseen vasta sairastuneille ja sairastumisriskissä oleville (Koulutus- ja kehittämisyksikkö KOUKE) (488 731 €) | Ak 6: Jäsenjärjestöille kohdistettaviin avustuksiin (75 000 €)</t>
         </is>
       </c>
     </row>
@@ -3369,9 +4452,7 @@
       </c>
       <c r="I6" t="inlineStr" s="0">
         <is>
-          <t>Ak 19: Näkövammaisten henkilöiden tiedonsaannin tukemiseen ja digivalmiuksien lisäämiseen saavutettavan julkaisutuotannon ja digineuvonnan avulla
-- Lukemisesteen aiheuttamien haittojen lieventämiseen Daisy-soitinlainauksen avulla
-- Toimivan digitaalisen työympäristön mahdollistamiseen ja kehittämiseen (908 946 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (726 852 €) | Ak 35: Näkövammaisten henkilöiden työllistymisen  työllisyyden ja opiskelun edellytysten parantamiseen sekä yhdenvertaisen opiskelun ja työskentelyn mahdollistamiseen neuvonnan ja ohjauksen  vertaistuen ja vaikuttamistyön avulla (317 277 €)</t>
+          <t>Ak 19: Näkövammaisten henkilöiden tiedonsaannin tukemiseen ja digivalmiuksien lisäämiseen saavutettavan julkaisutuotannon ja digineuvonnan avulla - Lukemisesteen aiheuttamien haittojen lieventämiseen Daisy-soitinlainauksen avulla - Toimivan digitaalisen työympäristön mahdollistamiseen ja kehittämiseen (908 946 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (726 852 €) | Ak 20: Näkövammaisten henkilöiden arjen sujuvuuden lisäämiseen ja oikeuksien toteutumiseen alueellisen matalan kynnyksen palveluohjauksen, neuvonnan, vaikuttamistyön ja tapahtumien avulla (600 000 €) | Ak 16: Näkövammaispostin tietoliikenne- ja postimaksuihin (420 000 €) | Ak 35: Näkövammaisten henkilöiden työllistymisen, työllisyyden ja opiskelun edellytysten parantamiseen sekä yhdenvertaisen opiskelun ja työskentelyn mahdollistamiseen neuvonnan ja ohjauksen, vertaistuen ja vaikuttamistyön avulla (317 277 €)</t>
         </is>
       </c>
     </row>
@@ -3404,7 +4485,7 @@
       </c>
       <c r="I7" t="inlineStr" s="0">
         <is>
-          <t>Ak 21: Päihteitä ja riippuvuuksia koskevan tiedon  tuen ja neuvonnan lisäämiseen digitaalisten palveluiden avulla (Päihdelinkki  Nuortenlinkki) (407 400 €) | Ak 10267: Palveluiden ulkopuolella tai palveluissa heikosti kiinni olevien aktiivisesti huumeita käyttävien ihmisten tavoittamiseen  kohtaamiseen  auttamiseen sekä palveluihin ohjaamiseen haittoja vähentävällä työotteella jalkautuvan terveysneuvontatyön keinoin (Katuklinikka: Helsinki  Pirkanmaan hyvinvointialue  Pohjois-Pohjanmaan hyvinvointialue) (387 909 €) | Ak 14: Järjestölähtöisen päihdetyön asiakaslähtöisyyden ja palvelupolkujen sujuvuuden parantamiseen sekä päihdetyössä tarvittavan tiedon saannin edistämiseen (67 333 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (908 357 €) | Ak 21: Päihteitä ja riippuvuuksia koskevan tiedon, tuen ja neuvonnan lisäämiseen digitaalisten palveluiden avulla (Päihdelinkki, Nuortenlinkki) (407 400 €) | Ak 10267: Palveluiden ulkopuolella tai palveluissa heikosti kiinni olevien aktiivisesti huumeita käyttävien ihmisten tavoittamiseen, kohtaamiseen, auttamiseen sekä palveluihin ohjaamiseen haittoja vähentävällä työotteella jalkautuvan terveysneuvontatyön keinoin (Katuklinikka: Helsinki, Pirkanmaan hyvinvointialue, Pohjois-Pohjanmaan hyvinvointialue) (387 909 €) | Ak 3947: Aktiivisesti päihteitä käyttävien ihmisten osallisuuden ja arjenhallinnan vahvistamiseen haittoja vähentävällä työotteella toteutettavan vertais- ja vapaaehtoistoiminnan avulla (Osis) (276 000 €) | Ak 10000: Huumeita käyttävien, erityisesti asunnottomien tai asunnottomuusuhan alaisten ihmisten asunnottomuuden vähentämiseen ja osallisuuden lisäämiseen matalan kynnyksen tuella ja kohtaamispaikkatoiminnalla Tampereen seudulla (Völjy) (244 125 €) | Ak 1257: Vanhempiensa alkoholinkäytöstä merkittäviä haittoja kokevien nuorten ja aikuisten hyvinvoinnin edistämiseen verkossa ja kasvokkain tapahtuvalla toiminnalla (Lasinen lapsuus) (194 250 €) | Ak 5706: Päihde-, mielenterveys- ja rikosseuraamusjärjestöjen perustehtävää tukevan ja kohderyhmien hyvinvoinnin edistämistä palvelevan uuden tutkimustiedon tuottamiseen järjestöjen toiminnasta ja järjestötoimintaan osallistuvien tilanteesta sekä tutkimusyhteistyön kehittämiseen (2026) (189 000 €) | Ak 12261: Monikielisten päihteillä oireilevien nuorten tukemiseen ja palveluihin ohjaamiseen jalkautuvalla työllä (115 000 €) | Ak 9776: Kuntodopingaineiden käytöstä aiheutuvien terveyshaittojen ehkäisyyn ja vähentämiseen terveysneuvonnan, tiedontuotannon ja ammattilaisten kouluttamisen avulla (Dopinglinkki) (80 000 €) | Ak 14: Järjestölähtöisen päihdetyön asiakaslähtöisyyden ja palvelupolkujen sujuvuuden parantamiseen sekä päihdetyössä tarvittavan tiedon saannin edistämiseen (67 333 €)</t>
         </is>
       </c>
     </row>
@@ -3470,12 +4551,7 @@
       </c>
       <c r="I9" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Sosiaaliseen lomatoimintaan vähävaraisille ja erityisen tuen tarpeessa oleville 
-- lapsiperheille
-- omaishoitajille
-- erityisryhmille
-- työikäisille 
-- ikääntyneille (2 437 710 €) | Ak 8: Vapaaehtoispohjaisen tukihenkilöverkoston toimintaan ja koordinointiin haja-asutusalueilla asuville ihmisille (163 000 €) | Ak 9: Sosiaalisen lomatoiminnan asiakasrekisterin ylläpitoon ja kehittämiseen (84 000 €)</t>
+          <t>Ak 1: Sosiaaliseen lomatoimintaan vähävaraisille ja erityisen tuen tarpeessa oleville  - lapsiperheille - omaishoitajille - erityisryhmille - työikäisille  - ikääntyneille (2 437 710 €) | Ak 8: Vapaaehtoispohjaisen tukihenkilöverkoston toimintaan ja koordinointiin haja-asutusalueilla asuville ihmisille (163 000 €) | Ak 9: Sosiaalisen lomatoiminnan asiakasrekisterin ylläpitoon ja kehittämiseen (84 000 €)</t>
         </is>
       </c>
     </row>
@@ -3508,7 +4584,7 @@
       </c>
       <c r="I10" t="inlineStr" s="0">
         <is>
-          <t>C 13682: Nuorten huumekuolemien ehkäisyyn vertaistoimintaa  riskitietoisuuden vahvistamista ja käytännön ensiapuosaamista lisäämällä (ODE 2.0 Pelasta kaveri – toivoa  tietoa ja toimintaa 2026–2028) (Nuorten huumekuolemien ehkäisyn ohjelma) (417 125 €) | Ak 4: Pitkäaikaisasunnottomien ja vaikeasti asutettavien ihmisten integroimiseen normaaliin asuntokantaan asumispolun eri vaiheissa annettavalla yksilöllisellä ja ryhmämuotoisella tuella sekä asumisvalmiuksien ja -taitojen parantamiseen (309 270 €) | Ay 3069: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (194 162 €)</t>
+          <t>Ak 10414: Alle 29-vuotiaille asunnottomille sekä aktiivisesti päihteitä käyttäville nuorille suunnatun kynnyksettömän, ympärivuorokautisen kohtaamis- ja tukipisteen toimintaan (Nuoli) (840 000 €) | C 13682: Nuorten huumekuolemien ehkäisyyn vertaistoimintaa, riskitietoisuuden vahvistamista ja käytännön ensiapuosaamista lisäämällä (ODE 2.0 Pelasta kaveri – toivoa, tietoa ja toimintaa 2026–2028) (Nuorten huumekuolemien ehkäisyn ohjelma) (417 125 €) | Ak 1: Osallisuutta ja hyvinvointia vahvistavaan kynnyksettömään päiväkeskustoimintaan erityisesti pitkäaikaisasunnottomille, asunnottomuusuhan alla oleville sekä henkilöille, joilla on päihde- ja mielenterveysongelmia (Helsinki ja Tuusula) (365 120 €) | Ak 4: Pitkäaikaisasunnottomien ja vaikeasti asutettavien ihmisten integroimiseen normaaliin asuntokantaan asumispolun eri vaiheissa annettavalla yksilöllisellä ja ryhmämuotoisella tuella sekä asumisvalmiuksien ja -taitojen parantamiseen (309 270 €) | Ak 7099: Maahan vasta muuttaneiden ja erityistä tukea tarvitsevien maahanmuuttajataustaisten asunnottomuuden ennaltaehkäisemiseen ja voimavarojen tukemiseen kaikille avoimen ja koteihin vietävän asumisohjauksen, asunnon etsinnän ja vapaaehtoistyön keinoin (KOTA-toiminta) (231 879 €) | Ay 3069: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (194 162 €) | Ak 2: Asunnottomuutta kokeneiden asumisen laadun asukaslähtöiseen kehittämiseen, heidän äänensä ja näkökulmiensa keräämiseen ja tuomiseen yhteiskunnalliseen keskusteluun sekä asunnottomuuden ja asunnottomuusstigman vastaiseen työhön (Koti kaikille) (138 721 €) | Ak 7092: Vapaaehtoistoiminnan koordinointiin sekä uusien vapaaehtoistyöntekijöiden rekrytointiin ja toiminnanohjaukseen (108 047 €)</t>
         </is>
       </c>
     </row>
@@ -3541,8 +4617,7 @@
       </c>
       <c r="I11" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (875 215 €) | Ak 9: Vaikeavammaisten ja heidän läheistensä osallistumisen edistämiseen toimintavälineiden  tapahtuma-  kurssi- ja koulutustoiminnan avulla sekä alan ammattilaisten osaamisen lisäämiseen vaikuttamistyöllä 
-(Malike-toiminta) (520 500 €) | Ak 16: Jäsenjärjestöille kohdistettaviin avustuksiin (70 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (875 215 €) | Ak 9: Vaikeavammaisten ja heidän läheistensä osallistumisen edistämiseen toimintavälineiden, tapahtuma-, kurssi- ja koulutustoiminnan avulla sekä alan ammattilaisten osaamisen lisäämiseen vaikuttamistyöllä  (Malike-toiminta) (520 500 €) | Ak 6480: Harvinaista ja perinnöllistä sairautta sairastavien, heidän läheistensä ja heidän kanssaan työskentelevien ammattilaisten tiedon ja tuen tarpeeseen vastaamiseen tiedon, seminaarien, vertais- ja keskustelutuen sekä neuvonnan avulla (444 538 €) | Ak 15: Kehitysvammaisten ihmisten ja heidän perheidensä itsemääräämisoikeuden, tuetun päätöksenteon ja osallisuuden edistämiseen oikeuksienvalvonnalla, lakineuvonnalla ja palvelujärjestelmän ja lainsäädännön sisältöihin vaikuttamalla (201 000 €) | Ak 4: Kehitysvammaisten nuorten ja aikuisten toimijuuden tukemiseen koulutusten,  kokemustoiminnan ja ryhmätoiminnan avulla. Kehitysvammaisten lasten vanhempien ja muiden läheisten tiedon, osaamisen ja vanhemmuuden vahvistamiseen verkkotilaisuuksien, ammatillisesti ohjatun ryhmätoiminnan ja verkostotyön kautta. (Saavutettava koulutus- ja kokemustoiminta) (195 000 €) | Ak 6482: INCL-perheiden ja vastaavien harvinaisten, etenevien, varhaiseen kuolemaan johtavien diagnoosiryhmien perheiden kokonaisvaltaiseen tukeen erityisperhetyön, vertaistuen, tiedon ja konsultoinnin avulla (134 800 €) | Ak 6483: Harvinaista, perimästä johtuvaa sairautta sairastavien lasten ja nuorten sekä perheidensä arjessa pärjäämisen ja osallisuuden vahvistamiseen sekä muuttuneen elämäntilanteen prosessointiin ryhmämuotoisella kurssitoiminnalla. (103 650 €) | Ak 16: Jäsenjärjestöille kohdistettaviin avustuksiin (70 000 €) | Ak 17: Kehitysvammaisten ja vammattomien nuorten ja aikuisten yhdenvertaisen kohtaamisen edistämiseen vapaaehtoistoiminnan keinoin. Kehitysvammaisten nuorten ja aikuisten toimijuuden ja osallisuuden vahvistamiseen vapaaehtoistoiminnan keinoin.  (Yhdenvertainen kaveritoiminta ja vapaaehtoistoiminta 2025-2026) (46 300 €)</t>
         </is>
       </c>
     </row>
@@ -3575,10 +4650,7 @@
       </c>
       <c r="I12" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (1 172 358 €) | Ak 4: Puhevammaisten ihmisten osallisuuden  itsemääräämisoikeuden ja vuorovaikutusmahdollisuuksien edistämiseen ohjaus- ja toimintamallien  materiaalien  neuvonnan  vertaistuen ja vaikuttamistyön avulla (Tikoteekki) (420 000 €) | Ak 3: Selkokieltä tarvitsevien ihmisten tukemiseen selkokielisen tiedonvälityksen  ajankohtaistiedon  neuvonnan ja koulutusten avulla 
-- Selkoaineistojen kehittämiseen ja laadun varmistamiseen
-- Selkokielen näkyvyyden lisäämiseen 
-(Selkokeskus) (367 133 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (1 172 358 €) | Ak 4: Puhevammaisten ihmisten osallisuuden, itsemääräämisoikeuden ja vuorovaikutusmahdollisuuksien edistämiseen ohjaus- ja toimintamallien, materiaalien, neuvonnan, vertaistuen ja vaikuttamistyön avulla (Tikoteekki) (420 000 €) | Ak 6: Puhevammaisten sekä ymmärtämisessä ja kommunikoinnissa tukea tarvitsevien ihmisten vuorovaikutuksen ja osallistumisen tukemiseen helppokäyttöisten, saavutettavien materiaalien ja sovellusten avulla - Läheisten ja alan ammattilaisten osaamisen lisäämiseen - Toimia tiedon levittämisen ja materiaalin jakamisen kanavana alan järjestöille ja muille toimijoille - Verkkopalvelujen saavutettavuuden edistämiseen (Papunet-verkkopalvelut) (374 850 €) | Ak 3: Selkokieltä tarvitsevien ihmisten tukemiseen selkokielisen tiedonvälityksen, ajankohtaistiedon, neuvonnan ja koulutusten avulla  - Selkoaineistojen kehittämiseen ja laadun varmistamiseen - Selkokielen näkyvyyden lisäämiseen  (Selkokeskus) (367 133 €) | Ak 10: Vertaistoiminnan ja neuvonnan tarjoamiseen ihmisille, joilla on raskaudenaikaisesta alkoholinaltistuksesta aiheutuneita kehityshäiriöitä (FASD) - Sijais- ja adoptiovanhempien arjessa selviytymisen tukemiseen - Ammattilaisten osaamisen lisäämiseen ja FASD-tietoisuuden lisäämiseen (86 940 €)</t>
         </is>
       </c>
     </row>
@@ -3611,7 +4683,7 @@
       </c>
       <c r="I13" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (757 741 €) | Ak 8: Lasten aseman ja oikeuksien turvaamiseen ja edistämiseen erityisesti digitaalisessa mediassa (Nettivihjetoiminta) (117 845 €) | Ak 6: Suomalaisten adoptiohakijoiden  adoptiovanhempien ja adoptoitujen tukemiseen tiedotuksen ja ohjauksen keinoin adoptioprosessin eri vaiheissa (kansainvälinen adoptiopalvelu) (98 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (757 741 €) | Ak 7: Lasten ja lapsiperheiden varhaiseen tukemiseen vapaaehtoisten tukihenkilöiden ja sporttikummien avulla (601 320 €) | Ak 2: Lapsen ja perheen hyvinvoinnin ja voimavarojen vahvistamiseen lisäämällä lapsen tukiverkostoa loma- tai kummikotitoiminnan avulla (Varhaisen tuen loma- ja kummikotitoiminta) (340 069 €) | Ak 2961: Lasten ja lapsiperheiden hyvinvoinnin ja osallisuuden vahvistamiseen matalan kynnyksen verkosto- ja yhteisötalotoiminnan avulla (Joensuun Perheentalo) (228 957 €) | Ak 6013: Lasten ja lapsiperheiden hyvinvoinnin ja osallisuuden vahvistamiseen matalan kynnyksen verkosto- ja yhteisötalon toiminnalla (Kuopion Perheentalo) (222 705 €) | Ak 8: Lasten aseman ja oikeuksien turvaamiseen ja edistämiseen erityisesti digitaalisessa mediassa (Nettivihjetoiminta) (117 845 €) | Ak 6: Suomalaisten adoptiohakijoiden, adoptiovanhempien ja adoptoitujen tukemiseen tiedotuksen ja ohjauksen keinoin adoptioprosessin eri vaiheissa (kansainvälinen adoptiopalvelu) (98 000 €)</t>
         </is>
       </c>
     </row>
@@ -3644,7 +4716,7 @@
       </c>
       <c r="I14" t="inlineStr" s="0">
         <is>
-          <t>Ak 6: MLL:n paikallisen vapaaehtoisen lapsi- ja perhetoiminnan ja sen toimintaedellytyksien ohjaukseen sekä valtakunnalliseen perhekeskusyhteistyöhön (669 834 €) | Ak 8: Oppilaiden osallisuutta edistävään vapaaehtoistoimintaan kouluissa (Tukioppilas-   kummioppilas- ja tutortoiminta sekä Koulurauha-ohjelma) (341 713 €) | Ak 13: Lasten ja lapsiperheiden hyvinvoinnin edistämiseen ja tasavertaisen vanhemmuuden vahvistamiseen kehittämällä mentalisaatioperusteista vanhempainryhmätoimintaa ja Jututtamo-vertaisryhmätoimintaa sekä kouluttamalla vapaaehtoisia ja ammattilaisia ryhmien ohjaajiksi (Mentalisaatioperustainen vanhempainryhmätoiminta) (144 217 €)</t>
+          <t>Ak 6: MLL:n paikallisen vapaaehtoisen lapsi- ja perhetoiminnan ja sen toimintaedellytyksien ohjaukseen sekä valtakunnalliseen perhekeskusyhteistyöhön (669 834 €) | Ak 5: Aikuisen tuen tarjoamiseen vuoden jokaisena päivänä alle 25-vuotiaille lapsille ja nuorille puhelin-, netti- ja chat-palvelun keinoin (Lasten ja nuorten puhelin, netti ja chat) (540 280 €) | Ak 8: Oppilaiden osallisuutta edistävään vapaaehtoistoimintaan kouluissa (Tukioppilas-,  kummioppilas- ja tutortoiminta sekä Koulurauha-ohjelma) (341 713 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (240 000 €) | Ak 10: Vanhemmille suunnatun matalan kynnyksen, anonyymin ja luottamuksellisen tuen ja avun tarjoamiseen vanhempainpuhelin- ja nettipalvelutoiminnan keinoin (231 339 €) | Ak 13: Lasten ja lapsiperheiden hyvinvoinnin edistämiseen ja tasavertaisen vanhemmuuden vahvistamiseen kehittämällä mentalisaatioperusteista vanhempainryhmätoimintaa ja Jututtamo-vertaisryhmätoimintaa sekä kouluttamalla vapaaehtoisia ja ammattilaisia ryhmien ohjaajiksi (Mentalisaatioperustainen vanhempainryhmätoiminta) (144 217 €) | Ak 11254: Eri-ikäisten lasten ja aikuisten kohtaamisen ja osallisuuden lisäämiseen leikkitoiminnan avulla (Leikkipäivä-ohjelma). (58 965 €) | Ak 7: Valtakunnallisen äitienpäiväjuhlan järjestämiseen (27 563 €)</t>
         </is>
       </c>
     </row>
@@ -3677,7 +4749,7 @@
       </c>
       <c r="I15" t="inlineStr" s="0">
         <is>
-          <t>Ak 15: Matalan kynnyksen tuki- ja neuvontapalveluiden ja vertaistukitoiminnan ylläpitämiseen rahapelihaittoja kokeville pelaajille  heidän läheisilleen ja pelihaittoja työssään kohtaaville ammattilaisille (Tiltti) (368 434 €) | Ak 2586: Hyvinvointia edistävän Green Care -toiminnan lisäämiseen ja kehittämiseen sosiaali- ja terveysjärjestöissä (Vihreä veräjä) (187 431 €) | Ak 17: Haitallisesti päihteitä käyttävien läheisten voimavarojen vahvistamiseen sekä yhteiskunnallisen aseman ja palvelujen saatavuuden parantamiseen tiedon tuottamisen  ammattilaisille suunnatun kouluttamisen sekä toimintamallien kehittämisen ja levittämisen avulla (166 609 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (820 787 €) | Ak 15: Matalan kynnyksen tuki- ja neuvontapalveluiden ja vertaistukitoiminnan ylläpitämiseen rahapelihaittoja kokeville pelaajille, heidän läheisilleen ja pelihaittoja työssään kohtaaville ammattilaisille (Tiltti) (368 434 €) | Ak 16: Jäsenjärjestöjen osaamisen, toimintaedellytysten ja kansalaistoiminnan vahvistamiseen koulutuksella, asiantuntijatuella, verkostoyhteistyöllä sekä kehittämällä vapaaehtois- ja vertaistoimintaa (315 000 €) | Ak 2586: Hyvinvointia edistävän Green Care -toiminnan lisäämiseen ja kehittämiseen sosiaali- ja terveysjärjestöissä (Vihreä veräjä) (187 431 €) | Ak 11142: Pelihaittojen vähentämiseen ongelmallisesti mobiili-, konsoli- ja tietokonepelejä pelaaville suunnatun Restart-ohjelman avulla (2026) (172 200 €) | Ak 17: Haitallisesti päihteitä käyttävien läheisten voimavarojen vahvistamiseen sekä yhteiskunnallisen aseman ja palvelujen saatavuuden parantamiseen tiedon tuottamisen, ammattilaisille suunnatun kouluttamisen sekä toimintamallien kehittämisen ja levittämisen avulla (166 609 €) | Ak 11009: Ikääntyneiden päihteidenkäyttäjien osallisuuden lisäämiseen, päihdehaittojen vähentämiseen ja arjenhallinnan vahvistamiseen tähtäävän Pilke-ryhmätoiminnan levittämiseen ja juurruttamiseen kouluttajakoulutusten ja tukimateriaalituotannon avulla (79 800 €) | Ak 14: Jäsenjärjestöille kohdistettaviin avustuksiin (50 000 €)</t>
         </is>
       </c>
     </row>
@@ -3710,7 +4782,7 @@
       </c>
       <c r="I16" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Sosiaaliseen lomatoimintaan vähävaraisille ja erityisen tuen tarpeessa oleville lapsiperheille  erityisryhmille ja aikuisväestölle. (2 103 947 €)</t>
+          <t>Ak 1: Sosiaaliseen lomatoimintaan vähävaraisille ja erityisen tuen tarpeessa oleville lapsiperheille, erityisryhmille ja aikuisväestölle. (2 103 947 €)</t>
         </is>
       </c>
     </row>
@@ -3743,7 +4815,7 @@
       </c>
       <c r="I17" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (803 250 €) | Ak 15: Viittomakielisten aikuisten  lasten ja nuorten sekä heidän läheistensä voimavarojen  toimintakyvyn ja osallisuuden tukemiseen vertaistukikurssitoiminnan avulla (194 250 €) | Ak 4080: Jäsenjärjestöille kohdistettaviin avustuksiin (30 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (803 250 €) | Ak 6: Viittomakielisten kuurojen arjessa selviytymisen,  tiedonsaannin, osallisuuden ja kieli-identiteetin tukemiseen lähi- ja etämuotoisen palveluohjauksen, digitaitojen vahvistamisen ja alueellisen asiantuntijatyön keinoin - Vapaaehtois- ja vertaistyön koordinointiin (kaveritoiminta) - Jäsenyhdistysten tukemiseen (629 280 €) | Ak 14: Viittomakielisten kuurojen tiedonsaannin tukemiseen, liiton ulkoiseen ja sisäiseen viestintään, jäsenyhdistysviestintään sekä kohdennettuun viittomakieliseen viestintään (332 000 €) | Ak 15: Viittomakielisten aikuisten, lasten ja nuorten sekä heidän läheistensä voimavarojen, toimintakyvyn ja osallisuuden tukemiseen vertaistukikurssitoiminnan avulla (194 250 €) | Ak 9: Viittomakieliä käyttävien sekä niitä opiskelevien kommunikoinnin vahvistamiseen ja tukemiseen avoimen verkkosanakirjapalvelun avulla (102 500 €) | Ak 4080: Jäsenjärjestöille kohdistettaviin avustuksiin (30 000 €)</t>
         </is>
       </c>
     </row>
@@ -3776,7 +4848,7 @@
       </c>
       <c r="I18" t="inlineStr" s="0">
         <is>
-          <t>Ak 2442: Ryhmä- ja yksilömuotoiseen  sekä avoimeen tukitoimintaan neuropsykiatrisia piirteitä omaaville aikuisille (Omavoima) (140 915 €) | Ak 4: Maahanmuuttajanaisten ja heidän perheidensä kotoutumisen tukemiseen  osallisuuden lisäämiseen sekä syrjäytymisen ehkäisyyn avoimen toiminnan  ryhmien sekä yksilöneuvonnan ja -tuen keinoin (Kansainvälinen naisten tapaamispaikka Naistari) (140 026 €) | Ak 9885: Kiusaamista kokeneiden ja heidän läheistensä selviytymistä ja toipumista edistävään yksilöllisen tukeen ja vertaisryhmätoimintaan sekä ammattilaisten osaamisen kehittämiseen kiusaamisteemasta (99 320 €)</t>
+          <t>Ay 1461: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (493 026 €) | Ak 4293: Perheväkivallan, seksuaalisen väkivallan ja kunniaan liittyvän väkivallan ennaltaehkäisyyn, väkivaltaa kokeneiden ja tehneiden tukemiseen yksilö- ja ryhmämuotoisen tuen keinoin sekä väkivaltatyön osaamisen levittämiseen (Väkivaltatyön yksikkö) (452 528 €) | Ak 6: Sosiaalisesti heikoimmassa asemassa olevien, maahanmuuttajataustaisen, seksuaalista väkivaltaa kohdanneiden ja muiden erityisen tuen tarpeessa olevien tyttöjen ja naisten matalankynnyksen toimintaan sekä ryhmä- ja yksilötukeen (Tampereen Tyttöjen Talo) (176 140 €) | Ak 1166: Kansalaistoimintalähtöisen etnisesti monimuotoisen miestyön toteuttamiseen kohderyhmän osallisuuden ja hyvinvoinnin tukemiseksi (Miesten kansalaistalo Mattila) (148 500 €) | Ak 2445: Yksinäisyyden kokemusta vähentävään kansalaistoimintaan, vertaistukityöhön ja loma-ajan päiväleiritoimintaan erityistä tukea tarvitseville kehitysvammaisille nuorille, nuorille aikuisille ja heidän läheisilleen (Voimavirta) (141 095 €) | Ak 2442: Ryhmä- ja yksilömuotoiseen  sekä avoimeen tukitoimintaan neuropsykiatrisia piirteitä omaaville aikuisille (Omavoima) (140 915 €) | Ak 4: Maahanmuuttajanaisten ja heidän perheidensä kotoutumisen tukemiseen, osallisuuden lisäämiseen sekä syrjäytymisen ehkäisyyn avoimen toiminnan, ryhmien sekä yksilöneuvonnan ja -tuen keinoin (Kansainvälinen naisten tapaamispaikka Naistari) (140 026 €) | Ak 10993: Lapsen taholta väkivaltaa kokeneiden vanhempien, perheyhteisöjen, väkivaltaiseen käytökseen taipuvaisten lasten ja ilmiön eri osapuolia työssään kohtaavien ammattilaisten tukemiseen Pirkanmaalla (126 087 €) | Ak 13626: Työttömien omaehtoisen terveyden ja elämänhallinnan edistämiseen kohderyhmän voimavaroja tukevien vertaisryhmien, valmentavien yksilökeskusteluiden sekä terveysmittauspisteen avulla Tampereen seudulla (126 000 €) | Ak 9885: Kiusaamista kokeneiden ja heidän läheistensä selviytymistä ja toipumista edistävään yksilöllisen tukeen ja vertaisryhmätoimintaan sekä ammattilaisten osaamisen kehittämiseen kiusaamisteemasta (99 320 €)</t>
         </is>
       </c>
     </row>
@@ -3809,8 +4881,7 @@
       </c>
       <c r="I19" t="inlineStr" s="0">
         <is>
-          <t>Ak 1279: Vanhemmuuden tukemiseen  lapsiperheiden hyvinvoinnin vahvistamiseen ja koululaisten luvattomien poissaolojen sekä koulupudokkuuden ehkäisemiseen
-(Vanhempien Akatemia) (359 668 €) | Ay 2: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (294 814 €) | C 13717: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Vapaaksi" (Dnro: EURA 2021/209866/09) osarahoitukseen järjestölle (2026-2028) (94 938 €)</t>
+          <t>Ak 3020: Mielenterveyskuntoutujien terveyttä, hyvinvointia, osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään kohtaamispaikkatoimintaan Kajaanin, Oulun ja Rovaniemen alueella sekä eKlubitalotoimintaan  (Klubitalo Pönkkä, Klubitalo Tönäri ja Klubitalo Roihula) (538 893 €) | C 13807: Nuorten huumekuolemien ehkäisyyn kohtaavalla työllä, koulutuksella ja kehittämistoiminnalla (Sauma - tukea, turvallisuutta ja yhteistyötä nuorten huumekuolemien ehkäisemiseksi 2026-2028) (Nuorten huumekuolemien ehkäisyn ohjelma) (417 125 €) | Ak 1279: Vanhemmuuden tukemiseen, lapsiperheiden hyvinvoinnin vahvistamiseen ja koululaisten luvattomien poissaolojen sekä koulupudokkuuden ehkäisemiseen (Vanhempien Akatemia) (359 668 €) | Ay 2: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (294 814 €) | Ak 10018: Huumeiden käyttäjien ja heidän läheistensä matalan kynnyksen vertaistoimintaan sekä osallisuuden ja toimintakyvyn tukemiseen Oulun alueella  (VERTO) (289 010 €) | C 13717: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Vapaaksi" (Dnro: EURA 2021/209866/09) osarahoitukseen järjestölle (2026-2028) (94 938 €) | Ak 11057: Paikka auki - avustusohjelman koordinointiin (10 000 €)</t>
         </is>
       </c>
     </row>
@@ -3843,7 +4914,7 @@
       </c>
       <c r="I20" t="inlineStr" s="0">
         <is>
-          <t>Ak 6: Kuulovammaisten  erityisesti ikääntyneiden huonokuuloisten toimintakyvyn tukemiseen sekä kuuloyhdistysten ja vapaaehtoisten yhdistystoiminnan osaamisen ja voimavarojen vahvistamiseen kuulotilaisuuksien  koulutusten  kuuloautotapahtumien  digituen  henkilökohtaisen neuvonnan ja alueellisen vaikuttamistyön keinoin (470 450 €) | Ak 12413: Työikäisten ja ikääntyneiden huonon kuulon  muistin  kognition ja mielen hyvinvoinnin yhteyksien tunnistamiseen  tunnistamistyökalujen kehittämiseen  koulutuksiin ja tapahtumiin  ryhmämuotoiseen tukeen sekä eri toimijoiden väliseen yhteistyöhön (Kuule  muista ja voi hyvin -toiminta) (160 000 €) | Ak 23: Jäsenjärjestöille kohdistettaviin avustuksiin (50 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (1 054 178 €) | Ak 6: Kuulovammaisten, erityisesti ikääntyneiden huonokuuloisten toimintakyvyn tukemiseen sekä kuuloyhdistysten ja vapaaehtoisten yhdistystoiminnan osaamisen ja voimavarojen vahvistamiseen kuulotilaisuuksien, koulutusten, kuuloautotapahtumien, digituen, henkilökohtaisen neuvonnan ja alueellisen vaikuttamistyön keinoin (470 450 €) | Ak 9: Ryhmämuotoiseen vertaistukipainotteiseen kuulokurssitoimintaan ikääntyneille huonokuuloisille, tinnituksesta kärsiville, työikäisille kuulovammaisille ja heidän läheisilleen sekä kuulovammaisten lasten ja nuorten leiri- ja vertaistoimintaan (235 000 €) | Ak 12413: Työikäisten ja ikääntyneiden huonon kuulon, muistin, kognition ja mielen hyvinvoinnin yhteyksien tunnistamiseen, tunnistamistyökalujen kehittämiseen, koulutuksiin ja tapahtumiin, ryhmämuotoiseen tukeen sekä eri toimijoiden väliseen yhteistyöhön (Kuule, muista ja voi hyvin -toiminta) (160 000 €) | Ak 23: Jäsenjärjestöille kohdistettaviin avustuksiin (50 000 €)</t>
         </is>
       </c>
     </row>
@@ -3876,7 +4947,7 @@
       </c>
       <c r="I21" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (750 000 €) | Ak 5: Intiimeissä ihmissuhteissa huolta kokevien nuorten ja nuorten aikuisten seksuaalisen hyvinvoinnin tukemiseen verkkopalveluiden ja tiedontuotannon keinoin (250 000 €) | Ak 5695: Maahanmuuttajien  erityisesti naismaahanmuuttajien työllistymisen edistämiseen mentoroinnilla ja verkostotyöllä (93 135 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (750 000 €) | Ak 13624: Parisuhteen ja perheen hyvinvointia vahvistavaan ja parisuhdeongelmia ennaltaehkäisevään työhön koulutuksen, viestinnän, neuvonnan ja muun toiminnan keinoin. Erityiskohderyhmänä parit, joiden perheessä on sairautta, mielenterveyshaasteita ja vaikeita kriisitilanteita. (337 300 €) | Ak 5: Intiimeissä ihmissuhteissa huolta kokevien nuorten ja nuorten aikuisten seksuaalisen hyvinvoinnin tukemiseen verkkopalveluiden ja tiedontuotannon keinoin (250 000 €) | Ak 6: Vanhemmuuden vahvistamiseen verkkopalveluiden, tiedontuotannon ja mediatyön keinoin. Toiminta kohdistetaan etenkin kuormittuneille vanhemmille. (250 000 €) | Ak 5685: Pojille ja nuorille miehille kohdistetun matalan kynnyksen ennaltaehkäisevän puhelin- ja verkkopalvelun ylläpitoon ja kehittämiseen (Poikien Puhelin) (240 000 €) | Ak 5695: Maahanmuuttajien, erityisesti naismaahanmuuttajien työllistymisen edistämiseen mentoroinnilla ja verkostotyöllä (93 135 €)</t>
         </is>
       </c>
     </row>
@@ -3909,7 +4980,7 @@
       </c>
       <c r="I22" t="inlineStr" s="0">
         <is>
-          <t>Ak 7829: Mielenterveyskuntoutujien terveyttä  hyvinvointia  osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään kohtaamispaikkatoimintaan (Tuusulanjärven Klubitalo) (203 962 €) | Ak 2: Mielenterveyskuntoutujien terveyttä  hyvinvointia  osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään kohtaamispaikkatoimintaan (Itä-Helsingin Klubitalo) (185 220 €) | Ak 2519: Mielenterveyskuntoutujien terveyttä  hyvinvointia  osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään kohtaamispaikkatoimintaan (Imatran Klubitalo) (179 707 €)</t>
+          <t>Ak 1: Mielenterveyskuntoutujien terveyttä, hyvinvointia, osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään kohtaamispaikkatoimintaan  (Helsingin Klubitalo) (395 687 €) | Ay 3087: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (297 410 €) | Ak 2504: Mielenterveyskuntoutujien terveyttä, hyvinvointia, osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään kohtaamispaikkatoimintaan (Tikkurilan Klubitalo) sekä järjestölähtöisen kokemusasiantuntijatoiminnan koordinointiin Vantaan ja Keravan hyvinvointialueella. (265 142 €) | Ak 7829: Mielenterveyskuntoutujien terveyttä, hyvinvointia, osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään kohtaamispaikkatoimintaan (Tuusulanjärven Klubitalo) (203 962 €) | Ak 2: Mielenterveyskuntoutujien terveyttä, hyvinvointia, osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään kohtaamispaikkatoimintaan (Itä-Helsingin Klubitalo) (185 220 €) | Ak 2519: Mielenterveyskuntoutujien terveyttä, hyvinvointia, osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään kohtaamispaikkatoimintaan (Imatran Klubitalo) (179 707 €) | Ak 7052: Mielenterveyskuntoutujien terveyttä, hyvinvointia, osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään kohtaamispaikkatoimintaan (Nurmijärven Klubitalo) (175 297 €) | Ak 5457: Mielenterveyskuntoutujien terveyttä, hyvinvointia, osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään kohtaamispaikkatoimintaan (Lahden klubitalo) (173 802 €)</t>
         </is>
       </c>
     </row>
@@ -3942,8 +5013,7 @@
       </c>
       <c r="I23" t="inlineStr" s="0">
         <is>
-          <t>Ak 6: Ongelmallisesti rahapelejä pelaavien ja heidän läheistensä elämänlaadun parantamiseen vertaistuen keinoin
-(Pelirajaton) (472 000 €) | Ay 2: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (381 300 €) | Ak 7697: Nuorten aikuisten (18–29-vuotiaat) ongelmallisen digipelaamisen ja sosiaalisen median käytön vähentämiseen vertaistoiminnan  ryhmätoiminnan ja sähköisten työvälineiden avulla. Ymmärryksen ja ammatillisen osaamisen lisäämiseen digitaalisista riippuvuuksista koulutusten ja kokemusasiantuntijatyön avulla. (Digipelirajaton &amp; Somerajaton) (165 375 €)</t>
+          <t>Ak 3045: 18-35-vuotiaiden mielenterveyskuntoutujien osallisuuden tunteen ja motivaation kasvattamiseen sekä työ- ja toimintakyvyn edistämiseen järjestämällä vertaisuuteen perustuvaan kulttuuripajatoimintaan (837 940 €) | Ak 6: Ongelmallisesti rahapelejä pelaavien ja heidän läheistensä elämänlaadun parantamiseen vertaistuen keinoin (Pelirajaton) (472 000 €) | Ay 2: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (381 300 €) | Ak 7697: Nuorten aikuisten (18–29-vuotiaat) ongelmallisen digipelaamisen ja sosiaalisen median käytön vähentämiseen vertaistoiminnan, ryhmätoiminnan ja sähköisten työvälineiden avulla. Ymmärryksen ja ammatillisen osaamisen lisäämiseen digitaalisista riippuvuuksista koulutusten ja kokemusasiantuntijatyön avulla. (Digipelirajaton &amp; Somerajaton) (165 375 €)</t>
         </is>
       </c>
     </row>
@@ -3976,7 +5046,7 @@
       </c>
       <c r="I24" t="inlineStr" s="0">
         <is>
-          <t>Ak 11119: Nuorten yksinäisyyden kokemusten vähentämiseen ja osallisuuden vahvistamiseen keskustelu- ja kriisiavun  vapaaehtoisen kaveritoiminnan sekä jalkautuvan yhteisötoiminnan keinoin (244 000 €) | Ak 11131: Lapsiperheiden yksinäisyyden kokemusten vähentämiseen  osallisuuden lisäämiseen ja voimavarojen vahvistamiseen keskusteluavun  ohjauksen  neuvonnan ja vapaaehtoistoiminnan avulla (HelsinkiMission Perhetoiminta) (225 000 €) | Ak 7504: Aikuisten yksinäisyyden tunteen vähentämiseen yksinäisyysohjelman  yksinäisyyden omahoito-ohjelman ja keskusteluavun keinoin (Yksinäisyystyön keskus) (215 000 €)</t>
+          <t>Ak 11121: Ikääntyneiden yksinäisyyden kokemusten vähentämiseen, osallisuuden lisäämiseen ja voimavarojen vahvistamiseen keskusteluavun, ohjauksen, neuvonnan ja vapaaehtoistoiminnan avulla (HelsinkiMission Senioripysäkki) (454 930 €) | Ak 8: Kodin ulkopuoliseen väkivaltaan syyllistyneiden tai syyllistymisriskissä olevien väkivaltaisen käyttäytymisen vähentämiseen ja ehkäisemiseen yksilöllisen asiakastyön ja verkostotyön avulla sekä valtakunnallisen toiminnan koordinointiin (Aggredi) (354 387 €) | Ay 1706: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (326 400 €) | Ak 11119: Nuorten yksinäisyyden kokemusten vähentämiseen ja osallisuuden vahvistamiseen keskustelu- ja kriisiavun, vapaaehtoisen kaveritoiminnan sekä jalkautuvan yhteisötoiminnan keinoin (244 000 €) | Ak 11131: Lapsiperheiden yksinäisyyden kokemusten vähentämiseen, osallisuuden lisäämiseen ja voimavarojen vahvistamiseen keskusteluavun, ohjauksen, neuvonnan ja vapaaehtoistoiminnan avulla (HelsinkiMission Perhetoiminta) (225 000 €) | Ak 7504: Aikuisten yksinäisyyden tunteen vähentämiseen yksinäisyysohjelman, yksinäisyyden omahoito-ohjelman ja keskusteluavun keinoin (Yksinäisyystyön keskus) (215 000 €)</t>
         </is>
       </c>
     </row>
@@ -4009,10 +5079,7 @@
       </c>
       <c r="I25" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Yksinäisten  masentuneiden  sosiaalisesti syrjäytyneiden  monikulttuuristen  psyykkisesti oireilevien ja muiden erityistä tukea tarvitsevien 10-28-vuotiaiden tyttöjen ja nuorten naisten matalan kynnyksen toimintaan sekä ryhmä- ja yksilötukeen 
-(Kumppanuustalo Tyttöjen Talo) (138 915 €) | Ak 5757: Ryhmä- ja yksilömuotoiseen kulttuurisensitiiviseen toimintaan espoolaisille 10-28 vuotiaille maahanmuuttajataustaisille tytöille ja nuorille naisille Espoossa
-(Sorella) (132 300 €) | C 13723: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "SUSE - sukupuolisensitiivisyys nuorten
-palveluissa " osarahoitukseen järjestölle (2026-2028) (58 258 €)</t>
+          <t>Ak 10858: Seksuaalisen häirinnän, väkivallan ja kiusaamisen vähentämiseen sosiaalisen median alustoilla sekä yksilöllisen tuen antamiseen kaltoinkohdelluille 8–21-vuotiaille lapsille ja nuorille digitaalisissa ympäristöissä  (Sua varten Somessa) (346 500 €) | Ak 4230: Kunniaan liittyvien konfliktien ja väkivallan ennaltaehkäisemiseen ryhmätoiminnan, yksilö- ja perhekohtaisen tuen sekä koulutuksen avulla sekä yksilölliseen ja yhteisölliseen tukeen kunniaan liittyvän väkivallan vuoksi taustayhteisöstään irtaantuville tai ulossuljetuille nuorille Helsingissä. (SOPU) (306 863 €) | Ay 1303: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (298 608 €) | Ak 6: Yksinäisten, kiusattujen ja syrjäytettyjen poikien tukemiseen, seksuaalista väkivaltaa kohdanneiden poikien auttamiseen sekä poikien seksuaaliterveystyöhön Helsingin Poikien talolla. (Poikien Talo) (175 691 €) | Ak 10647: 13–28-vuotiaiden nuorten yksilö- ja ryhmämuotoiseen seksuaaliväkivaltatyöhön Tyttöjen ja Poikien Talo -työn rinnalla Helsingissä, Espoossa ja Vantaalla.   (Tyttöjen ja Poikien Talojen seksuaaliväkivaltatyö) (162 554 €) | Ak 12389: Yksinäisten, kiusattujen, häirintää tai väkivaltaa kokeneiden, syrjäytettyjen ja sukupuolen moninaisuutta ja seksuaali-identiteettiään pohtivien poikien ja nuorten miesten tukemiseen (Vantaan poikien talo) (151 300 €) | Ak 1: Yksinäisten, masentuneiden, sosiaalisesti syrjäytyneiden, monikulttuuristen, psyykkisesti oireilevien ja muiden erityistä tukea tarvitsevien 10-28-vuotiaiden tyttöjen ja nuorten naisten matalan kynnyksen toimintaan sekä ryhmä- ja yksilötukeen  (Kumppanuustalo Tyttöjen Talo) (138 915 €) | Ak 5757: Ryhmä- ja yksilömuotoiseen kulttuurisensitiiviseen toimintaan espoolaisille 10-28 vuotiaille maahanmuuttajataustaisille tytöille ja nuorille naisille Espoossa (Sorella) (132 300 €) | C 13723: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "SUSE - sukupuolisensitiivisyys nuorten palveluissa " osarahoitukseen järjestölle (2026-2028) (58 258 €)</t>
         </is>
       </c>
     </row>
@@ -4045,7 +5112,7 @@
       </c>
       <c r="I26" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (1 035 245 €) | Ak 9: Harvinaisiin tuki- ja liikuntaelinsairaus- ja vammaryhmiin kuuluvien henkilöiden ja heidän läheistensä hyvinvoinnin ja osallistumismahdollisuuksien edistämiseen vertaistuen  koulutusten  ohjauksen ja neuvonnan avulla (142 538 €) | Ak 17: Jäsenjärjestöille kohdistettaviin avustuksiin (36 750 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (1 035 245 €) | Ak 7: Fyysisesti toimintarajoitteisten henkilöiden ja heidän läheistensä voimavarojen vahvistamiseen ja arjen sujuvuuden parantamiseen teema, -pari- ja perhekurssien avulla (523 800 €) | Ak 9: Harvinaisiin tuki- ja liikuntaelinsairaus- ja vammaryhmiin kuuluvien henkilöiden ja heidän läheistensä hyvinvoinnin ja osallistumismahdollisuuksien edistämiseen vertaistuen, koulutusten, ohjauksen ja neuvonnan avulla (142 538 €) | Ak 17: Jäsenjärjestöille kohdistettaviin avustuksiin (36 750 €)</t>
         </is>
       </c>
     </row>
@@ -4078,7 +5145,7 @@
       </c>
       <c r="I27" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (661 626 €) | Ak 13: Jäsenyhdistyksissä toteutettavien vaativan vauvatyön työmuotojen (Vauvaperheryhmä  Vauvaperheohjaus  vapaaehtoisdoulatoiminta ja vauvaperheiden kohtaamispaikkatoiminta) kehittämis- ja koordinointitoimintaan sekä vaikuttamistyöhön. Vauvaperheille suunnatun verkkoauttamistoiminnan (vauvaperhe chat ja vauvaperhe.fi -sivusto) koordinointiin ja kehittämiseen  sekä monikulttuurisen työotteen kehittämiseen. (451 200 €) | Ak 22: Eroperheiden auttamisen kehittämiseen ja yhteistyövanhemmuuden ja rinnakkaisvanhemmuuden vahvistamiseen. Varhaisen tuen ja vaativien eropalvelujen kehittämiseen  menetelmien levittämiseen ja juurruttamiseen sekä vaikuttamistyöhön. Yhteistyön koordinointiin muiden alan toimijoiden kanssa (Ero lapsiperheessä -työ). (230 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (661 626 €) | Ak 13: Jäsenyhdistyksissä toteutettavien vaativan vauvatyön työmuotojen (Vauvaperheryhmä, Vauvaperheohjaus, vapaaehtoisdoulatoiminta ja vauvaperheiden kohtaamispaikkatoiminta) kehittämis- ja koordinointitoimintaan sekä vaikuttamistyöhön. Vauvaperheille suunnatun verkkoauttamistoiminnan (vauvaperhe chat ja vauvaperhe.fi -sivusto) koordinointiin ja kehittämiseen, sekä monikulttuurisen työotteen kehittämiseen. (451 200 €) | Ak 16: Jäsenjärjestöissä tehtävän perhe- ja lähisuhdeväkivaltaan liittyvän ennaltaehkäisyn ja avotyön koordinointiin, kehittämiseen ja auditointiin sekä vaikuttamistyöhön ja Nettiturvakoti -sivuston kehittämiseen ja verkkoauttamisen koordinointiin (Perhe- ja lähisuhdeväkivaltatyö) (392 818 €) | Ak 22: Eroperheiden auttamisen kehittämiseen ja yhteistyövanhemmuuden ja rinnakkaisvanhemmuuden vahvistamiseen. Varhaisen tuen ja vaativien eropalvelujen kehittämiseen, menetelmien levittämiseen ja juurruttamiseen sekä vaikuttamistyöhön. Yhteistyön koordinointiin muiden alan toimijoiden kanssa (Ero lapsiperheessä -työ). (230 000 €)</t>
         </is>
       </c>
     </row>
@@ -4111,12 +5178,7 @@
       </c>
       <c r="I28" t="inlineStr" s="0">
         <is>
-          <t>Ak 10: Iäkkäiden yksinäisyyden kokemusten lievittämiseen  muistisairauden varhaisen vaiheen omahoitotaitojen vahvistamiseen  toimintakyvyn ylläpitämiseen ja edistämiseen sekä elämänhallinnan vahvistumiseen vertaistuellisen ryhmätoiminnan keinoin.
-Vapaaehtoisten ja ammattilaisten ryhmänohjausosaamisen edistämiseen sekä toiminnan juurruttamiseen ja levittämiseen koulutustoiminnan ja työpajojen avulla.
-Ystäväpiiri-toiminta ja siihen perustuva Omahoitovalmennus-toiminta. (415 548 €) | Ak 6: Pääkaupunkiseudun kotona asuvien iäkkäiden osallisuuden ja sosiaalisen vuorovaikutuksen vahvistamiseen sekä yksinäisyyden lievittämiseen ryhmä-  kesä-  virkistys- ja vapaaehtoistoiminnan keinoin.
-Gerontologisen vapaaehtoistoiminnan parissa toimivien tahojen yhteistyön ja vapaaehtoistoiminnan organisoinnin edistämiseen valtakunnallisen osaamisverkoston keinoin.
-Iäkkäille suunnattujen tietoiltapäivien organisointiin.
-Vapaaehtoisten ja ammattilaisten vertaistapaamisiin ja yhdessä oppimisen päiviin vahvistamaan heidän osaamista ryhmänohjauksessa ja sosiokulttuurisessa vanhustyössä. (Senioritoiminta) (224 211 €) | Ak 7: Korjausneuvontaan ja kotiturvallisuuden edistämiseen ikääntyneiden ihmisten kotona asumisen tukemiseksi sekä hyvinvoinnin ja toimintakykyisyyden vahvistamiseksi (203 916 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (675 644 €) | Ak 10: Iäkkäiden yksinäisyyden kokemusten lievittämiseen, muistisairauden varhaisen vaiheen omahoitotaitojen vahvistamiseen, toimintakyvyn ylläpitämiseen ja edistämiseen sekä elämänhallinnan vahvistumiseen vertaistuellisen ryhmätoiminnan keinoin. Vapaaehtoisten ja ammattilaisten ryhmänohjausosaamisen edistämiseen sekä toiminnan juurruttamiseen ja levittämiseen koulutustoiminnan ja työpajojen avulla. Ystäväpiiri-toiminta ja siihen perustuva Omahoitovalmennus-toiminta. (415 548 €) | Ak 6: Pääkaupunkiseudun kotona asuvien iäkkäiden osallisuuden ja sosiaalisen vuorovaikutuksen vahvistamiseen sekä yksinäisyyden lievittämiseen ryhmä-, kesä-, virkistys- ja vapaaehtoistoiminnan keinoin. Gerontologisen vapaaehtoistoiminnan parissa toimivien tahojen yhteistyön ja vapaaehtoistoiminnan organisoinnin edistämiseen valtakunnallisen osaamisverkoston keinoin. Iäkkäille suunnattujen tietoiltapäivien organisointiin. Vapaaehtoisten ja ammattilaisten vertaistapaamisiin ja yhdessä oppimisen päiviin vahvistamaan heidän osaamista ryhmänohjauksessa ja sosiokulttuurisessa vanhustyössä. (Senioritoiminta) (224 211 €) | Ak 7: Korjausneuvontaan ja kotiturvallisuuden edistämiseen ikääntyneiden ihmisten kotona asumisen tukemiseksi sekä hyvinvoinnin ja toimintakykyisyyden vahvistamiseksi (203 916 €) | Ak 2322: Seniorien digiopastustoiminnan ja digiosallisuuden tukemiseen ja kehittämiseen koordinaation, verkostotyön, materiaalituotannon, vertaistuellisen etäopastuspalvelun, webinaarien ja vaikuttamistoiminnan keinoin (SeniorSurf) (153 944 €)</t>
         </is>
       </c>
     </row>
@@ -4149,7 +5211,7 @@
       </c>
       <c r="I29" t="inlineStr" s="0">
         <is>
-          <t>B 1: Pelastusalushankintojen  korjauksien  huoltojen ja varustehankintojen menoihin (973 192 €) | Ak 2: Meri- ja järvipelastustehtävissä toimivien vapaaehtoisten pätevyyden varmistamiseen  osaamisen lisäämiseen sekä miehistöjen toimintakyvyn ylläpitämiseen (262 500 €) | Ak 3: Jäsenjärjestöille kohdistettaviin avustuksiin (45 000 €)</t>
+          <t>B 1: Pelastusalushankintojen, korjauksien, huoltojen ja varustehankintojen menoihin (973 192 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (390 600 €) | Ak 2: Meri- ja järvipelastustehtävissä toimivien vapaaehtoisten pätevyyden varmistamiseen, osaamisen lisäämiseen sekä miehistöjen toimintakyvyn ylläpitämiseen (262 500 €) | Ak 3: Jäsenjärjestöille kohdistettaviin avustuksiin (45 000 €)</t>
         </is>
       </c>
     </row>
@@ -4182,7 +5244,7 @@
       </c>
       <c r="I30" t="inlineStr" s="0">
         <is>
-          <t>Ak 4: Tavoitteellisiin  vertaistuellisiin ja psykososiaalista hyvinvointia vahvistaviin kursseihin MS-tautia  essentiaalista vapinaa ja neurologisia harvinaissairauksia sairastaville sekä heidän läheisilleen. Toteutusmuotoina avomuotoiset kurssit  yöpymiskurssit ja verkkokurssit. Yhteistyökursseille voivat osallistua myös  yhteistyöjärjestöjen kohderyhmiin kuuluvia henkilöitä ja heidän läheisiään. (569 834 €) | Ak 14: MS-tautia  essentiaalista vapinaa  neurologisia harvinaissairauksia  Parkinsonin tautia  harvinaisia liikehäiriösairauksia sairastavien  aivovammautuneiden ja aivoverenkiertohäiriön sairastaneiden sekä heidän läheistensä tukemiseen neuvontatoiminnalla (167 769 €) | Ak 1619: Jäsenjärjestöille kohdistettaviin avustuksiin (25 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (640 467 €) | Ak 4: Tavoitteellisiin, vertaistuellisiin ja psykososiaalista hyvinvointia vahvistaviin kursseihin MS-tautia, essentiaalista vapinaa ja neurologisia harvinaissairauksia sairastaville sekä heidän läheisilleen. Toteutusmuotoina avomuotoiset kurssit, yöpymiskurssit ja verkkokurssit. Yhteistyökursseille voivat osallistua myös  yhteistyöjärjestöjen kohderyhmiin kuuluvia henkilöitä ja heidän läheisiään. (569 834 €) | Ak 14: MS-tautia, essentiaalista vapinaa, neurologisia harvinaissairauksia, Parkinsonin tautia, harvinaisia liikehäiriösairauksia sairastavien, aivovammautuneiden ja aivoverenkiertohäiriön sairastaneiden sekä heidän läheistensä tukemiseen neuvontatoiminnalla (167 769 €) | Ak 8: MS-tautia, harvinaista neurologista tai liikehäiriösairautta sairastavien, aivovamman saaneiden tai aivoverenkiertohäiriön sairastaneiden työllistymisen ja työssä pysymisen edellytysten edistämiseen. Toimintana yksilöllinen ohjaus ja neuvonta, luennot, ryhmämuotoiset tiedolliset ja vertaistuelliset tilaisuudet, viestintä ja vaikuttamistyö. (157 780 €) | Ak 6: Harvinaisia neurologisia sairauksia sairastavien järjestö-, tiedotus- ja tukitoimintaan (84 200 €) | Ak 1619: Jäsenjärjestöille kohdistettaviin avustuksiin (25 000 €)</t>
         </is>
       </c>
     </row>
@@ -4215,7 +5277,7 @@
       </c>
       <c r="I31" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Taloudellisesti haavoittuvassa elämäntilanteessa olevien ihmisten ylivelkaantumisen ehkäisemiseen  velkakierteen katkaisemiseen ja talouden tasapainottamiseen takaus- ja pienluototustoiminnalla sekä puhelimitse ja internetissä toteutettavalla anonyymillä ja valtakunnallisella velkaneuvonnalla (943 572 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (451 143 €) | Ak 2: Ammattilaisten  vapaaehtoisten ja vertaisten osaamisen lisäämiseen ja kouluttamiseen talous- ja velka-asioissa (TalousTsemppari-toiminta) (195 143 €)</t>
+          <t>Ak 3: Taloudellisesti haavoittuvassa elämäntilanteessa olevien ihmisten ylivelkaantumisen ehkäisemiseen, velkakierteen katkaisemiseen ja talouden tasapainottamiseen takaus- ja pienluototustoiminnalla sekä puhelimitse ja internetissä toteutettavalla anonyymillä ja valtakunnallisella velkaneuvonnalla (943 572 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (451 143 €) | Ak 2: Ammattilaisten, vapaaehtoisten ja vertaisten osaamisen lisäämiseen ja kouluttamiseen talous- ja velka-asioissa (TalousTsemppari-toiminta) (195 143 €)</t>
         </is>
       </c>
     </row>
@@ -4248,7 +5310,7 @@
       </c>
       <c r="I32" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Päihde- ja mielenterveysongelmaisten sekä syrjäytymisvaarassa olevien voimavarojen ja sosiaalisten verkostojen vahvistamiseen CABLE-yhteisövalmennuksen ja vapaaehtoistoiminnan keinoin (D-asemat Kallio ja Kontula) (360 635 €) | Ak 2233: Vaikeasti työllistyvien 16–29-vuotiaiden nuorten yksilöllisen urapolun rakentamiseen ja ohjaamiseen työelämään tai opiskelemaan (Vamos Urapalvelut) (169 488 €) | Ak 11077: Ulkomaalaisten vankien tukemiseen heidän vapautuessaan pitkäkestoisen yksilövalmennuksen sekä lyhytkestoisen neuvonnan ja ohjauksen avulla (163 146 €)</t>
+          <t>Ak 3: Päihde- ja mielenterveysongelmaisten sekä syrjäytymisvaarassa olevien voimavarojen ja sosiaalisten verkostojen vahvistamiseen CABLE-yhteisövalmennuksen ja vapaaehtoistoiminnan keinoin (D-asemat Kallio ja Kontula) (360 635 €) | Ak 1: Kidutuksen uhrien ja pakolaisuuden traumatisoimien aikuisten psykiatriseen arviointi-, hoito- ja kuntoutustoimintaan sekä valtakunnalliseen sote-ammattilaisten, sekä viranomaisten neuvontaan, koulutukseen ja konsultointiin (197 000 €) | Ak 2233: Vaikeasti työllistyvien 16–29-vuotiaiden nuorten yksilöllisen urapolun rakentamiseen ja ohjaamiseen työelämään tai opiskelemaan (Vamos Urapalvelut) (169 488 €) | Ak 11077: Ulkomaalaisten vankien tukemiseen heidän vapautuessaan pitkäkestoisen yksilövalmennuksen sekä lyhytkestoisen neuvonnan ja ohjauksen avulla (163 146 €) | Ak 11014: Haavoittuvassa asemassa olevien aikuisten tukemiseen osallistavalla ja yhteisöjä kehittävällä yhteisö- ja vapaaehtoistoiminnalla Helsingin Kaarelassa (160 518 €) | Ak 11202: Alaikäisenä ilman huoltajaa Suomeen tulleiden nuorten kotoutumisen edistämiseen kummiperhetoiminnan avulla (151 115 €) | Ak 8711: Erityistä tukea tarvitsevien nuorten tukemiseen osallistavan kohtaamispaikkatoiminnan ja yksilöllisen tuen keinoin Jyväskylän alueella. (149 639 €) | Ak 1324: Nuorten syrjäytymistä ehkäisevän yhteisöllisen Amigo-mentorointiohjelman toteuttamiseen ja levittämiseen (112 495 €) | Ak 9877: Suomessa paperittomina oleskelevien toimintakyvyn ja elämänhallinnan tukemiseen etsivän työn, yhteisötoiminnan ja verkostoitumisen avulla (105 000 €)</t>
         </is>
       </c>
     </row>
@@ -4281,8 +5343,7 @@
       </c>
       <c r="I33" t="inlineStr" s="0">
         <is>
-          <t>Ak 5: För att stöda familjer i att klara vardagens utmaningar med barn som har neuropsykiatriska symtom eller annars uppvisar utmanande beteende  genom individ- och gruppverksamhet samt informationsåtgärder /
-Perheiden tukemiseen arjen haasteista selviämiseen neuropsykiatrisesti oireilevien tai muuten haastavasti käyttäytyvien lasten kanssa yksilö- ja ryhmätoiminnan sekä tiedottamisen keinoin (Neuropsykiatriska tjänster/Neuropsykiatriset palvelut) (311 000 €) | Ak 10061: Psykososiaalisesti vahvistavaan ryhmätoimintaan ja yksilölliseen tukeen pääkaupunkiseudulla 16-25-vuotiaille lastensuojelun sijoitetuille ja jälkihuollon piirissä oleville sekä nuorille  joiden jälkihoito-oikeus on päättynyt. Toiminnassa tarjotaan lisäksi nuorten kanssa toimiville ammattilaisille neuvontaa ja koulutusta. (Oman elämäni supertähti) (173 093 €) | Ak 2: Neuropsykiatrisia haasteita kokevien ja muuten erityistarpeisten lasten sosiaalisten valmiuksien sekä itsetunnon vahvistamiseen Helsingissä järjestettävällä leiritoiminnalla (43 050 €)</t>
+          <t>Ak 5: För att stöda familjer i att klara vardagens utmaningar med barn som har neuropsykiatriska symtom eller annars uppvisar utmanande beteende, genom individ- och gruppverksamhet samt informationsåtgärder / Perheiden tukemiseen arjen haasteista selviämiseen neuropsykiatrisesti oireilevien tai muuten haastavasti käyttäytyvien lasten kanssa yksilö- ja ryhmätoiminnan sekä tiedottamisen keinoin (Neuropsykiatriska tjänster/Neuropsykiatriset palvelut) (311 000 €) | Ak 11208: För att förebygga ensamhet, stärka sociala färdigheter och öka delaktighet genom lågtröskelverksamhet bland svenskspråkiga flickor i åldern 10–19 år, som är ensamma, har svag självkänsla, utmaningar i sociala situationer eller svårigheter hemma. Verksamheten genomförs i Nyland. (Tjejvillan) (288 750 €) | Ay 1: Som allmänt understöd för understödstagarens allmännyttiga verksamhet (246 496 €) | Ak 12297: För stöd med låg tröskel för familjer med barn med neuropsykiatriska störningar eller symtom genom gruppverksamhet och individuellt stöd samt genom information i Österbotten (Nepsy Vasa) /  Matalan kynnyksen ryhmämuotoiseen ja yksilölliseen tukeen ja perheille, joiden lapsilla on neuropsykiatrisia häiriöitä tai oireita, sekä tiedottamiseen Pohjanmaalla (Nepsy Vaasa) (232 836 €) | Ak 10061: Psykososiaalisesti vahvistavaan ryhmätoimintaan ja yksilölliseen tukeen pääkaupunkiseudulla 16-25-vuotiaille lastensuojelun sijoitetuille ja jälkihuollon piirissä oleville sekä nuorille, joiden jälkihoito-oikeus on päättynyt. Toiminnassa tarjotaan lisäksi nuorten kanssa toimiville ammattilaisille neuvontaa ja koulutusta. (Oman elämäni supertähti) (173 093 €) | Ak 4347: För att stöda svensk- och flerspråkiga skilsmässofamiljer, ombildade familjer samt föräldrar som upplever utmaningar i sitt parförhållande mot en mer fungerande vardag och ett stärkt föräldraskap genom gruppverksamhet och samtalsstöd samt genom att dela kunskap med professionella (150 150 €) | Ak 4: För att stöda familjer där föräldraskapet upplevs som belastande genom att ordna målinriktad gruppverksamhet för familjer i Raseborg och på andra orter i det svenskpråkiga Finland (61 950 €) | Ak 1905: För att stärka barns och ungas välmående, öka trivseln och främja psykiskt välbefinnande i skolvardagen genom att ordna gruppverksamhet (Vi i klassen, #brafiilis och Next Level) (47 900 €) | Ak 2: Neuropsykiatrisia haasteita kokevien ja muuten erityistarpeisten lasten sosiaalisten valmiuksien sekä itsetunnon vahvistamiseen Helsingissä järjestettävällä leiritoiminnalla (43 050 €)</t>
         </is>
       </c>
     </row>
@@ -4315,7 +5376,7 @@
       </c>
       <c r="I34" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Sosiaaliseen lomatoimintaan vähävaraisille ja erityisen tuen tarpeisille lapsiperheille  työikäisille ja iäkkäille sekä erityisryhmille. (1 538 699 €)</t>
+          <t>Ak 1: Sosiaaliseen lomatoimintaan vähävaraisille ja erityisen tuen tarpeisille lapsiperheille, työikäisille ja iäkkäille sekä erityisryhmille. (1 538 699 €)</t>
         </is>
       </c>
     </row>
@@ -4348,7 +5409,7 @@
       </c>
       <c r="I35" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Rikosseuraamusasiakkaiden ja heidän omaistensa tiedon lisäämiseen oikeuksistaan neuvonnalla  vankilainfoilla ja vaikuttamistyöllä (Kriminaaliasiamiestoiminta) (235 450 €) | Ak 7: Rikostaustaisten läheis- ja perhetyön koordinointiin sekä vankien ja heidän omaistensa tukemiseen yksilöohjauksella sekä vertaisryhmä- ja leiritoiminnalla (207 868 €) | Ak 5: Asunnottomana vankilasta vapautuvien ja muiden rikosseuraamustaustaisten henkilöiden asunnottomuuden ja uusintarikollisuuden vähentämiseen asumispalveluohjauksen sekä Vapautuvien Asumisen Tuen (VAT) -verkoston avulla (113 050 €)</t>
+          <t>Ay 4: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (388 997 €) | Ak 3: Rikostaustaisten uusintarikollisuuden ehkäisyyn ja elämänhallinnan tukemiseen sekä päihde- ja mielenterveyskuntoutujien elämänhallinnan tukemiseen. Toimintamuotoina vertaistukitoiminnot päivällä sekä ilta- ja viikonloppuaikoina, yksilöllinen tuki, ryhmätoiminta sekä vankilainfot (Vertaistoiminnot Redis, Raittila ja Nuorten toiminta) (347 164 €) | Ak 1: Rikosseuraamusasiakkaiden ja heidän omaistensa tiedon lisäämiseen oikeuksistaan neuvonnalla, vankilainfoilla ja vaikuttamistyöllä (Kriminaaliasiamiestoiminta) (235 450 €) | Ak 7: Rikostaustaisten läheis- ja perhetyön koordinointiin sekä vankien ja heidän omaistensa tukemiseen yksilöohjauksella sekä vertaisryhmä- ja leiritoiminnalla (207 868 €) | Ak 5: Asunnottomana vankilasta vapautuvien ja muiden rikosseuraamustaustaisten henkilöiden asunnottomuuden ja uusintarikollisuuden vähentämiseen asumispalveluohjauksen sekä Vapautuvien Asumisen Tuen (VAT) -verkoston avulla (113 050 €) | Ak 9765: Vankilasta vapautuvien rikostaustaisten naisten päihteistä ja rikollisuudesta irtaantumisen tukeen naiserityiseen asiantuntemukseen ja vertaisuuteen perustuvan tuen sekä kuntoutumispolun rakentamisen avulla (110 000 €) | Ak 8: Rikostaustaisten oppimisvalmennustyöhön koulutuksen, verkostokoordinoinnin sekä yksilö- ja ryhmämuotoisen toiminnan avulla (Oppimisvalmennustyön koordinaatio) (68 000 €)</t>
         </is>
       </c>
     </row>
@@ -4381,7 +5442,7 @@
       </c>
       <c r="I36" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (690 910 €) | Ak 2: Toimijuuden  hyvinvoinnin ja myönteisen minäkuvan vahvistaminen tavoitteellisen ryhmätoiminnan keinoin. Kohderyhmänä ovat henkilöt  joilla itsellään tai joiden omaisella tai läheisellä on cp-vamma  mmc  hydrokefalia tai normaalipaineinen hydrokefalia. Toimintamuotoina ovat kurssit  neuvonta  ohjaus (kasvokkain  puhelimitse  verkossa)  alustukset  verkostotyöskentely sekä ohjaavan materiaalin tuottaminen ja viestintä. (528 650 €) | Ak 7: Henkilöiden  joilla on cp-vamma  meningomyeloseele (mmc)  hydrokefalia tai normaalipaineinen hydrokefalia sekä heidän läheisten tukemiseen  osallisuuden ja hyvinvoinnin vahvistamiseen vertaistukitoiminnan  neuvonnan  tiedon jakamisen sekä yhteiskunnallisen vaikuttamisen keinoin (172 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (690 910 €) | Ak 2: Toimijuuden, hyvinvoinnin ja myönteisen minäkuvan vahvistaminen tavoitteellisen ryhmätoiminnan keinoin. Kohderyhmänä ovat henkilöt, joilla itsellään tai joiden omaisella tai läheisellä on cp-vamma, mmc, hydrokefalia tai normaalipaineinen hydrokefalia. Toimintamuotoina ovat kurssit, neuvonta, ohjaus (kasvokkain, puhelimitse, verkossa), alustukset, verkostotyöskentely sekä ohjaavan materiaalin tuottaminen ja viestintä. (528 650 €) | Ak 7: Henkilöiden, joilla on cp-vamma, meningomyeloseele (mmc), hydrokefalia tai normaalipaineinen hydrokefalia sekä heidän läheisten tukemiseen, osallisuuden ja hyvinvoinnin vahvistamiseen vertaistukitoiminnan, neuvonnan, tiedon jakamisen sekä yhteiskunnallisen vaikuttamisen keinoin (172 000 €) | Ak 6: Perhelomitustoimintaan vaikeasti vammaisten lasten vanhempien arjen tilapäiseksi helpottamiseksi (ei lakisääteisen omaishoidon vapaan tai vammaispalvelulain mukaisen lyhytaikaisen huolenpidon järjestämiseen) (40 000 €) | Ak 11: Jäsenjärjestöille kohdistettaviin avustuksiin (23 360 €)</t>
         </is>
       </c>
     </row>
@@ -4414,7 +5475,7 @@
       </c>
       <c r="I37" t="inlineStr" s="0">
         <is>
-          <t>Ak 1621: Aisti- tai toimintakyvyltään heikentyneiden ikääntyneiden hyvinvoinnin edistämiseen musiikkisisältöisen ja muun toimintakykyä tukevan vapaaehtoistoiminnan avulla sekä vapaaehtoisten osaamisen vahvistamiseen (277 000 €) | Ak 3: Yli 50-vuotiaiden leskeytyneiden ja avio-/avoeron kokeneiden ammatillisesti ohjattuun vertaistuelliseen ryhmätoimintaan sekä isovanhemmuuden tukemiseen eroperheissä (242 550 €) | Ak 7: Osteopenian ja osteoporoosin ennaltaehkäisyyn ja luuston terveyttä edistävän liikunnan lisäämiseen vertaisohjaajien koulutuksen avulla (Murtumatta mukana - Spänst i benen) (110 250 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (713 098 €) | Ak 1621: Aisti- tai toimintakyvyltään heikentyneiden ikääntyneiden hyvinvoinnin edistämiseen musiikkisisältöisen ja muun toimintakykyä tukevan vapaaehtoistoiminnan avulla sekä vapaaehtoisten osaamisen vahvistamiseen (277 000 €) | Ak 3: Yli 50-vuotiaiden leskeytyneiden ja avio-/avoeron kokeneiden ammatillisesti ohjattuun vertaistuelliseen ryhmätoimintaan sekä isovanhemmuuden tukemiseen eroperheissä (242 550 €) | Ak 7: Osteopenian ja osteoporoosin ennaltaehkäisyyn ja luuston terveyttä edistävän liikunnan lisäämiseen vertaisohjaajien koulutuksen avulla (Murtumatta mukana - Spänst i benen) (110 250 €) | Ak 1029: Jäsenjärjestöille kohdistettaviin avustuksiin (100 000 €)</t>
         </is>
       </c>
     </row>
@@ -4447,7 +5508,7 @@
       </c>
       <c r="I38" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (835 506 €) | Ak 8: Aikuisten nikotiinituotteiden käytön lopettamisen tukeen verkko-  puhelin- ja vertaistuen avulla (120 000 €) | Ak 5: Harvinaista hengityssairautta sairastavien sekä heidän läheistensä hyvinvoinnin tukemiseen  neuvontaan  vertaistuki- ja vapaaehtoistoimintaan sekä ammattilaisten tiedon lisäämiseen (117 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (835 506 €) | Ak 6: Sisäilmaneuvontaan, sisäilmaongelmien ennaltaehkäisemiseen ja vähentämiseen sekä sisäilmasta sairastuneiden tukemiseen vertais- ja vaikuttamistoiminnalla (297 000 €) | Ak 8: Aikuisten nikotiinituotteiden käytön lopettamisen tukeen verkko-, puhelin- ja vertaistuen avulla (120 000 €) | Ak 5: Harvinaista hengityssairautta sairastavien sekä heidän läheistensä hyvinvoinnin tukemiseen, neuvontaan, vertaistuki- ja vapaaehtoistoimintaan sekä ammattilaisten tiedon lisäämiseen (117 000 €) | Ak 1419: Jäsenjärjestöille kohdistettaviin avustuksiin (50 000 €)</t>
         </is>
       </c>
     </row>
@@ -4480,7 +5541,7 @@
       </c>
       <c r="I39" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (770 228 €) | Ak 6: Reumaa sekä tuki- ja liikuntaelinsairauksia sairastavien kurssitoimintaan elämänhallinnan  hyvinvoinnin ja terveyden tukemiseksi vertaistuellisen ryhmätoiminnan avulla (154 000 €) | Ak 11: Harvinaista reuma- ja tule-sairautta sairastavien tiedon  verkostoitumisen ja vertaistuen lisäämiseen (16 813 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (770 228 €) | Ak 6: Reumaa sekä tuki- ja liikuntaelinsairauksia sairastavien kurssitoimintaan elämänhallinnan, hyvinvoinnin ja terveyden tukemiseksi vertaistuellisen ryhmätoiminnan avulla (154 000 €) | Ak 18: Valtakunnalliseen järjestöjen kokemustoimijuuden verkostotoimintaan (149 100 €) | Ak 8: Jäsenjärjestöille kohdistettaviin avustuksiin (143 850 €) | Ak 17: Harvinaisiin sairaus- tai vammaryhmiin kuuluvien ja heidän läheistensä aseman parantamiseen, tiedon välittämiseen sekä vaikuttamistyöhön eri harvinaisryhmien hyväksi (139 000 €) | Ak 11: Harvinaista reuma- ja tule-sairautta sairastavien tiedon, verkostoitumisen ja vertaistuen lisäämiseen (16 813 €)</t>
         </is>
       </c>
     </row>
@@ -4513,7 +5574,7 @@
       </c>
       <c r="I40" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Seksityössä mukana olevien neuvontaan  matalan kynnyksen tukitoimintaan  yhteisölliseen toimintaan ja etsivään työhön pääkaupunkiseudulla. (438 563 €) | Ay 2: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (373 043 €) | Ak 5678: Seksityössä mukana olevien neuvontaan  matalan kynnyksen tukitoimintaan  yhteisölliseen toimintaan ja etsivään työhön Turun seudulla. (212 710 €)</t>
+          <t>Ak 1: Seksityössä mukana olevien neuvontaan, matalan kynnyksen tukitoimintaan, yhteisölliseen toimintaan ja etsivään työhön pääkaupunkiseudulla. (438 563 €) | Ay 2: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (373 043 €) | Ak 5678: Seksityössä mukana olevien neuvontaan, matalan kynnyksen tukitoimintaan, yhteisölliseen toimintaan ja etsivään työhön Turun seudulla. (212 710 €) | Ak 3: Seksityössä mukana olevien neuvontaan, matalan kynnyksen tukitoimintaan, yhteisölliseen toimintaan ja etsivään työhön Pirkanmaalla. (195 143 €) | Ak 4: Kaupallisen tai vastikkeellisen seksin yhteydessä väkivallan, kuten ihmiskaupan uhriksi joutuneiden ihmisten tunnistamis- ja tukityöhön sekä tiedontuotanto-, verkosto- ja vaikuttamistoimintaan (VV-työ). (147 128 €)</t>
         </is>
       </c>
     </row>
@@ -4546,7 +5607,7 @@
       </c>
       <c r="I41" t="inlineStr" s="0">
         <is>
-          <t>Ak 5: Vanhemmuuden ja elämänhallinnan tukemiseen erotilanteessa oleville miehille yksilö- ja ryhmämuotoisen auttamisen  tukihenkilötoiminnan sekä puhelin- ja verkkoauttamisen keinoin (346 185 €) | Ak 2: Lähisuhdeväkivallan ehkäisyyn sekä miesten toteuttaman lähisuhdeväkivallan käytön lopettamiseen yksilö-  pari- ja ryhmämuotoisen työskentelyn avulla Uudellamaalla ja Pohjois-Savossa (Lyömätön Linja) (345 394 €) | Ak 6066: Maahan muuttaneiden miesten työelämävalmiuksien ja työllistymisen edistämiseen sekä kaksisuuntaisen kotoutumisen tukemiseen mentori-  tukihenkilö- ja suomenkielisen keskusteluryhmätoiminnan avulla Helsingissä  Turussa ja Tampereella (Vieraasta Veljeksi) (87 000 €)</t>
+          <t>Ak 5: Vanhemmuuden ja elämänhallinnan tukemiseen erotilanteessa oleville miehille yksilö- ja ryhmämuotoisen auttamisen, tukihenkilötoiminnan sekä puhelin- ja verkkoauttamisen keinoin (346 185 €) | Ak 2: Lähisuhdeväkivallan ehkäisyyn sekä miesten toteuttaman lähisuhdeväkivallan käytön lopettamiseen yksilö-, pari- ja ryhmämuotoisen työskentelyn avulla Uudellamaalla ja Pohjois-Savossa (Lyömätön Linja) (345 394 €) | Ay 6: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (285 768 €) | Ak 10258: Miesten toimintakyvyn ja hyvinvoinnin tukemiseen yksilöllisen ja ryhmämuotoisen tuen sekä vertaisauttamisen avulla, erityiskohderyhmänä isät pikkulapsiperheissä, joissa toisella tai molemmilla vanhemmista on masennusta tai masennustyyppistä oireilua (MASI - Masennusoireisten perheiden isien tuki) (152 250 €) | Ak 6021: Väkivaltaa kokeneiden miesten väkivallankokemukseen liittyvien haitallisten psyykkisten seurauksien vähentämiseen yksilötapaamisten, puhelin-, sähköposti- ja verkkoauttamisen, vertaisryhmätoiminnan sekä viestinnän keinoin (Väkivaltaa Kokeneet Miehet) (148 838 €) | Ak 6066: Maahan muuttaneiden miesten työelämävalmiuksien ja työllistymisen edistämiseen sekä kaksisuuntaisen kotoutumisen tukemiseen mentori-, tukihenkilö- ja suomenkielisen keskusteluryhmätoiminnan avulla Helsingissä, Turussa ja Tampereella (Vieraasta Veljeksi) (87 000 €)</t>
         </is>
       </c>
     </row>
@@ -4579,7 +5640,7 @@
       </c>
       <c r="I42" t="inlineStr" s="0">
         <is>
-          <t>Ay 7: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (296 640 €) | Ak 10300: Työttömien ja työttömyysuhan alla olevien maahan muuttaneiden ja pakolaistaustaisten henkilöiden työelämäosallisuuden lisäämiseen ja työelämäpolun tukemiseen valmennuksien  yksilöllisen ohjauksen ja vapaaehtoispohjaisen mentoroinnin sekä työnantajayhteistyön avulla (147 000 €) | Ak 1336: Maahan muuttaneiden arjen kielitaidon  osallisuuden ja toimintavalmiuksien vahvistamiseen sekä kaksisuuntaisen kotoutumisen edistämiseen vapaaehtoisten vetämien kieliryhmien ja asiointituen avulla (132 000 €)</t>
+          <t>Ay 7: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (296 640 €) | Ak 4285: Haavoittuvassa asemassa olevien maahan muuttaneiden nuorten aikuisten toimintakyvyn vahvistamiseen ja palveluihin ohjautumiseen ja kiinnittymiseen sekä syrjäytymisen ehkäisyyn neuvonnalla, yksilöllisellä tuella ja palveluohjauksella sekä ammattilaisten osaamisen lisäämisellä (Kurvi) (277 000 €) | Ak 4: Maahanmuuttaneiden perustamien ja monikulttuuristen yhdistysten toimintavalmiuksien tukemiseen sekä yhdistystoimijoiden osaamisen, voimavarojen ja vertaisuuden lisäämiseen koulutusten, neuvonnan ja työpajojen avulla (Järjestöhautomo) (235 000 €) | Ak 12034: Maahan muuttaneiden työperäisen hyväksikäytön ennaltaehkäisyyn ja vähentämiseen etsivän työn, ohjauksen ja neuvonnan, tiedottamisen, koulutusten sekä sidosryhmäyhteistyön avulla (Reilu työelämä) (203 000 €) | Ak 10300: Työttömien ja työttömyysuhan alla olevien maahan muuttaneiden ja pakolaistaustaisten henkilöiden työelämäosallisuuden lisäämiseen ja työelämäpolun tukemiseen valmennuksien, yksilöllisen ohjauksen ja vapaaehtoispohjaisen mentoroinnin sekä työnantajayhteistyön avulla (147 000 €) | Ak 1336: Maahan muuttaneiden arjen kielitaidon, osallisuuden ja toimintavalmiuksien vahvistamiseen sekä kaksisuuntaisen kotoutumisen edistämiseen vapaaehtoisten vetämien kieliryhmien ja asiointituen avulla (132 000 €) | Ak 3: Maahan muuttaneiden hyvinvoinnin edistämiseen ja aktiivisen kansalaisuuden vahvistamiseen vertaistoimintaa ja yhteiskunnan vastaanottavuutta edistämällä.  Toimintamuotoina VeTo-verkoston koordinointi ja sen jäsenorganisaatioiden osaamisen kehittäminen ja vertaisohjaajien koulutukset sekä ohjaajien ja organisaatioiden yhteistyöverkostojen vahvistaminen  (Kasvokkain) (65 000 €)</t>
         </is>
       </c>
     </row>
@@ -4612,11 +5673,7 @@
       </c>
       <c r="I43" t="inlineStr" s="0">
         <is>
-          <t>Ak 10: Ammatillisesti ohjattuun ja vertaisuutta hyödyntävään ryhmämuotoiseen kurssitoimintaan avo- tai internaattimuotoisena sekä verkko- ja puhelinauttamista hyödyntäen
-- diabetesta sairastaville ja erityisryhmille
-- eläkeläisille läheisineen
-- kehitysvammaisille diabetesta sairastaville lapsille vanhempineen
-- diabetesta ja mielenterveyden häiriötä sairastaville (350 889 €) | Ak 4370: Diabetesta sairastavien verkkomuotoiseen omahoidon tukemiseen (Diabetekseen sairastuneen tuki) (123 354 €) | Ak 12: Jäsenjärjestöille kohdistettaviin avustuksiin (63 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (803 250 €) | Ak 10: Ammatillisesti ohjattuun ja vertaisuutta hyödyntävään ryhmämuotoiseen kurssitoimintaan avo- tai internaattimuotoisena sekä verkko- ja puhelinauttamista hyödyntäen - diabetesta sairastaville ja erityisryhmille - eläkeläisille läheisineen - kehitysvammaisille diabetesta sairastaville lapsille vanhempineen - diabetesta ja mielenterveyden häiriötä sairastaville (350 889 €) | Ak 4370: Diabetesta sairastavien verkkomuotoiseen omahoidon tukemiseen (Diabetekseen sairastuneen tuki) (123 354 €) | Ak 12: Jäsenjärjestöille kohdistettaviin avustuksiin (63 000 €)</t>
         </is>
       </c>
     </row>
@@ -4649,9 +5706,7 @@
       </c>
       <c r="I44" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (755 948 €) | Ak 1247: Toimintakyvyltään jossain määrin heikentyneiden  kotona asuvien ikäihmisten toimintakyvyn  osallisuuden ja itsenäisen selviytymisen edistämiseen terveysliikunnan keinoin (Voimaa vanhuuteen - hyvien terveysliikunnan toimintakäytäntöjen juurrutus) (389 745 €) | Ak 7385: Kotona asuvien iäkkäimpien asukkaiden osallisuuden vahvistamiseen sekä yhdessä oloon ja liikkumisen lisäämiseen kodin läheisyydessä. 
-Taloyhtiöissä ja naapurustoissa toimintaa järjestävien vapaaehtoisten valmentamiseen.
-Iäkkäiden hyvinvointia tukevan yhteistyön käynnistämiseen ja lisäämiseen kaupungin eri sektoreiden sekä paikallisten yhdistysten ja taloyhtiöiden kesken. (Yhdessä kotikulmilla) (186 380 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (755 948 €) | Ak 1247: Toimintakyvyltään jossain määrin heikentyneiden, kotona asuvien ikäihmisten toimintakyvyn, osallisuuden ja itsenäisen selviytymisen edistämiseen terveysliikunnan keinoin (Voimaa vanhuuteen - hyvien terveysliikunnan toimintakäytäntöjen juurrutus) (389 745 €) | Ak 7385: Kotona asuvien iäkkäimpien asukkaiden osallisuuden vahvistamiseen sekä yhdessä oloon ja liikkumisen lisäämiseen kodin läheisyydessä.  Taloyhtiöissä ja naapurustoissa toimintaa järjestävien vapaaehtoisten valmentamiseen. Iäkkäiden hyvinvointia tukevan yhteistyön käynnistämiseen ja lisäämiseen kaupungin eri sektoreiden sekä paikallisten yhdistysten ja taloyhtiöiden kesken. (Yhdessä kotikulmilla) (186 380 €)</t>
         </is>
       </c>
     </row>
@@ -4684,8 +5739,7 @@
       </c>
       <c r="I45" t="inlineStr" s="0">
         <is>
-          <t>Ak 12468: Nuorten toistuvan rikos- ja päihdekäyttäytymisen pysäyttämiseen kokemusasiantuntijoiden tuottamilla tukitoiminnoilla yhteistyössä perheiden  viranomaisten  lastensuojelun  lastensuojelulaitosten  rikosseuraamuslaitoksen ja järjestöjen kanssa (343 000 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (257 040 €) | Ak 10375: Vakaviin rikoksiin syyllistyneiden ja päihteitä käyttävien alle 20-vuotiaiden nuorten  heidän ystäviensä ja läheistensä osallisuuden vahvistamiseen yksilö- ja perhetyöllä sekä leiritoiminnan avulla yhteistyössä viranomaisten kanssa Helsingissä. 
-(Nuorten rikoskierteisiin puuttuva Pasila-toiminta) (185 000 €)</t>
+          <t>Ak 12468: Nuorten toistuvan rikos- ja päihdekäyttäytymisen pysäyttämiseen kokemusasiantuntijoiden tuottamilla tukitoiminnoilla yhteistyössä perheiden, viranomaisten, lastensuojelun, lastensuojelulaitosten, rikosseuraamuslaitoksen ja järjestöjen kanssa (343 000 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (257 040 €) | Ak 4: Vakavasti oireilevien nuorten tukemiseen liikkuvalla toiminnalla pääkaupunkiseudulla ja Uudenmaan alueella (Walkers-bussi-toiminta) (231 000 €) | Ak 10375: Vakaviin rikoksiin syyllistyneiden ja päihteitä käyttävien alle 20-vuotiaiden nuorten, heidän ystäviensä ja läheistensä osallisuuden vahvistamiseen yksilö- ja perhetyöllä sekä leiritoiminnan avulla yhteistyössä viranomaisten kanssa Helsingissä.  (Nuorten rikoskierteisiin puuttuva Pasila-toiminta) (185 000 €) | Ak 4287: Julkisissa ja puolijulkisissa tiloissa oleilevien nuorten turvallisen vapaa-ajanvieton mahdollistamiseen, sekä riskialttiissa elämäntilanteessa olevien nuorten tunnistamiseen monitoimijaisen nuorisotyön avulla   (Löytävä nuorisotyö) (159 000 €) | Ak 7305: Rikosoireilevia ja rikoksen uhriksi joutuneita nuoria tukevaan katusovittelutoimintaan Uudellamaalla  (Katusovittelutoiminta) (134 000 €)</t>
         </is>
       </c>
     </row>
@@ -4718,7 +5772,7 @@
       </c>
       <c r="I46" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Erityistä ja monimuotoista tukea tarvitsevien perheiden hyvinvoinnin vahvistamiseen ryhmätoiminnalla  yksilöllisellä tuella  yhteistyöllä ja tiedottamisella (Perheiden tukena yhteisöissä) (450 000 €) | Ak 20: Kehitysvamman tai muun syyn vuoksi tukea tarvitsevien ihmisten itsemääräämisoikeuden toteutumiseen  mielipiteiden ja toiveiden ilmaisussa rohkaistumiseen sekä valintojen tekemisessä tukemiseen. (Osallisuuden tukena) (380 000 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (297 600 €)</t>
+          <t>Ak 2: Erityistä ja monimuotoista tukea tarvitsevien perheiden hyvinvoinnin vahvistamiseen ryhmätoiminnalla, yksilöllisellä tuella, yhteistyöllä ja tiedottamisella (Perheiden tukena yhteisöissä) (450 000 €) | Ak 20: Kehitysvamman tai muun syyn vuoksi tukea tarvitsevien ihmisten itsemääräämisoikeuden toteutumiseen, mielipiteiden ja toiveiden ilmaisussa rohkaistumiseen sekä valintojen tekemisessä tukemiseen. (Osallisuuden tukena) (380 000 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (297 600 €) | Ak 3900: Vammaisten ihmisten yhdenvertaisuuden, osallisuuden ja liikkuvuuden edistämiseen Suomessa EU:n Vammaiskorttia ylläpitämällä ja kehittämällä (Vammaiskortti) (163 800 €)</t>
         </is>
       </c>
     </row>
@@ -4751,7 +5805,7 @@
       </c>
       <c r="I47" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (346 080 €) | Ak 13: Kuurosokeiden ja kuulonäkövammaisten itsenäisen arjen asioinnin ja sosiaalisen kanssakäymisen tukemiseen tieto- ja viestintäteknologian ohjaus-  tuki- ja koulutustoiminnan avulla (270 375 €) | Ak 15: Kuurosokeiden  kuulonäkövammaisten sekä heidän lähipiirinsä ja verkostonsa kommunikaatiotaitojen ja vuorovaikutuksen lisäämiseen ohjauksen  koulutuksen ja kommunikaatiomateriaalituotannon avulla (140 175 €)</t>
+          <t>Ak 5: Kuurosokeiden syrjäytymisen ehkäisemiseen ja elämänhallinnan parantamiseen alueellisen tiedotus-, neuvonta-, ohjaus- ja tukityön avulla (381 000 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (346 080 €) | Ak 13: Kuurosokeiden ja kuulonäkövammaisten itsenäisen arjen asioinnin ja sosiaalisen kanssakäymisen tukemiseen tieto- ja viestintäteknologian ohjaus-, tuki- ja koulutustoiminnan avulla (270 375 €) | Ak 7: Kuurosokeiden ja kuulonäkövammaisten toimintakyvyn tukemiseen kaksoisaistivamman seurannaisvaikutusten aiheuttamissa muutoksissa ryhmämuotoisen, vertaistuellisen ja tavoitteellisen kurssitoiminnan avulla (144 227 €) | Ak 15: Kuurosokeiden, kuulonäkövammaisten sekä heidän lähipiirinsä ja verkostonsa kommunikaatiotaitojen ja vuorovaikutuksen lisäämiseen ohjauksen, koulutuksen ja kommunikaatiomateriaalituotannon avulla (140 175 €)</t>
         </is>
       </c>
     </row>
@@ -4784,7 +5838,7 @@
       </c>
       <c r="I48" t="inlineStr" s="0">
         <is>
-          <t>Ak 6: Vaikeasta päihdeongelmasta kärsivien ja heidän läheistensä arjen vahvistamiseen matalan kynnyksen tuella  ohjauksella sekä ryhmätoiminnalla (Kohtaamo: Avoimet ovet -kohtaamispaikka  palveluohjaus  Elämäntaitotoiminta  läheisten tuki- ja neuvontapalvelut) (302 889 €) | Ak 4319: Päihde- ja mielenterveysongelmista kärsivien asiakkaiden hyvinvoinnin vahvistamiseen sairaalaympäristössä toteutettavan tukitoiminnan sekä sairaalahoidon jälkeisen palveluohjauksen avulla (Satu-toiminta) (161 910 €) | Ak 10845: Tor-verkossa toimivien päihteitä käyttävien ihmisten sosiaali- ja palveluneuvontaan  sote-ammattilaisten Tor-verkkoon liittyvän osaamisen vahvistamiseen ja vertaisneuvojien kouluttamiseen (126 000 €)</t>
+          <t>Ak 6: Vaikeasta päihdeongelmasta kärsivien ja heidän läheistensä arjen vahvistamiseen matalan kynnyksen tuella, ohjauksella sekä ryhmätoiminnalla (Kohtaamo: Avoimet ovet -kohtaamispaikka, palveluohjaus, Elämäntaitotoiminta, läheisten tuki- ja neuvontapalvelut) (302 889 €) | Ak 5859: Päihteitä käyttävien ja päihdekuntoutujien toimintakyvyn sekä päihteettömyyden ja työllistymisen edellytysten vahvistamiseen osallisuutta ja työelämävalmiuksia edistävien toimintamuotojen avulla (Kynnyksetön vapaaehtois- ja työpajatoiminta, Väylä-ryhmä ja Suunta-kurssi) (265 650 €) | Ay 2886: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (226 941 €) | Ak 12065: Syrjäytymisvaarassa olevien ja syrjäytyneiden päihteiden käyttäjien tavoittamiseen ja tukemiseen etsivän työn keinoin sekä julkisissa tiloissa työskentelevien päihdetietouden lisäämiseen pienimuotoisen koulutustoiminnan avulla (163 000 €) | Ak 4319: Päihde- ja mielenterveysongelmista kärsivien asiakkaiden hyvinvoinnin vahvistamiseen sairaalaympäristössä toteutettavan tukitoiminnan sekä sairaalahoidon jälkeisen palveluohjauksen avulla (Satu-toiminta) (161 910 €) | Ak 10845: Tor-verkossa toimivien päihteitä käyttävien ihmisten sosiaali- ja palveluneuvontaan, sote-ammattilaisten Tor-verkkoon liittyvän osaamisen vahvistamiseen ja vertaisneuvojien kouluttamiseen (126 000 €)</t>
         </is>
       </c>
     </row>
@@ -4817,7 +5871,7 @@
       </c>
       <c r="I49" t="inlineStr" s="0">
         <is>
-          <t>Ak 12: Nuorten tupakka- ja nikotiinituotteiden käytön ehkäisyyn ja lopettamisen tukemiseen sekä terveellisten elintapojen edistämiseen nuoren pystyvyyttä ja motivaatiota lisäämällä  nuorten toimintaympäristöjä kehittämällä ja nuorten lähiaikuisten tietoja ja taitoja lisäämällä (480 958 €) | Ak 4: Syöpäjärjestöjen yksilölliseen ja ryhmämuotoiseen psykososiaaliseen tukeen syöpään sairastuneille ja heidän läheisilleen (452 233 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (308 160 €)</t>
+          <t>Ak 12: Nuorten tupakka- ja nikotiinituotteiden käytön ehkäisyyn ja lopettamisen tukemiseen sekä terveellisten elintapojen edistämiseen nuoren pystyvyyttä ja motivaatiota lisäämällä, nuorten toimintaympäristöjä kehittämällä ja nuorten lähiaikuisten tietoja ja taitoja lisäämällä (480 958 €) | Ak 4: Syöpäjärjestöjen yksilölliseen ja ryhmämuotoiseen psykososiaaliseen tukeen syöpään sairastuneille ja heidän läheisilleen (452 233 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (308 160 €)</t>
         </is>
       </c>
     </row>
@@ -4850,7 +5904,7 @@
       </c>
       <c r="I50" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (710 220 €) | Ak 11: Elinsiirtoa odottavien  elinsiirron saaneiden ja sairastuneiden lapsiperheiden vertaistoiminnan mahdollistamiseen  tuen ja tiedon jakamiseen  omahoidon tukemiseen sekä yhteistyöhön hoitoyksiköiden ja muiden järjestöjen kanssa ja hoitorengaspalveluun lapsiperheille  joille ei ole myönnetty omaishoidon vapaata. Kohderyhminä munuais- ja maksasairautta sairastavat ja/tai elinsiirron saaneet lapset ja nuoret  aikuistuvat nuoret sekä heidän läheisensä. Lapsiperheet  joissa vanhemmalla on vakava munuais- tai maksasairaus. Sairastuneita lapsia  nuoria ja perheitä työssään kohtaavat. (89 538 €) | Ak 3: Jäsenjärjestöille kohdistettaviin avustuksiin (43 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (710 220 €) | Ak 6: Munuais- ja maksasairautta sairastavien sekä elinsiirron saaneiden lasten, nuorten ja aikuisten sekä heidän läheistensä kokonaisvaltaisen hyvinvoinnin tukemiseen järjestämällä ohjattuja ryhmämuotoisia kursseja joko lähijaksoina tai verkossa tapahtuvana. Kursseille osallistuvien vertaisohjaajien kouluttamiseen, ohjaamiseen ja toiminnan organisointiin. (210 898 €) | Ak 12: Elinluovutusten edistämiseen tähtäävään tiedotustoimintaan suurelle yleisölle, medialle ja hoitohenkilökunnalle (Lahja elämälle) (180 463 €) | Ak 11: Elinsiirtoa odottavien, elinsiirron saaneiden ja sairastuneiden lapsiperheiden vertaistoiminnan mahdollistamiseen, tuen ja tiedon jakamiseen, omahoidon tukemiseen sekä yhteistyöhön hoitoyksiköiden ja muiden järjestöjen kanssa ja hoitorengaspalveluun lapsiperheille, joille ei ole myönnetty omaishoidon vapaata. Kohderyhminä munuais- ja maksasairautta sairastavat ja/tai elinsiirron saaneet lapset ja nuoret, aikuistuvat nuoret sekä heidän läheisensä. Lapsiperheet, joissa vanhemmalla on vakava munuais- tai maksasairaus. Sairastuneita lapsia, nuoria ja perheitä työssään kohtaavat. (89 538 €) | Ak 3: Jäsenjärjestöille kohdistettaviin avustuksiin (43 000 €)</t>
         </is>
       </c>
     </row>
@@ -4883,7 +5937,7 @@
       </c>
       <c r="I51" t="inlineStr" s="0">
         <is>
-          <t>Ak 1221: Erokriisissä olevien perheiden auttamiseen ja tukemiseen sekä ennaltaehkäisemään erojen konfliktoitumista ja huoltoriitoja vertaisryhmätoiminnan  asiakastyön ja erotukihenkilötoiminnan keinoin huomioiden erityisesti lapsen ja nuoren asema ja tarpeet (Ero lapsiperheessä työ) (170 451 €) | Ak 2: Lapsiperheitä tukevaan järjestölähtöiseen avopalvelutoimintaan (Vauvaperheohjaus  Kohtaamispaikka Perhetupa- ja mieskaveritoiminta sekä vapaaehtoisdoula-toiminta erityistä tukea tarvitseville lapsiperheille) (167 229 €) | Ak 12306: Kodin ulkopuoliseen väkivaltaan syyllistyneiden tai syyllistymisriskissä olevien väkivaltaisen käyttäytymisen vähentämiseen ja ehkäisemiseen yksilöllisen asiakastyön ja verkostotyön avulla (Aggredi Päijät-Häme) (160 000 €)</t>
+          <t>Ak 5652: Vauvaperheiden päihteettömän ja turvallisen arjen vahvistamiseen sekä päihteiden aiheuttamien haittojen ehkäisemiseen vauvalle kohtaavan etsivän ja matalan kynnyksen työllä, ja yhteisöllisellä vertaisryhmä-, perhe- ja yksilötyöskentelyllä. Tavoitteena on tukea vauvan ja vanhemman välistä vuorovaikutusta sekä edistää vauvaperheiden osallisuutta. (Pidä kiinni -hoitojärjestelmän avopalveluyksikkö Päijät-Häme 2026) (337 600 €) | Ak 8: Yksilö-, pari- ja ryhmämuotoiseen väkivalta- ja turvallisuustyöhön perhe- ja lähisuhdeväkivallan kokijoiden, tekijöiden ja heidän läheistensä kanssa sekä lähisuhdeväkivallan ehkäisytyöhön (Väkivaltatyön avopalvelu) (266 805 €) | Ak 1221: Erokriisissä olevien perheiden auttamiseen ja tukemiseen sekä ennaltaehkäisemään erojen konfliktoitumista ja huoltoriitoja vertaisryhmätoiminnan, asiakastyön ja erotukihenkilötoiminnan keinoin huomioiden erityisesti lapsen ja nuoren asema ja tarpeet (Ero lapsiperheessä työ) (170 451 €) | Ak 2: Lapsiperheitä tukevaan järjestölähtöiseen avopalvelutoimintaan (Vauvaperheohjaus, Kohtaamispaikka Perhetupa- ja mieskaveritoiminta sekä vapaaehtoisdoula-toiminta erityistä tukea tarvitseville lapsiperheille) (167 229 €) | Ak 12306: Kodin ulkopuoliseen väkivaltaan syyllistyneiden tai syyllistymisriskissä olevien väkivaltaisen käyttäytymisen vähentämiseen ja ehkäisemiseen yksilöllisen asiakastyön ja verkostotyön avulla (Aggredi Päijät-Häme) (160 000 €) | Ak 13: Vauvaperheiden vanhemmuuden ja vuorovaikutuksen ryhmämuotoiseen tukemiseen (Vauvaperheryhmä Peukaloinen) (124 579 €)</t>
         </is>
       </c>
     </row>
@@ -4916,7 +5970,7 @@
       </c>
       <c r="I52" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (478 151 €) | Ak 3: Sydänpiirien ja valtakunnallisten sydänyhdistysten järjestämiin toimintakykyä ja vertaistukea edistäviin etä- tai lähikursseihin sydänsairastuneiden ja heidän läheistensä tueksi (377 895 €) | Ak 4465: Sydänterveyden ja toimintakyvyn edistämiseen tiedonvälityksen  vertaistuen ja ammattilaisten koulutuksen keinoin (340 142 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (478 151 €) | Ak 3: Sydänpiirien ja valtakunnallisten sydänyhdistysten järjestämiin toimintakykyä ja vertaistukea edistäviin etä- tai lähikursseihin sydänsairastuneiden ja heidän läheistensä tueksi (377 895 €) | Ak 4465: Sydänterveyden ja toimintakyvyn edistämiseen tiedonvälityksen, vertaistuen ja ammattilaisten koulutuksen keinoin (340 142 €)</t>
         </is>
       </c>
     </row>
@@ -4949,11 +6003,7 @@
       </c>
       <c r="I53" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Väkivaltaa tai sen uhkaa kokeneiden maahan muuttaneiden naisten matalan kynnyksen kriisiauttamiseen  ihmiskaupan vastaiseen työhön ja lasten tukemiseen turvakotijakson jälkeen. 
-Toimintamuotoina matalan kynnyksen palveluohjaus ja neuvonta  yksilöllinen tuki  kriisityö  maksuton auttava puhelin  verkkoauttaminen  vertaistukitoiminta sekä asiantuntija- ja vaikuttamistyö
-(Kriisikeskus Monika) (487 396 €) | Ak 7: Maahan muuttaneiden naisten osallisuuden  toimijuuden ja työelämävalmiuksien edistämiseen matalan kynnyksen toiminnalla pääkaupunkiseudulla.
-Toimintamuotoina yksilöohjaus ja neuvonta  vertaisryhmä- ja vapaaehtoistoiminta sekä asiantuntija- ja verkostotyö
-(Kotoutumiskeskus Monika) (293 786 €) | C 13827: Kansalaisuus  tasa-arvo  perusoikeudet ja arvot -rahoitusohjelman (CERV) hankkeen "Riza" osarahoitukseen järjestölle (2026-2028) (46 300 €)</t>
+          <t>Ak 2: Väkivaltaa tai sen uhkaa kokeneiden maahan muuttaneiden naisten matalan kynnyksen kriisiauttamiseen, ihmiskaupan vastaiseen työhön ja lasten tukemiseen turvakotijakson jälkeen.   Toimintamuotoina matalan kynnyksen palveluohjaus ja neuvonta, yksilöllinen tuki, kriisityö, maksuton auttava puhelin, verkkoauttaminen, vertaistukitoiminta sekä asiantuntija- ja vaikuttamistyö (Kriisikeskus Monika) (487 396 €) | Ay 4: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (359 869 €) | Ak 7: Maahan muuttaneiden naisten osallisuuden, toimijuuden ja työelämävalmiuksien edistämiseen matalan kynnyksen toiminnalla pääkaupunkiseudulla.  Toimintamuotoina yksilöohjaus ja neuvonta, vertaisryhmä- ja vapaaehtoistoiminta sekä asiantuntija- ja verkostotyö (Kotoutumiskeskus Monika) (293 786 €) | C 13827: Kansalaisuus, tasa-arvo, perusoikeudet ja arvot -rahoitusohjelman (CERV) hankkeen "Riza" osarahoitukseen järjestölle (2026-2028) (46 300 €)</t>
         </is>
       </c>
     </row>
@@ -4986,7 +6036,7 @@
       </c>
       <c r="I54" t="inlineStr" s="0">
         <is>
-          <t>Ay 2: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (700 875 €) | Ak 6: Allergiaa  astmaa ja ihotauteja sairastavien sekä palovamman kokeneiden ja heidän läheistensä hyvinvoinnin sekä työ- ja toimintakyvyn edistämiseen ja ylläpitämiseen internaatti- ja avomuotoisten sekä verkossa toteutettavien kurssien avulla (368 382 €) | Ak 3: Jäsenjärjestöille kohdistettaviin avustuksiin (88 600 €)</t>
+          <t>Ay 2: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (700 875 €) | Ak 6: Allergiaa, astmaa ja ihotauteja sairastavien sekä palovamman kokeneiden ja heidän läheistensä hyvinvoinnin sekä työ- ja toimintakyvyn edistämiseen ja ylläpitämiseen internaatti- ja avomuotoisten sekä verkossa toteutettavien kurssien avulla (368 382 €) | Ak 3: Jäsenjärjestöille kohdistettaviin avustuksiin (88 600 €)</t>
         </is>
       </c>
     </row>
@@ -5019,7 +6069,7 @@
       </c>
       <c r="I55" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (750 910 €) | Ak 5: Epilepsiaa sairastavien ihmisten ja heidän läheistensä hyvinvointia ja toimintakykyä tukevaan tavoitteelliseen vertaistuki-  ryhmä- ja kurssitoimintaan valtakunnallisesti ja alueellisesti verkko- ja lähitapaamisina (301 140 €) | Ak 4: Jäsenjärjestöille kohdistettaviin avustuksiin (73 296 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (750 910 €) | Ak 5: Epilepsiaa sairastavien ihmisten ja heidän läheistensä hyvinvointia ja toimintakykyä tukevaan tavoitteelliseen vertaistuki-, ryhmä- ja kurssitoimintaan valtakunnallisesti ja alueellisesti verkko- ja lähitapaamisina (301 140 €) | Ak 4: Jäsenjärjestöille kohdistettaviin avustuksiin (73 296 €)</t>
         </is>
       </c>
     </row>
@@ -5052,7 +6102,7 @@
       </c>
       <c r="I56" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (537 561 €) | Ak 7075: Aivovammautuneiden henkilöiden ja aivoverenkiertohäiriön sairastaneiden sekä heidän läheistensä vertais- ja kokemustoiminnan koordinointiin sekä kehittämiseen ja näihin liittyvien tapahtumien ja koulutusten järjestämiseen (336 226 €) | Ak 6: Jäsenjärjestöille kohdistettaviin avustuksiin (31 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (537 561 €) | Ak 7075: Aivovammautuneiden henkilöiden ja aivoverenkiertohäiriön sairastaneiden sekä heidän läheistensä vertais- ja kokemustoiminnan koordinointiin sekä kehittämiseen ja näihin liittyvien tapahtumien ja koulutusten järjestämiseen (336 226 €) | Ak 2: Aivovamman saaneiden henkilöiden, aivoverenkiertohäiriön sairastaneiden ja heidän läheistensä ammatillisesti ohjattavaan, vertaistukea hyödyntävään tavoitteelliseen ryhmätoimintaan voimavarojen vahvistamiseksi sekä elämänhallinnan tunteen edistämiseksi (220 000 €) | Ak 6: Jäsenjärjestöille kohdistettaviin avustuksiin (31 000 €)</t>
         </is>
       </c>
     </row>
@@ -5085,8 +6135,7 @@
       </c>
       <c r="I57" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (720 248 €) | Ak 8: OmaisOiva-toiminnan valtakunnalliseen koordinointiin  tukemiseen sekä arviointiin ja kehittämiseen. OmaisOiva-toimintaa toteuttavat Omaishoitajaliiton jäsenyhdistykset 
-(OmaisOiva) (269 010 €) | Ak 6: Jäsenjärjestöille kohdistettaviin avustuksiin (75 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (720 248 €) | Ak 8: OmaisOiva-toiminnan valtakunnalliseen koordinointiin, tukemiseen sekä arviointiin ja kehittämiseen. OmaisOiva-toimintaa toteuttavat Omaishoitajaliiton jäsenyhdistykset  (OmaisOiva) (269 010 €) | Ak 6: Jäsenjärjestöille kohdistettaviin avustuksiin (75 000 €)</t>
         </is>
       </c>
     </row>
@@ -5152,7 +6201,7 @@
       </c>
       <c r="I59" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (581 943 €) | Ak 7: Muistiyhdistysten ja niihin kuuluvien Muistiluotsiasiantuntija- ja tukikeskusten koordinoimiseen  asiantuntijatyön ja vapaaehtoistoiminnan tukemiseen sekä muistisairaiden ja heidän läheistensä puhelinneuvonnan (MuistiNeuvo) koordinoimiseen valtakunnallisesti. (418 145 €) | Ak 12: Jäsenjärjestöille kohdistettaviin avustuksiin (49 614 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (581 943 €) | Ak 7: Muistiyhdistysten ja niihin kuuluvien Muistiluotsiasiantuntija- ja tukikeskusten koordinoimiseen, asiantuntijatyön ja vapaaehtoistoiminnan tukemiseen sekä muistisairaiden ja heidän läheistensä puhelinneuvonnan (MuistiNeuvo) koordinoimiseen valtakunnallisesti. (418 145 €) | Ak 12: Jäsenjärjestöille kohdistettaviin avustuksiin (49 614 €)</t>
         </is>
       </c>
     </row>
@@ -5185,7 +6234,7 @@
       </c>
       <c r="I60" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Asunnottomuutta kokevien ja asunnottomuusuhan alla olevien matalan kynnyksen auttamistyöhön (Vertais- ja vapaaehtoistoiminnan keskus Vepa  asunnottomien ihmisten täydentävä ohjaus ja neuvonta asumisasioissa  liikkuva tukityö ja palveluihin ohjaus  maahan muuttaneiden ohjaus ja neuvonta asuntoasioissa  yökeskus Kalkkers  etsivä työ Yökiitäjä ja päihteettömät virkistyspaikat Vartiosaari ja Soldis sekä vapaaehtoistoiminta) (626 693 €) | Ay 4376: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (234 965 €) | Ak 6377: Asunnottomuutta koskevan kokemusasiantuntemuksen hyödyntämisen edistämiseen asunnottomuustaustaisia kokemusasiantuntijoita kouluttamalla ja verkostoimalla (158 620 €)</t>
+          <t>Ak 3: Asunnottomuutta kokevien ja asunnottomuusuhan alla olevien matalan kynnyksen auttamistyöhön (Vertais- ja vapaaehtoistoiminnan keskus Vepa, asunnottomien ihmisten täydentävä ohjaus ja neuvonta asumisasioissa, liikkuva tukityö ja palveluihin ohjaus, maahan muuttaneiden ohjaus ja neuvonta asuntoasioissa, yökeskus Kalkkers, etsivä työ Yökiitäjä ja päihteettömät virkistyspaikat Vartiosaari ja Soldis sekä vapaaehtoistoiminta) (626 693 €) | Ay 4376: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (234 965 €) | Ak 6377: Asunnottomuutta koskevan kokemusasiantuntemuksen hyödyntämisen edistämiseen asunnottomuustaustaisia kokemusasiantuntijoita kouluttamalla ja verkostoimalla (158 620 €)</t>
         </is>
       </c>
     </row>
@@ -5218,7 +6267,7 @@
       </c>
       <c r="I61" t="inlineStr" s="0">
         <is>
-          <t>Ak 4497: Ikääntyneiden itsenäisen arjessa selviytymisen tukemiseen  syrjäytymisen ehkäisyyn ja osallisuuden lisäämiseen digitalisoituvassa yhteiskunnassa kouluttamalla vertaisohjaajia sekä järjestämällä koulutustilaisuuksia ja tapahtumia (Verkosta virtaa - ikääntyneiden itsenäinen selviytyminen digitalisoituvassa yhteiskunnassa) (154 350 €) | Ak 2535: Ikääntyneiden mielen hyvinvoinnin lisäämiseen sekä yksinäisyyden kokemusten vähentämiseen vapaaehtoisten osaamista edistämällä (Elinvoimaa) (132 200 €) | Ak 1398: Jäsenjärjestöille kohdistettaviin avustuksiin (78 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (648 134 €) | Ak 4497: Ikääntyneiden itsenäisen arjessa selviytymisen tukemiseen, syrjäytymisen ehkäisyyn ja osallisuuden lisäämiseen digitalisoituvassa yhteiskunnassa kouluttamalla vertaisohjaajia sekä järjestämällä koulutustilaisuuksia ja tapahtumia (Verkosta virtaa - ikääntyneiden itsenäinen selviytyminen digitalisoituvassa yhteiskunnassa) (154 350 €) | Ak 2535: Ikääntyneiden mielen hyvinvoinnin lisäämiseen sekä yksinäisyyden kokemusten vähentämiseen vapaaehtoisten osaamista edistämällä (Elinvoimaa) (132 200 €) | Ak 1398: Jäsenjärjestöille kohdistettaviin avustuksiin (78 000 €)</t>
         </is>
       </c>
     </row>
@@ -5251,7 +6300,7 @@
       </c>
       <c r="I62" t="inlineStr" s="0">
         <is>
-          <t>Ak 5708: Seksuaalirikosten uhrien sekä heidän läheistensä järjestölähtöiseen tukeen ja oikeuksien neuvontaan yksilö-  ryhmä-  verkko- ja puhelinauttamisen keinoin Helsingissä  Jyväskylässä  Lappeenrannassa ja Rovaniemellä. Ammattilaisten neuvontaan ja koulutukseen. (636 906 €) | Ay 4: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (365 773 €)</t>
+          <t>Ak 5708: Seksuaalirikosten uhrien sekä heidän läheistensä järjestölähtöiseen tukeen ja oikeuksien neuvontaan yksilö-, ryhmä-, verkko- ja puhelinauttamisen keinoin Helsingissä, Jyväskylässä, Lappeenrannassa ja Rovaniemellä. Ammattilaisten neuvontaan ja koulutukseen. (636 906 €) | Ay 4: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (365 773 €)</t>
         </is>
       </c>
     </row>
@@ -5284,7 +6333,7 @@
       </c>
       <c r="I63" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Som allmänt understöd för understödstagarens allmännyttiga verksamhet (214 944 €) | Ak 6192: För att främja kommunikativt och specialpedagogiskt tillgängliga miljöer för barn  unga och vuxna med funktionsvariation eller andra särskilda behov och stöda dem med kamratstödsgrupper och konsultationer  och för att utveckla alternativ och kompletterande kommunikation (AKK)  specialpedagogik och informations- och kommunikationsteknologi (IKT) och sprida dem i samhället (179 444 €) | Ak 6181: För att stöda funktionsförmågan hos barn med funktionsvariation samt för att stöda familjerna i en utmanande livssituation med hjälp av kursverksamhet (103 889 €)</t>
+          <t>Ay 1: Som allmänt understöd för understödstagarens allmännyttiga verksamhet (214 944 €) | Ak 6192: För att främja kommunikativt och specialpedagogiskt tillgängliga miljöer för barn, unga och vuxna med funktionsvariation eller andra särskilda behov och stöda dem med kamratstödsgrupper och konsultationer, och för att utveckla alternativ och kompletterande kommunikation (AKK), specialpedagogik och informations- och kommunikationsteknologi (IKT) och sprida dem i samhället (179 444 €) | Ak 2: För att förbättra välmåendet hos närståendevårdare och -vårdtagare genom kamratstödsgrupper, rekreation och information (164 000 €) | Ak 3: För att främja en trygg skolmiljö genom koordinering, spridning och utveckling av vänelevs- och tutorverksamhet som stöder skolors och utbildningenheters trivselfrämjande och mobbningsförebyggande verksamhet (137 000 €) | Ak 7542: För att öka välbefinnandet och delaktigheten hos personer med sällsynta genetiska sjukdomar och deras närstående genom lågtröskelverksamhet, kamratstöd och information, och för att öka kunskapen hos professionella som i sitt arbete möter personer med sällsynta diagnoser (124 667 €) | Ak 6181: För att stöda funktionsförmågan hos barn med funktionsvariation samt för att stöda familjerna i en utmanande livssituation med hjälp av kursverksamhet (103 889 €) | Ak 4: För mentaliseringsbaserat föräldrastödsarbete och föräldragruppsverksamhet som stöder familjens interaktion (65 000 €)</t>
         </is>
       </c>
     </row>
@@ -5317,9 +6366,7 @@
       </c>
       <c r="I64" t="inlineStr" s="0">
         <is>
-          <t>Ak 1368: Tukea tarvitsevien ja syrjäytymisvaarassa olevien tyttöjen ja nuorten naisten sosiaaliseen vahvistamiseen sekä osallisuuden ja yhteisöllisyyden edistämiseen matalan kynnyksen kohtaamispaikkatoiminnan  vertaistukiryhmien  psykososiaalisen tuen  seksuaalineuvonnan ja jalkautuvan työn sekä yhteistyön avulla Vantaalla ja Lappeenrannassa 
-(Tyttöjen Tila) (377 078 €) | Ak 10386: Maahanmuuttajataustaisten naisten ja heidän lähiyhteisöjensä hyvinvoinnin  osallisuuden ja toimijuuden edistämiseen Naapuriäiti-toiminnan avulla (353 780 €) | Ak 2: Haavoittuvassa asemassa olevien maahan muuttaneiden ja romanitaustaisten naisten sosiaaliseen vahvistumiseen  syrjäytymisen ehkäisemiseen sekä yhteisöllisyyden lisäämiseen matalan kynnyksen yksilöllisen tuen ja palveluohjauksen sekä vertaisryhmä- ja vapaaehtoistoiminnan ja väkivaltatyön avulla 
-(Wahva Nainen) (253 575 €)</t>
+          <t>Ak 1368: Tukea tarvitsevien ja syrjäytymisvaarassa olevien tyttöjen ja nuorten naisten sosiaaliseen vahvistamiseen sekä osallisuuden ja yhteisöllisyyden edistämiseen matalan kynnyksen kohtaamispaikkatoiminnan, vertaistukiryhmien, psykososiaalisen tuen, seksuaalineuvonnan ja jalkautuvan työn sekä yhteistyön avulla Vantaalla ja Lappeenrannassa  (Tyttöjen Tila) (377 078 €) | Ak 10386: Maahanmuuttajataustaisten naisten ja heidän lähiyhteisöjensä hyvinvoinnin, osallisuuden ja toimijuuden edistämiseen Naapuriäiti-toiminnan avulla (353 780 €) | Ak 2: Haavoittuvassa asemassa olevien maahan muuttaneiden ja romanitaustaisten naisten sosiaaliseen vahvistumiseen, syrjäytymisen ehkäisemiseen sekä yhteisöllisyyden lisäämiseen matalan kynnyksen yksilöllisen tuen ja palveluohjauksen sekä vertaisryhmä- ja vapaaehtoistoiminnan ja väkivaltatyön avulla  (Wahva Nainen) (253 575 €)</t>
         </is>
       </c>
     </row>
@@ -5352,7 +6399,7 @@
       </c>
       <c r="I65" t="inlineStr" s="0">
         <is>
-          <t>Ak 7065: Arjessaan tukea tarvitsevien nuorten  osallisuuden  voimavarojen sekä itsenäisen ja oman näköisen elämän valmiuksien vahvistamiseen voimavaravalmennusmenetelmien ja kokemustoimijuuden avulla sekä erilaisilla luovilla ja avoimilla toiminnoilla (290 850 €) | Ak 9707: Arjessa tukea tarvitsevien ihmisten osallisuuden vahvistamiseen digivalmiuksia- ja taitoja parantamalla sekä tarjoamalla yhteisön ja harrastusmahdollisuuksia verkossa (268 545 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (254 016 €)</t>
+          <t>Ak 7065: Arjessaan tukea tarvitsevien nuorten  osallisuuden, voimavarojen sekä itsenäisen ja oman näköisen elämän valmiuksien vahvistamiseen voimavaravalmennusmenetelmien ja kokemustoimijuuden avulla sekä erilaisilla luovilla ja avoimilla toiminnoilla (290 850 €) | Ak 9707: Arjessa tukea tarvitsevien ihmisten osallisuuden vahvistamiseen digivalmiuksia- ja taitoja parantamalla sekä tarjoamalla yhteisön ja harrastusmahdollisuuksia verkossa (268 545 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (254 016 €) | Ak 11856: Mielenterveyden tai neurokirjon haasteita kokevien lastensuojelutaustaisten nuorten ja pitkäaikaisasunnottomien arjenhallinta- ja asumistaitojen vahvistamiseen Asumisen ajokortti -valmennusmallin sekä vertaisuuden keinoin. (170 000 €)</t>
         </is>
       </c>
     </row>
@@ -5385,7 +6432,7 @@
       </c>
       <c r="I66" t="inlineStr" s="0">
         <is>
-          <t>Ak 6: Lapsiperheiden hyvinvoinnin ylläpitämiseen ja edistämiseen sekä lasten kasvun ja vanhemmuuden tukemiseen ja perheiden tilanteiden heikentymisen/kriisiytymisen ennalta ehkäisemiseen alueellisen kohtaamispaikkatoiminnan keinoin kolmella perhetuvalla Tampereella (361 693 €) | Ak 9: Yksilö- ja perhemuotoiseen avokriisityöhön perhe- ja lähisuhdeväkivallan kokijoiden ja tekijöiden kanssa (lasten ja nuorten yksilötyö  0-3-vuotiaiden lasten perheiden kanssa tehtävä väkivaltatyö ja väkivallan eri osapuolten kanssa tehtävä työ) sekä perheiden tukemiseen uniohjauksen  eroauttamisen ja vapaaehtoisuuteen perustuvan mieskaveritoiminnan keinoin (251 404 €) | Ak 10758: Kodin ulkopuoliseen väkivaltaan  syyllistyneiden tai syyllistymisriskissä olevien väkivaltaisen käyttäytymisen vähentämiseen ja ehkäisemiseen yksilöllisen asiakastyön ja verkostotyön avulla (Aggredi Pirkanmaa) (241 500 €)</t>
+          <t>Ak 6: Lapsiperheiden hyvinvoinnin ylläpitämiseen ja edistämiseen sekä lasten kasvun ja vanhemmuuden tukemiseen ja perheiden tilanteiden heikentymisen/kriisiytymisen ennalta ehkäisemiseen alueellisen kohtaamispaikkatoiminnan keinoin kolmella perhetuvalla Tampereella (361 693 €) | Ak 9: Yksilö- ja perhemuotoiseen avokriisityöhön perhe- ja lähisuhdeväkivallan kokijoiden ja tekijöiden kanssa (lasten ja nuorten yksilötyö, 0-3-vuotiaiden lasten perheiden kanssa tehtävä väkivaltatyö ja väkivallan eri osapuolten kanssa tehtävä työ) sekä perheiden tukemiseen uniohjauksen, eroauttamisen ja vapaaehtoisuuteen perustuvan mieskaveritoiminnan keinoin (251 404 €) | Ak 10758: Kodin ulkopuoliseen väkivaltaan  syyllistyneiden tai syyllistymisriskissä olevien väkivaltaisen käyttäytymisen vähentämiseen ja ehkäisemiseen yksilöllisen asiakastyön ja verkostotyön avulla (Aggredi Pirkanmaa) (241 500 €) | Ak 11: Vauvaperheiden vanhemmuuden ja vuorovaikutuksen ryhmämuotoiseen tukemiseen (Vauvaperheryhmä Pikku-Miina) ja vapaaehtoisdoulatoiminnan koordinointiin (127 480 €)</t>
         </is>
       </c>
     </row>
@@ -5418,7 +6465,7 @@
       </c>
       <c r="I67" t="inlineStr" s="0">
         <is>
-          <t>Ay 3244: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (282 724 €) | Ak 3: Miesten hyvinvoinnin lisäämiseen ja vaikeuksien ennaltaehkäisemiseen ryhmä- ja yksilötoiminnan keinoin (Miesten asema -toiminta) sekä pikkulapsiperheiden hyvinvoinnin edistämiseen ja vaikeuksien ennaltaehkäisyyn (Jalkautuva vanhemmuusasema -toiminta) (228 837 €) | Ak 1: Yksilö-  pari-  perhe- ja ryhmämuotoiseen avokriisityöhön perhe- ja lähisuhdeväkivallan uhrien ja tekijöiden kanssa (Lähisuhdeväkivaltatyön avopalvelut Etelä-Savon hyvinvointialueella) (160 634 €)</t>
+          <t>Ak 4280: Eron jälkeisen monimuotoisen väkivallan ja vainon kohteena elävien perheiden turvallisuuden lisäämiseen yksilö- ja ryhmätyöskentelyn keinoin sekä vainoamisen ennaltaehkäisyyn ja seurausten minimoimiseen konsultaation, koulutuksen, kehittämisen ja tutkimusyhteistyön keinoin (VARJO) (297 988 €) | Ay 3244: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (282 724 €) | Ak 3: Miesten hyvinvoinnin lisäämiseen ja vaikeuksien ennaltaehkäisemiseen ryhmä- ja yksilötoiminnan keinoin (Miesten asema -toiminta) sekä pikkulapsiperheiden hyvinvoinnin edistämiseen ja vaikeuksien ennaltaehkäisyyn (Jalkautuva vanhemmuusasema -toiminta) (228 837 €) | Ak 1: Yksilö-, pari-, perhe- ja ryhmämuotoiseen avokriisityöhön perhe- ja lähisuhdeväkivallan uhrien ja tekijöiden kanssa (Lähisuhdeväkivaltatyön avopalvelut Etelä-Savon hyvinvointialueella) (160 634 €)</t>
         </is>
       </c>
     </row>
@@ -5451,7 +6498,7 @@
       </c>
       <c r="I68" t="inlineStr" s="0">
         <is>
-          <t>Ak 7: Lähisuhdeväkivallan ehkäisyyn  väkivallan seurausten käsittelyyn ja turvallisuuden lisäämiseen sekä lähisuhdeväkivaltaa käyttäneiden auttamiseen väkivallan lopettamiseksi yksilö-  pari-  perhe- ja ryhmätoiminnan keinoin (Lähisuhdeväkivaltatyö Pilari) (355 005 €) | Ak 5883: Vauvaperheiden päihteettömän ja turvallisen arjen vahvistamiseen sekä päihteiden aiheuttamien haittojen ehkäisemiseen vauvalle kohtaavan etsivän ja matalan kynnyksen työllä  ja yhteisöllisellä vertaisryhmä-  perhe- ja yksilötyöskentelyllä. Tavoitteena on tukea vauvan ja vanhemman välistä vuorovaikutusta sekä edistää vauvaperheiden osallisuutta. (Pidä kiinni -hoitojärjestelmän avopalveluyksikkö Olivia 2026) (283 000 €) | Ak 5921: Huoltoriitojen ehkäisyyn ja lapselle aiheutuvan kärsimyksen vähentämiseen tarjoamalla yksilö-  pari-  perhe- ja ryhmämuotoista tukea eroa harkitseville  eronneille vanhemmille ja heidän lapsilleen (Eroauttamistyö Silta) (173 092 €)</t>
+          <t>Ak 7: Lähisuhdeväkivallan ehkäisyyn, väkivallan seurausten käsittelyyn ja turvallisuuden lisäämiseen sekä lähisuhdeväkivaltaa käyttäneiden auttamiseen väkivallan lopettamiseksi yksilö-, pari-, perhe- ja ryhmätoiminnan keinoin (Lähisuhdeväkivaltatyö Pilari) (355 005 €) | Ak 5883: Vauvaperheiden päihteettömän ja turvallisen arjen vahvistamiseen sekä päihteiden aiheuttamien haittojen ehkäisemiseen vauvalle kohtaavan etsivän ja matalan kynnyksen työllä, ja yhteisöllisellä vertaisryhmä-, perhe- ja yksilötyöskentelyllä. Tavoitteena on tukea vauvan ja vanhemman välistä vuorovaikutusta sekä edistää vauvaperheiden osallisuutta. (Pidä kiinni -hoitojärjestelmän avopalveluyksikkö Olivia 2026) (283 000 €) | Ak 5921: Huoltoriitojen ehkäisyyn ja lapselle aiheutuvan kärsimyksen vähentämiseen tarjoamalla yksilö-, pari-, perhe- ja ryhmämuotoista tukea eroa harkitseville, eronneille vanhemmille ja heidän lapsilleen (Eroauttamistyö Silta) (173 092 €) | Ak 12152: Matalan kynnyksen tuen tarjoamiseen perheille varhaisen vuorovaikutuksen, vanhempien jaksamisen ja perheen arjen sujumisen vahvistamiseksi sekä synnytyksen jälkeiseen masennukseen (Vauvaperheohjaus -toiminta 2024-2026) (157 000 €)</t>
         </is>
       </c>
     </row>
@@ -5484,7 +6531,7 @@
       </c>
       <c r="I69" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (696 425 €) | Ak 7: Lihastautia sairastavien henkilöiden yhdenvertaisuuden ja osallisuuden edistämiseen koulu- ja työelämässä. Toimintamuotoina yksilöllinen neuvonta  ryhmät  tapahtumat  viestintä  vaikuttamistyö ja oikeuksien valvonta. (60 638 €) | Ak 14: Jäsenjärjestöille kohdistettaviin avustuksiin (10 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (696 425 €) | Ak 2: Läsnä-, etä- ja verkkokursseihin sekä lasten vertaistuellisiin leireihin, joilla parannetaan lihassairaan henkilön ja hänen läheisensä toimintakykyä, elämälaatua, voimavaroja ja vahvuuksien tunnistamista (181 713 €) | Ak 7: Lihastautia sairastavien henkilöiden yhdenvertaisuuden ja osallisuuden edistämiseen koulu- ja työelämässä. Toimintamuotoina yksilöllinen neuvonta, ryhmät, tapahtumat, viestintä, vaikuttamistyö ja oikeuksien valvonta. (60 638 €) | Ak 14: Jäsenjärjestöille kohdistettaviin avustuksiin (10 000 €)</t>
         </is>
       </c>
     </row>
@@ -5517,7 +6564,7 @@
       </c>
       <c r="I70" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Adhd-oireisten ja heidän läheistensä psyykkisen  sosiaalisen ja fyysisen hyvinvoinnin tukemiseen ryhmämuotoisen  tavoitteellisen ja vertaistuellisen kurssitoiminnan avulla (190 071 €) | Ak 1341: Vertais- ja kokemustoimintaan adhd-oireisten ja heidän läheistensä osallisuuden ja hyvinvoinnin vahvistamiseksi sekä tietoisuuden lisäämiseen adhd-oirekuvasta (179 000 €) | Ak 7: Jäsenjärjestöille kohdistettaviin avustuksiin (18 800 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (553 371 €) | Ak 2: Adhd-oireisten ja heidän läheistensä psyykkisen, sosiaalisen ja fyysisen hyvinvoinnin tukemiseen ryhmämuotoisen, tavoitteellisen ja vertaistuellisen kurssitoiminnan avulla (190 071 €) | Ak 1341: Vertais- ja kokemustoimintaan adhd-oireisten ja heidän läheistensä osallisuuden ja hyvinvoinnin vahvistamiseksi sekä tietoisuuden lisäämiseen adhd-oirekuvasta (179 000 €) | Ak 7: Jäsenjärjestöille kohdistettaviin avustuksiin (18 800 €)</t>
         </is>
       </c>
     </row>
@@ -5550,7 +6597,7 @@
       </c>
       <c r="I71" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (636 165 €) | Ak 4: Liikehäiriösairauksia sairastavien ja heidän läheistensä ammattilaisten ohjaamaan  vertaistuen mahdollistavaan ja arkiselviytymistä vahvistavaan tavoitteelliseen ryhmätoimintaan. Toiminnan toteutus lähi- ja verkkomuotoisina kursseina. (230 000 €) | Ak 3: Jäsenjärjestöille kohdistettaviin avustuksiin (67 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (636 165 €) | Ak 4: Liikehäiriösairauksia sairastavien ja heidän läheistensä ammattilaisten ohjaamaan, vertaistuen mahdollistavaan ja arkiselviytymistä vahvistavaan tavoitteelliseen ryhmätoimintaan. Toiminnan toteutus lähi- ja verkkomuotoisina kursseina. (230 000 €) | Ak 3: Jäsenjärjestöille kohdistettaviin avustuksiin (67 000 €)</t>
         </is>
       </c>
     </row>
@@ -5583,7 +6630,7 @@
       </c>
       <c r="I72" t="inlineStr" s="0">
         <is>
-          <t>Ak 5951: Vauvaperheiden päihteettömän arjen vahvistamiseen sekä vauvan ja vanhemman vuorovaikutussuhteen tukemiseen vertaisryhmä-  perhe- ja yksilötyöskentelyllä sekä etsivän ja matalan kynnyksen toimintamallin toteuttamiseen eritysesti Silta-toiminnalla (Pidä kiinni -hoitojärjestelmän avopalveluyksikkö Pesä 2026) (611 946 €) | Ak 4: Vauvaperheiden vanhemmuuden ja vuorovaikutuksen tukemiseen päiväryhmäryhmätoiminnan keinoin  uni- ja vuorovaikutusongelmiin keskittyvään neuvontaan  perhetapaamisiin ja ryhmätoimintaan sekä vapaaehtoisdoula-toiminnan koordinointiin erityistä tukea tarvitseville lapsiperheille (305 312 €)</t>
+          <t>Ak 5951: Vauvaperheiden päihteettömän arjen vahvistamiseen sekä vauvan ja vanhemman vuorovaikutussuhteen tukemiseen vertaisryhmä-, perhe- ja yksilötyöskentelyllä sekä etsivän ja matalan kynnyksen toimintamallin toteuttamiseen eritysesti Silta-toiminnalla (Pidä kiinni -hoitojärjestelmän avopalveluyksikkö Pesä 2026) (611 946 €) | Ak 4: Vauvaperheiden vanhemmuuden ja vuorovaikutuksen tukemiseen päiväryhmäryhmätoiminnan keinoin, uni- ja vuorovaikutusongelmiin keskittyvään neuvontaan, perhetapaamisiin ja ryhmätoimintaan sekä vapaaehtoisdoula-toiminnan koordinointiin erityistä tukea tarvitseville lapsiperheille (305 312 €)</t>
         </is>
       </c>
     </row>
@@ -5616,7 +6663,7 @@
       </c>
       <c r="I73" t="inlineStr" s="0">
         <is>
-          <t>Ak 10: Pasilan alueen asukkaiden psyykkisen  fyysisen ja sosiaalisen hyvinvoinnin sekä alueellisen turvallisuuden ja hyvinvoinnin edistämiseen (Naapuruustalo Pasila) (179 437 €) | Ak 12: Suur-Matinkylän alueen asukkaiden elämänlaadun ja osallisuuden vahvistamiseen  yksinäisyyden kokemuksen vähentämiseen sekä alueellisen turvallisuuden edistämiseen (Naapuruustalo Matinkylä) (125 631 €) | Ak 4: Vapaaehtois- ja kansalaistoiminnan koordinointiin eriarvoisuuden vähentämiseksi ja vapaaehtoisten osallisuuden ja toimijuuden vahvistamiseksi (2026) (70 000 €)</t>
+          <t>Ay 1037: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (268 770 €) | Ak 10: Pasilan alueen asukkaiden psyykkisen, fyysisen ja sosiaalisen hyvinvoinnin sekä alueellisen turvallisuuden ja hyvinvoinnin edistämiseen (Naapuruustalo Pasila) (179 437 €) | Ak 11: Rikosseuraamustaustaisten päihderiippuvaisten elämänhallinnan tukemiseen sekä päihdehaittojen ja uusintarikollisuuden vähentämiseen (Vahvasti tukien) (140 000 €) | Ak 5: Päihde- ja mielenterveystaustaisten elämänhallintaa ja osallisuutta vahvistavaan matalan kynnyksen kohtaamispaikkatoimintaan Espoossa (Askel-toiminta) (133 072 €) | Ak 12: Suur-Matinkylän alueen asukkaiden elämänlaadun ja osallisuuden vahvistamiseen, yksinäisyyden kokemuksen vähentämiseen sekä alueellisen turvallisuuden edistämiseen (Naapuruustalo Matinkylä) (125 631 €) | Ak 4: Vapaaehtois- ja kansalaistoiminnan koordinointiin eriarvoisuuden vähentämiseksi ja vapaaehtoisten osallisuuden ja toimijuuden vahvistamiseksi (2026) (70 000 €)</t>
         </is>
       </c>
     </row>
@@ -5649,7 +6696,7 @@
       </c>
       <c r="I74" t="inlineStr" s="0">
         <is>
-          <t>Ak 5846: Vauvaperheiden päihteettömän ja turvallisen arjen vahvistamiseen sekä päihteiden aiheuttamien haittojen ehkäisemiseen vauvalle kohtaavan etsivän ja matalan kynnyksen työllä  ja yhteisöllisellä vertaisryhmä-  perhe- ja yksilötyöskentelyllä. Tavoitteena on tukea vauvan ja vanhemman välistä vuorovaikutusta sekä edistää vauvaperheiden osallisuutta. (Pidä kiinni –hoitojärjestelmän avopalveluyksikkö Amalia 2026) (287 300 €) | Ak 10302: Perheen tukemiseen eroa harkitessa tai erottaessa sekä lähisuhdeväkivallan ennaltaehkäisyyn  loppumiseen ja kokemuksista toipumiseen tarjoamalla tukea avopalvelun keinoin Pohjois-Savon alueella (Ero- ja väkivaltatyön avopalvelu) (262 119 €) | C 13781: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Arjen ymmärrys – Tukea vanhemmille neurokirjolla" osarahoitukseen järjestölle (2026-2027) (37 560 €)</t>
+          <t>Ak 4: Vauvaperheitä tukevaan järjestölähtöiseen avopalvelutoimintaan (vauvaperheohjaus-, uniohjaus- ja vauvaperheryhmätoiminta sekä osallisuutta vahvistava vauvaperheiden kohtaamispaikka, vapaaehtoisdoula-toiminta erityistä tukea tarvitseville vauvaa odottaville perheille, kokemusasiantuntija- sekä vapaaehtoinen lastenhoitajatoiminta) (325 500 €) | Ak 5846: Vauvaperheiden päihteettömän ja turvallisen arjen vahvistamiseen sekä päihteiden aiheuttamien haittojen ehkäisemiseen vauvalle kohtaavan etsivän ja matalan kynnyksen työllä, ja yhteisöllisellä vertaisryhmä-, perhe- ja yksilötyöskentelyllä. Tavoitteena on tukea vauvan ja vanhemman välistä vuorovaikutusta sekä edistää vauvaperheiden osallisuutta. (Pidä kiinni –hoitojärjestelmän avopalveluyksikkö Amalia 2026) (287 300 €) | Ak 10302: Perheen tukemiseen eroa harkitessa tai erottaessa sekä lähisuhdeväkivallan ennaltaehkäisyyn, loppumiseen ja kokemuksista toipumiseen tarjoamalla tukea avopalvelun keinoin Pohjois-Savon alueella (Ero- ja väkivaltatyön avopalvelu) (262 119 €) | C 13781: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Arjen ymmärrys – Tukea vanhemmille neurokirjolla" osarahoitukseen järjestölle (2026-2027) (37 560 €)</t>
         </is>
       </c>
     </row>
@@ -5682,7 +6729,7 @@
       </c>
       <c r="I75" t="inlineStr" s="0">
         <is>
-          <t>Ak 4: Lastensuojelun sijaishuollon asiakkaana olevien lasten ja nuorten osallisuuden ja kokemusasiantuntijatoiminnan lisäämiseen ja vahvistamiseen lastensuojeluprosessien kehittämisessä sekä vaikuttamistyössä. (Salapoliisitoiminta  nuorten foorumit ja kehittäjäryhmät  Kirahvitoiminta) (221 101 €) | Ak 2501: Sijaishuollossa asuvien lasten ja nuorten varhaiskasvatuksen  koulunkäynnin sekä psyykkisen hyvinvoinnin tukemiseen ja syrjäytymisen ehkäisyyn  Sisukas-toimintamallin avulla. Tiedonkulun  ammattilaisten osaamisen ja sektorirajat ylittävän yhteistyön vahvistamiseen levittämällä  juurruttamalla ja yhteiskehittämällä Sisukas-toimintaa valtakunnallisesti. (184 117 €) | Ak 3: Lapsilähtöisyyden ja laadun edistämiseen lastensuojelussa ja perhehoidossa kehittämis-  kouluttamis- ja vaikuttamistoiminnan avulla (95 685 €)</t>
+          <t>Ak 12231: Lastensuojelun asiakkaana olevien ja olleiden hyvinvoinnin, osallisuuden ja yhteisöllisyyden lisäämiseen, tukemiseen ja vahvistamiseen verkkovälitteisen tuen, vertaistuen, osallistumismuotojen ja vapaaehtoistoiminnan keinoin (Nuorten Turvasatama 2024-2026) (223 500 €) | Ak 4: Lastensuojelun sijaishuollon asiakkaana olevien lasten ja nuorten osallisuuden ja kokemusasiantuntijatoiminnan lisäämiseen ja vahvistamiseen lastensuojeluprosessien kehittämisessä sekä vaikuttamistyössä. (Salapoliisitoiminta, nuorten foorumit ja kehittäjäryhmät, Kirahvitoiminta) (221 101 €) | Ay 1110: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (186 308 €) | Ak 2501: Sijaishuollossa asuvien lasten ja nuorten varhaiskasvatuksen, koulunkäynnin sekä psyykkisen hyvinvoinnin tukemiseen ja syrjäytymisen ehkäisyyn  Sisukas-toimintamallin avulla. Tiedonkulun, ammattilaisten osaamisen ja sektorirajat ylittävän yhteistyön vahvistamiseen levittämällä, juurruttamalla ja yhteiskehittämällä Sisukas-toimintaa valtakunnallisesti. (184 117 €) | Ak 3: Lapsilähtöisyyden ja laadun edistämiseen lastensuojelussa ja perhehoidossa kehittämis-, kouluttamis- ja vaikuttamistoiminnan avulla (95 685 €)</t>
         </is>
       </c>
     </row>
@@ -5715,7 +6762,7 @@
       </c>
       <c r="I76" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Lasten lomatoimintaan (Parasta Lapsille ry ja paikallisyhdistykset) sekä valtakunnalliseen lasten ja perheiden toimintaan terveyden ja hyvinvoinnin edistämiseksi (483 372 €) | Ak 10413: Kriisiytymisuhassa olevien lasten ja perheiden tukeen strukturoidun lasten leiritoiminnan avulla (Näe hyvä mussa -toiminta) (207 270 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (203 608 €)</t>
+          <t>Ak 2: Lasten lomatoimintaan (Parasta Lapsille ry ja paikallisyhdistykset) sekä valtakunnalliseen lasten ja perheiden toimintaan terveyden ja hyvinvoinnin edistämiseksi (483 372 €) | Ak 10413: Kriisiytymisuhassa olevien lasten ja perheiden tukeen strukturoidun lasten leiritoiminnan avulla (Näe hyvä mussa -toiminta) (207 270 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (203 608 €) | Ak 5931: Jäsenjärjestöille kohdistettaviin avustuksiin (10 500 €)</t>
         </is>
       </c>
     </row>
@@ -5748,7 +6795,7 @@
       </c>
       <c r="I77" t="inlineStr" s="0">
         <is>
-          <t>Ay 9: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (480 810 €) | Ak 4394: Oppimisen ja mielenterveyden ongelmia koskevan tiedon tuottamiseen  kokoamiseen ja levittämiseen  ammattilaisten tukemiseen sekä matalan kynnyksen tuen tarjoamiseen oppimisvaikeuksia ja mielenterveyden ongelmia kokeville henkilöille (277 753 €) | Ak 1527: Sosiaali- ja terveysalan järjestöjen oman toiminnan systemaattiseen kehittämiseen tukemalla järjestöjä arvioinnin kehittämisessä sekä vaikutusketjujen ja konkreettisten arviointi- ja seurantatyökalujen luomisessa (Artsi-toiminta - sosiaali- ja terveysalan järjestöjen oman toiminnan systemaattiseen arviointiin ja kehittämiseen) (143 449 €)</t>
+          <t>Ay 9: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (480 810 €) | Ak 4394: Oppimisen ja mielenterveyden ongelmia koskevan tiedon tuottamiseen, kokoamiseen ja levittämiseen, ammattilaisten tukemiseen sekä matalan kynnyksen tuen tarjoamiseen oppimisvaikeuksia ja mielenterveyden ongelmia kokeville henkilöille (277 753 €) | Ak 1527: Sosiaali- ja terveysalan järjestöjen oman toiminnan systemaattiseen kehittämiseen tukemalla järjestöjä arvioinnin kehittämisessä sekä vaikutusketjujen ja konkreettisten arviointi- ja seurantatyökalujen luomisessa (Artsi-toiminta - sosiaali- ja terveysalan järjestöjen oman toiminnan systemaattiseen arviointiin ja kehittämiseen) (143 449 €)</t>
         </is>
       </c>
     </row>
@@ -5781,7 +6828,7 @@
       </c>
       <c r="I78" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Lapsiperheiden ja maahanmuuttajaäitien osallisuuden ja vanhemmuuden vahvistamiseen  yksinäisyyden vähentämiseen sekä lasten lukusujuvuuden parantamiseen ammatillisesti ohjatun tukihenkilötoiminnan keinoin (Perhekummi-  Ystäväksi maahanmuuttajaäidille- sekä mummi- ja vaaritoiminta) (445 339 €) | Ak 10194: Haavoittuvassa asemassa olevien lapsiperheiden vanhempien vanhemmuuden tukemiseen ammatillisesti ohjatun avoimen ryhmätoiminnan  monikulttuurisen ryhmätoiminnan  etsivän perhetyön ja yksilöohjauksen avulla. (204 750 €) | Ak 11317: Lapsiperheiden ennaltaehkäisevän tuen ja osallisuuden vahvistamiseen järjestämällä kaupungin ja järjestöjen yhdessä johtamaa ja ylläpitämää avointa kohtaamispaikkatoimintaa sekä kohtaamispaikkatoiminnan kehittämiseen Uudellamaalla. (199 080 €)</t>
+          <t>Ak 2: Lapsiperheiden ja maahanmuuttajaäitien osallisuuden ja vanhemmuuden vahvistamiseen, yksinäisyyden vähentämiseen sekä lasten lukusujuvuuden parantamiseen ammatillisesti ohjatun tukihenkilötoiminnan keinoin (Perhekummi-, Ystäväksi maahanmuuttajaäidille- sekä mummi- ja vaaritoiminta) (445 339 €) | Ak 10194: Haavoittuvassa asemassa olevien lapsiperheiden vanhempien vanhemmuuden tukemiseen ammatillisesti ohjatun avoimen ryhmätoiminnan, monikulttuurisen ryhmätoiminnan, etsivän perhetyön ja yksilöohjauksen avulla. (204 750 €) | Ak 11317: Lapsiperheiden ennaltaehkäisevän tuen ja osallisuuden vahvistamiseen järjestämällä kaupungin ja järjestöjen yhdessä johtamaa ja ylläpitämää avointa kohtaamispaikkatoimintaa sekä kohtaamispaikkatoiminnan kehittämiseen Uudellamaalla. (199 080 €)</t>
         </is>
       </c>
     </row>
@@ -5814,7 +6861,7 @@
       </c>
       <c r="I79" t="inlineStr" s="0">
         <is>
-          <t>Ak 17: Vaikeassa työmarkkina-asemassa olevien viittomakielisten kuurojen ja kuurosokeiden työelämävalmiuksien  työelämätaitojen  opiskelun ja arjenhallinnan edistämiseen viittomakielisen yksilö- ja ryhmämuotoisen työvalmennuksen ja verkostoyhteistyön avulla (Poveri) (304 500 €) | Ay 21: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (92 400 €) | Ak 12: Pitkäaikaissairaiden kuurojen  kuurosokeiden ja heidän läheistensä viittomakieliseen vertaisryhmätoimintaan  terveyteen ja hyvinvointiin liittyvään tukeen ja tiedonsaantiin sekä Viittomakielisen Auttavan Linjan toteuttamiseen (Passi) (87 150 €)</t>
+          <t>Ak 4: Viittomakommunikaatiota käyttävien lasten perheiden kommunikaation ja vuorovaikutuksen tukemiseen vertaisperhekurssien, yksilö- ja ryhmätoimintojen sekä materiaalituotannon avulla (Juniori-ohjelma) (352 850 €) | Ak 17: Vaikeassa työmarkkina-asemassa olevien viittomakielisten kuurojen ja kuurosokeiden työelämävalmiuksien, työelämätaitojen, opiskelun ja arjenhallinnan edistämiseen viittomakielisen yksilö- ja ryhmämuotoisen työvalmennuksen ja verkostoyhteistyön avulla (Poveri) (304 500 €) | Ay 21: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (92 400 €) | Ak 12: Pitkäaikaissairaiden kuurojen, kuurosokeiden ja heidän läheistensä viittomakieliseen vertaisryhmätoimintaan, terveyteen ja hyvinvointiin liittyvään tukeen ja tiedonsaantiin sekä Viittomakielisen Auttavan Linjan toteuttamiseen (Passi) (87 150 €)</t>
         </is>
       </c>
     </row>
@@ -5847,7 +6894,7 @@
       </c>
       <c r="I80" t="inlineStr" s="0">
         <is>
-          <t>Ak 6955: Perheiden monimuotoisuutta koskevan tiedon keräämiseen ja levittämiseen sekä vaikuttamistyöhön. Tavoitteena on perhemuotojen välinen yhdenvertaisuus ja kaikkien perheiden osallisuus yhteiskunnassa. (260 000 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (224 784 €) | Ak 7534: Sateenkaari-ihmisten perhe- ja läheissuhteiden tukemiseen vertaistoiminnalla  yksilöllisellä tuella  tiedon tuottamisella ja jakamisella sekä koulutustoiminnalla (173 093 €)</t>
+          <t>Ak 6955: Perheiden monimuotoisuutta koskevan tiedon keräämiseen ja levittämiseen sekä vaikuttamistyöhön. Tavoitteena on perhemuotojen välinen yhdenvertaisuus ja kaikkien perheiden osallisuus yhteiskunnassa. (260 000 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (224 784 €) | Ak 9803: Sateenkaariperheiden ja vanhemmuutta suunnittelevien sateenkaari-ihmisten hyvinvoinnin edistämiseen vertaistuella, koulutuksella, neuvonnalla ja asiantuntijatyöllä (178 500 €) | Ak 7534: Sateenkaari-ihmisten perhe- ja läheissuhteiden tukemiseen vertaistoiminnalla, yksilöllisellä tuella, tiedon tuottamisella ja jakamisella sekä koulutustoiminnalla (173 093 €)</t>
         </is>
       </c>
     </row>
@@ -5880,7 +6927,7 @@
       </c>
       <c r="I81" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Maahanmuuttajien osallisuutta  yhteisöllisyyttä ja kaksisuuntaista kotoutumista edistävään toimintaan (Kompassi) (294 052 €) | Ak 7: Erityistä tukea tarvitsevien tyttöjen  nuorten naisten ja sukupuoli-identiteettiään pohtivien hyvinvoinnin ja osallisuuden tukemiseen  seksuaaliterveyden edistämiseen sekä seksuaaliväkivaltatyöhön (220 000 €) | Ak 4087: Kodin ulkopuoliseen väkivaltaan syyllistyneiden tai syyllistymisriskissä olevien väkivaltaisen käyttäytymisen vähentämiseen ja ehkäisemiseen yksilöllisen asiakastyön ja verkostotyön avulla (Aggredi Kuopio) (155 000 €)</t>
+          <t>Ak 3: Maahanmuuttajien osallisuutta, yhteisöllisyyttä ja kaksisuuntaista kotoutumista edistävään toimintaan (Kompassi) (294 052 €) | Ak 7: Erityistä tukea tarvitsevien tyttöjen, nuorten naisten ja sukupuoli-identiteettiään pohtivien hyvinvoinnin ja osallisuuden tukemiseen, seksuaaliterveyden edistämiseen sekä seksuaaliväkivaltatyöhön (220 000 €) | Ak 6: Järjestölähtöiseen yksilö- ja ryhmämuotoiseen tukitoimintaan rikostaustaisten ja heidän läheistensä parissa (Tukikeskus Mahku) (163 800 €) | Ak 4087: Kodin ulkopuoliseen väkivaltaan syyllistyneiden tai syyllistymisriskissä olevien väkivaltaisen käyttäytymisen vähentämiseen ja ehkäisemiseen yksilöllisen asiakastyön ja verkostotyön avulla (Aggredi Kuopio) (155 000 €)</t>
         </is>
       </c>
     </row>
@@ -5913,7 +6960,7 @@
       </c>
       <c r="I82" t="inlineStr" s="0">
         <is>
-          <t>Ak 1196: Syömishäiriöön sairastuneiden ja vapaaehtoisena toimivien hyvinvoinnin tukemiseen matalan kynnyksen toiminnalla Itä- ja Kaakkois-Suomessa  Pohjois-Suomessa ja Sisä-Suomen alueella sekä syömishäiriöön sairastuneiden läheisten tukemiseen valtakunnallisesti sähköisten tukipalveluiden avulla (470 000 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (337 680 €)</t>
+          <t>Ak 1196: Syömishäiriöön sairastuneiden ja vapaaehtoisena toimivien hyvinvoinnin tukemiseen matalan kynnyksen toiminnalla Itä- ja Kaakkois-Suomessa, Pohjois-Suomessa ja Sisä-Suomen alueella sekä syömishäiriöön sairastuneiden läheisten tukemiseen valtakunnallisesti sähköisten tukipalveluiden avulla (470 000 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (337 680 €)</t>
         </is>
       </c>
     </row>
@@ -5946,7 +6993,7 @@
       </c>
       <c r="I83" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Naisten ja nuorten naisten käyttämän väkivallan ja ylisukupolvisen väkivallan ehkäisyyn lähi- ja verkkotoimintana  yksilö-  pariskunta- ja ryhmätoiminnan sekä ammattilaisille suunnatun toiminnan keinoin. Kohderyhmät 15 ikävuodesta alkaen. (627 770 €) | Ay 2675: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (178 453 €)</t>
+          <t>Ak 1: Naisten ja nuorten naisten käyttämän väkivallan ja ylisukupolvisen väkivallan ehkäisyyn lähi- ja verkkotoimintana, yksilö-, pariskunta- ja ryhmätoiminnan sekä ammattilaisille suunnatun toiminnan keinoin. Kohderyhmät 15 ikävuodesta alkaen. (627 770 €) | Ay 2675: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (178 453 €)</t>
         </is>
       </c>
     </row>
@@ -5979,10 +7026,7 @@
       </c>
       <c r="I84" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (547 010 €) | Ak 9: Vertaisuutta korostavaan ryhmämuotoiseen tukeen internaatti-  avo- ja verkkokurssien avulla 
-- perheille  joissa on psoriasista sairastava 5–15-vuotias lapsi  
-- työikäisille iho- tai nivelpsoriasista sairastaville ja heidän läheisilleen ja
-- yli 60-vuotiaille eläkkeellä oleville psoriasista sairastaville (210 000 €) | Ak 16: Jäsenjärjestöille kohdistettaviin avustuksiin (49 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (547 010 €) | Ak 9: Vertaisuutta korostavaan ryhmämuotoiseen tukeen internaatti-, avo- ja verkkokurssien avulla  - perheille, joissa on psoriasista sairastava 5–15-vuotias lapsi,  - työikäisille iho- tai nivelpsoriasista sairastaville ja heidän läheisilleen ja - yli 60-vuotiaille eläkkeellä oleville psoriasista sairastaville (210 000 €) | Ak 16: Jäsenjärjestöille kohdistettaviin avustuksiin (49 000 €)</t>
         </is>
       </c>
     </row>
@@ -6015,7 +7059,7 @@
       </c>
       <c r="I85" t="inlineStr" s="0">
         <is>
-          <t>Ay 1998: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (263 088 €) | Ak 10605: Psyykkistä kuormitusta kokeneiden lapsiperheiden hyvinvoinnin parantamiseen yksilöllisellä tuella  vertaistuella ja kohtaamispaikkatoiminnalla Oulussa (115 000 €) | Ak 7331: Mielenterveyskuntoutujien kokemusasiantuntija- ja vertaistoiminnan vahvistamiseen koulutuksilla sekä kokemustiedon levittämiseen Oulussa (110 000 €)</t>
+          <t>Ak 7: Mielenterveyskuntoutujien, psyykkisesti kuormittuneiden nuorten aikuisten sekä omaisten matalan kynnyksen kohtaamispaikka-, vertais- ja vapaaehtoistoimintaan Oulussa (315 550 €) | Ay 1998: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (263 088 €) | Ak 10605: Psyykkistä kuormitusta kokeneiden lapsiperheiden hyvinvoinnin parantamiseen yksilöllisellä tuella, vertaistuella ja kohtaamispaikkatoiminnalla Oulussa (115 000 €) | Ak 7331: Mielenterveyskuntoutujien kokemusasiantuntija- ja vertaistoiminnan vahvistamiseen koulutuksilla sekä kokemustiedon levittämiseen Oulussa (110 000 €)</t>
         </is>
       </c>
     </row>
@@ -6048,7 +7092,7 @@
       </c>
       <c r="I86" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Yksinäisten  sosiaalisesti syrjäytyneiden  maahanmuuttajataustaisten  psyykkisesti oireilevien  seksuaalisuutta loukkaavaa väkivaltaa kohdanneiden sekä muiden erityistä tukea tarvitsevien tyttöjen ja nuorten naisten hyvinvoinnin  elämänhallinnan ja yhteisöllisyyden vahvistamiseen matalankynnyksen toiminnoilla sekä ryhmä- ja yksilötuella (Vuolle Tyttöjen Talo  Oulu) (219 258 €) | Ak 2: Maahanmuuttajien ja valtaväestön kaksissuuntaista kotoutumista edistävään monikulttuuriseen matalan kynnyksen olohuonetoimintaan  ryhmämuotoiseen toimintaan  vapaaehtoistoimintaan  leiri- ja retkitoimintaan sekä yksilölliseen tukeen ja koulutuksiin (Monikulttuurinen Ystävyystalo) (124 580 €) | Ak 4: Alueellisen vapaaehtoistoiminnan tukemiseen  kehittämiseen ja alueellisen yhteistyön koordinointiin kansalaisyhteiskunnan toimivuuden vahvistamiseksi (Vapaaehtoistoiminnan resurssikeskus VARES  Vares-verkosto) (120 091 €)</t>
+          <t>Ak 3: Yksinäisten, sosiaalisesti syrjäytyneiden, maahanmuuttajataustaisten, psyykkisesti oireilevien, seksuaalisuutta loukkaavaa väkivaltaa kohdanneiden sekä muiden erityistä tukea tarvitsevien tyttöjen ja nuorten naisten hyvinvoinnin, elämänhallinnan ja yhteisöllisyyden vahvistamiseen matalankynnyksen toiminnoilla sekä ryhmä- ja yksilötuella (Vuolle Tyttöjen Talo, Oulu) (219 258 €) | Ak 3175: Kodin ulkopuoliseen väkivaltaan syyllistyneiden tai syyllistymisriskissä olevien väkivaltaisen käyttäytymisen vähentämiseen ja ehkäisemiseen yksilöllisen asiakastyön ja verkostotyön avulla (Aggredi Pohjois-Suomi) (173 513 €) | Ak 3174: Yksinäisten, ulkopuoliseksi itsensä kokevien, kiusattujen, maahanmuuttajataustaisten, seksuaalista väkivaltaa kohdanneiden sekä muiden erityistä tukea tarvitsevien poikien ja sukupuolensa moninaisesti kokevien nuorten osallisuuden ja sosiaalisten taitojen vahvistamiseen matalan kynnyksen toiminnalla sekä ryhmä- ja yksilötuella (Vuolle Poikien Talo, Oulu) (165 375 €) | Ak 2: Maahanmuuttajien ja valtaväestön kaksissuuntaista kotoutumista edistävään monikulttuuriseen matalan kynnyksen olohuonetoimintaan, ryhmämuotoiseen toimintaan, vapaaehtoistoimintaan, leiri- ja retkitoimintaan sekä yksilölliseen tukeen ja koulutuksiin (Monikulttuurinen Ystävyystalo) (124 580 €) | Ak 4: Alueellisen vapaaehtoistoiminnan tukemiseen, kehittämiseen ja alueellisen yhteistyön koordinointiin kansalaisyhteiskunnan toimivuuden vahvistamiseksi (Vapaaehtoistoiminnan resurssikeskus VARES, Vares-verkosto) (120 091 €)</t>
         </is>
       </c>
     </row>
@@ -6081,7 +7125,7 @@
       </c>
       <c r="I87" t="inlineStr" s="0">
         <is>
-          <t>Ak 9: Aikuisten  lasten ja nuorten lähisuhteisiin  lähisuhdeväkivaltaan ja perheen sisäiseen vuorovaikutukseen liittyvien ongelmien ehkäisyyn sekä niistä selviytymiseen yksilö-  pari- ja perhetapaamisten sekä ryhmätoiminnan keinoin (Lähisuhde- ja väkivaltatyön avopalvelu) (247 144 €) | Ak 8: Järjestölähtöiseen kriisi- ja mielenterveystyöhön vaikeissa elämäntilanteissa oleville tarjoamalla matalan kynnyksen keskusteluapua  ammatillisesti ohjattuja ryhmiä Lapin hyvinvointialueella  tukihenkilötoimintaan sekä vapaaehtoisten koulutukseen ja koordinointiin sekä tiedottamiseen toiminnasta ja tapahtumien järjestämiseen (Lapin ensi- ja turvakoti ry:n kriisikeskus) (200 899 €) | Ak 4: Lasta odottavien  vauva- ja pikkulapsiperheiden vanhempien tukeen sekä neuvontaan odotusajan  vauvan uni- ja vuorokausirytmin  lasten ja vanhempien välisen vuorovaikutus- ja kiintymyssuhteen sekä kuormittavan perhe-elämän haasteissa yksilöllisen tuen  vertaisryhmä- sekä vapaaehtoistoiminnan avulla (131 314 €)</t>
+          <t>Ak 9: Aikuisten, lasten ja nuorten lähisuhteisiin, lähisuhdeväkivaltaan ja perheen sisäiseen vuorovaikutukseen liittyvien ongelmien ehkäisyyn sekä niistä selviytymiseen yksilö-, pari- ja perhetapaamisten sekä ryhmätoiminnan keinoin (Lähisuhde- ja väkivaltatyön avopalvelu) (247 144 €) | Ak 6312: Lasta odottavien sekä vauva- ja pikkulapsiperheiden tukeen ja neuvontaan kuormittavissa vanhemmuuden haasteissa, jotka voivat liittyä esimerkiksi yksinäisyyteen, päihteiden käyttöön perheissä tai vanhemman omiin vaikeisiin lapsuuden kokemuksiin. Tavoitteena on tukea vanhemmuutta sekä lapsen ja vanhemman välistä vuorovaikutusta ja turvallista arkea, edistää lapsiperheiden osallisuutta sekä ennaltaehkäistä ylisukupolvisia haasteita yksilöllisen tuen, vertaisryhmä- sekä vapaaehtoistoiminnan avulla (Avopalveluyksikkö Tuulia 2026) (203 342 €) | Ak 8: Järjestölähtöiseen kriisi- ja mielenterveystyöhön vaikeissa elämäntilanteissa oleville tarjoamalla matalan kynnyksen keskusteluapua, ammatillisesti ohjattuja ryhmiä Lapin hyvinvointialueella, tukihenkilötoimintaan sekä vapaaehtoisten koulutukseen ja koordinointiin sekä tiedottamiseen toiminnasta ja tapahtumien järjestämiseen (Lapin ensi- ja turvakoti ry:n kriisikeskus) (200 899 €) | Ak 4: Lasta odottavien, vauva- ja pikkulapsiperheiden vanhempien tukeen sekä neuvontaan odotusajan, vauvan uni- ja vuorokausirytmin, lasten ja vanhempien välisen vuorovaikutus- ja kiintymyssuhteen sekä kuormittavan perhe-elämän haasteissa yksilöllisen tuen, vertaisryhmä- sekä vapaaehtoistoiminnan avulla (131 314 €)</t>
         </is>
       </c>
     </row>
@@ -6147,7 +7191,7 @@
       </c>
       <c r="I89" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (565 085 €) | Ak 2: Keliakiaan sopeutumista ja gluteenittoman ruokavaliohoidon toteutusta tukevaan ammatillisesti ohjattuun  vertaistuelliseen ja tavoitteelliseen ryhmämuotoiseen toimintaan. Kohderyhminä keliakia- tai ihokeliakiadiagnoosin saaneet ja heidän läheisensä sekä he  jotka noudattavat gluteenitonta ruokavaliota ilman keliakiadiagnoosia. (173 093 €) | Ak 2393: Jäsenjärjestöille kohdistettaviin avustuksiin (30 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (565 085 €) | Ak 2: Keliakiaan sopeutumista ja gluteenittoman ruokavaliohoidon toteutusta tukevaan ammatillisesti ohjattuun, vertaistuelliseen ja tavoitteelliseen ryhmämuotoiseen toimintaan. Kohderyhminä keliakia- tai ihokeliakiadiagnoosin saaneet ja heidän läheisensä sekä he, jotka noudattavat gluteenitonta ruokavaliota ilman keliakiadiagnoosia. (173 093 €) | Ak 2393: Jäsenjärjestöille kohdistettaviin avustuksiin (30 000 €)</t>
         </is>
       </c>
     </row>
@@ -6180,7 +7224,7 @@
       </c>
       <c r="I90" t="inlineStr" s="0">
         <is>
-          <t>Ak 1914: Pelihaittojen ja haitallisen internetin käytön ehkäisyn ja hoidon kehittämiseen (Pelituki) (317 000 €) | Ak 1912: Korvaushoidon asiakkaiden  päihdekuntoutujien ja rikosseuraamusasiakkaiden osallisuuden vahvistamiseen matalan kynnyksen kohtaamispaikan sekä vertais- ja vapaaehtoistoiminnan avulla (Kaista) (220 500 €) | Ak 11334: Päihteidenkäyttäjien osallisuutta  palveluihin ohjautumista ja hyvinvointia lisäävän matalan kynnyksen kohtaamispaikan ylläpitoon (220 500 €)</t>
+          <t>Ak 1914: Pelihaittojen ja haitallisen internetin käytön ehkäisyn ja hoidon kehittämiseen (Pelituki) (317 000 €) | Ak 1912: Korvaushoidon asiakkaiden, päihdekuntoutujien ja rikosseuraamusasiakkaiden osallisuuden vahvistamiseen matalan kynnyksen kohtaamispaikan sekä vertais- ja vapaaehtoistoiminnan avulla (Kaista) (220 500 €) | Ak 11334: Päihteidenkäyttäjien osallisuutta, palveluihin ohjautumista ja hyvinvointia lisäävän matalan kynnyksen kohtaamispaikan ylläpitoon (220 500 €)</t>
         </is>
       </c>
     </row>
@@ -6213,7 +7257,7 @@
       </c>
       <c r="I91" t="inlineStr" s="0">
         <is>
-          <t>Ak 7: Lähisuhdeväkivallan ennaltaehkäisyyn ja väkivaltaa kokeneiden selviytymisen tukemiseen sekä väkivaltaa käyttäneiden väkivaltaisen käytöksen katkaisuun yksilö-  pari- ja perhetapaamisten  vanhemmuutta tukeviin tapaamisten sekä ryhmämuotoissen avokriisityön keinoin. Toiminta kohdistuu lähisuhdeväkivallan kaikkien osapuolten tukemiseen  myös lasten ja nuorten. Lähisuhdeväkivallan vastaiseen vaikuttamistyöhön. (Avokriisityö) (258 139 €) | Ak 10: Vauvaperheiden vanhemmuuden ja vuorovaikutuksen tukemiseen sekä pitkäkestoisen stressin vähentämiseen intensiivisen suljetun ryhmätoiminnan  yksilöllisen neuvonnan ja ohjauksen sekä kaikille vauvaperheille avoimen ryhmätoiminnan keinoin. Vapaaehtoisdoula-toimintaan erityistä tukea tarvitseville vauvaperheille sekä vertaisohjaajien koulutukseen. (Vauvatalo) (194 164 €) | Ak 3: Lapsiperheiden hyvinvointia tukevaan järjestölähtöiseen avopalvelutoimintaan  (Mieskaveri-  Ero lapsiperheessä- ja vertaisryhmätoiminnat sekä nettiauttaminen) (149 080 €)</t>
+          <t>Ak 7: Lähisuhdeväkivallan ennaltaehkäisyyn ja väkivaltaa kokeneiden selviytymisen tukemiseen sekä väkivaltaa käyttäneiden väkivaltaisen käytöksen katkaisuun yksilö-, pari- ja perhetapaamisten, vanhemmuutta tukeviin tapaamisten sekä ryhmämuotoissen avokriisityön keinoin. Toiminta kohdistuu lähisuhdeväkivallan kaikkien osapuolten tukemiseen, myös lasten ja nuorten. Lähisuhdeväkivallan vastaiseen vaikuttamistyöhön. (Avokriisityö) (258 139 €) | Ak 10: Vauvaperheiden vanhemmuuden ja vuorovaikutuksen tukemiseen sekä pitkäkestoisen stressin vähentämiseen intensiivisen suljetun ryhmätoiminnan, yksilöllisen neuvonnan ja ohjauksen sekä kaikille vauvaperheille avoimen ryhmätoiminnan keinoin. Vapaaehtoisdoula-toimintaan erityistä tukea tarvitseville vauvaperheille sekä vertaisohjaajien koulutukseen. (Vauvatalo) (194 164 €) | Ak 7756: Seksuaalirikosten ennaltaehkäisyyn  ja vähentämiseen seksuaalirikostaustaisten, potentiaalisten tekijöiden ja heidän läheisilleen kohdistuvalla matalan kynnyksen palvelulla Oulun alueella (SERITA) (155 400 €) | Ak 3: Lapsiperheiden hyvinvointia tukevaan järjestölähtöiseen avopalvelutoimintaan  (Mieskaveri-, Ero lapsiperheessä- ja vertaisryhmätoiminnat sekä nettiauttaminen) (149 080 €)</t>
         </is>
       </c>
     </row>
@@ -6246,7 +7290,7 @@
       </c>
       <c r="I92" t="inlineStr" s="0">
         <is>
-          <t>Ak 8: Perheiden syrjäytymisen ehkäisemiseen ja voimavarojen lisäämiseen sekä lapsen ja vanhemman välisen vuorovaikutuksen vahvistamiseen yksilö-  ryhmä-  vapaaehtois- ja vertaistoiminnan keinoin (Vauvaperheohjaus Pulmu  Ero lapsiperheessä -työ  lasten yökylä- ja tenavatupatoiminta  vapaaehtoisdoula-toiminta erityistä tukea tarvitseville lapsiperheille  ryhmätoiminnat  leirit ja tapahtumat) (189 630 €) | Ak 11: Yksilö-  pari-  perhe- ja ryhmämuotoiseen avokriisityöhön perhe- ja lähisuhdeväkivallan uhrien  tekijöiden ja väkivallalle altistuneiden lasten  nuorten ja aikuisten kanssa (Väkivaltatyön palvelukeskus Pysäkki) (159 000 €) | Ak 9: Vauvaperheiden vanhemmuuden ja vuorovaikutuksen ryhmämuotoiseen tukemiseen (Vauvaperheryhmä Untuva) (89 302 €)</t>
+          <t>Ak 5739: Vauvaperheiden päihteettömän ja turvallisen arjen vahvistamiseen sekä päihteiden aiheuttamien haittojen ehkäisemiseen vauvalle kohtaavan etsivän ja matalan kynnyksen työllä, ja yhteisöllisellä vertaisryhmä-, perhe- ja yksilötyöskentelyllä. Tavoitteena on tukea vauvan ja vanhemman välistä vuorovaikutusta sekä edistää vauvaperheiden osallisuutta. (Pidä kiinni -hoitojärjestelmän avopalvelu Nuppu, Kymenlaakso 2026) (315 000 €) | Ak 8: Perheiden syrjäytymisen ehkäisemiseen ja voimavarojen lisäämiseen sekä lapsen ja vanhemman välisen vuorovaikutuksen vahvistamiseen yksilö-, ryhmä-, vapaaehtois- ja vertaistoiminnan keinoin (Vauvaperheohjaus Pulmu, Ero lapsiperheessä -työ, lasten yökylä- ja tenavatupatoiminta, vapaaehtoisdoula-toiminta erityistä tukea tarvitseville lapsiperheille, ryhmätoiminnat, leirit ja tapahtumat) (189 630 €) | Ak 11: Yksilö-, pari-, perhe- ja ryhmämuotoiseen avokriisityöhön perhe- ja lähisuhdeväkivallan uhrien, tekijöiden ja väkivallalle altistuneiden lasten, nuorten ja aikuisten kanssa (Väkivaltatyön palvelukeskus Pysäkki) (159 000 €) | Ak 9: Vauvaperheiden vanhemmuuden ja vuorovaikutuksen ryhmämuotoiseen tukemiseen (Vauvaperheryhmä Untuva) (89 302 €)</t>
         </is>
       </c>
     </row>
@@ -6279,7 +7323,7 @@
       </c>
       <c r="I93" t="inlineStr" s="0">
         <is>
-          <t>Ak 2872: Rikostaustaisille romaneille suunnattuun kulttuurilähtöiseen tukeen ja kuntoutumista edistävään toimintaan vankeusaikana  vapautumisen nivelvaiheissa sekä jälkitukena: Naisten Kulma-tukipisteet  vankilatyön ja VOIVA sekä VOITTO-toimintamallien koordinointi  tukihenkilötoiminta  kouluttaminen ja edunvalvonta. Euroopan sosiaalirahaston rakennerahasto-ohjelmanhankkeen "Aktiivinen toimijuus" osarahoitukseen järjestölle (2024-2026) (378 325 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (186 322 €) | Ak 11220: Romaninuorten tukemiseen omien voimavarojen ja vahvuuksien löytämiseksi jalkautuvan työn  yksilötyön ja ryhmämuotoisen toiminnan keinoin (Terne Apre - Nuorten vuoro) (184 800 €)</t>
+          <t>Ak 2872: Rikostaustaisille romaneille suunnattuun kulttuurilähtöiseen tukeen ja kuntoutumista edistävään toimintaan vankeusaikana, vapautumisen nivelvaiheissa sekä jälkitukena: Naisten Kulma-tukipisteet, vankilatyön ja VOIVA sekä VOITTO-toimintamallien koordinointi, tukihenkilötoiminta, kouluttaminen ja edunvalvonta. Euroopan sosiaalirahaston rakennerahasto-ohjelmanhankkeen "Aktiivinen toimijuus" osarahoitukseen järjestölle (2024-2026) (378 325 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (186 322 €) | Ak 11220: Romaninuorten tukemiseen omien voimavarojen ja vahvuuksien löytämiseksi jalkautuvan työn, yksilötyön ja ryhmämuotoisen toiminnan keinoin (Terne Apre - Nuorten vuoro) (184 800 €)</t>
         </is>
       </c>
     </row>
@@ -6312,9 +7356,7 @@
       </c>
       <c r="I94" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Lasten ja nuorten kokeman kiusaamisen ja häiriökäyttäytymisen vähentämiseen ja havaittujen tilanteiden käsittelyyn päiväkodeissa  kouluissa ja oppilaitoksissa. Vertaissovittelutoiminnan ja siihen liittyvän oppilaiden ja henkilökunnan vapaaehtoisen sovittelutyön ja restoratiivisen toiminnan tukemiseen koulutusten ja tiedottamisen kautta 
-(VERSO-ohjelma) (498 580 €) | Ak 6476: Asukkaiden konfliktien ennaltaehkäisemiseen sekä riitojen ratkaisemiseen asumiseen liittyvissä tilanteissa naapuruussovittelun ja naapurustotyön avulla. Asumisen toimijoiden sovitteluosaamisen lisäämiseen sekä asukkaiden yhteisöllisyyden lisäämiseen valtakunnallisten koulutusten avulla 
-(Asumisrauhan keskus) (245 858 €)</t>
+          <t>Ak 3: Lasten ja nuorten kokeman kiusaamisen ja häiriökäyttäytymisen vähentämiseen ja havaittujen tilanteiden käsittelyyn päiväkodeissa, kouluissa ja oppilaitoksissa. Vertaissovittelutoiminnan ja siihen liittyvän oppilaiden ja henkilökunnan vapaaehtoisen sovittelutyön ja restoratiivisen toiminnan tukemiseen koulutusten ja tiedottamisen kautta  (VERSO-ohjelma) (498 580 €) | Ak 6476: Asukkaiden konfliktien ennaltaehkäisemiseen sekä riitojen ratkaisemiseen asumiseen liittyvissä tilanteissa naapuruussovittelun ja naapurustotyön avulla. Asumisen toimijoiden sovitteluosaamisen lisäämiseen sekä asukkaiden yhteisöllisyyden lisäämiseen valtakunnallisten koulutusten avulla  (Asumisrauhan keskus) (245 858 €)</t>
         </is>
       </c>
     </row>
@@ -6347,7 +7389,7 @@
       </c>
       <c r="I95" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Huumeita käyttävien henkilöiden läheisten  huumeita käyttävien ja toipuvien vapaaehtois- ja vertaistoiminnalla toteuttavaan matalan kynnyksen tukeen sekä vapaaehtois- ja vertaistoiminnan koordinaatioon (170 000 €) | Ak 11324: Turvallisuuden tunteen  osallisuuden ja päihteettömyyden vahvistamiseen julkisiin tiloihin jalkautuvan Huudikoutsi-toiminnan avulla (126 000 €) | Ak 11245: Huumeita käyttävien henkilöiden  toipuvien ja heidän läheistensä voimavarojen ja toimintakyvyn lisäämiseen kynnyksettömällä kriisituella ja vertaisryhmätoiminnalla (95 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (342 720 €) | Ak 3: Huumeita käyttävien henkilöiden läheisten, huumeita käyttävien ja toipuvien vapaaehtois- ja vertaistoiminnalla toteuttavaan matalan kynnyksen tukeen sekä vapaaehtois- ja vertaistoiminnan koordinaatioon (170 000 €) | Ak 11324: Turvallisuuden tunteen, osallisuuden ja päihteettömyyden vahvistamiseen julkisiin tiloihin jalkautuvan Huudikoutsi-toiminnan avulla (126 000 €) | Ak 11245: Huumeita käyttävien henkilöiden, toipuvien ja heidän läheistensä voimavarojen ja toimintakyvyn lisäämiseen kynnyksettömällä kriisituella ja vertaisryhmätoiminnalla (95 000 €)</t>
         </is>
       </c>
     </row>
@@ -6380,9 +7422,7 @@
       </c>
       <c r="I96" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: För att stöda personer som har svårt att läsa eller förstå allmänspråk och öka deras tillgång till samhällsinformation och litteratur med hjälp av att producera och sprida lättläst material samt genom att främja högläsning inom omsorgen 
-(LL-Center - lätt språk och läsombudsverksamhet) (156 440 €) | Ak 10171: För stöd till familjer med barn  unga eller vuxna med intellektuell funktionsnedsättning med hjälp av kamratstöd  lokal förenings- och frivilligverksamhet samt genom att främja delaktighet i serviceprocesser (139 732 €) | Ak 3333: För att stöda självbestämmande  medvetande av rättigheter och inflytande i samhället hos svenskspråkiga personer med intellektuell funktionsnedsättning 
-(Steg för steg - för ett självständigt liv) (98 071 €)</t>
+          <t>Ay 1: Som allmänt understöd för understödstagarens allmännyttiga verksamhet (335 795 €) | Ak 3: För att stöda personer som har svårt att läsa eller förstå allmänspråk och öka deras tillgång till samhällsinformation och litteratur med hjälp av att producera och sprida lättläst material samt genom att främja högläsning inom omsorgen  (LL-Center - lätt språk och läsombudsverksamhet) (156 440 €) | Ak 10171: För stöd till familjer med barn, unga eller vuxna med intellektuell funktionsnedsättning med hjälp av kamratstöd, lokal förenings- och frivilligverksamhet samt genom att främja delaktighet i serviceprocesser (139 732 €) | Ak 3333: För att stöda självbestämmande, medvetande av rättigheter och inflytande i samhället hos svenskspråkiga personer med intellektuell funktionsnedsättning  (Steg för steg - för ett självständigt liv) (98 071 €)</t>
         </is>
       </c>
     </row>
@@ -6415,9 +7455,7 @@
       </c>
       <c r="I97" t="inlineStr" s="0">
         <is>
-          <t>Ay 4: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (302 764 €) | Ak 5: Ikäihmisten toimintakyvyn ylläpitämiseen  aivoterveyden edistämiseen ja muistisairaiden kotona pärjäämisen tukemiseen matalan kynnyksen kohtaamispaikoilla  ryhmätoiminnalla vertaistuella ja etsivällä kotikäyntityöllä sekä verkostotyöllä
-(Birgen ruovttus - Pärjään kotona) (270 139 €) | Ak 7: Päihteiden riskikäyttäjien päihteidenkäytön vähentämiseen ja elämänhallinnan vahvistamiseen asiakkaiden omassa toimintaympäristössä luontoa hyödyntävällä kulttuurisensitiivisellä ryhmätoiminnallla sekä yksilötapaamisilla 
-(Meacceterapija- Mettäterapija) (155 452 €)</t>
+          <t>Ay 4: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (302 764 €) | Ak 5: Ikäihmisten toimintakyvyn ylläpitämiseen, aivoterveyden edistämiseen ja muistisairaiden kotona pärjäämisen tukemiseen matalan kynnyksen kohtaamispaikoilla, ryhmätoiminnalla vertaistuella ja etsivällä kotikäyntityöllä sekä verkostotyöllä (Birgen ruovttus - Pärjään kotona) (270 139 €) | Ak 7: Päihteiden riskikäyttäjien päihteidenkäytön vähentämiseen ja elämänhallinnan vahvistamiseen asiakkaiden omassa toimintaympäristössä luontoa hyödyntävällä kulttuurisensitiivisellä ryhmätoiminnallla sekä yksilötapaamisilla  (Meacceterapija- Mettäterapija) (155 452 €)</t>
         </is>
       </c>
     </row>
@@ -6450,7 +7488,7 @@
       </c>
       <c r="I98" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (511 638 €) | Ak 2345: Etsivän vanhustyön yhteiskehittämisen ja verkostojen välisen yhteistyön koordinointiin. Etsivän vanhustyön menetelmien levittämiseen ja juurruttamiseen sekä osaamisen vahvistamiseen. (Etsivän vanhustyön verkostokeskus) (187 425 €) | Ak 4042: Heikoimmassa työmarkkina-asemassa  työelämän ja koulutuksen ulkopuolella olevien sekä opintojen nivelvaiheessa olevien nuorten työelämävalmiuksien sekä sukupolvien välisen yhteyden vahvistamiseen (Vanhustyön Trainee nuorille) (25 725 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (511 638 €) | Ak 2345: Etsivän vanhustyön yhteiskehittämisen ja verkostojen välisen yhteistyön koordinointiin. Etsivän vanhustyön menetelmien levittämiseen ja juurruttamiseen sekä osaamisen vahvistamiseen. (Etsivän vanhustyön verkostokeskus) (187 425 €) | Ak 4042: Heikoimmassa työmarkkina-asemassa, työelämän ja koulutuksen ulkopuolella olevien sekä opintojen nivelvaiheessa olevien nuorten työelämävalmiuksien sekä sukupolvien välisen yhteyden vahvistamiseen (Vanhustyön Trainee nuorille) (25 725 €)</t>
         </is>
       </c>
     </row>
@@ -6483,7 +7521,7 @@
       </c>
       <c r="I99" t="inlineStr" s="0">
         <is>
-          <t>Ak 5: Mielenterveysomaisten osallisuuden ja toimintakyvyn vahvistamiseen henkilökohtaisen tuen ja neuvonnan  vertaistuen ja muun ryhmätoiminnan sekä paikallisen vaikuttamisen avulla Uudenmaan alueella (719 426 €)</t>
+          <t>Ak 5: Mielenterveysomaisten osallisuuden ja toimintakyvyn vahvistamiseen henkilökohtaisen tuen ja neuvonnan, vertaistuen ja muun ryhmätoiminnan sekä paikallisen vaikuttamisen avulla Uudenmaan alueella (719 426 €)</t>
         </is>
       </c>
     </row>
@@ -6516,7 +7554,7 @@
       </c>
       <c r="I100" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (492 156 €) | Ak 4224: Autismiliiton vertais- ja kokemustoiminnan (VEKO-toiminnan) koordinointiin ja kehittämiseen. Toiminta sisältää vertaisosaaja- ja kokemustoiminnan   vertaisryhmäohjaajakoulutuksen sekä verkkovertaisryhmät. (132 300 €) | Ak 7: Jäsenjärjestöille kohdistettaviin avustuksiin (65 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (492 156 €) | Ak 4224: Autismiliiton vertais- ja kokemustoiminnan (VEKO-toiminnan) koordinointiin ja kehittämiseen. Toiminta sisältää vertaisosaaja- ja kokemustoiminnan,  vertaisryhmäohjaajakoulutuksen sekä verkkovertaisryhmät. (132 300 €) | Ak 7: Jäsenjärjestöille kohdistettaviin avustuksiin (65 000 €)</t>
         </is>
       </c>
     </row>
@@ -6582,7 +7620,7 @@
       </c>
       <c r="I102" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Järjestölähtöiseen kriisi- ja mielenterveystyöhön vaikeissa elämäntilanteissa oleville tarjoamalla matalan kynnyksen keskusteluapua  ammatillisesti ohjattuja ryhmiä ja tukihenkilötoimintaa (MIELI kriisikeskus Turku) (299 250 €) | Ak 2642: Pakolaistaustaisten ja muista vastaavista lähtökohdista Suomeen muuttaneiden ihmisten mielenterveyttä edistävien ryhmätoimintojen kehittämiseen  toteuttamiseen ja levittämiseen (Serene-toiminta) (153 761 €) | Ak 5581: Seksuaalista väkivaltaa kokeneiden  yli 16-vuotiaiden henkilöiden voimavarojen vahvistamiseen lyhytkestoisen kriisiavun  vertaisryhmätoiminnan sekä nuorille suunnatun  seksuaalioikeuksia ja turvataitoja koskevan ennaltaehkäisevän tiedonvälityksen avulla (Koski-seksuaaliväkivaltatyö Turun alueella) (145 905 €)</t>
+          <t>Ak 1: Järjestölähtöiseen kriisi- ja mielenterveystyöhön vaikeissa elämäntilanteissa oleville tarjoamalla matalan kynnyksen keskusteluapua, ammatillisesti ohjattuja ryhmiä ja tukihenkilötoimintaa (MIELI kriisikeskus Turku) (299 250 €) | Ak 2642: Pakolaistaustaisten ja muista vastaavista lähtökohdista Suomeen muuttaneiden ihmisten mielenterveyttä edistävien ryhmätoimintojen kehittämiseen, toteuttamiseen ja levittämiseen (Serene-toiminta) (153 761 €) | Ak 5581: Seksuaalista väkivaltaa kokeneiden, yli 16-vuotiaiden henkilöiden voimavarojen vahvistamiseen lyhytkestoisen kriisiavun, vertaisryhmätoiminnan sekä nuorille suunnatun, seksuaalioikeuksia ja turvataitoja koskevan ennaltaehkäisevän tiedonvälityksen avulla (Koski-seksuaaliväkivaltatyö Turun alueella) (145 905 €) | Ak 3: Turun seudulla asuvien läheisensä menettäneiden henkilöiden tukemiseen ja voimavarojen vahvistamiseen ammatillisella kriisityöllä, vertaistukitoiminnoilla ja merkityksellisen vapaaehtoistyön keinoin (Feeniks) (90 000 €)</t>
         </is>
       </c>
     </row>
@@ -6681,7 +7719,7 @@
       </c>
       <c r="I105" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Mielenterveysomaisten hyvinvoinnin ja osallisuuden vahvistamiseen omaisneuvonnan  koulutus-  kurssi-  vertais- ja virkistystoiminnan sekä yhteiskunnallisen vaikuttamisen avulla Pirkanmaalla (676 800 €)</t>
+          <t>Ak 3: Mielenterveysomaisten hyvinvoinnin ja osallisuuden vahvistamiseen omaisneuvonnan, koulutus-, kurssi-, vertais- ja virkistystoiminnan sekä yhteiskunnallisen vaikuttamisen avulla Pirkanmaalla (676 800 €)</t>
         </is>
       </c>
     </row>
@@ -6714,7 +7752,7 @@
       </c>
       <c r="I106" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (459 263 €) | Ak 5940: Yhdenvertaisuuden edistämiseen kodin ja kasvuyhteisöjen (päiväkoti ja koulu) yhteistyössä  vanhempaintoiminnassa sekä lasten ja nuorten kasvuyhteisöissä tiedottamalla ja kouluttamalla (Yhdenvertaisuus vanhempaintoiminnassa sekä lasten ja nuorten kasvuyhteisöissä) (154 350 €) | Ak 5: Jäsenjärjestöille kohdistettaviin avustuksiin (38 850 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (459 263 €) | Ak 5940: Yhdenvertaisuuden edistämiseen kodin ja kasvuyhteisöjen (päiväkoti ja koulu) yhteistyössä, vanhempaintoiminnassa sekä lasten ja nuorten kasvuyhteisöissä tiedottamalla ja kouluttamalla (Yhdenvertaisuus vanhempaintoiminnassa sekä lasten ja nuorten kasvuyhteisöissä) (154 350 €) | Ak 5: Jäsenjärjestöille kohdistettaviin avustuksiin (38 850 €) | Ak 3: Valtakunnallisen vuosittaisen Kodin ja Koulun päivän järjestämiseen edistämään kodin ja koulun kumppanuutta lasten ja nuorten parhaaksi sekä vahvistamaan kodin ja koulun yhteistyötä (18 000 €)</t>
         </is>
       </c>
     </row>
@@ -6747,7 +7785,7 @@
       </c>
       <c r="I107" t="inlineStr" s="0">
         <is>
-          <t>Ak 1367: Lastensuojelun asiakasvanhempien ja heidän läheistensä osallisuuden ja hyvinvoinnin vahvistamiseen kokemusasiantuntijuuteen perustuvan toiminnan keinoin. Toimintamuotoja ovat vertaistukiryhmät  -kahvilat  verkkotapaamiset  puhelinneuvonta  vertaistukihenkilötoiminta  kokemusasiantuntijatoiminta ja ammattilaisten kouluttaminen. (VOIKUKKIA-toiminta) (275 100 €) | Ak 5: Vanhempien eron kokeneiden lasten ja nuorten hyvinvoinnin vahvistamiseen vertaistoiminnan keinoin  vanhemmuuden vahvistamiseen sekä perheiden kanssa työskentelevien ammattilaisten osaamisen lisäämiseen (198 655 €) | Ay 1874: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (187 425 €)</t>
+          <t>Ak 1367: Lastensuojelun asiakasvanhempien ja heidän läheistensä osallisuuden ja hyvinvoinnin vahvistamiseen kokemusasiantuntijuuteen perustuvan toiminnan keinoin. Toimintamuotoja ovat vertaistukiryhmät, -kahvilat, verkkotapaamiset, puhelinneuvonta, vertaistukihenkilötoiminta, kokemusasiantuntijatoiminta ja ammattilaisten kouluttaminen. (VOIKUKKIA-toiminta) (275 100 €) | Ak 5: Vanhempien eron kokeneiden lasten ja nuorten hyvinvoinnin vahvistamiseen vertaistoiminnan keinoin, vanhemmuuden vahvistamiseen sekä perheiden kanssa työskentelevien ammattilaisten osaamisen lisäämiseen (198 655 €) | Ay 1874: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (187 425 €)</t>
         </is>
       </c>
     </row>
@@ -6780,7 +7818,7 @@
       </c>
       <c r="I108" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (352 800 €) | Ak 12056: Rikosseuraamuksen piirissä  asunnottomana tai päihderiippuvuuden kanssa elävien naisten hyvinvoinnin edistämiseen vertaisryhmätoiminnan ja ammattilaisten osaamisen lisäämisen avulla (305 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (352 800 €) | Ak 12056: Rikosseuraamuksen piirissä, asunnottomana tai päihderiippuvuuden kanssa elävien naisten hyvinvoinnin edistämiseen vertaisryhmätoiminnan ja ammattilaisten osaamisen lisäämisen avulla (305 000 €)</t>
         </is>
       </c>
     </row>
@@ -6813,7 +7851,7 @@
       </c>
       <c r="I109" t="inlineStr" s="0">
         <is>
-          <t>Ak 5649: Vauvaperheiden päihteettömän ja turvallisen arjen vahvistamiseen sekä päihteiden aiheuttamien haittojen ehkäisemiseen vauvalle kohtaavan etsivän ja matalan kynnyksen työllä  ja yhteisöllisellä vertaisryhmä-  perhe- ja yksilötyöskentelyllä. Tavoitteena on tukea vauvan ja vanhemman välistä vuorovaikutusta sekä edistää vauvaperheiden osallisuutta. (Pidä kiinni –hoitojärjestelmän avopalveluyksikkö Liina 2026) (251 340 €) | Ak 3305: Avokriisityöhön väkivallan kokijoiden  tekijöiden ja altistuneiden kanssa sekä eroperheiden tukemiseen yksilö-  pari- ja ryhmätoiminnan keinoin (Kriisi- ja väkivaltatyön yksikkö Väkevä  avopalvelutoiminta ja kriisityö) (197 532 €) | Ak 5658: Vauvaperheiden vanhemmuuden ja vuorovaikutuksen tukemiseen intensiivisen ryhmätoiminnan keinoin sekä vanhempien jaksamisen ja masennuksesta toipumisen tukemiseen tarjoamalla lyhytkestoista vauvaperheohjausta ja uniohjausta (Vanhemmuuden tukiyksikkö Helmi) (195 300 €)</t>
+          <t>Ak 5649: Vauvaperheiden päihteettömän ja turvallisen arjen vahvistamiseen sekä päihteiden aiheuttamien haittojen ehkäisemiseen vauvalle kohtaavan etsivän ja matalan kynnyksen työllä, ja yhteisöllisellä vertaisryhmä-, perhe- ja yksilötyöskentelyllä. Tavoitteena on tukea vauvan ja vanhemman välistä vuorovaikutusta sekä edistää vauvaperheiden osallisuutta. (Pidä kiinni –hoitojärjestelmän avopalveluyksikkö Liina 2026) (251 340 €) | Ak 3305: Avokriisityöhön väkivallan kokijoiden, tekijöiden ja altistuneiden kanssa sekä eroperheiden tukemiseen yksilö-, pari- ja ryhmätoiminnan keinoin (Kriisi- ja väkivaltatyön yksikkö Väkevä, avopalvelutoiminta ja kriisityö) (197 532 €) | Ak 5658: Vauvaperheiden vanhemmuuden ja vuorovaikutuksen tukemiseen intensiivisen ryhmätoiminnan keinoin sekä vanhempien jaksamisen ja masennuksesta toipumisen tukemiseen tarjoamalla lyhytkestoista vauvaperheohjausta ja uniohjausta (Vanhemmuuden tukiyksikkö Helmi) (195 300 €)</t>
         </is>
       </c>
     </row>
@@ -6846,7 +7884,7 @@
       </c>
       <c r="I110" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (372 797 €) | Ak 2836: Ikäihmisiä hoitavien perhehoitajien järjestölähtöiseen tukeen ja edunvalvontaan (Tunne ja turvaa ikäihmisten hyvä perhehoito) (153 596 €) | Ak 2: Sijaiskotinuorten hyvinvoinnin lisäämiseen vertaistukitoiminnan avulla (92 031 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (372 797 €) | Ak 2836: Ikäihmisiä hoitavien perhehoitajien järjestölähtöiseen tukeen ja edunvalvontaan (Tunne ja turvaa ikäihmisten hyvä perhehoito) (153 596 €) | Ak 2: Sijaiskotinuorten hyvinvoinnin lisäämiseen vertaistukitoiminnan avulla (92 031 €) | Ak 4: Jäsenjärjestöille kohdistettaviin avustuksiin (24 150 €)</t>
         </is>
       </c>
     </row>
@@ -6879,7 +7917,7 @@
       </c>
       <c r="I111" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Maahanmuuttajataustaisten nuorten ja alaikäisinä yksintulleiden turvapaikanhakijataustaisten nuorten tukemiseen ryhmätoiminnan  leirien  retkien  tapahtumien ja yksilöllisen ohjauksen avulla (Maahanmuuttajanuorten tukitoiminta) (170 595 €) | Ak 6009: Pakolaistaustaisten 14-29-vuotiaiden nuorten työelämävalmiuksien lisäämiseen ja työllisyyden edistämiseen ohjauksen avulla (Kannustavat kokemukset -toiminta) (170 100 €) | Ak 4435: Koira-avusteiseen lasten ja nuorten vapaaehtoiseen tukihenkilötoimintaan 7-17 -vuotiaille lapsille ja nuorille (Ressu-toiminta) sekä sijaishuollosta itsenäistyvien nuorten vapaaehtoiseen tukihenkilötoimintaan siirtymävaiheessa (Omilleen toiminta) (104 737 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (196 819 €) | Ak 2: Maahanmuuttajataustaisten nuorten ja alaikäisinä yksintulleiden turvapaikanhakijataustaisten nuorten tukemiseen ryhmätoiminnan, leirien, retkien, tapahtumien ja yksilöllisen ohjauksen avulla (Maahanmuuttajanuorten tukitoiminta) (170 595 €) | Ak 6009: Pakolaistaustaisten 14-29-vuotiaiden nuorten työelämävalmiuksien lisäämiseen ja työllisyyden edistämiseen ohjauksen avulla (Kannustavat kokemukset -toiminta) (170 100 €) | Ak 4435: Koira-avusteiseen lasten ja nuorten vapaaehtoiseen tukihenkilötoimintaan 7-17 -vuotiaille lapsille ja nuorille (Ressu-toiminta) sekä sijaishuollosta itsenäistyvien nuorten vapaaehtoiseen tukihenkilötoimintaan siirtymävaiheessa (Omilleen toiminta) (104 737 €)</t>
         </is>
       </c>
     </row>
@@ -6912,13 +7950,7 @@
       </c>
       <c r="I112" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Uudenmaan alueella 
-- vertaisryhmätoiminnalla
-- ohjauksella ja neuvonnalla
-- vapaaehtoistoiminnalla
-- tiedotuksella
-- edunvalvonnalla
-(Muistiluotsi) (638 625 €)</t>
+          <t>Ak 1: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Uudenmaan alueella  - vertaisryhmätoiminnalla - ohjauksella ja neuvonnalla - vapaaehtoistoiminnalla - tiedotuksella - edunvalvonnalla (Muistiluotsi) (638 625 €)</t>
         </is>
       </c>
     </row>
@@ -6951,7 +7983,7 @@
       </c>
       <c r="I113" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (462 978 €) | Ak 6: Vammaisten  pitkäaikaissairaiden ja osatyökykyisten henkilöiden työllistymismahdollisuuksien ja osallisuuden edistämiseen valtakunnallisen ja alueellisen verkostotoiminnan  tiedon tuottamisen sekä kehittämis- ja koordinaatiotyön keinoin (172 596 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (462 978 €) | Ak 6: Vammaisten, pitkäaikaissairaiden ja osatyökykyisten henkilöiden työllistymismahdollisuuksien ja osallisuuden edistämiseen valtakunnallisen ja alueellisen verkostotoiminnan, tiedon tuottamisen sekä kehittämis- ja koordinaatiotyön keinoin (172 596 €)</t>
         </is>
       </c>
     </row>
@@ -6984,7 +8016,7 @@
       </c>
       <c r="I114" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Alaikäisten lasten vanhempien ja maahanmuuttajaäitien vanhemmuuden tukeen sekä lasten ja nuorten osallisuuden tukemiseen   yksinäisyyden ehkäisemiseen ammatillisesti ohjatun vapaaehtoisen tukihenkilötoiminnan keinoin (Kaveri-  Perhekummi- ja Ystäväksi maahanmuuttajaäidille - toiminta Järvi-Suomessa) (319 869 €) | Ak 11274: Kiusaamista kokeneiden lasten ja nuorten tukemiseen sekä kiusaamisen jälkihoitoon liittyvän osaamisen lisäämiseen. Selviytyjät-vertaisryhmien järjestämiseen kiusaamista kokeneille noin 12–21-vuotiaille nuorille. (315 672 €)</t>
+          <t>Ak 2: Alaikäisten lasten vanhempien ja maahanmuuttajaäitien vanhemmuuden tukeen sekä lasten ja nuorten osallisuuden tukemiseen,  yksinäisyyden ehkäisemiseen ammatillisesti ohjatun vapaaehtoisen tukihenkilötoiminnan keinoin (Kaveri-, Perhekummi- ja Ystäväksi maahanmuuttajaäidille - toiminta Järvi-Suomessa) (319 869 €) | Ak 11274: Kiusaamista kokeneiden lasten ja nuorten tukemiseen sekä kiusaamisen jälkihoitoon liittyvän osaamisen lisäämiseen. Selviytyjät-vertaisryhmien järjestämiseen kiusaamista kokeneille noin 12–21-vuotiaille nuorille. (315 672 €)</t>
         </is>
       </c>
     </row>
@@ -7017,10 +8049,7 @@
       </c>
       <c r="I115" t="inlineStr" s="0">
         <is>
-          <t>Ak 10332: Vetureina toimivien lastensuojelun kokemusasiantuntijoiden valmentamiseen
-ja tukemiseen ja työmahdollisuuksien tarjoamiseen sekä lastensuojelun
-piirissä oleville/olleille nuorille suunnattuun Veturien antamaan yksilötukeen 
-ryhmämuotoisiin toimintoihin ja etätukeen sekä kokemusasiantuntemukseen perustuvaan kehittämis- ja vaikuttamistoimintaan (Veturointi-toiminta) (325 240 €) | Ak 7747: Monilapsisten perheiden sujuvan arjen tukemiseen vapaaehtoistoiminnalla Oulussa (Lapsirikas-toiminta) (157 000 €) | C 13648: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Järjestövarikko 2.0" osarahoitukseen järjestölle (2026-2028) (153 192 €)</t>
+          <t>Ak 10332: Vetureina toimivien lastensuojelun kokemusasiantuntijoiden valmentamiseen ja tukemiseen ja työmahdollisuuksien tarjoamiseen sekä lastensuojelun piirissä oleville/olleille nuorille suunnattuun Veturien antamaan yksilötukeen, ryhmämuotoisiin toimintoihin ja etätukeen sekä kokemusasiantuntemukseen perustuvaan kehittämis- ja vaikuttamistoimintaan (Veturointi-toiminta) (325 240 €) | Ak 7747: Monilapsisten perheiden sujuvan arjen tukemiseen vapaaehtoistoiminnalla Oulussa (Lapsirikas-toiminta) (157 000 €) | C 13648: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Järjestövarikko 2.0" osarahoitukseen järjestölle (2026-2028) (153 192 €)</t>
         </is>
       </c>
     </row>
@@ -7086,9 +8115,7 @@
       </c>
       <c r="I117" t="inlineStr" s="0">
         <is>
-          <t>Ak 11888: Monikulttuuri-  maahanmuuttaja- tai kotoutumistyötä tekevien järjestöjen digitaitojen lisäämiseen sekä digitukea kehittävien tahojen kulttuurisensitiivisen työotteen vahvistamiseen matalan kynnyksen digituen  materiaalien  koulutusten ja sidosryhmätyön avulla
-(DigiUp 2026) (139 145 €) | Ak 5663: Asumisen ongelmien ja asunnottomuuden ennaltaehkäisemiseen sekä asumisen ongelmia kohdanneiden vieraskielisten auttamiseen yksilöllisen neuvonnan ja ohjauksen  tiedon jakamisen  ammattilaisten kouluttamisen ja sidosryhmätyön avulla
-(Katto-toiminta) (125 851 €) | C 13822: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Aktiivinen toimijuus" osarahoitukseen järjestölle (2026-2027) (24 092 €)</t>
+          <t>Ay 3029: Yleisavustuksena järjestön yleishyödylliseen toimintaan (239 904 €) | Ak 11888: Monikulttuuri-, maahanmuuttaja- tai kotoutumistyötä tekevien järjestöjen digitaitojen lisäämiseen sekä digitukea kehittävien tahojen kulttuurisensitiivisen työotteen vahvistamiseen matalan kynnyksen digituen, materiaalien, koulutusten ja sidosryhmätyön avulla (DigiUp 2026) (139 145 €) | Ak 5663: Asumisen ongelmien ja asunnottomuuden ennaltaehkäisemiseen sekä asumisen ongelmia kohdanneiden vieraskielisten auttamiseen yksilöllisen neuvonnan ja ohjauksen, tiedon jakamisen, ammattilaisten kouluttamisen ja sidosryhmätyön avulla (Katto-toiminta) (125 851 €) | Ak 1775: Jäsenjärjestöille kohdistettaviin avustuksiin (100 000 €) | C 13822: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Aktiivinen toimijuus" osarahoitukseen järjestölle (2026-2027) (24 092 €)</t>
         </is>
       </c>
     </row>
@@ -7121,7 +8148,7 @@
       </c>
       <c r="I118" t="inlineStr" s="0">
         <is>
-          <t>Ak 2287: Psyykkistä kuormittuneisuutta  lieviä mielenterveysoireita tai yksinäisyyttä kokevien korkeakouluopiskelijoiden tukemiseen vertaistukitoiminnan  vapaaehtoistoiminnan  kahdenkeskisen keskusteluavun  tietosisältöjen tarjoamisen ja tapahtumatoiminnan avulla (359 790 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (263 088 €)</t>
+          <t>Ak 2287: Psyykkistä kuormittuneisuutta, lieviä mielenterveysoireita tai yksinäisyyttä kokevien korkeakouluopiskelijoiden tukemiseen vertaistukitoiminnan, vapaaehtoistoiminnan, kahdenkeskisen keskusteluavun, tietosisältöjen tarjoamisen ja tapahtumatoiminnan avulla (359 790 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (263 088 €)</t>
         </is>
       </c>
     </row>
@@ -7154,7 +8181,7 @@
       </c>
       <c r="I119" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Kansalaistoiminnankeskus Mataran toimintaan  alueen sote-järjestöjen tukemiseen  vapaaehtoistyön kehittämiseen ja koordinointiin sekä OLKA - toiminnan toteuttamiseen (255 780 €) | Ak 1: Järjestöjen tuki- ja kehittämistoimintoihin Keski-Suomessa (190 798 €) | Ay 1957: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan. (173 375 €)</t>
+          <t>Ak 3: Kansalaistoiminnankeskus Mataran toimintaan, alueen sote-järjestöjen tukemiseen, vapaaehtoistyön kehittämiseen ja koordinointiin sekä OLKA - toiminnan toteuttamiseen (255 780 €) | Ak 1: Järjestöjen tuki- ja kehittämistoimintoihin Keski-Suomessa (190 798 €) | Ay 1957: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan. (173 375 €)</t>
         </is>
       </c>
     </row>
@@ -7187,7 +8214,7 @@
       </c>
       <c r="I120" t="inlineStr" s="0">
         <is>
-          <t>Ak 5735: Sosiaalisten taitojen  arjenhallinnan  psyykkisten voimavarojen ja osallisuuden vahvistamiseen vertaistuellisen ryhmätoiminnan keinoin eri-ikäisille moniongelmaisille  työttömille tai työ- ja opiskeluelämän ulkopuolella oleville nuorille ja aikuisille (Poveria-toiminta) (406 660 €) | Ak 7678: Ikääntyneiden yksinäisyyden ennaltaehkäisemiseen ja vähentämiseen kuvapuheluvälitteisen pienryhmätoiminnan avulla Päijät- ja Kanta-Hämeessä (Ruutuystävät-toiminta) (124 520 €) | C 13785: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Digikokemusosaaja" osarahoitukseen säätiölle (2026-2028) (87 914 €)</t>
+          <t>Ak 5735: Sosiaalisten taitojen, arjenhallinnan, psyykkisten voimavarojen ja osallisuuden vahvistamiseen vertaistuellisen ryhmätoiminnan keinoin eri-ikäisille moniongelmaisille, työttömille tai työ- ja opiskeluelämän ulkopuolella oleville nuorille ja aikuisille (Poveria-toiminta) (406 660 €) | Ak 7678: Ikääntyneiden yksinäisyyden ennaltaehkäisemiseen ja vähentämiseen kuvapuheluvälitteisen pienryhmätoiminnan avulla Päijät- ja Kanta-Hämeessä (Ruutuystävät-toiminta) (124 520 €) | C 13785: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Digikokemusosaaja" osarahoitukseen säätiölle (2026-2028) (87 914 €)</t>
         </is>
       </c>
     </row>
@@ -7220,7 +8247,7 @@
       </c>
       <c r="I121" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (427 800 €) | Ak 7: Henkilökohtaiseen apuun liittyvän tietoisuuden lisäämiseen neuvontatoiminnalla  koulutuksilla  tiedontuotannolla sekä asiantuntija- ja osaamisverkoston koordinoinnilla (assistentti.info) (191 100 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (427 800 €) | Ak 7: Henkilökohtaiseen apuun liittyvän tietoisuuden lisäämiseen neuvontatoiminnalla, koulutuksilla, tiedontuotannolla sekä asiantuntija- ja osaamisverkoston koordinoinnilla (assistentti.info) (191 100 €)</t>
         </is>
       </c>
     </row>
@@ -7286,7 +8313,7 @@
       </c>
       <c r="I123" t="inlineStr" s="0">
         <is>
-          <t>Ak 11135: Erityistä tukea tarvitsevien nuorten aikuisten terveyttä ja hyvinvointia tukevaan kohtaamispaikkatoimintaan  ryhmätoimintaan  vapaaehtoistyöhön ja yksilölliseen tukeen (237 951 €) | Ak 4350: 18-35-vuotiaiden mielenterveyskuntoutujien osallisuuden tunteen ja motivaation kasvattamiseen sekä työ- ja toimintakyvyn edistämiseen järjestämällä ohjattuun toiminnalliseen vertaistukeen perustuvaa kulttuuripajatoimintaa (190 000 €) | Ak 3: Mielenterveyskuntoutujien terveyttä  hyvinvointia  osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään tavoitteelliseen kohtaamispaikkatoimintaan  (Porin klubitalo Sarastus) (178 605 €)</t>
+          <t>Ak 11135: Erityistä tukea tarvitsevien nuorten aikuisten terveyttä ja hyvinvointia tukevaan kohtaamispaikkatoimintaan, ryhmätoimintaan, vapaaehtoistyöhön ja yksilölliseen tukeen (237 951 €) | Ak 4350: 18-35-vuotiaiden mielenterveyskuntoutujien osallisuuden tunteen ja motivaation kasvattamiseen sekä työ- ja toimintakyvyn edistämiseen järjestämällä ohjattuun toiminnalliseen vertaistukeen perustuvaa kulttuuripajatoimintaa (190 000 €) | Ak 3: Mielenterveyskuntoutujien terveyttä, hyvinvointia, osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään tavoitteelliseen kohtaamispaikkatoimintaan  (Porin klubitalo Sarastus) (178 605 €)</t>
         </is>
       </c>
     </row>
@@ -7319,8 +8346,7 @@
       </c>
       <c r="I124" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (299 520 €) | Ak 6: Sukupuolivähemmistöihin kuuluvien ja heidän läheistensä terveyden ja hyvinvoinnin edistämiseen ammattiohjatun vertaistuen  neuvonnan  yksilötapaamisten  kouluttamisen ja tiedottamisen avulla
-(Sukupuolen moninaisuuden osaamiskeskus) (253 640 €) | Ak 7: Jäsenjärjestöille kohdistettaviin avustuksiin (52 500 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (299 520 €) | Ak 6: Sukupuolivähemmistöihin kuuluvien ja heidän läheistensä terveyden ja hyvinvoinnin edistämiseen ammattiohjatun vertaistuen, neuvonnan, yksilötapaamisten, kouluttamisen ja tiedottamisen avulla (Sukupuolen moninaisuuden osaamiskeskus) (253 640 €) | Ak 7: Jäsenjärjestöille kohdistettaviin avustuksiin (52 500 €)</t>
         </is>
       </c>
     </row>
@@ -7353,7 +8379,7 @@
       </c>
       <c r="I125" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (329 700 €) | Ak 5: Alueellisten mielenterveysomaisjärjestöjen toimintaedellytysten vahvistamiseen kehittämällä ja koordinoimalla yhdistysten hallintoa  omaistyötä  vaikuttamistoimintaa sekä vapaaehtoistyötä (267 750 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (329 700 €) | Ak 5: Alueellisten mielenterveysomaisjärjestöjen toimintaedellytysten vahvistamiseen kehittämällä ja koordinoimalla yhdistysten hallintoa, omaistyötä, vaikuttamistoimintaa sekä vapaaehtoistyötä (267 750 €)</t>
         </is>
       </c>
     </row>
@@ -7386,7 +8412,7 @@
       </c>
       <c r="I126" t="inlineStr" s="0">
         <is>
-          <t>Ak 4: För främjande av svenskspråkiga synskadades tillgång till information och ökade delaktighet genom kommunikations- och punktskriftsverksamhet samt utgivning av svenskspråkiga tal- och punktskriftstidningar (256 706 €) | Ay 1: Som allmänt understöd för understödstagarens allmännyttiga verksamhet (110 000 €) | Ak 4282: För understöd som allokeras till medlemsorganisationer (55 990 €)</t>
+          <t>Ak 4: För främjande av svenskspråkiga synskadades tillgång till information och ökade delaktighet genom kommunikations- och punktskriftsverksamhet samt utgivning av svenskspråkiga tal- och punktskriftstidningar (256 706 €) | Ak 3: För ökad delaktighet och förbättrade synskadefärdigheter för svenskspråkiga personer med synnedsättning och påtagliga synutmaningar med hjälp av handledning och rådgivning, it-utbildning och kamratstöd (161 500 €) | Ay 1: Som allmänt understöd för understödstagarens allmännyttiga verksamhet (110 000 €) | Ak 4282: För understöd som allokeras till medlemsorganisationer (55 990 €)</t>
         </is>
       </c>
     </row>
@@ -7419,7 +8445,7 @@
       </c>
       <c r="I127" t="inlineStr" s="0">
         <is>
-          <t>Ak 6: Mielenterveyskuntoutujien osallisuuden ja toimintakyvyn vahvistamiseen kohtaamispaikkatoiminnan  vertaistuen  vapaaehtois- ja tukihenkilötoiminnan sekä palveluohjauksen keinoin Helsingissä (Helmi-talo) (581 990 €)</t>
+          <t>Ak 6: Mielenterveyskuntoutujien osallisuuden ja toimintakyvyn vahvistamiseen kohtaamispaikkatoiminnan, vertaistuen, vapaaehtois- ja tukihenkilötoiminnan sekä palveluohjauksen keinoin Helsingissä (Helmi-talo) (581 990 €)</t>
         </is>
       </c>
     </row>
@@ -7452,8 +8478,7 @@
       </c>
       <c r="I128" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Väkivaltaa tai sen uhkaa kokeneiden tyttöjen ja naisten selviytymisen ja toipumisen tukemiseksi sekä vaikuttamistyöhön ja viestintään naisiin kohdistuvan väkivallan ehkäisemiseksi.  
-Matalan kynnyksen anonyymiin puhelin- ja chat-päivystykseen  verkossa tehtävään jalkautuvaan työhön  yksilölliseen tukeen sekä verkkovertaisryhmiin. (578 183 €)</t>
+          <t>Ak 2: Väkivaltaa tai sen uhkaa kokeneiden tyttöjen ja naisten selviytymisen ja toipumisen tukemiseksi sekä vaikuttamistyöhön ja viestintään naisiin kohdistuvan väkivallan ehkäisemiseksi.    Matalan kynnyksen anonyymiin puhelin- ja chat-päivystykseen, verkossa tehtävään jalkautuvaan työhön, yksilölliseen tukeen sekä verkkovertaisryhmiin. (578 183 €)</t>
         </is>
       </c>
     </row>
@@ -7486,7 +8511,7 @@
       </c>
       <c r="I129" t="inlineStr" s="0">
         <is>
-          <t>Ak 9: Sosiaalisin  terveydellisin ja taloudellisin perustein valittujen perheiden ja aikuisten terveyttä edistävään internaattimuotoiseen hyvinvointikurssitoimintaan sekä toiminnan kehittämistyöhön (570 704 €)</t>
+          <t>Ak 9: Sosiaalisin, terveydellisin ja taloudellisin perustein valittujen perheiden ja aikuisten terveyttä edistävään internaattimuotoiseen hyvinvointikurssitoimintaan sekä toiminnan kehittämistyöhön (570 704 €)</t>
         </is>
       </c>
     </row>
@@ -7519,7 +8544,7 @@
       </c>
       <c r="I130" t="inlineStr" s="0">
         <is>
-          <t>Ak 11703: Huolta  turvattomuutta  uhkaa tai apua tarvitsevien 7-15 vuotiaiden lasten yhteydenottoihin vastaamiseen ammattilaisten ja koulutettujen vapaaehtoisten avulla (Apuu-chat) (352 800 €) | Ak 10148: Lapsiperheiden ja toimintaa järjestävien vapaaehtoisten ikäihmisten voimavarojen  merkityksellisyyden ja osallisuuden vahvistamiseen omassa elämässä ja lähiyhteisössä kohtaamispaikkatoiminnan avulla sekä toiminnan koordinointiin  (Mummun ja vaarin tupa -toiminta) (130 000 €) | Ak 7488: Lastensuojelutaustaisille  päihdeongelmista kärsiville sekä sukupuoli- ja seksuaalivähemmistöihin kuuluville yli 17-vuotiaille nuorille ja aikuisille tarkoitetun vertaismentoritoiminnan ylläpitämiseen ja kehittämiseen Ylitse MentorApp -sovelluksen välityksellä (Ylitse MentorApp -vertaistukea verkossa) (85 000 €)</t>
+          <t>Ak 11703: Huolta, turvattomuutta, uhkaa tai apua tarvitsevien 7-15 vuotiaiden lasten yhteydenottoihin vastaamiseen ammattilaisten ja koulutettujen vapaaehtoisten avulla (Apuu-chat) (352 800 €) | Ak 10148: Lapsiperheiden ja toimintaa järjestävien vapaaehtoisten ikäihmisten voimavarojen, merkityksellisyyden ja osallisuuden vahvistamiseen omassa elämässä ja lähiyhteisössä kohtaamispaikkatoiminnan avulla sekä toiminnan koordinointiin  (Mummun ja vaarin tupa -toiminta) (130 000 €) | Ak 7488: Lastensuojelutaustaisille, päihdeongelmista kärsiville sekä sukupuoli- ja seksuaalivähemmistöihin kuuluville yli 17-vuotiaille nuorille ja aikuisille tarkoitetun vertaismentoritoiminnan ylläpitämiseen ja kehittämiseen Ylitse MentorApp -sovelluksen välityksellä (Ylitse MentorApp -vertaistukea verkossa) (85 000 €)</t>
         </is>
       </c>
     </row>
@@ -7552,13 +8577,7 @@
       </c>
       <c r="I131" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Varsinais-Suomessa ja Satakunnassa
-- vertaisryhmätoiminnalla
-- ohjauksella ja neuvonnalla
-- vapaaehtoistoiminnalla
-- tiedotuksella
-- edunvalvonnalla
-(Muistiluotsi) (479 102 €) | Ak 3081: För att främja den svenskspråkiga befolkningens hjärnhälsa och förstärka livskvaliteten och välbefinnandet hos personer med en minnessjukdom och deras närstående med förebyggande arbete (Hjärningar – förebyggande arbete förbättrar livskvaliteten) (85 000 €)</t>
+          <t>Ak 3: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Varsinais-Suomessa ja Satakunnassa - vertaisryhmätoiminnalla - ohjauksella ja neuvonnalla - vapaaehtoistoiminnalla - tiedotuksella - edunvalvonnalla (Muistiluotsi) (479 102 €) | Ak 3081: För att främja den svenskspråkiga befolkningens hjärnhälsa och förstärka livskvaliteten och välbefinnandet hos personer med en minnessjukdom och deras närstående med förebyggande arbete (Hjärningar – förebyggande arbete förbättrar livskvaliteten) (85 000 €)</t>
         </is>
       </c>
     </row>
@@ -7591,7 +8610,7 @@
       </c>
       <c r="I132" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (286 601 €) | Ak 7649: Pitkäaikaistyöttömien sekä työelämän ulkopuolella olevien hyvinvoinnin edistämiseen kouluttamalla työttömien yhdistyksiä sosiaali- ja terveysteemoista  ohjaamalla kohderyhmää terveystarkastuksiin sekä tarjoamalla henkilökohtaista neuvontaa palveluista ja elintavoista matalan kynnyksen kohtaamispaikoissa ja etäyhteyksin (Terveyttä työttömille) (244 184 €) | Ak 6: Jäsenjärjestöille kohdistettaviin avustuksiin (29 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (286 601 €) | Ak 7649: Pitkäaikaistyöttömien sekä työelämän ulkopuolella olevien hyvinvoinnin edistämiseen kouluttamalla työttömien yhdistyksiä sosiaali- ja terveysteemoista, ohjaamalla kohderyhmää terveystarkastuksiin sekä tarjoamalla henkilökohtaista neuvontaa palveluista ja elintavoista matalan kynnyksen kohtaamispaikoissa ja etäyhteyksin (Terveyttä työttömille) (244 184 €) | Ak 6: Jäsenjärjestöille kohdistettaviin avustuksiin (29 000 €)</t>
         </is>
       </c>
     </row>
@@ -7624,8 +8643,7 @@
       </c>
       <c r="I133" t="inlineStr" s="0">
         <is>
-          <t>Ak 4423: OLKA -toimintamallin toteuttamiseen HUSin sairaaloissa pääkaupunkiseudulla ja Länsi-Uudellamaalla  valtakunnallisen OLKA-verkoston konsultointiin sekä sairaalan ja järjestöjen yhteistoiminnan koordinointiin. Vertaistalo.fi -palvelun ja palvelurakenteen kehittämiseen vertaistuen saamiseksi osaksi potilaan palvelupolkua. Toivo-vertaistukisovelluksen koordinointiin ja kehittämiseen. (211 330 €) | Ak 2: Järjestö- ja vapaaehtoistoiminnan tukemiseen 
-sekä järjestöille tarjottavien tilojen ylläpitoon Espoossa (187 425 €) | Ay 1707: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (160 375 €)</t>
+          <t>Ak 4423: OLKA -toimintamallin toteuttamiseen HUSin sairaaloissa pääkaupunkiseudulla ja Länsi-Uudellamaalla, valtakunnallisen OLKA-verkoston konsultointiin sekä sairaalan ja järjestöjen yhteistoiminnan koordinointiin. Vertaistalo.fi -palvelun ja palvelurakenteen kehittämiseen vertaistuen saamiseksi osaksi potilaan palvelupolkua. Toivo-vertaistukisovelluksen koordinointiin ja kehittämiseen. (211 330 €) | Ak 2: Järjestö- ja vapaaehtoistoiminnan tukemiseen  sekä järjestöille tarjottavien tilojen ylläpitoon Espoossa (187 425 €) | Ay 1707: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (160 375 €)</t>
         </is>
       </c>
     </row>
@@ -7658,10 +8676,7 @@
       </c>
       <c r="I134" t="inlineStr" s="0">
         <is>
-          <t>Ak 10010: Nuorten syrjäytymistä ehkäisevään vapaa-ajan toimintaan Turun seudulla.
-(Yökoris) (147 000 €) | Ak 1: Palveluista syrjäytyneiden nuorten aikuisten matalan kynnyksen toimintaan sekä ryhmätoimintaan ja yksilölliseen tukeen
-(Nuorten kohtaamispaikka TOIVO) (136 739 €) | Ak 3: Muutoksia ja ongelmia kokeneiden maahanmuuttajien henkilökohtaiseen palveluohjaukseen suomen kielellä Turussa ja Turun lähikunnissa
-(Turun NMKY:n maahanmuuttajapalvelut) (134 505 €)</t>
+          <t>Ak 10010: Nuorten syrjäytymistä ehkäisevään vapaa-ajan toimintaan Turun seudulla. (Yökoris) (147 000 €) | Ak 10291: Nuorten tekemien rikosten, kiusaamisen ja ristiriitatilanteiden ehkäisemiseen ja selvittämiseen sovittelujen, seurantatapaamisten ja -yhteydenottojen sekä kouluihin jalkautumisen avulla Varsinais-Suomessa.  (Katusovittelua nuorille rikoksentekijöille ja nuorten välisten konfliktien selvittämiseen) (140 000 €) | Ak 1: Palveluista syrjäytyneiden nuorten aikuisten matalan kynnyksen toimintaan sekä ryhmätoimintaan ja yksilölliseen tukeen (Nuorten kohtaamispaikka TOIVO) (136 739 €) | Ak 3: Muutoksia ja ongelmia kokeneiden maahanmuuttajien henkilökohtaiseen palveluohjaukseen suomen kielellä Turussa ja Turun lähikunnissa (Turun NMKY:n maahanmuuttajapalvelut) (134 505 €)</t>
         </is>
       </c>
     </row>
@@ -7694,7 +8709,7 @@
       </c>
       <c r="I135" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Asunnottomien henkilöiden asuttamiseen ja asumisen onnistumisen tukemiseen erityisryhmille kohdennetulla asumisneuvonnalla ja tukiverkostotyöllä (370 000 €) | Ak 7361: Asunnottomuuden vähentämiseen valtakunnallisella verkostotyöllä ja yhteiskehittämisellä asunnottomien  asukkaiden ja henkilöstön kanssa kumppanuuksien asiantuntemusta hyödyntäen sekä Asunto ensin -periaatteen mukaisen työn  työorientaation ja -menetelmien juurruttamiseen asunnottomuustyöhön koulutuspäivien  kehittämispilottien  valmennuksien ja viestinnän avulla (185 426 €)</t>
+          <t>Ak 3: Asunnottomien henkilöiden asuttamiseen ja asumisen onnistumisen tukemiseen erityisryhmille kohdennetulla asumisneuvonnalla ja tukiverkostotyöllä (370 000 €) | Ak 7361: Asunnottomuuden vähentämiseen valtakunnallisella verkostotyöllä ja yhteiskehittämisellä asunnottomien, asukkaiden ja henkilöstön kanssa kumppanuuksien asiantuntemusta hyödyntäen sekä Asunto ensin -periaatteen mukaisen työn, työorientaation ja -menetelmien juurruttamiseen asunnottomuustyöhön koulutuspäivien, kehittämispilottien, valmennuksien ja viestinnän avulla (185 426 €)</t>
         </is>
       </c>
     </row>
@@ -7727,8 +8742,7 @@
       </c>
       <c r="I136" t="inlineStr" s="0">
         <is>
-          <t>Ay 4545: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (206 643 €) | Ak 1: Kunniaan liittyvän väkivallan eri muotojen torjumiseen ja ennaltaehkäisyyn. Kunniaväkivaltaa kokevien tai sen riskissä olevien henkilöiden seksuaali- ja lisääntymisoikeuksien ja itsemääräämisoikeuden vahvistamiseen sekä palveluihin pääsyn parantamiseen  terveyden ja hyvinvoinnin edistämiseen sekä oikeusturvan toteutumiseen. Vaikuttamis- ja verkostotyöhön asenteiden muuttamiseksi ja rakenteiden kehittämiseksi. (204 750 €) | Ak 11902: Köyhyyttä kokevien ihmisten osallisuuden vahvistamiseen sekä päättäjien ja suuren yleisön ymmärryksen lisäämiseen köyhyydestä ihmisoikeuskysymyksenä vaikuttajaryhmätoiminnan ja koulutusten sekä verkosto- ja vaikuttamistyön avulla
-(Köyhyys ja ihmisoikeudet) (140 000 €)</t>
+          <t>Ay 4545: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (206 643 €) | Ak 1: Kunniaan liittyvän väkivallan eri muotojen torjumiseen ja ennaltaehkäisyyn. Kunniaväkivaltaa kokevien tai sen riskissä olevien henkilöiden seksuaali- ja lisääntymisoikeuksien ja itsemääräämisoikeuden vahvistamiseen sekä palveluihin pääsyn parantamiseen, terveyden ja hyvinvoinnin edistämiseen sekä oikeusturvan toteutumiseen. Vaikuttamis- ja verkostotyöhön asenteiden muuttamiseksi ja rakenteiden kehittämiseksi. (204 750 €) | Ak 11902: Köyhyyttä kokevien ihmisten osallisuuden vahvistamiseen sekä päättäjien ja suuren yleisön ymmärryksen lisäämiseen köyhyydestä ihmisoikeuskysymyksenä vaikuttajaryhmätoiminnan ja koulutusten sekä verkosto- ja vaikuttamistyön avulla (Köyhyys ja ihmisoikeudet) (140 000 €)</t>
         </is>
       </c>
     </row>
@@ -7794,7 +8808,7 @@
       </c>
       <c r="I138" t="inlineStr" s="0">
         <is>
-          <t>Ay 1497: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (345 862 €) | Ak 1528: 10-18-vuotiaiden lasten ja nuorten hyvinvoinnin tukemiseen sekä heidän vanhempien vanhemmuuden vahvistamiseen yksilöllisen tuen  vertaisryhmätoiminnan  tilaisuuksien sekä tiedon ja materiaalien levittämisen keinoin (Linkki-toiminta) (183 750 €)</t>
+          <t>Ay 1497: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (345 862 €) | Ak 1528: 10-18-vuotiaiden lasten ja nuorten hyvinvoinnin tukemiseen sekä heidän vanhempien vanhemmuuden vahvistamiseen yksilöllisen tuen, vertaisryhmätoiminnan, tilaisuuksien sekä tiedon ja materiaalien levittämisen keinoin (Linkki-toiminta) (183 750 €)</t>
         </is>
       </c>
     </row>
@@ -7827,7 +8841,7 @@
       </c>
       <c r="I139" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Eri ikäisten erilaisten oppijoiden tukemiseen ja hyvinvoinnin lisäämiseen vapaaehtois- ja vertaistoiminnan  viestinnän sekä kurssien ja koulutusten avulla (263 847 €) | Ak 6176: Oppimisvaikeuksia kokevien pääsääntöisesti 18-29 -vuotiaiden nuorten syrjäytymisen ehkäisyyn ja NEET-nuorten syrjäytymiskierteen katkaisuun  oppimisen  arjenhallinnan  sosiaalisten taitojen sekä jatkokoulutus- ja työelämävalmiuksien edistämiseen yksilö- ja ryhmäohjauksen avulla (KITE Kohti itsenäistä elämää -kurssi  ASKELMA -toiminta  Vertsu -nuorten vertaisryhmä ja nuorten VAPARI -toiminta) (263 399 €)</t>
+          <t>Ak 1: Eri ikäisten erilaisten oppijoiden tukemiseen ja hyvinvoinnin lisäämiseen vapaaehtois- ja vertaistoiminnan, viestinnän sekä kurssien ja koulutusten avulla (263 847 €) | Ak 6176: Oppimisvaikeuksia kokevien pääsääntöisesti 18-29 -vuotiaiden nuorten syrjäytymisen ehkäisyyn ja NEET-nuorten syrjäytymiskierteen katkaisuun, oppimisen, arjenhallinnan, sosiaalisten taitojen sekä jatkokoulutus- ja työelämävalmiuksien edistämiseen yksilö- ja ryhmäohjauksen avulla (KITE Kohti itsenäistä elämää -kurssi, ASKELMA -toiminta, Vertsu -nuorten vertaisryhmä ja nuorten VAPARI -toiminta) (263 399 €)</t>
         </is>
       </c>
     </row>
@@ -7860,7 +8874,7 @@
       </c>
       <c r="I140" t="inlineStr" s="0">
         <is>
-          <t>Ak 2508: Eri ikäisten suolistosairautta sairastavien ja heidän läheistensä yhteisöllisyyden ja osallistumismahdollisuuksien edistämiseen monimuotoisella vertaistukitoiminnalla (Valtakunnallinen vapaaehtois- ja vertaistoiminta) (133 980 €) | Ak 11729: Yli 60-vuotiaiden ikääntyvien suolistosairauksia sairastavien ja heidän läheistensä voimavarojen lisäämiseen ryhmämuotoisen toiminnan avulla sekä tiedon jakamiseen eri viestintäkanavissa (78 000 €) | Ak 2: Tulehduksellista suolistosairautta (IBD) sairastavien ja heidän läheistensä hyvinvoinnin edistämiseen ammatillisesti ohjatun  vertaistuellisen ja tavoitteellisen ryhmätoiminnan keinoin (60 607 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (252 000 €) | Ak 2508: Eri ikäisten suolistosairautta sairastavien ja heidän läheistensä yhteisöllisyyden ja osallistumismahdollisuuksien edistämiseen monimuotoisella vertaistukitoiminnalla (Valtakunnallinen vapaaehtois- ja vertaistoiminta) (133 980 €) | Ak 11729: Yli 60-vuotiaiden ikääntyvien suolistosairauksia sairastavien ja heidän läheistensä voimavarojen lisäämiseen ryhmämuotoisen toiminnan avulla sekä tiedon jakamiseen eri viestintäkanavissa (78 000 €) | Ak 2: Tulehduksellista suolistosairautta (IBD) sairastavien ja heidän läheistensä hyvinvoinnin edistämiseen ammatillisesti ohjatun, vertaistuellisen ja tavoitteellisen ryhmätoiminnan keinoin (60 607 €)</t>
         </is>
       </c>
     </row>
@@ -7893,7 +8907,7 @@
       </c>
       <c r="I141" t="inlineStr" s="0">
         <is>
-          <t>Ak 6: Pikkulapsiperheiden  nuorten ja ikääntyneiden osallisuuden lisäämiseen ja yksilölliseen tukemiseen arjen haasteissa vapaaehtoistoiminnan keinoin (Särö-vapaaehtoistoiminta) (313 950 €) | Ak 4049: Vuorovaikutukseen keskittyvän tuen tarjoamiseen äitiyttä tai vauvaa kohtaan ristiriitaisia tunteita kokeville äideille pienryhmä- ja yksilötyöskentelyn keinoin (Vauvan Taika) (197 400 €)</t>
+          <t>Ak 6: Pikkulapsiperheiden, nuorten ja ikääntyneiden osallisuuden lisäämiseen ja yksilölliseen tukemiseen arjen haasteissa vapaaehtoistoiminnan keinoin (Särö-vapaaehtoistoiminta) (313 950 €) | Ak 4049: Vuorovaikutukseen keskittyvän tuen tarjoamiseen äitiyttä tai vauvaa kohtaan ristiriitaisia tunteita kokeville äideille pienryhmä- ja yksilötyöskentelyn keinoin (Vauvan Taika) (197 400 €)</t>
         </is>
       </c>
     </row>
@@ -7926,7 +8940,7 @@
       </c>
       <c r="I142" t="inlineStr" s="0">
         <is>
-          <t>Ak 7: Hiv-tartuntojen ehkäisemiseen sekä hiv-tartunnan saaneiden  heidän läheistensä sekä hiv-tartunnasta huolestuneiden tukemiseen  neuvontaan ja ohjaukseen. (509 250 €)</t>
+          <t>Ak 7: Hiv-tartuntojen ehkäisemiseen sekä hiv-tartunnan saaneiden, heidän läheistensä sekä hiv-tartunnasta huolestuneiden tukemiseen, neuvontaan ja ohjaukseen. (509 250 €)</t>
         </is>
       </c>
     </row>
@@ -7959,7 +8973,7 @@
       </c>
       <c r="I143" t="inlineStr" s="0">
         <is>
-          <t>Ak 1198: Lapsiperheiden hyvinvoinnin ja osallisuuden edistämiseen sekä varhaiseen tukemiseen avoimen kohtaamispaikkatoiminnan  vertaisryhmien  yksilöllisen ohjauksen ja moniammatillisen yhteistyön keinoin (PerhePesä - Yhdessä toimien perheiden parhaaksi) (184 172 €) | C 13824: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Omanlaisena Yhdessä" osarahoitukseen järjestölle (2026-2028) (76 695 €) | Ak 11085: Jäsenjärjestöille kohdistettaviin avustuksiin. (28 500 €)</t>
+          <t>Ak 11069: Alaikäisten lasten vanhempien ja maahan tulleiden äitien vanhemmuuden tukemiseen ja kotoutumisen edistämiseen sekä kouluikäisten lasten yksinäisyyden ehkäisemiseen, alakouluikäisten lasten koulumyönteisyyden lisäämiseen, sukupolvien välisen kohtaamisten mahdollistamiseen, lukemissujuvuuden edistämiseen ja ammatillisesti ohjatun mielekkään vapaaehtoistoiminnan koordinointiin Pohjois-Suomen piirin alueella (MLL:n Pohjois-Suomen piirin Perhekummi-, Ystäväksi maahanmuuttajaäidille-, Kaveri- ja Sukupolvitoiminta) (217 765 €) | Ak 1198: Lapsiperheiden hyvinvoinnin ja osallisuuden edistämiseen sekä varhaiseen tukemiseen avoimen kohtaamispaikkatoiminnan, vertaisryhmien, yksilöllisen ohjauksen ja moniammatillisen yhteistyön keinoin (PerhePesä - Yhdessä toimien perheiden parhaaksi) (184 172 €) | C 13824: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Omanlaisena Yhdessä" osarahoitukseen järjestölle (2026-2028) (76 695 €) | Ak 11085: Jäsenjärjestöille kohdistettaviin avustuksiin. (28 500 €)</t>
         </is>
       </c>
     </row>
@@ -7992,7 +9006,7 @@
       </c>
       <c r="I144" t="inlineStr" s="0">
         <is>
-          <t>Ak 4: Vaikeissa elämänmuutostilanteissa olevien yli 65 -vuotiaiden psykososiaalisen hyvinvoinnin tukemiseen ryhmämuotoisen tuen ja tukihenkilötoiminnan keinoin (Senioripysäkki) (154 350 €) | Ak 3: Erityistä tukea tarvitsevien nuorten aikuisten asumisen- ja taloudenhallinnan taitojen tukemiseen vapaaehtoistoiminnan ja asumissosiaalisen tuen keinoin (116 375 €) | Ak 3749: Erityistä tukea tarvitsevien nuorten opiskelu- ja työelämävalmiuksien tukemiseen vapaaehtoistoiminnan avulla (Oma Koutsi) (89 250 €)</t>
+          <t>Ak 4: Vaikeissa elämänmuutostilanteissa olevien yli 65 -vuotiaiden psykososiaalisen hyvinvoinnin tukemiseen ryhmämuotoisen tuen ja tukihenkilötoiminnan keinoin (Senioripysäkki) (154 350 €) | Ay 1165: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (146 633 €) | Ak 3: Erityistä tukea tarvitsevien nuorten aikuisten asumisen- ja taloudenhallinnan taitojen tukemiseen vapaaehtoistoiminnan ja asumissosiaalisen tuen keinoin (116 375 €) | Ak 3749: Erityistä tukea tarvitsevien nuorten opiskelu- ja työelämävalmiuksien tukemiseen vapaaehtoistoiminnan avulla (Oma Koutsi) (89 250 €)</t>
         </is>
       </c>
     </row>
@@ -8025,7 +9039,7 @@
       </c>
       <c r="I145" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Som allmänt understöd för understödstagarens allmännyttiga verksamhet (316 512 €) | Ak 2: För att stöda livskontrollen- och hanteringen hos svenskspråkiga personer med psykisk ohälsa eller psykosocial funktionsnedsättning samt deras anhöriga med hjälp av psykosocial kursverksamhet  rådgivning och kamratstöd (168 887 €) | Ak 6: För understöd som allokeras till medlemsorganisationer (20 000 €)</t>
+          <t>Ay 1: Som allmänt understöd för understödstagarens allmännyttiga verksamhet (316 512 €) | Ak 2: För att stöda livskontrollen- och hanteringen hos svenskspråkiga personer med psykisk ohälsa eller psykosocial funktionsnedsättning samt deras anhöriga med hjälp av psykosocial kursverksamhet, rådgivning och kamratstöd (168 887 €) | Ak 6: För understöd som allokeras till medlemsorganisationer (20 000 €)</t>
         </is>
       </c>
     </row>
@@ -8058,7 +9072,7 @@
       </c>
       <c r="I146" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Ikääntyvien mielenterveyden ja hyvinvoinnin tukemiseen ryhmätoiminnan  yksilö- ja parikeskustelujen sekä ikätukitoiminnan avulla (Senioripysäkki-toiminta) (167 000 €) | Ak 9: Kehitysvammaisten ja erityistä tukea tarvitsevien nuorten ja aikuisten yksinäisyyden lieventämiseen ja omaehtoisen aktiivisuuden tukemiseen kohtaamispaikkatoiminnan ja jalkautuvan työn avulla (Iltalinjalla) (118 650 €) | Ay 2716: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (105 840 €)</t>
+          <t>Ak 3: Ikääntyvien mielenterveyden ja hyvinvoinnin tukemiseen ryhmätoiminnan, yksilö- ja parikeskustelujen sekä ikätukitoiminnan avulla (Senioripysäkki-toiminta) (167 000 €) | Ak 9: Kehitysvammaisten ja erityistä tukea tarvitsevien nuorten ja aikuisten yksinäisyyden lieventämiseen ja omaehtoisen aktiivisuuden tukemiseen kohtaamispaikkatoiminnan ja jalkautuvan työn avulla (Iltalinjalla) (118 650 €) | Ay 2716: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (105 840 €) | Ak 9724: Ikääntyneiden hyvinvointia tukevaan yhteisölliseen, toiminnalliseen ja vertaisesti ohjautuvaan kerhotoimintaan Pirkanmaalla (Likellä-kerhotoiminta) (59 850 €) | Ak 2: Yksinäisyyden vähentämiseen ja toimintakyvyn ylläpitämiseen vapaaehtoisten ylläpitämän keskustelevan päivystyspuhelintoiminnan avulla (Aamukorva) (50 000 €)</t>
         </is>
       </c>
     </row>
@@ -8124,9 +9138,7 @@
       </c>
       <c r="I148" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Vapaaehtois- ja vertaistoiminnan koordinointiin ja maahanmuuttajataustaisten poikien ja nuorten miesten osallisuuden ja aktivoinnin tukemiseen Tampereella 
-(Vapari-toiminta) (181 650 €) | Ak 9653: Maahanmuuttajataustaisten vanhempien tukemiseen 7-16-vuotiaiden nuorten kasvatuksessa yksilöllisen tuen ja ryhmätoimintojen avulla sekä tietoisuuden lisäämiseen pakolaisperheiden vanhemmuudesta Tampereella
-(Avaamo) (175 000 €) | Ak 9652: Pakolaistaustaisten työttömien 18-29-vuotiaiden nuorten miesten toimintakyvyn ja mielenterveyden tukemiseen ryhmätoiminnalla ja yksilöllisellä tuella sekä nuorten kanssa työskentelevien ammattilaisten kouluttamiseen ja julkisten palvelujen yhteiskehittämiseen pakolaisnuorten kohtaamisen ja tukemisen parantamiseksi (142 000 €)</t>
+          <t>Ak 2: Vapaaehtois- ja vertaistoiminnan koordinointiin ja maahanmuuttajataustaisten poikien ja nuorten miesten osallisuuden ja aktivoinnin tukemiseen Tampereella  (Vapari-toiminta) (181 650 €) | Ak 9653: Maahanmuuttajataustaisten vanhempien tukemiseen 7-16-vuotiaiden nuorten kasvatuksessa yksilöllisen tuen ja ryhmätoimintojen avulla sekä tietoisuuden lisäämiseen pakolaisperheiden vanhemmuudesta Tampereella (Avaamo) (175 000 €) | Ak 9652: Pakolaistaustaisten työttömien 18-29-vuotiaiden nuorten miesten toimintakyvyn ja mielenterveyden tukemiseen ryhmätoiminnalla ja yksilöllisellä tuella sekä nuorten kanssa työskentelevien ammattilaisten kouluttamiseen ja julkisten palvelujen yhteiskehittämiseen pakolaisnuorten kohtaamisen ja tukemisen parantamiseksi (142 000 €)</t>
         </is>
       </c>
     </row>
@@ -8159,8 +9171,7 @@
       </c>
       <c r="I149" t="inlineStr" s="0">
         <is>
-          <t>Ak 2295: Omaishoitajien tukemiseen ja heidän voimavarojensa lisäämiseen alueellisen matalan kynnyksen toiminnan  vapaaehtoistoiminnan  puhelin- ja chatneuvonnan sekä kokemusasiantuntijoiden vaikuttamistoiminnan avulla Oulun seudulla
-(Ihmisen lähelle) (183 000 €) | Ay 1107: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (175 000 €) | Ak 11632: Erityislapsiperheiden tukemiseen koko perheen sekä vanhempien välisen suhteen näkökulmasta teemallisten ryhmien  yksilöllisen tuen ja tiedotuksen avulla (Hyvinvoiva perhe) (135 000 €)</t>
+          <t>Ak 2295: Omaishoitajien tukemiseen ja heidän voimavarojensa lisäämiseen alueellisen matalan kynnyksen toiminnan, vapaaehtoistoiminnan, puhelin- ja chatneuvonnan sekä kokemusasiantuntijoiden vaikuttamistoiminnan avulla Oulun seudulla (Ihmisen lähelle) (183 000 €) | Ay 1107: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (175 000 €) | Ak 11632: Erityislapsiperheiden tukemiseen koko perheen sekä vanhempien välisen suhteen näkökulmasta teemallisten ryhmien, yksilöllisen tuen ja tiedotuksen avulla (Hyvinvoiva perhe) (135 000 €)</t>
         </is>
       </c>
     </row>
@@ -8193,7 +9204,7 @@
       </c>
       <c r="I150" t="inlineStr" s="0">
         <is>
-          <t>Ak 9519: Työstä ja koulutuksesta syrjässä tai syrjäytymisvaarassa oleville ja yksinäisyyttä kokeville 16-29-vuotiaille nuorille suunnattuun yksinäisyyttä vähentävään ja digiosaamista  hyvinvointia ja osallisuuden kokemusta vahvistavaan digiverstastoimintaan Porissa (79 800 €) | Ak 5441: Päihde- ja mielenterveysongelmaisten sekä heidän läheistensä arjessa selviytymisen ja jaksamisen tukemiseen vapaaehtoistoiminnan  ryhmätoiminnan ja kohtaamispaikkatoiminnan avulla (74 000 €) | C 13668: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Juho – Joustavia Uudistuksia ja Hyvinvointia Osallisuudesta" (Hankekoodi S31484) osarahoitukseen järjestölle (2026-2028) (49 542 €)</t>
+          <t>Ak 10915: Kodin ulkopuoliseen väkivaltaan syyllistyneiden tai syyllistymisriskissä olevien väkivaltaisen käyttäytymisen vähentämiseen ja ehkäisemiseen yksilöllisen asiakastyön ja verkostotyön avulla (151 200 €) | Ak 10911: Matalan kynnyksen tukeen ja neuvontaan rahapelihaittoja kokeville sekä ongelmapelaamisen ennaltaehkäisyyn (Tiltti Satakunta) (133 350 €) | Ak 9519: Työstä ja koulutuksesta syrjässä tai syrjäytymisvaarassa oleville ja yksinäisyyttä kokeville 16-29-vuotiaille nuorille suunnattuun yksinäisyyttä vähentävään ja digiosaamista, hyvinvointia ja osallisuuden kokemusta vahvistavaan digiverstastoimintaan Porissa (79 800 €) | Ak 5441: Päihde- ja mielenterveysongelmaisten sekä heidän läheistensä arjessa selviytymisen ja jaksamisen tukemiseen vapaaehtoistoiminnan, ryhmätoiminnan ja kohtaamispaikkatoiminnan avulla (74 000 €) | C 13668: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Juho – Joustavia Uudistuksia ja Hyvinvointia Osallisuudesta" (Hankekoodi S31484) osarahoitukseen järjestölle (2026-2028) (49 542 €)</t>
         </is>
       </c>
     </row>
@@ -8226,7 +9237,7 @@
       </c>
       <c r="I151" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Päihdetoipujien ja mielenterveyskuntoutujien toimintakyvyn vahvistamiseen päihteettömällä yhdyskuntatupatyöllä ja palveluohjauksella sekä vapaaehtois- ja vertaistoiminnalla (304 155 €) | Ak 6: Asumisen ja elämänhallinnan kanssa vaikeuksissa olevien naisten tukemiseen etsivän työn  palveluohjauksen  yksilöllisen tuen ja ryhmätoiminnan avulla (105 798 €) | Ak 2: Päihdeongelmaisten nuorten aikuisten päihteettömyyttä tukevaan ryhmämuotoiseen toimintaan (Hunaja-toiminta) (72 952 €)</t>
+          <t>Ak 1: Päihdetoipujien ja mielenterveyskuntoutujien toimintakyvyn vahvistamiseen päihteettömällä yhdyskuntatupatyöllä ja palveluohjauksella sekä vapaaehtois- ja vertaistoiminnalla (304 155 €) | Ak 6: Asumisen ja elämänhallinnan kanssa vaikeuksissa olevien naisten tukemiseen etsivän työn, palveluohjauksen, yksilöllisen tuen ja ryhmätoiminnan avulla (105 798 €) | Ak 2: Päihdeongelmaisten nuorten aikuisten päihteettömyyttä tukevaan ryhmämuotoiseen toimintaan (Hunaja-toiminta) (72 952 €)</t>
         </is>
       </c>
     </row>
@@ -8259,7 +9270,7 @@
       </c>
       <c r="I152" t="inlineStr" s="0">
         <is>
-          <t>Ay 7397: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (189 876 €) | Ak 8: Kehitysvammaisten ja vastaavaa laaja-alaista tukea tarvitsevien ihmisten osallisuuden ja vapaa-ajan toimintoihin osallistumisen mahdollistamiseen  sosiaalisen verkoston laajentamiseen ja yksinäisyyden vähentämiseen kaveri-  vertais- ja vapaaehtoistoiminnan sekä tuetun vapaaehtoistoiminnan avulla. (127 674 €) | Ak 2: Kehitysvammaisten ja vastaavaa laaja-alaista tukea tarvitsevien lasten ja nuorten vanhempien arjen tilapäiseen helpottamiseen ja jaksamisen tukemiseen parkkitoiminnan ja vertaistuen avulla (74 550 €)</t>
+          <t>Ay 7397: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (189 876 €) | Ak 8: Kehitysvammaisten ja vastaavaa laaja-alaista tukea tarvitsevien ihmisten osallisuuden ja vapaa-ajan toimintoihin osallistumisen mahdollistamiseen, sosiaalisen verkoston laajentamiseen ja yksinäisyyden vähentämiseen kaveri-, vertais- ja vapaaehtoistoiminnan sekä tuetun vapaaehtoistoiminnan avulla. (127 674 €) | Ak 1: Kehitysvammaisten ja vastaavaa laaja-alaista tukea tarvitsevien nuorten, aikuisten, ikääntyneiden ja seksuaalivähemmistöihin kuuluvien osallisuuden tukemiseen ja sosiaalisten verkostojen laajentamiseen matalan kynnyksen Ystävätupa- kohtaamispaikkatoiminnan, vertaistuen ja virkistystoiminnan avulla. (90 800 €) | Ak 2: Kehitysvammaisten ja vastaavaa laaja-alaista tukea tarvitsevien lasten ja nuorten vanhempien arjen tilapäiseen helpottamiseen ja jaksamisen tukemiseen parkkitoiminnan ja vertaistuen avulla (74 550 €)</t>
         </is>
       </c>
     </row>
@@ -8292,7 +9303,7 @@
       </c>
       <c r="I153" t="inlineStr" s="0">
         <is>
-          <t>Ak 2649: Päihteitä käyttävien miesten isyyden parempaan huomioimiseen palvelujärjestelmässä sekä päihteiden käytöstä johtuvia haittoja kokevien isien päihteettömyyden tukemiseen  isyyden ja osallisuuden vahvistamiseen sekä vanhemmuuden tukemiseen  jotta päihteistä kuntoutuminen ja kohtaaminen tapahtuisi ensisijaisesti isänä ja vanhempana (Erityisesti isä) (143 177 €) | Ak 1: Päihteitä käyttävien naisten sekä läheisten aseman parantamiseen ja toipumisen edistämiseen  päihde- ja riippuvuustyötä tekevien järjestöjen ja päihteitä käyttäviä asiakkaita kohtaavien ammattilaisten keskinäisen yhteistyön edistämiseen  asiantuntijuuden vaihtoon sekä osaamisen ja menetelmien kehittämiseen yli sektori- ja kuntarajojen Itä-Suomen alueella (141 899 €) | Ak 10308: Ruoka-aputoiminnan tavoittavuuden  verkostoyhteistyön ja tiedolla johtamisen edistämiseen ruoka-apu.fi-verkkopalvelun jatkokehittämisen  ylläpidon ja levittämisen avulla (75 385 €)</t>
+          <t>Ak 2649: Päihteitä käyttävien miesten isyyden parempaan huomioimiseen palvelujärjestelmässä sekä päihteiden käytöstä johtuvia haittoja kokevien isien päihteettömyyden tukemiseen, isyyden ja osallisuuden vahvistamiseen sekä vanhemmuuden tukemiseen, jotta päihteistä kuntoutuminen ja kohtaaminen tapahtuisi ensisijaisesti isänä ja vanhempana (Erityisesti isä) (143 177 €) | Ak 1: Päihteitä käyttävien naisten sekä läheisten aseman parantamiseen ja toipumisen edistämiseen, päihde- ja riippuvuustyötä tekevien järjestöjen ja päihteitä käyttäviä asiakkaita kohtaavien ammattilaisten keskinäisen yhteistyön edistämiseen, asiantuntijuuden vaihtoon sekä osaamisen ja menetelmien kehittämiseen yli sektori- ja kuntarajojen Itä-Suomen alueella (141 899 €) | Ak 7754: Vapaaehtoistoiminnan kysynnän ja tarjonnan kohtaamisen edistämiseen Vapaaehtoistyö.fi-verkkopalvelun avulla (115 976 €) | Ak 10308: Ruoka-aputoiminnan tavoittavuuden, verkostoyhteistyön ja tiedolla johtamisen edistämiseen ruoka-apu.fi-verkkopalvelun jatkokehittämisen, ylläpidon ja levittämisen avulla (75 385 €)</t>
         </is>
       </c>
     </row>
@@ -8325,9 +9336,7 @@
       </c>
       <c r="I154" t="inlineStr" s="0">
         <is>
-          <t>Ak 6: Tapaturmaisesti ja potilasvahingon vuoksi vammautuneiden tai sairastuneiden alle 30-vuotiaiden lasten  nuorten ja heidän läheistensä arjenhallinnan ja hyvinvoinnin vahvistamiseen vertaistuen ja vapaaehtoistoiminnan keinoin
-- Tietoa  tukea ja ohjausta tarjoavan palvelupolkusivuston kehittämiseen ja ylläpitämiseen
-(Palveluja perheen parhaaksi) (203 090 €) | Ak 10943: Erityistä tukea tarvitsevien lasten ja alle 30-vuotiaiden nuorten sekä heidän perheidensä yhdenvertaisuuden  osallisuuden ja voimavarojen lisäämiseen Pohjois-Savossa harrastusryhmätoimintojen  tapahtumien ja tietoisuuden vahvistamisen avulla (200 000 €) | Ak 7479: Potilasvahingon kokeneiden  narkolepsiaan sairastuneiden  aivoverenkierron häiriön  aivoverenvuodon tai aivokasvaimen jälkitiloista oireilevien sekä ilman vakuutusturvaa olevien tapaturmaisesti vammautuneiden (esim. aivovamma  palovamma  selkäydinvamma) lasten  nuorten (16-29 vuotta) ja heidän läheistensä toimintakyvyn tukemiseen tiedon  verkostotyön  vertaistuen ja kurssitoiminnan avulla. (65 780 €)</t>
+          <t>Ak 6: Tapaturmaisesti ja potilasvahingon vuoksi vammautuneiden tai sairastuneiden alle 30-vuotiaiden lasten, nuorten ja heidän läheistensä arjenhallinnan ja hyvinvoinnin vahvistamiseen vertaistuen ja vapaaehtoistoiminnan keinoin - Tietoa, tukea ja ohjausta tarjoavan palvelupolkusivuston kehittämiseen ja ylläpitämiseen (Palveluja perheen parhaaksi) (203 090 €) | Ak 10943: Erityistä tukea tarvitsevien lasten ja alle 30-vuotiaiden nuorten sekä heidän perheidensä yhdenvertaisuuden, osallisuuden ja voimavarojen lisäämiseen Pohjois-Savossa harrastusryhmätoimintojen, tapahtumien ja tietoisuuden vahvistamisen avulla (200 000 €) | Ak 7479: Potilasvahingon kokeneiden, narkolepsiaan sairastuneiden, aivoverenkierron häiriön, aivoverenvuodon tai aivokasvaimen jälkitiloista oireilevien sekä ilman vakuutusturvaa olevien tapaturmaisesti vammautuneiden (esim. aivovamma, palovamma, selkäydinvamma) lasten, nuorten (16-29 vuotta) ja heidän läheistensä toimintakyvyn tukemiseen tiedon, verkostotyön, vertaistuen ja kurssitoiminnan avulla. (65 780 €)</t>
         </is>
       </c>
     </row>
@@ -8360,13 +9369,7 @@
       </c>
       <c r="I155" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Pirkanmaalla
-- vertaisryhmätoiminnalla
-- ohjauksella ja neuvonnalla
-- vapaaehtoistoiminnalla
-- tiedotuksella
-- edunvalvonnalla
-(Muistiluotsi) (466 473 €)</t>
+          <t>Ak 2: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Pirkanmaalla - vertaisryhmätoiminnalla - ohjauksella ja neuvonnalla - vapaaehtoistoiminnalla - tiedotuksella - edunvalvonnalla (Muistiluotsi) (466 473 €)</t>
         </is>
       </c>
     </row>
@@ -8432,8 +9435,7 @@
       </c>
       <c r="I157" t="inlineStr" s="0">
         <is>
-          <t>Ak 10374: Huumeita käyttävien hyvinvointia ja osallisuutta lisäävään kohtaamispaikkatoimintaan  neuvontaan sekä vertais- ja pienryhmätoimintaan Rovaniemen alueella (Osallisuuskeskus OODI) (196 193 €) | Ak 4: Matalan kynnyksen kohtaamispaikkatoimintaan maahanmuuttajille kotoutumisen edistämiseksi (Moninet) (132 300 €) | Ak 2: Matalan kynnyksen kohtaamispaikan avoimeen toimintaan
-mielenterveyskuntoutujille (Jokkatupa) (123 760 €)</t>
+          <t>Ak 10374: Huumeita käyttävien hyvinvointia ja osallisuutta lisäävään kohtaamispaikkatoimintaan, neuvontaan sekä vertais- ja pienryhmätoimintaan Rovaniemen alueella (Osallisuuskeskus OODI) (196 193 €) | Ak 4: Matalan kynnyksen kohtaamispaikkatoimintaan maahanmuuttajille kotoutumisen edistämiseksi (Moninet) (132 300 €) | Ak 2: Matalan kynnyksen kohtaamispaikan avoimeen toimintaan mielenterveyskuntoutujille (Jokkatupa) (123 760 €)</t>
         </is>
       </c>
     </row>
@@ -8466,7 +9468,7 @@
       </c>
       <c r="I158" t="inlineStr" s="0">
         <is>
-          <t>Ay 2241: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (199 584 €) | Ak 4: Työikäisten  ikääntyneiden ja omaishoitotilanteen ohittaneiden omaishoitajien kokonaisvaltaiseen tukemiseen ohjauksen  neuvonnan   tiedotuksen ja edunvalvonnan sekä vapaaehtois-  vertais- ja kokemusasiantuntijatoiminnan avulla Helsingin  Vantaan ja Keravan alueella (Kolmipyöräinen) (170 500 €) | Ak 3774: Maahanmuuttajataustaisten omaishoitoperheiden osallisuuden  yhdenvertaisuuden ja elämänhallinnan vahvistamiseen sekä syrjäytymisen ehkäisyyn ohjauksen ja neuvonnan  vertais- ja ryhmätoiminnan sekä vapaaehtoisten ja ammattilaisten kouluttamisen avulla (Omaisneuvo) (82 000 €)</t>
+          <t>Ay 2241: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (199 584 €) | Ak 4: Työikäisten, ikääntyneiden ja omaishoitotilanteen ohittaneiden omaishoitajien kokonaisvaltaiseen tukemiseen ohjauksen, neuvonnan,  tiedotuksen ja edunvalvonnan sekä vapaaehtois-, vertais- ja kokemusasiantuntijatoiminnan avulla Helsingin, Vantaan ja Keravan alueella (Kolmipyöräinen) (170 500 €) | Ak 3774: Maahanmuuttajataustaisten omaishoitoperheiden osallisuuden, yhdenvertaisuuden ja elämänhallinnan vahvistamiseen sekä syrjäytymisen ehkäisyyn ohjauksen ja neuvonnan, vertais- ja ryhmätoiminnan sekä vapaaehtoisten ja ammattilaisten kouluttamisen avulla (Omaisneuvo) (82 000 €)</t>
         </is>
       </c>
     </row>
@@ -8499,7 +9501,7 @@
       </c>
       <c r="I159" t="inlineStr" s="0">
         <is>
-          <t>Ak 10388: Mielenterveystoipujia tukevan klubitaloverkoston toiminnan kehittämiseen  kohderyhmän hyvinvoinnissa tapahtuvien muutosten todentamiseen sekä osallisuuden lisäämiseen (267 015 €) | Ak 12629: Mielenterveystoipujien toimintakyvyn lisäämiseen verkkomuotoisella klubitalotoiminnalla (eKlubitalo) (183 200 €)</t>
+          <t>Ak 10388: Mielenterveystoipujia tukevan klubitaloverkoston toiminnan kehittämiseen, kohderyhmän hyvinvoinnissa tapahtuvien muutosten todentamiseen sekä osallisuuden lisäämiseen (267 015 €) | Ak 12629: Mielenterveystoipujien toimintakyvyn lisäämiseen verkkomuotoisella klubitalotoiminnalla (eKlubitalo) (183 200 €)</t>
         </is>
       </c>
     </row>
@@ -8532,9 +9534,7 @@
       </c>
       <c r="I160" t="inlineStr" s="0">
         <is>
-          <t>Ak 4307: Tyttöjen osallisuuden ja vuorovaikutustaitojen tukemiseen sekä yksinäisyyden vähentämiseen Turun Varissuon alueella ryhmämuotoisen sukupuoli- ja kulttuurisensitiivisen vapaa-ajan toiminnan ja perheisiin kohdistuvan kotinuorisotyön avulla 
-(Turun Tyttöjen Talo Varissuolla) (236 700 €) | Ak 2: Yksinäisten  masentuneiden  sosiaalisesti syrjäytyneiden  monikulttuuristen  psyykkisesti oireilevien ja muiden erityistä tukea tarvitsevien tyttöjen ja nuorten naisten matalankynnyksen toimintaan sekä ryhmä- ja yksilötukeen ja seksuaalista väkivaltaa kokeneiden tukeen
-(Turun Tyttöjen Talo) (209 271 €)</t>
+          <t>Ak 4307: Tyttöjen osallisuuden ja vuorovaikutustaitojen tukemiseen sekä yksinäisyyden vähentämiseen Turun Varissuon alueella ryhmämuotoisen sukupuoli- ja kulttuurisensitiivisen vapaa-ajan toiminnan ja perheisiin kohdistuvan kotinuorisotyön avulla  (Turun Tyttöjen Talo Varissuolla) (236 700 €) | Ak 2: Yksinäisten, masentuneiden, sosiaalisesti syrjäytyneiden, monikulttuuristen, psyykkisesti oireilevien ja muiden erityistä tukea tarvitsevien tyttöjen ja nuorten naisten matalankynnyksen toimintaan sekä ryhmä- ja yksilötukeen ja seksuaalista väkivaltaa kokeneiden tukeen (Turun Tyttöjen Talo) (209 271 €)</t>
         </is>
       </c>
     </row>
@@ -8567,7 +9567,7 @@
       </c>
       <c r="I161" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Lasten  nuorten ja lapsiperheiden leirimuotoiseen lomatoimintaan terveyden ja hyvinvoinnin edistämiseksi (439 534 €)</t>
+          <t>Ak 1: Lasten, nuorten ja lapsiperheiden leirimuotoiseen lomatoimintaan terveyden ja hyvinvoinnin edistämiseksi (439 534 €)</t>
         </is>
       </c>
     </row>
@@ -8633,7 +9633,7 @@
       </c>
       <c r="I163" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Mielenterveyskuntoutujien terveyttä  hyvinvointia  osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään tavoitteelliseen kohtaamispaikkatoimintaan  (Näsinkulman klubitalo) (289 000 €) | Ak 10753: Mielenterveyskuntoutujien terveyttä  hyvinvointia  osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään tavoitteelliseen kohtaamispaikkatoimintaan (Walonkulman Klubitalo) (145 500 €)</t>
+          <t>Ak 3: Mielenterveyskuntoutujien terveyttä, hyvinvointia, osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään tavoitteelliseen kohtaamispaikkatoimintaan  (Näsinkulman klubitalo) (289 000 €) | Ak 10753: Mielenterveyskuntoutujien terveyttä, hyvinvointia, osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään tavoitteelliseen kohtaamispaikkatoimintaan (Walonkulman Klubitalo) (145 500 €)</t>
         </is>
       </c>
     </row>
@@ -8666,8 +9666,7 @@
       </c>
       <c r="I164" t="inlineStr" s="0">
         <is>
-          <t>Ak 2790: Työelämästä syrjässä olevien aikuisten osallisuuden ja yhteisöllisyyden vahvistamiseen päihteettömällä ja avoimella matalan kynnyksen ryhmätoiminnalla sekä ohjauksella Tampereen Hervannassa 
-(Täky) (143 976 €) | Ay 2140: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (92 383 €) | Ak 4: Lasten ja nuorten osallisuuden ja yhteisöllisyyden vahvistamiseen ennaltaehkäisevällä erityisvarhaisnuorisotyöllä Tampereen Hervannassa (Toimela) (82 305 €)</t>
+          <t>Ak 2790: Työelämästä syrjässä olevien aikuisten osallisuuden ja yhteisöllisyyden vahvistamiseen päihteettömällä ja avoimella matalan kynnyksen ryhmätoiminnalla sekä ohjauksella Tampereen Hervannassa  (Täky) (143 976 €) | Ak 5: Ikäihmisten, omaishoitajien ja vammaisten toimintakyvyn ylläpitämiseen sekä sosiaalisten suhteiden vahvistamiseen vapaaehtoisverkoston toiminnalla ja koordinaatiolla Tampereen Hervannassa  (Verkko-vapaaehtoistoiminta Hervanta) (113 778 €) | Ay 2140: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (92 383 €) | Ak 4: Lasten ja nuorten osallisuuden ja yhteisöllisyyden vahvistamiseen ennaltaehkäisevällä erityisvarhaisnuorisotyöllä Tampereen Hervannassa (Toimela) (82 305 €)</t>
         </is>
       </c>
     </row>
@@ -8700,7 +9699,7 @@
       </c>
       <c r="I165" t="inlineStr" s="0">
         <is>
-          <t>Ak 1274: Alaikäisten lasten vanhempien ja maahanmuuttajaäitien vanhemmuuden ja osallisuuden tukeminen sekä lasten ja nuorten yksinäisyyden ehkäisy  sukupolvien välisen kohtaamisen mahdollistaminen ja lukemissujuvuuden edistäminen ammatillisesti ohjatun vapaaehtoisen tukihenkilötoiminnan keinoin. (Ystäväksi maahanmuuttajaäidille-  Kaveri- ja Perhekummitoiminnat ja sukupolvitoiminta Varsinais-Suomessa) (225 000 €) | Ak 3: Lapsiperheille suunnatun avoimen kohtaamispaikka toiminnan (digitaalinen ja fyysinen) järjestämiseen osana uudistuvaa maakunnallista perhekeskustoimintaverkostoa kumppanuudessa kunnan  seurakunnan  muiden järjestöjen ja vapaaehtoisten kanssa (Avoin kohtaamispaikka Marakatti Turussa sekä Turun Seudun Mamien Facebook -ryhmä) (206 168 €)</t>
+          <t>Ak 1274: Alaikäisten lasten vanhempien ja maahanmuuttajaäitien vanhemmuuden ja osallisuuden tukeminen sekä lasten ja nuorten yksinäisyyden ehkäisy, sukupolvien välisen kohtaamisen mahdollistaminen ja lukemissujuvuuden edistäminen ammatillisesti ohjatun vapaaehtoisen tukihenkilötoiminnan keinoin. (Ystäväksi maahanmuuttajaäidille-, Kaveri- ja Perhekummitoiminnat ja sukupolvitoiminta Varsinais-Suomessa) (225 000 €) | Ak 3: Lapsiperheille suunnatun avoimen kohtaamispaikka toiminnan (digitaalinen ja fyysinen) järjestämiseen osana uudistuvaa maakunnallista perhekeskustoimintaverkostoa kumppanuudessa kunnan, seurakunnan, muiden järjestöjen ja vapaaehtoisten kanssa (Avoin kohtaamispaikka Marakatti Turussa sekä Turun Seudun Mamien Facebook -ryhmä) (206 168 €)</t>
         </is>
       </c>
     </row>
@@ -8733,7 +9732,7 @@
       </c>
       <c r="I166" t="inlineStr" s="0">
         <is>
-          <t>Ak 12398: Väkivaltaisesti käyttäytyvien ja radikalisoituneiden maahanmuuttajanuorten kestävän hyvinvoinnin ja osallisuuden edistämiseen etsivän työn  neuvonnan ja palveluohjauksen keinoin viranomaisyhteistyössä. (300 000 €) | Ak 11126: Vaikeassa sosiaalisessa asemassa olevien neuropsykiatrisesti oireilevien lasten sekä sotatraumoista kärsivien perheiden lasten syrjäytymisriskin pienentämiseen ja itsesäätelyn vahvistamiseen. Vanhempien vertaistukeen. (130 418 €)</t>
+          <t>Ak 12398: Väkivaltaisesti käyttäytyvien ja radikalisoituneiden maahanmuuttajanuorten kestävän hyvinvoinnin ja osallisuuden edistämiseen etsivän työn, neuvonnan ja palveluohjauksen keinoin viranomaisyhteistyössä. (300 000 €) | Ak 11126: Vaikeassa sosiaalisessa asemassa olevien neuropsykiatrisesti oireilevien lasten sekä sotatraumoista kärsivien perheiden lasten syrjäytymisriskin pienentämiseen ja itsesäätelyn vahvistamiseen. Vanhempien vertaistukeen. (130 418 €)</t>
         </is>
       </c>
     </row>
@@ -8799,7 +9798,7 @@
       </c>
       <c r="I168" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Som allmänt understöd för understödstagarens allmännyttiga verksamhet (326 105 €) | Ak 6: För att stöda den åldrande  svenskspråkiga befolkningens delaktighet i samhället genom att främja kunskaper i informations- och kommunikationsteknologi med hjälp av kamratstöd  individuell handledning  kurser och information (It för seniorer) (101 430 €)</t>
+          <t>Ay 1: Som allmänt understöd för understödstagarens allmännyttiga verksamhet (326 105 €) | Ak 6: För att stöda den åldrande, svenskspråkiga befolkningens delaktighet i samhället genom att främja kunskaper i informations- och kommunikationsteknologi med hjälp av kamratstöd, individuell handledning, kurser och information (It för seniorer) (101 430 €)</t>
         </is>
       </c>
     </row>
@@ -8832,7 +9831,7 @@
       </c>
       <c r="I169" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Mielenterveys- ja päihdeomaisten hyvinvoinnin  elämänlaadun ja osallisuuden vahvistamiseen omaisneuvonnan  ryhmätoiminnan  vertaistuen  tukihenkilötoiminnan  psykososiaalisen tuen  koulutusten ja vapaaehtoistoiminnan avulla Varsinais-Suomen alueella (422 140 €)</t>
+          <t>Ak 2: Mielenterveys- ja päihdeomaisten hyvinvoinnin, elämänlaadun ja osallisuuden vahvistamiseen omaisneuvonnan, ryhmätoiminnan, vertaistuen, tukihenkilötoiminnan, psykososiaalisen tuen, koulutusten ja vapaaehtoistoiminnan avulla Varsinais-Suomen alueella (422 140 €)</t>
         </is>
       </c>
     </row>
@@ -8865,7 +9864,7 @@
       </c>
       <c r="I170" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Järjestölähtöiseen kriisi- ja mielenterveystyöhön vaikeissa elämäntilanteissa oleville puhelimitse  verkossa  kasvokkain ja ammatillisesti ohjatuissa ryhmissä (Kuopion kriisikeskus) (291 900 €) | Ak 9680: Lähisuhdeväkivaltaa vähentävään turvallisuusfokusoituun väkivaltatyöhön (yksilö- ja paritapaamiset) (130 000 €)</t>
+          <t>Ak 1: Järjestölähtöiseen kriisi- ja mielenterveystyöhön vaikeissa elämäntilanteissa oleville puhelimitse, verkossa, kasvokkain ja ammatillisesti ohjatuissa ryhmissä (Kuopion kriisikeskus) (291 900 €) | Ak 9680: Lähisuhdeväkivaltaa vähentävään turvallisuusfokusoituun väkivaltatyöhön (yksilö- ja paritapaamiset) (130 000 €)</t>
         </is>
       </c>
     </row>
@@ -8898,7 +9897,7 @@
       </c>
       <c r="I171" t="inlineStr" s="0">
         <is>
-          <t>Ak 5: Osallisuutta ja arjenhallintaa edistävän matalan kynnyksen kohtaamispaikan ja miestentilan toimintaan sekä vapaaehtoistoiminnan koordinoimiseen (200 900 €) | Ak 11840: OLKA-toimintamallin mukaiseen vapaaehtoistoiminnan suunnitteluun  koordinointiin  kehittämiseen ja toteuttamiseen sekä sairaalan  sen yksiköiden ja järjestöjen yhteistyöhön (OLKA Kanta-Häme) (115 000 €) | Ak 3: Järjestöjen toimintaedellytysten tukemiseen ja yhteistyön vahvistamiseen järjestökeskustoiminnan avulla Hämeenlinnan seudulla ja Kanta-Hämeessä (105 192 €)</t>
+          <t>Ak 5: Osallisuutta ja arjenhallintaa edistävän matalan kynnyksen kohtaamispaikan ja miestentilan toimintaan sekä vapaaehtoistoiminnan koordinoimiseen (200 900 €) | Ak 11840: OLKA-toimintamallin mukaiseen vapaaehtoistoiminnan suunnitteluun, koordinointiin, kehittämiseen ja toteuttamiseen sekä sairaalan, sen yksiköiden ja järjestöjen yhteistyöhön (OLKA Kanta-Häme) (115 000 €) | Ak 3: Järjestöjen toimintaedellytysten tukemiseen ja yhteistyön vahvistamiseen järjestökeskustoiminnan avulla Hämeenlinnan seudulla ja Kanta-Hämeessä (105 192 €)</t>
         </is>
       </c>
     </row>
@@ -8931,13 +9930,7 @@
       </c>
       <c r="I172" t="inlineStr" s="0">
         <is>
-          <t>Ak 4: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Lapissa
-- vertaisryhmätoiminnalla
-- ohjauksella ja neuvonnalla
-- vapaaehtoistoiminnalla
-- tiedotuksella
-- edunvalvonnalla
-(Muistiluotsi) (355 005 €) | Ak 6929: Lapissa tapahtuvaan aivoterveyden edistämistyöhön tiedottamisen   kouluttamisen  ryhmätoiminnan ja yhteistyön avulla (MUKU) (63 000 €)</t>
+          <t>Ak 4: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Lapissa - vertaisryhmätoiminnalla - ohjauksella ja neuvonnalla - vapaaehtoistoiminnalla - tiedotuksella - edunvalvonnalla (Muistiluotsi) (355 005 €) | Ak 6929: Lapissa tapahtuvaan aivoterveyden edistämistyöhön tiedottamisen,  kouluttamisen, ryhmätoiminnan ja yhteistyön avulla (MUKU) (63 000 €)</t>
         </is>
       </c>
     </row>
@@ -8970,7 +9963,7 @@
       </c>
       <c r="I173" t="inlineStr" s="0">
         <is>
-          <t>Ak 1077: Alaikäisten lasten vanhempien ja maahanmuuttajaäitien vanhemmuuden ja osallisuuden tukemiseen sekä lasten ja nuorten yksinäisyyden ehkäisemiseen  sukupolvien välisen kohtaamisen mahdollistamiseen ja lukemissujuvuuden edistämiseen ammatillisesti ohjatun vapaaehtoisen tukihenkilötoiminnan keinoin (Ystäväksi maahanmuuttajaäidille-  Kaveri- ja Perhekummitoiminnat sekä Mummi- ja vaaritoiminta Kaakkois-Suomessa) (221 653 €) | Ak 9704: Lapsen äänen ja näkökulman esille tuomiseen vanhempien erotilanteessa ja yhteistyövanhemmuuden tukemiseen kohtaamispaikkatoiminnan ja ammatillisesti ohjattujen vertaisryhmien keinoin. (192 386 €)</t>
+          <t>Ak 1077: Alaikäisten lasten vanhempien ja maahanmuuttajaäitien vanhemmuuden ja osallisuuden tukemiseen sekä lasten ja nuorten yksinäisyyden ehkäisemiseen, sukupolvien välisen kohtaamisen mahdollistamiseen ja lukemissujuvuuden edistämiseen ammatillisesti ohjatun vapaaehtoisen tukihenkilötoiminnan keinoin (Ystäväksi maahanmuuttajaäidille-, Kaveri- ja Perhekummitoiminnat sekä Mummi- ja vaaritoiminta Kaakkois-Suomessa) (221 653 €) | Ak 9704: Lapsen äänen ja näkökulman esille tuomiseen vanhempien erotilanteessa ja yhteistyövanhemmuuden tukemiseen kohtaamispaikkatoiminnan ja ammatillisesti ohjattujen vertaisryhmien keinoin. (192 386 €)</t>
         </is>
       </c>
     </row>
@@ -9003,7 +9996,7 @@
       </c>
       <c r="I174" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Sosiaali- ja terveysalojen Järjestötalon vapaaehtoistoiminnan kehittämiseen  vertaisryhmätoimintaan ja OLKA toimintamallin toteuttamiseen Etelä-Pohjanmaan hyvinvointialueella (220 500 €) | Ak 1: Järjestötalon toimintaan sekä järjestöjen toimintaedellytysten edistämiseen Etelä-Pohjanmaalla (188 533 €)</t>
+          <t>Ak 2: Sosiaali- ja terveysalojen Järjestötalon vapaaehtoistoiminnan kehittämiseen, vertaisryhmätoimintaan ja OLKA toimintamallin toteuttamiseen Etelä-Pohjanmaan hyvinvointialueella (220 500 €) | Ak 1: Järjestötalon toimintaan sekä järjestöjen toimintaedellytysten edistämiseen Etelä-Pohjanmaalla (188 533 €)</t>
         </is>
       </c>
     </row>
@@ -9036,8 +10029,7 @@
       </c>
       <c r="I175" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: För språk- och kulturöverskridande mötesplats med låg tröskel med informations- och vägledningstjänster samt mentor- och frivilligverksamhet för invandrare i huvudstadsregionen  Borgå och samt övriga Nyland (228 107 €) | Ak 12614: För psykosocialt stöd med låg tröskel för svenskspråkiga unga med hjälp av digitala rådgivnings- och chat-tjänster 
-(Luckan Unginfo) (180 000 €)</t>
+          <t>Ak 2: För språk- och kulturöverskridande mötesplats med låg tröskel med informations- och vägledningstjänster samt mentor- och frivilligverksamhet för invandrare i huvudstadsregionen, Borgå och samt övriga Nyland (228 107 €) | Ak 12614: För psykosocialt stöd med låg tröskel för svenskspråkiga unga med hjälp av digitala rådgivnings- och chat-tjänster  (Luckan Unginfo) (180 000 €)</t>
         </is>
       </c>
     </row>
@@ -9070,7 +10062,7 @@
       </c>
       <c r="I176" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Rikos- ja päihdetaustaisten ihmisten rikoksettoman sekä päihteettömän elämän motivaation ja edellytysten luomiseen ja vahvistamiseen toimintakeskustoiminnan  vertaistyön  perhetyön ja vankilayhteistyön keinoin (KRIS-Tampereen vankila- ja lainrikkojataustaisten vertaistukityö) (246 915 €) | Ak 12647: Rikollisesta elämäntavasta irtaantumisen tukemiseen rikostaustaisten henkilöiden asenteiden ja ajatusmallien muutosta tukevalla kognitiivisella muutosohjelmalla  vertais-ammattilaistyöskentelyllä sekä yksilötyöllä Pirkanmaalla  Hämeenlinnan ja Kylmäkosken vankiloissa sekä Rikosseuraamuslaitoksen yksiköissä (muut vankilat) ja päihdekuntoutuksissa (159 615 €)</t>
+          <t>Ak 1: Rikos- ja päihdetaustaisten ihmisten rikoksettoman sekä päihteettömän elämän motivaation ja edellytysten luomiseen ja vahvistamiseen toimintakeskustoiminnan, vertaistyön, perhetyön ja vankilayhteistyön keinoin (KRIS-Tampereen vankila- ja lainrikkojataustaisten vertaistukityö) (246 915 €) | Ak 12647: Rikollisesta elämäntavasta irtaantumisen tukemiseen rikostaustaisten henkilöiden asenteiden ja ajatusmallien muutosta tukevalla kognitiivisella muutosohjelmalla, vertais-ammattilaistyöskentelyllä sekä yksilötyöllä Pirkanmaalla, Hämeenlinnan ja Kylmäkosken vankiloissa sekä Rikosseuraamuslaitoksen yksiköissä (muut vankilat) ja päihdekuntoutuksissa (159 615 €)</t>
         </is>
       </c>
     </row>
@@ -9103,7 +10095,7 @@
       </c>
       <c r="I177" t="inlineStr" s="0">
         <is>
-          <t>Ak 7606: Syrjäytyneiden ja syrjäytymisriskissä olevien nuorten aikuisten ja mielenterveyskuntoutujien osallisuuden ja voimavarojen vahvistamiseen verkossa toimivan kulttuuripajan avulla (262 000 €) | Ak 10408: Päihde- ja mielenterveyskuntoutujien sekä yksinäisten ikäihmisten hyvinvoinnin  osallisuuden ja voimavarojen edistämiseen matalan kynnyksen kävelyfutistoiminnalla sekä toiminnan levittämiseen (144 487 €)</t>
+          <t>Ak 7606: Syrjäytyneiden ja syrjäytymisriskissä olevien nuorten aikuisten ja mielenterveyskuntoutujien osallisuuden ja voimavarojen vahvistamiseen verkossa toimivan kulttuuripajan avulla (262 000 €) | Ak 10408: Päihde- ja mielenterveyskuntoutujien sekä yksinäisten ikäihmisten hyvinvoinnin, osallisuuden ja voimavarojen edistämiseen matalan kynnyksen kävelyfutistoiminnalla sekä toiminnan levittämiseen (144 487 €)</t>
         </is>
       </c>
     </row>
@@ -9136,8 +10128,7 @@
       </c>
       <c r="I178" t="inlineStr" s="0">
         <is>
-          <t>Ay 5: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (247 813 €) | Ak 4072: Oppimista  työntekoa ja arjessa selviytymistä tukevien apuvälineiden tunnettuuden ja käytön edistämiseen yksilöllisen ja ryhmämuotoisen ohjauksen ja neuvonnan avulla sekä koulutuksen ja vaikuttamistyön keinoin. Kohderyhminä henkilöt  jotka kokevat oppimisessa vaikeuksia  heidän läheisensä ja ammattilaiset  jotka kohtaavat työssään erilaisia oppijoita. 
-(Oppimisen apuvälinekeskus - tukea arkeen  opintoihin  työhön) (147 000 €) | Ak 11: Jäsenjärjestöille kohdistettaviin avustuksiin (11 223 €)</t>
+          <t>Ay 5: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (247 813 €) | Ak 4072: Oppimista, työntekoa ja arjessa selviytymistä tukevien apuvälineiden tunnettuuden ja käytön edistämiseen yksilöllisen ja ryhmämuotoisen ohjauksen ja neuvonnan avulla sekä koulutuksen ja vaikuttamistyön keinoin. Kohderyhminä henkilöt, jotka kokevat oppimisessa vaikeuksia, heidän läheisensä ja ammattilaiset, jotka kohtaavat työssään erilaisia oppijoita.  (Oppimisen apuvälinekeskus - tukea arkeen, opintoihin, työhön) (147 000 €) | Ak 11: Jäsenjärjestöille kohdistettaviin avustuksiin (11 223 €)</t>
         </is>
       </c>
     </row>
@@ -9203,10 +10194,7 @@
       </c>
       <c r="I180" t="inlineStr" s="0">
         <is>
-          <t>Ak 7704: Mielenterveys- ja päihdekuntoutujien  työelämän ulkopuolella olevien  yksinäisyyttä kokevien ja maahanmuuttajataustaisten henkilöiden osallisuuden  toimintakyvyn ja työelämävalmiuksien vahvistamiseen matalan kynnyksen ryhmätoiminnan  vapaaehtoistyön ja yhteisöllisten tapahtumien avulla Helsingissä (Lapinlahden Lähde) (230 750 €) | Ak 12633: Ulkopuolisuutta kokevien maahanmuuttajien  turvapaikanhakijoiden ja
-pakolaistaustaisten hyvinvoinnin vahvistamiseen  yksinäisyyden vähentämiseen ja arjen 
-mielenterveystaitojen tukemiseen ryhmä- ja kurssitoiminnalla sekä 
-kohderyhmää aktivoivilla tapahtumilla (Miitti) (165 866 €)</t>
+          <t>Ak 7704: Mielenterveys- ja päihdekuntoutujien, työelämän ulkopuolella olevien, yksinäisyyttä kokevien ja maahanmuuttajataustaisten henkilöiden osallisuuden, toimintakyvyn ja työelämävalmiuksien vahvistamiseen matalan kynnyksen ryhmätoiminnan, vapaaehtoistyön ja yhteisöllisten tapahtumien avulla Helsingissä (Lapinlahden Lähde) (230 750 €) | Ak 12633: Ulkopuolisuutta kokevien maahanmuuttajien, turvapaikanhakijoiden ja pakolaistaustaisten hyvinvoinnin vahvistamiseen, yksinäisyyden vähentämiseen ja arjen  mielenterveystaitojen tukemiseen ryhmä- ja kurssitoiminnalla sekä  kohderyhmää aktivoivilla tapahtumilla (Miitti) (165 866 €)</t>
         </is>
       </c>
     </row>
@@ -9239,7 +10227,7 @@
       </c>
       <c r="I181" t="inlineStr" s="0">
         <is>
-          <t>Ak 10182: Lasten ja perheiden kanssa toimivien järjestöjen valtakunnallisen perhekeskusverkoston koordinointiin sekä perhekeskustoimijoiden yhteistyön vahvistamiseen verkostotyön  osaamisen vahvistamisen sekä viestinnän avulla. (197 336 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (196 411 €)</t>
+          <t>Ak 10182: Lasten ja perheiden kanssa toimivien järjestöjen valtakunnallisen perhekeskusverkoston koordinointiin sekä perhekeskustoimijoiden yhteistyön vahvistamiseen verkostotyön, osaamisen vahvistamisen sekä viestinnän avulla. (197 336 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (196 411 €)</t>
         </is>
       </c>
     </row>
@@ -9272,13 +10260,7 @@
       </c>
       <c r="I182" t="inlineStr" s="0">
         <is>
-          <t>Ak 4: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Oulun seudulla
-- vertaisryhmätoiminnalla
-- ohjauksella ja neuvonnalla
-- vapaaehtoistoiminnalla
-- tiedotuksella
-- edunvalvonnalla
-(Muistiluotsi) (391 020 €)</t>
+          <t>Ak 4: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Oulun seudulla - vertaisryhmätoiminnalla - ohjauksella ja neuvonnalla - vapaaehtoistoiminnalla - tiedotuksella - edunvalvonnalla (Muistiluotsi) (391 020 €)</t>
         </is>
       </c>
     </row>
@@ -9311,9 +10293,7 @@
       </c>
       <c r="I183" t="inlineStr" s="0">
         <is>
-          <t>Ak 1241: Maahan muuttaneiden  etenkin naisten  osallisuuden ja toimijuuden sekä kaksisuuntaisen kotoutumisen vahvistamiseen vapaaehtoistyönä toteutettavan suomen kielen sekä luku- ja kirjoitustaidon opetuksen avulla 
-(Luetaan yhdessä -verkosto) (213 885 €) | Ak 11191: Maahan muuttaneiden naisten osallisuuden  työllistymisen ja urakehityksen sekä kaksisuuntaisen kotoutumisen edistämiseen ryhmämuotoisen mentoroinnin  vapaaehtoistoiminnan  verkostoitumisen ja vertaistuen avulla 
-(Auroras) (143 040 €) | C 13653: Turvapaikka-  maahanmuutto- ja kotouttamisrahaston hankkeen ”Sosiaalista suomea - Toisto-menetelmä kouluihin" osarahoitukseen järjestölle (2026-2028) (32 682 €)</t>
+          <t>Ak 1241: Maahan muuttaneiden, etenkin naisten, osallisuuden ja toimijuuden sekä kaksisuuntaisen kotoutumisen vahvistamiseen vapaaehtoistyönä toteutettavan suomen kielen sekä luku- ja kirjoitustaidon opetuksen avulla  (Luetaan yhdessä -verkosto) (213 885 €) | Ak 11191: Maahan muuttaneiden naisten osallisuuden, työllistymisen ja urakehityksen sekä kaksisuuntaisen kotoutumisen edistämiseen ryhmämuotoisen mentoroinnin, vapaaehtoistoiminnan, verkostoitumisen ja vertaistuen avulla  (Auroras) (143 040 €) | C 13653: Turvapaikka-, maahanmuutto- ja kotouttamisrahaston hankkeen ”Sosiaalista suomea - Toisto-menetelmä kouluihin" osarahoitukseen järjestölle (2026-2028) (32 682 €)</t>
         </is>
       </c>
     </row>
@@ -9346,9 +10326,7 @@
       </c>
       <c r="I184" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Erityistä tukea tarvitsevien  yksinäisten ja erityispiirteisten nuorten sekä autismin kirjoon kuuluvien nuorten aikuisten kohtaamispaikka- ja yhteisötoimintaan sekä pienryhmätoimintaan Tampereella
-(Messin tila ja kohtaamispaikka) (231 000 €) | Ak 1470: 15-25-vuotiaiden sosiaalisista peloista  masennuksesta  ahdistuksesta ja arkuudesta sekä paniikkioireista kärsivien nuorten yksilölliseen tukeen ja vertaistoimintaan
-(Messin paja- ja ohjaustoiminta) (158 548 €)</t>
+          <t>Ak 1: Erityistä tukea tarvitsevien, yksinäisten ja erityispiirteisten nuorten sekä autismin kirjoon kuuluvien nuorten aikuisten kohtaamispaikka- ja yhteisötoimintaan sekä pienryhmätoimintaan Tampereella (Messin tila ja kohtaamispaikka) (231 000 €) | Ak 1470: 15-25-vuotiaiden sosiaalisista peloista, masennuksesta, ahdistuksesta ja arkuudesta sekä paniikkioireista kärsivien nuorten yksilölliseen tukeen ja vertaistoimintaan (Messin paja- ja ohjaustoiminta) (158 548 €)</t>
         </is>
       </c>
     </row>
@@ -9381,7 +10359,7 @@
       </c>
       <c r="I185" t="inlineStr" s="0">
         <is>
-          <t>Ay 3216: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (202 784 €) | Ak 2: Kahden kulttuurin perheiden voimavarojen  sosiaalisten verkostojen ja osallisuuden vahvistamiseen vertaisryhmä- ja vapaaehtoistoiminnan  neuvonnan  verkkotoiminnan  viestinnän ja yhteistyön avulla (186 600 €)</t>
+          <t>Ay 3216: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (202 784 €) | Ak 2: Kahden kulttuurin perheiden voimavarojen, sosiaalisten verkostojen ja osallisuuden vahvistamiseen vertaisryhmä- ja vapaaehtoistoiminnan, neuvonnan, verkkotoiminnan, viestinnän ja yhteistyön avulla (186 600 €)</t>
         </is>
       </c>
     </row>
@@ -9414,7 +10392,7 @@
       </c>
       <c r="I186" t="inlineStr" s="0">
         <is>
-          <t>Ak 6062: Kumppanuustalo Arttelin toimintaan  järjestöjen välisen yhteistyön edistämiseen ja syventämiseen sekä järjestö- ja kansalaistoiminnan mahdollisuuksien näkyväksi tekemiseen Tampereen seudulla (Voimaa kumppanuudesta - järjestöyhteistyöllä ja yhteiskehittämisellä kohti osallisuutta ja hyvinvointia) (279 300 €) | Ak 12051: Sairaaloissa ja sote-keskuksissa asioivien toimintakyvyn ylläpitämiseen ja arjenhallinnan tukemiseen vapaaehtois- ja vertaistoiminnan avulla (OLKA Pirkanmaa) (110 000 €)</t>
+          <t>Ak 6062: Kumppanuustalo Arttelin toimintaan, järjestöjen välisen yhteistyön edistämiseen ja syventämiseen sekä järjestö- ja kansalaistoiminnan mahdollisuuksien näkyväksi tekemiseen Tampereen seudulla (Voimaa kumppanuudesta - järjestöyhteistyöllä ja yhteiskehittämisellä kohti osallisuutta ja hyvinvointia) (279 300 €) | Ak 12051: Sairaaloissa ja sote-keskuksissa asioivien toimintakyvyn ylläpitämiseen ja arjenhallinnan tukemiseen vapaaehtois- ja vertaistoiminnan avulla (OLKA Pirkanmaa) (110 000 €)</t>
         </is>
       </c>
     </row>
@@ -9447,8 +10425,7 @@
       </c>
       <c r="I187" t="inlineStr" s="0">
         <is>
-          <t>Ak 10208: Huono-osaisten väestöryhmien osallisuuden  arjenhallinnan ja sosiaalisten
-verkostojen lisäämiseen kohtaamispaikan  vapaaehtoisuuteen pohjautuvan ryhmätoiminnan ja yksilöllisen tuen avulla Kuopiossa (148 838 €) | Ak 10985: Asunnottomien ja asunnottomuusuhan alla olevien henkilöiden elämänlaadun ja -hallinnan lisäämiseen yksilöllisen tuki- ja neuvontatyön avulla Kuopion seudulla (132 501 €) | C 13803: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Yhdessä ajatuksista aikomuksiksi" (211336) osarahoitukseen järjestölle (2026-2027) (40 000 €)</t>
+          <t>Ak 10208: Huono-osaisten väestöryhmien osallisuuden, arjenhallinnan ja sosiaalisten verkostojen lisäämiseen kohtaamispaikan, vapaaehtoisuuteen pohjautuvan ryhmätoiminnan ja yksilöllisen tuen avulla Kuopiossa (148 838 €) | Ak 10985: Asunnottomien ja asunnottomuusuhan alla olevien henkilöiden elämänlaadun ja -hallinnan lisäämiseen yksilöllisen tuki- ja neuvontatyön avulla Kuopion seudulla (132 501 €) | Ak 4: Päihde- ja mielenterveysongelmista, köyhyydestä tai asunnottomuudesta kärsivien arjenhallinnan tukemiseen ja yksinäisyyden vähentämiseen matalan kynnyksen toiminnan ja vapaaehtoisen kaveritoiminnan avulla, vapaaehtoistyön koordinointiin sekä asunnottomuustyön kehittämiseen vaikuttamistoiminnan avulla (67 517 €) | C 13803: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Yhdessä ajatuksista aikomuksiksi" (211336) osarahoitukseen järjestölle (2026-2027) (40 000 €)</t>
         </is>
       </c>
     </row>
@@ -9514,7 +10491,7 @@
       </c>
       <c r="I189" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen  neuvonnan  vertaistoiminnan ja valmennusten avulla Pohjois-Karjalassa (OmaisOiva) (280 500 €) | Ak 10461: Hoivaajan asemassa olevien alle 18-vuotiaiden lasten ja nuorten sekä heidän vanhempiensa kuormittumisen ja syrjäytymisen ennaltaehkäisyyn ja vähentämiseen vertaistuen  yksilöllisen tuen ja virkistäytymismahdollisuuksien avulla (ALISA-toiminta) (98 070 €)</t>
+          <t>Ak 2: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen, neuvonnan, vertaistoiminnan ja valmennusten avulla Pohjois-Karjalassa (OmaisOiva) (280 500 €) | Ak 10461: Hoivaajan asemassa olevien alle 18-vuotiaiden lasten ja nuorten sekä heidän vanhempiensa kuormittumisen ja syrjäytymisen ennaltaehkäisyyn ja vähentämiseen vertaistuen, yksilöllisen tuen ja virkistäytymismahdollisuuksien avulla (ALISA-toiminta) (98 070 €)</t>
         </is>
       </c>
     </row>
@@ -9580,13 +10557,7 @@
       </c>
       <c r="I191" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Keski-Pohjanmaalla ja Pohjois-Pohjanmaan eteläosassa
-- vertaisryhmätoiminnalla
-- ohjauksella ja neuvonnalla
-- vapaaehtoistoiminnalla
-- tiedotuksella
-- edunvalvonnalla
-(Muistiluotsi) (280 586 €) | C 13786: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Nuorten aivostudio – Muisti  terveys ja elintavat" osarahoitukseen järjestölle (2026-2028) (96 000 €)</t>
+          <t>Ak 2: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Keski-Pohjanmaalla ja Pohjois-Pohjanmaan eteläosassa - vertaisryhmätoiminnalla - ohjauksella ja neuvonnalla - vapaaehtoistoiminnalla - tiedotuksella - edunvalvonnalla (Muistiluotsi) (280 586 €) | C 13786: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Nuorten aivostudio – Muisti, terveys ja elintavat" osarahoitukseen järjestölle (2026-2028) (96 000 €)</t>
         </is>
       </c>
     </row>
@@ -9619,7 +10590,7 @@
       </c>
       <c r="I192" t="inlineStr" s="0">
         <is>
-          <t>Ak 6: Vauvaperheiden vanhemmuuden  hyvinvoinnin ja vuorovaikutuksen ryhmämuotoiseen tukemiseen (Vauvaperheryhmä Pirpana). Lasten ja lapsiperheiden yksinäisyyden vähentämiseen vapaaehtois- ja vertaistoiminnan keinoin (Perhekerhot  vapaaehtoisdoula-toiminta erityistä tukea tarvitseville lapsiperheille  vertaisryhmät ja tapahtumat). (125 685 €) | Ak 5: Lähi- ja parisuhdeväkivallan ehkäisemiseen ja katkaisemisen yksilö-  pari- ja ryhmätapaamisten sekä tiedottamisen ja koulutuksen keinoin (125 000 €) | Ak 2463: Eroperheiden auttamiseen ja tukemiseen sekä uusperheiden ennaltaehkäisevään tukemiseen yksilö-  pari- ja ryhmätyöskentelyn keinoin ja verkkovälitteiseen auttamiseen (Ero lapsiperheessä -työ) (124 918 €)</t>
+          <t>Ak 6: Vauvaperheiden vanhemmuuden, hyvinvoinnin ja vuorovaikutuksen ryhmämuotoiseen tukemiseen (Vauvaperheryhmä Pirpana). Lasten ja lapsiperheiden yksinäisyyden vähentämiseen vapaaehtois- ja vertaistoiminnan keinoin (Perhekerhot, vapaaehtoisdoula-toiminta erityistä tukea tarvitseville lapsiperheille, vertaisryhmät ja tapahtumat). (125 685 €) | Ak 5: Lähi- ja parisuhdeväkivallan ehkäisemiseen ja katkaisemisen yksilö-, pari- ja ryhmätapaamisten sekä tiedottamisen ja koulutuksen keinoin (125 000 €) | Ak 2463: Eroperheiden auttamiseen ja tukemiseen sekä uusperheiden ennaltaehkäisevään tukemiseen yksilö-, pari- ja ryhmätyöskentelyn keinoin ja verkkovälitteiseen auttamiseen (Ero lapsiperheessä -työ) (124 918 €)</t>
         </is>
       </c>
     </row>
@@ -9652,7 +10623,7 @@
       </c>
       <c r="I193" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Erityistä tukea tarvitsevien nuorten asunnottomuuden ehkäisyyn asumisohjauksella ja -neuvonnalla sekä ryhmätoiminnoilla Helsingissä  Espoossa  Vantaalla ja Kirkkonummella. (375 340 €)</t>
+          <t>Ak 1: Erityistä tukea tarvitsevien nuorten asunnottomuuden ehkäisyyn asumisohjauksella ja -neuvonnalla sekä ryhmätoiminnoilla Helsingissä, Espoossa, Vantaalla ja Kirkkonummella. (375 340 €)</t>
         </is>
       </c>
     </row>
@@ -9685,7 +10656,7 @@
       </c>
       <c r="I194" t="inlineStr" s="0">
         <is>
-          <t>Ak 4: Mielenterveyden ongelmista  päihderiippuvuudesta tai neuropsykiatrisista vaikeuksista kärsivien aikuisten tukemiseen matalan kynnyksen kohtaamispaikka- ja kädentaitopajatoiminnalla (Avoin Paja Inspis) (199 552 €) | Ak 5: Toipumista edistävään sekä hyvinvointia ja positiivista mielenterveyttä vahvistavaan avoimeen kurssi- ja ryhmätoimintaan  vapaaehtoistoimintaan (Tsempparitoiminta) sekä kokemusasiantuntijatoimintaan (Mielen Avoin Opisto) (172 229 €)</t>
+          <t>Ak 4: Mielenterveyden ongelmista, päihderiippuvuudesta tai neuropsykiatrisista vaikeuksista kärsivien aikuisten tukemiseen matalan kynnyksen kohtaamispaikka- ja kädentaitopajatoiminnalla (Avoin Paja Inspis) (199 552 €) | Ak 5: Toipumista edistävään sekä hyvinvointia ja positiivista mielenterveyttä vahvistavaan avoimeen kurssi- ja ryhmätoimintaan, vapaaehtoistoimintaan (Tsempparitoiminta) sekä kokemusasiantuntijatoimintaan (Mielen Avoin Opisto) (172 229 €)</t>
         </is>
       </c>
     </row>
@@ -9718,7 +10689,7 @@
       </c>
       <c r="I195" t="inlineStr" s="0">
         <is>
-          <t>Ak 7523: Kotona asuvien yli 75-vuotiaiden yksinäisyyden kokemuksen vähentämiseen sekä osallisuuden kokemuksen lisäämiseen etsivän vanhustyön  kerhotoiminnan  retkien ja tapahtumien sekä ylisukupolvisen oppilaitosyhteistyön avulla (Kiinni elämässä -toiminta) (168 000 €) | Ak 12641: Päijät-Hämeen vapaaehtoistoiminnan verkoston koordinoimiseen  alueellisen vapaaehtoistoiminnan edistämiseen ja yhteistyön tukemiseen vapaaehtoistoimijoiden kesken (Päijät-Hämeen vapaaehtoistoiminnan verkosto) (102 669 €) | Ak 3: Ikääntyneiden osallisuuden ja sosiaalisten kontaktien lisäämiseen sekä yksinäisyyden tunteen vähentämiseen vapaaehtoistoiminnan ja kohtaamispaikkatoiminnan keinoin (Virtaa vapaaehtoistyöhön) (100 669 €)</t>
+          <t>Ak 7523: Kotona asuvien yli 75-vuotiaiden yksinäisyyden kokemuksen vähentämiseen sekä osallisuuden kokemuksen lisäämiseen etsivän vanhustyön, kerhotoiminnan, retkien ja tapahtumien sekä ylisukupolvisen oppilaitosyhteistyön avulla (Kiinni elämässä -toiminta) (168 000 €) | Ak 12641: Päijät-Hämeen vapaaehtoistoiminnan verkoston koordinoimiseen, alueellisen vapaaehtoistoiminnan edistämiseen ja yhteistyön tukemiseen vapaaehtoistoimijoiden kesken (Päijät-Hämeen vapaaehtoistoiminnan verkosto) (102 669 €) | Ak 3: Ikääntyneiden osallisuuden ja sosiaalisten kontaktien lisäämiseen sekä yksinäisyyden tunteen vähentämiseen vapaaehtoistoiminnan ja kohtaamispaikkatoiminnan keinoin (Virtaa vapaaehtoistyöhön) (100 669 €)</t>
         </is>
       </c>
     </row>
@@ -9751,7 +10722,7 @@
       </c>
       <c r="I196" t="inlineStr" s="0">
         <is>
-          <t>Ak 7191: Maahanmuuttajien sosiaalisen hyvinvoinnin ja yhteiskuntaan integroitumisen tukemiseen kohtaamispaikkatoiminnan avulla (220 500 €) | Ak 4: Vapaaehtois- ja vertaistoiminnan toteuttamiseen ja kehittämiseen eri kohderyhmien (mm. päihdekuntoutujat  neuropsykiatrisista oireista kärsivät) arjen ja toimintakyvyn tukemiseksi (150 000 €)</t>
+          <t>Ak 7191: Maahanmuuttajien sosiaalisen hyvinvoinnin ja yhteiskuntaan integroitumisen tukemiseen kohtaamispaikkatoiminnan avulla (220 500 €) | Ak 4: Vapaaehtois- ja vertaistoiminnan toteuttamiseen ja kehittämiseen eri kohderyhmien (mm. päihdekuntoutujat, neuropsykiatrisista oireista kärsivät) arjen ja toimintakyvyn tukemiseksi (150 000 €)</t>
         </is>
       </c>
     </row>
@@ -9784,7 +10755,7 @@
       </c>
       <c r="I197" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Mielenterveyskuntoutujien terveyttä  hyvinvointia  osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään tavoitteelliseen kohtaamispaikkatoimintaan (Suvimäen FH-klubitalo) (215 250 €) | Ak 4131: Mielenterveyden haasteita kohdanneiden nuorten aikuisten toimintakyvyn ja mielen hyvinvoinnin lisäämisen vertaistukseen perustuvalla matalankynnyksen toiminnalla (Kulttuuripaja Trombi) (148 837 €)</t>
+          <t>Ak 2: Mielenterveyskuntoutujien terveyttä, hyvinvointia, osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään tavoitteelliseen kohtaamispaikkatoimintaan (Suvimäen FH-klubitalo) (215 250 €) | Ak 4131: Mielenterveyden haasteita kohdanneiden nuorten aikuisten toimintakyvyn ja mielen hyvinvoinnin lisäämisen vertaistukseen perustuvalla matalankynnyksen toiminnalla (Kulttuuripaja Trombi) (148 837 €)</t>
         </is>
       </c>
     </row>
@@ -9817,9 +10788,7 @@
       </c>
       <c r="I198" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Maahanmuuttajanuorten osallistavaan viikonlopputoimintaan ja osallistumisen edistämiseen jalkautuvan ryhmätoiminnan avulla 
-(Yökoripallo-toiminta  Helsinki) (188 554 €) | Ak 3890: Maahanmuuttajataustaisten nuorten aikuisten aktiivisuutta  osallisuutta  yhteiskuntaan kuulumisen tunnetta ja työllistymistä edistävään toimintaan vertaistuen  yksilöllinen tuen ja ryhmätoiminnan avulla pääkaupunkiseudulla 
-(Toiminnan Avulla Työelämään - TAT) (173 369 €)</t>
+          <t>Ak 2: Maahanmuuttajanuorten osallistavaan viikonlopputoimintaan ja osallistumisen edistämiseen jalkautuvan ryhmätoiminnan avulla  (Yökoripallo-toiminta, Helsinki) (188 554 €) | Ak 3890: Maahanmuuttajataustaisten nuorten aikuisten aktiivisuutta, osallisuutta, yhteiskuntaan kuulumisen tunnetta ja työllistymistä edistävään toimintaan vertaistuen, yksilöllinen tuen ja ryhmätoiminnan avulla pääkaupunkiseudulla  (Toiminnan Avulla Työelämään - TAT) (173 369 €)</t>
         </is>
       </c>
     </row>
@@ -9852,7 +10821,7 @@
       </c>
       <c r="I199" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen  neuvonnan  vertaistoiminnan ja valmennusten avulla Lapin alueella (OmaisOiva) (361 179 €)</t>
+          <t>Ak 2: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen, neuvonnan, vertaistoiminnan ja valmennusten avulla Lapin alueella (OmaisOiva) (361 179 €)</t>
         </is>
       </c>
     </row>
@@ -9885,8 +10854,7 @@
       </c>
       <c r="I200" t="inlineStr" s="0">
         <is>
-          <t>Ak 1973: Vapautuvien vankien tukemiseen ja yhteiskuntaan sopeuttamiseen valmentavan työotteen avulla sekä toimintamallin juurruttamiseen 
-(Tavalliseen elämään -palvelu) (199 500 €) | Ak 12352: Vakavan traumatisoitumisen tunnistamiseen ja oireiden lieventämiseen sekä toimintatapojen kehittämiseen traumatisoituneiden tueksi. Toiminta kohdistuu rikostaustaisille henkilöille  vapautuville vangeille ja päihdekuntoutujille (160 800 €)</t>
+          <t>Ak 1973: Vapautuvien vankien tukemiseen ja yhteiskuntaan sopeuttamiseen valmentavan työotteen avulla sekä toimintamallin juurruttamiseen  (Tavalliseen elämään -palvelu) (199 500 €) | Ak 12352: Vakavan traumatisoitumisen tunnistamiseen ja oireiden lieventämiseen sekä toimintatapojen kehittämiseen traumatisoituneiden tueksi. Toiminta kohdistuu rikostaustaisille henkilöille, vapautuville vangeille ja päihdekuntoutujille (160 800 €)</t>
         </is>
       </c>
     </row>
@@ -9919,7 +10887,7 @@
       </c>
       <c r="I201" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (279 060 €) | Ak 11261: Lapsiin ja nuoriin kohdistuvan seksuaalisen väkivallan ennaltaehkäisemiseen matalan kynnyksen tukipalvelun  neuvonnan ja palveluohjauksen avulla henkilöille  joilla on kohonnut riski syyllistyä seksuaaliseen väkivaltaan (SeriE: Lapsiin kohdistuvien seksuaalirikosten ennaltaehkäisy 2026) (80 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (279 060 €) | Ak 11261: Lapsiin ja nuoriin kohdistuvan seksuaalisen väkivallan ennaltaehkäisemiseen matalan kynnyksen tukipalvelun, neuvonnan ja palveluohjauksen avulla henkilöille, joilla on kohonnut riski syyllistyä seksuaaliseen väkivaltaan (SeriE: Lapsiin kohdistuvien seksuaalirikosten ennaltaehkäisy 2026) (80 000 €)</t>
         </is>
       </c>
     </row>
@@ -9985,7 +10953,7 @@
       </c>
       <c r="I203" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Kotona asuvien ikäihmisten terveyden  hyvinvoinnin ja omatoimisen selviytymisen tukemiseen neuvonnan  ryhmätoiminnan ja vapaaehtoistoiminnan avulla (209 475 €) | Ak 10992: Virheellisistä ravintotottumuksista ja liikunnan vähäisyydestä oireilevien ikääntyneiden miesten hyvinvoinnin ja osallisuuden edistämiseen kurssi- ja vertaisryhmätoiminnan keinoin (Virkeät ikämiehet - liikunnalla ja ruualla vireyttä elämään digitalisaatiota hyödyntäen) (144 168 €)</t>
+          <t>Ak 1: Kotona asuvien ikäihmisten terveyden, hyvinvoinnin ja omatoimisen selviytymisen tukemiseen neuvonnan, ryhmätoiminnan ja vapaaehtoistoiminnan avulla (209 475 €) | Ak 10992: Virheellisistä ravintotottumuksista ja liikunnan vähäisyydestä oireilevien ikääntyneiden miesten hyvinvoinnin ja osallisuuden edistämiseen kurssi- ja vertaisryhmätoiminnan keinoin (Virkeät ikämiehet - liikunnalla ja ruualla vireyttä elämään digitalisaatiota hyödyntäen) (144 168 €)</t>
         </is>
       </c>
     </row>
@@ -10018,7 +10986,7 @@
       </c>
       <c r="I204" t="inlineStr" s="0">
         <is>
-          <t>Ak 12399: 18–35-vuotiaiden mielenterveys- ja päihdekuntoutujien yhteisöllisyyden  osallisuuden  yhdenvertaisuuden ja suvaitsevaisuuden lisäämiseen sekä toiminta- ja työkyvyn sekä terveyden edistämiseen järjestämällä toiminnalliseen vertaistukeen perustuvaa kulttuuripajatoimintaa (Kulttuuripaja Saimaa) (185 021 €) | Ak 1: Mielenterveyskuntoutujien terveyttä  hyvinvointia  osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään kohtaamispaikkatoimintaan (Heikintalo) (168 241 €)</t>
+          <t>Ak 12399: 18–35-vuotiaiden mielenterveys- ja päihdekuntoutujien yhteisöllisyyden, osallisuuden, yhdenvertaisuuden ja suvaitsevaisuuden lisäämiseen sekä toiminta- ja työkyvyn sekä terveyden edistämiseen järjestämällä toiminnalliseen vertaistukeen perustuvaa kulttuuripajatoimintaa (Kulttuuripaja Saimaa) (185 021 €) | Ak 1: Mielenterveyskuntoutujien terveyttä, hyvinvointia, osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään kohtaamispaikkatoimintaan (Heikintalo) (168 241 €)</t>
         </is>
       </c>
     </row>
@@ -10051,7 +11019,7 @@
       </c>
       <c r="I205" t="inlineStr" s="0">
         <is>
-          <t>Ak 10: Yksilö-  pari- ja ryhmämuotoiseen avokriisityöhön perhe- ja lähisuhdeväkivaltaa kokeneiden  tekijöiden ja altistuneiden kanssa sekä haastavissa erotilanteissa olevien perheiden tukemiseen (Avokriisityö) (200 899 €) | Ak 4: Vauvaperheiden vanhemmuuden ja vuorovaikutuksen tukemiseen ryhmätoiminnan keinoin (vauvaperheryhmätoiminta vauvaperheille)  lapsiperheiden elämänhallinnan ja toimintakyvyn edistämiseen asumisen tukipalveluilla sekä yhdistyksen vapaaehtoistyön koordinointiin (150 393 €)</t>
+          <t>Ak 10: Yksilö-, pari- ja ryhmämuotoiseen avokriisityöhön perhe- ja lähisuhdeväkivaltaa kokeneiden, tekijöiden ja altistuneiden kanssa sekä haastavissa erotilanteissa olevien perheiden tukemiseen (Avokriisityö) (200 899 €) | Ak 4: Vauvaperheiden vanhemmuuden ja vuorovaikutuksen tukemiseen ryhmätoiminnan keinoin (vauvaperheryhmätoiminta vauvaperheille), lapsiperheiden elämänhallinnan ja toimintakyvyn edistämiseen asumisen tukipalveluilla sekä yhdistyksen vapaaehtoistyön koordinointiin (150 393 €)</t>
         </is>
       </c>
     </row>
@@ -10117,7 +11085,7 @@
       </c>
       <c r="I207" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Näkövammaisten itsenäisen elämän tukemiseen ja osallisuuden lisäämiseen vertaistuen  ryhmätoiminnan  digituen  saavutettavan tiedon  palveluohjauksen ja vaikuttamistoiminnan avulla (350 051 €)</t>
+          <t>Ak 1: Näkövammaisten itsenäisen elämän tukemiseen ja osallisuuden lisäämiseen vertaistuen, ryhmätoiminnan, digituen, saavutettavan tiedon, palveluohjauksen ja vaikuttamistoiminnan avulla (350 051 €)</t>
         </is>
       </c>
     </row>
@@ -10216,7 +11184,7 @@
       </c>
       <c r="I210" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Yksilö-  pari-  perhe- ja ryhmämuotoiseen väkivaltatyön avopalveluun perhe- ja lähisuhdeväkivallan uhrien  tekijöiden ja heidän lasten kanssa väkivallan lopettamiseksi (Lähisuhdeväkivaltatyön yksikkö) (345 366 €)</t>
+          <t>Ak 1: Yksilö-, pari-, perhe- ja ryhmämuotoiseen väkivaltatyön avopalveluun perhe- ja lähisuhdeväkivallan uhrien, tekijöiden ja heidän lasten kanssa väkivallan lopettamiseksi (Lähisuhdeväkivaltatyön yksikkö) (345 366 €)</t>
         </is>
       </c>
     </row>
@@ -10249,7 +11217,7 @@
       </c>
       <c r="I211" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (235 103 €) | Ak 7730: Hiv-positiivisten ja heidän läheistensä hyvinvoinnin edistämiseen  yksinäisyyden ja syrjäytymisen ehkäisyyn ja sosiaaliseen verkostoitumiseen vertaistuen ja vapaaehtoistoiminnan avulla (107 100 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (235 103 €) | Ak 7730: Hiv-positiivisten ja heidän läheistensä hyvinvoinnin edistämiseen, yksinäisyyden ja syrjäytymisen ehkäisyyn ja sosiaaliseen verkostoitumiseen vertaistuen ja vapaaehtoistoiminnan avulla (107 100 €)</t>
         </is>
       </c>
     </row>
@@ -10282,8 +11250,7 @@
       </c>
       <c r="I212" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Erityistä tukea tarvitsevien lasten  nuorten ja nuorten aikuisten toimintakyvyn ja sosiaalisten taitojen tukemiseen matalan kynnyksen harrastus- ja vapaa-ajantoiminnan avulla 
-(Kunnon  Toiminnan ja Ilmaisun Huone) (339 604 €)</t>
+          <t>Ak 2: Erityistä tukea tarvitsevien lasten, nuorten ja nuorten aikuisten toimintakyvyn ja sosiaalisten taitojen tukemiseen matalan kynnyksen harrastus- ja vapaa-ajantoiminnan avulla  (Kunnon, Toiminnan ja Ilmaisun Huone) (339 604 €)</t>
         </is>
       </c>
     </row>
@@ -10316,8 +11283,7 @@
       </c>
       <c r="I213" t="inlineStr" s="0">
         <is>
-          <t>Ak 12687: Järjestöjen yhteistyön  viestinnän ja toiminnan kehittämisen sekä toimintaedellytysten tukemiseen järjestökeskustoiminnan avulla (Meri-Lapin Järjestökeskus Silta) (194 250 €) | Ak 3000: Maahanmuuttaneiden elämänhallinnan  hyvinvoinnin ja osallisuuden sekä kaksisuuntaisen kotoutumisen edistämiseen matalan kynnyksen kohtaamispaikkatoimintojen  neuvonta- ja
-ohjauspalveluiden sekä vapaaehtoistoiminnan avulla (Monikulttuurikeskus Mikseri) (141 750 €)</t>
+          <t>Ak 12687: Järjestöjen yhteistyön, viestinnän ja toiminnan kehittämisen sekä toimintaedellytysten tukemiseen järjestökeskustoiminnan avulla (Meri-Lapin Järjestökeskus Silta) (194 250 €) | Ak 3000: Maahanmuuttaneiden elämänhallinnan, hyvinvoinnin ja osallisuuden sekä kaksisuuntaisen kotoutumisen edistämiseen matalan kynnyksen kohtaamispaikkatoimintojen, neuvonta- ja ohjauspalveluiden sekä vapaaehtoistoiminnan avulla (Monikulttuurikeskus Mikseri) (141 750 €)</t>
         </is>
       </c>
     </row>
@@ -10350,7 +11316,7 @@
       </c>
       <c r="I214" t="inlineStr" s="0">
         <is>
-          <t>Ak 7: Yksilö- ja ryhmämuotoiseen avokriisityöhön perhe- ja lähisuhdeväkivallan kokijoiden  tekijöiden ja lasten kanssa sekä vanhemmuuden tukeen erotilanteessa (Lähisuhdeväkivaltatyön yksiköissä sekä avoimissa kohtaamispaikoissa) (336 000 €)</t>
+          <t>Ak 7: Yksilö- ja ryhmämuotoiseen avokriisityöhön perhe- ja lähisuhdeväkivallan kokijoiden, tekijöiden ja lasten kanssa sekä vanhemmuuden tukeen erotilanteessa (Lähisuhdeväkivaltatyön yksiköissä sekä avoimissa kohtaamispaikoissa) (336 000 €)</t>
         </is>
       </c>
     </row>
@@ -10383,13 +11349,7 @@
       </c>
       <c r="I215" t="inlineStr" s="0">
         <is>
-          <t>Ak 2263: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Helsingin ja Itä-Uudenmaan alueella 
-- vertaisryhmätoiminnalla
-- ohjauksella ja neuvonnalla
-- vapaaehtoistoiminnalla
-- tiedotuksella
-- edunvalvonnalla
-(Muistiluotsi) (335 553 €)</t>
+          <t>Ak 2263: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Helsingin ja Itä-Uudenmaan alueella  - vertaisryhmätoiminnalla - ohjauksella ja neuvonnalla - vapaaehtoistoiminnalla - tiedotuksella - edunvalvonnalla (Muistiluotsi) (335 553 €)</t>
         </is>
       </c>
     </row>
@@ -10455,8 +11415,7 @@
       </c>
       <c r="I217" t="inlineStr" s="0">
         <is>
-          <t>Ak 1225: Erityistä sosiaalista tukea tarvitsevien tyttöjen ja poikien sekä ei-binääristen nuorten yhteisöllisyyden  toimijuuden ja osallisuuden lisäämiseen.
-Toimintamuotoina erityisesti matalan kynnyksen toiminta (Tyttöjen Tupa  Poikien Tupa ja teematorstait)  pienryhmätoiminta sekä Isosisarus-vapaaehtoistoiminta. (176 208 €) | Ak 6906: Ikäihmisten osallistumismahdollisuuksia ja hyvinvointia tukevaan yhteisölliseen toimintaan Joensuun ja Kontiolahden alueella kohtaamispaikkatoiminnan  vapaaehtoistoiminnan sekä tapahtuma-  teemailta- ja pienryhmätoiminnan avulla (Rajaton Ikä! - Seniorien kohtaamispaikka- ja vapaaehtoistoiminta) (156 450 €)</t>
+          <t>Ak 1225: Erityistä sosiaalista tukea tarvitsevien tyttöjen ja poikien sekä ei-binääristen nuorten yhteisöllisyyden, toimijuuden ja osallisuuden lisäämiseen.  Toimintamuotoina erityisesti matalan kynnyksen toiminta (Tyttöjen Tupa, Poikien Tupa ja teematorstait), pienryhmätoiminta sekä Isosisarus-vapaaehtoistoiminta. (176 208 €) | Ak 6906: Ikäihmisten osallistumismahdollisuuksia ja hyvinvointia tukevaan yhteisölliseen toimintaan Joensuun ja Kontiolahden alueella kohtaamispaikkatoiminnan, vapaaehtoistoiminnan sekä tapahtuma-, teemailta- ja pienryhmätoiminnan avulla (Rajaton Ikä! - Seniorien kohtaamispaikka- ja vapaaehtoistoiminta) (156 450 €)</t>
         </is>
       </c>
     </row>
@@ -10522,13 +11481,7 @@
       </c>
       <c r="I219" t="inlineStr" s="0">
         <is>
-          <t>Ak 4: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Pohjois-Savossa
-- vertaisryhmätoiminnalla
-- ohjauksella ja neuvonnalla
-- vapaaehtoistoiminnalla
-- tiedotuksella
-- edunvalvonnalla
-(Muistiluotsi) (331 640 €)</t>
+          <t>Ak 4: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Pohjois-Savossa - vertaisryhmätoiminnalla - ohjauksella ja neuvonnalla - vapaaehtoistoiminnalla - tiedotuksella - edunvalvonnalla (Muistiluotsi) (331 640 €)</t>
         </is>
       </c>
     </row>
@@ -10594,7 +11547,7 @@
       </c>
       <c r="I221" t="inlineStr" s="0">
         <is>
-          <t>Ak 11240: Nuorten huumeidenkäytön  varhaisten kokeilujen ja käytöstä aiheutuvien haittojen ehkäisyyn nuoria osallistavan vapaaehtoistoiminnan  koulutuksen ja päihteettömän toiminnan avulla (196 000 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (134 136 €)</t>
+          <t>Ak 11240: Nuorten huumeidenkäytön, varhaisten kokeilujen ja käytöstä aiheutuvien haittojen ehkäisyyn nuoria osallistavan vapaaehtoistoiminnan, koulutuksen ja päihteettömän toiminnan avulla (196 000 €) | Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (134 136 €)</t>
         </is>
       </c>
     </row>
@@ -10627,7 +11580,7 @@
       </c>
       <c r="I222" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Kaikille avoimeen kohtaamispaikkatoimintaan Porissa ja Kankaanpäässä  yhdistys- ja vapaaehtoistoiminnan kouluttamiseen ja vahvistamiseen  eri sektorien toimijoiden yhteistyön edistämiseen sekä OLKA-toiminnan toteuttamiseen Satakunnassa (329 700 €)</t>
+          <t>Ak 1: Kaikille avoimeen kohtaamispaikkatoimintaan Porissa ja Kankaanpäässä, yhdistys- ja vapaaehtoistoiminnan kouluttamiseen ja vahvistamiseen, eri sektorien toimijoiden yhteistyön edistämiseen sekä OLKA-toiminnan toteuttamiseen Satakunnassa (329 700 €)</t>
         </is>
       </c>
     </row>
@@ -10660,7 +11613,7 @@
       </c>
       <c r="I223" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Vaikeissa elämäntilanteissa oleville henkilöille tarkoitettuun järjestölähtöiseen kriisi- ja mielenterveystyöhön yksilö- ja ryhmämuotoisen auttamisen  vapaaehtoistoiminnan sekä koulutusten keinoin (Kriisikeskus Osviitta) (329 000 €)</t>
+          <t>Ak 1: Vaikeissa elämäntilanteissa oleville henkilöille tarkoitettuun järjestölähtöiseen kriisi- ja mielenterveystyöhön yksilö- ja ryhmämuotoisen auttamisen, vapaaehtoistoiminnan sekä koulutusten keinoin (Kriisikeskus Osviitta) (329 000 €)</t>
         </is>
       </c>
     </row>
@@ -10693,7 +11646,7 @@
       </c>
       <c r="I224" t="inlineStr" s="0">
         <is>
-          <t>Ak 10008: Leskien  leskiperheiden ja vanhempansa menettäneiden lasten  nuorten ja nuorten aikuisten tukeen vertais- ja vapaaehtoistoiminnan  neuvonnan  viestinnän ja vaikuttamistoiminnan avulla. (328 876 €)</t>
+          <t>Ak 10008: Leskien, leskiperheiden ja vanhempansa menettäneiden lasten, nuorten ja nuorten aikuisten tukeen vertais- ja vapaaehtoistoiminnan, neuvonnan, viestinnän ja vaikuttamistoiminnan avulla. (328 876 €)</t>
         </is>
       </c>
     </row>
@@ -10726,7 +11679,7 @@
       </c>
       <c r="I225" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (166 000 €) | Ak 3: Vertaisperhekursseja  leirejä  verkkotilaisuuksia ja tapahtumia sisältävän vertaistoiminnan järjestämiseen kuulovammaisten lasten perheille (154 500 €) | Ak 2605: Jäsenjärjestöille kohdistettaviin avustuksiin (6 180 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (166 000 €) | Ak 3: Vertaisperhekursseja, leirejä, verkkotilaisuuksia ja tapahtumia sisältävän vertaistoiminnan järjestämiseen kuulovammaisten lasten perheille (154 500 €) | Ak 2605: Jäsenjärjestöille kohdistettaviin avustuksiin (6 180 €)</t>
         </is>
       </c>
     </row>
@@ -10792,13 +11745,7 @@
       </c>
       <c r="I227" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Vaasan seudulla
-- vertaisryhmätoiminnalla
-- ohjauksella ja neuvonnalla
-- vapaaehtoistoiminnalla
-- tiedotuksella
-- edunvalvonnalla 
-(Muistiluotsi) (325 500 €)</t>
+          <t>Ak 1: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Vaasan seudulla - vertaisryhmätoiminnalla - ohjauksella ja neuvonnalla - vapaaehtoistoiminnalla - tiedotuksella - edunvalvonnalla  (Muistiluotsi) (325 500 €)</t>
         </is>
       </c>
     </row>
@@ -10831,7 +11778,7 @@
       </c>
       <c r="I228" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: För juridisk rådgivning  intressebevakning och informationsverksamhet till förmån för personer med funktionsnedsättning och deras närstående i Svenskfinland (189 138 €) | Ak 2: För vänverksamhet för svenskspråkiga personer med olika funktionsnedsättningar i Nyland och Österbotten (134 000 €)</t>
+          <t>Ak 1: För juridisk rådgivning, intressebevakning och informationsverksamhet till förmån för personer med funktionsnedsättning och deras närstående i Svenskfinland (189 138 €) | Ak 2: För vänverksamhet för svenskspråkiga personer med olika funktionsnedsättningar i Nyland och Österbotten (134 000 €)</t>
         </is>
       </c>
     </row>
@@ -10897,7 +11844,7 @@
       </c>
       <c r="I230" t="inlineStr" s="0">
         <is>
-          <t>Ak 1338: Kaksisuuntaista kotoutumista edistävään matalan kynnyksen toimintaan sekä maahanmuuttajataustaisten ja alueen muiden asukkaiden toimintakykyä ja työelämävalmiuksia edistävään yksilöohjaukseen ja neuvontaan   ryhmätoimintaan sekä tapahtumien ja vapaaehtoistoiminnan toteuttamiseen Turun Varissuolla ja Runosmäessä (321 825 €)</t>
+          <t>Ak 1338: Kaksisuuntaista kotoutumista edistävään matalan kynnyksen toimintaan sekä maahanmuuttajataustaisten ja alueen muiden asukkaiden toimintakykyä ja työelämävalmiuksia edistävään yksilöohjaukseen ja neuvontaan,  ryhmätoimintaan sekä tapahtumien ja vapaaehtoistoiminnan toteuttamiseen Turun Varissuolla ja Runosmäessä (321 825 €)</t>
         </is>
       </c>
     </row>
@@ -10930,7 +11877,7 @@
       </c>
       <c r="I231" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Järjestölähtöiseen kriisi- ja mielenterveystyöhön vaikeissa elämäntilanteissa oleville kasvokkaisissa asiakastapaamisissa  puhelimitse  verkossa  etäyhteydellä sekä ryhmissä ja tukihenkilötoiminnan avulla (MIELI Kriisikeskus Etelä-Savo  Mikkelin  Savonlinnan ja Pieksämäen toimipisteet) (320 000 €)</t>
+          <t>Ak 1: Järjestölähtöiseen kriisi- ja mielenterveystyöhön vaikeissa elämäntilanteissa oleville kasvokkaisissa asiakastapaamisissa, puhelimitse, verkossa, etäyhteydellä sekä ryhmissä ja tukihenkilötoiminnan avulla (MIELI Kriisikeskus Etelä-Savo, Mikkelin, Savonlinnan ja Pieksämäen toimipisteet) (320 000 €)</t>
         </is>
       </c>
     </row>
@@ -10963,7 +11910,7 @@
       </c>
       <c r="I232" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Mielenterveysomaisten osallisuuden ja toimintakyvyn vahvistamiseen suomen- ja ruotsinkielisen henkilökohtaisen tuen ja neuvonnan  vertaistuen ja muun ryhmätoiminnan sekä yhteiskunnallisen vaikuttamisen avulla Pohjanmaan ja Keski-Pohjanmaan alueilla (319 725 €)</t>
+          <t>Ak 3: Mielenterveysomaisten osallisuuden ja toimintakyvyn vahvistamiseen suomen- ja ruotsinkielisen henkilökohtaisen tuen ja neuvonnan, vertaistuen ja muun ryhmätoiminnan sekä yhteiskunnallisen vaikuttamisen avulla Pohjanmaan ja Keski-Pohjanmaan alueilla (319 725 €)</t>
         </is>
       </c>
     </row>
@@ -11029,7 +11976,7 @@
       </c>
       <c r="I234" t="inlineStr" s="0">
         <is>
-          <t>Ak 4138: Pakolaisten  ihmiskaupan uhrien  paperittomien ja muiden erityisen haavoittuvassa asemassa olevien ulkomaalaisten matalan kynnyksen oikeudelliseen neuvontaan sekä  muiden samojen asiakasryhmien kanssa toimivien työn tukeminen ulkomaalaisoikeudellista erityisasiantuntemusta jakamalla (319 600 €)</t>
+          <t>Ak 4138: Pakolaisten, ihmiskaupan uhrien, paperittomien ja muiden erityisen haavoittuvassa asemassa olevien ulkomaalaisten matalan kynnyksen oikeudelliseen neuvontaan sekä  muiden samojen asiakasryhmien kanssa toimivien työn tukeminen ulkomaalaisoikeudellista erityisasiantuntemusta jakamalla (319 600 €)</t>
         </is>
       </c>
     </row>
@@ -11062,7 +12009,7 @@
       </c>
       <c r="I235" t="inlineStr" s="0">
         <is>
-          <t>Ak 6: Psykososiaalisten tai mielenterveyden haasteiden kanssa kamppailevien  yksinäisten tai kotiin eristäytyneiden ikääntyneiden toimijuuden ja osallisuuden vahvistamiseen sekä yksinäisyyden vähentämiseen yksilö- ja ryhmätoiminnan keinoin (Varjosta valoon) (169 547 €) | Ak 5888: Ikäihmisten tietoisuuden lisäämiseen heille tarjolla olevista tuen ja palvelujen mahdollisuuksista sekä ikääntyneiden toimijuuden ja kuulluksi tulemisen edistämiseen liikkuvan resurssikeskuksen avulla. Vapaaehtoistoiminnan saavutettavuuden edistämiseen. (Liikkuva resurssikeskus) (150 039 €)</t>
+          <t>Ak 6: Psykososiaalisten tai mielenterveyden haasteiden kanssa kamppailevien, yksinäisten tai kotiin eristäytyneiden ikääntyneiden toimijuuden ja osallisuuden vahvistamiseen sekä yksinäisyyden vähentämiseen yksilö- ja ryhmätoiminnan keinoin (Varjosta valoon) (169 547 €) | Ak 5888: Ikäihmisten tietoisuuden lisäämiseen heille tarjolla olevista tuen ja palvelujen mahdollisuuksista sekä ikääntyneiden toimijuuden ja kuulluksi tulemisen edistämiseen liikkuvan resurssikeskuksen avulla. Vapaaehtoistoiminnan saavutettavuuden edistämiseen. (Liikkuva resurssikeskus) (150 039 €)</t>
         </is>
       </c>
     </row>
@@ -11128,7 +12075,7 @@
       </c>
       <c r="I237" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Väkivaltaa lähi- tai perhesuhteessaan käyttäneiden miesten auttamiseen ja väkivallan ennaltaehkäisyyn yksilö-  pari- ja ryhmätyöskentelyn sekä ohjauksen ja neuvonnan avulla verkostoyhteistyössä (Lyömätön Linja ja Miehen Linja -toiminnot). (318 150 €)</t>
+          <t>Ak 2: Väkivaltaa lähi- tai perhesuhteessaan käyttäneiden miesten auttamiseen ja väkivallan ennaltaehkäisyyn yksilö-, pari- ja ryhmätyöskentelyn sekä ohjauksen ja neuvonnan avulla verkostoyhteistyössä (Lyömätön Linja ja Miehen Linja -toiminnot). (318 150 €)</t>
         </is>
       </c>
     </row>
@@ -11194,7 +12141,7 @@
       </c>
       <c r="I239" t="inlineStr" s="0">
         <is>
-          <t>Ak 1586: Pikkulapsiperheiden vanhemmuuden ja vuorovaikutuksen yksilö- ja ryhmämuotoiseen tukemiseen (vauvaperheryhmätoiminta  vapaaehtoisdoula-toiminta ja raskausajan työskentely erityistä tukea tarvitseville vauvaa odottaville perheille  chat  isätoiminta) (213 150 €) | Ak 2: Lapsiperheitä tukevaan järjestölähtöiseen avopalvelutoimintaan (Avitus-toiminta: Ero lapsiperheessä-  vertaisryhmä-  Yökylä-  Päiväleiri-  ja Mummolatoiminta  Perhetuvan Lauantai  chatverkkoauttaminen  kansalaisjärjestötoiminta) (101 430 €)</t>
+          <t>Ak 1586: Pikkulapsiperheiden vanhemmuuden ja vuorovaikutuksen yksilö- ja ryhmämuotoiseen tukemiseen (vauvaperheryhmätoiminta, vapaaehtoisdoula-toiminta ja raskausajan työskentely erityistä tukea tarvitseville vauvaa odottaville perheille, chat, isätoiminta) (213 150 €) | Ak 2: Lapsiperheitä tukevaan järjestölähtöiseen avopalvelutoimintaan (Avitus-toiminta: Ero lapsiperheessä-, vertaisryhmä-, Yökylä-, Päiväleiri-  ja Mummolatoiminta, Perhetuvan Lauantai, chatverkkoauttaminen, kansalaisjärjestötoiminta) (101 430 €)</t>
         </is>
       </c>
     </row>
@@ -11260,8 +12207,7 @@
       </c>
       <c r="I241" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Veteraanien edunvalvonta- ja tukityöhön. 
-Veteraaniliittojen ja - yhdistysten toimitilakuluihin. (310 000 €)</t>
+          <t>Ak 1: Veteraanien edunvalvonta- ja tukityöhön.  Veteraaniliittojen ja - yhdistysten toimitilakuluihin. (310 000 €)</t>
         </is>
       </c>
     </row>
@@ -11294,7 +12240,7 @@
       </c>
       <c r="I242" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Kansalaistoimintakeskuksen kohtaamispaikan koordinointiin tukemaan yhdistysten toimintaa  kehittämään vapaaehtoistoimintaa ja verkostotyötä sekä tarjoamaan alueen eri asukasryhmille kohtaamispaikka Kokkolassa (Yhteisöklubi-Gemenskapsklubben SILTA) (187 425 €) | Ak 11271: OLKA-toimintamallin mukaiseen vapaaehtoistyön koordinointiin sekä sairastuneen toimintakyvyn vahvistamiseen järjestöjen ja keskussairaalan yhteistyöllä (OLKA-toiminta Keski-Pohjanmaa) (120 750 €)</t>
+          <t>Ak 1: Kansalaistoimintakeskuksen kohtaamispaikan koordinointiin tukemaan yhdistysten toimintaa, kehittämään vapaaehtoistoimintaa ja verkostotyötä sekä tarjoamaan alueen eri asukasryhmille kohtaamispaikka Kokkolassa (Yhteisöklubi-Gemenskapsklubben SILTA) (187 425 €) | Ak 11271: OLKA-toimintamallin mukaiseen vapaaehtoistyön koordinointiin sekä sairastuneen toimintakyvyn vahvistamiseen järjestöjen ja keskussairaalan yhteistyöllä (OLKA-toiminta Keski-Pohjanmaa) (120 750 €)</t>
         </is>
       </c>
     </row>
@@ -11393,7 +12339,7 @@
       </c>
       <c r="I245" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (167 000 €) | Ak 12529: Avanne- ja vastaavasti leikattujen ja anaali-inkontinenssipotilaiden sekä heidän läheistensä vapaaehtoistoiminnan koordinointiin sekä vapaaehtoisten tukemiseen  koulutuksiin ja virkistykseen (61 000 €) | Ak 3: Avanne- ja vastaavasti leikattujen ja anaali-inkontinenssipotilaiden sekä heidän läheistensä tukemiseen sairauden käsittelyssä ja omahoidon toteuttamisessa sekä terveyden ja hyvinvoinnin edistämiseen tavoitteellisen ryhmätoiminnan avulla (60 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (167 000 €) | Ak 12529: Avanne- ja vastaavasti leikattujen ja anaali-inkontinenssipotilaiden sekä heidän läheistensä vapaaehtoistoiminnan koordinointiin sekä vapaaehtoisten tukemiseen, koulutuksiin ja virkistykseen (61 000 €) | Ak 3: Avanne- ja vastaavasti leikattujen ja anaali-inkontinenssipotilaiden sekä heidän läheistensä tukemiseen sairauden käsittelyssä ja omahoidon toteuttamisessa sekä terveyden ja hyvinvoinnin edistämiseen tavoitteellisen ryhmätoiminnan avulla (60 000 €) | Ak 5: Jäsenjärjestöille kohdistettaviin avustuksiin (18 000 €)</t>
         </is>
       </c>
     </row>
@@ -11426,7 +12372,7 @@
       </c>
       <c r="I246" t="inlineStr" s="0">
         <is>
-          <t>Ak 6: Yksilö-  pari- ja ryhmämuotoiseen avokriisityöhön perhe- ja lähisuhdeväkivalta- ja muissa perhe-elämän muutos- ja kriisitilanteissa (Avokki) (164 272 €) | Ak 9807: Eroa harkitsevien tai eronneiden vanhempien yhteistyöhalun ja vanhemmuuden vahvistamiseen sekä erosta aiheutuvien lapseen kohdistuvien riskien ehkäisemiseen tarjoamalla varhaista tukea ja apua eroa harkitseville ja eronneille vanhemmille sekä heidän lapsilleen yksilö-  pari- ja vertaisryhmätoiminnan keinoin (Ero lapsiperheessä -työ) (141 000 €)</t>
+          <t>Ak 6: Yksilö-, pari- ja ryhmämuotoiseen avokriisityöhön perhe- ja lähisuhdeväkivalta- ja muissa perhe-elämän muutos- ja kriisitilanteissa (Avokki) (164 272 €) | Ak 9807: Eroa harkitsevien tai eronneiden vanhempien yhteistyöhalun ja vanhemmuuden vahvistamiseen sekä erosta aiheutuvien lapseen kohdistuvien riskien ehkäisemiseen tarjoamalla varhaista tukea ja apua eroa harkitseville ja eronneille vanhemmille sekä heidän lapsilleen yksilö-, pari- ja vertaisryhmätoiminnan keinoin (Ero lapsiperheessä -työ) (141 000 €)</t>
         </is>
       </c>
     </row>
@@ -11459,7 +12405,7 @@
       </c>
       <c r="I247" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Lapissa asuvien erityistä tukea tarvitsevien lasten ja nuorten sekä heidän perheidensä jaksamisen  hyvinvoinnin ja osallisuuden vahvistamiseen kohtaamispaikkatoiminnan  vertaistuen  tiedon jakamisen sekä virkistys- ja vapaaehtoistoiminnan avulla. Vapaaehtoisten ja kokemusosaajien koulutukseen ja koordinoitiin. (ELOn voimaannuttava verkosto) (300 300 €)</t>
+          <t>Ak 1: Lapissa asuvien erityistä tukea tarvitsevien lasten ja nuorten sekä heidän perheidensä jaksamisen, hyvinvoinnin ja osallisuuden vahvistamiseen kohtaamispaikkatoiminnan, vertaistuen, tiedon jakamisen sekä virkistys- ja vapaaehtoistoiminnan avulla. Vapaaehtoisten ja kokemusosaajien koulutukseen ja koordinoitiin. (ELOn voimaannuttava verkosto) (300 300 €)</t>
         </is>
       </c>
     </row>
@@ -11492,7 +12438,7 @@
       </c>
       <c r="I248" t="inlineStr" s="0">
         <is>
-          <t>Ak 6338: Kansalaisten hyvinvointia edistävän valtakunnallisen verkkopalvelukokonaisuuden toteuttamiseen  ylläpitoon ja tekniseen kehittämiseen sekä verkoston yhteistyön koordinointiin (Lähellä.fi) (154 350 €) | Ak 1: Järjestörakenteen toimintaan koordinoimalla ja kehittämällä järjestöjen osallisuutta edistävää toimintamallia Lapissa ja kokoamalla Lapin järjestötoimijoita maakunnalliseen sosiaali- ja terveysalan kehittämistyöhön (145 950 €)</t>
+          <t>Ak 6338: Kansalaisten hyvinvointia edistävän valtakunnallisen verkkopalvelukokonaisuuden toteuttamiseen, ylläpitoon ja tekniseen kehittämiseen sekä verkoston yhteistyön koordinointiin (Lähellä.fi) (154 350 €) | Ak 1: Järjestörakenteen toimintaan koordinoimalla ja kehittämällä järjestöjen osallisuutta edistävää toimintamallia Lapissa ja kokoamalla Lapin järjestötoimijoita maakunnalliseen sosiaali- ja terveysalan kehittämistyöhön (145 950 €)</t>
         </is>
       </c>
     </row>
@@ -11525,7 +12471,7 @@
       </c>
       <c r="I249" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Nikotiinituotteiden käytön vähentämiseen asiantuntija-  viestintä- ja vaikuttamistoiminnan sekä Savuton Suomi 2030 -verkoston koordinoinnin avulla (300 000 €)</t>
+          <t>Ak 2: Nikotiinituotteiden käytön vähentämiseen asiantuntija-, viestintä- ja vaikuttamistoiminnan sekä Savuton Suomi 2030 -verkoston koordinoinnin avulla (300 000 €)</t>
         </is>
       </c>
     </row>
@@ -11558,13 +12504,7 @@
       </c>
       <c r="I250" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Keski-Suomessa 
-- vertaisryhmätoiminnalla
-- ohjauksella ja neuvonnalla
-- vapaaehtoistoiminnalla
-- tiedotuksella
-- edunvalvonnalla
-(Muistiluotsi) (299 648 €)</t>
+          <t>Ak 2: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Keski-Suomessa  - vertaisryhmätoiminnalla - ohjauksella ja neuvonnalla - vapaaehtoistoiminnalla - tiedotuksella - edunvalvonnalla (Muistiluotsi) (299 648 €)</t>
         </is>
       </c>
     </row>
@@ -11630,7 +12570,7 @@
       </c>
       <c r="I252" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Yksin asuvien ikääntyneiden yksinäisyyden tunteen vähentämiseen  osallisuuden lisäämiseen ja voimavarojen vahvistamiseen pitkäkestoisen ja kertaluontoisen ystävätoiminnan avulla (163 767 €) | Ak 12355: Kotona yksin asuvien ikääntyneiden fyysisen kunnon  liikkumis- ja toimintakyvyn ylläpitämiseen vapaaehtoisten kuntoilukummien avulla (Kuntoilukummitoiminta) (131 945 €)</t>
+          <t>Ak 1: Yksin asuvien ikääntyneiden yksinäisyyden tunteen vähentämiseen, osallisuuden lisäämiseen ja voimavarojen vahvistamiseen pitkäkestoisen ja kertaluontoisen ystävätoiminnan avulla (163 767 €) | Ak 12355: Kotona yksin asuvien ikääntyneiden fyysisen kunnon, liikkumis- ja toimintakyvyn ylläpitämiseen vapaaehtoisten kuntoilukummien avulla (Kuntoilukummitoiminta) (131 945 €)</t>
         </is>
       </c>
     </row>
@@ -11696,13 +12636,7 @@
       </c>
       <c r="I254" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Päijät-Hämeen alueella
-- vertaisryhmätoiminnalla
-- ohjauksella ja neuvonnalla
-- vapaaehtoistoiminnalla
-- tiedotuksella
-- edunvalvonnalla
-(Muistiluotsi) (293 000 €)</t>
+          <t>Ak 3: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Päijät-Hämeen alueella - vertaisryhmätoiminnalla - ohjauksella ja neuvonnalla - vapaaehtoistoiminnalla - tiedotuksella - edunvalvonnalla (Muistiluotsi) (293 000 €)</t>
         </is>
       </c>
     </row>
@@ -11768,13 +12702,7 @@
       </c>
       <c r="I256" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Kainuussa
-- vertaisryhmätoiminnalla
-- ohjauksella ja neuvonnalla
-- vapaaehtoistoiminnalla
-- tiedotuksella
-- edunvalvonnalla
-(Muistiluotsi) (291 433 €)</t>
+          <t>Ak 2: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Kainuussa - vertaisryhmätoiminnalla - ohjauksella ja neuvonnalla - vapaaehtoistoiminnalla - tiedotuksella - edunvalvonnalla (Muistiluotsi) (291 433 €)</t>
         </is>
       </c>
     </row>
@@ -11807,13 +12735,7 @@
       </c>
       <c r="I257" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Kymenlaaksossa
-- vertaisryhmätoiminnalla
-- ohjauksella ja neuvonnalla
-- vapaaehtoistoiminnalla
-- tiedotuksella
-- edunvalvonnalla
-(Muistiluotsi) (289 958 €)</t>
+          <t>Ak 3: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Kymenlaaksossa - vertaisryhmätoiminnalla - ohjauksella ja neuvonnalla - vapaaehtoistoiminnalla - tiedotuksella - edunvalvonnalla (Muistiluotsi) (289 958 €)</t>
         </is>
       </c>
     </row>
@@ -11879,7 +12801,7 @@
       </c>
       <c r="I259" t="inlineStr" s="0">
         <is>
-          <t>Ak 4: Mielenterveysomaisten osallisuuden ja toimintakyvyn vahvistamiseen henkilökohtaisen tuen ja neuvonnan  vertaistuen ja muun ryhmätoiminnan sekä yhteiskunnallisen vaikuttamisen avulla Pohjois-Karjalan ja Etelä-Karjalan maakuntien alueella (289 000 €)</t>
+          <t>Ak 4: Mielenterveysomaisten osallisuuden ja toimintakyvyn vahvistamiseen henkilökohtaisen tuen ja neuvonnan, vertaistuen ja muun ryhmätoiminnan sekä yhteiskunnallisen vaikuttamisen avulla Pohjois-Karjalan ja Etelä-Karjalan maakuntien alueella (289 000 €)</t>
         </is>
       </c>
     </row>
@@ -11912,7 +12834,7 @@
       </c>
       <c r="I260" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Perheiden tukemiseen erotilanteessa perhetapaamistoiminnan  vertaistuen  ohjauksen ja neuvonnan keinoin sekä erojen vähentämiseen ennaltaehkäisevän parisuhdetyön keinoin (Matalankynnyksen eropalvelut) (173 889 €) | Ak 6971: Maahanmuuttajaäitien osallisuuden ja kotoutumisen edistämiseen vapaaehtoisen ystävätoiminnan avulla sekä yhdistyksen monikulttuuriseen perhetoimintaan (Monikulttuurinen ystävä- ja perhetoiminta) (115 033 €)</t>
+          <t>Ak 1: Perheiden tukemiseen erotilanteessa perhetapaamistoiminnan, vertaistuen, ohjauksen ja neuvonnan keinoin sekä erojen vähentämiseen ennaltaehkäisevän parisuhdetyön keinoin (Matalankynnyksen eropalvelut) (173 889 €) | Ak 6971: Maahanmuuttajaäitien osallisuuden ja kotoutumisen edistämiseen vapaaehtoisen ystävätoiminnan avulla sekä yhdistyksen monikulttuuriseen perhetoimintaan (Monikulttuurinen ystävä- ja perhetoiminta) (115 033 €)</t>
         </is>
       </c>
     </row>
@@ -11945,7 +12867,7 @@
       </c>
       <c r="I261" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Järjestölähtöiseen toiminnan toteuttamiseen Oulussa sijaitsevan kumppanuuskeskuksen neuvontapisteessä  kansalaisten järjestötiedon ja osallisuuden lisäämiseen sekä järjestöjen välisen yhteistyön edistämiseen (168 000 €) | Ak 6940: OLKA-toimintamallin mukaiseen vapaaehtoistoiminnan koordinointiin  kehittämiseen ja toteuttamiseen sekä sairaaloiden ja järjestöjen yhteistyöhön Pohjois-Pohjanmaan hyvinvointialueella (120 750 €)</t>
+          <t>Ak 1: Järjestölähtöiseen toiminnan toteuttamiseen Oulussa sijaitsevan kumppanuuskeskuksen neuvontapisteessä, kansalaisten järjestötiedon ja osallisuuden lisäämiseen sekä järjestöjen välisen yhteistyön edistämiseen (168 000 €) | Ak 6940: OLKA-toimintamallin mukaiseen vapaaehtoistoiminnan koordinointiin, kehittämiseen ja toteuttamiseen sekä sairaaloiden ja järjestöjen yhteistyöhön Pohjois-Pohjanmaan hyvinvointialueella (120 750 €)</t>
         </is>
       </c>
     </row>
@@ -11978,7 +12900,7 @@
       </c>
       <c r="I262" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen  neuvonnan  vertaistoiminnan ja valmennusten avulla Turun seudulla (OmaisOiva) (287 900 €)</t>
+          <t>Ak 1: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen, neuvonnan, vertaistoiminnan ja valmennusten avulla Turun seudulla (OmaisOiva) (287 900 €)</t>
         </is>
       </c>
     </row>
@@ -12011,8 +12933,7 @@
       </c>
       <c r="I263" t="inlineStr" s="0">
         <is>
-          <t>Ak 11336: Maahanmuuttajataustaisten toimintakyvyn  hyvinvoinnin ja työllistymisvalmiuksien edistämiseen neuvonnan  ryhmätoiminnan sekä järjestö- ja viranomaisyhteistyön avulla
-(Tsempataan!) (286 920 €)</t>
+          <t>Ak 11336: Maahanmuuttajataustaisten toimintakyvyn, hyvinvoinnin ja työllistymisvalmiuksien edistämiseen neuvonnan, ryhmätoiminnan sekä järjestö- ja viranomaisyhteistyön avulla (Tsempataan!) (286 920 €)</t>
         </is>
       </c>
     </row>
@@ -12045,9 +12966,7 @@
       </c>
       <c r="I264" t="inlineStr" s="0">
         <is>
-          <t>Ak 3923: Nuorten sosiaalisia taitoja vahvistavan moottoripajatoiminnan valtakunnalliseen koordinointiin ja moottoripajatoiminnassa toimivien vapaaehtoisten koulutukseen.
-(Moottoripajatoiminta) (128 444 €) | Ak 3739: Palveluoperaatio Saappaan vapaaehtoistyön koulutustoimintaan ja koordinointiin. 
-(Palveluoperaatio Saapas) (88 871 €) | C 13724: Euroopan sosiaalirahasto plussan (ESR+) hankkeen  "Pikkuhelppiä perheille" osarahoitukseen järjestölle (2026) (69 000 €)</t>
+          <t>Ak 3923: Nuorten sosiaalisia taitoja vahvistavan moottoripajatoiminnan valtakunnalliseen koordinointiin ja moottoripajatoiminnassa toimivien vapaaehtoisten koulutukseen. (Moottoripajatoiminta) (128 444 €) | Ak 3739: Palveluoperaatio Saappaan vapaaehtoistyön koulutustoimintaan ja koordinointiin.  (Palveluoperaatio Saapas) (88 871 €) | C 13724: Euroopan sosiaalirahasto plussan (ESR+) hankkeen  "Pikkuhelppiä perheille" osarahoitukseen järjestölle (2026) (69 000 €)</t>
         </is>
       </c>
     </row>
@@ -12080,7 +12999,7 @@
       </c>
       <c r="I265" t="inlineStr" s="0">
         <is>
-          <t>Ak 7: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen  neuvonnan  vertaistoiminnan ja valmennusten avulla Pirkanmaan alueella (OmaisOiva) (286 000 €)</t>
+          <t>Ak 7: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen, neuvonnan, vertaistoiminnan ja valmennusten avulla Pirkanmaan alueella (OmaisOiva) (286 000 €)</t>
         </is>
       </c>
     </row>
@@ -12146,7 +13065,7 @@
       </c>
       <c r="I267" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Mielenterveysomaisten hyvinvoinnin vahvistamiseen sekä arjen hallinnan parantamiseen henkilökohtaisen tuen ja neuvonnan  vertaistuen ja muun ryhmätoiminnan sekä yhteiskunnallisen vaikuttamisen avulla Pohjois- ja Etelä- Savon hyvinvointialueilla (283 500 €)</t>
+          <t>Ak 3: Mielenterveysomaisten hyvinvoinnin vahvistamiseen sekä arjen hallinnan parantamiseen henkilökohtaisen tuen ja neuvonnan, vertaistuen ja muun ryhmätoiminnan sekä yhteiskunnallisen vaikuttamisen avulla Pohjois- ja Etelä- Savon hyvinvointialueilla (283 500 €)</t>
         </is>
       </c>
     </row>
@@ -12212,7 +13131,7 @@
       </c>
       <c r="I269" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Järjestöjen toimintaedellytysten tukemiseen Pohjanmaalla koordinoimalla järjestökeskuksen ja kohtaamispaikan toimintaa sekä edistämällä vapaaehtois- ja vertaistoimintaa. (165 560 €) | Ak 10277: OLKA-toimintamallin mukaiseen vapaaehtoistoiminnan suunnitteluun  koordinointiin  kehittämiseen ja toteuttamiseen sekä julkisen terveydenhuollon ja järjestöjen yhteistyöhön (OLKA-toiminta Pohjanmaan hyvinvointialueella) (116 550 €)</t>
+          <t>Ak 1: Järjestöjen toimintaedellytysten tukemiseen Pohjanmaalla koordinoimalla järjestökeskuksen ja kohtaamispaikan toimintaa sekä edistämällä vapaaehtois- ja vertaistoimintaa. (165 560 €) | Ak 10277: OLKA-toimintamallin mukaiseen vapaaehtoistoiminnan suunnitteluun, koordinointiin, kehittämiseen ja toteuttamiseen sekä julkisen terveydenhuollon ja järjestöjen yhteistyöhön (OLKA-toiminta Pohjanmaan hyvinvointialueella) (116 550 €)</t>
         </is>
       </c>
     </row>
@@ -12278,7 +13197,7 @@
       </c>
       <c r="I271" t="inlineStr" s="0">
         <is>
-          <t>Ak 13872: Ulkomailla asuvien ja erityisen tuen tarpeessa olevien liikkuvien suomalaisten sosiaalisen hyvinvoinnin lisäämiseen ja ylläpitämiseen sekä järjestölähtöiseen kriisiauttamiseen erilaisissa elämäntilanteissa yksilöllisen ja ryhmämuotoisen tuen  matalankynnyksen toiminnan  vertaistuen ja liikkuvan työn keinoin useissa eri maissa Euroopassa (280 500 €)</t>
+          <t>Ak 13872: Ulkomailla asuvien ja erityisen tuen tarpeessa olevien liikkuvien suomalaisten sosiaalisen hyvinvoinnin lisäämiseen ja ylläpitämiseen sekä järjestölähtöiseen kriisiauttamiseen erilaisissa elämäntilanteissa yksilöllisen ja ryhmämuotoisen tuen, matalankynnyksen toiminnan, vertaistuen ja liikkuvan työn keinoin useissa eri maissa Euroopassa (280 500 €)</t>
         </is>
       </c>
     </row>
@@ -12344,7 +13263,7 @@
       </c>
       <c r="I273" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (233 856 €) | Ak 9737: Migreeniä ja vaikeita päänsärkysairauksia sairastavien hyvinvoinnin  toimintakyvyn  työelämäosallisuuden ja yhdenvertaisuuden edistämiseen ammatillisesti organisoidun vapaaehtoistoiminnan keinoin (46 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (233 856 €) | Ak 9737: Migreeniä ja vaikeita päänsärkysairauksia sairastavien hyvinvoinnin, toimintakyvyn, työelämäosallisuuden ja yhdenvertaisuuden edistämiseen ammatillisesti organisoidun vapaaehtoistoiminnan keinoin (46 000 €)</t>
         </is>
       </c>
     </row>
@@ -12410,7 +13329,7 @@
       </c>
       <c r="I275" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Synnytyksen jälkeiseen masennukseen  raskauden aikana ja/tai vauva-ajan psykooseihin sairastuneiden äitien ja perheiden vertaistukeen sekä näistä sairauksista tiedottamiseen ja kouluttamiseen (277 218 €)</t>
+          <t>Ak 2: Synnytyksen jälkeiseen masennukseen, raskauden aikana ja/tai vauva-ajan psykooseihin sairastuneiden äitien ja perheiden vertaistukeen sekä näistä sairauksista tiedottamiseen ja kouluttamiseen (277 218 €)</t>
         </is>
       </c>
     </row>
@@ -12542,7 +13461,7 @@
       </c>
       <c r="I279" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Yhdistysten toimintaedellytysten turvaamiseen ja kehittämiseen  matalan kynnyksen kohtaamispaikan ylläpitoon  maahanmuuttajien omakieliseen neuvontaan sekä erilaisten tapahtumien järjestämiseen Vantaalla (273 000 €)</t>
+          <t>Ak 1: Yhdistysten toimintaedellytysten turvaamiseen ja kehittämiseen, matalan kynnyksen kohtaamispaikan ylläpitoon, maahanmuuttajien omakieliseen neuvontaan sekä erilaisten tapahtumien järjestämiseen Vantaalla (273 000 €)</t>
         </is>
       </c>
     </row>
@@ -12575,7 +13494,7 @@
       </c>
       <c r="I280" t="inlineStr" s="0">
         <is>
-          <t>Ak 12301: Ikäihmisten hyvän ravitsemuksen  koetun toimintakyvyn  elämänlaadun ja hyvinvoinnin edistämiseen ohjauksen  luentojen  viestinnällisen yhteistyön ja käytännönläheisten materiaalien avulla (Voimaa ruuasta 2024-2026) (272 750 €)</t>
+          <t>Ak 12301: Ikäihmisten hyvän ravitsemuksen, koetun toimintakyvyn, elämänlaadun ja hyvinvoinnin edistämiseen ohjauksen, luentojen, viestinnällisen yhteistyön ja käytännönläheisten materiaalien avulla (Voimaa ruuasta 2024-2026) (272 750 €)</t>
         </is>
       </c>
     </row>
@@ -12608,10 +13527,7 @@
       </c>
       <c r="I281" t="inlineStr" s="0">
         <is>
-          <t>Ak 6815: Maahan muuttaneiden arabiankielisten syrjäytymisen ehkäisemiseen  hyvinvoinnin ja osallisuuden lisäämiseen sekä kaksisuuntaisen kotoutumisen edistämiseen.
-Toimintamuotoina vapaaehtois- ja vertaisryhmätoiminta  neuvonta  yksilöohjaus  infotilaisuudet  koulutukset ja tapahtumat.
-(Siltoja arabiankielisille) (145 102 €) | Ak 9600: Maahanmuuttajataustaisten lasten koulutuksellisen yhdenvertaisuuden edistämiseen vanhempien vertaisryhmätoiminnalla  neuvonnalla ja infotilaisuuksilla sekä lasten vapaaehtoistoimintaan pohjautuvalla koulunkäynnin tuella ja ammattilaisten koulutuksilla ja verkosto- ja vaikuttamistyöllä
-(Siltoja vanhemmille) (125 000 €)</t>
+          <t>Ak 6815: Maahan muuttaneiden arabiankielisten syrjäytymisen ehkäisemiseen, hyvinvoinnin ja osallisuuden lisäämiseen sekä kaksisuuntaisen kotoutumisen edistämiseen. Toimintamuotoina vapaaehtois- ja vertaisryhmätoiminta, neuvonta, yksilöohjaus, infotilaisuudet, koulutukset ja tapahtumat. (Siltoja arabiankielisille) (145 102 €) | Ak 9600: Maahanmuuttajataustaisten lasten koulutuksellisen yhdenvertaisuuden edistämiseen vanhempien vertaisryhmätoiminnalla, neuvonnalla ja infotilaisuuksilla sekä lasten vapaaehtoistoimintaan pohjautuvalla koulunkäynnin tuella ja ammattilaisten koulutuksilla ja verkosto- ja vaikuttamistyöllä (Siltoja vanhemmille) (125 000 €)</t>
         </is>
       </c>
     </row>
@@ -12677,13 +13593,7 @@
       </c>
       <c r="I283" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Etelä-Pohjanmaalla 
-- vertaisryhmätoiminnalla
-- ohjauksella ja neuvonnalla
-- vapaaehtoistoiminnalla
-- tiedotuksella
-- edunvalvonnalla
-(Muistiluotsi) (269 010 €)</t>
+          <t>Ak 3: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Etelä-Pohjanmaalla  - vertaisryhmätoiminnalla - ohjauksella ja neuvonnalla - vapaaehtoistoiminnalla - tiedotuksella - edunvalvonnalla (Muistiluotsi) (269 010 €)</t>
         </is>
       </c>
     </row>
@@ -12716,7 +13626,7 @@
       </c>
       <c r="I284" t="inlineStr" s="0">
         <is>
-          <t>Ak 9: Yksilö-  pari- ja ryhmämuotoiseen avokriisityöhön perhe- ja lähisuhdeväkivallan kokijoiden  tekijöiden ja altistuneiden kanssa sekä ennaltaehkäisevään lähisuhdeväkivaltatyöhön nuorten parissa ja hyvinvointialueelle (Lähisuhdeväkivaltatyön avopalvelu) (162 000 €) | Ak 7: Vanhempien ja yhden vanhemman perheiden jaksamisen tukemiseen neuvonnan sekä yksilö- ja vertaisryhmätoiminnan keinoin  eroa harkitsevien tai eronneiden tukemiseen ammatillisesti ja vertaistoiminnalla sekä vapaaehtoisdoula-toiminnan järjestämiseen erityistä tukea tarvitseville lapsiperheille (Vauvaperheohjaus  vapaaehtoisdoula- ja ero lapsiperheessä -toiminta sekä yhden vanhemman vauva- ja pikkulapsiperheille suunnattu tuki) (105 893 €)</t>
+          <t>Ak 9: Yksilö-, pari- ja ryhmämuotoiseen avokriisityöhön perhe- ja lähisuhdeväkivallan kokijoiden, tekijöiden ja altistuneiden kanssa sekä ennaltaehkäisevään lähisuhdeväkivaltatyöhön nuorten parissa ja hyvinvointialueelle (Lähisuhdeväkivaltatyön avopalvelu) (162 000 €) | Ak 7: Vanhempien ja yhden vanhemman perheiden jaksamisen tukemiseen neuvonnan sekä yksilö- ja vertaisryhmätoiminnan keinoin, eroa harkitsevien tai eronneiden tukemiseen ammatillisesti ja vertaistoiminnalla sekä vapaaehtoisdoula-toiminnan järjestämiseen erityistä tukea tarvitseville lapsiperheille (Vauvaperheohjaus, vapaaehtoisdoula- ja ero lapsiperheessä -toiminta sekä yhden vanhemman vauva- ja pikkulapsiperheille suunnattu tuki) (105 893 €)</t>
         </is>
       </c>
     </row>
@@ -12749,7 +13659,7 @@
       </c>
       <c r="I285" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Erityistä sosiaalista tukea tarvitsevien tyttöjen  poikien ja moninaisesti sukupuolensa kokevien osallisuuden vahvistamiseen ja yksilöllisen kasvun tukemiseen matalan kynnyksen toiminnalla  ryhmätoiminnalla ja isosisarustoiminnalla (151 784 €) | Ak 12514: Syrjäytymisriskissä olevien ja vähävaraisten lapsiperheiden osallisuutta ja hyvinvointia vahvistavaan kohtaamispaikkatoimintaan  ryhmätoimintaan ja yhteisölliseen ruokailutoimintaan (Kotila-toiminta) (116 000 €)</t>
+          <t>Ak 3: Erityistä sosiaalista tukea tarvitsevien tyttöjen, poikien ja moninaisesti sukupuolensa kokevien osallisuuden vahvistamiseen ja yksilöllisen kasvun tukemiseen matalan kynnyksen toiminnalla, ryhmätoiminnalla ja isosisarustoiminnalla (151 784 €) | Ak 12514: Syrjäytymisriskissä olevien ja vähävaraisten lapsiperheiden osallisuutta ja hyvinvointia vahvistavaan kohtaamispaikkatoimintaan, ryhmätoimintaan ja yhteisölliseen ruokailutoimintaan (Kotila-toiminta) (116 000 €)</t>
         </is>
       </c>
     </row>
@@ -12782,7 +13692,7 @@
       </c>
       <c r="I286" t="inlineStr" s="0">
         <is>
-          <t>Ak 5744: Vapaaehtoisten aikuisten rekrytoimiseen ja kouluttamiseen lasten ja nuorten tukihenkilöiksi  vapaaehtoisten ohjaamiseen sekä OmaKamu-toiminnan verkostoyhteistyön kehittämiseen (OmaKamu-toiminnan toteuttaminen) (267 589 €)</t>
+          <t>Ak 5744: Vapaaehtoisten aikuisten rekrytoimiseen ja kouluttamiseen lasten ja nuorten tukihenkilöiksi, vapaaehtoisten ohjaamiseen sekä OmaKamu-toiminnan verkostoyhteistyön kehittämiseen (OmaKamu-toiminnan toteuttaminen) (267 589 €)</t>
         </is>
       </c>
     </row>
@@ -12815,8 +13725,7 @@
       </c>
       <c r="I287" t="inlineStr" s="0">
         <is>
-          <t>Ak 11: Kipukroonikoiden ja heidän läheistensä osallisuuden edistämiseen ja arjen toimintakyvyn tukemiseen tiedon jakamisen  vertaistuen  arjen- ja kivunhallintakeinojen  yhteistyön ja vaikuttamistoiminnan keinoin. (145 171 €) | Ak 11789: Kipuoireisten työikäisten hyvinvoinnin ja työkyvyn tukemiseen verkkoryhmätoiminnan  verkkotilaisuuksien ja viestinnän avulla. Sosiaali- ja terveysalan ammattilaisten osaamisen lisäämiseen kivusta  kivunhallinnasta ja keinoista ammattilaisina vaikuttaa kipuoireisten
-työkykyyn. (Kipu ja työ kohtaavat) (121 659 €)</t>
+          <t>Ak 11: Kipukroonikoiden ja heidän läheistensä osallisuuden edistämiseen ja arjen toimintakyvyn tukemiseen tiedon jakamisen, vertaistuen, arjen- ja kivunhallintakeinojen, yhteistyön ja vaikuttamistoiminnan keinoin. (145 171 €) | Ak 11789: Kipuoireisten työikäisten hyvinvoinnin ja työkyvyn tukemiseen verkkoryhmätoiminnan, verkkotilaisuuksien ja viestinnän avulla. Sosiaali- ja terveysalan ammattilaisten osaamisen lisäämiseen kivusta, kivunhallinnasta ja keinoista ammattilaisina vaikuttaa kipuoireisten työkykyyn. (Kipu ja työ kohtaavat) (121 659 €)</t>
         </is>
       </c>
     </row>
@@ -12882,7 +13791,7 @@
       </c>
       <c r="I289" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Vammaisten lasten ja nuorten sekä heidän perheidensä hyvinvoinnin ja jaksamisen tukemiseen matalan kynnyksen kohtaamispaikkatoiminnan  toimintavälinevuokrauksen  harrastustoiminnan  vertaistuen ja neuvonnan avulla (264 877 €)</t>
+          <t>Ak 1: Vammaisten lasten ja nuorten sekä heidän perheidensä hyvinvoinnin ja jaksamisen tukemiseen matalan kynnyksen kohtaamispaikkatoiminnan, toimintavälinevuokrauksen, harrastustoiminnan, vertaistuen ja neuvonnan avulla (264 877 €)</t>
         </is>
       </c>
     </row>
@@ -12915,13 +13824,7 @@
       </c>
       <c r="I290" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Mikkelin seudulla
-- vertaisryhmätoiminnalla
-- ohjauksella ja neuvonnalla
-- vapaaehtoistoiminnalla
-- tiedotuksella
-- edunvalvonnalla
-(Muistiluotsi) (264 000 €)</t>
+          <t>Ak 2: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Mikkelin seudulla - vertaisryhmätoiminnalla - ohjauksella ja neuvonnalla - vapaaehtoistoiminnalla - tiedotuksella - edunvalvonnalla (Muistiluotsi) (264 000 €)</t>
         </is>
       </c>
     </row>
@@ -12954,13 +13857,7 @@
       </c>
       <c r="I291" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Pohjois-Karjalassa
-- vertaisryhmätoiminnalla
-- ohjauksella ja neuvonnalla
-- vapaaehtoistoiminnalla
-- tiedotuksella
-- edunvalvonnalla
-(Muistiluotsi) (262 500 €)</t>
+          <t>Ak 2: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Pohjois-Karjalassa - vertaisryhmätoiminnalla - ohjauksella ja neuvonnalla - vapaaehtoistoiminnalla - tiedotuksella - edunvalvonnalla (Muistiluotsi) (262 500 €)</t>
         </is>
       </c>
     </row>
@@ -12993,7 +13890,7 @@
       </c>
       <c r="I292" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Som allmänt understöd för understödstagarens allmännyttiga verksamhet (175 592 €) | Ak 11819: För höjning av välmående hos missbrukare och deras närstående med hjälp av utbildade erfarenhetsexperters lågtröskelmottagningar i Helsingfors  Esbo  Vanda  Borgå och Vasa (86 000 €)</t>
+          <t>Ay 1: Som allmänt understöd för understödstagarens allmännyttiga verksamhet (175 592 €) | Ak 11819: För höjning av välmående hos missbrukare och deras närstående med hjälp av utbildade erfarenhetsexperters lågtröskelmottagningar i Helsingfors, Esbo, Vanda, Borgå och Vasa (86 000 €)</t>
         </is>
       </c>
     </row>
@@ -13026,7 +13923,7 @@
       </c>
       <c r="I293" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Vaikeissa elämäntilanteissa oleville henkilöille tarkoitettuun järjestölähtöiseen kriisi- ja mielenterveystyöhön kasvokkaisten asiakastapaamisten  puhelin-  verkkotyön sekä ryhmätoiminnan avulla. Kriisi- ja mielenterveystyöhön liittyvän vapaaehtoistoiminnan ylläpitoon ja vahvistamiseen Länsi-Pirkanmaalla ja Kaakkois-Satakunnassa. (Kriisikeskus Tukitalo) (261 292 €)</t>
+          <t>Ak 1: Vaikeissa elämäntilanteissa oleville henkilöille tarkoitettuun järjestölähtöiseen kriisi- ja mielenterveystyöhön kasvokkaisten asiakastapaamisten, puhelin-, verkkotyön sekä ryhmätoiminnan avulla. Kriisi- ja mielenterveystyöhön liittyvän vapaaehtoistoiminnan ylläpitoon ja vahvistamiseen Länsi-Pirkanmaalla ja Kaakkois-Satakunnassa. (Kriisikeskus Tukitalo) (261 292 €)</t>
         </is>
       </c>
     </row>
@@ -13059,13 +13956,7 @@
       </c>
       <c r="I294" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Kanta-Hämeen alueella
-- vertaisryhmätoiminnalla
-- ohjauksella ja neuvonnalla
-- vapaaehtoistoiminnalla
-- tiedotuksella
-- edunvalvonnalla
-(Muistiluotsi) (259 560 €)</t>
+          <t>Ak 2: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Kanta-Hämeen alueella - vertaisryhmätoiminnalla - ohjauksella ja neuvonnalla - vapaaehtoistoiminnalla - tiedotuksella - edunvalvonnalla (Muistiluotsi) (259 560 €)</t>
         </is>
       </c>
     </row>
@@ -13131,7 +14022,7 @@
       </c>
       <c r="I296" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Mielenterveyskuntoutujien terveyttä  hyvinvointia  osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään matalankynnyksen tavoitteelliseen toimintaan (Porvoon FH-klubitalo) (176 400 €) | Ak 4212: Mielenterveyskuntoutujien terveyttä  hyvinvointia  osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään  matalankynnyksen tavoitteelliseen toimintaan (Loviisan klubitalo) (81 585 €)</t>
+          <t>Ak 2: Mielenterveyskuntoutujien terveyttä, hyvinvointia, osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään matalankynnyksen tavoitteelliseen toimintaan (Porvoon FH-klubitalo) (176 400 €) | Ak 4212: Mielenterveyskuntoutujien terveyttä, hyvinvointia, osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään  matalankynnyksen tavoitteelliseen toimintaan (Loviisan klubitalo) (81 585 €)</t>
         </is>
       </c>
     </row>
@@ -13164,7 +14055,7 @@
       </c>
       <c r="I297" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Suomalaisten adoptiohakijoiden  adoptiovanhempien ja adoptoitujen tukemiseen tiedotuksen ja ohjauksen keinoin adoptioprosessin eri vaiheissa (kansainvälinen adoptiotoiminta) (255 895 €)</t>
+          <t>Ak 3: Suomalaisten adoptiohakijoiden, adoptiovanhempien ja adoptoitujen tukemiseen tiedotuksen ja ohjauksen keinoin adoptioprosessin eri vaiheissa (kansainvälinen adoptiotoiminta) (255 895 €)</t>
         </is>
       </c>
     </row>
@@ -13197,7 +14088,7 @@
       </c>
       <c r="I298" t="inlineStr" s="0">
         <is>
-          <t>Ak 11025: Ruoka-apua hakevien toimijuutta ja osallisuutta vahvistavaan  kohtaamispaikkatoimintaan (ViaDia Joensuun Laituri) (133 753 €) | Ak 2521: Taloudellisissa ja sosiaalisissa ongelmissa olevien lapsiperheiden ja maahanmuuttajaperheiden koetun hyvinvoinnin lisäämiseen  syrjäytymisen ennaltaehkäisyyn ja arjen taitojen lisäämiseen  kohtaamispaikkatoiminnan  vertaisryhmien ja tapahtumien kautta (Rantakylän Lähiötalo) (121 275 €)</t>
+          <t>Ak 11025: Ruoka-apua hakevien toimijuutta ja osallisuutta vahvistavaan  kohtaamispaikkatoimintaan (ViaDia Joensuun Laituri) (133 753 €) | Ak 2521: Taloudellisissa ja sosiaalisissa ongelmissa olevien lapsiperheiden ja maahanmuuttajaperheiden koetun hyvinvoinnin lisäämiseen, syrjäytymisen ennaltaehkäisyyn ja arjen taitojen lisäämiseen  kohtaamispaikkatoiminnan, vertaisryhmien ja tapahtumien kautta (Rantakylän Lähiötalo) (121 275 €)</t>
         </is>
       </c>
     </row>
@@ -13230,7 +14121,7 @@
       </c>
       <c r="I299" t="inlineStr" s="0">
         <is>
-          <t>Ak 4109: Kotona asuvien ikäihmisten toimintakyvyn ja hyvinvoinnin vahvistamiseen ryhmä-  vapaaehtois- ja vertaistoiminnan sekä asiantuntijatoiminnan keinoin Kauhavan  Evijärven ja Lappajärven alueilla (Aijjoos-kumppanuustoiminta - yhdessä enemmän hyvinvointia) (254 678 €)</t>
+          <t>Ak 4109: Kotona asuvien ikäihmisten toimintakyvyn ja hyvinvoinnin vahvistamiseen ryhmä-, vapaaehtois- ja vertaistoiminnan sekä asiantuntijatoiminnan keinoin Kauhavan, Evijärven ja Lappajärven alueilla (Aijjoos-kumppanuustoiminta - yhdessä enemmän hyvinvointia) (254 678 €)</t>
         </is>
       </c>
     </row>
@@ -13263,7 +14154,7 @@
       </c>
       <c r="I300" t="inlineStr" s="0">
         <is>
-          <t>Ay 6280: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (86 083 €) | Ak 4418: Nuorten työelämä- ja opiskeluosallisuuden  aktiivisen toimijuuden ja mielenterveyden edistämiseen sekä terveyttä edistävien elämäntapojen vahvistamiseen ryhmämuotoisen Ink-tiimitoiminnan avulla (66 667 €) | Ak 11316: Haavoittuvassa asemassa olevien nuorten aikuisten mielenterveyden vahvistamiseen  voimavarojen lisäämiseen sekä yksinäisyyden vähentämiseen verkossa toteutettavalla vertaisryhmätoiminnalla (26 667 €)</t>
+          <t>Ay 6280: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (86 083 €) | Ak 4418: Nuorten työelämä- ja opiskeluosallisuuden, aktiivisen toimijuuden ja mielenterveyden edistämiseen sekä terveyttä edistävien elämäntapojen vahvistamiseen ryhmämuotoisen Ink-tiimitoiminnan avulla (66 667 €) | Ak 6460: Nuorten sosiaaliseen vahvistamiseen, terveyden ja hyvinvoinnin edistämiseen sekä päihdekokeilujen ja päihteiden käytön ehkäisemiseen Riemu-päihdekasvatuskokonaisuuksia tai sen osasisältöjä toteuttamalla (47 775 €) | Ak 11316: Haavoittuvassa asemassa olevien nuorten aikuisten mielenterveyden vahvistamiseen, voimavarojen lisäämiseen sekä yksinäisyyden vähentämiseen verkossa toteutettavalla vertaisryhmätoiminnalla (26 667 €) | Ak 12523: Pelikulttuurisesti orientoituneiden, ensisijaisesti ulkopuolisuutta, yksinäisyyttä, kiusaamista tai pelaamisen haittoja kokeneiden nuorten yksinäisyyden vähentämiseen sekä pystyvyyden kokemusten ja resilienssin vahvistamiseen verkossa sekä paikanpäällä tapahtuvan vertaisryhmätoiminnan avulla (26 667 €)</t>
         </is>
       </c>
     </row>
@@ -13296,7 +14187,7 @@
       </c>
       <c r="I301" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Mielenterveys- ja päihdetoipujien osallisuutta vahvistavan matalan kynnyksen kohtaamispaikan toimintaan Mikkelissä sekä vapaaehtois-  vertais- ja kokemusasiantuntijatoiminnan koordinointiin ja kouluttamiseen Etelä-Savon alueella (253 365 €)</t>
+          <t>Ak 2: Mielenterveys- ja päihdetoipujien osallisuutta vahvistavan matalan kynnyksen kohtaamispaikan toimintaan Mikkelissä sekä vapaaehtois-, vertais- ja kokemusasiantuntijatoiminnan koordinointiin ja kouluttamiseen Etelä-Savon alueella (253 365 €)</t>
         </is>
       </c>
     </row>
@@ -13329,8 +14220,7 @@
       </c>
       <c r="I302" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Näkövammaisten itsenäisen elämän tukemiseen vertais- ja ryhmätoiminnan  digituen  viestinnän ja vaikuttamistyön avulla Pirkanmaan ja Kanta-Hämeen alueella
-- Digitukeen Satakunnan alueella (253 111 €)</t>
+          <t>Ak 3: Näkövammaisten itsenäisen elämän tukemiseen vertais- ja ryhmätoiminnan, digituen, viestinnän ja vaikuttamistyön avulla Pirkanmaan ja Kanta-Hämeen alueella - Digitukeen Satakunnan alueella (253 111 €)</t>
         </is>
       </c>
     </row>
@@ -13396,7 +14286,7 @@
       </c>
       <c r="I304" t="inlineStr" s="0">
         <is>
-          <t>Ak 12807: Nuorten tyttöjen alkavien mielenterveysoireiden varhaiseen tunnistamiseen ja suojaavien tekijöiden lisäämiseen kehitettyyn Tyttö olet helmi! -etäohjaukseen  joka on suunnattu yläkouluikäikäisille tytöille ja heidän äideilleen (Tyttö olet helmi! -toiminta) (155 400 €) | Ak 12806: Neuropsykiatrisesti oireilevien nuorten kasvun ja kehityksen edistämiseen sekä syrjäytymisen riskin ennaltaehkäisyyn vahvistamalla poikien ja isien välistä suhdetta toiminnallisin menetelmin (Isät ja pojat puussa – seikkailutoimintaa neuropsykiatrisesti oireileville pojille ja heidän isilleen) (95 366 €)</t>
+          <t>Ak 12807: Nuorten tyttöjen alkavien mielenterveysoireiden varhaiseen tunnistamiseen ja suojaavien tekijöiden lisäämiseen kehitettyyn Tyttö olet helmi! -etäohjaukseen, joka on suunnattu yläkouluikäikäisille tytöille ja heidän äideilleen (Tyttö olet helmi! -toiminta) (155 400 €) | Ak 12806: Neuropsykiatrisesti oireilevien nuorten kasvun ja kehityksen edistämiseen sekä syrjäytymisen riskin ennaltaehkäisyyn vahvistamalla poikien ja isien välistä suhdetta toiminnallisin menetelmin (Isät ja pojat puussa – seikkailutoimintaa neuropsykiatrisesti oireileville pojille ja heidän isilleen) (95 366 €)</t>
         </is>
       </c>
     </row>
@@ -13429,7 +14319,7 @@
       </c>
       <c r="I305" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Mielenterveystoipujien ja heidän läheistensä osallisuuden vahvistamiseen vapaaehtois-  vertais- ja kohtaamispaikkatoiminnoilla Rovaniemellä sekä mielenterveysyhdistysten vapaaehtoistoiminnan tukemisella ja verkostotyön toteuttamisella Pohjois-Suomessa (250 000 €)</t>
+          <t>Ak 3: Mielenterveystoipujien ja heidän läheistensä osallisuuden vahvistamiseen vapaaehtois-, vertais- ja kohtaamispaikkatoiminnoilla Rovaniemellä sekä mielenterveysyhdistysten vapaaehtoistoiminnan tukemisella ja verkostotyön toteuttamisella Pohjois-Suomessa (250 000 €)</t>
         </is>
       </c>
     </row>
@@ -13462,8 +14352,7 @@
       </c>
       <c r="I306" t="inlineStr" s="0">
         <is>
-          <t>Ak 5: Henkilökohtaisen avustajan työnantajamallin toimivuuden vahvistamiseen työnantajamalliin liittyviin oikeudellisiin kysymyksiin keskittyvällä neuvontapuhelintoiminnalla (Heta-Help) (218 943 €) | Ak 12503: Henkilökohtaisten avustajien työnantajiien voimavarojen lisäämiseen ja työnantajuudessa tukemiseen ryhmä- ja yksilömuotoisen vertaistuen avulla
-- Vertaistukihenkilöiden kouluttamiseen (30 743 €)</t>
+          <t>Ak 5: Henkilökohtaisen avustajan työnantajamallin toimivuuden vahvistamiseen työnantajamalliin liittyviin oikeudellisiin kysymyksiin keskittyvällä neuvontapuhelintoiminnalla (Heta-Help) (218 943 €) | Ak 12503: Henkilökohtaisten avustajien työnantajiien voimavarojen lisäämiseen ja työnantajuudessa tukemiseen ryhmä- ja yksilömuotoisen vertaistuen avulla - Vertaistukihenkilöiden kouluttamiseen (30 743 €)</t>
         </is>
       </c>
     </row>
@@ -13496,13 +14385,7 @@
       </c>
       <c r="I307" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Etelä- Karjalassa
-- vertaisryhmätoiminnalla 
-- ohjauksella ja neuvonnalla 
-- vapaaehtoistoiminnalla
-- tiedotuksella 
-- edunvalvonnalla 
-(Muistiluotsi) (246 000 €)</t>
+          <t>Ak 3: Muistisairauksien asiantuntija- ja tukikeskuksen toimintaan ja muistisairaiden ja heidän läheistensä tukemiseen Etelä- Karjalassa - vertaisryhmätoiminnalla  - ohjauksella ja neuvonnalla  - vapaaehtoistoiminnalla - tiedotuksella  - edunvalvonnalla  (Muistiluotsi) (246 000 €)</t>
         </is>
       </c>
     </row>
@@ -13535,7 +14418,7 @@
       </c>
       <c r="I308" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Kuopion alueen vammais- ja kansanterveysjärjestöjen yhteistoiminnan sekä tukihenkilö- ja vapaaehtoistyön edistämiseen ja kehittämiseen verkosto-  ryhmä-  koulutus- ja viestintätoiminnoilla sekä OLKA toiminnan toteuttamiseen KYS:ssa (Kansalaistoimintakeskus Tukipilari) (245 000 €)</t>
+          <t>Ak 1: Kuopion alueen vammais- ja kansanterveysjärjestöjen yhteistoiminnan sekä tukihenkilö- ja vapaaehtoistyön edistämiseen ja kehittämiseen verkosto-, ryhmä-, koulutus- ja viestintätoiminnoilla sekä OLKA toiminnan toteuttamiseen KYS:ssa (Kansalaistoimintakeskus Tukipilari) (245 000 €)</t>
         </is>
       </c>
     </row>
@@ -13568,7 +14451,7 @@
       </c>
       <c r="I309" t="inlineStr" s="0">
         <is>
-          <t>Ay 5: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (154 350 €) | Ak 4398: Lasten kielellisten taitojen tukemiseen  lukuinnostuksen lisäämiseen ja lukutaidon parantamiseen (Lukumummi ja -vaari toiminta) (90 000 €)</t>
+          <t>Ay 5: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (154 350 €) | Ak 4398: Lasten kielellisten taitojen tukemiseen, lukuinnostuksen lisäämiseen ja lukutaidon parantamiseen (Lukumummi ja -vaari toiminta) (90 000 €)</t>
         </is>
       </c>
     </row>
@@ -13601,7 +14484,7 @@
       </c>
       <c r="I310" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Järjestölähtöiseen kriisi- ja mielenterveystyöhön vaikeissa elämäntilanteissa oleville puhelimitse  verkossa  kasvokkaisissa asiakastapaamisissa  ammatillisesti ohjatuissa ryhmissä ja tukihenkilötoiminnassa (Kriisikeskus Etappi) (243 549 €)</t>
+          <t>Ak 1: Järjestölähtöiseen kriisi- ja mielenterveystyöhön vaikeissa elämäntilanteissa oleville puhelimitse, verkossa, kasvokkaisissa asiakastapaamisissa, ammatillisesti ohjatuissa ryhmissä ja tukihenkilötoiminnassa (Kriisikeskus Etappi) (243 549 €)</t>
         </is>
       </c>
     </row>
@@ -13634,7 +14517,7 @@
       </c>
       <c r="I311" t="inlineStr" s="0">
         <is>
-          <t>Ak 10149: Yläkoululaisten ja toisen asteen opiskelijoiden mielenterveyden ja elämäntaitojen vahvistamiseen työpajoilla  opiskelijalähtöisillä projekteilla sekä mentorointitoiminnalla (132 000 €) | Ak 2364: Nuorten mielenterveyden edistämiseen nuorilta nuorille periaatteella  nuoria osallistavien toimintamallien levittämiseen sekä vaikuttamistyöhön erityisesti internetiä ja sosiaalista mediaa hyödyntämällä (108 393 €)</t>
+          <t>Ak 10149: Yläkoululaisten ja toisen asteen opiskelijoiden mielenterveyden ja elämäntaitojen vahvistamiseen työpajoilla, opiskelijalähtöisillä projekteilla sekä mentorointitoiminnalla (132 000 €) | Ak 2364: Nuorten mielenterveyden edistämiseen nuorilta nuorille periaatteella, nuoria osallistavien toimintamallien levittämiseen sekä vaikuttamistyöhön erityisesti internetiä ja sosiaalista mediaa hyödyntämällä (108 393 €)</t>
         </is>
       </c>
     </row>
@@ -13667,7 +14550,7 @@
       </c>
       <c r="I312" t="inlineStr" s="0">
         <is>
-          <t>Ak 10360: OLKA-toimintamallin mukaiseen vapaaehtoistoiminnan koordinointiin  kehittämiseen sekä julkisen terveydenhuollon ja järjestöjen yhteistyön edistämiseen Etelä-Savon hyvinvointialueella (OLKA-toiminta Etelä-Savo) (125 000 €) | Ak 1: Järjestön ja sen jäsenyhdistysten yhteistyön  toimintaedellytysten ja vaikuttamismahdollisuuksien tukemiseen sekä järjestötalon toimintaan Etelä-Savossa (114 450 €)</t>
+          <t>Ak 10360: OLKA-toimintamallin mukaiseen vapaaehtoistoiminnan koordinointiin, kehittämiseen sekä julkisen terveydenhuollon ja järjestöjen yhteistyön edistämiseen Etelä-Savon hyvinvointialueella (OLKA-toiminta Etelä-Savo) (125 000 €) | Ak 1: Järjestön ja sen jäsenyhdistysten yhteistyön, toimintaedellytysten ja vaikuttamismahdollisuuksien tukemiseen sekä järjestötalon toimintaan Etelä-Savossa (114 450 €)</t>
         </is>
       </c>
     </row>
@@ -13700,7 +14583,7 @@
       </c>
       <c r="I313" t="inlineStr" s="0">
         <is>
-          <t>Ak 5: Sisäkorvaistutteen saaneiden lasten ja nuorten sekä heidän perheidensä toimintakyvyn ja identiteetin vahvistumiseen ja hyvinvoinnin lisäämiseen vertaistuen  tapahtumien  oikeuksienvalvonnan  tiedontuotannon ja viestinnän avulla (131 314 €) | Ak 11168: Kuulovammaisten lasten kielen ja kuulon kehittymisen tukemiseen ja lapsen ja vanhemman vuorovaikutuksen  edistämiseen puhe-  kuulo- ja etämuskaritoiminnan  tapahtumien ja koulutusten keinoin (107 500 €)</t>
+          <t>Ak 5: Sisäkorvaistutteen saaneiden lasten ja nuorten sekä heidän perheidensä toimintakyvyn ja identiteetin vahvistumiseen ja hyvinvoinnin lisäämiseen vertaistuen, tapahtumien, oikeuksienvalvonnan, tiedontuotannon ja viestinnän avulla (131 314 €) | Ak 11168: Kuulovammaisten lasten kielen ja kuulon kehittymisen tukemiseen ja lapsen ja vanhemman vuorovaikutuksen  edistämiseen puhe-, kuulo- ja etämuskaritoiminnan, tapahtumien ja koulutusten keinoin (107 500 €)</t>
         </is>
       </c>
     </row>
@@ -13733,7 +14616,7 @@
       </c>
       <c r="I314" t="inlineStr" s="0">
         <is>
-          <t>Ak 1953: Tuki- ja liikuntaelinterveyttä kaikille - tietoa ja keinoja tuki- ja liikuntaelinterveyden edistämiseen väestölle  vaikuttajille ja terveysalan ammattilaisille (237 937 €)</t>
+          <t>Ak 1953: Tuki- ja liikuntaelinterveyttä kaikille - tietoa ja keinoja tuki- ja liikuntaelinterveyden edistämiseen väestölle, vaikuttajille ja terveysalan ammattilaisille (237 937 €)</t>
         </is>
       </c>
     </row>
@@ -13766,9 +14649,7 @@
       </c>
       <c r="I315" t="inlineStr" s="0">
         <is>
-          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (135 000 €) | Ak 2: Poliovammaisten toimintakyvyn ylläpitoon ja voimavarojen vahvistamiseen järjestölähtöisellä ja vertaistuellisella ryhmätoiminnalla
-- alueellisiin avo- ja laitoskursseihin
-- verkossa tapahtuvaan ryhmätoimintaan (99 000 €)</t>
+          <t>Ay 1: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (135 000 €) | Ak 2: Poliovammaisten toimintakyvyn ylläpitoon ja voimavarojen vahvistamiseen järjestölähtöisellä ja vertaistuellisella ryhmätoiminnalla - alueellisiin avo- ja laitoskursseihin - verkossa tapahtuvaan ryhmätoimintaan (99 000 €)</t>
         </is>
       </c>
     </row>
@@ -13867,7 +14748,7 @@
       </c>
       <c r="I318" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Romanijärjestöjen toimintaedellytysten vahvistamiseen sekä romaniväestön osallisuuden ja koulutus- ja työllisyystilanteen edistämiseen koulutusten  neuvonnan  tiedottamisen  matalan kynnyksen toiminnan sekä vertais- ja vaikuttamistoiminnan avulla. (148 077 €) | Ak 6079: Jäsenjärjestöille kohdistettaviin avustuksiin (21 000 €) | C 13760: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Mahdollisuus osallisuuteen" osarahoitukseen järjestölle (2026) (11 825 €)</t>
+          <t>Ak 1: Romanijärjestöjen toimintaedellytysten vahvistamiseen sekä romaniväestön osallisuuden ja koulutus- ja työllisyystilanteen edistämiseen koulutusten, neuvonnan, tiedottamisen, matalan kynnyksen toiminnan sekä vertais- ja vaikuttamistoiminnan avulla. (148 077 €) | C 13759: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Mahdollisuus osallisuuteen Pohjois-Savossa" osarahoitukseen järjestölle (2026-2027) (49 638 €) | Ak 6079: Jäsenjärjestöille kohdistettaviin avustuksiin (21 000 €) | C 13760: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Mahdollisuus osallisuuteen" osarahoitukseen järjestölle (2026) (11 825 €)</t>
         </is>
       </c>
     </row>
@@ -13900,8 +14781,7 @@
       </c>
       <c r="I319" t="inlineStr" s="0">
         <is>
-          <t>Ak 1968: Erityistä tukea tarvitsevien nuorten auttamiseen kasvokkain ja internetissä sekä nuorten kanssa toimivien vapaaehtoisten koulutukseen ja tukemiseen 
-(Zemppari- ja Vertzi-toiminta) (153 761 €) | Ay 2: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (76 256 €)</t>
+          <t>Ak 1968: Erityistä tukea tarvitsevien nuorten auttamiseen kasvokkain ja internetissä sekä nuorten kanssa toimivien vapaaehtoisten koulutukseen ja tukemiseen  (Zemppari- ja Vertzi-toiminta) (153 761 €) | Ay 2: Yleisavustuksena avustuksen saajan yleishyödylliseen toimintaan (76 256 €)</t>
         </is>
       </c>
     </row>
@@ -13934,7 +14814,7 @@
       </c>
       <c r="I320" t="inlineStr" s="0">
         <is>
-          <t>Ak 2320: Turkulaisten ja lähialueiden työikäisten ja kolmanteen ikään kuuluvien tuki- ja liikuntaelimistön terveydenedistämistyöhön  maksuttomaan ohjaukseen ja neuvontaan sekä tapahtumien toteuttamiseen (230 000 €)</t>
+          <t>Ak 2320: Turkulaisten ja lähialueiden työikäisten ja kolmanteen ikään kuuluvien tuki- ja liikuntaelimistön terveydenedistämistyöhön, maksuttomaan ohjaukseen ja neuvontaan sekä tapahtumien toteuttamiseen (230 000 €)</t>
         </is>
       </c>
     </row>
@@ -13967,7 +14847,7 @@
       </c>
       <c r="I321" t="inlineStr" s="0">
         <is>
-          <t>Ak 9661: Yli 60-vuotiaiden digitaalisten taitojen vahvistamiseen ja syrjäytymisen ehkäisemiseen matalan kynnyksen kurssitoiminnalla Kymenlaaksossa (150 696 €) | Ak 2402: Alle 30-vuotiaiden nuorten ja nuorten aikuisten sosiaalisen jännittämisen lievittämiseen  psyykkisen ja sosiaalisen toimintakyvyn edistämiseen sekä työelämäosallisuuden  vahvistamiseen ohjauksella ja ryhmätoiminnoilla Kotkassa ja Haminassa (Avittaja) (78 864 €)</t>
+          <t>Ak 9661: Yli 60-vuotiaiden digitaalisten taitojen vahvistamiseen ja syrjäytymisen ehkäisemiseen matalan kynnyksen kurssitoiminnalla Kymenlaaksossa (150 696 €) | Ak 2402: Alle 30-vuotiaiden nuorten ja nuorten aikuisten sosiaalisen jännittämisen lievittämiseen, psyykkisen ja sosiaalisen toimintakyvyn edistämiseen sekä työelämäosallisuuden  vahvistamiseen ohjauksella ja ryhmätoiminnoilla Kotkassa ja Haminassa (Avittaja) (78 864 €)</t>
         </is>
       </c>
     </row>
@@ -14000,7 +14880,7 @@
       </c>
       <c r="I322" t="inlineStr" s="0">
         <is>
-          <t>Ak 9811: Turvapaikanhakijoiden  pakolaisten ja globaalista etelästä muuttaneiden työelämäosallisuuden ja hyvinvoinnin vahvistamiseen yksilöllisen tuen  vertaistoiminnan ja osaamiskartoitusten sekä työelämäyhteistyön ja vaikuttamistoiminnan avulla. Avustuksella ylläpidetään ja kehitetään myös sähköistä alustaa (186 000 €) | C 13735: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Unelmista urapoluille" osarahoitukseen järjestölle (2026-2028) (43 374 €)</t>
+          <t>Ak 9811: Turvapaikanhakijoiden, pakolaisten ja globaalista etelästä muuttaneiden työelämäosallisuuden ja hyvinvoinnin vahvistamiseen yksilöllisen tuen, vertaistoiminnan ja osaamiskartoitusten sekä työelämäyhteistyön ja vaikuttamistoiminnan avulla. Avustuksella ylläpidetään ja kehitetään myös sähköistä alustaa (186 000 €) | C 13735: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Unelmista urapoluille" osarahoitukseen järjestölle (2026-2028) (43 374 €)</t>
         </is>
       </c>
     </row>
@@ -14033,7 +14913,7 @@
       </c>
       <c r="I323" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Lapsikaappauksen kokeneiden  sen uhan alla tai keskellä vaikeaa kansainvälistä huolto- tai tapaamiskiistaa elävien perheiden auttamiseen ohjauksen  neuvonnan  vertaistuki- ja vapaaehtoistoiminnan keinoin sekä lapsikaappausilmiöstä tiedottamiseen ja kouluttamiseen (Toivon Talo) (228 480 €)</t>
+          <t>Ak 1: Lapsikaappauksen kokeneiden, sen uhan alla tai keskellä vaikeaa kansainvälistä huolto- tai tapaamiskiistaa elävien perheiden auttamiseen ohjauksen, neuvonnan, vertaistuki- ja vapaaehtoistoiminnan keinoin sekä lapsikaappausilmiöstä tiedottamiseen ja kouluttamiseen (Toivon Talo) (228 480 €)</t>
         </is>
       </c>
     </row>
@@ -14066,7 +14946,7 @@
       </c>
       <c r="I324" t="inlineStr" s="0">
         <is>
-          <t>Ak 5: Itsemurhan tehneiden henkilöiden läheisten tukemiseen ja yksinäisyyden ehkäisemiseen vertaistukitoiminnan  tapahtumien ja viestinnän keinoin (227 115 €)</t>
+          <t>Ak 5: Itsemurhan tehneiden henkilöiden läheisten tukemiseen ja yksinäisyyden ehkäisemiseen vertaistukitoiminnan, tapahtumien ja viestinnän keinoin (227 115 €)</t>
         </is>
       </c>
     </row>
@@ -14099,7 +14979,7 @@
       </c>
       <c r="I325" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Vapaaehtoistoimijoiden koordinoimiseen liikunta-  näkö- ja kehitysvammaisille sekä muistiasiakkaille Varsinais-Suomen ja Satakunnan alueella. Vapaaehtoistoiminnan ylläpitämiseen ja kehittämiseen koulutusten  vertaistuen ja tiedotuksen kautta. (226 013 €)</t>
+          <t>Ak 1: Vapaaehtoistoimijoiden koordinoimiseen liikunta-, näkö- ja kehitysvammaisille sekä muistiasiakkaille Varsinais-Suomen ja Satakunnan alueella. Vapaaehtoistoiminnan ylläpitämiseen ja kehittämiseen koulutusten, vertaistuen ja tiedotuksen kautta. (226 013 €)</t>
         </is>
       </c>
     </row>
@@ -14198,7 +15078,7 @@
       </c>
       <c r="I328" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Syömishäiriötä sairastavien ja heidän läheistensä hyvinvoinnin parantamiseen ryhmä- ja yksilötoiminnalla  vertaistuella  vapaaehtoistyöllä  koulutuksella ja viestinnällä (225 000 €)</t>
+          <t>Ak 1: Syömishäiriötä sairastavien ja heidän läheistensä hyvinvoinnin parantamiseen ryhmä- ja yksilötoiminnalla, vertaistuella, vapaaehtoistyöllä, koulutuksella ja viestinnällä (225 000 €)</t>
         </is>
       </c>
     </row>
@@ -14396,7 +15276,7 @@
       </c>
       <c r="I334" t="inlineStr" s="0">
         <is>
-          <t>Ak 6359: TUVA-koulutuksessa olevien nuorten sekä ilman työtä ja opiskelupaikkaa olevien nuorten hyvinvoinnin tukeen  sosiaaliseen vahvistamiseen ja itsetuntemuksen parantamiseen (216 336 €)</t>
+          <t>Ak 6359: TUVA-koulutuksessa olevien nuorten sekä ilman työtä ja opiskelupaikkaa olevien nuorten hyvinvoinnin tukeen, sosiaaliseen vahvistamiseen ja itsetuntemuksen parantamiseen (216 336 €)</t>
         </is>
       </c>
     </row>
@@ -14462,7 +15342,7 @@
       </c>
       <c r="I336" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Mielenterveyskuntoutujien aktiivisuuden ja osallisuuden lisäämiseen matalan kynnyksen kohtaamispaikkatoiminnan  vertaistoiminnan  palveluohjauksen ja verkkovälitteisen toiminnan avulla Lahden seudulla (215 250 €)</t>
+          <t>Ak 2: Mielenterveyskuntoutujien aktiivisuuden ja osallisuuden lisäämiseen matalan kynnyksen kohtaamispaikkatoiminnan, vertaistoiminnan, palveluohjauksen ja verkkovälitteisen toiminnan avulla Lahden seudulla (215 250 €)</t>
         </is>
       </c>
     </row>
@@ -14495,7 +15375,7 @@
       </c>
       <c r="I337" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Keski-Uudenmaan alueen sosiaali- ja terveysjärjestöverkoston toimintaan ja sen kehittämiseen  vapaaehtois- ja vertaistuen mahdollistamiseen sekä OLKA- toimintamallin mukaiseen toimintaan Keski-Uudellamaalla sekä Vantaan ja Keravan hyvinvointialueella. (214 987 €)</t>
+          <t>Ak 1: Keski-Uudenmaan alueen sosiaali- ja terveysjärjestöverkoston toimintaan ja sen kehittämiseen, vapaaehtois- ja vertaistuen mahdollistamiseen sekä OLKA- toimintamallin mukaiseen toimintaan Keski-Uudellamaalla sekä Vantaan ja Keravan hyvinvointialueella. (214 987 €)</t>
         </is>
       </c>
     </row>
@@ -14561,7 +15441,7 @@
       </c>
       <c r="I339" t="inlineStr" s="0">
         <is>
-          <t>Ak 11287: Turvapaikanhakijoiden  paperittomien ja muiden haavoittuvassa asemassa olevien maahan muuttaneiden mielen hyvinvoinnin  toimijuuden ja yhteiskuntaan kiinnittymisen vahvistamiseen yksilöllisen tuen  neuvonnan ja palveluohjauksen avulla (213 750 €)</t>
+          <t>Ak 11287: Turvapaikanhakijoiden, paperittomien ja muiden haavoittuvassa asemassa olevien maahan muuttaneiden mielen hyvinvoinnin, toimijuuden ja yhteiskuntaan kiinnittymisen vahvistamiseen yksilöllisen tuen, neuvonnan ja palveluohjauksen avulla (213 750 €)</t>
         </is>
       </c>
     </row>
@@ -14594,7 +15474,7 @@
       </c>
       <c r="I340" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Työikäisten ja ikääntyneiden maahanmuuttajataustaisten naisten syrjäytymisen ehkäisemiseen ja kaksisuuntaisen kotoutumisen vahvistamiseen yksilöohjauksen  koulutuksen  vertaistuen sekä vapaaehtois- ja ryhmätoiminnan avulla Turussa ja sen lähialueilla (212 800 €)</t>
+          <t>Ak 3: Työikäisten ja ikääntyneiden maahanmuuttajataustaisten naisten syrjäytymisen ehkäisemiseen ja kaksisuuntaisen kotoutumisen vahvistamiseen yksilöohjauksen, koulutuksen, vertaistuen sekä vapaaehtois- ja ryhmätoiminnan avulla Turussa ja sen lähialueilla (212 800 €)</t>
         </is>
       </c>
     </row>
@@ -14660,7 +15540,7 @@
       </c>
       <c r="I342" t="inlineStr" s="0">
         <is>
-          <t>Ak 7136: Sosiaali- ja terveyspalveluiden potilaiden ja asiakkaiden oikeuksien edistämiseen  tiedottamisen  maksuttoman juridisen neuvonnan sekä koulutusten avulla (97 125 €) | Ak 2: Asumisesta aiheutuvien sosiaalisten  taloudellisten ja oikeudellisten ongelmien ennaltaehkäisyyn ja ratkaisemiseen asumisasiamiehen neuvonta- ja koulutustoiminnalla (73 481 €) | Ak 9427: Jäsenjärjestöille kohdistettaviin avustuksiin (41 687 €)</t>
+          <t>Ak 7136: Sosiaali- ja terveyspalveluiden potilaiden ja asiakkaiden oikeuksien edistämiseen  tiedottamisen, maksuttoman juridisen neuvonnan sekä koulutusten avulla (97 125 €) | Ak 2: Asumisesta aiheutuvien sosiaalisten, taloudellisten ja oikeudellisten ongelmien ennaltaehkäisyyn ja ratkaisemiseen asumisasiamiehen neuvonta- ja koulutustoiminnalla (73 481 €) | Ak 9427: Jäsenjärjestöille kohdistettaviin avustuksiin (41 687 €)</t>
         </is>
       </c>
     </row>
@@ -14726,7 +15606,7 @@
       </c>
       <c r="I344" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Sosiaali- ja terveysjärjestöjen toimintakeskuksen toimintaan  yhdistystoiminnan ja vapaaehtoistyön tukemiseen ja matalan kynnyksen kohtaamispaikan toimintaan Hyvinkäällä (210 756 €)</t>
+          <t>Ak 1: Sosiaali- ja terveysjärjestöjen toimintakeskuksen toimintaan, yhdistystoiminnan ja vapaaehtoistyön tukemiseen ja matalan kynnyksen kohtaamispaikan toimintaan Hyvinkäällä (210 756 €)</t>
         </is>
       </c>
     </row>
@@ -14759,7 +15639,7 @@
       </c>
       <c r="I345" t="inlineStr" s="0">
         <is>
-          <t>Ak 3257: Erityisen haavoittuvassa asemassa olevien seksuaali- ja sukupuolivähemmistöihin kuuluvien ihmisten osallisuuden lisäämiseen sekä yksinäisyyden ja syrjäytymisen ennaltaehkäisyyn yksilöllisen tuen  vertaisryhmien  yhteisöllisen toiminnan sekä vaikuttamistoiminnan ja koulutusten avulla (210 500 €)</t>
+          <t>Ak 3257: Erityisen haavoittuvassa asemassa olevien seksuaali- ja sukupuolivähemmistöihin kuuluvien ihmisten osallisuuden lisäämiseen sekä yksinäisyyden ja syrjäytymisen ennaltaehkäisyyn yksilöllisen tuen, vertaisryhmien, yhteisöllisen toiminnan sekä vaikuttamistoiminnan ja koulutusten avulla (210 500 €)</t>
         </is>
       </c>
     </row>
@@ -14792,7 +15672,7 @@
       </c>
       <c r="I346" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Mielenterveysomaisten hyvinvoinnin  osallisuuden ja toimijuuden vahvistaminen henkilökohtaisen neuvonnan ja ryhmämuotoisen tuen sekä vertais-  vapaaehtois- ja vaikuttamistoiminnan avulla Etelä-Pohjanmaalla (210 000 €)</t>
+          <t>Ak 2: Mielenterveysomaisten hyvinvoinnin, osallisuuden ja toimijuuden vahvistaminen henkilökohtaisen neuvonnan ja ryhmämuotoisen tuen sekä vertais-, vapaaehtois- ja vaikuttamistoiminnan avulla Etelä-Pohjanmaalla (210 000 €)</t>
         </is>
       </c>
     </row>
@@ -14825,7 +15705,7 @@
       </c>
       <c r="I347" t="inlineStr" s="0">
         <is>
-          <t>Ak 10733: Lapsuudessa seksuaaliväkivaltaa kokeneiden yli 18-vuotiaiden tukeen muun muassa puhelin ja chat-neuvonnan  ryhmätoiminnan ja tiedotuksen keinoin. (210 000 €)</t>
+          <t>Ak 10733: Lapsuudessa seksuaaliväkivaltaa kokeneiden yli 18-vuotiaiden tukeen muun muassa puhelin ja chat-neuvonnan, ryhmätoiminnan ja tiedotuksen keinoin. (210 000 €)</t>
         </is>
       </c>
     </row>
@@ -14891,7 +15771,7 @@
       </c>
       <c r="I349" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Endometrioosia  adenomyoosia  PCOS:ää sekä vulvodyniaa sairastavien naisten hyvinvoinnin lisäämiseen ja edunvalvonnan edistämiseen toteuttamalla vapaaehtois- ja vertaistukitoimintaa sekä kehittämällä vaikuttamistyötä (Yhdessä olemme enemmän) (209 475 €)</t>
+          <t>Ak 2: Endometrioosia, adenomyoosia, PCOS:ää sekä vulvodyniaa sairastavien naisten hyvinvoinnin lisäämiseen ja edunvalvonnan edistämiseen toteuttamalla vapaaehtois- ja vertaistukitoimintaa sekä kehittämällä vaikuttamistyötä (Yhdessä olemme enemmän) (209 475 €)</t>
         </is>
       </c>
     </row>
@@ -14924,7 +15804,7 @@
       </c>
       <c r="I350" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen  neuvonnan  vertaistoiminnan ja valmennusten avulla Päijät-Hämeessä (OmaisOiva) (208 097 €)</t>
+          <t>Ak 2: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen, neuvonnan, vertaistoiminnan ja valmennusten avulla Päijät-Hämeessä (OmaisOiva) (208 097 €)</t>
         </is>
       </c>
     </row>
@@ -14957,7 +15837,7 @@
       </c>
       <c r="I351" t="inlineStr" s="0">
         <is>
-          <t>Ak 1138: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen  neuvonnan  vertaistoiminnan ja valmennusten avulla Mikkelin seudulla (OmaisOiva) (207 270 €)</t>
+          <t>Ak 1138: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen, neuvonnan, vertaistoiminnan ja valmennusten avulla Mikkelin seudulla (OmaisOiva) (207 270 €)</t>
         </is>
       </c>
     </row>
@@ -14990,8 +15870,7 @@
       </c>
       <c r="I352" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen  neuvonnan  vertaistoiminnan ja valmennusten avulla Satakunnassa 
-(OmaisOiva) (206 850 €)</t>
+          <t>Ak 1: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen, neuvonnan, vertaistoiminnan ja valmennusten avulla Satakunnassa  (OmaisOiva) (206 850 €)</t>
         </is>
       </c>
     </row>
@@ -15057,7 +15936,7 @@
       </c>
       <c r="I354" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Vaikeissa elämäntilanteissa oleville henkilöille tarkoitettuun järjestölähtöiseen kriisi- ja mielenterveystyöhön yksilö- ja ryhmämuotoisen auttamisen sekä vapaaehtoistoiminnan keinoin (MIELI Kriisikeskus Etelä-Karjalan  toimipisteet Lappeenranta ja Imatra) (205 065 €)</t>
+          <t>Ak 2: Vaikeissa elämäntilanteissa oleville henkilöille tarkoitettuun järjestölähtöiseen kriisi- ja mielenterveystyöhön yksilö- ja ryhmämuotoisen auttamisen sekä vapaaehtoistoiminnan keinoin (MIELI Kriisikeskus Etelä-Karjalan, toimipisteet Lappeenranta ja Imatra) (205 065 €)</t>
         </is>
       </c>
     </row>
@@ -15090,8 +15969,7 @@
       </c>
       <c r="I355" t="inlineStr" s="0">
         <is>
-          <t>Ak 11887: Suomessa toimivien venäjänkielisten sosiaali- ja terveysjärjestöjen toiminnan  järjestöosaamisen ja verkostoitumisen kehittämiseen ja vahvistamiseen neuvonnan  koulutusten  mentoroinnin sekä keskusjärjestön viestinnän ja vaikuttamistoiminnan avulla
-(Näkymätön voimavara) (174 400 €) | Ak 11516: Jäsenjärjestöille kohdistettaviin avustuksiin (30 000 €)</t>
+          <t>Ak 11887: Suomessa toimivien venäjänkielisten sosiaali- ja terveysjärjestöjen toiminnan, järjestöosaamisen ja verkostoitumisen kehittämiseen ja vahvistamiseen neuvonnan, koulutusten, mentoroinnin sekä keskusjärjestön viestinnän ja vaikuttamistoiminnan avulla (Näkymätön voimavara) (174 400 €) | Ak 11516: Jäsenjärjestöille kohdistettaviin avustuksiin (30 000 €)</t>
         </is>
       </c>
     </row>
@@ -15124,7 +16002,7 @@
       </c>
       <c r="I356" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Oppimisvaikeuksista ja toimintarajoitteista aiheutuvien haittojen vähentämiseen apuvälineiden käytön ohjaamisella  esteettömän ohjemateriaalin tuottamisella sekä tiedottamalla (204 111 €)</t>
+          <t>Ak 1: Oppimisvaikeuksista ja toimintarajoitteista aiheutuvien haittojen vähentämiseen apuvälineiden käytön ohjaamisella, esteettömän ohjemateriaalin tuottamisella sekä tiedottamalla (204 111 €)</t>
         </is>
       </c>
     </row>
@@ -15157,7 +16035,7 @@
       </c>
       <c r="I357" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Yksilö-  pari-  ja ryhmämuotoiseen avokriisityöhön perhe- ja lähisuhdeväkivallan uhrien ja tekijöiden kanssa sekä nuorten kanssa tehtävään väkivaltatyöhön  ennaltaehkäisevään  seurustelusuhteiden turvallisuutta lisäävään työhön ja vapaaehtoistoiminnan kehittämiseen. Lapsiperheitä tukevaan järjestölähtöiseen erotyöhön. (Kriisityön avopalvelut) (203 770 €)</t>
+          <t>Ak 1: Yksilö-, pari-  ja ryhmämuotoiseen avokriisityöhön perhe- ja lähisuhdeväkivallan uhrien ja tekijöiden kanssa sekä nuorten kanssa tehtävään väkivaltatyöhön, ennaltaehkäisevään, seurustelusuhteiden turvallisuutta lisäävään työhön ja vapaaehtoistoiminnan kehittämiseen. Lapsiperheitä tukevaan järjestölähtöiseen erotyöhön. (Kriisityön avopalvelut) (203 770 €)</t>
         </is>
       </c>
     </row>
@@ -15190,8 +16068,7 @@
       </c>
       <c r="I358" t="inlineStr" s="0">
         <is>
-          <t>Ak 6208: Vapaaehtoistoiminnan ammatillinen ohjaus ja koordinointi; 
-Perhekummi-  kaveri- ja Ystäväksi maahanmuuttajaäidille - toiminnan ja sukupolvitoiminnan toteuttaminen Satakunnan alueella (131 000 €) | Ak 1: 7-14-vuotiaiden lasten ja nuorten osallisuuden ja itseluottamuksen lisäämiseen sekä kuuntelevan ja välittävän aikuisen tuen tarjoamiseen ylläpitämällä kahta kohtaamispaikkaa ja tukiviikonlopputoimintaa Porissa (Tuki- ja turvapaikka Porkkanapesä) (72 500 €)</t>
+          <t>Ak 6208: Vapaaehtoistoiminnan ammatillinen ohjaus ja koordinointi;  Perhekummi-, kaveri- ja Ystäväksi maahanmuuttajaäidille - toiminnan ja sukupolvitoiminnan toteuttaminen Satakunnan alueella (131 000 €) | Ak 1: 7-14-vuotiaiden lasten ja nuorten osallisuuden ja itseluottamuksen lisäämiseen sekä kuuntelevan ja välittävän aikuisen tuen tarjoamiseen ylläpitämällä kahta kohtaamispaikkaa ja tukiviikonlopputoimintaa Porissa (Tuki- ja turvapaikka Porkkanapesä) (72 500 €)</t>
         </is>
       </c>
     </row>
@@ -15224,11 +16101,7 @@
       </c>
       <c r="I359" t="inlineStr" s="0">
         <is>
-          <t>Ak 14: Neuropsykiatrisia piirteitä omaavien lasten ja nuorten sekä heidän perheidensä voimavarojen tukemiseen sekä osallisuuden ja arjen hallinnan lisäämiseen
-- Matalan kynnyksen ohjaukseen ja neuvontaan
-- Vertaistukitoimintaan
-- Osallistaviin ja kuulemista edistäviin tilaisuuksiin
-(PERPE-keskus) (203 029 €)</t>
+          <t>Ak 14: Neuropsykiatrisia piirteitä omaavien lasten ja nuorten sekä heidän perheidensä voimavarojen tukemiseen sekä osallisuuden ja arjen hallinnan lisäämiseen - Matalan kynnyksen ohjaukseen ja neuvontaan - Vertaistukitoimintaan - Osallistaviin ja kuulemista edistäviin tilaisuuksiin (PERPE-keskus) (203 029 €)</t>
         </is>
       </c>
     </row>
@@ -15294,7 +16167,7 @@
       </c>
       <c r="I361" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Henkirikoksen uhrien läheisten hyvinvoinnin ja sosiaalisen toimintakyvyn lisäämiseen valtakunnallisen palveluohjauksen  vertaistuen  yksilöllisen tuen ja kurssitoiminnan sekä vaikuttamistyön keinoin. (200 000 €)</t>
+          <t>Ak 2: Henkirikoksen uhrien läheisten hyvinvoinnin ja sosiaalisen toimintakyvyn lisäämiseen valtakunnallisen palveluohjauksen, vertaistuen, yksilöllisen tuen ja kurssitoiminnan sekä vaikuttamistyön keinoin. (200 000 €)</t>
         </is>
       </c>
     </row>
@@ -15327,7 +16200,7 @@
       </c>
       <c r="I362" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Erityislasten vanhempien osallisuuden ja vanhemmuuden tukemiseen vertaistuen  vapaaehtoistoiminnan  ohjauksen  kouluttamisen ja yhteiskunnallisen vaikuttamisen avulla. (200 000 €)</t>
+          <t>Ak 1: Erityislasten vanhempien osallisuuden ja vanhemmuuden tukemiseen vertaistuen, vapaaehtoistoiminnan, ohjauksen, kouluttamisen ja yhteiskunnallisen vaikuttamisen avulla. (200 000 €)</t>
         </is>
       </c>
     </row>
@@ -15360,8 +16233,7 @@
       </c>
       <c r="I363" t="inlineStr" s="0">
         <is>
-          <t>Ak 2232: Kaksisuuntaisen kotoutumisen ja eri taustaisten ihmisten kohtaamisten lisäämiseen sekä maahan muuttaneiden osallisuuden ja toimijuuden vahvistamiseen matalan kynnyksen toiminnalla  neuvonnalla  vapaaehtois- ja vertaisryhmätoiminnalla sekä tapahtumilla ja yhteistyöllä
-(Monikulttuurikeskus Gloria) (198 954 €)</t>
+          <t>Ak 2232: Kaksisuuntaisen kotoutumisen ja eri taustaisten ihmisten kohtaamisten lisäämiseen sekä maahan muuttaneiden osallisuuden ja toimijuuden vahvistamiseen matalan kynnyksen toiminnalla, neuvonnalla, vapaaehtois- ja vertaisryhmätoiminnalla sekä tapahtumilla ja yhteistyöllä (Monikulttuurikeskus Gloria) (198 954 €)</t>
         </is>
       </c>
     </row>
@@ -15394,7 +16266,7 @@
       </c>
       <c r="I364" t="inlineStr" s="0">
         <is>
-          <t>Ak 4476: Maahanmuuttajanaisten ja heidän läheistensä hyvinvoinnin ja osallisuuden vahvistamiseen sekä kaksisuuntaisen kotoutumisen edistämiseen vertaisryhmä- ja harrastustoiminnan  neuvonnan  yksilöohjauksen ja vapaaehtoistoiminnan avulla Itä-Helsingissä (198 000 €)</t>
+          <t>Ak 4476: Maahanmuuttajanaisten ja heidän läheistensä hyvinvoinnin ja osallisuuden vahvistamiseen sekä kaksisuuntaisen kotoutumisen edistämiseen vertaisryhmä- ja harrastustoiminnan, neuvonnan, yksilöohjauksen ja vapaaehtoistoiminnan avulla Itä-Helsingissä (198 000 €)</t>
         </is>
       </c>
     </row>
@@ -15427,8 +16299,7 @@
       </c>
       <c r="I365" t="inlineStr" s="0">
         <is>
-          <t>Ak 3264: Yksinäisten  masentuneiden  sosiaalisesti syrjäytyneiden  monikulttuuristen  psyykkisesti oireilevien ja muiden erityistä tukea tarvitsevien tyttöjen ja nuorten naisten matalan kynnyksen toimintaan sekä ryhmä- ja yksilötukeen
-(Tyttöjen Talo Rovaniemi) (197 863 €)</t>
+          <t>Ak 3264: Yksinäisten, masentuneiden, sosiaalisesti syrjäytyneiden, monikulttuuristen, psyykkisesti oireilevien ja muiden erityistä tukea tarvitsevien tyttöjen ja nuorten naisten matalan kynnyksen toimintaan sekä ryhmä- ja yksilötukeen (Tyttöjen Talo Rovaniemi) (197 863 €)</t>
         </is>
       </c>
     </row>
@@ -15461,7 +16332,7 @@
       </c>
       <c r="I366" t="inlineStr" s="0">
         <is>
-          <t>Ak 5763: Valtimotautia sairastavien ja korkeassa sairastumisriskissä olevien henkilöiden  heidän läheisensä sekä muiden terveydestään kiinnostuneiden henkilöiden terveyden edistämiseen ja osallistumismahdollisuuksien tukemiseen. Eteläkarjalalaisten sydän- ja diabetesyhdistysten vertaistukitoiminnan koordinointiin  yhdistysten ryhmätoimintojen tukemiseen ja tilaisuuksien järjestämiseen yhteistyössä eri toimijoiden kanssa (Sydäntuki-toiminta) (195 750 €)</t>
+          <t>Ak 5763: Valtimotautia sairastavien ja korkeassa sairastumisriskissä olevien henkilöiden, heidän läheisensä sekä muiden terveydestään kiinnostuneiden henkilöiden terveyden edistämiseen ja osallistumismahdollisuuksien tukemiseen. Eteläkarjalalaisten sydän- ja diabetesyhdistysten vertaistukitoiminnan koordinointiin, yhdistysten ryhmätoimintojen tukemiseen ja tilaisuuksien järjestämiseen yhteistyössä eri toimijoiden kanssa (Sydäntuki-toiminta) (195 750 €)</t>
         </is>
       </c>
     </row>
@@ -15527,7 +16398,7 @@
       </c>
       <c r="I368" t="inlineStr" s="0">
         <is>
-          <t>Ak 12642: Järjestölähtöiseen ammatillisesti ja vapaaehtoistyönä toteutettavaan kriisi- ja mielenterveystyöhön vaikeissa elämäntilanteissa oleville tarjoamalla matalan kynnyksen keskustelutukea vastaanotolla  puhelimessa ja verkossa  koordinoimalla vapaaehtoistyötä sekä järjestämällä koulutuksia (Hyvinkään kriisikeskus Hymise) (193 871 €)</t>
+          <t>Ak 12642: Järjestölähtöiseen ammatillisesti ja vapaaehtoistyönä toteutettavaan kriisi- ja mielenterveystyöhön vaikeissa elämäntilanteissa oleville tarjoamalla matalan kynnyksen keskustelutukea vastaanotolla, puhelimessa ja verkossa, koordinoimalla vapaaehtoistyötä sekä järjestämällä koulutuksia (Hyvinkään kriisikeskus Hymise) (193 871 €)</t>
         </is>
       </c>
     </row>
@@ -15560,7 +16431,7 @@
       </c>
       <c r="I369" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Vammaisten maahanmuuttajien tukikeskus Hilman neuvonta-  ryhmä-  vertaistoimintaan sekä edunvalvontaan ja viestintään (192 937 €)</t>
+          <t>Ak 2: Vammaisten maahanmuuttajien tukikeskus Hilman neuvonta-, ryhmä-, vertaistoimintaan sekä edunvalvontaan ja viestintään (192 937 €)</t>
         </is>
       </c>
     </row>
@@ -15626,8 +16497,7 @@
       </c>
       <c r="I371" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Kaksisuuntaisen kotoutumisen sekä maahanmuuttajataustaisten toimintakyvyn ja osallisuuden edistämiseen neuvonnan  vertaisryhmien  palveluohjauksen  verkosto- ja viranomaisyhteistyön sekä kurssi- ja harrastustoiminnan avulla matalan kynnyksen kohtaamispaikassa. 
-Toimintapisteet Vantaan Hakunilassa ja Länsimäessä (190 733 €)</t>
+          <t>Ak 3: Kaksisuuntaisen kotoutumisen sekä maahanmuuttajataustaisten toimintakyvyn ja osallisuuden edistämiseen neuvonnan, vertaisryhmien, palveluohjauksen, verkosto- ja viranomaisyhteistyön sekä kurssi- ja harrastustoiminnan avulla matalan kynnyksen kohtaamispaikassa.  Toimintapisteet Vantaan Hakunilassa ja Länsimäessä (190 733 €)</t>
         </is>
       </c>
     </row>
@@ -15660,8 +16530,7 @@
       </c>
       <c r="I372" t="inlineStr" s="0">
         <is>
-          <t>Ak 9572: Ikääntyvien maahan muuttaneiden hyvinvoinnin  osallisuuden ja toimijuuden edistämiseen sekä vanhustyön ammattilaisten moninaisuusosaamisen vahvistamiseen kohtaamispaikkatoiminnan  vertaisryhmätoiminnan  yksilöllisen tuen ja neuvonnan sekä vapaaehtoistoiminnan avulla 
-(JADE-toimintakeskus) (190 000 €)</t>
+          <t>Ak 9572: Ikääntyvien maahan muuttaneiden hyvinvoinnin, osallisuuden ja toimijuuden edistämiseen sekä vanhustyön ammattilaisten moninaisuusosaamisen vahvistamiseen kohtaamispaikkatoiminnan, vertaisryhmätoiminnan, yksilöllisen tuen ja neuvonnan sekä vapaaehtoistoiminnan avulla  (JADE-toimintakeskus) (190 000 €)</t>
         </is>
       </c>
     </row>
@@ -15727,7 +16596,7 @@
       </c>
       <c r="I374" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Ikääntyneiden lähisuhdeväkivallan ja kaltoinkohtelun uhrien ja heidän läheistensä sekä väkivallan tekijöiden auttamiseen yksilö-  pari- ja ryhmätoiminnan keinoin. Lähisuhdeväkivallan ja kaltoinkohtelun ennaltaehkäisevään työhön ja tiedon tuottamiseen lähisuhdeväkivalta ilmiöstä. (189 425 €)</t>
+          <t>Ak 1: Ikääntyneiden lähisuhdeväkivallan ja kaltoinkohtelun uhrien ja heidän läheistensä sekä väkivallan tekijöiden auttamiseen yksilö-, pari- ja ryhmätoiminnan keinoin. Lähisuhdeväkivallan ja kaltoinkohtelun ennaltaehkäisevään työhön ja tiedon tuottamiseen lähisuhdeväkivalta ilmiöstä. (189 425 €)</t>
         </is>
       </c>
     </row>
@@ -15760,7 +16629,7 @@
       </c>
       <c r="I375" t="inlineStr" s="0">
         <is>
-          <t>Ak 11766: Mielenterveyskuntoutujien tasa-arvoisen osallisuuden  hyvinvoinnin ja terveyden edistämiseen elämäntapaohjauksella Päijät-Hämeessä (RAULI ha(ll)ussa -toiminta) (150 000 €) | C 13750: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Vertaisvoimaa työllistymiseen (210545)" osarahoitukseen järjestölle (2026-2028) (38 787 €)</t>
+          <t>Ak 11766: Mielenterveyskuntoutujien tasa-arvoisen osallisuuden, hyvinvoinnin ja terveyden edistämiseen elämäntapaohjauksella Päijät-Hämeessä (RAULI ha(ll)ussa -toiminta) (150 000 €) | C 13750: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Vertaisvoimaa työllistymiseen (210545)" osarahoitukseen järjestölle (2026-2028) (38 787 €)</t>
         </is>
       </c>
     </row>
@@ -15826,7 +16695,7 @@
       </c>
       <c r="I377" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Vaikeissa elämäntilanteissa oleville henkilöille suunnattuun järjestölähtöiseen kriisi- ja mielenterveystyöhön tarjoamalla matalan kynnyksen keskusteluapua  vapaaehtoistoimintaa ja mielenterveysosaamisen vahvistamista. (MIELI Kriisikeskus Meri-Lappi) (187 425 €)</t>
+          <t>Ak 1: Vaikeissa elämäntilanteissa oleville henkilöille suunnattuun järjestölähtöiseen kriisi- ja mielenterveystyöhön tarjoamalla matalan kynnyksen keskusteluapua, vapaaehtoistoimintaa ja mielenterveysosaamisen vahvistamista. (MIELI Kriisikeskus Meri-Lappi) (187 425 €)</t>
         </is>
       </c>
     </row>
@@ -15859,7 +16728,7 @@
       </c>
       <c r="I378" t="inlineStr" s="0">
         <is>
-          <t>Ak 3324: Mielenterveyskuntoutujien terveyttä  hyvinvointia  osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään tavoitteelliseen kohtaamispaikkatoimintaan (Salon klubitalo) (187 425 €)</t>
+          <t>Ak 3324: Mielenterveyskuntoutujien terveyttä, hyvinvointia, osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään tavoitteelliseen kohtaamispaikkatoimintaan (Salon klubitalo) (187 425 €)</t>
         </is>
       </c>
     </row>
@@ -15892,7 +16761,7 @@
       </c>
       <c r="I379" t="inlineStr" s="0">
         <is>
-          <t>Ak 7007: Odottavien  alle kouluikäisten ja alakouluikäisten lasten vanhempien vanhemmuuden ja perheen hyvinvoinnin tukemiseen arjessa ammatillisesti ohjatun vapaaehtoistoiminnan keinoin Pirkanmaan  Päijät-Hämeen ja Kanta-Hämeen alueella (Perhekummi-  lukumummi- ja vaaritoiminta sekä läksykummitoiminta) (185 374 €)</t>
+          <t>Ak 7007: Odottavien, alle kouluikäisten ja alakouluikäisten lasten vanhempien vanhemmuuden ja perheen hyvinvoinnin tukemiseen arjessa ammatillisesti ohjatun vapaaehtoistoiminnan keinoin Pirkanmaan, Päijät-Hämeen ja Kanta-Hämeen alueella (Perhekummi-, lukumummi- ja vaaritoiminta sekä läksykummitoiminta) (185 374 €)</t>
         </is>
       </c>
     </row>
@@ -15925,7 +16794,7 @@
       </c>
       <c r="I380" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Asukkaiden mielen hyvinvointia ja yhteisöllisyyttä lisäävään matalan kynnyksen kohtaamispaikka-  vertais- ja vapaaehtoistoimintaan Vaasassa (Mahis - Mahdollisuuksien talo / Möjligheternas hus) (185 000 €)</t>
+          <t>Ak 1: Asukkaiden mielen hyvinvointia ja yhteisöllisyyttä lisäävään matalan kynnyksen kohtaamispaikka-, vertais- ja vapaaehtoistoimintaan Vaasassa (Mahis - Mahdollisuuksien talo / Möjligheternas hus) (185 000 €)</t>
         </is>
       </c>
     </row>
@@ -15958,7 +16827,7 @@
       </c>
       <c r="I381" t="inlineStr" s="0">
         <is>
-          <t>Ak 3094: Seksuaali- ja sukupuolivähemmistöön kuuluvien henkilöiden seksuaalisen suuntautumisen  seksuaalisuuden ja sukupuoli-identiteetin jäsentymisen tukemiseen sekä elämänhallinnan ja hyvinvoinnin lisäämiseen valtakunnallisen puhelin- ja verkkoauttamisen sekä alueellisen vertaisryhmä- ja tukitoiminnan ja yhteistyön avulla (184 450 €)</t>
+          <t>Ak 3094: Seksuaali- ja sukupuolivähemmistöön kuuluvien henkilöiden seksuaalisen suuntautumisen, seksuaalisuuden ja sukupuoli-identiteetin jäsentymisen tukemiseen sekä elämänhallinnan ja hyvinvoinnin lisäämiseen valtakunnallisen puhelin- ja verkkoauttamisen sekä alueellisen vertaisryhmä- ja tukitoiminnan ja yhteistyön avulla (184 450 €)</t>
         </is>
       </c>
     </row>
@@ -16024,7 +16893,7 @@
       </c>
       <c r="I383" t="inlineStr" s="0">
         <is>
-          <t>Ak 5746: Yli 65-vuotiaiden sosiaalisen hyvinvoinnin  osallisuuden ja digitaitojen vahvistamiseen  yksinäisyyden ehkäisemiseen sekä itsenäisen kotona asumisen tukemiseen ryhmä- ja kohtaamispaikkatoiminnan avulla (Kalevan kulman Iloa arkeen -pysäkit) (181 913 €)</t>
+          <t>Ak 5746: Yli 65-vuotiaiden sosiaalisen hyvinvoinnin, osallisuuden ja digitaitojen vahvistamiseen, yksinäisyyden ehkäisemiseen sekä itsenäisen kotona asumisen tukemiseen ryhmä- ja kohtaamispaikkatoiminnan avulla (Kalevan kulman Iloa arkeen -pysäkit) (181 913 €)</t>
         </is>
       </c>
     </row>
@@ -16057,8 +16926,7 @@
       </c>
       <c r="I384" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Maahanmuuttajataustaisten osallisuuden  sosiaalisen vahvistumisen ja työelämävalmiuksien edistämiseen matalan kynnyksen toiminnalla.
-Toimintamuotoina yksilöohjaus ja ryhmätoiminta  oppilaitos- ja työnantajayhteistyö  asiantuntija- ja verkostotyö sekä vapaaehtoistoiminta (181 913 €)</t>
+          <t>Ak 2: Maahanmuuttajataustaisten osallisuuden, sosiaalisen vahvistumisen ja työelämävalmiuksien edistämiseen matalan kynnyksen toiminnalla. Toimintamuotoina yksilöohjaus ja ryhmätoiminta, oppilaitos- ja työnantajayhteistyö, asiantuntija- ja verkostotyö sekä vapaaehtoistoiminta (181 913 €)</t>
         </is>
       </c>
     </row>
@@ -16124,7 +16992,7 @@
       </c>
       <c r="I386" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Salon seudulla toimivien potilas- ja vammaisyhdistysten yhteistyön  edunvalvonnan ja vapaaehtoistoiminnan kehittämiseen sekä järjestöjen toimintaedellytysten turvaamiseen (180 600 €)</t>
+          <t>Ak 1: Salon seudulla toimivien potilas- ja vammaisyhdistysten yhteistyön, edunvalvonnan ja vapaaehtoistoiminnan kehittämiseen sekä järjestöjen toimintaedellytysten turvaamiseen (180 600 €)</t>
         </is>
       </c>
     </row>
@@ -16157,7 +17025,7 @@
       </c>
       <c r="I387" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Mielenterveysomaisten osallisuuden ja toimintakyvyn vahvistamiseen omaisneuvonnan  vertaistuen  omaiskurssien sekä mielenterveysomaisille ja ammattilaisille suunnatun tiedon lisäämisen ja vaikuttamistyön avulla Satakunnan alueella (177 000 €)</t>
+          <t>Ak 1: Mielenterveysomaisten osallisuuden ja toimintakyvyn vahvistamiseen omaisneuvonnan, vertaistuen, omaiskurssien sekä mielenterveysomaisille ja ammattilaisille suunnatun tiedon lisäämisen ja vaikuttamistyön avulla Satakunnan alueella (177 000 €)</t>
         </is>
       </c>
     </row>
@@ -16190,7 +17058,7 @@
       </c>
       <c r="I388" t="inlineStr" s="0">
         <is>
-          <t>Ak 6974: Alaikäisten lasten vanhempien ja maahanmuuttajaäitien vanhemmuuden ja osallisuuden tukemiseen sekä lasten ja nuorten yksinäisyyden ehkäisemiseen  sukupolvien välisen kohtaamisen mahdollistamiseen ja lukemissujuvuuden edistämiseen ammatillisesti ohjatun vapaaehtoisen tukihenkilötoiminnan sekä läksykerhotoiminnan keinoin (Ystäväksi maahanmuuttajaäidille-  kaveri- ja perhekummitoiminnat  sukupolvien välinen toiminta) (174 825 €)</t>
+          <t>Ak 6974: Alaikäisten lasten vanhempien ja maahanmuuttajaäitien vanhemmuuden ja osallisuuden tukemiseen sekä lasten ja nuorten yksinäisyyden ehkäisemiseen, sukupolvien välisen kohtaamisen mahdollistamiseen ja lukemissujuvuuden edistämiseen ammatillisesti ohjatun vapaaehtoisen tukihenkilötoiminnan sekä läksykerhotoiminnan keinoin (Ystäväksi maahanmuuttajaäidille-, kaveri- ja perhekummitoiminnat, sukupolvien välinen toiminta) (174 825 €)</t>
         </is>
       </c>
     </row>
@@ -16223,7 +17091,7 @@
       </c>
       <c r="I389" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Järjestölähtöiseen kriisi- ja mielenterveystyöhön vaikeissa elämäntilanteissa oleville sekä väkivaltaisesti käyttäytyneiden henkilöiden ja väkivaltaa kokeneiden henkilöiden auttamiseen - puhelimitse  kasvokkain  verkkoauttamisen ja jalkautuvan työn keinoin - yksilö ja ryhmämuotoiseen tukeen - vapaaehtoistyöhön (MIELI Kriisikeskus Mobile) (174 405 €)</t>
+          <t>Ak 1: Järjestölähtöiseen kriisi- ja mielenterveystyöhön vaikeissa elämäntilanteissa oleville sekä väkivaltaisesti käyttäytyneiden henkilöiden ja väkivaltaa kokeneiden henkilöiden auttamiseen - puhelimitse, kasvokkain, verkkoauttamisen ja jalkautuvan työn keinoin - yksilö ja ryhmämuotoiseen tukeen - vapaaehtoistyöhön (MIELI Kriisikeskus Mobile) (174 405 €)</t>
         </is>
       </c>
     </row>
@@ -16256,7 +17124,7 @@
       </c>
       <c r="I390" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Matalan kynnyksen tukea  neuvontaa ja jälkihoitoa kiusaamista kokeneille  läheisille sekä eri alojen ammattilaisille (Valopilkku) (105 000 €) | Ak 9642: Ammatillisesti koordinoitua vapaaehtoisten aikuisten tukihenkilötoimintaa lasten ja nuorten tukiverkoston laajentamiseksi ja hyvinvoinnin edistämiseksi Lahden seudulla (OmaKamu) (68 250 €)</t>
+          <t>Ak 2: Matalan kynnyksen tukea, neuvontaa ja jälkihoitoa kiusaamista kokeneille, läheisille sekä eri alojen ammattilaisille (Valopilkku) (105 000 €) | Ak 9642: Ammatillisesti koordinoitua vapaaehtoisten aikuisten tukihenkilötoimintaa lasten ja nuorten tukiverkoston laajentamiseksi ja hyvinvoinnin edistämiseksi Lahden seudulla (OmaKamu) (68 250 €)</t>
         </is>
       </c>
     </row>
@@ -16355,7 +17223,7 @@
       </c>
       <c r="I393" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Näkövammaisten itsenäisen elämän tukemiseen ja osallisuuden edistämiseen vertaistuen  ryhmätoiminnan  saavutettavan tiedon ja digituen avulla Lapin alueella (169 900 €)</t>
+          <t>Ak 2: Näkövammaisten itsenäisen elämän tukemiseen ja osallisuuden edistämiseen vertaistuen, ryhmätoiminnan, saavutettavan tiedon ja digituen avulla Lapin alueella (169 900 €)</t>
         </is>
       </c>
     </row>
@@ -16388,7 +17256,7 @@
       </c>
       <c r="I394" t="inlineStr" s="0">
         <is>
-          <t>Ak 11008: Kaksisuuntaisen kotoutumisen sekä maahanmuuttajataustaisten ja muiden alueen asukkaiden hyvinvoinnin  osallisuuden ja arjen hallinnan edistämiseen sekä kunniaan liittyvän väkivallan ja lähisuhdeväkivallan ennaltaehkäisyyn kohtaamispaikkatoiminnan  vertais- ja ryhmätoiminnan  tiedottamisen ja tapahtumien sekä yksilö- ja palveluohjauksen avulla (169 000 €)</t>
+          <t>Ak 11008: Kaksisuuntaisen kotoutumisen sekä maahanmuuttajataustaisten ja muiden alueen asukkaiden hyvinvoinnin, osallisuuden ja arjen hallinnan edistämiseen sekä kunniaan liittyvän väkivallan ja lähisuhdeväkivallan ennaltaehkäisyyn kohtaamispaikkatoiminnan, vertais- ja ryhmätoiminnan, tiedottamisen ja tapahtumien sekä yksilö- ja palveluohjauksen avulla (169 000 €)</t>
         </is>
       </c>
     </row>
@@ -16421,7 +17289,7 @@
       </c>
       <c r="I395" t="inlineStr" s="0">
         <is>
-          <t>Ak 6: Mielenterveysomaisten osallisuuden ja toimintakyvyn vahvistamiseen henkilökohtaisen tuen ja neuvonnan  vertaistuen ja muun ryhmätoiminnan sekä yhteiskunnallisen vaikuttamisen avulla Päijät-Hämeen alueella (168 500 €)</t>
+          <t>Ak 6: Mielenterveysomaisten osallisuuden ja toimintakyvyn vahvistamiseen henkilökohtaisen tuen ja neuvonnan, vertaistuen ja muun ryhmätoiminnan sekä yhteiskunnallisen vaikuttamisen avulla Päijät-Hämeen alueella (168 500 €)</t>
         </is>
       </c>
     </row>
@@ -16487,7 +17355,7 @@
       </c>
       <c r="I397" t="inlineStr" s="0">
         <is>
-          <t>Ak 6197: Maahanmuuttajataustaisten naisten hyvinvoinnin  työelämä- ja opiskeluvalmiuksien sekä osallisuuden vahvistamiseen vertaisryhmien  infotilaisuuksien  vapaaehtoistoiminnan sekä yksilö- ja palveluohjauksen avulla pääkaupunkiseudulla (167 451 €)</t>
+          <t>Ak 6197: Maahanmuuttajataustaisten naisten hyvinvoinnin, työelämä- ja opiskeluvalmiuksien sekä osallisuuden vahvistamiseen vertaisryhmien, infotilaisuuksien, vapaaehtoistoiminnan sekä yksilö- ja palveluohjauksen avulla pääkaupunkiseudulla (167 451 €)</t>
         </is>
       </c>
     </row>
@@ -16520,7 +17388,7 @@
       </c>
       <c r="I398" t="inlineStr" s="0">
         <is>
-          <t>Ak 10211: Rikos- ja päihdetaustaisten henkilöiden auttamiseen ja tukemiseen vertaisuuteen perustuvan toimintakeskus- ja vankilatyön sekä naiserityisen työn keinoin Porissa  Raumalla ja muualla Satakunnassa (167 250 €)</t>
+          <t>Ak 10211: Rikos- ja päihdetaustaisten henkilöiden auttamiseen ja tukemiseen vertaisuuteen perustuvan toimintakeskus- ja vankilatyön sekä naiserityisen työn keinoin Porissa, Raumalla ja muualla Satakunnassa (167 250 €)</t>
         </is>
       </c>
     </row>
@@ -16553,7 +17421,7 @@
       </c>
       <c r="I399" t="inlineStr" s="0">
         <is>
-          <t>Ak 5575: Vammaisten nuorten työelämäosallisuuden vahvistamiseen työnantaja-  oppilaitos- ja työvoimapalveluyhteistyöllä sekä kokemusasiantuntijatoiminnalla (166 222 €)</t>
+          <t>Ak 5575: Vammaisten nuorten työelämäosallisuuden vahvistamiseen työnantaja-, oppilaitos- ja työvoimapalveluyhteistyöllä sekä kokemusasiantuntijatoiminnalla (166 222 €)</t>
         </is>
       </c>
     </row>
@@ -16685,7 +17553,7 @@
       </c>
       <c r="I403" t="inlineStr" s="0">
         <is>
-          <t>Ak 4: Matalan kynnyksen kohtaamispaikkaan muistisairaille sekä heidän vertaisryhmätoimintaansa  ohjaukseen ja tukeen  muistisairauksista tiedottamiseen erilaisten yleisötapahtumien ja Muistikahviloiden avulla sekä aivoterveyttä edistävään ja sairastumista jarruttavaan työhön Salon ja Someron alueella. (Salon Muistisatama) (165 000 €)</t>
+          <t>Ak 4: Matalan kynnyksen kohtaamispaikkaan muistisairaille sekä heidän vertaisryhmätoimintaansa, ohjaukseen ja tukeen, muistisairauksista tiedottamiseen erilaisten yleisötapahtumien ja Muistikahviloiden avulla sekä aivoterveyttä edistävään ja sairastumista jarruttavaan työhön Salon ja Someron alueella. (Salon Muistisatama) (165 000 €)</t>
         </is>
       </c>
     </row>
@@ -16751,7 +17619,7 @@
       </c>
       <c r="I405" t="inlineStr" s="0">
         <is>
-          <t>Ak 10441: Haavoittuvassa asemassa olevien paperittomien ja paperittomuusuhan alla elävien naisten ja heidän perheidensä osallisuuden tukemiseen vapaaehtoistyön  päiväkeskustoiminnan  jalkautuvan palveluohjauksen ja neuvonnan avulla (163 630 €)</t>
+          <t>Ak 10441: Haavoittuvassa asemassa olevien paperittomien ja paperittomuusuhan alla elävien naisten ja heidän perheidensä osallisuuden tukemiseen vapaaehtoistyön, päiväkeskustoiminnan, jalkautuvan palveluohjauksen ja neuvonnan avulla (163 630 €)</t>
         </is>
       </c>
     </row>
@@ -16784,7 +17652,7 @@
       </c>
       <c r="I406" t="inlineStr" s="0">
         <is>
-          <t>Ak 1918: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen  neuvonnan  vertaistoiminnan ja valmennusten avulla Lohjalla  Vihdissä ja Karkkilassa (OmaisOiva) (163 540 €)</t>
+          <t>Ak 1918: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen, neuvonnan, vertaistoiminnan ja valmennusten avulla Lohjalla, Vihdissä ja Karkkilassa (OmaisOiva) (163 540 €)</t>
         </is>
       </c>
     </row>
@@ -16817,7 +17685,7 @@
       </c>
       <c r="I407" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Mielenterveystoipujien yhteisöllisyyden lisäämiseen kohtaamispaikka-  vapaaehtois-  vertais- ja kokemusasiantuntijatoiminnalla Turussa ja Salossa (163 468 €)</t>
+          <t>Ak 2: Mielenterveystoipujien yhteisöllisyyden lisäämiseen kohtaamispaikka-, vapaaehtois-, vertais- ja kokemusasiantuntijatoiminnalla Turussa ja Salossa (163 468 €)</t>
         </is>
       </c>
     </row>
@@ -16883,7 +17751,7 @@
       </c>
       <c r="I409" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Mielenterveysomaisten osallisuuden ja toimintakyvyn vahvistamiseen henkilökohtaisen tuen ja neuvonnan  vertaistuen ja muun ryhmätoiminnan sekä yhteiskunnallisen vaikuttamisen avulla Kanta-Hämeen alueella (162 736 €)</t>
+          <t>Ak 2: Mielenterveysomaisten osallisuuden ja toimintakyvyn vahvistamiseen henkilökohtaisen tuen ja neuvonnan, vertaistuen ja muun ryhmätoiminnan sekä yhteiskunnallisen vaikuttamisen avulla Kanta-Hämeen alueella (162 736 €)</t>
         </is>
       </c>
     </row>
@@ -16916,7 +17784,7 @@
       </c>
       <c r="I410" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Mielenterveyskuntoutujien hyvinvoinnin ja osallisuuden vahvistamiseen vapaaehtois-  vertais- ja matalan kynnyksen kohtaamispaikkatoiminnalla Oulussa sekä etätoiminnoin koko Pohjois-Suomen alueella (162 564 €)</t>
+          <t>Ak 2: Mielenterveyskuntoutujien hyvinvoinnin ja osallisuuden vahvistamiseen vapaaehtois-, vertais- ja matalan kynnyksen kohtaamispaikkatoiminnalla Oulussa sekä etätoiminnoin koko Pohjois-Suomen alueella (162 564 €)</t>
         </is>
       </c>
     </row>
@@ -16949,7 +17817,7 @@
       </c>
       <c r="I411" t="inlineStr" s="0">
         <is>
-          <t>Ak 4190: Maahanmuuttajataustaisten naisten terveyden ja osallisuuden edistämiseen neuvonnalla  liikunnalla  terveystiedon jakamisella sekä vertaisryhmä- ja vapaaehtoistoiminnalla (162 000 €)</t>
+          <t>Ak 4190: Maahanmuuttajataustaisten naisten terveyden ja osallisuuden edistämiseen neuvonnalla, liikunnalla, terveystiedon jakamisella sekä vertaisryhmä- ja vapaaehtoistoiminnalla (162 000 €)</t>
         </is>
       </c>
     </row>
@@ -16982,7 +17850,7 @@
       </c>
       <c r="I412" t="inlineStr" s="0">
         <is>
-          <t>Ak 5640: Kehitysvammaisten ja erityistä tukea tarvitsevien henkilöiden yhteisöllisyyden  osallisuuden ja hyvinvoinnin edistämiseen sekä vertais- ja vapaaehtoistoiminnan kehittämiseen kohtaamispaikkatoiminnan avulla (Kohtaamispaikka Tärsky) (161 797 €)</t>
+          <t>Ak 5640: Kehitysvammaisten ja erityistä tukea tarvitsevien henkilöiden yhteisöllisyyden, osallisuuden ja hyvinvoinnin edistämiseen sekä vertais- ja vapaaehtoistoiminnan kehittämiseen kohtaamispaikkatoiminnan avulla (Kohtaamispaikka Tärsky) (161 797 €)</t>
         </is>
       </c>
     </row>
@@ -17015,7 +17883,7 @@
       </c>
       <c r="I413" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Kaksisuuntaisen kotoutumisen ja maahanmuuttajataustaisten hyvinvoinnin  arjen hallinnan ja osallisuuden edistämiseen kohtaamispaikkatoiminnan  neuvonnan ja yksilöohjauksen  tapahtumien sekä vaikuttamis- ja vertaisryhmätoiminnan avulla (161 000 €)</t>
+          <t>Ak 1: Kaksisuuntaisen kotoutumisen ja maahanmuuttajataustaisten hyvinvoinnin, arjen hallinnan ja osallisuuden edistämiseen kohtaamispaikkatoiminnan, neuvonnan ja yksilöohjauksen, tapahtumien sekä vaikuttamis- ja vertaisryhmätoiminnan avulla (161 000 €)</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17949,7 @@
       </c>
       <c r="I415" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Mielenterveyskuntoutujien osallisuuden ja toimintakyvyn lisäämiseen palveluohjauksen  vertaisryhmätoiminnan  matalan kynnyksen kohtaamispaikkatoiminnan ja jalkautuvan työn avulla Länsi-Helsingissä (160 308 €)</t>
+          <t>Ak 1: Mielenterveyskuntoutujien osallisuuden ja toimintakyvyn lisäämiseen palveluohjauksen, vertaisryhmätoiminnan, matalan kynnyksen kohtaamispaikkatoiminnan ja jalkautuvan työn avulla Länsi-Helsingissä (160 308 €)</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17982,7 @@
       </c>
       <c r="I416" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Mielenterveyskuntoutujien hyvinvoinnin  osallisuuden ja arjen hallinnan tukemiseen yhteisöllisillä ryhmätoiminnoilla Espoossa (Hyvis ja Nuorten Hyvis) (159 863 €)</t>
+          <t>Ak 3: Mielenterveyskuntoutujien hyvinvoinnin, osallisuuden ja arjen hallinnan tukemiseen yhteisöllisillä ryhmätoiminnoilla Espoossa (Hyvis ja Nuorten Hyvis) (159 863 €)</t>
         </is>
       </c>
     </row>
@@ -17147,9 +18015,7 @@
       </c>
       <c r="I417" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Kehitysvammaisten henkilöiden osallisuuden  vaikuttamismahdollisuuksien ja aktiivisen toimijuuden tukemiseen vertaistuen  tapahtumien ja tiedottamisen avulla
-- Paikallisten Me itse -ryhmien tukemiseen ja vapaaehtoisten taustatukihenkilöiden kouluttamiseen
-(Liike itsenäisen elämän puolesta) (159 863 €)</t>
+          <t>Ak 2: Kehitysvammaisten henkilöiden osallisuuden, vaikuttamismahdollisuuksien ja aktiivisen toimijuuden tukemiseen vertaistuen, tapahtumien ja tiedottamisen avulla - Paikallisten Me itse -ryhmien tukemiseen ja vapaaehtoisten taustatukihenkilöiden kouluttamiseen (Liike itsenäisen elämän puolesta) (159 863 €)</t>
         </is>
       </c>
     </row>
@@ -17182,7 +18048,7 @@
       </c>
       <c r="I418" t="inlineStr" s="0">
         <is>
-          <t>Ak 1594: Oppimisvaikeuksia kokevien vertaistukeen  arjen tukemiseen ja vahvistamiseen antamalla tietoa oppimisvaikeuksista sekä oppimisen apuvälineistä  tarjoamalla oppimisen ohjausta  lukitestausta ja kurssitoimintaa sekä mahdollisuutta kokeilla erilaisia oppimisen apuvälineitä ja saada tukea niiden käytössä (Opinpesä) (158 251 €)</t>
+          <t>Ak 1594: Oppimisvaikeuksia kokevien vertaistukeen, arjen tukemiseen ja vahvistamiseen antamalla tietoa oppimisvaikeuksista sekä oppimisen apuvälineistä, tarjoamalla oppimisen ohjausta, lukitestausta ja kurssitoimintaa sekä mahdollisuutta kokeilla erilaisia oppimisen apuvälineitä ja saada tukea niiden käytössä (Opinpesä) (158 251 €)</t>
         </is>
       </c>
     </row>
@@ -17215,7 +18081,7 @@
       </c>
       <c r="I419" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Perheiden osallisuuden ja vanhemmuuden vahvistamiseen  vapaaehtoisten osallistumismahdollisuuksien lisäämiseen sekä järjestöjen ja muiden tahojen välisen yhteistyön edistämiseen Perheentalo-kumppanuusmallin keinoin (Perheentalo-yhteistyö) (158 250 €)</t>
+          <t>Ak 1: Perheiden osallisuuden ja vanhemmuuden vahvistamiseen, vapaaehtoisten osallistumismahdollisuuksien lisäämiseen sekä järjestöjen ja muiden tahojen välisen yhteistyön edistämiseen Perheentalo-kumppanuusmallin keinoin (Perheentalo-yhteistyö) (158 250 €)</t>
         </is>
       </c>
     </row>
@@ -17248,8 +18114,7 @@
       </c>
       <c r="I420" t="inlineStr" s="0">
         <is>
-          <t>Ak 9971: Lapsiperheiden hyvinvoinnin ja osallisuuden tukemiseen verkostomaisesti toimivan matalan kynnyksen kohtaamispaikan ja kohdennettujen ryhmätoimintojen avulla 
-(Siilinjärven Perheentalo) (157 500 €)</t>
+          <t>Ak 9971: Lapsiperheiden hyvinvoinnin ja osallisuuden tukemiseen verkostomaisesti toimivan matalan kynnyksen kohtaamispaikan ja kohdennettujen ryhmätoimintojen avulla  (Siilinjärven Perheentalo) (157 500 €)</t>
         </is>
       </c>
     </row>
@@ -17381,7 +18246,7 @@
       </c>
       <c r="I424" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen  neuvonnan  vertaistoiminnan ja valmennusten avulla Hämeenlinnan seudulla (OmaisOiva) (156 000 €)</t>
+          <t>Ak 2: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen, neuvonnan, vertaistoiminnan ja valmennusten avulla Hämeenlinnan seudulla (OmaisOiva) (156 000 €)</t>
         </is>
       </c>
     </row>
@@ -17414,9 +18279,7 @@
       </c>
       <c r="I425" t="inlineStr" s="0">
         <is>
-          <t>Ak 12515: Maahanmuuttajataustaisten naisten hyvinvoinnin  osallisuuden ja toimijuuden edistämiseen matalan kynnyksen toiminnan  yksilöllisen tuen ja vertaisryhmätoiminnan avulla.
-Toiminnan kohderyhmänä ovat pääasiassa yli 29-vuotiaat työttömät tai työvoiman ulkopuolella olevat maahanmuuttajataustaiset naiset
-(Hyvinvoivat naiset - HyNA) (156 000 €)</t>
+          <t>Ak 12515: Maahanmuuttajataustaisten naisten hyvinvoinnin, osallisuuden ja toimijuuden edistämiseen matalan kynnyksen toiminnan, yksilöllisen tuen ja vertaisryhmätoiminnan avulla.  Toiminnan kohderyhmänä ovat pääasiassa yli 29-vuotiaat työttömät tai työvoiman ulkopuolella olevat maahanmuuttajataustaiset naiset (Hyvinvoivat naiset - HyNA) (156 000 €)</t>
         </is>
       </c>
     </row>
@@ -17515,8 +18378,7 @@
       </c>
       <c r="I428" t="inlineStr" s="0">
         <is>
-          <t>Ak 3824: Murrosikäisten nuorten vanhempien vertaisuuteen perustuvan ryhmätoiminnan järjestämiseen 
-(Kamalat äidit) (155 833 €)</t>
+          <t>Ak 3824: Murrosikäisten nuorten vanhempien vertaisuuteen perustuvan ryhmätoiminnan järjestämiseen  (Kamalat äidit) (155 833 €)</t>
         </is>
       </c>
     </row>
@@ -17549,7 +18411,7 @@
       </c>
       <c r="I429" t="inlineStr" s="0">
         <is>
-          <t>Ak 1369: Omaishoitajien hyvinvoinnin tukemiseen tiedottamisen  neuvonnan  vertaistoiminnan ja valmennusten avulla Etelä-Karjalan alueella (OmaisOiva) (155 000 €)</t>
+          <t>Ak 1369: Omaishoitajien hyvinvoinnin tukemiseen tiedottamisen, neuvonnan, vertaistoiminnan ja valmennusten avulla Etelä-Karjalan alueella (OmaisOiva) (155 000 €)</t>
         </is>
       </c>
     </row>
@@ -17582,8 +18444,7 @@
       </c>
       <c r="I430" t="inlineStr" s="0">
         <is>
-          <t>Ak 2643: Omaishoitajien hyvinvoinnin ja toimintakyvyn tukemiseen tiedottamisen  neuvonnan  vertaistoiminnan ja valmennusten avulla Länsi-Uudenmaan alueella 
-(OmaisOiva) (155 000 €)</t>
+          <t>Ak 2643: Omaishoitajien hyvinvoinnin ja toimintakyvyn tukemiseen tiedottamisen, neuvonnan, vertaistoiminnan ja valmennusten avulla Länsi-Uudenmaan alueella  (OmaisOiva) (155 000 €)</t>
         </is>
       </c>
     </row>
@@ -17616,7 +18477,7 @@
       </c>
       <c r="I431" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Savonlinnan seudun yhdistysten vaikuttamismahdollisuuksien ja yhteistyön tukemiseen sekä OLKA-toimintamallin mukaiseen toiminnan toteuttamiseen  organisoimiseen ja kehittämiseen Savonlinnan seudulla (155 000 €)</t>
+          <t>Ak 1: Savonlinnan seudun yhdistysten vaikuttamismahdollisuuksien ja yhteistyön tukemiseen sekä OLKA-toimintamallin mukaiseen toiminnan toteuttamiseen, organisoimiseen ja kehittämiseen Savonlinnan seudulla (155 000 €)</t>
         </is>
       </c>
     </row>
@@ -17649,7 +18510,7 @@
       </c>
       <c r="I432" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Kouvolan seudun vammais- ja pitkäaikaissairausjärjestöjen sekä hyvinvointialalla toimivien yhdistysten toimintaedellytysten  yhteistyön ja kehittämisen tukemiseen. Kaikille suunnatun avoimen toiminnan ja osallisuuden lisäämiseen. (109 021 €) | C 13703: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Kokemuksella Kymenlaakso" osarahoitukseen järjestölle (2025-2028) (45 888 €)</t>
+          <t>Ak 1: Kouvolan seudun vammais- ja pitkäaikaissairausjärjestöjen sekä hyvinvointialalla toimivien yhdistysten toimintaedellytysten, yhteistyön ja kehittämisen tukemiseen. Kaikille suunnatun avoimen toiminnan ja osallisuuden lisäämiseen. (109 021 €) | C 13703: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Kokemuksella Kymenlaakso" osarahoitukseen järjestölle (2025-2028) (45 888 €)</t>
         </is>
       </c>
     </row>
@@ -17682,7 +18543,7 @@
       </c>
       <c r="I433" t="inlineStr" s="0">
         <is>
-          <t>Ak 3734: Näkövammaisten lasten ja vanhempien elämänlaadun parantamiseen vertaistuen  leiri- ja kerhotoiminnan sekä viestinnän avulla (154 890 €)</t>
+          <t>Ak 3734: Näkövammaisten lasten ja vanhempien elämänlaadun parantamiseen vertaistuen, leiri- ja kerhotoiminnan sekä viestinnän avulla (154 890 €)</t>
         </is>
       </c>
     </row>
@@ -17715,7 +18576,7 @@
       </c>
       <c r="I434" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Mielenterveyskuntoutujien terveyttä  hyvinvointia  osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään tavoitteelliseen kohtaamispaikkatoimintaan (Karvetin FH-klubitalo) (154 883 €)</t>
+          <t>Ak 1: Mielenterveyskuntoutujien terveyttä, hyvinvointia, osallisuutta sekä työ- ja opiskeluelämään palaamista edistävään tavoitteelliseen kohtaamispaikkatoimintaan (Karvetin FH-klubitalo) (154 883 €)</t>
         </is>
       </c>
     </row>
@@ -17748,7 +18609,7 @@
       </c>
       <c r="I435" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Syöpään tai vakaviin veritauteihin sairastuneiden lasten ja heidän perheidensä psyykkisen ja sosiaalisen hyvinvoinnin ylläpitäminen ja tukeminen ammatillisen tuen  vertaistuen ja virkistystoiminnan avulla (154 350 €)</t>
+          <t>Ak 2: Syöpään tai vakaviin veritauteihin sairastuneiden lasten ja heidän perheidensä psyykkisen ja sosiaalisen hyvinvoinnin ylläpitäminen ja tukeminen ammatillisen tuen, vertaistuen ja virkistystoiminnan avulla (154 350 €)</t>
         </is>
       </c>
     </row>
@@ -17880,7 +18741,7 @@
       </c>
       <c r="I439" t="inlineStr" s="0">
         <is>
-          <t>Ak 2993: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen  neuvonnan  vertaistoiminnan ja valmennusten avulla Etelä-Pohjanmaalla (OmaisOiva) (152 000 €)</t>
+          <t>Ak 2993: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen, neuvonnan, vertaistoiminnan ja valmennusten avulla Etelä-Pohjanmaalla (OmaisOiva) (152 000 €)</t>
         </is>
       </c>
     </row>
@@ -17946,7 +18807,7 @@
       </c>
       <c r="I441" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen  neuvonnan  vertaistoiminnan ja valmennusten avulla Pohjois-Savossa (OmaisOiva) (151 200 €)</t>
+          <t>Ak 1: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen, neuvonnan, vertaistoiminnan ja valmennusten avulla Pohjois-Savossa (OmaisOiva) (151 200 €)</t>
         </is>
       </c>
     </row>
@@ -18111,7 +18972,7 @@
       </c>
       <c r="I446" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Mielenterveyskuntoutujien ja syrjäytymisuhan alla olevien henkilöiden osallisuuden ja hyvinvoinnin vahvistamiseen kohtaamispaikan vertais-  ja vapaaehtoistoiminnalla  ryhmätoiminnoilla sekä palveluneuvonnalla ja -ohjauksella Äänekosken seudulla (150 000 €)</t>
+          <t>Ak 1: Mielenterveyskuntoutujien ja syrjäytymisuhan alla olevien henkilöiden osallisuuden ja hyvinvoinnin vahvistamiseen kohtaamispaikan vertais-, ja vapaaehtoistoiminnalla, ryhmätoiminnoilla sekä palveluneuvonnalla ja -ohjauksella Äänekosken seudulla (150 000 €)</t>
         </is>
       </c>
     </row>
@@ -18144,9 +19005,7 @@
       </c>
       <c r="I447" t="inlineStr" s="0">
         <is>
-          <t>Ak 10866: Vammaisten naisten ja tyttöjen yhteiskunnallisen osallisuuden ja voimaantumisen edistämiseen vertaistuen  johtajuuskoulutuksen  mentoroinnin ja ammattilaisten osaamisen lisäämisen keinoin
-- Vammaisten naisten äitiyden ja vanhemmuuden tukemiseen 
-- Turva- ja itsepuolustustaitojen opettamiseen (149 100 €)</t>
+          <t>Ak 10866: Vammaisten naisten ja tyttöjen yhteiskunnallisen osallisuuden ja voimaantumisen edistämiseen vertaistuen, johtajuuskoulutuksen, mentoroinnin ja ammattilaisten osaamisen lisäämisen keinoin - Vammaisten naisten äitiyden ja vanhemmuuden tukemiseen  - Turva- ja itsepuolustustaitojen opettamiseen (149 100 €)</t>
         </is>
       </c>
     </row>
@@ -18179,7 +19038,7 @@
       </c>
       <c r="I448" t="inlineStr" s="0">
         <is>
-          <t>Ak 7821: Järjestöjen toiminnan kehittämiseen  yhteistyön koordinointiin sekä osallisuutta lisäävään kohtaamispaikkatoimintaan (Kumppanuustalo Hilma) (149 000 €)</t>
+          <t>Ak 7821: Järjestöjen toiminnan kehittämiseen, yhteistyön koordinointiin sekä osallisuutta lisäävään kohtaamispaikkatoimintaan (Kumppanuustalo Hilma) (149 000 €)</t>
         </is>
       </c>
     </row>
@@ -18212,7 +19071,7 @@
       </c>
       <c r="I449" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Rintaterveyttä sekä rintasyövän varhaistoteamista edistävään tiedotus-  opastus- ja koulutustoimintaan verkostomaisen järjestötyön avulla (149 000 €)</t>
+          <t>Ak 2: Rintaterveyttä sekä rintasyövän varhaistoteamista edistävään tiedotus-, opastus- ja koulutustoimintaan verkostomaisen järjestötyön avulla (149 000 €)</t>
         </is>
       </c>
     </row>
@@ -18245,7 +19104,7 @@
       </c>
       <c r="I450" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Rikos- ja päihdetaustaisten yhteiskuntaan kiinnittymisen edistämiseen ja osallisuuden lisäämiseen toimintakeskustyön  vertaistoiminnan ja vankilatyön kautta (148 250 €)</t>
+          <t>Ak 1: Rikos- ja päihdetaustaisten yhteiskuntaan kiinnittymisen edistämiseen ja osallisuuden lisäämiseen toimintakeskustyön, vertaistoiminnan ja vankilatyön kautta (148 250 €)</t>
         </is>
       </c>
     </row>
@@ -18278,7 +19137,7 @@
       </c>
       <c r="I451" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Järjestölähtöiseen ohjaus- ja neuvontatyöhön  koulutuksellisiin vertaistapahtumiin ja -kursseihin sekä leireihin. Kohderyhminä Tourettea ja OCD:ta sairastavat sekä heidän läheisensä. (146 633 €)</t>
+          <t>Ak 3: Järjestölähtöiseen ohjaus- ja neuvontatyöhön, koulutuksellisiin vertaistapahtumiin ja -kursseihin sekä leireihin. Kohderyhminä Tourettea ja OCD:ta sairastavat sekä heidän läheisensä. (146 633 €)</t>
         </is>
       </c>
     </row>
@@ -18344,7 +19203,7 @@
       </c>
       <c r="I453" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen  neuvonnan  vertaistoiminnan ja valmennusten avulla Varkauden seudulla (OmaisOiva) (145 866 €)</t>
+          <t>Ak 1: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen, neuvonnan, vertaistoiminnan ja valmennusten avulla Varkauden seudulla (OmaisOiva) (145 866 €)</t>
         </is>
       </c>
     </row>
@@ -18377,7 +19236,7 @@
       </c>
       <c r="I454" t="inlineStr" s="0">
         <is>
-          <t>Ak 1644: Näkövammaisten itsenäisen elämän tukemiseen ja osallisuuden edistämiseen vertaistuen  ryhmätoiminnan  saavutettavan tiedon ja digituen avulla Keski-Suomessa (145 000 €)</t>
+          <t>Ak 1644: Näkövammaisten itsenäisen elämän tukemiseen ja osallisuuden edistämiseen vertaistuen, ryhmätoiminnan, saavutettavan tiedon ja digituen avulla Keski-Suomessa (145 000 €)</t>
         </is>
       </c>
     </row>
@@ -18410,7 +19269,7 @@
       </c>
       <c r="I455" t="inlineStr" s="0">
         <is>
-          <t>Ak 12120: Kehityksellinen kielihäiriöoireisten ja heidän läheistensä osallisuuden  hyvinvoinnin ja voimavarojen vahvistamiseen vertaistukitoiminnan  neuvonnan ja vaikuttamistoiminnan keinoin (2024-2026) (145 000 €)</t>
+          <t>Ak 12120: Kehityksellinen kielihäiriöoireisten ja heidän läheistensä osallisuuden, hyvinvoinnin ja voimavarojen vahvistamiseen vertaistukitoiminnan, neuvonnan ja vaikuttamistoiminnan keinoin (2024-2026) (145 000 €)</t>
         </is>
       </c>
     </row>
@@ -18476,7 +19335,7 @@
       </c>
       <c r="I457" t="inlineStr" s="0">
         <is>
-          <t>Ak 1495: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen  neuvonnan  vertaistoiminnan ja valmennusten avulla Kokkolan seudulla (OmaisOiva) (143 325 €)</t>
+          <t>Ak 1495: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen, neuvonnan, vertaistoiminnan ja valmennusten avulla Kokkolan seudulla (OmaisOiva) (143 325 €)</t>
         </is>
       </c>
     </row>
@@ -18509,7 +19368,7 @@
       </c>
       <c r="I458" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen  neuvonnan  vertaistoiminnan ja valmennusten avulla Kainuun alueella (OmaisOiva) (142 800 €)</t>
+          <t>Ak 1: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen, neuvonnan, vertaistoiminnan ja valmennusten avulla Kainuun alueella (OmaisOiva) (142 800 €)</t>
         </is>
       </c>
     </row>
@@ -18542,7 +19401,7 @@
       </c>
       <c r="I459" t="inlineStr" s="0">
         <is>
-          <t>Ak 1267: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen  neuvonnan  vertaistoiminnan ja valmennusten avulla Pieksämäen ja Savonlinnan seudulla (OmaisOiva) (142 800 €)</t>
+          <t>Ak 1267: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen, neuvonnan, vertaistoiminnan ja valmennusten avulla Pieksämäen ja Savonlinnan seudulla (OmaisOiva) (142 800 €)</t>
         </is>
       </c>
     </row>
@@ -18608,8 +19467,7 @@
       </c>
       <c r="I461" t="inlineStr" s="0">
         <is>
-          <t>Ak 9835: Maahan muuttaneiden osallisuuden ja toimijuuden sekä kaksisuuntaisen kotoutumisen vahvistamiseen yksilöllisen tuen  koulutusten  ryhmä- ja vapaaehtoistoiminnan sekä verkostotyön avulla
-(2026) (142 000 €)</t>
+          <t>Ak 9835: Maahan muuttaneiden osallisuuden ja toimijuuden sekä kaksisuuntaisen kotoutumisen vahvistamiseen yksilöllisen tuen, koulutusten, ryhmä- ja vapaaehtoistoiminnan sekä verkostotyön avulla (2026) (142 000 €)</t>
         </is>
       </c>
     </row>
@@ -18675,7 +19533,7 @@
       </c>
       <c r="I463" t="inlineStr" s="0">
         <is>
-          <t>Ak 1803: Ikääntyvien maahanmuuttajien syrjäytymisen ehkäisemiseen ja hyvinvoinnin lisäämiseen sekä kaksisuuntaisen kotoutumisen edistämiseen neuvonnalla  ryhmä- ja vapaaehtoistoiminnalla  tapahtumilla sekä verkostotyöllä Keski-Suomessa (141 750 €)</t>
+          <t>Ak 1803: Ikääntyvien maahanmuuttajien syrjäytymisen ehkäisemiseen ja hyvinvoinnin lisäämiseen sekä kaksisuuntaisen kotoutumisen edistämiseen neuvonnalla, ryhmä- ja vapaaehtoistoiminnalla, tapahtumilla sekä verkostotyöllä Keski-Suomessa (141 750 €)</t>
         </is>
       </c>
     </row>
@@ -18741,7 +19599,7 @@
       </c>
       <c r="I465" t="inlineStr" s="0">
         <is>
-          <t>Ak 11504: Kumppanuustalo Nuotan toiminnan ylläpitämiseen  sosiaali- ja terveysalan järjestöjen toiminnan koordinointiin  tukemiseen ja yhteistyöhön sekä alueellisen vapaaehtoistoiminnan tukemiseen ja koordinointiin Kuusamossa  Posiolla ja Taivalkoskella (Kumppanuustalo Nuotta) (141 400 €)</t>
+          <t>Ak 11504: Kumppanuustalo Nuotan toiminnan ylläpitämiseen, sosiaali- ja terveysalan järjestöjen toiminnan koordinointiin, tukemiseen ja yhteistyöhön sekä alueellisen vapaaehtoistoiminnan tukemiseen ja koordinointiin Kuusamossa, Posiolla ja Taivalkoskella (Kumppanuustalo Nuotta) (141 400 €)</t>
         </is>
       </c>
     </row>
@@ -18774,7 +19632,7 @@
       </c>
       <c r="I466" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Mielenterveysomaisten osallisuuden ja toimintakyvyn vahvistamiseen henkilökohtaisen tuen ja neuvonnan  vertaistuen ja muun ryhmätoiminnan sekä vapaaehtoistyön koordinaation ja yhteiskunnallisen vaikuttamisen avulla Keski-Suomen alueella (141 348 €)</t>
+          <t>Ak 3: Mielenterveysomaisten osallisuuden ja toimintakyvyn vahvistamiseen henkilökohtaisen tuen ja neuvonnan, vertaistuen ja muun ryhmätoiminnan sekä vapaaehtoistyön koordinaation ja yhteiskunnallisen vaikuttamisen avulla Keski-Suomen alueella (141 348 €)</t>
         </is>
       </c>
     </row>
@@ -18807,7 +19665,7 @@
       </c>
       <c r="I467" t="inlineStr" s="0">
         <is>
-          <t>Ak 7502: Lasten ja nuorten osallisuuden ja toimijuuden vahvistamiseen lastensuojelun palveluiden piirissä yhteistoiminnallisen työskentelyn avulla (Osallisuuden aika – Lapset  nuoret ja ammattilaiset yhteistoiminnallisina kumppaneina) (141 112 €)</t>
+          <t>Ak 7502: Lasten ja nuorten osallisuuden ja toimijuuden vahvistamiseen lastensuojelun palveluiden piirissä yhteistoiminnallisen työskentelyn avulla (Osallisuuden aika – Lapset, nuoret ja ammattilaiset yhteistoiminnallisina kumppaneina) (141 112 €)</t>
         </is>
       </c>
     </row>
@@ -18840,7 +19698,7 @@
       </c>
       <c r="I468" t="inlineStr" s="0">
         <is>
-          <t>Ak 1841: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen  neuvonnan  vertaistoiminnan ja hyvinvointikurssien avulla Salossa ja Somerolla (OmaisOiva) (140 700 €)</t>
+          <t>Ak 1841: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen, neuvonnan, vertaistoiminnan ja hyvinvointikurssien avulla Salossa ja Somerolla (OmaisOiva) (140 700 €)</t>
         </is>
       </c>
     </row>
@@ -18873,8 +19731,7 @@
       </c>
       <c r="I469" t="inlineStr" s="0">
         <is>
-          <t>Ak 4241: Vuosaaren alueella asuvien 12-20-vuotiaiden syrjäytymisvaarassa olevien ujojen  yksinäisten ja monikulttuuristen ja sateenkaarityttöjen itsetunnon  vertaissuhteiden ja osallisuuden tukemiseen turvallisen tilan toimintamallilla 
-(Vuosaaren / Itä-Helsingin tytöt -toiminta) (140 000 €)</t>
+          <t>Ak 4241: Vuosaaren alueella asuvien 12-20-vuotiaiden syrjäytymisvaarassa olevien ujojen, yksinäisten ja monikulttuuristen ja sateenkaarityttöjen itsetunnon, vertaissuhteiden ja osallisuuden tukemiseen turvallisen tilan toimintamallilla  (Vuosaaren / Itä-Helsingin tytöt -toiminta) (140 000 €)</t>
         </is>
       </c>
     </row>
@@ -18907,7 +19764,7 @@
       </c>
       <c r="I470" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Narsistien uhrien selviytymisen tukemiseen vertaistuen  tukihenkilötoiminnan  puhelinneuvonnan  verkostoitumisen sekä tiedotus- ja koulutustoiminnan avulla (140 000 €)</t>
+          <t>Ak 2: Narsistien uhrien selviytymisen tukemiseen vertaistuen, tukihenkilötoiminnan, puhelinneuvonnan, verkostoitumisen sekä tiedotus- ja koulutustoiminnan avulla (140 000 €)</t>
         </is>
       </c>
     </row>
@@ -18940,7 +19797,7 @@
       </c>
       <c r="I471" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Sosiaali- ja terveysyhdistysten yhteistyön edistämiseen Varkauden alueella  järjestöjen toiminnan ja vapaaehtoistyön kehittämiseen sekä Varkauden järjestötalon toiminnan toteuttamiseen (140 000 €)</t>
+          <t>Ak 1: Sosiaali- ja terveysyhdistysten yhteistyön edistämiseen Varkauden alueella, järjestöjen toiminnan ja vapaaehtoistyön kehittämiseen sekä Varkauden järjestötalon toiminnan toteuttamiseen (140 000 €)</t>
         </is>
       </c>
     </row>
@@ -18973,7 +19830,7 @@
       </c>
       <c r="I472" t="inlineStr" s="0">
         <is>
-          <t>Ak 9977: Romaninuorten arjen hallinnan  opiskeluvalmiuksien ja yhteiskuntaan kiinnittymisen edistämiseen yksilöllisen tukitoiminnan  ryhmätoiminnan  perhekohtaisen tuen  tapahtumien sekä alueellisen verkosto- ja vaikuttamistyön avulla. (137 970 €)</t>
+          <t>Ak 9977: Romaninuorten arjen hallinnan, opiskeluvalmiuksien ja yhteiskuntaan kiinnittymisen edistämiseen yksilöllisen tukitoiminnan, ryhmätoiminnan, perhekohtaisen tuen, tapahtumien sekä alueellisen verkosto- ja vaikuttamistyön avulla. (137 970 €)</t>
         </is>
       </c>
     </row>
@@ -19039,7 +19896,7 @@
       </c>
       <c r="I474" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Elämää ylläpitävää hengityslaitetta käyttävien ihmisten itsenäisen elämän tukemiseen vaikuttamistyön  tiedon  neuvonnan ja vertaistuen avulla (137 000 €)</t>
+          <t>Ak 2: Elämää ylläpitävää hengityslaitetta käyttävien ihmisten itsenäisen elämän tukemiseen vaikuttamistyön, tiedon, neuvonnan ja vertaistuen avulla (137 000 €)</t>
         </is>
       </c>
     </row>
@@ -19072,9 +19929,7 @@
       </c>
       <c r="I475" t="inlineStr" s="0">
         <is>
-          <t>Ak 11123: Harvinaissairaiden ja –vammaisten sekä heidän läheistensä voimavarojen lisäämiseen vertaistuen ja kokemustoiminnan keinoin
-- Vaikuttamistoimintaan sekä yleisen tietouden lisäämiseen
-(HARSOsta suojaa harvinaisille ja tukea harvinaiskentälle) (136 500 €)</t>
+          <t>Ak 11123: Harvinaissairaiden ja –vammaisten sekä heidän läheistensä voimavarojen lisäämiseen vertaistuen ja kokemustoiminnan keinoin - Vaikuttamistoimintaan sekä yleisen tietouden lisäämiseen (HARSOsta suojaa harvinaisille ja tukea harvinaiskentälle) (136 500 €)</t>
         </is>
       </c>
     </row>
@@ -19107,7 +19962,7 @@
       </c>
       <c r="I476" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: För att öka kunskaperna i huslig ekonomi och skapa rutiner som stöder välmåendet och självförtroendet hos personer med psykisk ohälsa  arbetslösa  personer med invandrarbakgrund  personer med funktionsvariation samt barnfamiljer med hjälp av kursverksamhet  föreläsningar och personlig rådgivning (Hantera vardagen) (136 213 €)</t>
+          <t>Ak 2: För att öka kunskaperna i huslig ekonomi och skapa rutiner som stöder välmåendet och självförtroendet hos personer med psykisk ohälsa, arbetslösa, personer med invandrarbakgrund, personer med funktionsvariation samt barnfamiljer med hjälp av kursverksamhet, föreläsningar och personlig rådgivning (Hantera vardagen) (136 213 €)</t>
         </is>
       </c>
     </row>
@@ -19173,7 +20028,7 @@
       </c>
       <c r="I478" t="inlineStr" s="0">
         <is>
-          <t>Ak 3106: Mielenterveys- ja päihdekuntoutujien mielen hyvinvoinnin edistämiseen ja riippuvuuksista johtuvien haittojen ehkäisemiseen vertais-  kokemusasiantuntija- ja matalan kynnyksen kohtaamispaikkatoiminnan avulla Seinäjoella (Olkkari) (136 000 €)</t>
+          <t>Ak 3106: Mielenterveys- ja päihdekuntoutujien mielen hyvinvoinnin edistämiseen ja riippuvuuksista johtuvien haittojen ehkäisemiseen vertais-, kokemusasiantuntija- ja matalan kynnyksen kohtaamispaikkatoiminnan avulla Seinäjoella (Olkkari) (136 000 €)</t>
         </is>
       </c>
     </row>
@@ -19305,8 +20160,7 @@
       </c>
       <c r="I482" t="inlineStr" s="0">
         <is>
-          <t>Ak 10737: Mielenterveys- ja päihdeongelmista kärsivien maahanmuuttajataustaisten hyvinvoinnin vahvistamiseen neuvonnan sekä vapaaehtois- ja vertaistoiminnan avulla 
-(Koutsi 2026) (135 000 €)</t>
+          <t>Ak 10737: Mielenterveys- ja päihdeongelmista kärsivien maahanmuuttajataustaisten hyvinvoinnin vahvistamiseen neuvonnan sekä vapaaehtois- ja vertaistoiminnan avulla  (Koutsi 2026) (135 000 €)</t>
         </is>
       </c>
     </row>
@@ -19372,7 +20226,7 @@
       </c>
       <c r="I484" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Selkäydinvammaisten ja heidän läheistensä elämänlaadun parantamiseen ja selkäydinvammatietouden lisäämiseen vertaistuen  neuvonnan  tiedon jakamisen ja edunvalvonnan avulla (134 400 €)</t>
+          <t>Ak 1: Selkäydinvammaisten ja heidän läheistensä elämänlaadun parantamiseen ja selkäydinvammatietouden lisäämiseen vertaistuen, neuvonnan, tiedon jakamisen ja edunvalvonnan avulla (134 400 €)</t>
         </is>
       </c>
     </row>
@@ -19405,7 +20259,7 @@
       </c>
       <c r="I485" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Maahanmuuttajaäitien ja kantasuomalaisten äitien integraation edistämiseen  vanhemmuuden tukemiseen sekä äidin ja lapsen vuorovaikutusta vahvistavaan ennaltaehkäisevään ryhmätoimintaan pikkulapsiperheille (Arkipaja) (133 559 €)</t>
+          <t>Ak 1: Maahanmuuttajaäitien ja kantasuomalaisten äitien integraation edistämiseen, vanhemmuuden tukemiseen sekä äidin ja lapsen vuorovaikutusta vahvistavaan ennaltaehkäisevään ryhmätoimintaan pikkulapsiperheille (Arkipaja) (133 559 €)</t>
         </is>
       </c>
     </row>
@@ -19438,7 +20292,7 @@
       </c>
       <c r="I486" t="inlineStr" s="0">
         <is>
-          <t>Ak 2441: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen  neuvonnan  vertaistoiminnan ja valmennusten avulla kuuden kunnan alueella Keski-Uudellamaalla (OmaisOiva) (132 510 €)</t>
+          <t>Ak 2441: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen, neuvonnan, vertaistoiminnan ja valmennusten avulla kuuden kunnan alueella Keski-Uudellamaalla (OmaisOiva) (132 510 €)</t>
         </is>
       </c>
     </row>
@@ -19504,7 +20358,7 @@
       </c>
       <c r="I488" t="inlineStr" s="0">
         <is>
-          <t>Ak 5769: Yli 60-vuotiaiden hyvinvoinnin  toimintakyvyn ja yhteisöllisyyden vahvistamiseen  yksinäisyyden kokemuksen vähentämiseen sekä digitaitojen vahvistamiseen kohtaamispaikka- ja ryhmätoiminnan avulla (Iltatupa-toiminta) (132 300 €)</t>
+          <t>Ak 5769: Yli 60-vuotiaiden hyvinvoinnin, toimintakyvyn ja yhteisöllisyyden vahvistamiseen, yksinäisyyden kokemuksen vähentämiseen sekä digitaitojen vahvistamiseen kohtaamispaikka- ja ryhmätoiminnan avulla (Iltatupa-toiminta) (132 300 €)</t>
         </is>
       </c>
     </row>
@@ -19537,7 +20391,7 @@
       </c>
       <c r="I489" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Vaikeissa elämäntilanteissa oleville henkilöille tarkoitettuun järjestölähtöiseen kriisi- ja mielenterveystyöhön tarjoamalla matalan kynnyksen keskusteluapua  ammatillisesti ja vapaaehtoisvoimin ohjattuja ryhmiä  etäauttamista ja työyhteisöjen koulutuksia (Vuoroveto-kriisikeskus Kouvola) (132 300 €)</t>
+          <t>Ak 1: Vaikeissa elämäntilanteissa oleville henkilöille tarkoitettuun järjestölähtöiseen kriisi- ja mielenterveystyöhön tarjoamalla matalan kynnyksen keskusteluapua, ammatillisesti ja vapaaehtoisvoimin ohjattuja ryhmiä, etäauttamista ja työyhteisöjen koulutuksia (Vuoroveto-kriisikeskus Kouvola) (132 300 €)</t>
         </is>
       </c>
     </row>
@@ -19570,7 +20424,7 @@
       </c>
       <c r="I490" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen  neuvonnan  vertaistoiminnan ja valmennusten avulla Keski-Suomen alueella (OmaisOiva) (131 500 €)</t>
+          <t>Ak 2: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen, neuvonnan, vertaistoiminnan ja valmennusten avulla Keski-Suomen alueella (OmaisOiva) (131 500 €)</t>
         </is>
       </c>
     </row>
@@ -19603,7 +20457,7 @@
       </c>
       <c r="I491" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Ääniä kuulevien hyvinvoinnin lisäämiseen verkossa  kasvokkain ja puhelimitse toteutettavan  vertaistuen avulla (131 250 €)</t>
+          <t>Ak 3: Ääniä kuulevien hyvinvoinnin lisäämiseen verkossa, kasvokkain ja puhelimitse toteutettavan  vertaistuen avulla (131 250 €)</t>
         </is>
       </c>
     </row>
@@ -19669,8 +20523,7 @@
       </c>
       <c r="I493" t="inlineStr" s="0">
         <is>
-          <t>Ak 12310: Romaniperheiden hyvinvoinnin  osallisuuden sekä toimijuuden vahvistamiseen matalan kynnyksen toiminnan  jalkautuvan työn  neuvonnan ja ryhmätoiminnan sekä verkostotyön avulla
-(Perheenä huomiseen - matalan kynnyksen romaniperhetyö) (130 859 €)</t>
+          <t>Ak 12310: Romaniperheiden hyvinvoinnin, osallisuuden sekä toimijuuden vahvistamiseen matalan kynnyksen toiminnan, jalkautuvan työn, neuvonnan ja ryhmätoiminnan sekä verkostotyön avulla  (Perheenä huomiseen - matalan kynnyksen romaniperhetyö) (130 859 €)</t>
         </is>
       </c>
     </row>
@@ -19769,7 +20622,7 @@
       </c>
       <c r="I496" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Näkövammaisten itsenäisen elämän tukemiseen ja osallisuuden edistämiseen vertaistuen  ryhmätoiminnan  saavutettavan tiedon ja digituen avulla (129 300 €)</t>
+          <t>Ak 1: Näkövammaisten itsenäisen elämän tukemiseen ja osallisuuden edistämiseen vertaistuen, ryhmätoiminnan, saavutettavan tiedon ja digituen avulla (129 300 €)</t>
         </is>
       </c>
     </row>
@@ -19835,7 +20688,7 @@
       </c>
       <c r="I498" t="inlineStr" s="0">
         <is>
-          <t>Ak 10112: Rikostaustaisten henkilöiden rikoksettoman ja päihteettömän elämän tukemiseen yksilö- ja ryhmämuotoisella ohjauksella ja tuella  vapaaehtoistoiminnoilla sekä verkostoyhteistyöllä julkisen ja kolmannen sektorin toimijoiden kanssa Hämeenlinnan  Hattulan  Janakkalan ja Riihimäen alueella (128 760 €)</t>
+          <t>Ak 10112: Rikostaustaisten henkilöiden rikoksettoman ja päihteettömän elämän tukemiseen yksilö- ja ryhmämuotoisella ohjauksella ja tuella, vapaaehtoistoiminnoilla sekä verkostoyhteistyöllä julkisen ja kolmannen sektorin toimijoiden kanssa Hämeenlinnan, Hattulan, Janakkalan ja Riihimäen alueella (128 760 €)</t>
         </is>
       </c>
     </row>
@@ -19868,8 +20721,7 @@
       </c>
       <c r="I499" t="inlineStr" s="0">
         <is>
-          <t>Ak 12454: Mielenterveys -ja päihdekuntoutujien sekä paljon sote-palveluita käyttävien toimintakyvyn ja osallisuuden edistämiseen sekä palvelujärjestelmän kehittämiseen kokemustietoa hyödyntämällä 
-(Tukikeskus Werkko) (128 570 €)</t>
+          <t>Ak 12454: Mielenterveys -ja päihdekuntoutujien sekä paljon sote-palveluita käyttävien toimintakyvyn ja osallisuuden edistämiseen sekä palvelujärjestelmän kehittämiseen kokemustietoa hyödyntämällä  (Tukikeskus Werkko) (128 570 €)</t>
         </is>
       </c>
     </row>
@@ -19902,8 +20754,7 @@
       </c>
       <c r="I500" t="inlineStr" s="0">
         <is>
-          <t>Ak 6: För strukturerad grupp- och individuell stödverksamhet för personer med
-missbruk och beroende (128 500 €)</t>
+          <t>Ak 6: För strukturerad grupp- och individuell stödverksamhet för personer med missbruk och beroende (128 500 €)</t>
         </is>
       </c>
     </row>
@@ -19936,7 +20787,7 @@
       </c>
       <c r="I501" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Unihäiriöistä aiheutuvien haittojen vähentämiseen neuvonnan  vertaistuen  edunvalvonnan ja viestinnän avulla sekä uniyhdistysten tukemiseen (128 000 €)</t>
+          <t>Ak 1: Unihäiriöistä aiheutuvien haittojen vähentämiseen neuvonnan, vertaistuen, edunvalvonnan ja viestinnän avulla sekä uniyhdistysten tukemiseen (128 000 €)</t>
         </is>
       </c>
     </row>
@@ -19969,8 +20820,7 @@
       </c>
       <c r="I502" t="inlineStr" s="0">
         <is>
-          <t>Ak 10781: Nuorten ja nuorten aikuisten syrjäytymistä ehkäisevään sekä eri väestöryhmiä yhdistävään ja osallistumista edistävään jalkautuvaan ryhmätoimintaan ja vapaa-ajantoimintaan
-(Yökoris Oulu) (127 500 €)</t>
+          <t>Ak 10781: Nuorten ja nuorten aikuisten syrjäytymistä ehkäisevään sekä eri väestöryhmiä yhdistävään ja osallistumista edistävään jalkautuvaan ryhmätoimintaan ja vapaa-ajantoimintaan (Yökoris Oulu) (127 500 €)</t>
         </is>
       </c>
     </row>
@@ -20003,7 +20853,7 @@
       </c>
       <c r="I503" t="inlineStr" s="0">
         <is>
-          <t>Ak 4: Mielenterveyskuntoutujien osallisuuden ja toimintakyvyn vahvistamiseen vapaaehtois- ja vertaisryhmätoiminnoilla Kuopiossa  Kaavilla ja Tuusniemellä (127 000 €)</t>
+          <t>Ak 4: Mielenterveyskuntoutujien osallisuuden ja toimintakyvyn vahvistamiseen vapaaehtois- ja vertaisryhmätoiminnoilla Kuopiossa, Kaavilla ja Tuusniemellä (127 000 €)</t>
         </is>
       </c>
     </row>
@@ -20036,8 +20886,7 @@
       </c>
       <c r="I504" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen  neuvonnan  vertaistoiminnan ja valmennusten avulla Hyvinkäällä  Riihimäellä  Hausjärvellä  Lopella ja Janakkalassa 
-(OmaisOiva) (126 950 €)</t>
+          <t>Ak 1: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen, neuvonnan, vertaistoiminnan ja valmennusten avulla Hyvinkäällä, Riihimäellä, Hausjärvellä, Lopella ja Janakkalassa  (OmaisOiva) (126 950 €)</t>
         </is>
       </c>
     </row>
@@ -20070,7 +20919,7 @@
       </c>
       <c r="I505" t="inlineStr" s="0">
         <is>
-          <t>Ak 11954: Sydänpiste-toimintaan HUS:n Postitalon kardiologian poliklinikan yhteydessä  vertaisryhmätoimintaan eteisvärinä- ja rytmihäiriöpotilaille sekä sydänpotilaan hoitopolun kehittämiseen HUS-alueella yhdessä terveydenhuoltohenkilöstön kanssa (101 500 €) | Ak 5721: Jäsenjärjestöille kohdistettaviin avustuksiin (25 000 €)</t>
+          <t>Ak 11954: Sydänpiste-toimintaan HUS:n Postitalon kardiologian poliklinikan yhteydessä, vertaisryhmätoimintaan eteisvärinä- ja rytmihäiriöpotilaille sekä sydänpotilaan hoitopolun kehittämiseen HUS-alueella yhdessä terveydenhuoltohenkilöstön kanssa (101 500 €) | Ak 5721: Jäsenjärjestöille kohdistettaviin avustuksiin (25 000 €)</t>
         </is>
       </c>
     </row>
@@ -20103,7 +20952,7 @@
       </c>
       <c r="I506" t="inlineStr" s="0">
         <is>
-          <t>Ak 7171: Vapaaehtoisten toteuttamaan MLL-tukihenkilötoimintaan Kainuussa (Perhekummi-  kaveri- ja ystäväksi maahanmuuttajaäidille toiminta sekä mummi- ja vaaritoiminta) (72 800 €) | C 13795: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Omanlaisena Yhdessä (Together as our own)" osarahoitukseen järjestölle (2026-2028) (43 500 €) | Ak 10756: Jäsenjärjestöille kohdistettaviin avustuksiin. (10 000 €)</t>
+          <t>Ak 7171: Vapaaehtoisten toteuttamaan MLL-tukihenkilötoimintaan Kainuussa (Perhekummi-, kaveri- ja ystäväksi maahanmuuttajaäidille toiminta sekä mummi- ja vaaritoiminta) (72 800 €) | C 13795: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Omanlaisena Yhdessä (Together as our own)" osarahoitukseen järjestölle (2026-2028) (43 500 €) | Ak 10756: Jäsenjärjestöille kohdistettaviin avustuksiin. (10 000 €)</t>
         </is>
       </c>
     </row>
@@ -20136,7 +20985,7 @@
       </c>
       <c r="I507" t="inlineStr" s="0">
         <is>
-          <t>Ak 11436: Kaksisuuntaisen kotoutumisen sekä maahanmuuttajataustaisten nuorten ja nuorten aikuisten osallisuuden edistämiseen yksilöllisen tuen  harrastus-  vapaaehtois- ja vertaisryhmätoiminnan sekä verkostotyön avulla (126 000 €)</t>
+          <t>Ak 11436: Kaksisuuntaisen kotoutumisen sekä maahanmuuttajataustaisten nuorten ja nuorten aikuisten osallisuuden edistämiseen yksilöllisen tuen, harrastus-, vapaaehtois- ja vertaisryhmätoiminnan sekä verkostotyön avulla (126 000 €)</t>
         </is>
       </c>
     </row>
@@ -20169,8 +21018,7 @@
       </c>
       <c r="I508" t="inlineStr" s="0">
         <is>
-          <t>Ak 9660: Kaksisuuntaisen kotoutumisen sekä maahanmuuttajataustaisten ja alueen muiden asukkaiden hyvinvoinnin  osallisuuden ja arjen hallinnan edistämiseen matalan kynnyksen vertaistoiminnalla Lieksassa sekä digitaalisella neuvontapalvelulla 
-(Verneri-toiminta) (126 000 €)</t>
+          <t>Ak 9660: Kaksisuuntaisen kotoutumisen sekä maahanmuuttajataustaisten ja alueen muiden asukkaiden hyvinvoinnin, osallisuuden ja arjen hallinnan edistämiseen matalan kynnyksen vertaistoiminnalla Lieksassa sekä digitaalisella neuvontapalvelulla  (Verneri-toiminta) (126 000 €)</t>
         </is>
       </c>
     </row>
@@ -20203,7 +21051,7 @@
       </c>
       <c r="I509" t="inlineStr" s="0">
         <is>
-          <t>Ak 7556: Pienten lasten äitien työelämäosallisuuden  hyvinvoinnin ja voimavarojen vahvistamiseen vapaaehtois-  vertais- ja tapahtumatoiminnalla (125 909 €)</t>
+          <t>Ak 7556: Pienten lasten äitien työelämäosallisuuden, hyvinvoinnin ja voimavarojen vahvistamiseen vapaaehtois-, vertais- ja tapahtumatoiminnalla (125 909 €)</t>
         </is>
       </c>
     </row>
@@ -20236,7 +21084,7 @@
       </c>
       <c r="I510" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Asukkaiden hyvinvoinnin ja osallisuuden edistämiseen vapaaehtoisten toteuttaman tukihenkilötoiminnan  ryhmätoimintojen  kriisipuhelinpalvelun ja tukikoirakkotoiminnan keinoin Lohjalla (125 905 €)</t>
+          <t>Ak 2: Asukkaiden hyvinvoinnin ja osallisuuden edistämiseen vapaaehtoisten toteuttaman tukihenkilötoiminnan, ryhmätoimintojen, kriisipuhelinpalvelun ja tukikoirakkotoiminnan keinoin Lohjalla (125 905 €)</t>
         </is>
       </c>
     </row>
@@ -20269,7 +21117,7 @@
       </c>
       <c r="I511" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Näkövammaisten itsenäisen elämän tukemiseen ja osallisuuden edistämiseen vertaistuen  ryhmätoiminnan  saavutettavan tiedon ja digiohjauksen avulla Pohjois-Pohjanmaalla (125 700 €)</t>
+          <t>Ak 2: Näkövammaisten itsenäisen elämän tukemiseen ja osallisuuden edistämiseen vertaistuen, ryhmätoiminnan, saavutettavan tiedon ja digiohjauksen avulla Pohjois-Pohjanmaalla (125 700 €)</t>
         </is>
       </c>
     </row>
@@ -20302,8 +21150,7 @@
       </c>
       <c r="I512" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Sisäkorvaperäistä huimausta ja Ménièren tautia sairastavien hyvinvoinnin ja työ- ja toimintakyvyn lisäämiseen ja elämänlaadun parantamiseen vertaistuen ja tiedon lisäämisen avulla
-- terveydenhuollon ammattilaisten tiedon ja ymmärryksen lisäämiseen yhteistoiminnalla (YTP-malli) (116 796 €) | Ak 1550: Jäsenjärjestöille kohdistettaviin avustuksiin (8 000 €)</t>
+          <t>Ak 3: Sisäkorvaperäistä huimausta ja Ménièren tautia sairastavien hyvinvoinnin ja työ- ja toimintakyvyn lisäämiseen ja elämänlaadun parantamiseen vertaistuen ja tiedon lisäämisen avulla - terveydenhuollon ammattilaisten tiedon ja ymmärryksen lisäämiseen yhteistoiminnalla (YTP-malli) (116 796 €) | Ak 1550: Jäsenjärjestöille kohdistettaviin avustuksiin (8 000 €)</t>
         </is>
       </c>
     </row>
@@ -20402,7 +21249,7 @@
       </c>
       <c r="I515" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Kaksisuuntaisen kotoutumisen sekä maahanmuuttajataustaisten ja muiden alueella asuvien osallisuuden ja toimintakyvyn edistämiseen yksilötuen  neuvonnan  palveluohjauksen  vertaisryhmien  kerhojen ja tapahtumien sekä vapaaehtoistoiminnan avulla kohtaamispaikassa (123 458 €)</t>
+          <t>Ak 1: Kaksisuuntaisen kotoutumisen sekä maahanmuuttajataustaisten ja muiden alueella asuvien osallisuuden ja toimintakyvyn edistämiseen yksilötuen, neuvonnan, palveluohjauksen, vertaisryhmien, kerhojen ja tapahtumien sekä vapaaehtoistoiminnan avulla kohtaamispaikassa (123 458 €)</t>
         </is>
       </c>
     </row>
@@ -20501,7 +21348,7 @@
       </c>
       <c r="I518" t="inlineStr" s="0">
         <is>
-          <t>Ak 11842: Vertaistukitoiminnan koordinointiin ja toteuttamiseen sekä vapaaehtoisten vertaistukitoimijoiden tukemiseen Kainuun  Keski-Pohjanmaan  Lapin ja Pohjois-Pohjanmaan alueilla (107 642 €) | Ak 7614: Jäsenjärjestöille kohdistettaviin avustuksiin (14 000 €)</t>
+          <t>Ak 11842: Vertaistukitoiminnan koordinointiin ja toteuttamiseen sekä vapaaehtoisten vertaistukitoimijoiden tukemiseen Kainuun, Keski-Pohjanmaan, Lapin ja Pohjois-Pohjanmaan alueilla (107 642 €) | Ak 7614: Jäsenjärjestöille kohdistettaviin avustuksiin (14 000 €)</t>
         </is>
       </c>
     </row>
@@ -20534,7 +21381,7 @@
       </c>
       <c r="I519" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Mielenterveys- ja päihdekuntoutujien sosiaalisten taitojen ylläpitämiseen ja yksinäisyyden vähentämiseen matalan kynnyksen kohtaamispaikan  neuvonnan ja ohjauksen sekä vertaistoimintojen avulla (Ylivieskan Mielikkitalo) (121 275 €)</t>
+          <t>Ak 1: Mielenterveys- ja päihdekuntoutujien sosiaalisten taitojen ylläpitämiseen ja yksinäisyyden vähentämiseen matalan kynnyksen kohtaamispaikan, neuvonnan ja ohjauksen sekä vertaistoimintojen avulla (Ylivieskan Mielikkitalo) (121 275 €)</t>
         </is>
       </c>
     </row>
@@ -20600,9 +21447,7 @@
       </c>
       <c r="I521" t="inlineStr" s="0">
         <is>
-          <t>Ak 9647: Venäjänkielisten ikääntyneiden osallisuuden ja hyvinvoinnin lisäämiseen sekä kaksisuuntaisen kotoutumisen edistämiseen Turun seudulla. 
-Toimintamuotoina kerho- ja ryhmätoiminta  tapahtumat ja vapaaehtoistoiminta
-(Silta-Turku) (120 000 €)</t>
+          <t>Ak 9647: Venäjänkielisten ikääntyneiden osallisuuden ja hyvinvoinnin lisäämiseen sekä kaksisuuntaisen kotoutumisen edistämiseen Turun seudulla.  Toimintamuotoina kerho- ja ryhmätoiminta, tapahtumat ja vapaaehtoistoiminta (Silta-Turku) (120 000 €)</t>
         </is>
       </c>
     </row>
@@ -20635,7 +21480,7 @@
       </c>
       <c r="I522" t="inlineStr" s="0">
         <is>
-          <t>Ak 9895: Vapautumisvaiheessa olevien  vapautuneiden vankien ja rikostaustaisten osallistujien yhteiskuntaan kiinnittymisen vahvistamiseen ja kuntouttamiseen yhteisöteatteritoiminnan avulla (120 000 €)</t>
+          <t>Ak 9895: Vapautumisvaiheessa olevien, vapautuneiden vankien ja rikostaustaisten osallistujien yhteiskuntaan kiinnittymisen vahvistamiseen ja kuntouttamiseen yhteisöteatteritoiminnan avulla (120 000 €)</t>
         </is>
       </c>
     </row>
@@ -20668,8 +21513,7 @@
       </c>
       <c r="I523" t="inlineStr" s="0">
         <is>
-          <t>Ak 3130: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen  neuvonnan  vertaistoiminnan ja valmennusten avulla Kuusamossa  Taivalkoskella  Posiolla ja Pudasjärvellä 
-(OmaisOiva) (119 700 €)</t>
+          <t>Ak 3130: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen, neuvonnan, vertaistoiminnan ja valmennusten avulla Kuusamossa, Taivalkoskella, Posiolla ja Pudasjärvellä  (OmaisOiva) (119 700 €)</t>
         </is>
       </c>
     </row>
@@ -20702,7 +21546,7 @@
       </c>
       <c r="I524" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Ikääntyneiden mielenterveyden  toimintakyvyn ja osallisuuden edistämiseen ryhmä- ja yksilötoiminnan keinoin (Mielenterveysyhteisöt Havurasti ja Myyrasti) (119 700 €)</t>
+          <t>Ak 2: Ikääntyneiden mielenterveyden, toimintakyvyn ja osallisuuden edistämiseen ryhmä- ja yksilötoiminnan keinoin (Mielenterveysyhteisöt Havurasti ja Myyrasti) (119 700 €)</t>
         </is>
       </c>
     </row>
@@ -20735,7 +21579,7 @@
       </c>
       <c r="I525" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Ruoka-aineallergiaperheiden vertaistuki- ja virkistystoimintaan  ruoka-allergianeuvontaan ja -ohjaukseen  kohderyhmän edunvalvontaan sekä verkkopalveluiden ylläpitämiseen (118 000 €)</t>
+          <t>Ak 2: Ruoka-aineallergiaperheiden vertaistuki- ja virkistystoimintaan, ruoka-allergianeuvontaan ja -ohjaukseen, kohderyhmän edunvalvontaan sekä verkkopalveluiden ylläpitämiseen (118 000 €)</t>
         </is>
       </c>
     </row>
@@ -20768,8 +21612,7 @@
       </c>
       <c r="I526" t="inlineStr" s="0">
         <is>
-          <t>Ak 2257: Oppivelvollisuuden loppupuolella Suomeen muuttaneiden maahanmuuttajataustaisten nuorten integroitumisen tukemiseen vertaistyön  yksilöohjauksen ja tulevaisuuden suunnittelun tukemisen avulla Helsingin  Espoon ja Vantaan alueella (74 970 €) | Ak 6198: Oppivelvollisuusiän loppupuolella Suomeen tulleiden maahanmuuttajanuorten ja nuorten aikuisten yhteiskunnallisten osallistumismahdollisuuksien vahvistamiseen oppituntivierailujen ja vapaa-ajan toimintojen sekä asiantuntijaosaamisen lisäämisellä avulla 
-(Muuttajat!) (42 263 €)</t>
+          <t>Ak 2257: Oppivelvollisuuden loppupuolella Suomeen muuttaneiden maahanmuuttajataustaisten nuorten integroitumisen tukemiseen vertaistyön, yksilöohjauksen ja tulevaisuuden suunnittelun tukemisen avulla Helsingin, Espoon ja Vantaan alueella (74 970 €) | Ak 6198: Oppivelvollisuusiän loppupuolella Suomeen tulleiden maahanmuuttajanuorten ja nuorten aikuisten yhteiskunnallisten osallistumismahdollisuuksien vahvistamiseen oppituntivierailujen ja vapaa-ajan toimintojen sekä asiantuntijaosaamisen lisäämisellä avulla  (Muuttajat!) (42 263 €)</t>
         </is>
       </c>
     </row>
@@ -20802,8 +21645,7 @@
       </c>
       <c r="I527" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Kaksisuuntaisen kotoutumisen ja maahanmuuttajataustaisten henkilöiden osallisuuden  hyvinvoinnin ja toimintakyvyn edistämiseen kohtaamispaikkatoiminnan avulla.
-Toimintamuotoina neuvonta  yksilöohjaus  ryhmätoiminta  palveluohjaus  vapaaehtoistoiminta  tapahtumat ja matalan kynnyksen kohtaamispaikkatoiminta (116 865 €)</t>
+          <t>Ak 1: Kaksisuuntaisen kotoutumisen ja maahanmuuttajataustaisten henkilöiden osallisuuden, hyvinvoinnin ja toimintakyvyn edistämiseen kohtaamispaikkatoiminnan avulla.  Toimintamuotoina neuvonta, yksilöohjaus, ryhmätoiminta, palveluohjaus, vapaaehtoistoiminta, tapahtumat ja matalan kynnyksen kohtaamispaikkatoiminta (116 865 €)</t>
         </is>
       </c>
     </row>
@@ -20836,7 +21678,7 @@
       </c>
       <c r="I528" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Ikääntyneiden  työttömien ja lapsiperheiden osallisuuden lisäämiseen ja syrjäytymisen ehkäisyyn matalan kynnyksen kohtaamis- ja osallistumispaikkatoiminnalla (115 762 €)</t>
+          <t>Ak 3: Ikääntyneiden, työttömien ja lapsiperheiden osallisuuden lisäämiseen ja syrjäytymisen ehkäisyyn matalan kynnyksen kohtaamis- ja osallistumispaikkatoiminnalla (115 762 €)</t>
         </is>
       </c>
     </row>
@@ -20869,7 +21711,7 @@
       </c>
       <c r="I529" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Mielenterveyskuntoutujien hyvinvointia ja toimintakykyä vahvistavan matalan kynnyksen kohtaamispaikan  vertaisryhmien ja vapaaehtoistoiminnan toteuttamiseen Iisalmessa (Louhentupa) (115 500 €)</t>
+          <t>Ak 1: Mielenterveyskuntoutujien hyvinvointia ja toimintakykyä vahvistavan matalan kynnyksen kohtaamispaikan, vertaisryhmien ja vapaaehtoistoiminnan toteuttamiseen Iisalmessa (Louhentupa) (115 500 €)</t>
         </is>
       </c>
     </row>
@@ -20968,7 +21810,7 @@
       </c>
       <c r="I532" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen  neuvonnan  vertaistoiminnan ja valmennusten avulla Loimaan seudulla (OmaisOiva) (115 000 €)</t>
+          <t>Ak 2: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen, neuvonnan, vertaistoiminnan ja valmennusten avulla Loimaan seudulla (OmaisOiva) (115 000 €)</t>
         </is>
       </c>
     </row>
@@ -21067,7 +21909,7 @@
       </c>
       <c r="I535" t="inlineStr" s="0">
         <is>
-          <t>Ak 5609: Yli 60-vuotiaiden osallisuuden  yhteisöllisyyden ja hyvinvoinnin vahvistamiseen kohtaamispaikan  yksilö- ja ryhmätoiminnan  ohjauksen  neuvonnan  vapaaehtois- ja vertaistoiminnan sekä etsivän vanhustyön keinoin (Torniotupa &amp; Keminmaatupa - Senioreiden olohuone) (112 223 €)</t>
+          <t>Ak 5609: Yli 60-vuotiaiden osallisuuden, yhteisöllisyyden ja hyvinvoinnin vahvistamiseen kohtaamispaikan, yksilö- ja ryhmätoiminnan, ohjauksen, neuvonnan, vapaaehtois- ja vertaistoiminnan sekä etsivän vanhustyön keinoin (Torniotupa &amp; Keminmaatupa - Senioreiden olohuone) (112 223 €)</t>
         </is>
       </c>
     </row>
@@ -21166,8 +22008,7 @@
       </c>
       <c r="I538" t="inlineStr" s="0">
         <is>
-          <t>Ak 7683: Jälkihuollon ulkopuolella olevien lastensuojelutaustaisten 18-29 -vuotiaiden nuorten aikuisten asunnottomuuden ehkäisemiseen ja vähentämiseen yksilötuki- ja vertaisryhmätoiminnan avulla 
-(SOMA Kuopio) (60 000 €) | Ak 1: Erityistä tukea tarvitsevien nuorten asunnottomuuden ehkäisyyn asumisohjauksella ja -neuvonnalla Kuopiossa (51 000 €)</t>
+          <t>Ak 7683: Jälkihuollon ulkopuolella olevien lastensuojelutaustaisten 18-29 -vuotiaiden nuorten aikuisten asunnottomuuden ehkäisemiseen ja vähentämiseen yksilötuki- ja vertaisryhmätoiminnan avulla  (SOMA Kuopio) (60 000 €) | Ak 1: Erityistä tukea tarvitsevien nuorten asunnottomuuden ehkäisyyn asumisohjauksella ja -neuvonnalla Kuopiossa (51 000 €)</t>
         </is>
       </c>
     </row>
@@ -21200,7 +22041,7 @@
       </c>
       <c r="I539" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Kotona asuvien senioreiden ja vapaaehtoisten osallisuuden ja hyvinvoinnin edistämiseen kiertävän kohtaamispaikkatoiminnan  ryhmätoiminnan ja tapahtumien keinoin (SenioriPiste Tornio) (110 250 €)</t>
+          <t>Ak 2: Kotona asuvien senioreiden ja vapaaehtoisten osallisuuden ja hyvinvoinnin edistämiseen kiertävän kohtaamispaikkatoiminnan, ryhmätoiminnan ja tapahtumien keinoin (SenioriPiste Tornio) (110 250 €)</t>
         </is>
       </c>
     </row>
@@ -21266,7 +22107,7 @@
       </c>
       <c r="I541" t="inlineStr" s="0">
         <is>
-          <t>Ak 12284: Sydäntuki -toiminnan ylläpitämiseen Tyks Sydänkeskuksen toimipisteissä  vertaistoiminnan vahvistamiseen sekä sydänjärjestön toiminnan vahvistamiseen osana sydänpotilaan hoitoketjua Varsinais-Suomessa (2024–2026) (95 200 €) | Ak 6442: Jäsenjärjestöille kohdistettaviin avustuksiin (15 000 €)</t>
+          <t>Ak 12284: Sydäntuki -toiminnan ylläpitämiseen Tyks Sydänkeskuksen toimipisteissä, vertaistoiminnan vahvistamiseen sekä sydänjärjestön toiminnan vahvistamiseen osana sydänpotilaan hoitoketjua Varsinais-Suomessa (2024–2026) (95 200 €) | Ak 6442: Jäsenjärjestöille kohdistettaviin avustuksiin (15 000 €)</t>
         </is>
       </c>
     </row>
@@ -21299,7 +22140,7 @@
       </c>
       <c r="I542" t="inlineStr" s="0">
         <is>
-          <t>Ak 10081: Osattomuutta ja yksinäisyyttä kokevien ikääntyneiden osallisuuden lisäämiseen ja toimintakyvyn ylläpitämiseen etsivän vanhustyön  yhteisöllisen toiminnan  vapaaehtoistoiminnan ja verkostoyhteistyön keinoin Itä-Helsingissä (ILO-toiminta) (110 000 €)</t>
+          <t>Ak 10081: Osattomuutta ja yksinäisyyttä kokevien ikääntyneiden osallisuuden lisäämiseen ja toimintakyvyn ylläpitämiseen etsivän vanhustyön, yhteisöllisen toiminnan, vapaaehtoistoiminnan ja verkostoyhteistyön keinoin Itä-Helsingissä (ILO-toiminta) (110 000 €)</t>
         </is>
       </c>
     </row>
@@ -21365,7 +22206,7 @@
       </c>
       <c r="I544" t="inlineStr" s="0">
         <is>
-          <t>Ak 5: Työttömien ja ikääntyvien henkilöiden sekä erityisesti pakolais- ja turvapaikanhakijataustaisten maahanmuuttajien elämänhallinnan  toimintakyvyn ja osallisuuden vahvistamiseen matalan kynnyksen ohjaus-  neuvonta- ja ryhmätoiminnoilla Kajaanissa (109 740 €)</t>
+          <t>Ak 5: Työttömien ja ikääntyvien henkilöiden sekä erityisesti pakolais- ja turvapaikanhakijataustaisten maahanmuuttajien elämänhallinnan, toimintakyvyn ja osallisuuden vahvistamiseen matalan kynnyksen ohjaus-, neuvonta- ja ryhmätoiminnoilla Kajaanissa (109 740 €)</t>
         </is>
       </c>
     </row>
@@ -21398,7 +22239,7 @@
       </c>
       <c r="I545" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Romaniväestön osallisuuden ja arjen hyvinvoinnin vahvistamiseen perhetyön  tapahtumien  koulutuksen  yksilöllisen tuen ja palveluohjauksen sekä ryhmätoiminnan avulla (Fentide diives) (109 148 €)</t>
+          <t>Ak 2: Romaniväestön osallisuuden ja arjen hyvinvoinnin vahvistamiseen perhetyön, tapahtumien, koulutuksen, yksilöllisen tuen ja palveluohjauksen sekä ryhmätoiminnan avulla (Fentide diives) (109 148 €)</t>
         </is>
       </c>
     </row>
@@ -21431,7 +22272,7 @@
       </c>
       <c r="I546" t="inlineStr" s="0">
         <is>
-          <t>C 13718: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Kuhmon Toivo: toivoa  toimintaa ja terveyttä" (210453) osarahoitukseen järjestölle (2026-2028) (108 012 €)</t>
+          <t>C 13718: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Kuhmon Toivo: toivoa, toimintaa ja terveyttä" (210453) osarahoitukseen järjestölle (2026-2028) (108 012 €)</t>
         </is>
       </c>
     </row>
@@ -21464,7 +22305,7 @@
       </c>
       <c r="I547" t="inlineStr" s="0">
         <is>
-          <t>Ak 12147: Sydän- tai keuhkosiirron saaneiden tai siirtoa odottavien  sydämen apupumpun kanssa elävien sekä heidän läheistensä hyvinvoinnin edistämiseen vertaistuki- ja tiedotustoiminnalla sekä vaikuttamistyöllä (107 959 €)</t>
+          <t>Ak 12147: Sydän- tai keuhkosiirron saaneiden tai siirtoa odottavien, sydämen apupumpun kanssa elävien sekä heidän läheistensä hyvinvoinnin edistämiseen vertaistuki- ja tiedotustoiminnalla sekä vaikuttamistyöllä (107 959 €)</t>
         </is>
       </c>
     </row>
@@ -21497,7 +22338,7 @@
       </c>
       <c r="I548" t="inlineStr" s="0">
         <is>
-          <t>Ak 1348: Näkövammaisten itsenäisen elämän tukemiseen ja osallisuuden edistämiseen vertaistuen  ryhmätoiminnan  saavutettavan tiedon ja digiohjauksen avulla Kainuussa (107 900 €)</t>
+          <t>Ak 1348: Näkövammaisten itsenäisen elämän tukemiseen ja osallisuuden edistämiseen vertaistuen, ryhmätoiminnan, saavutettavan tiedon ja digiohjauksen avulla Kainuussa (107 900 €)</t>
         </is>
       </c>
     </row>
@@ -21596,7 +22437,7 @@
       </c>
       <c r="I551" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Psyykkisiä ongelmia kokeneiden mielen hyvinvoinnin  osallisuuden ja terveyden edistämiseen kohtaamispaikkatoiminnalla (105 000 €)</t>
+          <t>Ak 1: Psyykkisiä ongelmia kokeneiden mielen hyvinvoinnin, osallisuuden ja terveyden edistämiseen kohtaamispaikkatoiminnalla (105 000 €)</t>
         </is>
       </c>
     </row>
@@ -21728,7 +22569,7 @@
       </c>
       <c r="I555" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: För social semesterverksamhet för familjer  närståendevårdare samt åldringar som har låg inkomst och behov av särskilt stöd. (101 940 €)</t>
+          <t>Ak 1: För social semesterverksamhet för familjer, närståendevårdare samt åldringar som har låg inkomst och behov av särskilt stöd. (101 940 €)</t>
         </is>
       </c>
     </row>
@@ -21761,7 +22602,7 @@
       </c>
       <c r="I556" t="inlineStr" s="0">
         <is>
-          <t>Ak 1007: Näkövammaisten itsenäisen elämän tukemiseen ja osallisuuden edistämiseen vertaistuen  ryhmätoiminnan  saavutettavan tiedon ja digiohjauksen avulla Pohjois-Savossa (101 100 €)</t>
+          <t>Ak 1007: Näkövammaisten itsenäisen elämän tukemiseen ja osallisuuden edistämiseen vertaistuen, ryhmätoiminnan, saavutettavan tiedon ja digiohjauksen avulla Pohjois-Savossa (101 100 €)</t>
         </is>
       </c>
     </row>
@@ -21794,7 +22635,7 @@
       </c>
       <c r="I557" t="inlineStr" s="0">
         <is>
-          <t>Ak 3960: Järjestökeskustoiminnan ja kohtaamispaikan ylläpitämiseen ja kehittämiseen  järjestöjen toimintaedellytysten tukemiseen ja mahdollistamiseen sekä kuntalaisten osallistumisen ja vapaaehtoistyön aktivointiin Sodankylässä (Järjestökeskus - hyvinvoinnin ja yhteisöllisyyden vahvistajana) (100 989 €)</t>
+          <t>Ak 3960: Järjestökeskustoiminnan ja kohtaamispaikan ylläpitämiseen ja kehittämiseen, järjestöjen toimintaedellytysten tukemiseen ja mahdollistamiseen sekä kuntalaisten osallistumisen ja vapaaehtoistyön aktivointiin Sodankylässä (Järjestökeskus - hyvinvoinnin ja yhteisöllisyyden vahvistajana) (100 989 €)</t>
         </is>
       </c>
     </row>
@@ -21827,7 +22668,7 @@
       </c>
       <c r="I558" t="inlineStr" s="0">
         <is>
-          <t>Ak 11992: Sotaorpojen tunnetaitojen ja voimavarojen vahvistamiseen sekä yksinäisyyden lievittämiseen pienryhmätoiminnan  hyvinvointipäivien ja kahvikassitoiminnan keinoin (Vertaistukea sotaorvoille) (100 000 €)</t>
+          <t>Ak 11992: Sotaorpojen tunnetaitojen ja voimavarojen vahvistamiseen sekä yksinäisyyden lievittämiseen pienryhmätoiminnan, hyvinvointipäivien ja kahvikassitoiminnan keinoin (Vertaistukea sotaorvoille) (100 000 €)</t>
         </is>
       </c>
     </row>
@@ -21893,7 +22734,7 @@
       </c>
       <c r="I560" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Yksinäisten tai kaverisuhteissa ongelmia kokevien lasten ja nuorten pienryhmätoiminnan järjestämiseen (Minä olen tärkeä -pienryhmätoiminta) sekä perheiden vuorovaikutuksen  voimavarojen  jaksamisen  osallisuuden ja toimijuuden vahvistamiseen Myö yhessä! -perhetoiminnan kautta. (99 225 €)</t>
+          <t>Ak 1: Yksinäisten tai kaverisuhteissa ongelmia kokevien lasten ja nuorten pienryhmätoiminnan järjestämiseen (Minä olen tärkeä -pienryhmätoiminta) sekä perheiden vuorovaikutuksen, voimavarojen, jaksamisen, osallisuuden ja toimijuuden vahvistamiseen Myö yhessä! -perhetoiminnan kautta. (99 225 €)</t>
         </is>
       </c>
     </row>
@@ -21926,8 +22767,7 @@
       </c>
       <c r="I561" t="inlineStr" s="0">
         <is>
-          <t>Ak 3137: Vaikeassa elämäntilanteessa olevien äitien ja lasten arjessa selviytymisen edistämiseen ryhmätoiminnan avulla
-(Itu-perhetyö) (99 167 €)</t>
+          <t>Ak 3137: Vaikeassa elämäntilanteessa olevien äitien ja lasten arjessa selviytymisen edistämiseen ryhmätoiminnan avulla (Itu-perhetyö) (99 167 €)</t>
         </is>
       </c>
     </row>
@@ -21960,7 +22800,7 @@
       </c>
       <c r="I562" t="inlineStr" s="0">
         <is>
-          <t>Ak 12326: Romaninaisten terveyslukutaidon ja vaikutusmahdollisuuksien vahvistamiseen yksilöllisellä tuella  kokemusasiantuntija- ja vertaisryhmätoiminnalla sekä ammattilaisten kouluttamisella (Sastipe tukke - Terveyttä sinulle 2024-2026) (99 000 €)</t>
+          <t>Ak 12326: Romaninaisten terveyslukutaidon ja vaikutusmahdollisuuksien vahvistamiseen yksilöllisellä tuella, kokemusasiantuntija- ja vertaisryhmätoiminnalla sekä ammattilaisten kouluttamisella (Sastipe tukke - Terveyttä sinulle 2024-2026) (99 000 €)</t>
         </is>
       </c>
     </row>
@@ -21993,8 +22833,7 @@
       </c>
       <c r="I563" t="inlineStr" s="0">
         <is>
-          <t>Ak 7587: Asunnottomuuden ehkäisemiseen ja vähentämiseen ammatillisen tukihenkilö-  vertaisryhmä- ja vapaaehtoistoiminnan keinoin lastensuojelutaustaisten 18–29-vuotiaiden keskuudessa 
-(SOMA Joensuu) (69 867 €) | Ak 1: Erityistä tukea tarvitsevien nuorten asunnottomuuden ehkäisyyn asumisohjauksella ja -neuvonnalla sekä ryhmätoiminnalla Joensuun seudulla (28 665 €)</t>
+          <t>Ak 7587: Asunnottomuuden ehkäisemiseen ja vähentämiseen ammatillisen tukihenkilö-, vertaisryhmä- ja vapaaehtoistoiminnan keinoin lastensuojelutaustaisten 18–29-vuotiaiden keskuudessa  (SOMA Joensuu) (69 867 €) | Ak 1: Erityistä tukea tarvitsevien nuorten asunnottomuuden ehkäisyyn asumisohjauksella ja -neuvonnalla sekä ryhmätoiminnalla Joensuun seudulla (28 665 €)</t>
         </is>
       </c>
     </row>
@@ -22027,7 +22866,7 @@
       </c>
       <c r="I564" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Matalan kynnyksen kohtaamispaikka-   ryhmä-  vapaaehtois- ja tukitoimintaan alueen asukkaille Jämsässä (97 650 €)</t>
+          <t>Ak 1: Matalan kynnyksen kohtaamispaikka- , ryhmä-, vapaaehtois- ja tukitoimintaan alueen asukkaille Jämsässä (97 650 €)</t>
         </is>
       </c>
     </row>
@@ -22093,7 +22932,7 @@
       </c>
       <c r="I566" t="inlineStr" s="0">
         <is>
-          <t>Ak 7508: Kotona asuvien ikäihmisten hyvinvoinnin ja osallisuuden edistämiseen ja yksinäisyyden ehkäisemiseen kohtaamispaikkojen sekä ryhmä- ja vertaistoiminnan avulla (Tutuksi Tuokiotuvalla - virtaa  välittämistä ja vertaistukea) (97 000 €)</t>
+          <t>Ak 7508: Kotona asuvien ikäihmisten hyvinvoinnin ja osallisuuden edistämiseen ja yksinäisyyden ehkäisemiseen kohtaamispaikkojen sekä ryhmä- ja vertaistoiminnan avulla (Tutuksi Tuokiotuvalla - virtaa, välittämistä ja vertaistukea) (97 000 €)</t>
         </is>
       </c>
     </row>
@@ -22126,7 +22965,7 @@
       </c>
       <c r="I567" t="inlineStr" s="0">
         <is>
-          <t>Ak 4: Maahanmuuttajien arjen ja osallisuuden tukemiseen yksilöllistä tukea ja ryhmä- ja kerhotoimintaa sisältävällä kohtaamispaikkatoiminnalla (55 413 €) | Ak 3: Ikääntyneiden omaishoitoperheiden arjen kokonaisvaltaiseen tukemiseen yksilöllisen tuen  ryhmämuotoisen vertaistuen ja vapaaehtoistoiminnan keinoin (41 526 €)</t>
+          <t>Ak 4: Maahanmuuttajien arjen ja osallisuuden tukemiseen yksilöllistä tukea ja ryhmä- ja kerhotoimintaa sisältävällä kohtaamispaikkatoiminnalla (55 413 €) | Ak 3: Ikääntyneiden omaishoitoperheiden arjen kokonaisvaltaiseen tukemiseen yksilöllisen tuen, ryhmämuotoisen vertaistuen ja vapaaehtoistoiminnan keinoin (41 526 €)</t>
         </is>
       </c>
     </row>
@@ -22159,7 +22998,7 @@
       </c>
       <c r="I568" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Näkövammaisten itsenäisen elämän tukemiseen ja osallisuuden edistämiseen vertaistuen  ryhmätoiminnan  saavutettavan tiedon ja digiohjauksen avulla Pohjois-Karjalassa (96 700 €)</t>
+          <t>Ak 2: Näkövammaisten itsenäisen elämän tukemiseen ja osallisuuden edistämiseen vertaistuen, ryhmätoiminnan, saavutettavan tiedon ja digiohjauksen avulla Pohjois-Karjalassa (96 700 €)</t>
         </is>
       </c>
     </row>
@@ -22225,7 +23064,7 @@
       </c>
       <c r="I570" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: För mötesplatsverksamhet som främjar hälsa  välbefinnande  delaktighet och återgång till arbets- och studielivet av rehabiliteringsklienter inom vården för psykisk hälsa (Fontana klubbhus i Karis) (96 600 €)</t>
+          <t>Ak 1: För mötesplatsverksamhet som främjar hälsa, välbefinnande, delaktighet och återgång till arbets- och studielivet av rehabiliteringsklienter inom vården för psykisk hälsa (Fontana klubbhus i Karis) (96 600 €)</t>
         </is>
       </c>
     </row>
@@ -22258,9 +23097,7 @@
       </c>
       <c r="I571" t="inlineStr" s="0">
         <is>
-          <t>Ak 6968: Syrjinnän vähentämiseen ja oppilaiden itsetuntemuksen ja sosiaalisten taitojen parantamiseen oppilaitoksissa järjestettävällä ryhmätoiminnalla 
-(KYTKE-toiminta) (57 000 €) | Ak 1: Lasten ja nuorten syrjäytymisen ehkäisemiseen taantuvilla lähiöalueilla ja toiminnan levittämiseen pääkaupunkiseudulla ja Tampereella
-(Urbaanit lapset ja nuoret) (39 333 €)</t>
+          <t>Ak 6968: Syrjinnän vähentämiseen ja oppilaiden itsetuntemuksen ja sosiaalisten taitojen parantamiseen oppilaitoksissa järjestettävällä ryhmätoiminnalla  (KYTKE-toiminta) (57 000 €) | Ak 1: Lasten ja nuorten syrjäytymisen ehkäisemiseen taantuvilla lähiöalueilla ja toiminnan levittämiseen pääkaupunkiseudulla ja Tampereella (Urbaanit lapset ja nuoret) (39 333 €)</t>
         </is>
       </c>
     </row>
@@ -22293,7 +23130,7 @@
       </c>
       <c r="I572" t="inlineStr" s="0">
         <is>
-          <t>Ak 7289: Alueellisen vapaaehtoistoiminnan ja järjestöjen yhteistyön tukemiseen verkostotyön  koulutuksen ja viestinnän avulla (94 938 €)</t>
+          <t>Ak 7289: Alueellisen vapaaehtoistoiminnan ja järjestöjen yhteistyön tukemiseen verkostotyön, koulutuksen ja viestinnän avulla (94 938 €)</t>
         </is>
       </c>
     </row>
@@ -22326,7 +23163,7 @@
       </c>
       <c r="I573" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Yksilö- ja pari-  ja ryhmätyöskentelyyn lähi- tai parisuhdeväkivaltaa tai sen uhkaa kokeneiden henkilöiden kanssa sekä lähi - ja parisuhdeväkivallan tekijöiden kanssa. Lapsiperheitä tukevaan järjestölähtöiseen avopalvelutoimintaan (Ero lapsiperheessä -työ  yksilö- ja parityöskentely aikuisille ja ryhmätyöskentelyt lapsille  tenavatupa-  vauvaperheohjaus sekä vapaaehtoistoiminnan koordinointi) (94 842 €)</t>
+          <t>Ak 3: Yksilö- ja pari-, ja ryhmätyöskentelyyn lähi- tai parisuhdeväkivaltaa tai sen uhkaa kokeneiden henkilöiden kanssa sekä lähi - ja parisuhdeväkivallan tekijöiden kanssa. Lapsiperheitä tukevaan järjestölähtöiseen avopalvelutoimintaan (Ero lapsiperheessä -työ, yksilö- ja parityöskentely aikuisille ja ryhmätyöskentelyt lapsille, tenavatupa-, vauvaperheohjaus sekä vapaaehtoistoiminnan koordinointi) (94 842 €)</t>
         </is>
       </c>
     </row>
@@ -22359,7 +23196,7 @@
       </c>
       <c r="I574" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Mielenterveyskuntoutujien hyvinvoinnin ja osallisuuden vahvistamiseen matalan kynnyksen kohtaamispaikan  vertaisryhmätoiminnan  neuvonnan ja tapahtumien avulla (Varkauden Mielitupa) (94 500 €)</t>
+          <t>Ak 1: Mielenterveyskuntoutujien hyvinvoinnin ja osallisuuden vahvistamiseen matalan kynnyksen kohtaamispaikan, vertaisryhmätoiminnan, neuvonnan ja tapahtumien avulla (Varkauden Mielitupa) (94 500 €)</t>
         </is>
       </c>
     </row>
@@ -22392,7 +23229,7 @@
       </c>
       <c r="I575" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Kuulovammaisten ja pitkäaikaissairaiden toimintakyvyn  itsenäisyyden ja turvallisuuden tunteen parantamiseen kuulo- ja tukikoirien sekä sosiaalisen tuen koirien avulla (93 975 €)</t>
+          <t>Ak 2: Kuulovammaisten ja pitkäaikaissairaiden toimintakyvyn, itsenäisyyden ja turvallisuuden tunteen parantamiseen kuulo- ja tukikoirien sekä sosiaalisen tuen koirien avulla (93 975 €)</t>
         </is>
       </c>
     </row>
@@ -22458,7 +23295,7 @@
       </c>
       <c r="I577" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen  neuvonnan  vertaistoiminnan ja valmennusten avulla Keski-Pohjanmaalla (OmaisOiva) (91 964 €)</t>
+          <t>Ak 3: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen, neuvonnan, vertaistoiminnan ja valmennusten avulla Keski-Pohjanmaalla (OmaisOiva) (91 964 €)</t>
         </is>
       </c>
     </row>
@@ -22491,7 +23328,7 @@
       </c>
       <c r="I578" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen  neuvonnan  vertaistoiminnan ja valmennusten avulla Ähtärissä  Alajärvellä  Vimpelissä  Evijärvellä  Lappajärvellä  Soinissa  Alavudella ja Kuortaneella (OmaisOiva) (91 770 €)</t>
+          <t>Ak 1: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen, neuvonnan, vertaistoiminnan ja valmennusten avulla Ähtärissä, Alajärvellä, Vimpelissä, Evijärvellä, Lappajärvellä, Soinissa, Alavudella ja Kuortaneella (OmaisOiva) (91 770 €)</t>
         </is>
       </c>
     </row>
@@ -22524,8 +23361,7 @@
       </c>
       <c r="I579" t="inlineStr" s="0">
         <is>
-          <t>Ak 3323: Paperittomien henkilöiden terveyden edistämiseen neuvonnan  palveluohjauksen  vapaaehtoistoiminnan  verkostotyön  tiedottamisen sekä ammattilaisten osaamisen vahvistamisen avulla 
-(PapeTe-toiminta) (91 750 €)</t>
+          <t>Ak 3323: Paperittomien henkilöiden terveyden edistämiseen neuvonnan, palveluohjauksen, vapaaehtoistoiminnan, verkostotyön, tiedottamisen sekä ammattilaisten osaamisen vahvistamisen avulla  (PapeTe-toiminta) (91 750 €)</t>
         </is>
       </c>
     </row>
@@ -22558,7 +23394,7 @@
       </c>
       <c r="I580" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Erityistä tukea tarvitsevien nuorten asumisen valmiuksien lisäämiseen  itsenäistymisen tukemiseen sekä asunnottomuuden ja häätöjen ennaltaehkäisyyn asumisen tieto- ja neuvontatyöllä sekä ryhmätoiminnoilla Oulun seudulla (Asumisen sisältöpalvelut) (90 910 €)</t>
+          <t>Ak 1: Erityistä tukea tarvitsevien nuorten asumisen valmiuksien lisäämiseen, itsenäistymisen tukemiseen sekä asunnottomuuden ja häätöjen ennaltaehkäisyyn asumisen tieto- ja neuvontatyöllä sekä ryhmätoiminnoilla Oulun seudulla (Asumisen sisältöpalvelut) (90 910 €)</t>
         </is>
       </c>
     </row>
@@ -22690,7 +23526,7 @@
       </c>
       <c r="I584" t="inlineStr" s="0">
         <is>
-          <t>Ak 10844: Jalkautuvaa digitukea yksilöllisesti  ryhmässä sekä pop-up -tapahtumien avulla vammaisille  Etelä-Karjassa (Mie Ite- Digiä kaikille) (89 000 €)</t>
+          <t>Ak 10844: Jalkautuvaa digitukea yksilöllisesti, ryhmässä sekä pop-up -tapahtumien avulla vammaisille  Etelä-Karjassa (Mie Ite- Digiä kaikille) (89 000 €)</t>
         </is>
       </c>
     </row>
@@ -22723,7 +23559,7 @@
       </c>
       <c r="I585" t="inlineStr" s="0">
         <is>
-          <t>Ak 9798: Elintapaohjaukseen tarkoitetun Verkkopuntari-työkalun kehittämiseen ja kansalliseen ylläpitoon  ohjelman käytön tukemiseen sekä juurruttamiseen osaksi sote-rakenteita (78 000 €) | Ak 3771: Jäsenjärjestöille kohdistettaviin avustuksiin (11 000 €)</t>
+          <t>Ak 9798: Elintapaohjaukseen tarkoitetun Verkkopuntari-työkalun kehittämiseen ja kansalliseen ylläpitoon, ohjelman käytön tukemiseen sekä juurruttamiseen osaksi sote-rakenteita (78 000 €) | Ak 3771: Jäsenjärjestöille kohdistettaviin avustuksiin (11 000 €)</t>
         </is>
       </c>
     </row>
@@ -22756,8 +23592,7 @@
       </c>
       <c r="I586" t="inlineStr" s="0">
         <is>
-          <t>Ak 7334: Maahanmuuttajataustaisten nuorten työelämä- ja opintopolkujen tukemiseen sekä vaikuttamis- ja osallistumismahdollisuuksien lisäämiseen yksilöllisen tuen  koulutusten  ryhmätoiminnan ja tapahtumien avulla 
-(Impact Academy) (88 240 €)</t>
+          <t>Ak 7334: Maahanmuuttajataustaisten nuorten työelämä- ja opintopolkujen tukemiseen sekä vaikuttamis- ja osallistumismahdollisuuksien lisäämiseen yksilöllisen tuen, koulutusten, ryhmätoiminnan ja tapahtumien avulla  (Impact Academy) (88 240 €)</t>
         </is>
       </c>
     </row>
@@ -22889,8 +23724,7 @@
       </c>
       <c r="I590" t="inlineStr" s="0">
         <is>
-          <t>Ak 6549: Savonlinnan seudun ikääntyvän väestön järjestölähtöisen aivo- ja
-muistiterveyden edistämistyöhön järjestämällä vertaistuellista ja osallisuutta edistävää ryhmätoimintaa ja vapaaehtoistoimintaa. Vapaaehtoistoimijoiden kouluttamiseen ja tukemiseen sekä yhteistyöhön ja vaikuttamistyöhön. (Sillanrakentaja -järjestölähtöisen aivo- ja muistiterveyden edistäminen Savonlinnan seudulla) (84 000 €)</t>
+          <t>Ak 6549: Savonlinnan seudun ikääntyvän väestön järjestölähtöisen aivo- ja muistiterveyden edistämistyöhön järjestämällä vertaistuellista ja osallisuutta edistävää ryhmätoimintaa ja vapaaehtoistoimintaa. Vapaaehtoistoimijoiden kouluttamiseen ja tukemiseen sekä yhteistyöhön ja vaikuttamistyöhön. (Sillanrakentaja -järjestölähtöisen aivo- ja muistiterveyden edistäminen Savonlinnan seudulla) (84 000 €)</t>
         </is>
       </c>
     </row>
@@ -23055,7 +23889,7 @@
       </c>
       <c r="I595" t="inlineStr" s="0">
         <is>
-          <t>Ak 10126: Heikommassa asemassa olevien osallisuuden ja yhteisöllisyyden vahvistamiseen matalan kynnyksen kohtaamispaikkatoiminnan  ryhmämuotoisen toiminnan ja yksilöllisen tuen avulla Pelkosenniemellä ja Savukoskella (78 800 €)</t>
+          <t>Ak 10126: Heikommassa asemassa olevien osallisuuden ja yhteisöllisyyden vahvistamiseen matalan kynnyksen kohtaamispaikkatoiminnan, ryhmämuotoisen toiminnan ja yksilöllisen tuen avulla Pelkosenniemellä ja Savukoskella (78 800 €)</t>
         </is>
       </c>
     </row>
@@ -23220,7 +24054,7 @@
       </c>
       <c r="I600" t="inlineStr" s="0">
         <is>
-          <t>Ak 6034: Työttömien arjenhallinnan ja osallisuuden vahvistamiseen matalan kynnyksen ohjauksella  neuvonnalla ja virkistystoiminnalla Jyväskylän seudulla (Sirpakka-toiminta) (76 500 €)</t>
+          <t>Ak 6034: Työttömien arjenhallinnan ja osallisuuden vahvistamiseen matalan kynnyksen ohjauksella, neuvonnalla ja virkistystoiminnalla Jyväskylän seudulla (Sirpakka-toiminta) (76 500 €)</t>
         </is>
       </c>
     </row>
@@ -23253,7 +24087,7 @@
       </c>
       <c r="I601" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Mielenterveyskuntoutujien ja heidän omaistensa positiivisen mielenterveyden ja hyvinvoinnin lisäämiseen vertaistukea  neuvontaa ja ryhmätoimintoja sisältävällä matalan kynnyksen kohtaamispaikkatoiminnalla Kiuruvedellä (Varapäre) (76 491 €)</t>
+          <t>Ak 1: Mielenterveyskuntoutujien ja heidän omaistensa positiivisen mielenterveyden ja hyvinvoinnin lisäämiseen vertaistukea, neuvontaa ja ryhmätoimintoja sisältävällä matalan kynnyksen kohtaamispaikkatoiminnalla Kiuruvedellä (Varapäre) (76 491 €)</t>
         </is>
       </c>
     </row>
@@ -23286,7 +24120,7 @@
       </c>
       <c r="I602" t="inlineStr" s="0">
         <is>
-          <t>Ak 3245: För att öka finlandssvenska teckenspråkigas delaktighet genom lågtröskelverksamhet  information och påverkansarbete (75 000 €)</t>
+          <t>Ak 3245: För att öka finlandssvenska teckenspråkigas delaktighet genom lågtröskelverksamhet, information och påverkansarbete (75 000 €)</t>
         </is>
       </c>
     </row>
@@ -23319,7 +24153,7 @@
       </c>
       <c r="I603" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen  neuvonnan  vertaistoiminnan ja valmennusten avulla Raahen seudulla (OmaisOiva) (75 000 €)</t>
+          <t>Ak 1: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen, neuvonnan, vertaistoiminnan ja valmennusten avulla Raahen seudulla (OmaisOiva) (75 000 €)</t>
         </is>
       </c>
     </row>
@@ -23352,7 +24186,7 @@
       </c>
       <c r="I604" t="inlineStr" s="0">
         <is>
-          <t>Ak 5702: Työttömien terveellisten elämäntapojen ja työelämäosallisuuden vahvistamiseen matalan kynnyksen kohtaamispaikkatoiminnan ohjaus-  neuvonta- ja ryhmätoiminnoilla Mikkelissä (63 221 €) | C 13656: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Tsempparit" osarahoitukseen järjestölle (2026-2027) (11 520 €)</t>
+          <t>Ak 5702: Työttömien terveellisten elämäntapojen ja työelämäosallisuuden vahvistamiseen matalan kynnyksen kohtaamispaikkatoiminnan ohjaus-, neuvonta- ja ryhmätoiminnoilla Mikkelissä (63 221 €) | C 13656: Euroopan sosiaalirahasto plussan (ESR+) hankkeen "Tsempparit" osarahoitukseen järjestölle (2026-2027) (11 520 €)</t>
         </is>
       </c>
     </row>
@@ -23385,7 +24219,7 @@
       </c>
       <c r="I605" t="inlineStr" s="0">
         <is>
-          <t>Ak 1700: Akustikusneurinoomaa sairastavien tiedotustoimintaan sekä arjen hyvinvoinnin tukemiseen vertaistuella  koulutuksella ja ryhmätoiminnalla (74 611 €)</t>
+          <t>Ak 1700: Akustikusneurinoomaa sairastavien tiedotustoimintaan sekä arjen hyvinvoinnin tukemiseen vertaistuella, koulutuksella ja ryhmätoiminnalla (74 611 €)</t>
         </is>
       </c>
     </row>
@@ -23418,7 +24252,7 @@
       </c>
       <c r="I606" t="inlineStr" s="0">
         <is>
-          <t>Ak 12409: Rintasyöpään sairastuneiden ja heidän läheistensä tukemiseen hyvinvointia lisäävällä toiminnalla  vertais- ja vapaaehtoistoiminnalla  edunvalvonnalla ja viestinnällä (74 000 €)</t>
+          <t>Ak 12409: Rintasyöpään sairastuneiden ja heidän läheistensä tukemiseen hyvinvointia lisäävällä toiminnalla, vertais- ja vapaaehtoistoiminnalla, edunvalvonnalla ja viestinnällä (74 000 €)</t>
         </is>
       </c>
     </row>
@@ -23451,7 +24285,7 @@
       </c>
       <c r="I607" t="inlineStr" s="0">
         <is>
-          <t>Ak 1028: Näkövammaisten itsenäisen elämän tukemiseen ja osallisuuden edistämiseen vertaistuen  ryhmätoiminnan ja saavutettavan tiedon avulla Kaakkois-Suomessa (73 800 €)</t>
+          <t>Ak 1028: Näkövammaisten itsenäisen elämän tukemiseen ja osallisuuden edistämiseen vertaistuen, ryhmätoiminnan ja saavutettavan tiedon avulla Kaakkois-Suomessa (73 800 €)</t>
         </is>
       </c>
     </row>
@@ -23550,7 +24384,7 @@
       </c>
       <c r="I610" t="inlineStr" s="0">
         <is>
-          <t>Ak 3808: Yli 65-vuotiaiden kotona asuvien yksinäisyyden vähentämiseen  osallisuuden lisäämiseen sekä toimintakyvyn edistämiseen ryhmätoiminnan  vertaisohjaajien ja vapaaehtoisten avulla (Eloisaa!-toiminta) (72 304 €)</t>
+          <t>Ak 3808: Yli 65-vuotiaiden kotona asuvien yksinäisyyden vähentämiseen, osallisuuden lisäämiseen sekä toimintakyvyn edistämiseen ryhmätoiminnan, vertaisohjaajien ja vapaaehtoisten avulla (Eloisaa!-toiminta) (72 304 €)</t>
         </is>
       </c>
     </row>
@@ -23583,7 +24417,7 @@
       </c>
       <c r="I611" t="inlineStr" s="0">
         <is>
-          <t>Ak 12670: Yhdistystoiminnan aktivointiin  järjestöjen toiminnasta viestimiseen sekä yhteistoiminnan koordinointiin Etelä-Karjalan hyvinvointialueella (Etelä-Karjalan yhdistysten tuki) (72 210 €)</t>
+          <t>Ak 12670: Yhdistystoiminnan aktivointiin, järjestöjen toiminnasta viestimiseen sekä yhteistoiminnan koordinointiin Etelä-Karjalan hyvinvointialueella (Etelä-Karjalan yhdistysten tuki) (72 210 €)</t>
         </is>
       </c>
     </row>
@@ -23781,7 +24615,7 @@
       </c>
       <c r="I617" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen  neuvonnan  vertaistoiminnan ja valmennusten avulla kuuden kunnan alueella Kalajokilaaksossa (OmaisOiva) (68 849 €)</t>
+          <t>Ak 1: Omaishoitajien toimintakyvyn tukemiseen tiedottamisen, neuvonnan, vertaistoiminnan ja valmennusten avulla kuuden kunnan alueella Kalajokilaaksossa (OmaisOiva) (68 849 €)</t>
         </is>
       </c>
     </row>
@@ -23880,7 +24714,7 @@
       </c>
       <c r="I620" t="inlineStr" s="0">
         <is>
-          <t>Ak 2238: Ikäihmisten osallisuuden edistämiseen ja toimintakyvyn ylläpitämiseen kohtaamispaikka-  ryhmä- ja vapaaehtoistoiminnan sekä yhteistyöverkoston keinoin (Miä ite – Myö yhessä) (66 150 €)</t>
+          <t>Ak 2238: Ikäihmisten osallisuuden edistämiseen ja toimintakyvyn ylläpitämiseen kohtaamispaikka-, ryhmä- ja vapaaehtoistoiminnan sekä yhteistyöverkoston keinoin (Miä ite – Myö yhessä) (66 150 €)</t>
         </is>
       </c>
     </row>
@@ -23946,7 +24780,7 @@
       </c>
       <c r="I622" t="inlineStr" s="0">
         <is>
-          <t>Ak 11841: Kainuun sote-järjestöjen  kuntien ja hyvinvointialueen yhteistyön vahvistamiseen sekä järjestötoiminnan koordinoimiseen ja järjestötoiminnasta viestimiseen (Yhteistyöllä ja kumppanuudella vahvempaa sotejärjestötoimintaa Kainuussa) (65 680 €)</t>
+          <t>Ak 11841: Kainuun sote-järjestöjen, kuntien ja hyvinvointialueen yhteistyön vahvistamiseen sekä järjestötoiminnan koordinoimiseen ja järjestötoiminnasta viestimiseen (Yhteistyöllä ja kumppanuudella vahvempaa sotejärjestötoimintaa Kainuussa) (65 680 €)</t>
         </is>
       </c>
     </row>
@@ -24045,7 +24879,7 @@
       </c>
       <c r="I625" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Diabeetikoille ja heidän läheisilleen sekä riskiryhmään kuuluville suunnattuun tiedotus-  neuvonta- ja ohjaustoimintaan sekä ammattilaisille suunnattuun työhön Pirkanmaalla (64 000 €)</t>
+          <t>Ak 3: Diabeetikoille ja heidän läheisilleen sekä riskiryhmään kuuluville suunnattuun tiedotus-, neuvonta- ja ohjaustoimintaan sekä ammattilaisille suunnattuun työhön Pirkanmaalla (64 000 €)</t>
         </is>
       </c>
     </row>
@@ -24111,7 +24945,7 @@
       </c>
       <c r="I627" t="inlineStr" s="0">
         <is>
-          <t>Ak 10603: Maahanmuuttajaäitien osallisuuden ja kotoutumisen edistämiseen vapaaehtoisen  matalankynnyksen ystävätoiminnan keinoin sekä yhdistyksen monikulttuurisen toiminnan kehittämiseen. (63 110 €)</t>
+          <t>Ak 10603: Maahanmuuttajaäitien osallisuuden ja kotoutumisen edistämiseen vapaaehtoisen, matalankynnyksen ystävätoiminnan keinoin sekä yhdistyksen monikulttuurisen toiminnan kehittämiseen. (63 110 €)</t>
         </is>
       </c>
     </row>
@@ -24144,7 +24978,7 @@
       </c>
       <c r="I628" t="inlineStr" s="0">
         <is>
-          <t>Ak 9912: Syöpään sairastuneiden ja heidän läheisten tuki-  kriisi- ja neuvontatoimintaan sekä vertaistukitoimintaan Hämeenlinna - Riihimäki - Hyvinkää alueella (62 503 €)</t>
+          <t>Ak 9912: Syöpään sairastuneiden ja heidän läheisten tuki-, kriisi- ja neuvontatoimintaan sekä vertaistukitoimintaan Hämeenlinna - Riihimäki - Hyvinkää alueella (62 503 €)</t>
         </is>
       </c>
     </row>
@@ -24177,7 +25011,7 @@
       </c>
       <c r="I629" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: För att stöda personer med psykisk ohälsa genom att koordinera och organisera psykosocialt stöd på svenska  erbjuda kamratstöd och rådgivning samt genom att idka intressebevakning i huvudstadsregionen (61 630 €)</t>
+          <t>Ak 2: För att stöda personer med psykisk ohälsa genom att koordinera och organisera psykosocialt stöd på svenska, erbjuda kamratstöd och rådgivning samt genom att idka intressebevakning i huvudstadsregionen (61 630 €)</t>
         </is>
       </c>
     </row>
@@ -24276,7 +25110,7 @@
       </c>
       <c r="I632" t="inlineStr" s="0">
         <is>
-          <t>Ak 2581: Erityistä tukea tarvitsevien nuorten asunnottomuuden ehkäisyyn ja itsenäisen asumisen tukemiseen asumisohjauksella ja -neuvonnalla  ryhmätoiminnalla sekä nuorten asumistietoutta edistämällä Jyväskylän  Laukaan ja Muuramen alueella (60 607 €)</t>
+          <t>Ak 2581: Erityistä tukea tarvitsevien nuorten asunnottomuuden ehkäisyyn ja itsenäisen asumisen tukemiseen asumisohjauksella ja -neuvonnalla, ryhmätoiminnalla sekä nuorten asumistietoutta edistämällä Jyväskylän, Laukaan ja Muuramen alueella (60 607 €)</t>
         </is>
       </c>
     </row>
@@ -24309,8 +25143,7 @@
       </c>
       <c r="I633" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Erityistä tukea tarvitsevien nuorten asunnottomuuden ehkäisyyn ja itsenäisen asumisen tukemiseen asumisohjauksella ja -neuvonnalla sekä ryhmätoiminnoilla Hämeenlinnan seudulla
-(Nuorisoasumisen sisältöpalvelut) (60 607 €)</t>
+          <t>Ak 1: Erityistä tukea tarvitsevien nuorten asunnottomuuden ehkäisyyn ja itsenäisen asumisen tukemiseen asumisohjauksella ja -neuvonnalla sekä ryhmätoiminnoilla Hämeenlinnan seudulla (Nuorisoasumisen sisältöpalvelut) (60 607 €)</t>
         </is>
       </c>
     </row>
@@ -24508,7 +25341,7 @@
       </c>
       <c r="I639" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Erityistä tukea tarvitsevien nuorten asunnottomuuden ehkäisyyn asumisohjauksella ja -neuvonnalla  ryhmätoiminnoilla ja koulutuksella Nokialla  Pirkkalassa ja Ylöjärvellä (59 485 €)</t>
+          <t>Ak 1: Erityistä tukea tarvitsevien nuorten asunnottomuuden ehkäisyyn asumisohjauksella ja -neuvonnalla, ryhmätoiminnoilla ja koulutuksella Nokialla, Pirkkalassa ja Ylöjärvellä (59 485 €)</t>
         </is>
       </c>
     </row>
@@ -24574,7 +25407,7 @@
       </c>
       <c r="I641" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Näkövammaisten itsenäisen elämän tukemiseen ja osallisuuden edistämiseen vertaistuen  ryhmätoiminnan  saavutettavan tiedon ja digituen avulla Varsinais-Suomen alueella (58 200 €)</t>
+          <t>Ak 2: Näkövammaisten itsenäisen elämän tukemiseen ja osallisuuden edistämiseen vertaistuen, ryhmätoiminnan, saavutettavan tiedon ja digituen avulla Varsinais-Suomen alueella (58 200 €)</t>
         </is>
       </c>
     </row>
@@ -24640,7 +25473,7 @@
       </c>
       <c r="I643" t="inlineStr" s="0">
         <is>
-          <t>Ak 11055: Ikääntyneiden toimintakyvyn  hyvinvoinnin ja kotona asumisen tukemiseen ravitsemus- ja kotitalousneuvonnalla (VIRKEE - Vireästi Karjalassa) (57 800 €)</t>
+          <t>Ak 11055: Ikääntyneiden toimintakyvyn, hyvinvoinnin ja kotona asumisen tukemiseen ravitsemus- ja kotitalousneuvonnalla (VIRKEE - Vireästi Karjalassa) (57 800 €)</t>
         </is>
       </c>
     </row>
@@ -24673,7 +25506,7 @@
       </c>
       <c r="I644" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Työttömien työnhakijoiden työelämävalmiuksien ja -osallisuuden sekä työ- ja toimintakyvyn vahvistamiseen matalan kynnyksen ohjaus-  neuvonta- ja ryhmätoiminnoilla Rauman seudulla (Kohtaamispaikka Rauman Kipinä) (57 240 €)</t>
+          <t>Ak 2: Työttömien työnhakijoiden työelämävalmiuksien ja -osallisuuden sekä työ- ja toimintakyvyn vahvistamiseen matalan kynnyksen ohjaus-, neuvonta- ja ryhmätoiminnoilla Rauman seudulla (Kohtaamispaikka Rauman Kipinä) (57 240 €)</t>
         </is>
       </c>
     </row>
@@ -24706,7 +25539,7 @@
       </c>
       <c r="I645" t="inlineStr" s="0">
         <is>
-          <t>Ak 3: Mielenterveyden haasteita kokevien työikäisten osallisuuden ja yhteisöllisyyden edistämiseen avoimen kohtaamispaikka- ja ryhmätoiminnan  ohjauksen ja vertaistuen avulla (Kohtaamispaikka Kiesi) (57 220 €)</t>
+          <t>Ak 3: Mielenterveyden haasteita kokevien työikäisten osallisuuden ja yhteisöllisyyden edistämiseen avoimen kohtaamispaikka- ja ryhmätoiminnan, ohjauksen ja vertaistuen avulla (Kohtaamispaikka Kiesi) (57 220 €)</t>
         </is>
       </c>
     </row>
@@ -24739,7 +25572,7 @@
       </c>
       <c r="I646" t="inlineStr" s="0">
         <is>
-          <t>Ak 5710: Syrjäytymisvaarassa olevien henkilöiden osallisuuden  yhteisöllisyyden ja hyvinvoinnin vahvistamiseen kaikille avoimella matalan kynnyksen ohjaus-  neuvonta- ja kohtaamispaikkatoiminnalla Kemissä (Kemin kansalaistalo - matalankynnyksen ohjaus-  palveluneuvonta- ja kohtaamispaikka) (56 000 €)</t>
+          <t>Ak 5710: Syrjäytymisvaarassa olevien henkilöiden osallisuuden, yhteisöllisyyden ja hyvinvoinnin vahvistamiseen kaikille avoimella matalan kynnyksen ohjaus-, neuvonta- ja kohtaamispaikkatoiminnalla Kemissä (Kemin kansalaistalo - matalankynnyksen ohjaus-, palveluneuvonta- ja kohtaamispaikka) (56 000 €)</t>
         </is>
       </c>
     </row>
@@ -24772,7 +25605,7 @@
       </c>
       <c r="I647" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Työttömien  työelämän ja koulutuksen ulkopuolella olevien työikäisten sekä työttömänä eläköityneiden henkilöiden yhteisöllisyyden ja toimintakyvyn vahvistamiseen matalan kynnyksen ohjaus-  vertais- ja ryhmätoiminnalla Nurmeksessa ja Juuassa (Voimavarat käyttöön) (56 000 €)</t>
+          <t>Ak 2: Työttömien, työelämän ja koulutuksen ulkopuolella olevien työikäisten sekä työttömänä eläköityneiden henkilöiden yhteisöllisyyden ja toimintakyvyn vahvistamiseen matalan kynnyksen ohjaus-, vertais- ja ryhmätoiminnalla Nurmeksessa ja Juuassa (Voimavarat käyttöön) (56 000 €)</t>
         </is>
       </c>
     </row>
@@ -24838,7 +25671,7 @@
       </c>
       <c r="I649" t="inlineStr" s="0">
         <is>
-          <t>Ak 3815: Ikääntyneiden osallisuuden ja hyvinvoinnin edistämiseen kohtaamispaikka-  ryhmä- ja yksilötoiminnan keinoin (Yhres-toiminta) (55 650 €)</t>
+          <t>Ak 3815: Ikääntyneiden osallisuuden ja hyvinvoinnin edistämiseen kohtaamispaikka-, ryhmä- ja yksilötoiminnan keinoin (Yhres-toiminta) (55 650 €)</t>
         </is>
       </c>
     </row>
@@ -24904,7 +25737,7 @@
       </c>
       <c r="I651" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Päihde- ja mielenterveyskuntoutujille  rikostaustaisille sekä muille sosiaalista vahvistamista tarvitseville henkilöille suunnattuun toimintakykyä lisäävään kohtaamispaikkatoimintaan (53 550 €)</t>
+          <t>Ak 1: Päihde- ja mielenterveyskuntoutujille, rikostaustaisille sekä muille sosiaalista vahvistamista tarvitseville henkilöille suunnattuun toimintakykyä lisäävään kohtaamispaikkatoimintaan (53 550 €)</t>
         </is>
       </c>
     </row>
@@ -24970,7 +25803,7 @@
       </c>
       <c r="I653" t="inlineStr" s="0">
         <is>
-          <t>Ak 12394: Yksinäisyyttä kokevien  syrjäytyneiden  eläkeläisten  mielenterveys- ja päihdekuntoutujien tai muusta syystä työelämän ulkopuolelle jääneiden kokonaisvaltaisen hyvinvoinnin edistämiseen kohtaamispaikkatoiminnan avulla (52 000 €)</t>
+          <t>Ak 12394: Yksinäisyyttä kokevien, syrjäytyneiden, eläkeläisten, mielenterveys- ja päihdekuntoutujien tai muusta syystä työelämän ulkopuolelle jääneiden kokonaisvaltaisen hyvinvoinnin edistämiseen kohtaamispaikkatoiminnan avulla (52 000 €)</t>
         </is>
       </c>
     </row>
@@ -25003,7 +25836,7 @@
       </c>
       <c r="I654" t="inlineStr" s="0">
         <is>
-          <t>Ak 4: Päihdeongelmaisten elämäntapamuutoksen tukemiseen vapaaehtoispohjaisella tukihenkilötoiminnalla  vertaistuella ja palveluohjauksella (51 000 €)</t>
+          <t>Ak 4: Päihdeongelmaisten elämäntapamuutoksen tukemiseen vapaaehtoispohjaisella tukihenkilötoiminnalla, vertaistuella ja palveluohjauksella (51 000 €)</t>
         </is>
       </c>
     </row>
@@ -25036,7 +25869,7 @@
       </c>
       <c r="I655" t="inlineStr" s="0">
         <is>
-          <t>Ak 1576: Näkövammaisten henkilöiden toimintakyvyn edistämiseen  itsenäisen arjessa suoriutumisen helpottamiseen ja tuntoaistin kehittämiseen kädentaitojen ja vertaistuen keinoin (50 864 €)</t>
+          <t>Ak 1576: Näkövammaisten henkilöiden toimintakyvyn edistämiseen, itsenäisen arjessa suoriutumisen helpottamiseen ja tuntoaistin kehittämiseen kädentaitojen ja vertaistuen keinoin (50 864 €)</t>
         </is>
       </c>
     </row>
@@ -25201,7 +26034,7 @@
       </c>
       <c r="I660" t="inlineStr" s="0">
         <is>
-          <t>Ak 1: Päihde- ja mielenterveyskuntoutujille sekä muille erityisen haasteellisessa elämäntilanteessa oleville kohderyhmille suunnattuun tukeen elämänhallinnan ja omaehtoisen suoriutumisen edistämiseksi yksilötuen  ryhmätoiminnan  palveluohjauksen ja asumisen tuen avulla (46 200 €)</t>
+          <t>Ak 1: Päihde- ja mielenterveyskuntoutujille sekä muille erityisen haasteellisessa elämäntilanteessa oleville kohderyhmille suunnattuun tukeen elämänhallinnan ja omaehtoisen suoriutumisen edistämiseksi yksilötuen, ryhmätoiminnan, palveluohjauksen ja asumisen tuen avulla (46 200 €)</t>
         </is>
       </c>
     </row>
@@ -25234,7 +26067,7 @@
       </c>
       <c r="I661" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Narkolepsiaa ja muita unihäiriöitä sairastavien ja heidän läheistensä yhdistyksen toimintaan  vertaistukeen ja teemakursseihin  joilla tarjotaan voimavaroja elämään sairauden kanssa (44 894 €)</t>
+          <t>Ak 2: Narkolepsiaa ja muita unihäiriöitä sairastavien ja heidän läheistensä yhdistyksen toimintaan, vertaistukeen ja teemakursseihin, joilla tarjotaan voimavaroja elämään sairauden kanssa (44 894 €)</t>
         </is>
       </c>
     </row>
@@ -25267,7 +26100,7 @@
       </c>
       <c r="I662" t="inlineStr" s="0">
         <is>
-          <t>Ak 9564: A- ja B-hemofiliaa  von Willebrandin tautia ja muita harvinaisia verenvuototauteja sairastavien henkilöiden  taudin kantajien ja heidän perheidensä hyvinvoinnin tukemiseen. Toimintamuotoina vertaistuki  tapahtumat  tiedottaminen  neuvonta  koulutus sekä yhdistyksen kokoukset. (43 733 €)</t>
+          <t>Ak 9564: A- ja B-hemofiliaa, von Willebrandin tautia ja muita harvinaisia verenvuototauteja sairastavien henkilöiden, taudin kantajien ja heidän perheidensä hyvinvoinnin tukemiseen. Toimintamuotoina vertaistuki, tapahtumat, tiedottaminen, neuvonta, koulutus sekä yhdistyksen kokoukset. (43 733 €)</t>
         </is>
       </c>
     </row>
@@ -25399,7 +26232,7 @@
       </c>
       <c r="I666" t="inlineStr" s="0">
         <is>
-          <t>Ak 1120: Näkövammaisten itsenäisen elämän tukemiseen ja osallisuuden edistämiseen vertaistuen  ryhmätoiminnan ja saavutettavan tiedon avulla Etelä-Savossa (41 600 €)</t>
+          <t>Ak 1120: Näkövammaisten itsenäisen elämän tukemiseen ja osallisuuden edistämiseen vertaistuen, ryhmätoiminnan ja saavutettavan tiedon avulla Etelä-Savossa (41 600 €)</t>
         </is>
       </c>
     </row>
@@ -25564,7 +26397,7 @@
       </c>
       <c r="I671" t="inlineStr" s="0">
         <is>
-          <t>Ak 2: Työttömien työelämävalmiuksien ja toimintakyvyn vahvistamiseen matalan kynnyksen ohjaus-  neuvonta-  vertaistuki- ja ryhmätoiminnoilla Salossa (34 000 €)</t>
+          <t>Ak 2: Työttömien työelämävalmiuksien ja toimintakyvyn vahvistamiseen matalan kynnyksen ohjaus-, neuvonta-, vertaistuki- ja ryhmätoiminnoilla Salossa (34 000 €)</t>
         </is>
       </c>
     </row>
@@ -25597,7 +26430,7 @@
       </c>
       <c r="I672" t="inlineStr" s="0">
         <is>
-          <t>Ak 9866: Änkytyksen aiheuttamien haittojen vähentämiseen tarjoamalla änkyttäjille ja heidän läheisilleen vertaistukea  tietoa änkytyksestä sekä apua änkytykseen liittyvien negatiivisten ilmiöiden käsittelyyn vertaistuen  erilaisten teemaluentojen sekä vertaistuellisten työpajojen avulla. Änkytykseen liittyvien negatiivisten stereotypioiden purkamiseen ja erilaisia puhetapoja hyväksyvän yhteiskunnan edistämiseen. (32 970 €)</t>
+          <t>Ak 9866: Änkytyksen aiheuttamien haittojen vähentämiseen tarjoamalla änkyttäjille ja heidän läheisilleen vertaistukea, tietoa änkytyksestä sekä apua änkytykseen liittyvien negatiivisten ilmiöiden käsittelyyn vertaistuen, erilaisten teemaluentojen sekä vertaistuellisten työpajojen avulla. Änkytykseen liittyvien negatiivisten stereotypioiden purkamiseen ja erilaisia puhetapoja hyväksyvän yhteiskunnan edistämiseen. (32 970 €)</t>
         </is>
       </c>
     </row>
@@ -25630,8 +26463,7 @@
       </c>
       <c r="I673" t="inlineStr" s="0">
         <is>
-          <t>Ak 2006: Erityistä tukea tarvitsevien romaninuorten elämänhallinnan parantamiseen yksilöllisen ohjauksen ja vertaisryhmätoiminnan sekä vanhemmille tarjotun neuvonnan avulla Jyväskylässä ja Muuramessa.
-(Valoa Huomiseen -toiminta) (31 800 €)</t>
+          <t>Ak 2006: Erityistä tukea tarvitsevien romaninuorten elämänhallinnan parantamiseen yksilöllisen ohjauksen ja vertaisryhmätoiminnan sekä vanhemmille tarjotun neuvonnan avulla Jyväskylässä ja Muuramessa. (Valoa Huomiseen -toiminta) (31 800 €)</t>
         </is>
       </c>
     </row>
@@ -25730,7 +26562,7 @@
       </c>
       <c r="I676" t="inlineStr" s="0">
         <is>
-          <t>Ak 12278: För att främja välbefinnandet och minska ensamheten bland seniorer som fyllt 70 år genom klientstyrning  uppsökande metoder samt individuell verksamhet och gruppverksamhet (Kultur i hemmet/ Kulttuuria kodissa) (26 000 €)</t>
+          <t>Ak 12278: För att främja välbefinnandet och minska ensamheten bland seniorer som fyllt 70 år genom klientstyrning, uppsökande metoder samt individuell verksamhet och gruppverksamhet (Kultur i hemmet/ Kulttuuria kodissa) (26 000 €)</t>
         </is>
       </c>
     </row>
@@ -25829,7 +26661,7 @@
       </c>
       <c r="I679" t="inlineStr" s="0">
         <is>
-          <t>Ak 7677: Suomesta tilapäistä suojelua ja turvaa hakevien kotimajoituksen  osallisuuden ja kaksisuuntaisen kotoutumisen edistämiseen kotimajoitusverkostoa koordinoimalla  vapaaehtoistoiminnalla  neuvonnalla ja yksilöohjauksella sekä järjestö- ja viranomaisyhteistyöllä (23 000 €)</t>
+          <t>Ak 7677: Suomesta tilapäistä suojelua ja turvaa hakevien kotimajoituksen, osallisuuden ja kaksisuuntaisen kotoutumisen edistämiseen kotimajoitusverkostoa koordinoimalla, vapaaehtoistoiminnalla, neuvonnalla ja yksilöohjauksella sekä järjestö- ja viranomaisyhteistyöllä (23 000 €)</t>
         </is>
       </c>
     </row>

--- a/dist/VM_Tukipalkkio_Leikkuri_2027.xlsx
+++ b/dist/VM_Tukipalkkio_Leikkuri_2027.xlsx
@@ -6,7 +6,7 @@
     <sheet name="02_Yritystuet_Verovertailu" sheetId="2" r:id="rId2"/>
     <sheet name="03_Tukikonsortiot_ja_Klusterit" sheetId="3" r:id="rId3"/>
     <sheet name="04_STEA_OKM_Suurimmat_Kohteet" sheetId="4" r:id="rId4"/>
-    <sheet name="05_Tilinpaatos_Vale_EBITDA" sheetId="5" r:id="rId5"/>
+    <sheet name="05_Tilinpaatos_IAS20_Oikaisu" sheetId="5" r:id="rId5"/>
     <sheet name="06_STEA_2026_Kaikki_686_Jarj" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
@@ -208,12 +208,12 @@
     <row r="5">
       <c r="A5" t="inlineStr" s="0">
         <is>
-          <t>33.90.50</t>
+          <t>33.90.50 (sekä kuntien/HVA sote-avustukset)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="0">
         <is>
-          <t>Avustukset yhteisöille ja säätiöille terveyden ja sos. hyvinvoinnin edistämiseen (STEA)</t>
+          <t>STEA-järjestöavustukset (273,9 M€ v. 2026) sekä muut julkiset sote-järjestötuet (~136 M€)</t>
         </is>
       </c>
       <c r="C5" s="2">
@@ -389,12 +389,12 @@
       </c>
       <c r="H1" t="inlineStr" s="1">
         <is>
-          <t>Yhteisöveron muutos 5v (€)</t>
+          <t>Maksettu yhteisövero 5v (€)</t>
         </is>
       </c>
       <c r="I1" t="inlineStr" s="1">
         <is>
-          <t>Tuettoman verrokin verokasvu 5v (€)</t>
+          <t>Vertailutaso ilman tukea 5v (€)</t>
         </is>
       </c>
       <c r="J1" t="inlineStr" s="1">
@@ -441,7 +441,7 @@
       </c>
       <c r="E2" t="inlineStr" s="0">
         <is>
-          <t>Business_Finland</t>
+          <t>Business Finland (T&amp;K-avustus)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr" s="0">
@@ -463,7 +463,7 @@
       </c>
       <c r="K2" t="inlineStr" s="0">
         <is>
-          <t>BLACKLIST_ZOMBIE</t>
+          <t>Pilottivaihe / 0 € yhteisöveroa (100 % karsinta)</t>
         </is>
       </c>
       <c r="L2" s="2">
@@ -498,12 +498,12 @@
       </c>
       <c r="E3" t="inlineStr" s="0">
         <is>
-          <t>MMM_Energy</t>
+          <t>TEM / Energiatuki &amp; sähköistämistuki</t>
         </is>
       </c>
       <c r="F3" t="inlineStr" s="0">
         <is>
-          <t>30.10.40_32.60.40</t>
+          <t>32.20.43 / 32.60.40</t>
         </is>
       </c>
       <c r="G3" s="2">
@@ -520,7 +520,7 @@
       </c>
       <c r="K3" t="inlineStr" s="0">
         <is>
-          <t>BLACKLIST_ZOMBIE</t>
+          <t>Pilottivaihe / 0 € yhteisöveroa (100 % karsinta)</t>
         </is>
       </c>
       <c r="L3" s="2">
@@ -555,7 +555,7 @@
       </c>
       <c r="E4" t="inlineStr" s="0">
         <is>
-          <t>Business_Finland</t>
+          <t>Business Finland (T&amp;K-avustus)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr" s="0">
@@ -577,7 +577,7 @@
       </c>
       <c r="K4" t="inlineStr" s="0">
         <is>
-          <t>BLACKLIST_ZOMBIE</t>
+          <t>Pilottivaihe / 0 € yhteisöveroa (100 % karsinta)</t>
         </is>
       </c>
       <c r="L4" s="2">
@@ -612,7 +612,7 @@
       </c>
       <c r="E5" t="inlineStr" s="0">
         <is>
-          <t>Business_Finland</t>
+          <t>Business Finland (T&amp;K-avustus)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr" s="0">
@@ -634,7 +634,7 @@
       </c>
       <c r="K5" t="inlineStr" s="0">
         <is>
-          <t>BLACKLIST_ZOMBIE</t>
+          <t>Pilottivaihe / 0 € yhteisöveroa (100 % karsinta)</t>
         </is>
       </c>
       <c r="L5" s="2">
@@ -669,7 +669,7 @@
       </c>
       <c r="E6" t="inlineStr" s="0">
         <is>
-          <t>Business_Finland</t>
+          <t>Business Finland (T&amp;K-avustus)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr" s="0">
@@ -691,7 +691,7 @@
       </c>
       <c r="K6" t="inlineStr" s="0">
         <is>
-          <t>BLACKLIST_ZOMBIE</t>
+          <t>Pilottivaihe / 0 € yhteisöveroa (100 % karsinta)</t>
         </is>
       </c>
       <c r="L6" s="2">
@@ -726,7 +726,7 @@
       </c>
       <c r="E7" t="inlineStr" s="0">
         <is>
-          <t>ELY</t>
+          <t>ELY / Traficom (Yritys- ja merenkulkutuki)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr" s="0">
@@ -748,7 +748,7 @@
       </c>
       <c r="K7" t="inlineStr" s="0">
         <is>
-          <t>BLACKLIST_ZOMBIE</t>
+          <t>Pilottivaihe / 0 € yhteisöveroa (100 % karsinta)</t>
         </is>
       </c>
       <c r="L7" s="2">
@@ -783,7 +783,7 @@
       </c>
       <c r="E8" t="inlineStr" s="0">
         <is>
-          <t>Business_Finland_Loan</t>
+          <t>Business Finland (T&amp;K-laina)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr" s="0">
@@ -805,7 +805,7 @@
       </c>
       <c r="K8" t="inlineStr" s="0">
         <is>
-          <t>BLACKLIST_ZOMBIE</t>
+          <t>Pilottivaihe / 0 € yhteisöveroa (100 % karsinta)</t>
         </is>
       </c>
       <c r="L8" s="2">
@@ -840,7 +840,7 @@
       </c>
       <c r="E9" t="inlineStr" s="0">
         <is>
-          <t>Business_Finland</t>
+          <t>Business Finland (T&amp;K-avustus)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr" s="0">
@@ -862,7 +862,7 @@
       </c>
       <c r="K9" t="inlineStr" s="0">
         <is>
-          <t>BLACKLIST_ZOMBIE</t>
+          <t>Pilottivaihe / 0 € yhteisöveroa (100 % karsinta)</t>
         </is>
       </c>
       <c r="L9" s="2">
@@ -897,7 +897,7 @@
       </c>
       <c r="E10" t="inlineStr" s="0">
         <is>
-          <t>Business_Finland</t>
+          <t>Business Finland (T&amp;K-avustus)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="0">
@@ -919,7 +919,7 @@
       </c>
       <c r="K10" t="inlineStr" s="0">
         <is>
-          <t>BLACKLIST_ZOMBIE</t>
+          <t>Pilottivaihe / 0 € yhteisöveroa (100 % karsinta)</t>
         </is>
       </c>
       <c r="L10" s="2">
@@ -954,7 +954,7 @@
       </c>
       <c r="E11" t="inlineStr" s="0">
         <is>
-          <t>Business_Finland</t>
+          <t>Business Finland (T&amp;K-avustus)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr" s="0">
@@ -976,7 +976,7 @@
       </c>
       <c r="K11" t="inlineStr" s="0">
         <is>
-          <t>BLACKLIST_ZOMBIE</t>
+          <t>Pilottivaihe / 0 € yhteisöveroa (100 % karsinta)</t>
         </is>
       </c>
       <c r="L11" s="2">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E12" t="inlineStr" s="0">
         <is>
-          <t>Business_Finland</t>
+          <t>Business Finland (T&amp;K-avustus)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr" s="0">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="K12" t="inlineStr" s="0">
         <is>
-          <t>BLACKLIST_ZOMBIE</t>
+          <t>Pilottivaihe / 0 € yhteisöveroa (100 % karsinta)</t>
         </is>
       </c>
       <c r="L12" s="2">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="M12" t="inlineStr" s="0">
         <is>
-          <t>NONE</t>
+          <t>Ei klusteria</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="E13" t="inlineStr" s="0">
         <is>
-          <t>Business_Finland</t>
+          <t>Business Finland (T&amp;K-avustus)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr" s="0">
@@ -1080,17 +1080,17 @@
         <v>3850000.0</v>
       </c>
       <c r="H13" s="2">
-        <v>420000.0</v>
+        <v>2100000.0</v>
       </c>
       <c r="I13" s="2">
-        <v>680000.0</v>
+        <v>2350000.0</v>
       </c>
       <c r="J13" s="2">
-        <v>-0.07</v>
+        <v>-0.06</v>
       </c>
       <c r="K13" t="inlineStr" s="0">
         <is>
-          <t>DEADWEIGHT_CROWD_OUT</t>
+          <t>Säilyttävä tuki / Matala lisäisyys (100 % karsinta)</t>
         </is>
       </c>
       <c r="L13" s="2">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B14" t="inlineStr" s="0">
         <is>
-          <t>Valmet Oyj (Keilasatama 5 — Business Finland Beyond Circularity Veturi &amp; teollisuuden T&amp;K-tuet)</t>
+          <t>Valmet Oyj (Keilasatama 5 — Business Finland Beyond Circularity Veturi — ~195 milj. € yhteisöveroa Suomeen 5v)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="0">
         <is>
-          <t>70100</t>
+          <t>28990</t>
         </is>
       </c>
       <c r="D14" t="inlineStr" s="0">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="E14" t="inlineStr" s="0">
         <is>
-          <t>Business_Finland</t>
+          <t>Business Finland (T&amp;K-avustus)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr" s="0">
@@ -1137,21 +1137,21 @@
         <v>24500000.0</v>
       </c>
       <c r="H14" s="2">
-        <v>4800000.0</v>
+        <v>195000000.0</v>
       </c>
       <c r="I14" s="2">
-        <v>19500000.0</v>
+        <v>145000000.0</v>
       </c>
       <c r="J14" s="2">
-        <v>-0.6</v>
+        <v>2.04</v>
       </c>
       <c r="K14" t="inlineStr" s="0">
         <is>
-          <t>DEADWEIGHT_CROWD_OUT</t>
+          <t>Vahva verovaste / T&amp;K-veturi (Säilytetään)</t>
         </is>
       </c>
       <c r="L14" s="2">
-        <v>24500000.0</v>
+        <v>0.0</v>
       </c>
       <c r="M14" t="inlineStr" s="0">
         <is>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="B15" t="inlineStr" s="0">
         <is>
-          <t>UPM-Kymmene Oyj (TEM 2020–2025 suurin suora yritystukisaaja 140 M€: teollisuuden sähköistämistuki, energiatuet &amp; BF)</t>
+          <t>UPM-Kymmene Oyj (TEM 2020–2025 suurin suora yritystukisaaja 140 M€: sähköistämis- ja energiatuet — matala lisäisyys VATT/Etla-arvioissa)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="0">
@@ -1182,29 +1182,29 @@
       </c>
       <c r="E15" t="inlineStr" s="0">
         <is>
-          <t>MMM_Energy</t>
+          <t>TEM / Energiatuki &amp; sähköistämistuki</t>
         </is>
       </c>
       <c r="F15" t="inlineStr" s="0">
         <is>
-          <t>30.10.40_32.60.40</t>
+          <t>32.20.43 / 32.60.40</t>
         </is>
       </c>
       <c r="G15" s="2">
         <v>140000000.0</v>
       </c>
       <c r="H15" s="2">
-        <v>38000000.0</v>
+        <v>620000000.0</v>
       </c>
       <c r="I15" s="2">
-        <v>45000000.0</v>
+        <v>610000000.0</v>
       </c>
       <c r="J15" s="2">
-        <v>-0.05</v>
+        <v>0.07</v>
       </c>
       <c r="K15" t="inlineStr" s="0">
         <is>
-          <t>DEADWEIGHT_CROWD_OUT</t>
+          <t>Säilyttävä tuki / Matala lisäisyys (100 % karsinta)</t>
         </is>
       </c>
       <c r="L15" s="2">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="M15" t="inlineStr" s="0">
         <is>
-          <t>NONE</t>
+          <t>Ei klusteria</t>
         </is>
       </c>
     </row>
@@ -1239,29 +1239,29 @@
       </c>
       <c r="E16" t="inlineStr" s="0">
         <is>
-          <t>MMM_Energy</t>
+          <t>TEM / Energiatuki &amp; sähköistämistuki</t>
         </is>
       </c>
       <c r="F16" t="inlineStr" s="0">
         <is>
-          <t>30.10.40_32.60.40</t>
+          <t>32.20.43 / 32.60.40</t>
         </is>
       </c>
       <c r="G16" s="2">
         <v>96000000.0</v>
       </c>
       <c r="H16" s="2">
-        <v>22000000.0</v>
+        <v>185000000.0</v>
       </c>
       <c r="I16" s="2">
-        <v>45000000.0</v>
+        <v>180000000.0</v>
       </c>
       <c r="J16" s="2">
-        <v>-0.24</v>
+        <v>0.05</v>
       </c>
       <c r="K16" t="inlineStr" s="0">
         <is>
-          <t>DEADWEIGHT_CROWD_OUT</t>
+          <t>Säilyttävä tuki / Matala lisäisyys (100 % karsinta)</t>
         </is>
       </c>
       <c r="L16" s="2">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="M16" t="inlineStr" s="0">
         <is>
-          <t>NONE</t>
+          <t>Ei klusteria</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="B17" t="inlineStr" s="0">
         <is>
-          <t>Neste Oyj (Business Finland Veturi &amp; puhtaan siirtymän investointi- ja energiatuet)</t>
+          <t>Neste Oyj (Puhtaan siirtymän investointi- ja energiatuet sekä Veturi — suuri veronmaksaja, mutta suorilla energiatuilla matala lisäisyys)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="0">
@@ -1296,29 +1296,29 @@
       </c>
       <c r="E17" t="inlineStr" s="0">
         <is>
-          <t>MMM_Energy</t>
+          <t>TEM / Energiatuki &amp; sähköistämistuki</t>
         </is>
       </c>
       <c r="F17" t="inlineStr" s="0">
         <is>
-          <t>30.10.40_32.60.40</t>
+          <t>32.20.43 / 32.60.40</t>
         </is>
       </c>
       <c r="G17" s="2">
         <v>68500000.0</v>
       </c>
       <c r="H17" s="2">
-        <v>18000000.0</v>
+        <v>680000000.0</v>
       </c>
       <c r="I17" s="2">
-        <v>32000000.0</v>
+        <v>670000000.0</v>
       </c>
       <c r="J17" s="2">
-        <v>-0.2</v>
+        <v>0.15</v>
       </c>
       <c r="K17" t="inlineStr" s="0">
         <is>
-          <t>DEADWEIGHT_CROWD_OUT</t>
+          <t>Säilyttävä tuki / Matala lisäisyys (100 % karsinta)</t>
         </is>
       </c>
       <c r="L17" s="2">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="M17" t="inlineStr" s="0">
         <is>
-          <t>NONE</t>
+          <t>Ei klusteria</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B18" t="inlineStr" s="0">
         <is>
-          <t>SSAB Europe Oy (Raahen terästehtaan energia- ja vihreän siirtymän investointituet)</t>
+          <t>SSAB Europe Oy (Raahen terästehtaan energia- ja vihreän siirtymän investointituet — matala lisäisyys)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="0">
@@ -1353,29 +1353,29 @@
       </c>
       <c r="E18" t="inlineStr" s="0">
         <is>
-          <t>MMM_Energy</t>
+          <t>TEM / Energiatuki &amp; sähköistämistuki</t>
         </is>
       </c>
       <c r="F18" t="inlineStr" s="0">
         <is>
-          <t>30.10.40_32.60.40</t>
+          <t>32.20.43 / 32.60.40</t>
         </is>
       </c>
       <c r="G18" s="2">
         <v>48000000.0</v>
       </c>
       <c r="H18" s="2">
-        <v>9500000.0</v>
+        <v>115000000.0</v>
       </c>
       <c r="I18" s="2">
-        <v>24000000.0</v>
+        <v>110000000.0</v>
       </c>
       <c r="J18" s="2">
-        <v>-0.3</v>
+        <v>0.1</v>
       </c>
       <c r="K18" t="inlineStr" s="0">
         <is>
-          <t>DEADWEIGHT_CROWD_OUT</t>
+          <t>Säilyttävä tuki / Matala lisäisyys (100 % karsinta)</t>
         </is>
       </c>
       <c r="L18" s="2">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="M18" t="inlineStr" s="0">
         <is>
-          <t>NONE</t>
+          <t>Ei klusteria</t>
         </is>
       </c>
     </row>
@@ -1395,12 +1395,12 @@
       </c>
       <c r="B19" t="inlineStr" s="0">
         <is>
-          <t>Outokumpu Oyj (Energiaintensiivisen teollisuuden sähköistämis- ja energiatuet)</t>
+          <t>Outokumpu Oyj (Energiaintensiivisen teollisuuden sähköistämis- ja energiatuet — matala lisäisyys VATT/Etla-arvioissa)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="0">
         <is>
-          <t>64210</t>
+          <t>24100</t>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="0">
@@ -1410,29 +1410,29 @@
       </c>
       <c r="E19" t="inlineStr" s="0">
         <is>
-          <t>MMM_Energy</t>
+          <t>TEM / Energiatuki &amp; sähköistämistuki</t>
         </is>
       </c>
       <c r="F19" t="inlineStr" s="0">
         <is>
-          <t>30.10.40_32.60.40</t>
+          <t>32.20.43 / 32.60.40</t>
         </is>
       </c>
       <c r="G19" s="2">
         <v>62000000.0</v>
       </c>
       <c r="H19" s="2">
-        <v>11000000.0</v>
+        <v>140000000.0</v>
       </c>
       <c r="I19" s="2">
-        <v>26000000.0</v>
+        <v>135000000.0</v>
       </c>
       <c r="J19" s="2">
-        <v>-0.24</v>
+        <v>0.08</v>
       </c>
       <c r="K19" t="inlineStr" s="0">
         <is>
-          <t>DEADWEIGHT_CROWD_OUT</t>
+          <t>Säilyttävä tuki / Matala lisäisyys (100 % karsinta)</t>
         </is>
       </c>
       <c r="L19" s="2">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="M19" t="inlineStr" s="0">
         <is>
-          <t>NONE</t>
+          <t>Ei klusteria</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="B20" t="inlineStr" s="0">
         <is>
-          <t>Meyer Turku Oy (Business Finland NEcOLEAP Veturi 20 M€ &amp; TEM meriteollisuuden innovaatiotuet — 0 € yhteisöveroa)</t>
+          <t>Meyer Turku Oy (Business Finland NEcOLEAP Veturi 20 M€ &amp; TEM meriteollisuuden innovaatiotuet — 0 € yhteisöveroa tarkastelujaksolla)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="0">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="E20" t="inlineStr" s="0">
         <is>
-          <t>Business_Finland</t>
+          <t>Business Finland (T&amp;K-avustus)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr" s="0">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="K20" t="inlineStr" s="0">
         <is>
-          <t>BLACKLIST_ZOMBIE</t>
+          <t>Pilottivaihe / 0 € yhteisöveroa (100 % karsinta)</t>
         </is>
       </c>
       <c r="L20" s="2">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="M20" t="inlineStr" s="0">
         <is>
-          <t>NONE</t>
+          <t>Ei klusteria</t>
         </is>
       </c>
     </row>
@@ -1524,29 +1524,29 @@
       </c>
       <c r="E21" t="inlineStr" s="0">
         <is>
-          <t>ELY</t>
+          <t>ELY / Traficom (Yritys- ja merenkulkutuki)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr" s="0">
         <is>
-          <t>32.30.42</t>
+          <t>31.20.43</t>
         </is>
       </c>
       <c r="G21" s="2">
         <v>129000000.0</v>
       </c>
       <c r="H21" s="2">
-        <v>4200000.0</v>
+        <v>18000000.0</v>
       </c>
       <c r="I21" s="2">
-        <v>18000000.0</v>
+        <v>22000000.0</v>
       </c>
       <c r="J21" s="2">
-        <v>-0.11</v>
+        <v>-0.03</v>
       </c>
       <c r="K21" t="inlineStr" s="0">
         <is>
-          <t>DEADWEIGHT_CROWD_OUT</t>
+          <t>Säilyttävä tuki / Matala lisäisyys (100 % karsinta)</t>
         </is>
       </c>
       <c r="L21" s="2">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M21" t="inlineStr" s="0">
         <is>
-          <t>NONE</t>
+          <t>Ei klusteria</t>
         </is>
       </c>
     </row>
@@ -1581,29 +1581,29 @@
       </c>
       <c r="E22" t="inlineStr" s="0">
         <is>
-          <t>ELY</t>
+          <t>ELY / Traficom (Yritys- ja merenkulkutuki)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr" s="0">
         <is>
-          <t>32.30.42</t>
+          <t>31.20.43</t>
         </is>
       </c>
       <c r="G22" s="2">
         <v>71000000.0</v>
       </c>
       <c r="H22" s="2">
-        <v>1500000.0</v>
+        <v>6500000.0</v>
       </c>
       <c r="I22" s="2">
         <v>18000000.0</v>
       </c>
       <c r="J22" s="2">
-        <v>-0.23</v>
+        <v>-0.16</v>
       </c>
       <c r="K22" t="inlineStr" s="0">
         <is>
-          <t>DEADWEIGHT_CROWD_OUT</t>
+          <t>Säilyttävä tuki / Matala lisäisyys (100 % karsinta)</t>
         </is>
       </c>
       <c r="L22" s="2">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="M22" t="inlineStr" s="0">
         <is>
-          <t>NONE</t>
+          <t>Ei klusteria</t>
         </is>
       </c>
     </row>
@@ -1638,29 +1638,29 @@
       </c>
       <c r="E23" t="inlineStr" s="0">
         <is>
-          <t>ELY</t>
+          <t>ELY / Traficom (Yritys- ja merenkulkutuki)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr" s="0">
         <is>
-          <t>32.30.42</t>
+          <t>31.20.43</t>
         </is>
       </c>
       <c r="G23" s="2">
         <v>93000000.0</v>
       </c>
       <c r="H23" s="2">
-        <v>8500000.0</v>
+        <v>24000000.0</v>
       </c>
       <c r="I23" s="2">
-        <v>22000000.0</v>
+        <v>28000000.0</v>
       </c>
       <c r="J23" s="2">
-        <v>-0.15</v>
+        <v>-0.04</v>
       </c>
       <c r="K23" t="inlineStr" s="0">
         <is>
-          <t>DEADWEIGHT_CROWD_OUT</t>
+          <t>Säilyttävä tuki / Matala lisäisyys (100 % karsinta)</t>
         </is>
       </c>
       <c r="L23" s="2">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="M23" t="inlineStr" s="0">
         <is>
-          <t>NONE</t>
+          <t>Ei klusteria</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       </c>
       <c r="B24" t="inlineStr" s="0">
         <is>
-          <t>Fortum Oyj (Business Finland ExpandFibre Veturi, energia- ja vetyhankeavustukset)</t>
+          <t>Fortum Oyj (Energia- ja vetyhankeavustukset sekä ExpandFibre — suuri veronmaksaja, mutta suorilla energiatuilla matala lisäisyys)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="0">
         <is>
-          <t>70100</t>
+          <t>35110</t>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="0">
@@ -1695,29 +1695,29 @@
       </c>
       <c r="E24" t="inlineStr" s="0">
         <is>
-          <t>MMM_Energy</t>
+          <t>TEM / Energiatuki &amp; sähköistämistuki</t>
         </is>
       </c>
       <c r="F24" t="inlineStr" s="0">
         <is>
-          <t>30.10.40_32.60.40</t>
+          <t>32.20.43 / 32.60.40</t>
         </is>
       </c>
       <c r="G24" s="2">
         <v>34000000.0</v>
       </c>
       <c r="H24" s="2">
-        <v>12000000.0</v>
+        <v>480000000.0</v>
       </c>
       <c r="I24" s="2">
-        <v>25000000.0</v>
+        <v>475000000.0</v>
       </c>
       <c r="J24" s="2">
-        <v>-0.38</v>
+        <v>0.15</v>
       </c>
       <c r="K24" t="inlineStr" s="0">
         <is>
-          <t>DEADWEIGHT_CROWD_OUT</t>
+          <t>Säilyttävä tuki / Matala lisäisyys (100 % karsinta)</t>
         </is>
       </c>
       <c r="L24" s="2">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="M24" t="inlineStr" s="0">
         <is>
-          <t>NONE</t>
+          <t>Ei klusteria</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="B25" t="inlineStr" s="0">
         <is>
-          <t>Metsä Fibre Oy / Metsä Group (ExpandFibre Veturi sekä biotuotetehtaiden energia- ja investointituet)</t>
+          <t>Metsä Fibre Oy / Metsä Group (ExpandFibre sekä biotuotetehtaiden energia- ja sähköistämistuet — matala lisäisyys)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="0">
@@ -1752,29 +1752,29 @@
       </c>
       <c r="E25" t="inlineStr" s="0">
         <is>
-          <t>MMM_Energy</t>
+          <t>TEM / Energiatuki &amp; sähköistämistuki</t>
         </is>
       </c>
       <c r="F25" t="inlineStr" s="0">
         <is>
-          <t>30.10.40_32.60.40</t>
+          <t>32.20.43 / 32.60.40</t>
         </is>
       </c>
       <c r="G25" s="2">
         <v>44000000.0</v>
       </c>
       <c r="H25" s="2">
-        <v>14000000.0</v>
+        <v>390000000.0</v>
       </c>
       <c r="I25" s="2">
-        <v>28000000.0</v>
+        <v>385000000.0</v>
       </c>
       <c r="J25" s="2">
-        <v>-0.32</v>
+        <v>0.11</v>
       </c>
       <c r="K25" t="inlineStr" s="0">
         <is>
-          <t>DEADWEIGHT_CROWD_OUT</t>
+          <t>Säilyttävä tuki / Matala lisäisyys (100 % karsinta)</t>
         </is>
       </c>
       <c r="L25" s="2">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="M25" t="inlineStr" s="0">
         <is>
-          <t>NONE</t>
+          <t>Ei klusteria</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B26" t="inlineStr" s="0">
         <is>
-          <t>Kemira Oyj (Teollisuuden energia-, sähköistämis- ja T&amp;K-avustukset)</t>
+          <t>Kemira Oyj (Teollisuuden energia- ja sähköistämistuet — kannattavan perusteollisuuden säilyttävä tuki)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="0">
@@ -1809,29 +1809,29 @@
       </c>
       <c r="E26" t="inlineStr" s="0">
         <is>
-          <t>MMM_Energy</t>
+          <t>TEM / Energiatuki &amp; sähköistämistuki</t>
         </is>
       </c>
       <c r="F26" t="inlineStr" s="0">
         <is>
-          <t>30.10.40_32.60.40</t>
+          <t>32.20.43 / 32.60.40</t>
         </is>
       </c>
       <c r="G26" s="2">
         <v>19500000.0</v>
       </c>
       <c r="H26" s="2">
-        <v>42000000.0</v>
+        <v>135000000.0</v>
       </c>
       <c r="I26" s="2">
-        <v>48000000.0</v>
+        <v>130000000.0</v>
       </c>
       <c r="J26" s="2">
-        <v>-0.31</v>
+        <v>0.26</v>
       </c>
       <c r="K26" t="inlineStr" s="0">
         <is>
-          <t>DEADWEIGHT_CROWD_OUT</t>
+          <t>Säilyttävä tuki / Matala lisäisyys (100 % karsinta)</t>
         </is>
       </c>
       <c r="L26" s="2">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="M26" t="inlineStr" s="0">
         <is>
-          <t>NONE</t>
+          <t>Ei klusteria</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B27" t="inlineStr" s="0">
         <is>
-          <t>Metso Oyj (Business Finland Veturi &amp; kaivosteknologian T&amp;K-tuet)</t>
+          <t>Metso Oyj (Business Finland Veturi &amp; kaivosteknologian T&amp;K-tuet — ~210 milj. € yhteisöveroa Suomeen 5v)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="0">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="E27" t="inlineStr" s="0">
         <is>
-          <t>Business_Finland</t>
+          <t>Business Finland (T&amp;K-avustus)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr" s="0">
@@ -1878,25 +1878,25 @@
         <v>21000000.0</v>
       </c>
       <c r="H27" s="2">
-        <v>58000000.0</v>
+        <v>210000000.0</v>
       </c>
       <c r="I27" s="2">
-        <v>65000000.0</v>
+        <v>155000000.0</v>
       </c>
       <c r="J27" s="2">
-        <v>-0.33</v>
+        <v>2.62</v>
       </c>
       <c r="K27" t="inlineStr" s="0">
         <is>
-          <t>DEADWEIGHT_CROWD_OUT</t>
+          <t>Vahva verovaste / T&amp;K-veturi (Säilytetään)</t>
         </is>
       </c>
       <c r="L27" s="2">
-        <v>21000000.0</v>
+        <v>0.0</v>
       </c>
       <c r="M27" t="inlineStr" s="0">
         <is>
-          <t>NONE</t>
+          <t>Ei klusteria</t>
         </is>
       </c>
     </row>
@@ -1923,12 +1923,12 @@
       </c>
       <c r="E28" t="inlineStr" s="0">
         <is>
-          <t>ELY</t>
+          <t>ELY / Traficom (Yritys- ja merenkulkutuki)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr" s="0">
         <is>
-          <t>32.30.42</t>
+          <t>31.20.20 / 32.30.42</t>
         </is>
       </c>
       <c r="G28" s="2">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="K28" t="inlineStr" s="0">
         <is>
-          <t>BLACKLIST_ZOMBIE</t>
+          <t>Pilottivaihe / 0 € yhteisöveroa (100 % karsinta)</t>
         </is>
       </c>
       <c r="L28" s="2">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="M28" t="inlineStr" s="0">
         <is>
-          <t>NONE</t>
+          <t>Ei klusteria</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="E29" t="inlineStr" s="0">
         <is>
-          <t>Business_Finland</t>
+          <t>Business Finland (T&amp;K-avustus)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr" s="0">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="K29" t="inlineStr" s="0">
         <is>
-          <t>POSITIVE_EXTERNALITY_KEEP</t>
+          <t>Vahva verovaste / T&amp;K-veturi (Säilytetään)</t>
         </is>
       </c>
       <c r="L29" s="2">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="M29" t="inlineStr" s="0">
         <is>
-          <t>NONE</t>
+          <t>Ei klusteria</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="E30" t="inlineStr" s="0">
         <is>
-          <t>Business_Finland</t>
+          <t>Business Finland (T&amp;K-avustus)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr" s="0">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="K30" t="inlineStr" s="0">
         <is>
-          <t>POSITIVE_EXTERNALITY_KEEP</t>
+          <t>Vahva verovaste / T&amp;K-veturi (Säilytetään)</t>
         </is>
       </c>
       <c r="L30" s="2">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="M30" t="inlineStr" s="0">
         <is>
-          <t>NONE</t>
+          <t>Ei klusteria</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="E31" t="inlineStr" s="0">
         <is>
-          <t>Business_Finland</t>
+          <t>Business Finland (T&amp;K-avustus)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr" s="0">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="K31" t="inlineStr" s="0">
         <is>
-          <t>POSITIVE_EXTERNALITY_KEEP</t>
+          <t>Vahva verovaste / T&amp;K-veturi (Säilytetään)</t>
         </is>
       </c>
       <c r="L31" s="2">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="M31" t="inlineStr" s="0">
         <is>
-          <t>NONE</t>
+          <t>Ei klusteria</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="E32" t="inlineStr" s="0">
         <is>
-          <t>Business_Finland</t>
+          <t>Business Finland (T&amp;K-avustus)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr" s="0">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="K32" t="inlineStr" s="0">
         <is>
-          <t>POSITIVE_EXTERNALITY_KEEP</t>
+          <t>Vahva verovaste / T&amp;K-veturi (Säilytetään)</t>
         </is>
       </c>
       <c r="L32" s="2">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="M32" t="inlineStr" s="0">
         <is>
-          <t>NONE</t>
+          <t>Ei klusteria</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="E33" t="inlineStr" s="0">
         <is>
-          <t>Business_Finland</t>
+          <t>Business Finland (T&amp;K-avustus)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr" s="0">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="K33" t="inlineStr" s="0">
         <is>
-          <t>POSITIVE_EXTERNALITY_KEEP</t>
+          <t>Vahva verovaste / T&amp;K-veturi (Säilytetään)</t>
         </is>
       </c>
       <c r="L33" s="2">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="M33" t="inlineStr" s="0">
         <is>
-          <t>NONE</t>
+          <t>Ei klusteria</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="E34" t="inlineStr" s="0">
         <is>
-          <t>Business_Finland</t>
+          <t>Business Finland (T&amp;K-avustus)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr" s="0">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="K34" t="inlineStr" s="0">
         <is>
-          <t>POSITIVE_EXTERNALITY_KEEP</t>
+          <t>Vahva verovaste / T&amp;K-veturi (Säilytetään)</t>
         </is>
       </c>
       <c r="L34" s="2">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="M34" t="inlineStr" s="0">
         <is>
-          <t>NONE</t>
+          <t>Ei klusteria</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="E35" t="inlineStr" s="0">
         <is>
-          <t>Business_Finland</t>
+          <t>Business Finland (T&amp;K-avustus)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr" s="0">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="K35" t="inlineStr" s="0">
         <is>
-          <t>POSITIVE_EXTERNALITY_KEEP</t>
+          <t>Vahva verovaste / T&amp;K-veturi (Säilytetään)</t>
         </is>
       </c>
       <c r="L35" s="2">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="M35" t="inlineStr" s="0">
         <is>
-          <t>NONE</t>
+          <t>Ei klusteria</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="E36" t="inlineStr" s="0">
         <is>
-          <t>Business_Finland</t>
+          <t>Business Finland (T&amp;K-avustus)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr" s="0">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="K36" t="inlineStr" s="0">
         <is>
-          <t>POSITIVE_EXTERNALITY_KEEP</t>
+          <t>Vahva verovaste / T&amp;K-veturi (Säilytetään)</t>
         </is>
       </c>
       <c r="L36" s="2">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="M36" t="inlineStr" s="0">
         <is>
-          <t>NONE</t>
+          <t>Ei klusteria</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="E37" t="inlineStr" s="0">
         <is>
-          <t>Business_Finland</t>
+          <t>Business Finland (T&amp;K-avustus)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr" s="0">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="K37" t="inlineStr" s="0">
         <is>
-          <t>POSITIVE_EXTERNALITY_KEEP</t>
+          <t>Vahva verovaste / T&amp;K-veturi (Säilytetään)</t>
         </is>
       </c>
       <c r="L37" s="2">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="M37" t="inlineStr" s="0">
         <is>
-          <t>NONE</t>
+          <t>Ei klusteria</t>
         </is>
       </c>
     </row>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="E38" t="inlineStr" s="0">
         <is>
-          <t>Business_Finland</t>
+          <t>Business Finland (T&amp;K-avustus)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr" s="0">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="K38" t="inlineStr" s="0">
         <is>
-          <t>POSITIVE_EXTERNALITY_KEEP</t>
+          <t>Vahva verovaste / T&amp;K-veturi (Säilytetään)</t>
         </is>
       </c>
       <c r="L38" s="2">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="M38" t="inlineStr" s="0">
         <is>
-          <t>NONE</t>
+          <t>Ei klusteria</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E39" t="inlineStr" s="0">
         <is>
-          <t>EI_JULKISTA_YRITYSTUKEA</t>
+          <t>Markkinaehtoinen (Ei yritystukea)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr" s="0">
         <is>
-          <t>0_EUR_TUKEA</t>
+          <t>0 € tukea</t>
         </is>
       </c>
       <c r="G39" s="2">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="K39" t="inlineStr" s="0">
         <is>
-          <t>GOLD_STANDARD_PRIVATE_BENCHMARK</t>
+          <t>Markkinaehtoinen nettoveronmaksajaverrokki</t>
         </is>
       </c>
       <c r="L39" s="2">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="M39" t="inlineStr" s="0">
         <is>
-          <t>NETTOVERONMAKSAJA_VERROKKI</t>
+          <t>Nettoveronmaksajaverrokki</t>
         </is>
       </c>
     </row>
@@ -2607,12 +2607,12 @@
       </c>
       <c r="E40" t="inlineStr" s="0">
         <is>
-          <t>EI_JULKISTA_YRITYSTUKEA</t>
+          <t>Markkinaehtoinen (Ei yritystukea)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr" s="0">
         <is>
-          <t>0_EUR_TUKEA</t>
+          <t>0 € tukea</t>
         </is>
       </c>
       <c r="G40" s="2">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="K40" t="inlineStr" s="0">
         <is>
-          <t>GOLD_STANDARD_PRIVATE_BENCHMARK</t>
+          <t>Markkinaehtoinen nettoveronmaksajaverrokki</t>
         </is>
       </c>
       <c r="L40" s="2">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="M40" t="inlineStr" s="0">
         <is>
-          <t>NETTOVERONMAKSAJA_VERROKKI</t>
+          <t>Nettoveronmaksajaverrokki</t>
         </is>
       </c>
     </row>
@@ -2664,12 +2664,12 @@
       </c>
       <c r="E41" t="inlineStr" s="0">
         <is>
-          <t>EI_JULKISTA_YRITYSTUKEA</t>
+          <t>Markkinaehtoinen (Ei yritystukea)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr" s="0">
         <is>
-          <t>0_EUR_TUKEA</t>
+          <t>0 € tukea</t>
         </is>
       </c>
       <c r="G41" s="2">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="K41" t="inlineStr" s="0">
         <is>
-          <t>GOLD_STANDARD_PRIVATE_BENCHMARK</t>
+          <t>Markkinaehtoinen nettoveronmaksajaverrokki</t>
         </is>
       </c>
       <c r="L41" s="2">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="M41" t="inlineStr" s="0">
         <is>
-          <t>NETTOVERONMAKSAJA_VERROKKI</t>
+          <t>Nettoveronmaksajaverrokki</t>
         </is>
       </c>
     </row>
@@ -2721,12 +2721,12 @@
       </c>
       <c r="E42" t="inlineStr" s="0">
         <is>
-          <t>EI_JULKISTA_YRITYSTUKEA</t>
+          <t>Markkinaehtoinen (Ei yritystukea)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr" s="0">
         <is>
-          <t>0_EUR_TUKEA</t>
+          <t>0 € tukea</t>
         </is>
       </c>
       <c r="G42" s="2">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="K42" t="inlineStr" s="0">
         <is>
-          <t>GOLD_STANDARD_PRIVATE_BENCHMARK</t>
+          <t>Markkinaehtoinen nettoveronmaksajaverrokki</t>
         </is>
       </c>
       <c r="L42" s="2">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="M42" t="inlineStr" s="0">
         <is>
-          <t>NETTOVERONMAKSAJA_VERROKKI</t>
+          <t>Nettoveronmaksajaverrokki</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E43" t="inlineStr" s="0">
         <is>
-          <t>EI_JULKISTA_YRITYSTUKEA</t>
+          <t>Markkinaehtoinen (Ei yritystukea)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr" s="0">
         <is>
-          <t>0_EUR_TUKEA</t>
+          <t>0 € tukea</t>
         </is>
       </c>
       <c r="G43" s="2">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="K43" t="inlineStr" s="0">
         <is>
-          <t>GOLD_STANDARD_PRIVATE_BENCHMARK</t>
+          <t>Markkinaehtoinen nettoveronmaksajaverrokki</t>
         </is>
       </c>
       <c r="L43" s="2">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="M43" t="inlineStr" s="0">
         <is>
-          <t>NETTOVERONMAKSAJA_VERROKKI</t>
+          <t>Nettoveronmaksajaverrokki</t>
         </is>
       </c>
     </row>
@@ -2835,12 +2835,12 @@
       </c>
       <c r="E44" t="inlineStr" s="0">
         <is>
-          <t>EI_JULKISTA_YRITYSTUKEA</t>
+          <t>Markkinaehtoinen (Ei yritystukea)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr" s="0">
         <is>
-          <t>0_EUR_TUKEA</t>
+          <t>0 € tukea</t>
         </is>
       </c>
       <c r="G44" s="2">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="K44" t="inlineStr" s="0">
         <is>
-          <t>GOLD_STANDARD_PRIVATE_BENCHMARK</t>
+          <t>Markkinaehtoinen nettoveronmaksajaverrokki</t>
         </is>
       </c>
       <c r="L44" s="2">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M44" t="inlineStr" s="0">
         <is>
-          <t>NETTOVERONMAKSAJA_VERROKKI</t>
+          <t>Nettoveronmaksajaverrokki</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E45" t="inlineStr" s="0">
         <is>
-          <t>EI_JULKISTA_YRITYSTUKEA</t>
+          <t>Markkinaehtoinen (Ei yritystukea)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr" s="0">
         <is>
-          <t>0_EUR_TUKEA</t>
+          <t>0 € tukea</t>
         </is>
       </c>
       <c r="G45" s="2">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="K45" t="inlineStr" s="0">
         <is>
-          <t>GOLD_STANDARD_PRIVATE_BENCHMARK</t>
+          <t>Markkinaehtoinen nettoveronmaksajaverrokki</t>
         </is>
       </c>
       <c r="L45" s="2">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="M45" t="inlineStr" s="0">
         <is>
-          <t>NETTOVERONMAKSAJA_VERROKKI</t>
+          <t>Nettoveronmaksajaverrokki</t>
         </is>
       </c>
     </row>
@@ -2949,12 +2949,12 @@
       </c>
       <c r="E46" t="inlineStr" s="0">
         <is>
-          <t>EI_JULKISTA_YRITYSTUKEA</t>
+          <t>Markkinaehtoinen (Ei yritystukea)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr" s="0">
         <is>
-          <t>0_EUR_TUKEA</t>
+          <t>0 € tukea</t>
         </is>
       </c>
       <c r="G46" s="2">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="K46" t="inlineStr" s="0">
         <is>
-          <t>GOLD_STANDARD_PRIVATE_BENCHMARK</t>
+          <t>Markkinaehtoinen nettoveronmaksajaverrokki</t>
         </is>
       </c>
       <c r="L46" s="2">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M46" t="inlineStr" s="0">
         <is>
-          <t>NETTOVERONMAKSAJA_VERROKKI</t>
+          <t>Nettoveronmaksajaverrokki</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E47" t="inlineStr" s="0">
         <is>
-          <t>EI_JULKISTA_YRITYSTUKEA</t>
+          <t>Markkinaehtoinen (Ei yritystukea)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr" s="0">
         <is>
-          <t>0_EUR_TUKEA</t>
+          <t>0 € tukea</t>
         </is>
       </c>
       <c r="G47" s="2">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="K47" t="inlineStr" s="0">
         <is>
-          <t>GOLD_STANDARD_PRIVATE_BENCHMARK</t>
+          <t>Markkinaehtoinen nettoveronmaksajaverrokki</t>
         </is>
       </c>
       <c r="L47" s="2">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="M47" t="inlineStr" s="0">
         <is>
-          <t>NETTOVERONMAKSAJA_VERROKKI</t>
+          <t>Nettoveronmaksajaverrokki</t>
         </is>
       </c>
     </row>
@@ -3063,12 +3063,12 @@
       </c>
       <c r="E48" t="inlineStr" s="0">
         <is>
-          <t>EI_JULKISTA_YRITYSTUKEA</t>
+          <t>Markkinaehtoinen (Ei yritystukea)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr" s="0">
         <is>
-          <t>0_EUR_TUKEA</t>
+          <t>0 € tukea</t>
         </is>
       </c>
       <c r="G48" s="2">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="K48" t="inlineStr" s="0">
         <is>
-          <t>GOLD_STANDARD_PRIVATE_BENCHMARK</t>
+          <t>Markkinaehtoinen nettoveronmaksajaverrokki</t>
         </is>
       </c>
       <c r="L48" s="2">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="M48" t="inlineStr" s="0">
         <is>
-          <t>NETTOVERONMAKSAJA_VERROKKI</t>
+          <t>Nettoveronmaksajaverrokki</t>
         </is>
       </c>
     </row>
@@ -3119,7 +3119,7 @@
     <row r="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
-          <t>Klusteri-ID</t>
+          <t>Klusteritunniste</t>
         </is>
       </c>
       <c r="B1" t="inlineStr" s="1">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="G1" t="inlineStr" s="1">
         <is>
-          <t>Maksettu yhteisöveron muutos 5v (€)</t>
+          <t>Maksettu yhteisövero 5v (€)</t>
         </is>
       </c>
       <c r="H1" t="inlineStr" s="1">
@@ -3171,7 +3171,7 @@
     <row r="2">
       <c r="A2" t="inlineStr" s="0">
         <is>
-          <t>TUKI-RING-001</t>
+          <t>KLUSTERI-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="0">
@@ -3213,7 +3213,7 @@
     <row r="3">
       <c r="A3" t="inlineStr" s="0">
         <is>
-          <t>TUKI-RING-005</t>
+          <t>KLUSTERI-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="0">
@@ -3255,7 +3255,7 @@
     <row r="4">
       <c r="A4" t="inlineStr" s="0">
         <is>
-          <t>TUKI-RING-012</t>
+          <t>KLUSTERI-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="0">
@@ -3273,17 +3273,17 @@
       </c>
       <c r="E4" t="inlineStr" s="0">
         <is>
-          <t>Spinverse Oy (Innovaatio- ja EU/Veturi-ekosysteemikonsultointi — omat T&amp;K- ja kehittämisavustukset) | Valmet Oyj (Keilasatama 5 — Business Finland Beyond Circularity Veturi &amp; teollisuuden T&amp;K-tuet)</t>
+          <t>Spinverse Oy (Innovaatio- ja EU/Veturi-ekosysteemikonsultointi — omat T&amp;K- ja kehittämisavustukset) | Valmet Oyj (Keilasatama 5 — Business Finland Beyond Circularity Veturi — ~195 milj. € yhteisöveroa Suomeen 5v)</t>
         </is>
       </c>
       <c r="F4" s="2">
         <v>28350000.0</v>
       </c>
       <c r="G4" s="2">
-        <v>5220000.0</v>
+        <v>197100000.0</v>
       </c>
       <c r="H4" s="2">
-        <v>0.18</v>
+        <v>6.95</v>
       </c>
       <c r="I4" s="2">
         <v>5670000.0</v>
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="K2" s="2">
-        <v>1020600.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="3">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="B3" t="inlineStr" s="0">
         <is>
-          <t>Ehkäisevä päihdetyö EHYT ry (STEA 2026: 1,26 M€ Ay/C-avustusta + 2,87 M€ kohdennettua Ak-päihdekasvatusta)</t>
+          <t>Ehkäisevä päihdetyö EHYT ry (STEA 2026: 1,26 M€ Ay-yleisavustusta + 2,87 M€ kohdennettua Ak-päihdekasvatusta)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="0">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="B4" t="inlineStr" s="0">
         <is>
-          <t>Suomen Punainen Risti (STEA 2026: 3,03 M€ kohdennettua Ak-avustusta Nuorten turvataloihin ja Vapepa-valmiuteen + 0,52 M€ C-hankkeita)</t>
+          <t>Suomen Punainen Risti (STEA 2026: 3,03 M€ kohdennettua Ak-avustusta Nuorten turvataloihin ja Vapepa-valmiuteen + 0,35 M€ Ay 1 + 0,17 M€ C-hanke)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="0">
@@ -3492,14 +3492,14 @@
       </c>
       <c r="E4" t="inlineStr" s="0">
         <is>
-          <t>Ak/C</t>
+          <t>Ak/Ay/C</t>
         </is>
       </c>
       <c r="F4" s="2">
         <v>3547809.0</v>
       </c>
       <c r="G4" s="2">
-        <v>14.5</v>
+        <v>9.8</v>
       </c>
       <c r="H4" s="2">
         <v>38000000.0</v>
@@ -3511,11 +3511,11 @@
       </c>
       <c r="J4" t="inlineStr" s="0">
         <is>
-          <t>STEA 2026: 0 € Ay-yleisavustusta; 3,03 M€ kohdennettua Ak-kenttätyötä (Nuorten turvatalot, Vapepa) + julkiset palvelusopimukset</t>
+          <t>STEA 2026: Ay 1 yleisavustus vain 349 440 € (9,8 %); 3,03 M€ kohdennettua Ak-kenttätyötä (Nuorten turvatalot, Vapepa) + 165 750 € C-hanke</t>
         </is>
       </c>
       <c r="K4" s="2">
-        <v>515190.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="5">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="B7" t="inlineStr" s="0">
         <is>
-          <t>A-klinikkasäätiö sr (STEA 2026: 0,91 M€ Ay/C-avustusta + 1,96 M€ kohdennettua Ak-päihdetyötä; konsernilla myös sote-palvelumyyntiä)</t>
+          <t>A-klinikkasäätiö sr (STEA 2026: 0,91 M€ Ay-yleisavustusta + 1,96 M€ kohdennettua Ak-päihdetyötä; konsernilla myös sote-palvelumyyntiä)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="0">
@@ -3956,7 +3956,7 @@
         </is>
       </c>
       <c r="K13" s="2">
-        <v>240000.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="14">
@@ -4118,24 +4118,24 @@
       </c>
       <c r="B2" t="inlineStr" s="0">
         <is>
-          <t>Spinnova Oyj (IFRS/KPL: Liiketoiminnan muiden tuottojen avustuserät ja T&amp;K-aktivoinnit vs. omavarainen käyttökate)</t>
+          <t>Spinnova Oyj (Tilinpäätös 2024 IFRS: Liiketoiminnan muut tuotot / avustukset ja T&amp;K-aktivoinnit vs. omavarainen käyttökate)</t>
         </is>
       </c>
       <c r="C2" s="2">
-        <v>7600000.0</v>
+        <v>762000.0</v>
       </c>
       <c r="D2" s="2">
-        <v>-8400000.0</v>
+        <v>-15600000.0</v>
       </c>
       <c r="E2" s="2">
         <v>5050000.0</v>
       </c>
       <c r="F2" s="2">
-        <v>-13450000.0</v>
+        <v>-20650000.0</v>
       </c>
       <c r="G2" t="inlineStr" s="0">
         <is>
-          <t>CRITICAL_GRANT_ZOMBIE_DO_NOT_BUY</t>
+          <t>Negatiivinen käyttökate ennen julkisia avustuksia (IAS 20 / KPL)</t>
         </is>
       </c>
     </row>
@@ -4147,24 +4147,24 @@
       </c>
       <c r="B3" t="inlineStr" s="0">
         <is>
-          <t>Infinited Fiber Company Oy (KPL: Julkisten T&amp;K-avustusten ja kehittämisaktivointien osuus ennen pilottituotannon sopeutusta)</t>
+          <t>Infinited Fiber Company Oy (Tilinpäätös 2024 KPL: Julkisten T&amp;K-avustusten ja kehittämisaktivointien oikaisu)</t>
         </is>
       </c>
       <c r="C3" s="2">
-        <v>4200000.0</v>
+        <v>186000.0</v>
       </c>
       <c r="D3" s="2">
-        <v>-6500000.0</v>
+        <v>-7100000.0</v>
       </c>
       <c r="E3" s="2">
         <v>6500000.0</v>
       </c>
       <c r="F3" s="2">
-        <v>-13000000.0</v>
+        <v>-13600000.0</v>
       </c>
       <c r="G3" t="inlineStr" s="0">
         <is>
-          <t>CRITICAL_GRANT_ZOMBIE_DO_NOT_BUY</t>
+          <t>Negatiivinen käyttökate ennen julkisia avustuksia (IAS 20 / KPL)</t>
         </is>
       </c>
     </row>
@@ -4176,24 +4176,24 @@
       </c>
       <c r="B4" t="inlineStr" s="0">
         <is>
-          <t>Solar Foods Oyj (IFRS/KPL: Liiketoiminnan muihin tuottoihin kirjatut julkiset IPCEI/BF-kehittämisavustukset)</t>
+          <t>Solar Foods Oyj (Tilinpäätös 2024–2025: Liiketoiminnan muihin tuottoihin kirjatut julkiset IPCEI/BF-kehittämisavustukset)</t>
         </is>
       </c>
       <c r="C4" s="2">
-        <v>2100000.0</v>
+        <v>124000.0</v>
       </c>
       <c r="D4" s="2">
-        <v>-5900000.0</v>
+        <v>-8900000.0</v>
       </c>
       <c r="E4" s="2">
-        <v>6500000.0</v>
+        <v>10000000.0</v>
       </c>
       <c r="F4" s="2">
-        <v>-12400000.0</v>
+        <v>-18900000.0</v>
       </c>
       <c r="G4" t="inlineStr" s="0">
         <is>
-          <t>CRITICAL_GRANT_ZOMBIE_DO_NOT_BUY</t>
+          <t>Negatiivinen käyttökate ennen julkisia avustuksia (IAS 20 / KPL)</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="G5" t="inlineStr" s="0">
         <is>
-          <t>CLEAN_ORGANIC_EARNINGS</t>
+          <t>Vahva operatiivinen kassavirta-EBITDA (avustusosuus &lt;1 %)</t>
         </is>
       </c>
     </row>

--- a/dist/VM_Tukipalkkio_Leikkuri_2027.xlsx
+++ b/dist/VM_Tukipalkkio_Leikkuri_2027.xlsx
@@ -4200,7 +4200,7 @@
     <row r="5">
       <c r="A5" t="inlineStr" s="0">
         <is>
-          <t>2804523-7</t>
+          <t>2800638-3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="0">
@@ -4316,7 +4316,7 @@
     <row r="9">
       <c r="A9" t="inlineStr" s="0">
         <is>
-          <t>2617450-6</t>
+          <t>2612169-5</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="0">
